--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>76618</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>4.92000007629395</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>69953</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>4.96999979019165</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>52674</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>47462</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>4.99499988555908</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>24197</v>
+        <v>16739</v>
       </c>
       <c r="C2715" t="n">
-        <v>5.34000015258789</v>
+        <v>5.28000020980835</v>
       </c>
       <c r="D2715" t="n">
-        <v>5.19999980926514</v>
+        <v>5.21000003814697</v>
       </c>
       <c r="E2715" t="n">
-        <v>5.34000015258789</v>
+        <v>5.21000003814697</v>
       </c>
       <c r="F2715" t="n">
-        <v>5.21000003814697</v>
+        <v>5.26999998092651</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>38762</v>
+        <v>24197</v>
       </c>
       <c r="C2716" t="n">
-        <v>5.25</v>
+        <v>5.34000015258789</v>
       </c>
       <c r="D2716" t="n">
-        <v>5.1399998664856</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="E2716" t="n">
-        <v>5.21999979019165</v>
+        <v>5.34000015258789</v>
       </c>
       <c r="F2716" t="n">
-        <v>5.1399998664856</v>
+        <v>5.21000003814697</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>28838</v>
+        <v>38762</v>
       </c>
       <c r="C2717" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="E2717" t="n">
         <v>5.21999979019165</v>
       </c>
-      <c r="D2717" t="n">
-        <v>5.1100001335144</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>5.15000009536743</v>
-      </c>
       <c r="F2717" t="n">
-        <v>5.1100001335144</v>
+        <v>5.1399998664856</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>107534</v>
+        <v>28838</v>
       </c>
       <c r="C2718" t="n">
-        <v>5.13000011444092</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="D2718" t="n">
-        <v>4.96000003814697</v>
+        <v>5.1100001335144</v>
       </c>
       <c r="E2718" t="n">
+        <v>5.15000009536743</v>
+      </c>
+      <c r="F2718" t="n">
         <v>5.1100001335144</v>
-      </c>
-      <c r="F2718" t="n">
-        <v>5.03000020980835</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>76618</v>
+        <v>107534</v>
       </c>
       <c r="C2719" t="n">
-        <v>5.03999996185303</v>
+        <v>5.13000011444092</v>
       </c>
       <c r="D2719" t="n">
-        <v>4.92000007629395</v>
+        <v>4.96000003814697</v>
       </c>
       <c r="E2719" t="n">
-        <v>5.03999996185303</v>
+        <v>5.1100001335144</v>
       </c>
       <c r="F2719" t="n">
-        <v>5.01999998092651</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>69953</v>
+        <v>76618</v>
       </c>
       <c r="C2720" t="n">
-        <v>5.1100001335144</v>
+        <v>5.03999996185303</v>
       </c>
       <c r="D2720" t="n">
-        <v>4.96000003814697</v>
+        <v>4.92000007629395</v>
       </c>
       <c r="E2720" t="n">
-        <v>4.98000001907349</v>
+        <v>5.03999996185303</v>
       </c>
       <c r="F2720" t="n">
-        <v>4.96999979019165</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>52674</v>
+        <v>69953</v>
       </c>
       <c r="C2721" t="n">
-        <v>5.09000015258789</v>
+        <v>5.1100001335144</v>
       </c>
       <c r="D2721" t="n">
-        <v>4.98000001907349</v>
+        <v>4.96000003814697</v>
       </c>
       <c r="E2721" t="n">
         <v>4.98000001907349</v>
       </c>
       <c r="F2721" t="n">
-        <v>5.01999998092651</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>47462</v>
+        <v>52674</v>
       </c>
       <c r="C2722" t="n">
-        <v>5.07000017166138</v>
+        <v>5.09000015258789</v>
       </c>
       <c r="D2722" t="n">
-        <v>5</v>
+        <v>4.98000001907349</v>
       </c>
       <c r="E2722" t="n">
-        <v>5.05000019073486</v>
+        <v>4.98000001907349</v>
       </c>
       <c r="F2722" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>117834</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>4.90500020980835</v>
+      </c>
+      <c r="E2723" t="n">
         <v>4.99499988555908</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>4.90500020980835</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -525,7 +525,7 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12.397403717041</v>
+        <v>12.3974046707153</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>9.79822444915771</v>
+        <v>9.7982234954834</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3539705276489</v>
+        <v>10.3539695739746</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G14" t="n">
-        <v>9.84952354431152</v>
+        <v>9.84952449798584</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>12.25</v>
       </c>
       <c r="G15" t="n">
-        <v>10.4736680984497</v>
+        <v>10.473669052124</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941207885742</v>
+        <v>10.2941217422485</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G17" t="n">
-        <v>10.7814674377441</v>
+        <v>10.7814655303955</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156671524048</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G20" t="n">
-        <v>10.576268196106</v>
+        <v>10.5762672424316</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156671524048</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1915216445923</v>
+        <v>10.1915197372437</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4565696716309</v>
+        <v>10.4565677642822</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907684326172</v>
+        <v>10.4907703399658</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.037278175354</v>
+        <v>9.03727912902832</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743034362793</v>
+        <v>8.97743129730225</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842891693115</v>
+        <v>9.14842987060547</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057727813721</v>
+        <v>9.43057632446289</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082359313965</v>
+        <v>9.90082454681396</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142654418945</v>
+        <v>9.66142559051514</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G34" t="n">
-        <v>10.4394693374634</v>
+        <v>10.4394683837891</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>10.2000713348389</v>
+        <v>10.2000722885132</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0037641525269</v>
+        <v>11.0037660598755</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506191253662</v>
+        <v>10.5506181716919</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257213592529</v>
+        <v>10.2257204055786</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G40" t="n">
-        <v>10.1829710006714</v>
+        <v>10.1829719543457</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0379657745361</v>
+        <v>11.0379648208618</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097156524658</v>
+        <v>10.9097166061401</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8074598312378</v>
+        <v>11.8074588775635</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442596435547</v>
+        <v>11.9442577362061</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G45" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732591629028</v>
+        <v>11.7732582092285</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>14</v>
       </c>
       <c r="G47" t="n">
-        <v>11.9699077606201</v>
+        <v>11.9699068069458</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.6279096603394</v>
+        <v>11.6279106140137</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>11.3714113235474</v>
+        <v>11.3714122772217</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3799619674683</v>
+        <v>11.3799629211426</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6621103286743</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416604995728</v>
+        <v>11.8416585922241</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.918607711792</v>
+        <v>11.9186086654663</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>12.046856880188</v>
+        <v>12.0468587875366</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922073364258</v>
+        <v>12.1922054290771</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665563583374</v>
+        <v>12.1665554046631</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178564071655</v>
+        <v>12.2178554534912</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5680618286133</v>
+        <v>11.568060874939</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.2859125137329</v>
+        <v>11.2859134674072</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G69" t="n">
-        <v>11.7390584945679</v>
+        <v>11.7390594482422</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5680618286133</v>
+        <v>11.568060874939</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6621103286743</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048578262329</v>
+        <v>11.7048597335815</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.6621103286743</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G78" t="n">
-        <v>11.4740114212036</v>
+        <v>11.4740123748779</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918630599976</v>
+        <v>11.1918649673462</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.1149129867554</v>
+        <v>11.1149139404297</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3799619674683</v>
+        <v>11.3799629211426</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3201122283936</v>
+        <v>11.3201112747192</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0550651550293</v>
+        <v>11.0550661087036</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.9866647720337</v>
+        <v>10.9866676330566</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1405649185181</v>
+        <v>11.1405630111694</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>10.6019172668457</v>
+        <v>10.6019191741943</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>10.954140663147</v>
+        <v>10.9541425704956</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.4346113204956</v>
+        <v>10.4346122741699</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G92" t="n">
-        <v>10.3553628921509</v>
+        <v>10.3553609848022</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>10.4346113204956</v>
+        <v>10.4346122741699</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G94" t="n">
-        <v>10.2232780456543</v>
+        <v>10.22327709198</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G95" t="n">
-        <v>10.2673063278198</v>
+        <v>10.2673053741455</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G97" t="n">
-        <v>10.3201398849487</v>
+        <v>10.3201379776001</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.003137588501</v>
+        <v>10.0031385421753</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3025283813477</v>
+        <v>10.3025274276733</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496938705444</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120311737061</v>
+        <v>11.4120321273804</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>11.2359199523926</v>
+        <v>11.2359209060669</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G113" t="n">
-        <v>10.8132514953613</v>
+        <v>10.813250541687</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G114" t="n">
-        <v>10.5138607025146</v>
+        <v>10.513861656189</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647764205933</v>
+        <v>10.0647773742676</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.99433422088623</v>
+        <v>9.9943323135376</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.0383596420288</v>
+        <v>10.0383605957031</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962520599365</v>
+        <v>10.4962491989136</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522218704224</v>
+        <v>10.452223777771</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843067169189</v>
+        <v>10.5843076705933</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G124" t="n">
-        <v>9.87986183166504</v>
+        <v>9.87986087799072</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G125" t="n">
-        <v>9.12258052825928</v>
+        <v>9.12257957458496</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733001708984</v>
+        <v>9.67733097076416</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>9.93269443511963</v>
+        <v>9.93269348144531</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.18422031402588</v>
+        <v>9.18421936035156</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019203186035</v>
+        <v>9.14019107818604</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G137" t="n">
-        <v>10.3201398849487</v>
+        <v>10.3201379776001</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>10.2849178314209</v>
+        <v>10.2849168777466</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1352233886719</v>
+        <v>10.1352224349976</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>10.2144746780396</v>
+        <v>10.2144727706909</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.15283203125</v>
+        <v>10.1528329849243</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496938705444</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496938705444</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G144" t="n">
-        <v>10.2673063278198</v>
+        <v>10.2673053741455</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.3025283813477</v>
+        <v>10.3025274276733</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987800598145</v>
+        <v>10.6987791061401</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>11.0333919525146</v>
+        <v>11.0333909988403</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>11.0333919525146</v>
+        <v>11.0333909988403</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893636703491</v>
+        <v>10.9893627166748</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748903274536</v>
+        <v>10.8748922348022</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748903274536</v>
+        <v>10.8748922348022</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G157" t="n">
-        <v>11.253529548645</v>
+        <v>11.2535305023193</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>11.3151702880859</v>
+        <v>11.3151721954346</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>11.253529548645</v>
+        <v>11.2535305023193</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7251968383789</v>
+        <v>10.7251958847046</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>11.0510015487671</v>
+        <v>11.0510025024414</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G165" t="n">
-        <v>11.0598087310791</v>
+        <v>11.0598096847534</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G167" t="n">
-        <v>11.1214475631714</v>
+        <v>11.1214466094971</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>11.183084487915</v>
+        <v>11.1830863952637</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>11.5265045166016</v>
+        <v>11.5265054702759</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G175" t="n">
-        <v>11.685004234314</v>
+        <v>11.6850061416626</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.7994775772095</v>
+        <v>11.7994766235352</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G177" t="n">
-        <v>11.6497802734375</v>
+        <v>11.6497812271118</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>13.25</v>
       </c>
       <c r="G178" t="n">
-        <v>11.6673927307129</v>
+        <v>11.6673946380615</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>11.6497802734375</v>
+        <v>11.6497812271118</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472522735596</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680038452148</v>
+        <v>11.3680047988892</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472522735596</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.0636425018311</v>
+        <v>12.0636444091797</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303392410278</v>
+        <v>12.5303382873535</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070615768433</v>
+        <v>12.4070625305176</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837839126587</v>
+        <v>12.2837829589844</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>12.9177856445312</v>
+        <v>12.9177865982056</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8121185302734</v>
+        <v>12.8121194839478</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782032012939</v>
+        <v>13.5782041549683</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>14.3707046508789</v>
+        <v>14.3707056045532</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210111618042</v>
+        <v>14.2210121154785</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G206" t="n">
-        <v>14.2562351226807</v>
+        <v>14.2562341690063</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.1329536437988</v>
+        <v>14.1329555511475</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241512298584</v>
+        <v>14.1241502761841</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9216213226318</v>
+        <v>13.9216203689575</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>13.7807321548462</v>
+        <v>13.7807312011719</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>13.6046199798584</v>
+        <v>13.6046209335327</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631216049194</v>
+        <v>13.7631196975708</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G214" t="n">
-        <v>13.8335666656494</v>
+        <v>13.8335647583008</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7278995513916</v>
+        <v>13.727897644043</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486482620239</v>
+        <v>13.6486492156982</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605926513672</v>
+        <v>13.5605936050415</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>13.736704826355</v>
+        <v>13.7367038726807</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>14.1769847869873</v>
+        <v>14.176983833313</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>14.0977334976196</v>
+        <v>14.0977325439453</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G226" t="n">
-        <v>14.7845687866211</v>
+        <v>14.7845697402954</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040971755981</v>
+        <v>15.3040962219238</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.2776823043823</v>
+        <v>15.2776803970337</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G229" t="n">
-        <v>15.4890155792236</v>
+        <v>15.489013671875</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978199005127</v>
+        <v>15.497820854187</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657341003418</v>
+        <v>15.3657369613647</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3393201828003</v>
+        <v>15.3393211364746</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G235" t="n">
-        <v>15.6651277542114</v>
+        <v>15.6651258468628</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418453216553</v>
+        <v>15.5418472290039</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>15.2424583435059</v>
+        <v>15.2424573898315</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.2776823043823</v>
+        <v>15.2776803970337</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>15.8060159683228</v>
+        <v>15.8060140609741</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G240" t="n">
-        <v>16.1934585571289</v>
+        <v>16.1934604644775</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G241" t="n">
-        <v>16.369571685791</v>
+        <v>16.3695755004883</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.4664344787598</v>
+        <v>16.4664325714111</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.5104598999023</v>
+        <v>16.5104637145996</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.5104598999023</v>
+        <v>16.5104637145996</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.889102935791</v>
+        <v>16.8890991210938</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G247" t="n">
-        <v>17.1532669067383</v>
+        <v>17.1532707214355</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>16.7746295928955</v>
+        <v>16.7746276855469</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>16.5544891357422</v>
+        <v>16.5544872283936</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G251" t="n">
-        <v>16.5897121429443</v>
+        <v>16.5897102355957</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G252" t="n">
-        <v>16.6513519287109</v>
+        <v>16.6513500213623</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>16.5720996856689</v>
+        <v>16.5720977783203</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947662353516</v>
+        <v>16.9947700500488</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G255" t="n">
-        <v>16.7041854858398</v>
+        <v>16.7041835784912</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.8802967071533</v>
+        <v>16.8802947998047</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538818359375</v>
+        <v>16.8538780212402</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>17.1532669067383</v>
+        <v>17.1532707214355</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G260" t="n">
-        <v>17.2941589355469</v>
+        <v>17.2941570281982</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G261" t="n">
-        <v>17.1268501281738</v>
+        <v>17.1268520355225</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G263" t="n">
-        <v>16.5368804931641</v>
+        <v>16.5368766784668</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>17.0828247070312</v>
+        <v>17.0828227996826</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>17.2061042785645</v>
+        <v>17.2061023712158</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>17.3469924926758</v>
+        <v>17.3469944000244</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551856994629</v>
+        <v>17.6551876068115</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>17.540714263916</v>
+        <v>17.5407123565674</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G270" t="n">
-        <v>17.5054912567139</v>
+        <v>17.5054931640625</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G272" t="n">
-        <v>17.4526596069336</v>
+        <v>17.452657699585</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432422637939</v>
+        <v>17.7432403564453</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>17.8401031494141</v>
+        <v>17.8401050567627</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G276" t="n">
-        <v>17.5054912567139</v>
+        <v>17.5054931640625</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482147216797</v>
+        <v>16.7482089996338</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G282" t="n">
-        <v>17.2765483856201</v>
+        <v>17.2765464782715</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.889102935791</v>
+        <v>16.8890991210938</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G287" t="n">
-        <v>16.8186588287354</v>
+        <v>16.8186550140381</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>17.0828247070312</v>
+        <v>17.0828227996826</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>17.2853527069092</v>
+        <v>17.2853507995605</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.391019821167</v>
+        <v>17.3910179138184</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G295" t="n">
-        <v>17.2853527069092</v>
+        <v>17.2853507995605</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350471496582</v>
+        <v>17.4350452423096</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734092712402</v>
+        <v>17.3734073638916</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>17.9457702636719</v>
+        <v>17.9457721710205</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G302" t="n">
-        <v>19.9358310699463</v>
+        <v>19.9358329772949</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8340015411377</v>
+        <v>20.8339996337891</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>21.0893650054932</v>
+        <v>21.0893630981445</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>21.327112197876</v>
+        <v>21.3271141052246</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G311" t="n">
-        <v>21.6529216766357</v>
+        <v>21.6529197692871</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497806549072</v>
+        <v>21.7497844696045</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>21.917085647583</v>
+        <v>21.9170875549316</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>21.8114204406738</v>
+        <v>21.8114185333252</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.2869243621826</v>
+        <v>22.2869205474854</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605075836182</v>
+        <v>22.2605056762695</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G318" t="n">
-        <v>22.348560333252</v>
+        <v>22.3485584259033</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>22.6303405761719</v>
+        <v>22.6303443908691</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743659973145</v>
+        <v>22.6743679046631</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945045471191</v>
+        <v>22.8945083618164</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G329" t="n">
-        <v>23.0970344543457</v>
+        <v>23.0970363616943</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>22.3749771118164</v>
+        <v>22.374979019165</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G333" t="n">
-        <v>23.1938953399658</v>
+        <v>23.1938991546631</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>23.5108966827393</v>
+        <v>23.5108985900879</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>23.9159526824951</v>
+        <v>23.9159545898438</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417621612549</v>
+        <v>24.2417583465576</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.9197864532471</v>
+        <v>24.9197902679443</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870971679688</v>
+        <v>25.0870952606201</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>28.2700004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>24.8933715820312</v>
+        <v>24.8933753967285</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255447387695</v>
+        <v>26.4255485534668</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G345" t="n">
-        <v>26.4879341125488</v>
+        <v>26.4879322052002</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G346" t="n">
-        <v>27.3970050811768</v>
+        <v>27.397008895874</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>28.1545715332031</v>
+        <v>28.1545696258545</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>29.3666667938232</v>
+        <v>29.3666687011719</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>33.0900001525879</v>
       </c>
       <c r="G355" t="n">
-        <v>29.4914417266846</v>
+        <v>29.4914474487305</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>29.767728805542</v>
+        <v>29.7677345275879</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>34.5299987792969</v>
       </c>
       <c r="G359" t="n">
-        <v>30.774845123291</v>
+        <v>30.7748432159424</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400951385498</v>
+        <v>30.2400913238525</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283233642578</v>
+        <v>30.8283195495605</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154781341553</v>
+        <v>31.0154800415039</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.997652053833</v>
+        <v>30.9976577758789</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G367" t="n">
-        <v>30.6500663757324</v>
+        <v>30.6500682830811</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.7481060028076</v>
+        <v>30.7481079101562</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857166290283</v>
+        <v>30.685718536377</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G370" t="n">
-        <v>29.357759475708</v>
+        <v>29.3577556610107</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>29.5003509521484</v>
+        <v>29.5003528594971</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G376" t="n">
-        <v>29.9994564056396</v>
+        <v>29.999454498291</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G378" t="n">
-        <v>30.0529289245605</v>
+        <v>30.0529346466064</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.4825286865234</v>
+        <v>29.4825344085693</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G381" t="n">
-        <v>28.9121341705322</v>
+        <v>28.912130355835</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.126033782959</v>
+        <v>29.1260318756104</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>31.0699996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>27.6911201477051</v>
+        <v>27.6911182403564</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>27.4861316680908</v>
+        <v>27.4861335754395</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>31.8099994659424</v>
       </c>
       <c r="G390" t="n">
-        <v>28.3506412506104</v>
+        <v>28.350643157959</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178592681885</v>
+        <v>27.7178554534912</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855529785156</v>
+        <v>29.7855567932129</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>32.9099998474121</v>
       </c>
       <c r="G399" t="n">
-        <v>29.3310222625732</v>
+        <v>29.3310203552246</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.170597076416</v>
+        <v>29.1705932617188</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>29.2329788208008</v>
+        <v>29.2329807281494</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221092224121</v>
+        <v>29.3221073150635</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>32.5</v>
       </c>
       <c r="G404" t="n">
-        <v>28.9656066894531</v>
+        <v>28.9656047821045</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>32.2099990844727</v>
       </c>
       <c r="G405" t="n">
-        <v>28.707145690918</v>
+        <v>28.7071437835693</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>32.5</v>
       </c>
       <c r="G406" t="n">
-        <v>28.9656066894531</v>
+        <v>28.9656047821045</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G407" t="n">
-        <v>28.9923419952393</v>
+        <v>28.9923439025879</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477787017822</v>
+        <v>28.9477825164795</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>29.767728805542</v>
+        <v>29.7677345275879</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>33.5</v>
       </c>
       <c r="G411" t="n">
-        <v>29.8568534851074</v>
+        <v>29.8568572998047</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>32.9900016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>29.4023189544678</v>
+        <v>29.4023208618164</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G414" t="n">
-        <v>28.814094543457</v>
+        <v>28.8140926361084</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>29.6162166595459</v>
+        <v>29.6162204742432</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964302062988</v>
+        <v>29.6964321136475</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>30.1420555114746</v>
+        <v>30.142053604126</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>33.8699989318848</v>
       </c>
       <c r="G422" t="n">
-        <v>30.1866188049316</v>
+        <v>30.1866207122803</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G425" t="n">
-        <v>29.1795101165771</v>
+        <v>29.1795043945312</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648662567139</v>
+        <v>30.3648700714111</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G431" t="n">
-        <v>30.2935695648193</v>
+        <v>30.2935676574707</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.0618419647217</v>
+        <v>30.0618457794189</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.23118019104</v>
+        <v>30.2311763763428</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>31.496753692627</v>
+        <v>31.4967517852783</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G438" t="n">
-        <v>30.8194103240967</v>
+        <v>30.819408416748</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>31.9958553314209</v>
+        <v>31.9958515167236</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928310394287</v>
+        <v>31.6928272247314</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>36.1100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>32.1830215454102</v>
+        <v>32.1830177307129</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>35.9900016784668</v>
       </c>
       <c r="G444" t="n">
-        <v>32.0760726928711</v>
+        <v>32.0760688781738</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.9512882232666</v>
+        <v>31.9512920379639</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990432739258</v>
+        <v>33.1990394592285</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>37.4700012207031</v>
       </c>
       <c r="G448" t="n">
-        <v>33.3951187133789</v>
+        <v>33.3951148986816</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>39</v>
       </c>
       <c r="G449" t="n">
-        <v>34.7587280273438</v>
+        <v>34.7587242126465</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>34.6963386535645</v>
+        <v>34.6963424682617</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.7319946289062</v>
+        <v>34.7319869995117</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>34.5804786682129</v>
+        <v>34.5804748535156</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>34.5804786682129</v>
+        <v>34.5804748535156</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>39.5200004577637</v>
       </c>
       <c r="G459" t="n">
-        <v>35.2221794128418</v>
+        <v>35.2221755981445</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G464" t="n">
-        <v>34.1437644958496</v>
+        <v>34.1437683105469</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>38.2200012207031</v>
       </c>
       <c r="G467" t="n">
-        <v>34.0635566711426</v>
+        <v>34.0635528564453</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G470" t="n">
-        <v>34.1170310974121</v>
+        <v>34.1170234680176</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G472" t="n">
-        <v>34.1170310974121</v>
+        <v>34.1170234680176</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>38.8400001525879</v>
       </c>
       <c r="G474" t="n">
-        <v>34.6161308288574</v>
+        <v>34.6161270141602</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041954040527</v>
+        <v>34.3041915893555</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081161499023</v>
+        <v>34.1081123352051</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8425369262695</v>
+        <v>32.8425407409668</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>39.3899993896484</v>
       </c>
       <c r="G479" t="n">
-        <v>35.1063194274902</v>
+        <v>35.106315612793</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>36.4966659545898</v>
+        <v>36.4966621398926</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G484" t="n">
-        <v>37.4146499633789</v>
+        <v>37.4146537780762</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>43.6699981689453</v>
       </c>
       <c r="G486" t="n">
-        <v>38.9208564758301</v>
+        <v>38.9208641052246</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>43.2900009155273</v>
       </c>
       <c r="G488" t="n">
-        <v>38.5821914672852</v>
+        <v>38.5821876525879</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.8050003051758</v>
+        <v>38.805004119873</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G493" t="n">
-        <v>37.8067970275879</v>
+        <v>37.8068008422852</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>43.0299987792969</v>
       </c>
       <c r="G494" t="n">
-        <v>38.3504600524902</v>
+        <v>38.3504638671875</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.3415489196777</v>
+        <v>38.341552734375</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>43.2200012207031</v>
       </c>
       <c r="G498" t="n">
-        <v>38.5198020935059</v>
+        <v>38.5198059082031</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>38.5643653869629</v>
+        <v>38.5643615722656</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089248657227</v>
+        <v>38.6089210510254</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.6891403198242</v>
+        <v>38.6891326904297</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>39.0812835693359</v>
+        <v>39.0812873840332</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545501708984</v>
+        <v>39.0545539855957</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>42.9599990844727</v>
       </c>
       <c r="G509" t="n">
-        <v>38.2880783081055</v>
+        <v>38.2880744934082</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G510" t="n">
-        <v>38.3772010803223</v>
+        <v>38.3772048950195</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>47.1199989318848</v>
       </c>
       <c r="G515" t="n">
-        <v>41.9956703186035</v>
+        <v>41.9956741333008</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G516" t="n">
-        <v>42.655200958252</v>
+        <v>42.6551933288574</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>48.0400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>42.8156242370605</v>
+        <v>42.8156204223633</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.4234733581543</v>
+        <v>42.423469543457</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G519" t="n">
-        <v>42.031322479248</v>
+        <v>42.0313186645508</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G520" t="n">
-        <v>42.0847969055176</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G521" t="n">
-        <v>41.9243774414062</v>
+        <v>41.9243698120117</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>41.6213531494141</v>
+        <v>41.6213455200195</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>42.031322479248</v>
+        <v>42.0313186645508</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G525" t="n">
-        <v>42.0847969055176</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G527" t="n">
-        <v>41.9243774414062</v>
+        <v>41.9243698120117</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G528" t="n">
-        <v>41.6926498413086</v>
+        <v>41.6926460266113</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>46.8800010681152</v>
       </c>
       <c r="G530" t="n">
-        <v>41.7817764282227</v>
+        <v>41.7817687988281</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G531" t="n">
-        <v>41.3539772033691</v>
+        <v>41.3539733886719</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>40.819221496582</v>
+        <v>40.8192253112793</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G535" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784286499023</v>
+        <v>39.6784248352051</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>48</v>
       </c>
       <c r="G538" t="n">
-        <v>42.7799682617188</v>
+        <v>42.779972076416</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G539" t="n">
-        <v>41.4787483215332</v>
+        <v>41.4787445068359</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>38.680233001709</v>
+        <v>38.6802291870117</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>42.1599998474121</v>
       </c>
       <c r="G541" t="n">
-        <v>37.5750732421875</v>
+        <v>37.5750770568848</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>41.8400001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>37.2898826599121</v>
+        <v>37.2898788452148</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>45</v>
       </c>
       <c r="G546" t="n">
-        <v>40.1062240600586</v>
+        <v>40.1062278747559</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>45.5200004577637</v>
       </c>
       <c r="G547" t="n">
-        <v>40.5696754455566</v>
+        <v>40.5696716308594</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>45.939998626709</v>
       </c>
       <c r="G549" t="n">
-        <v>40.9440002441406</v>
+        <v>40.9439964294434</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400718688965</v>
+        <v>41.1400756835938</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>46</v>
       </c>
       <c r="G552" t="n">
-        <v>40.9974746704102</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G553" t="n">
-        <v>40.5162010192871</v>
+        <v>40.5161972045898</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>45.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>40.9618186950684</v>
+        <v>40.9618225097656</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131767272949</v>
+        <v>40.2131729125977</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914222717285</v>
+        <v>40.3914260864258</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>46</v>
       </c>
       <c r="G559" t="n">
-        <v>40.9974746704102</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>46.439998626709</v>
       </c>
       <c r="G560" t="n">
-        <v>41.3896217346191</v>
+        <v>41.3896179199219</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>42.6017189025879</v>
+        <v>42.6017227172852</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446472167969</v>
+        <v>44.5446510314941</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G563" t="n">
-        <v>43.9029426574707</v>
+        <v>43.902946472168</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>50.75</v>
       </c>
       <c r="G564" t="n">
-        <v>45.2309074401855</v>
+        <v>45.2309112548828</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G565" t="n">
-        <v>43.8851203918457</v>
+        <v>43.885124206543</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253402709961</v>
+        <v>47.3253440856934</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874061584473</v>
+        <v>45.5874099731445</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494758605957</v>
+        <v>43.8494720458984</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>42.655200958252</v>
+        <v>42.6551933288574</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>41.4787483215332</v>
+        <v>41.4787445068359</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G579" t="n">
-        <v>41.1578979492188</v>
+        <v>41.1578941345215</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>46.0200004577637</v>
       </c>
       <c r="G580" t="n">
-        <v>41.0152969360352</v>
+        <v>41.0152931213379</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675514221191</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G582" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.108024597168</v>
+        <v>39.1080284118652</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479209899902</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7319030761719</v>
+        <v>39.7318992614746</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3040962219238</v>
+        <v>39.3041000366211</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675514221191</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479209899902</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G599" t="n">
-        <v>41.0149269104004</v>
+        <v>41.0149230957031</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>45.2000007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>40.7087097167969</v>
+        <v>40.7087059020996</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G601" t="n">
-        <v>40.6366539001465</v>
+        <v>40.6366577148438</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>45</v>
       </c>
       <c r="G602" t="n">
-        <v>40.5285758972168</v>
+        <v>40.5285835266113</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G604" t="n">
-        <v>37.7366142272949</v>
+        <v>37.7366104125977</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G607" t="n">
-        <v>37.0521278381348</v>
+        <v>37.052131652832</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>40.6399993896484</v>
       </c>
       <c r="G609" t="n">
-        <v>36.6018142700195</v>
+        <v>36.6018104553223</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241325378418</v>
+        <v>34.2241363525391</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G619" t="n">
-        <v>35.1427803039551</v>
+        <v>35.1427841186523</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>38.560001373291</v>
       </c>
       <c r="G620" t="n">
-        <v>34.7284889221191</v>
+        <v>34.7284927368164</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241325378418</v>
+        <v>34.2241363525391</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>37.560001373291</v>
       </c>
       <c r="G625" t="n">
-        <v>33.8278579711914</v>
+        <v>33.8278541564941</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247673034668</v>
+        <v>35.1247711181641</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.4048538208008</v>
+        <v>32.4048500061035</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>32.3868446350098</v>
+        <v>32.3868370056152</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G632" t="n">
-        <v>31.7744045257568</v>
+        <v>31.7744083404541</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5315341949463</v>
+        <v>30.5315322875977</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.4867973327637</v>
+        <v>29.4867935180664</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371128082275</v>
+        <v>29.9371166229248</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346134185791</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.1532649993896</v>
+        <v>30.153263092041</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147434234619</v>
+        <v>29.4147415161133</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>27.8296241760254</v>
+        <v>27.829626083374</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>29.540828704834</v>
+        <v>29.5408325195312</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520351409912</v>
+        <v>31.2520389556885</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054412841797</v>
+        <v>30.4054374694824</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>30.5315341949463</v>
+        <v>30.5315322875977</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.666332244873</v>
+        <v>31.6663284301758</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>31.1079406738281</v>
+        <v>31.1079368591309</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601150512695</v>
+        <v>31.3601169586182</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>30.9818477630615</v>
+        <v>30.9818515777588</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520351409912</v>
+        <v>31.2520389556885</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122913360596</v>
+        <v>31.6122894287109</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G659" t="n">
-        <v>31.7744045257568</v>
+        <v>31.7744083404541</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.901086807251</v>
+        <v>29.9010887145996</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346134185791</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>28.0998153686523</v>
+        <v>28.099817276001</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G670" t="n">
-        <v>26.2805347442627</v>
+        <v>26.2805328369141</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>26.5146999359131</v>
+        <v>26.5146980285645</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G673" t="n">
-        <v>27.2352066040039</v>
+        <v>27.2352046966553</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.0550785064697</v>
+        <v>27.0550804138184</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>27.1091175079346</v>
+        <v>27.1091194152832</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>27.1091175079346</v>
+        <v>27.1091194152832</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>30</v>
       </c>
       <c r="G677" t="n">
-        <v>27.0190544128418</v>
+        <v>27.0190525054932</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>26.7488613128662</v>
+        <v>26.7488651275635</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196910858154</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G681" t="n">
-        <v>27.577449798584</v>
+        <v>27.5774478912354</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>27.8296241760254</v>
+        <v>27.829626083374</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476371765137</v>
+        <v>27.8476390838623</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>27.7936019897461</v>
+        <v>27.7936000823975</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G689" t="n">
-        <v>27.7755889892578</v>
+        <v>27.7755908966064</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G695" t="n">
-        <v>29.1625671386719</v>
+        <v>29.1625690460205</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762237548828</v>
+        <v>28.6762218475342</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.0550785064697</v>
+        <v>27.0550804138184</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196910858154</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196910858154</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.5594348907471</v>
+        <v>27.5594367980957</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>25.7581634521484</v>
+        <v>25.7581653594971</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320289611816</v>
+        <v>22.7320308685303</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233200073242</v>
+        <v>21.7233219146729</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860698699951</v>
+        <v>22.7860679626465</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606155395508</v>
+        <v>23.5606136322021</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>23.2363872528076</v>
+        <v>23.236385345459</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G715" t="n">
-        <v>23.4345264434814</v>
+        <v>23.4345283508301</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G719" t="n">
-        <v>21.3630619049072</v>
+        <v>21.3630638122559</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.3450527191162</v>
+        <v>21.3450546264648</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>19.7239093780518</v>
+        <v>19.7239074707031</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G724" t="n">
-        <v>18.318920135498</v>
+        <v>18.3189182281494</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>18.2828922271729</v>
+        <v>18.2828941345215</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.8773078918457</v>
+        <v>18.877311706543</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>18.3909702301025</v>
+        <v>18.3909683227539</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G730" t="n">
-        <v>18.318920135498</v>
+        <v>18.3189182281494</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120662689209</v>
+        <v>17.1120681762695</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.2024269104004</v>
+        <v>16.2024250030518</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.950249671936</v>
+        <v>15.9502458572388</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800575256348</v>
+        <v>15.6800584793091</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6170129776001</v>
+        <v>15.6170139312744</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>16.490629196167</v>
+        <v>16.4906272888184</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>18.8232727050781</v>
+        <v>18.8232746124268</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968463897705</v>
+        <v>16.7968444824219</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>16.490629196167</v>
+        <v>16.4906272888184</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G752" t="n">
-        <v>16.0132942199707</v>
+        <v>16.0132923126221</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.905216217041</v>
+        <v>15.9052171707153</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G754" t="n">
-        <v>16.2654685974121</v>
+        <v>16.2654705047607</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>16.1934223175049</v>
+        <v>16.1934185028076</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250890731812</v>
+        <v>15.7250881195068</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496110916138</v>
+        <v>15.0496139526367</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800575256348</v>
+        <v>15.6800584793091</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G760" t="n">
-        <v>14.7524042129517</v>
+        <v>14.7524032592773</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639053344727</v>
+        <v>15.463906288147</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>19.75</v>
       </c>
       <c r="G765" t="n">
-        <v>17.7875423431396</v>
+        <v>17.7875442504883</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G767" t="n">
-        <v>17.6434440612793</v>
+        <v>17.6434421539307</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>20</v>
       </c>
       <c r="G769" t="n">
-        <v>18.0127048492432</v>
+        <v>18.0127029418945</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G770" t="n">
-        <v>18.0487270355225</v>
+        <v>18.0487289428711</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>20</v>
       </c>
       <c r="G773" t="n">
-        <v>18.0127048492432</v>
+        <v>18.0127029418945</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>17.9226398468018</v>
+        <v>17.9226379394531</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791725158691</v>
+        <v>18.6791706085205</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G777" t="n">
-        <v>18.8052616119385</v>
+        <v>18.8052635192871</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G782" t="n">
-        <v>18.9493637084961</v>
+        <v>18.9493656158447</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G783" t="n">
-        <v>18.7872505187988</v>
+        <v>18.7872486114502</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>18.3549423217773</v>
+        <v>18.354944229126</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>20</v>
       </c>
       <c r="G786" t="n">
-        <v>18.0127048492432</v>
+        <v>18.0127029418945</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>20</v>
       </c>
       <c r="G787" t="n">
-        <v>18.0127048492432</v>
+        <v>18.0127029418945</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G788" t="n">
-        <v>18.4269962310791</v>
+        <v>18.4269924163818</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>17.3552417755127</v>
+        <v>17.3552398681641</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>18.3009071350098</v>
+        <v>18.3009052276611</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6071224212646</v>
+        <v>18.607120513916</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>19.3996829986572</v>
+        <v>19.3996810913086</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698703765869</v>
+        <v>19.6698722839355</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537200927734</v>
+        <v>19.4537220001221</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G802" t="n">
-        <v>20.2823047637939</v>
+        <v>20.2823028564453</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>18.8232727050781</v>
+        <v>18.8232746124268</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>17.7515182495117</v>
+        <v>17.7515163421631</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>17.7965526580811</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G809" t="n">
-        <v>17.4182834625244</v>
+        <v>17.418285369873</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120662689209</v>
+        <v>17.1120681762695</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490245819092</v>
+        <v>17.0490226745605</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>17.3822574615479</v>
+        <v>17.3822593688965</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2831897735596</v>
+        <v>17.2831878662109</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9766750335693</v>
+        <v>17.976676940918</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.4272880554199</v>
+        <v>17.4272899627686</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G828" t="n">
-        <v>17.9136295318604</v>
+        <v>17.913631439209</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>20</v>
       </c>
       <c r="G829" t="n">
-        <v>18.0127048492432</v>
+        <v>18.0127029418945</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496593475342</v>
+        <v>17.9496555328369</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3822574615479</v>
+        <v>17.3822593688965</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300811767578</v>
+        <v>17.1300792694092</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676723480225</v>
+        <v>17.9676704406738</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667381286621</v>
+        <v>18.0667419433594</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G840" t="n">
-        <v>17.8686008453369</v>
+        <v>17.8685989379883</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>17.7965526580811</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G844" t="n">
-        <v>17.5894050598145</v>
+        <v>17.5894031524658</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G845" t="n">
-        <v>17.7695331573486</v>
+        <v>17.76953125</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G846" t="n">
-        <v>17.8686008453369</v>
+        <v>17.8685989379883</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G849" t="n">
-        <v>17.2434272766113</v>
+        <v>17.24342918396</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G850" t="n">
-        <v>16.6621875762939</v>
+        <v>16.6621913909912</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G851" t="n">
-        <v>17.2249755859375</v>
+        <v>17.2249774932861</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G852" t="n">
-        <v>16.5330257415771</v>
+        <v>16.5330276489258</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>16.1916618347168</v>
+        <v>16.1916599273682</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232385635376</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021240234375</v>
+        <v>13.8021230697632</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G860" t="n">
-        <v>13.894383430481</v>
+        <v>13.8943843841553</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>15</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G862" t="n">
-        <v>13.4792127609253</v>
+        <v>13.4792137145996</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G864" t="n">
-        <v>13.0732679367065</v>
+        <v>13.0732688903809</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G865" t="n">
-        <v>13.0732679367065</v>
+        <v>13.0732688903809</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G866" t="n">
-        <v>13.0179128646851</v>
+        <v>13.0179119110107</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G867" t="n">
-        <v>13.3039197921753</v>
+        <v>13.303918838501</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009473800659</v>
+        <v>13.1009454727173</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G870" t="n">
-        <v>13.1378498077393</v>
+        <v>13.1378507614136</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>13.7006378173828</v>
+        <v>13.7006387710571</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4756240844727</v>
+        <v>14.4756231307983</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>14.4202680587769</v>
+        <v>14.4202661514282</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>14.5771102905273</v>
+        <v>14.577109336853</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>13.7928981781006</v>
+        <v>13.7928991317749</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15</v>
       </c>
       <c r="G880" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.5125274658203</v>
+        <v>14.512526512146</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486215591431</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G889" t="n">
-        <v>10.4161758422852</v>
+        <v>10.4161748886108</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>10.5914697647095</v>
+        <v>10.5914688110352</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.9236068725586</v>
+        <v>10.9236059188843</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837291717529</v>
+        <v>10.6837282180786</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G896" t="n">
-        <v>10.5361127853394</v>
+        <v>10.5361137390137</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762981414795</v>
+        <v>10.1762971878052</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964221954346</v>
+        <v>9.65964126586914</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G906" t="n">
-        <v>10.5730171203613</v>
+        <v>10.573016166687</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>10.5176601409912</v>
+        <v>10.5176610946655</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3054628372192</v>
+        <v>10.3054618835449</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438524246216</v>
+        <v>10.4438533782959</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>10.056360244751</v>
+        <v>10.0563611984253</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486215591431</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G917" t="n">
-        <v>10.1209421157837</v>
+        <v>10.120943069458</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G918" t="n">
-        <v>9.50279998779297</v>
+        <v>9.50279903411865</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G920" t="n">
-        <v>9.5766077041626</v>
+        <v>9.57660675048828</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G921" t="n">
-        <v>9.21218013763428</v>
+        <v>9.21217823028564</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964221954346</v>
+        <v>9.65964126586914</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>8.9861421585083</v>
+        <v>8.98614120483398</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447059631348</v>
+        <v>9.24447154998779</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G933" t="n">
-        <v>9.28137588500977</v>
+        <v>9.28137493133545</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G935" t="n">
-        <v>9.21218013763428</v>
+        <v>9.21217823028564</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G938" t="n">
-        <v>9.99177837371826</v>
+        <v>9.99177742004395</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486215591431</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G942" t="n">
-        <v>10.434627532959</v>
+        <v>10.4346284866333</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>10.5176601409912</v>
+        <v>10.5176610946655</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>10.0840396881104</v>
+        <v>10.0840377807617</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G945" t="n">
-        <v>10.1024904251099</v>
+        <v>10.1024894714355</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G947" t="n">
-        <v>9.61351108551025</v>
+        <v>9.61351203918457</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886615753174</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>9.61351108551025</v>
+        <v>9.61351203918457</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G950" t="n">
-        <v>9.5212516784668</v>
+        <v>9.52125072479248</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886615753174</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>9.5766077041626</v>
+        <v>9.57660675048828</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G958" t="n">
-        <v>9.65041542053223</v>
+        <v>9.65041637420654</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G959" t="n">
-        <v>9.28137588500977</v>
+        <v>9.28137493133545</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G962" t="n">
-        <v>9.81648349761963</v>
+        <v>9.81648445129395</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G966" t="n">
-        <v>9.7519006729126</v>
+        <v>9.75190162658691</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655860900879</v>
+        <v>10.0655851364136</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822429656982</v>
+        <v>10.5822439193726</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G971" t="n">
-        <v>10.7298593521118</v>
+        <v>10.7298603057861</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>10.2870111465454</v>
+        <v>10.2870092391968</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G973" t="n">
-        <v>10.5084362030029</v>
+        <v>10.5084352493286</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G975" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>10.3515939712524</v>
+        <v>10.3515930175781</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337017059326</v>
+        <v>12.2337007522583</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>12.086085319519</v>
+        <v>12.0860843658447</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>12.1875715255737</v>
+        <v>12.1875705718994</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G986" t="n">
-        <v>11.9661464691162</v>
+        <v>11.9661474227905</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>11.7539472579956</v>
+        <v>11.7539482116699</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>11.8277568817139</v>
+        <v>11.8277549743652</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G990" t="n">
-        <v>11.8277568817139</v>
+        <v>11.8277549743652</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G991" t="n">
-        <v>11.7354965209961</v>
+        <v>11.7354955673218</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G992" t="n">
-        <v>12.0676317214966</v>
+        <v>12.0676326751709</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>13.5</v>
       </c>
       <c r="G993" t="n">
-        <v>12.4551258087158</v>
+        <v>12.4551248550415</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G994" t="n">
-        <v>13.2577886581421</v>
+        <v>13.2577877044678</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G995" t="n">
-        <v>13.2485637664795</v>
+        <v>13.2485628128052</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G999" t="n">
-        <v>13.2024335861206</v>
+        <v>13.2024326324463</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.7098636627197</v>
+        <v>13.7098627090454</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283163070679</v>
+        <v>13.7283153533936</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.0143232345581</v>
+        <v>14.0143222808838</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.6821851730347</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.7006378173828</v>
+        <v>13.7006387710571</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.4571704864502</v>
+        <v>14.4571714401245</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.6821851730347</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1020" t="n">
-        <v>13.8482532501221</v>
+        <v>13.8482542037964</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0327739715576</v>
+        <v>14.0327749252319</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.9312896728516</v>
+        <v>13.9312877655029</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6473274230957</v>
+        <v>15.6473264694214</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303619384766</v>
+        <v>15.7303609848022</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.865161895752</v>
+        <v>16.8651638031006</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.9979162216187</v>
+        <v>15.9979152679443</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333362579346</v>
+        <v>15.9333333969116</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720344543457</v>
+        <v>15.4720325469971</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.2044792175293</v>
+        <v>15.204478263855</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.8538904190063</v>
+        <v>14.8538913726807</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.1491222381592</v>
+        <v>15.1491231918335</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506113052368</v>
+        <v>15.2506084442139</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.2044792175293</v>
+        <v>15.204478263855</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.8538904190063</v>
+        <v>14.8538913726807</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>12.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>11.301872253418</v>
+        <v>11.3018732070923</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.97589445114136</v>
+        <v>7.97589349746704</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.89285945892334</v>
+        <v>7.89285898208618</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.55047369003296</v>
+        <v>6.55047273635864</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.91028785705566</v>
+        <v>6.91028738021851</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.01177453994751</v>
+        <v>7.01177406311035</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.47307586669922</v>
+        <v>7.47307538986206</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697937011719</v>
+        <v>8.85697746276855</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.33673000335693</v>
+        <v>9.33673095703125</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.01382064819336</v>
+        <v>9.01382160186768</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.34954738616943</v>
+        <v>8.34954643249512</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.25728702545166</v>
+        <v>8.25728607177734</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.92976331710815</v>
+        <v>7.92976379394531</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675985336304</v>
+        <v>7.78675937652588</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.89285945892334</v>
+        <v>7.89285898208618</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.47307586669922</v>
+        <v>7.47307538986206</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>7.42694520950317</v>
+        <v>7.42694568634033</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.42694520950317</v>
+        <v>7.42694568634033</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.28855514526367</v>
+        <v>7.28855466842651</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.33468437194824</v>
+        <v>7.3346848487854</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.1132607460022</v>
+        <v>7.11326026916504</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.93437576293945</v>
+        <v>7.93437623977661</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.60223960876465</v>
+        <v>7.60223913192749</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1103" t="n">
-        <v>7.14555168151855</v>
+        <v>7.1455512046814</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874002456665</v>
+        <v>6.92874050140381</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533432006836</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533432006836</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.445396900177</v>
+        <v>7.44539737701416</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217750549316</v>
+        <v>7.72217798233032</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.66784477233887</v>
+        <v>8.66784572601318</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310764312744</v>
+        <v>8.90310859680176</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.69090843200684</v>
+        <v>8.69091033935547</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.8754301071167</v>
+        <v>8.87542915344238</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420566558838</v>
+        <v>10.9420576095581</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.82571029663086</v>
+        <v>9.82570934295654</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.82571029663086</v>
+        <v>9.82570934295654</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.74267578125</v>
+        <v>9.74267768859863</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.462306022644</v>
+        <v>10.4623050689697</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5084362030029</v>
+        <v>10.5084352493286</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.194751739502</v>
+        <v>10.1947498321533</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1134" t="n">
-        <v>10.0194549560547</v>
+        <v>10.019455909729</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1136" t="n">
-        <v>10.5361127853394</v>
+        <v>10.5361137390137</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792695999146</v>
+        <v>10.3792715072632</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.5176601409912</v>
+        <v>10.5176610946655</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.360818862915</v>
+        <v>10.3608198165894</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.5361127853394</v>
+        <v>10.5361137390137</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667646408081</v>
+        <v>10.7667636871338</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.4402627944946</v>
+        <v>11.4402637481689</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.5417499542236</v>
+        <v>11.5417490005493</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>11.8093032836914</v>
+        <v>11.8093042373657</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.7078161239624</v>
+        <v>11.7078170776367</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.7539472579956</v>
+        <v>11.7539482116699</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616868972778</v>
+        <v>11.6616888046265</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.5694274902344</v>
+        <v>11.5694284439087</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.3480033874512</v>
+        <v>11.3480043411255</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.2741956710815</v>
+        <v>11.2741947174072</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.1450300216675</v>
+        <v>11.1450309753418</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.7042284011841</v>
+        <v>12.7042274475098</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961782455444</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.2854661941528</v>
+        <v>13.2854671478271</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4423084259033</v>
+        <v>13.4423093795776</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.2577886581421</v>
+        <v>13.2577877044678</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>13.2024335861206</v>
+        <v>13.2024326324463</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.543794631958</v>
+        <v>13.5437955856323</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500490188599</v>
+        <v>13.3500499725342</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>15</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714731216431</v>
+        <v>13.5714740753174</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>13.368501663208</v>
+        <v>13.3685007095337</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>14.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.1470775604248</v>
+        <v>13.1470756530762</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1192" t="n">
-        <v>13.267014503479</v>
+        <v>13.2670154571533</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1195" t="n">
-        <v>13.2024335861206</v>
+        <v>13.2024326324463</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.0455904006958</v>
+        <v>13.0455913543701</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.3315963745117</v>
+        <v>13.331597328186</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.5104818344116</v>
+        <v>12.5104808807373</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.3351879119873</v>
+        <v>12.335186958313</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1208" t="n">
-        <v>13.5068922042847</v>
+        <v>13.5068912506104</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.433084487915</v>
+        <v>13.4330835342407</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.4515361785889</v>
+        <v>13.4515352249146</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1211" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>15.2690591812134</v>
+        <v>15.269061088562</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735197067261</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>15.3613214492798</v>
+        <v>15.3613204956055</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628076553345</v>
+        <v>15.4628057479858</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232385635376</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.5125274658203</v>
+        <v>14.512526512146</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>16</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.7616291046143</v>
+        <v>14.7616300582886</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>14.5955610275269</v>
+        <v>14.5955619812012</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1226" t="n">
-        <v>13.9128360748291</v>
+        <v>13.9128351211548</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1228" t="n">
-        <v>13.8482532501221</v>
+        <v>13.8482542037964</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>13.6545085906982</v>
+        <v>13.6545076370239</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033016204834</v>
+        <v>14.5033025741577</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735197067261</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1235" t="n">
-        <v>15.6750059127808</v>
+        <v>15.6750068664551</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.416675567627</v>
+        <v>15.4166765213013</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G1237" t="n">
-        <v>15.1029949188232</v>
+        <v>15.1029930114746</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184722900391</v>
+        <v>14.9184713363647</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764930725098</v>
+        <v>15.7764911651611</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827445983887</v>
+        <v>15.5827474594116</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547584533691</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410749435425</v>
+        <v>15.8410739898682</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>15.9241094589233</v>
+        <v>15.924108505249</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.1178531646729</v>
+        <v>16.1178550720215</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>15.8502998352051</v>
+        <v>15.8503007888794</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351282119751</v>
+        <v>15.4351272583008</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919713973999</v>
+        <v>15.5919723510742</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517889022827</v>
+        <v>15.9517869949341</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.099401473999</v>
+        <v>16.0994033813477</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>16.0717239379883</v>
+        <v>16.0717258453369</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>16.5145740509033</v>
+        <v>16.5145721435547</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.3910465240479</v>
+        <v>17.3910446166992</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.4648551940918</v>
+        <v>17.4648532867432</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>17.1142635345459</v>
+        <v>17.1142654418945</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1267" t="n">
-        <v>17.5386600494385</v>
+        <v>17.5386619567871</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.4463996887207</v>
+        <v>17.4464015960693</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1270" t="n">
-        <v>17.3725929260254</v>
+        <v>17.372594833374</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.6216983795166</v>
+        <v>17.6216945648193</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.0368671417236</v>
+        <v>18.036865234375</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1279" t="n">
-        <v>19.448450088501</v>
+        <v>19.4484481811523</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>19.1901206970215</v>
+        <v>19.1901187896729</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377323150635</v>
+        <v>19.3377342224121</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1287" t="n">
-        <v>18.5627517700195</v>
+        <v>18.5627498626709</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="n">
-        <v>18.2029361724854</v>
+        <v>18.2029342651367</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="n">
-        <v>17.9722843170166</v>
+        <v>17.972282409668</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.1844825744629</v>
+        <v>18.1844844818115</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.6109256744385</v>
+        <v>20.6109237670898</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="n">
-        <v>20.9430618286133</v>
+        <v>20.9430637359619</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>21.3121032714844</v>
+        <v>21.312105178833</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.1829395294189</v>
+        <v>21.1829376220703</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G1303" t="n">
-        <v>22.290060043335</v>
+        <v>22.2900619506836</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745826721191</v>
+        <v>22.4745845794678</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.5371189117432</v>
+        <v>20.5371170043945</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.6293773651123</v>
+        <v>20.6293792724609</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="n">
-        <v>20.7216377258301</v>
+        <v>20.7216396331787</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>20.6847343444824</v>
+        <v>20.6847362518311</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4633083343506</v>
+        <v>20.4633102416992</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.8728466033936</v>
+        <v>19.8728446960449</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>20.8508014678955</v>
+        <v>20.8508033752441</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.112720489502</v>
+        <v>20.1127223968506</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="n">
-        <v>19.6145153045654</v>
+        <v>19.6145172119141</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.8543910980225</v>
+        <v>19.8543930053711</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1331" t="n">
-        <v>20.8323516845703</v>
+        <v>20.8323497772217</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="n">
-        <v>22.5483913421631</v>
+        <v>22.5483894348145</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.2162532806396</v>
+        <v>22.2162551879883</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="n">
-        <v>22.2531585693359</v>
+        <v>22.2531604766846</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846775054932</v>
+        <v>23.7846755981445</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="n">
-        <v>23.7293186187744</v>
+        <v>23.729320526123</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1343" t="n">
-        <v>24.3935947418213</v>
+        <v>24.3935928344727</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>23.8953876495361</v>
+        <v>23.8953895568848</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1347" t="n">
-        <v>23.3049240112305</v>
+        <v>23.3049221038818</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971862792969</v>
+        <v>23.3971843719482</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.1388549804688</v>
+        <v>23.1388568878174</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="n">
-        <v>22.5852909088135</v>
+        <v>22.5852928161621</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>23.8953876495361</v>
+        <v>23.8953895568848</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662258148193</v>
+        <v>23.7662239074707</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="n">
-        <v>23.7293186187744</v>
+        <v>23.729320526123</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>26.4786758422852</v>
+        <v>26.4786739349365</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935340881348</v>
+        <v>27.4935359954834</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="n">
-        <v>28.1578102111816</v>
+        <v>28.1578121185303</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>28.04709815979</v>
+        <v>28.0470962524414</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="n">
-        <v>28.04709815979</v>
+        <v>28.0470962524414</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721099853516</v>
+        <v>27.2721118927002</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>27.4012756347656</v>
+        <v>27.4012775421143</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="n">
-        <v>26.9030723571777</v>
+        <v>26.9030704498291</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="n">
-        <v>26.497127532959</v>
+        <v>26.4971256256104</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.497127532959</v>
+        <v>26.4971256256104</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="n">
-        <v>25.9989223480225</v>
+        <v>25.9989204406738</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>25.9620132446289</v>
+        <v>25.9620170593262</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>26.6631927490234</v>
+        <v>26.6631946563721</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>25.9989223480225</v>
+        <v>25.9989204406738</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="n">
-        <v>26.5155773162842</v>
+        <v>26.5155754089355</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1403" t="n">
-        <v>26.737003326416</v>
+        <v>26.7370014190674</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G1408" t="n">
-        <v>26.534029006958</v>
+        <v>26.5340309143066</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>25.4269065856934</v>
+        <v>25.426908493042</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>27.5</v>
       </c>
       <c r="G1410" t="n">
-        <v>25.3715534210205</v>
+        <v>25.3715515136719</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="n">
-        <v>26.5155773162842</v>
+        <v>26.5155754089355</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750862121582</v>
+        <v>27.4750843048096</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="n">
-        <v>28.9143409729004</v>
+        <v>28.914342880249</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="n">
-        <v>30.9625205993652</v>
+        <v>30.9625225067139</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>27.0322360992432</v>
+        <v>27.0322341918945</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>26.8846168518066</v>
+        <v>26.8846187591553</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923564910889</v>
+        <v>26.7923583984375</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="n">
-        <v>27.1798496246338</v>
+        <v>27.1798534393311</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>27.5857963562012</v>
+        <v>27.5857982635498</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="n">
-        <v>27.3643703460693</v>
+        <v>27.364372253418</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>27.3090171813965</v>
+        <v>27.3090152740479</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>27.9548377990723</v>
+        <v>27.9548358917236</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.674467086792</v>
+        <v>28.6744651794434</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="n">
-        <v>28.0286464691162</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.8072185516357</v>
+        <v>27.8072204589844</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.3423290252686</v>
+        <v>28.3423309326172</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="n">
-        <v>28.0286464691162</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G1445" t="n">
-        <v>27.6965065002441</v>
+        <v>27.6965084075928</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="n">
-        <v>27.050687789917</v>
+        <v>27.0506858825684</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.8256721496582</v>
+        <v>27.8256702423096</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732875823975</v>
+        <v>27.9732894897461</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="n">
-        <v>27.7887668609619</v>
+        <v>27.7887687683105</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>26.2941551208496</v>
+        <v>26.2941513061523</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="n">
-        <v>26.8846168518066</v>
+        <v>26.8846187591553</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191669464111</v>
+        <v>25.5191688537598</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="n">
-        <v>24.9656047821045</v>
+        <v>24.9656066894531</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.7108669281006</v>
+        <v>23.7108707427979</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="n">
-        <v>23.7293186187744</v>
+        <v>23.729320526123</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="n">
-        <v>23.3418273925781</v>
+        <v>23.3418254852295</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971862792969</v>
+        <v>23.3971843719482</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1469" t="n">
-        <v>23.3049240112305</v>
+        <v>23.3049221038818</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="n">
-        <v>24.2090740203857</v>
+        <v>24.2090721130371</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.2423858642578</v>
+        <v>25.2423877716064</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="n">
-        <v>24.9102516174316</v>
+        <v>24.910249710083</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="n">
-        <v>25.1870307922363</v>
+        <v>25.1870288848877</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>25.1870307922363</v>
+        <v>25.1870288848877</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G1483" t="n">
-        <v>24.6703758239746</v>
+        <v>24.670373916626</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="n">
-        <v>25.537618637085</v>
+        <v>25.5376205444336</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="n">
-        <v>24.9102516174316</v>
+        <v>24.910249710083</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1486" t="n">
-        <v>24.8733463287354</v>
+        <v>24.8733444213867</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="n">
-        <v>23.8769359588623</v>
+        <v>23.8769340515137</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>23.8769359588623</v>
+        <v>23.8769340515137</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>23.1573066711426</v>
+        <v>23.1573047637939</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>21.8656635284424</v>
+        <v>21.865665435791</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841133117676</v>
+        <v>21.8841152191162</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.8508014678955</v>
+        <v>20.8508033752441</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>21.0353202819824</v>
+        <v>21.0353221893311</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="n">
-        <v>20.7031879425049</v>
+        <v>20.7031860351562</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="n">
-        <v>21.4597187042236</v>
+        <v>21.4597206115723</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>21.0353202819824</v>
+        <v>21.0353221893311</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.7031879425049</v>
+        <v>20.7031860351562</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525943756104</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.8323516845703</v>
+        <v>20.8323497772217</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525943756104</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.9948291778564</v>
+        <v>21.9948272705078</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="n">
-        <v>23.1204032897949</v>
+        <v>23.1204013824463</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1529" t="n">
-        <v>22.935884475708</v>
+        <v>22.9358825683594</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674583435059</v>
+        <v>21.3674564361572</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>21.0353202819824</v>
+        <v>21.0353221893311</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877048492432</v>
+        <v>20.8877067565918</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="n">
-        <v>20.7216377258301</v>
+        <v>20.7216396331787</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.3121032714844</v>
+        <v>21.312105178833</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="n">
-        <v>20.5371189117432</v>
+        <v>20.5371170043945</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>20.2049808502197</v>
+        <v>20.2049789428711</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="n">
-        <v>20.5002117156982</v>
+        <v>20.5002136230469</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.7585391998291</v>
+        <v>20.7585430145264</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770496368408</v>
+        <v>17.6770534515381</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.1291275024414</v>
+        <v>18.1291255950928</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.0681343078613</v>
+        <v>17.06813621521</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633670806885</v>
+        <v>17.3633651733398</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033016204834</v>
+        <v>14.5033025741577</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3705472946167</v>
+        <v>15.3705463409424</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.0604524612427</v>
+        <v>14.060453414917</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.337233543396</v>
+        <v>14.3372325897217</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634239196777</v>
+        <v>14.2634248733521</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.6565542221069</v>
+        <v>15.6565532684326</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.4571704864502</v>
+        <v>14.4571714401245</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021240234375</v>
+        <v>13.8021230697632</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.0327739715576</v>
+        <v>14.0327749252319</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.8205757141113</v>
+        <v>13.820574760437</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.8667068481445</v>
+        <v>13.8667058944702</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8482532501221</v>
+        <v>13.8482542037964</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>15</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.6821851730347</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.2854661941528</v>
+        <v>13.2854671478271</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1614" t="n">
-        <v>13.2024335861206</v>
+        <v>13.2024326324463</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.7134532928467</v>
+        <v>12.713454246521</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961782455444</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>14.9461517333984</v>
+        <v>14.9461507797241</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3059644699097</v>
+        <v>15.305965423584</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="n">
-        <v>15.342869758606</v>
+        <v>15.3428678512573</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.9367227554321</v>
+        <v>14.9367218017578</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="n">
-        <v>15.9823894500732</v>
+        <v>15.9823875427246</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>15.5410995483398</v>
+        <v>15.5410985946655</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.7137765884399</v>
+        <v>15.7137775421143</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9823894500732</v>
+        <v>15.9823875427246</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.8576774597168</v>
+        <v>15.8576755523682</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="n">
-        <v>14.5529918670654</v>
+        <v>14.5529909133911</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>13.8430891036987</v>
+        <v>13.843090057373</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.0180683135986</v>
+        <v>13.0180673599243</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="n">
-        <v>12.7590494155884</v>
+        <v>12.7590503692627</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="n">
-        <v>12.4040985107422</v>
+        <v>12.4040994644165</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.780535697937</v>
+        <v>11.7805366516113</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="n">
-        <v>11.5502977371216</v>
+        <v>11.5502986907959</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="n">
-        <v>12.7974233627319</v>
+        <v>12.7974224090576</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="n">
-        <v>12.2026405334473</v>
+        <v>12.2026395797729</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="n">
-        <v>12.8933553695679</v>
+        <v>12.8933544158936</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1666" t="n">
-        <v>13.1715593338013</v>
+        <v>13.1715602874756</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1667" t="n">
-        <v>13.1715593338013</v>
+        <v>13.1715602874756</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>13.1044073104858</v>
+        <v>13.1044082641602</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="n">
-        <v>12.4712505340576</v>
+        <v>12.4712514877319</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1673" t="n">
-        <v>12.7782363891602</v>
+        <v>12.7782354354858</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="n">
-        <v>13.3058662414551</v>
+        <v>13.3058652877808</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="n">
-        <v>12.8933553695679</v>
+        <v>12.8933544158936</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.3154592514038</v>
+        <v>13.3154602050781</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.1044073104858</v>
+        <v>13.1044082641602</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="n">
-        <v>12.4808444976807</v>
+        <v>12.480845451355</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.6055583953857</v>
+        <v>12.6055574417114</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1683" t="n">
-        <v>12.7782363891602</v>
+        <v>12.7782354354858</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="n">
-        <v>12.2793855667114</v>
+        <v>12.2793865203857</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="n">
-        <v>12.2506065368652</v>
+        <v>12.2506055831909</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>11.780535697937</v>
+        <v>11.7805366516113</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="n">
-        <v>12.1546745300293</v>
+        <v>12.154673576355</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1694" t="n">
-        <v>12.3081655502319</v>
+        <v>12.3081665039062</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.1163005828857</v>
+        <v>12.1162996292114</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1697" t="n">
-        <v>11.8476886749268</v>
+        <v>11.8476896286011</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="n">
-        <v>11.4927377700806</v>
+        <v>11.4927368164062</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>12.1354866027832</v>
+        <v>12.1354856491089</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1706" t="n">
-        <v>11.7709436416626</v>
+        <v>11.7709426879883</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1711" t="n">
-        <v>11.3680248260498</v>
+        <v>11.3680257797241</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="n">
-        <v>10.9363269805908</v>
+        <v>10.9363279342651</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.7540559768677</v>
+        <v>10.754056930542</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="n">
-        <v>11.1090068817139</v>
+        <v>11.1090059280396</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.5694847106934</v>
+        <v>11.5694856643677</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>11.5790777206421</v>
+        <v>11.5790767669678</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="n">
-        <v>12.049147605896</v>
+        <v>12.0491485595703</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="n">
-        <v>12.1546745300293</v>
+        <v>12.154673576355</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="n">
-        <v>12.9413213729858</v>
+        <v>12.9413223266602</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="n">
-        <v>13.2003402709961</v>
+        <v>13.2003412246704</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="n">
-        <v>11.6941967010498</v>
+        <v>11.6941957473755</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="n">
-        <v>10.9267358779907</v>
+        <v>10.9267349243164</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.5790777206421</v>
+        <v>11.5790767669678</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="n">
-        <v>11.8956546783447</v>
+        <v>11.895655632019</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="n">
-        <v>11.7229776382446</v>
+        <v>11.7229766845703</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="n">
-        <v>12.2026405334473</v>
+        <v>12.2026395797729</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.2889795303345</v>
+        <v>12.2889804840088</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.2601985931396</v>
+        <v>12.260199546814</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.2506065368652</v>
+        <v>12.2506055831909</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="n">
-        <v>12.4136915206909</v>
+        <v>12.4136905670166</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>12.3273525238037</v>
+        <v>12.327353477478</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1768" t="n">
-        <v>12.3177585601807</v>
+        <v>12.317759513855</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1769" t="n">
-        <v>12.3177585601807</v>
+        <v>12.317759513855</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1772" t="n">
-        <v>12.3177585601807</v>
+        <v>12.317759513855</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>12.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.991587638855</v>
+        <v>11.9915885925293</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="n">
-        <v>12.1163005828857</v>
+        <v>12.1162996292114</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1777" t="n">
-        <v>11.9244356155396</v>
+        <v>11.9244346618652</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1781" t="n">
-        <v>12.3081655502319</v>
+        <v>12.3081665039062</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="n">
-        <v>12.4712505340576</v>
+        <v>12.4712514877319</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.5000305175781</v>
+        <v>12.5000314712524</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1785" t="n">
-        <v>12.8262033462524</v>
+        <v>12.8262023925781</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1787" t="n">
-        <v>13.0852212905884</v>
+        <v>13.0852222442627</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.7663440704346</v>
+        <v>13.7663431167603</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.7855291366577</v>
+        <v>13.7855281829834</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1799" t="n">
-        <v>14.1404809951782</v>
+        <v>14.1404800415039</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1800" t="n">
-        <v>14.1980409622192</v>
+        <v>14.1980400085449</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>15</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.3899059295654</v>
+        <v>14.3899049758911</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>14.313159942627</v>
+        <v>14.3131589889526</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.3323459625244</v>
+        <v>14.3323450088501</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.3515329360962</v>
+        <v>14.3515319824219</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="n">
-        <v>15.9823894500732</v>
+        <v>15.9823875427246</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1827" t="n">
-        <v>16.3277454376221</v>
+        <v>16.3277473449707</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1828" t="n">
-        <v>16.2030334472656</v>
+        <v>16.2030353546143</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1830" t="n">
-        <v>16.1454753875732</v>
+        <v>16.1454734802246</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1831" t="n">
-        <v>16.2030334472656</v>
+        <v>16.2030353546143</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1832" t="n">
-        <v>16.0207614898682</v>
+        <v>16.0207633972168</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.3588256835938</v>
+        <v>15.3588266372681</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1834" t="n">
-        <v>16.0783214569092</v>
+        <v>16.0783195495605</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>15.25</v>
       </c>
       <c r="G1835" t="n">
-        <v>14.6297378540039</v>
+        <v>14.6297369003296</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1838" t="n">
-        <v>14.1980409622192</v>
+        <v>14.1980400085449</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1840" t="n">
-        <v>14.6393308639526</v>
+        <v>14.639331817627</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="n">
-        <v>14.5529918670654</v>
+        <v>14.5529909133911</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.1308870315552</v>
+        <v>14.1308879852295</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1846" t="n">
-        <v>13.9390211105347</v>
+        <v>13.939022064209</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1853" t="n">
-        <v>13.5552911758423</v>
+        <v>13.555290222168</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>13.459358215332</v>
+        <v>13.4593572616577</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1858" t="n">
-        <v>13.353832244873</v>
+        <v>13.3538331985474</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1859" t="n">
-        <v>13.2195262908936</v>
+        <v>13.2195272445679</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>13.75</v>
       </c>
       <c r="G1862" t="n">
-        <v>13.1907472610474</v>
+        <v>13.190746307373</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1863" t="n">
-        <v>12.9701023101807</v>
+        <v>12.9701013565063</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>13.75</v>
       </c>
       <c r="G1864" t="n">
-        <v>13.1907472610474</v>
+        <v>13.190746307373</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2579002380371</v>
+        <v>13.2578992843628</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1866" t="n">
-        <v>13.0180683135986</v>
+        <v>13.0180673599243</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1867" t="n">
-        <v>13.0276613235474</v>
+        <v>13.027660369873</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="n">
-        <v>12.9413213729858</v>
+        <v>12.9413223266602</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1873" t="n">
-        <v>12.8862724304199</v>
+        <v>12.8862733840942</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1874" t="n">
-        <v>12.2768535614014</v>
+        <v>12.2768526077271</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1878" t="n">
-        <v>12.2080478668213</v>
+        <v>12.2080488204956</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1880" t="n">
-        <v>12.7093448638916</v>
+        <v>12.7093458175659</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1885" t="n">
-        <v>11.7165813446045</v>
+        <v>11.7165803909302</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1888" t="n">
-        <v>11.5593118667603</v>
+        <v>11.5593109130859</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1894" t="n">
-        <v>11.6969223022461</v>
+        <v>11.6969213485718</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1895" t="n">
-        <v>11.7755565643311</v>
+        <v>11.7755556106567</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1898" t="n">
-        <v>11.9524841308594</v>
+        <v>11.9524850845337</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1902" t="n">
-        <v>11.5593118667603</v>
+        <v>11.5593109130859</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1906" t="n">
-        <v>11.5887985229492</v>
+        <v>11.5887994766235</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1911" t="n">
-        <v>11.5593118667603</v>
+        <v>11.5593109130859</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1917" t="n">
-        <v>11.4216995239258</v>
+        <v>11.4217004776001</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1919" t="n">
-        <v>11.4216995239258</v>
+        <v>11.4217004776001</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1922" t="n">
-        <v>11.6969223022461</v>
+        <v>11.6969213485718</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>12</v>
       </c>
       <c r="G1923" t="n">
-        <v>11.7952146530151</v>
+        <v>11.7952156066895</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1924" t="n">
-        <v>11.7460680007935</v>
+        <v>11.7460689544678</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1927" t="n">
-        <v>11.7264099121094</v>
+        <v>11.7264108657837</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1929" t="n">
-        <v>11.8738498687744</v>
+        <v>11.8738508224487</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1931" t="n">
-        <v>12.1097536087036</v>
+        <v>12.1097545623779</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1934" t="n">
-        <v>11.5986289978027</v>
+        <v>11.5986280441284</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1935" t="n">
-        <v>11.402042388916</v>
+        <v>11.4020414352417</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1939" t="n">
-        <v>11.2251138687134</v>
+        <v>11.2251129150391</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1941" t="n">
-        <v>11.7755565643311</v>
+        <v>11.7755556106567</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1943" t="n">
-        <v>11.8345327377319</v>
+        <v>11.8345336914062</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1945" t="n">
-        <v>12.2473649978638</v>
+        <v>12.2473659515381</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1948" t="n">
-        <v>11.8345327377319</v>
+        <v>11.8345336914062</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1950" t="n">
-        <v>12.2375364303589</v>
+        <v>12.2375354766846</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1951" t="n">
-        <v>12.2670230865479</v>
+        <v>12.2670240402222</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="n">
-        <v>11.8935089111328</v>
+        <v>11.8935098648071</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1962" t="n">
-        <v>11.5593118667603</v>
+        <v>11.5593109130859</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1964" t="n">
-        <v>11.3725528717041</v>
+        <v>11.3725538253784</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1965" t="n">
-        <v>11.2251138687134</v>
+        <v>11.2251129150391</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1966" t="n">
-        <v>11.3823833465576</v>
+        <v>11.3823823928833</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1968" t="n">
-        <v>11.0481843948364</v>
+        <v>11.0481853485107</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1973" t="n">
-        <v>10.8614282608032</v>
+        <v>10.8614273071289</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1975" t="n">
-        <v>10.6746692657471</v>
+        <v>10.6746702194214</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1977" t="n">
-        <v>10.6746692657471</v>
+        <v>10.6746702194214</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1981" t="n">
-        <v>11.1563081741333</v>
+        <v>11.1563091278076</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>11.25</v>
       </c>
       <c r="G1982" t="n">
-        <v>11.0580139160156</v>
+        <v>11.0580148696899</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1990" t="n">
-        <v>10.0455923080444</v>
+        <v>10.0455913543701</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1992" t="n">
-        <v>9.79985809326172</v>
+        <v>9.79985904693604</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G1993" t="n">
-        <v>9.53938102722168</v>
+        <v>9.53938007354736</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1997" t="n">
-        <v>10.0161027908325</v>
+        <v>10.0161037445068</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2015" t="n">
-        <v>11.1563081741333</v>
+        <v>11.1563091278076</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>11</v>
       </c>
       <c r="G2019" t="n">
-        <v>10.8122816085815</v>
+        <v>10.8122806549072</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G2021" t="n">
-        <v>11.1366491317749</v>
+        <v>11.1366500854492</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2022" t="n">
-        <v>11.0285272598267</v>
+        <v>11.0285263061523</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2024" t="n">
-        <v>11.2742595672607</v>
+        <v>11.2742605209351</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2028" t="n">
-        <v>11.8738498687744</v>
+        <v>11.8738508224487</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2029" t="n">
-        <v>11.6969223022461</v>
+        <v>11.6969213485718</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2030" t="n">
-        <v>11.7755565643311</v>
+        <v>11.7755556106567</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2032" t="n">
-        <v>11.8935089111328</v>
+        <v>11.8935098648071</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G2034" t="n">
-        <v>12.4341230392456</v>
+        <v>12.4341220855713</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2043" t="n">
-        <v>12.0507783889771</v>
+        <v>12.0507793426514</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>12</v>
       </c>
       <c r="G2046" t="n">
-        <v>11.7952146530151</v>
+        <v>11.7952156066895</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>12</v>
       </c>
       <c r="G2049" t="n">
-        <v>11.7952146530151</v>
+        <v>11.7952156066895</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2050" t="n">
-        <v>11.5887985229492</v>
+        <v>11.5887994766235</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2051" t="n">
-        <v>11.6969223022461</v>
+        <v>11.6969213485718</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G2054" t="n">
-        <v>12.0802669525146</v>
+        <v>12.0802659988403</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2061" t="n">
-        <v>11.7264099121094</v>
+        <v>11.7264108657837</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2062" t="n">
-        <v>11.7264099121094</v>
+        <v>11.7264108657837</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2064" t="n">
-        <v>11.7067518234253</v>
+        <v>11.706750869751</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2066" t="n">
-        <v>11.6969223022461</v>
+        <v>11.6969213485718</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G2068" t="n">
-        <v>11.7460680007935</v>
+        <v>11.7460689544678</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G2078" t="n">
-        <v>12.2768535614014</v>
+        <v>12.2768526077271</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2079" t="n">
-        <v>11.9524841308594</v>
+        <v>11.9524850845337</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2081" t="n">
-        <v>11.8345327377319</v>
+        <v>11.8345336914062</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2084" t="n">
-        <v>11.5396528244019</v>
+        <v>11.5396518707275</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G2088" t="n">
-        <v>11.5298223495483</v>
+        <v>11.5298233032227</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2090" t="n">
-        <v>10.9695510864258</v>
+        <v>10.9695501327515</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2091" t="n">
-        <v>11.1563081741333</v>
+        <v>11.1563091278076</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2092" t="n">
-        <v>11.2152833938599</v>
+        <v>11.2152843475342</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2094" t="n">
-        <v>11.431529045105</v>
+        <v>11.4315299987793</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2097" t="n">
-        <v>12.2080478668213</v>
+        <v>12.2080488204956</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2098" t="n">
-        <v>12.1687316894531</v>
+        <v>12.1687307357788</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2100" t="n">
-        <v>11.8935089111328</v>
+        <v>11.8935098648071</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2109" t="n">
-        <v>11.5986289978027</v>
+        <v>11.5986280441284</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G2110" t="n">
-        <v>11.5593118667603</v>
+        <v>11.5593109130859</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2111" t="n">
-        <v>11.3430662155151</v>
+        <v>11.3430652618408</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G2112" t="n">
-        <v>11.3725528717041</v>
+        <v>11.3725538253784</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2116" t="n">
-        <v>11.5396528244019</v>
+        <v>11.5396518707275</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2118" t="n">
-        <v>11.3430662155151</v>
+        <v>11.3430652618408</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2119" t="n">
-        <v>11.8738498687744</v>
+        <v>11.8738508224487</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>4.94000005722046</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>52854</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>4.94000005722046</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>4.94000005722046</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2523975372314</v>
+        <v>13.2523984909058</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12.3974046707153</v>
+        <v>12.3974027633667</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G7" t="n">
-        <v>12.243504524231</v>
+        <v>12.2435064315796</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>12.1409063339233</v>
+        <v>12.1409072875977</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4825620651245</v>
+        <v>11.4825630187988</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>9.79822540283203</v>
+        <v>9.79822444915771</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3539695739746</v>
+        <v>10.3539705276489</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G14" t="n">
-        <v>9.84952449798584</v>
+        <v>9.84952259063721</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>12.25</v>
       </c>
       <c r="G15" t="n">
-        <v>10.473669052124</v>
+        <v>10.4736700057983</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941198348999</v>
+        <v>10.2941217422485</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156671524048</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>10.7301683425903</v>
+        <v>10.730167388916</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361179351807</v>
+        <v>10.636118888855</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156671524048</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1915216445923</v>
+        <v>10.191520690918</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907703399658</v>
+        <v>10.4907693862915</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743129730225</v>
+        <v>8.97743034362793</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9.40492630004883</v>
+        <v>9.40492725372314</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057632446289</v>
+        <v>9.43057727813721</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082359313965</v>
+        <v>9.90082263946533</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142463684082</v>
+        <v>9.66142654418945</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.345419883728</v>
+        <v>10.3454208374023</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0037641525269</v>
+        <v>11.0037651062012</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506181716919</v>
+        <v>10.5506191253662</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0379638671875</v>
+        <v>11.0379648208618</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097166061401</v>
+        <v>10.9097175598145</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8074579238892</v>
+        <v>11.8074607849121</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442577362061</v>
+        <v>11.9442586898804</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G45" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067056655884</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732610702515</v>
+        <v>11.7732601165771</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3799619674683</v>
+        <v>11.3799629211426</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6621103286743</v>
+        <v>11.6621122360229</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416585922241</v>
+        <v>11.8416595458984</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.9186086654663</v>
+        <v>11.918607711792</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>12.0468578338623</v>
+        <v>12.0468587875366</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922073364258</v>
+        <v>12.1922063827515</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G57" t="n">
-        <v>12.200756072998</v>
+        <v>12.2007570266724</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375568389893</v>
+        <v>12.3375549316406</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1409063339233</v>
+        <v>12.1409072875977</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>12.1323556900024</v>
+        <v>12.1323566436768</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665554046631</v>
+        <v>12.1665563583374</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067056655884</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1409063339233</v>
+        <v>12.1409072875977</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.2859125137329</v>
+        <v>11.2859134674072</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G69" t="n">
-        <v>11.7390584945679</v>
+        <v>11.7390594482422</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6621103286743</v>
+        <v>11.6621122360229</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160085678101</v>
+        <v>11.8160076141357</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048597335815</v>
+        <v>11.7048587799072</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.6621103286743</v>
+        <v>11.6621122360229</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364612579346</v>
+        <v>11.6364583969116</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G78" t="n">
-        <v>11.4740114212036</v>
+        <v>11.4740104675293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G80" t="n">
-        <v>11.1063642501831</v>
+        <v>11.1063652038574</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.1149139404297</v>
+        <v>11.1149129867554</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3799619674683</v>
+        <v>11.3799629211426</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3201122283936</v>
+        <v>11.3201131820679</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G84" t="n">
-        <v>11.3457622528076</v>
+        <v>11.3457632064819</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1576633453369</v>
+        <v>11.1576642990112</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.055064201355</v>
+        <v>11.0550651550293</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.986665725708</v>
+        <v>10.9866647720337</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>10.60191822052</v>
+        <v>10.6019172668457</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G92" t="n">
-        <v>10.3553619384766</v>
+        <v>10.3553638458252</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G94" t="n">
-        <v>10.22327709198</v>
+        <v>10.2232780456543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G95" t="n">
-        <v>10.2673053741455</v>
+        <v>10.2673063278198</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92389011383057</v>
+        <v>9.92388820648193</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.302529335022</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496957778931</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>10.6107244491577</v>
+        <v>10.610725402832</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120321273804</v>
+        <v>11.4120311737061</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189195632935</v>
+        <v>10.9189186096191</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>11.2799472808838</v>
+        <v>11.2799482345581</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0069742202759</v>
+        <v>11.0069751739502</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8308629989624</v>
+        <v>10.8308620452881</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396682739258</v>
+        <v>10.8396701812744</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647764205933</v>
+        <v>10.0647783279419</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>11</v>
       </c>
       <c r="G118" t="n">
-        <v>9.68613719940186</v>
+        <v>9.68613815307617</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.0383605957031</v>
+        <v>10.0383596420288</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962501525879</v>
+        <v>10.4962511062622</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.75</v>
       </c>
       <c r="G121" t="n">
-        <v>10.3465566635132</v>
+        <v>10.3465547561646</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843076705933</v>
+        <v>10.5843067169189</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G127" t="n">
-        <v>9.5716667175293</v>
+        <v>9.57166481018066</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>9.93269443511963</v>
+        <v>9.93269348144531</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1880569458008</v>
+        <v>10.1880559921265</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>9.68613719940186</v>
+        <v>9.68613815307617</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.18421936035156</v>
+        <v>9.18422031402588</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019107818604</v>
+        <v>9.14019298553467</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G136" t="n">
-        <v>10.3817796707153</v>
+        <v>10.3817768096924</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>10.2849168777466</v>
+        <v>10.2849178314209</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1352214813232</v>
+        <v>10.1352224349976</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>10.2144718170166</v>
+        <v>10.2144746780396</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1528339385986</v>
+        <v>10.1528329849243</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496957778931</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496957778931</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G144" t="n">
-        <v>10.2673053741455</v>
+        <v>10.2673063278198</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.302529335022</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987781524658</v>
+        <v>10.6987791061401</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G147" t="n">
-        <v>11.0774192810059</v>
+        <v>11.0774183273315</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>10.8308629989624</v>
+        <v>10.8308620452881</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893617630005</v>
+        <v>10.9893636703491</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748903274536</v>
+        <v>10.8748912811279</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748903274536</v>
+        <v>10.8748912811279</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.0950298309326</v>
+        <v>11.0950317382812</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654739379883</v>
+        <v>11.1654758453369</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G165" t="n">
-        <v>11.0598077774048</v>
+        <v>11.0598087310791</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G167" t="n">
-        <v>11.1214466094971</v>
+        <v>11.1214475631714</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>11.0774192810059</v>
+        <v>11.0774183273315</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>11.5265026092529</v>
+        <v>11.5265045166016</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472522735596</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>11.323974609375</v>
+        <v>11.3239736557007</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680028915405</v>
+        <v>11.3680038452148</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472522735596</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G187" t="n">
-        <v>11.8258934020996</v>
+        <v>11.8258953094482</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.0636434555054</v>
+        <v>12.0636444091797</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>12.5039215087891</v>
+        <v>12.5039234161377</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303401947021</v>
+        <v>12.5303392410278</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070615768433</v>
+        <v>12.4070625305176</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837829589844</v>
+        <v>12.2837839126587</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>12.9177865982056</v>
+        <v>12.9177846908569</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8121175765991</v>
+        <v>12.8121185302734</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>13.0322570800781</v>
+        <v>13.0322589874268</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782051086426</v>
+        <v>13.5782041549683</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G202" t="n">
-        <v>13.6838703155518</v>
+        <v>13.6838712692261</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285087585449</v>
+        <v>13.4285097122192</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210092544556</v>
+        <v>14.2210102081299</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9216222763062</v>
+        <v>13.9216213226318</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>13.7807302474976</v>
+        <v>13.7807331085205</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>13.6046209335327</v>
+        <v>13.6046199798584</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631206512451</v>
+        <v>13.7631216049194</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7278995513916</v>
+        <v>13.7278985977173</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>13.375675201416</v>
+        <v>13.3756761550903</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486482620239</v>
+        <v>13.6486492156982</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605916976929</v>
+        <v>13.5605926513672</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285087585449</v>
+        <v>13.4285097122192</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G226" t="n">
-        <v>14.7845687866211</v>
+        <v>14.7845697402954</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.277681350708</v>
+        <v>15.2776794433594</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978199005127</v>
+        <v>15.4978189468384</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657379150391</v>
+        <v>15.3657369613647</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5330419540405</v>
+        <v>15.5330410003662</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G235" t="n">
-        <v>15.6651268005371</v>
+        <v>15.6651277542114</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418472290039</v>
+        <v>15.5418462753296</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.277681350708</v>
+        <v>15.2776794433594</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>15.8060169219971</v>
+        <v>15.8060159683228</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.5104637145996</v>
+        <v>16.510461807251</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.5104637145996</v>
+        <v>16.510461807251</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G247" t="n">
-        <v>17.1532707214355</v>
+        <v>17.1532669067383</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>16.7746276855469</v>
+        <v>16.7746295928955</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>16.5544872283936</v>
+        <v>16.5544891357422</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>16.2374897003174</v>
+        <v>16.237491607666</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G252" t="n">
-        <v>16.6513538360596</v>
+        <v>16.6513500213623</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>16.5721015930176</v>
+        <v>16.5720996856689</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947681427002</v>
+        <v>16.9947643280029</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.880298614502</v>
+        <v>16.8802947998047</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538780212402</v>
+        <v>16.8538761138916</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.012378692627</v>
+        <v>17.0123805999756</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>17.1532707214355</v>
+        <v>17.1532669067383</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G261" t="n">
-        <v>17.1268539428711</v>
+        <v>17.1268501281738</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>16.8626842498779</v>
+        <v>16.8626861572266</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>17.2061023712158</v>
+        <v>17.2061042785645</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551856994629</v>
+        <v>17.6551876068115</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>17.5407161712646</v>
+        <v>17.540714263916</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G271" t="n">
-        <v>17.7168254852295</v>
+        <v>17.7168273925781</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G272" t="n">
-        <v>17.4526557922363</v>
+        <v>17.4526596069336</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432422637939</v>
+        <v>17.7432441711426</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>17.8401069641113</v>
+        <v>17.8401050567627</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>17.5759334564209</v>
+        <v>17.5759353637695</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G279" t="n">
-        <v>16.7658252716064</v>
+        <v>16.7658233642578</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>19.25</v>
       </c>
       <c r="G280" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507389068604</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G282" t="n">
-        <v>17.2765464782715</v>
+        <v>17.2765445709229</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092433929443</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>16.8626842498779</v>
+        <v>16.8626861572266</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G287" t="n">
-        <v>16.8186569213867</v>
+        <v>16.8186588287354</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19.25</v>
       </c>
       <c r="G288" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507389068604</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>19.25</v>
       </c>
       <c r="G289" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507389068604</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G290" t="n">
-        <v>17.2325172424316</v>
+        <v>17.2325191497803</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>17.2853507995605</v>
+        <v>17.2853527069092</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3910217285156</v>
+        <v>17.391019821167</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092433929443</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G295" t="n">
-        <v>17.2853507995605</v>
+        <v>17.2853527069092</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2501277923584</v>
+        <v>17.250129699707</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350471496582</v>
+        <v>17.4350490570068</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734092712402</v>
+        <v>17.3734073638916</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G299" t="n">
-        <v>17.6463832855225</v>
+        <v>17.6463813781738</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>17.9457721710205</v>
+        <v>17.9457683563232</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>22</v>
       </c>
       <c r="G301" t="n">
-        <v>19.3722743988037</v>
+        <v>19.3722763061523</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G302" t="n">
-        <v>19.9358329772949</v>
+        <v>19.9358348846436</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G303" t="n">
-        <v>20.3849182128906</v>
+        <v>20.384916305542</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962505340576</v>
+        <v>20.5962524414062</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8340015411377</v>
+        <v>20.8340034484863</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>21.0453357696533</v>
+        <v>21.0453338623047</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824794769287</v>
+        <v>21.5824775695801</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>21.0893611907959</v>
+        <v>21.0893650054932</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G311" t="n">
-        <v>21.6529216766357</v>
+        <v>21.6529235839844</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497806549072</v>
+        <v>21.7497825622559</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>21.9170875549316</v>
+        <v>21.917085647583</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>21.8114204406738</v>
+        <v>21.8114185333252</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>25</v>
       </c>
       <c r="G315" t="n">
-        <v>22.0139484405518</v>
+        <v>22.0139503479004</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.2869205474854</v>
+        <v>22.286922454834</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605075836182</v>
+        <v>22.2605056762695</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221435546875</v>
+        <v>22.3221454620361</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>22.1900596618652</v>
+        <v>22.1900634765625</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G323" t="n">
-        <v>22.4806442260742</v>
+        <v>22.4806461334229</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G324" t="n">
-        <v>22.6655616760254</v>
+        <v>22.665563583374</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G325" t="n">
-        <v>22.4806442260742</v>
+        <v>22.4806461334229</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743640899658</v>
+        <v>22.6743659973145</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945064544678</v>
+        <v>22.8945045471191</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G329" t="n">
-        <v>23.0970363616943</v>
+        <v>23.0970344543457</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>25.9300003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>22.8328666687012</v>
+        <v>22.8328704833984</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>22.374979019165</v>
+        <v>22.3749771118164</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>25</v>
       </c>
       <c r="G332" t="n">
-        <v>22.0139484405518</v>
+        <v>22.0139503479004</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G333" t="n">
-        <v>23.1938972473145</v>
+        <v>23.1938953399658</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>23.5108966827393</v>
+        <v>23.5108985900879</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>23.9159564971924</v>
+        <v>23.9159545898438</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417602539062</v>
+        <v>24.2417621612549</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>24.7084560394287</v>
+        <v>24.7084579467773</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.919792175293</v>
+        <v>24.9197902679443</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870952606201</v>
+        <v>25.0870971679688</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255447387695</v>
+        <v>26.4255466461182</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G346" t="n">
-        <v>27.397008895874</v>
+        <v>27.3970069885254</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G350" t="n">
-        <v>28.6804046630859</v>
+        <v>28.6804065704346</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>32.560001373291</v>
       </c>
       <c r="G354" t="n">
-        <v>29.0190830230713</v>
+        <v>29.0190811157227</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>29.7677326202393</v>
+        <v>29.7677307128906</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746795654297</v>
+        <v>29.8746814727783</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024806976318</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>34.5299987792969</v>
       </c>
       <c r="G359" t="n">
-        <v>30.7748394012451</v>
+        <v>30.7748413085938</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283233642578</v>
+        <v>30.8283195495605</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996162414551</v>
+        <v>30.8996143341064</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154800415039</v>
+        <v>31.0154781341553</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.9352684020996</v>
+        <v>30.935266494751</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857223510742</v>
+        <v>30.685718536377</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G370" t="n">
-        <v>29.3577556610107</v>
+        <v>29.3577575683594</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>29.5003509521484</v>
+        <v>29.5003528594971</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G372" t="n">
-        <v>29.3131942749023</v>
+        <v>29.3131923675537</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>29.2775402069092</v>
+        <v>29.2775421142578</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.1687927246094</v>
+        <v>30.1687908172607</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331424713135</v>
+        <v>30.1331462860107</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.4825325012207</v>
+        <v>29.4825305938721</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G381" t="n">
-        <v>28.912130355835</v>
+        <v>28.9121322631836</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.1260299682617</v>
+        <v>29.1260318756104</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>27.7713317871094</v>
+        <v>27.7713356018066</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544078826904</v>
+        <v>27.2544059753418</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>28.1189155578613</v>
+        <v>28.1189193725586</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>31.8099994659424</v>
       </c>
       <c r="G390" t="n">
-        <v>28.3506393432617</v>
+        <v>28.350643157959</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178554534912</v>
+        <v>27.7178573608398</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734558105469</v>
+        <v>28.5734596252441</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>32</v>
       </c>
       <c r="G394" t="n">
-        <v>28.5199813842773</v>
+        <v>28.5199794769287</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>28.787353515625</v>
+        <v>28.7873554229736</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855548858643</v>
+        <v>29.7855529785156</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G398" t="n">
-        <v>29.5360088348389</v>
+        <v>29.5360050201416</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>29.143856048584</v>
+        <v>29.1438579559326</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221111297607</v>
+        <v>29.3221054077148</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>32.2099990844727</v>
       </c>
       <c r="G405" t="n">
-        <v>28.7071418762207</v>
+        <v>28.7071437835693</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G407" t="n">
-        <v>28.9923419952393</v>
+        <v>28.9923439025879</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477825164795</v>
+        <v>28.9477806091309</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>29.7677326202393</v>
+        <v>29.7677307128906</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>33</v>
       </c>
       <c r="G413" t="n">
-        <v>29.4112319946289</v>
+        <v>29.4112339019775</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G414" t="n">
-        <v>28.814094543457</v>
+        <v>28.8140964508057</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>33</v>
       </c>
       <c r="G415" t="n">
-        <v>29.4112319946289</v>
+        <v>29.4112339019775</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.6875190734863</v>
+        <v>29.6875228881836</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>29.6162204742432</v>
+        <v>29.6162166595459</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964321136475</v>
+        <v>29.6964302062988</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>30.1420574188232</v>
+        <v>30.142053604126</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>33.8699989318848</v>
       </c>
       <c r="G422" t="n">
-        <v>30.1866149902344</v>
+        <v>30.186616897583</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G425" t="n">
-        <v>29.1795082092285</v>
+        <v>29.1795101165771</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>29.437967300415</v>
+        <v>29.4379692077637</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648681640625</v>
+        <v>30.3648662567139</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629096984863</v>
+        <v>30.4629058837891</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024806976318</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G431" t="n">
-        <v>30.293571472168</v>
+        <v>30.2935695648193</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974960327148</v>
+        <v>30.0974903106689</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.0618419647217</v>
+        <v>30.061840057373</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.23118019104</v>
+        <v>30.2311820983887</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>31.4967517852783</v>
+        <v>31.496753692627</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G440" t="n">
-        <v>31.7730388641357</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G441" t="n">
-        <v>31.7730388641357</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928272247314</v>
+        <v>31.6928291320801</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>36.1100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>32.1830177307129</v>
+        <v>32.1830215454102</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>36.25</v>
       </c>
       <c r="G446" t="n">
-        <v>32.3077964782715</v>
+        <v>32.3077926635742</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990394592285</v>
+        <v>33.1990432739258</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>37.4700012207031</v>
       </c>
       <c r="G448" t="n">
-        <v>33.3951187133789</v>
+        <v>33.3951225280762</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>39</v>
       </c>
       <c r="G449" t="n">
-        <v>34.7587242126465</v>
+        <v>34.7587280273438</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>34.6963424682617</v>
+        <v>34.6963386535645</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.731990814209</v>
+        <v>34.7319946289062</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.437873840332</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.437873840332</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G470" t="n">
-        <v>34.1170272827148</v>
+        <v>34.1170234680176</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>38.6199989318848</v>
       </c>
       <c r="G471" t="n">
-        <v>34.420051574707</v>
+        <v>34.4200477600098</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G472" t="n">
-        <v>34.1170272827148</v>
+        <v>34.1170234680176</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041877746582</v>
+        <v>34.3041954040527</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>40.7299995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>36.300594329834</v>
+        <v>36.3005867004395</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G482" t="n">
-        <v>36.1847229003906</v>
+        <v>36.1847267150879</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G484" t="n">
-        <v>37.4146499633789</v>
+        <v>37.4146461486816</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.8584747314453</v>
+        <v>38.858470916748</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>43.6699981689453</v>
       </c>
       <c r="G486" t="n">
-        <v>38.9208602905273</v>
+        <v>38.9208641052246</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>42.939998626709</v>
       </c>
       <c r="G489" t="n">
-        <v>38.2702445983887</v>
+        <v>38.2702484130859</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G490" t="n">
-        <v>38.4306716918945</v>
+        <v>38.4306755065918</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.805004119873</v>
+        <v>38.8049964904785</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G493" t="n">
-        <v>37.8068008422852</v>
+        <v>37.8067970275879</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.341552734375</v>
+        <v>38.3415565490723</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>43.2200012207031</v>
       </c>
       <c r="G498" t="n">
-        <v>38.5198059082031</v>
+        <v>38.5198020935059</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>38.5643615722656</v>
+        <v>38.5643653869629</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G500" t="n">
-        <v>38.4306716918945</v>
+        <v>38.4306755065918</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089248657227</v>
+        <v>38.6089286804199</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.689136505127</v>
+        <v>38.6891403198242</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>44.25</v>
       </c>
       <c r="G504" t="n">
-        <v>39.4377899169922</v>
+        <v>39.4377861022949</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>39.0812873840332</v>
+        <v>39.0812835693359</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>42.9599990844727</v>
       </c>
       <c r="G509" t="n">
-        <v>38.2880744934082</v>
+        <v>38.2880783081055</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G510" t="n">
-        <v>38.3772048950195</v>
+        <v>38.3772010803223</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G513" t="n">
-        <v>37.6820259094238</v>
+        <v>37.6820220947266</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G514" t="n">
-        <v>38.4663276672363</v>
+        <v>38.4663238525391</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G516" t="n">
-        <v>42.6551933288574</v>
+        <v>42.655200958252</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>48.0400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>42.8156242370605</v>
+        <v>42.8156204223633</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.423469543457</v>
+        <v>42.4234733581543</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G519" t="n">
-        <v>42.031322479248</v>
+        <v>42.0313186645508</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G521" t="n">
-        <v>41.924373626709</v>
+        <v>41.9243774414062</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>41.6213455200195</v>
+        <v>41.6213531494141</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>42.031322479248</v>
+        <v>42.0313186645508</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>46.8600006103516</v>
       </c>
       <c r="G524" t="n">
-        <v>41.7639503479004</v>
+        <v>41.7639465332031</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G527" t="n">
-        <v>41.924373626709</v>
+        <v>41.9243774414062</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G528" t="n">
-        <v>41.6926460266113</v>
+        <v>41.6926498413086</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>41.5322189331055</v>
+        <v>41.5322227478027</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>46.8800010681152</v>
       </c>
       <c r="G530" t="n">
-        <v>41.7817687988281</v>
+        <v>41.7817726135254</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G531" t="n">
-        <v>41.3539733886719</v>
+        <v>41.3539772033691</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G533" t="n">
-        <v>40.3557739257812</v>
+        <v>40.3557777404785</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G534" t="n">
-        <v>40.5874977111816</v>
+        <v>40.5875015258789</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G536" t="n">
-        <v>39.143669128418</v>
+        <v>39.1436767578125</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784286499023</v>
+        <v>39.6784248352051</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>48</v>
       </c>
       <c r="G538" t="n">
-        <v>42.7799682617188</v>
+        <v>42.779972076416</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G539" t="n">
-        <v>41.4787521362305</v>
+        <v>41.4787483215332</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>42.1599998474121</v>
       </c>
       <c r="G541" t="n">
-        <v>37.5750732421875</v>
+        <v>37.5750770568848</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>41.8400001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>37.2898750305176</v>
+        <v>37.2898788452148</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>44.4199981689453</v>
       </c>
       <c r="G544" t="n">
-        <v>39.589298248291</v>
+        <v>39.5892944335938</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>40.1953468322754</v>
+        <v>40.1953506469727</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>45</v>
       </c>
       <c r="G546" t="n">
-        <v>40.1062278747559</v>
+        <v>40.1062240600586</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G548" t="n">
-        <v>40.8013954162598</v>
+        <v>40.801399230957</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G550" t="n">
-        <v>40.8013954162598</v>
+        <v>40.801399230957</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400718688965</v>
+        <v>41.1400756835938</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G553" t="n">
-        <v>40.5161933898926</v>
+        <v>40.5161972045898</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>45.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>40.9618186950684</v>
+        <v>40.9618263244629</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793251037598</v>
+        <v>39.1793212890625</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914260864258</v>
+        <v>40.3914184570312</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>46.439998626709</v>
       </c>
       <c r="G560" t="n">
-        <v>41.3896141052246</v>
+        <v>41.3896217346191</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446434020996</v>
+        <v>44.5446472167969</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G563" t="n">
-        <v>43.902946472168</v>
+        <v>43.9029426574707</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G565" t="n">
-        <v>43.8851203918457</v>
+        <v>43.885124206543</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253440856934</v>
+        <v>47.3253402709961</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>45.9439086914062</v>
+        <v>45.943904876709</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>50.1500015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>44.6961631774902</v>
+        <v>44.696159362793</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>49.3800010681152</v>
       </c>
       <c r="G572" t="n">
-        <v>44.0098991394043</v>
+        <v>44.0099029541016</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G574" t="n">
-        <v>42.9582214355469</v>
+        <v>42.9582290649414</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>42.6551933288574</v>
+        <v>42.655200958252</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>41.4787521362305</v>
+        <v>41.4787483215332</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.1080284118652</v>
+        <v>39.108024597168</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479209899902</v>
+        <v>40.7479286193848</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>45.5</v>
       </c>
       <c r="G586" t="n">
-        <v>40.5518531799316</v>
+        <v>40.5518493652344</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3041000366211</v>
+        <v>39.3040962219238</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488250732422</v>
+        <v>40.2488288879395</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>44.7799987792969</v>
       </c>
       <c r="G591" t="n">
-        <v>39.9101486206055</v>
+        <v>39.9101448059082</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G593" t="n">
-        <v>39.143669128418</v>
+        <v>39.1436767578125</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479209899902</v>
+        <v>40.7479286193848</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.0509490966797</v>
+        <v>41.050952911377</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>46.560001373291</v>
       </c>
       <c r="G598" t="n">
-        <v>41.9335708618164</v>
+        <v>41.9335670471191</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G599" t="n">
-        <v>41.0149230957031</v>
+        <v>41.0149269104004</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G601" t="n">
-        <v>40.6366577148438</v>
+        <v>40.6366539001465</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G603" t="n">
-        <v>39.8441047668457</v>
+        <v>39.8441009521484</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>41.9000015258789</v>
       </c>
       <c r="G604" t="n">
-        <v>37.7366104125977</v>
+        <v>37.7366142272949</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.4844360351562</v>
+        <v>37.484432220459</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316230773926</v>
+        <v>36.3316268920898</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>40.6399993896484</v>
       </c>
       <c r="G609" t="n">
-        <v>36.6018104553223</v>
+        <v>36.6018142700195</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.007396697998</v>
+        <v>36.0073928833008</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>33.4135627746582</v>
+        <v>33.4135589599609</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>37.6199989318848</v>
       </c>
       <c r="G616" t="n">
-        <v>33.8818893432617</v>
+        <v>33.8818969726562</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G617" t="n">
-        <v>34.4763145446777</v>
+        <v>34.4763069152832</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924705505371</v>
+        <v>34.6924667358398</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G619" t="n">
-        <v>35.1427841186523</v>
+        <v>35.1427803039551</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>38.560001373291</v>
       </c>
       <c r="G620" t="n">
-        <v>34.7284927368164</v>
+        <v>34.7284889221191</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>37.7400016784668</v>
       </c>
       <c r="G622" t="n">
-        <v>33.9899711608887</v>
+        <v>33.9899749755859</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>37.6199989318848</v>
       </c>
       <c r="G624" t="n">
-        <v>33.8818893432617</v>
+        <v>33.8818969726562</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>38.2400016784668</v>
       </c>
       <c r="G626" t="n">
-        <v>34.4402885437012</v>
+        <v>34.4402923583984</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247749328613</v>
+        <v>35.1247673034668</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G631" t="n">
-        <v>31.468189239502</v>
+        <v>31.4681873321533</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G632" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744045257568</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371128082275</v>
+        <v>29.9371109008789</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346153259277</v>
+        <v>29.2346134185791</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>27.829626083374</v>
+        <v>27.8296241760254</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>29.5408325195312</v>
+        <v>29.540828704834</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520427703857</v>
+        <v>31.2520351409912</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551219940186</v>
+        <v>29.9551239013672</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172409057617</v>
+        <v>30.1172351837158</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054393768311</v>
+        <v>30.4054412841797</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.666332244873</v>
+        <v>31.6663341522217</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>31.6483154296875</v>
+        <v>31.6483173370361</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>31.1079368591309</v>
+        <v>31.1079425811768</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601169586182</v>
+        <v>31.3601150512695</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>30.9818515777588</v>
+        <v>30.9818477630615</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G656" t="n">
-        <v>31.7383861541748</v>
+        <v>31.7383823394775</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520427703857</v>
+        <v>31.2520351409912</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122894287109</v>
+        <v>31.6122932434082</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G659" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744045257568</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>34.2400016784668</v>
       </c>
       <c r="G660" t="n">
-        <v>30.8377475738525</v>
+        <v>30.8377513885498</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G661" t="n">
-        <v>29.9191017150879</v>
+        <v>29.9190998077393</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.9010887145996</v>
+        <v>29.901086807251</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346153259277</v>
+        <v>29.2346134185791</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>28.099817276001</v>
+        <v>28.0998153686523</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G670" t="n">
-        <v>26.2805328369141</v>
+        <v>26.2805347442627</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G673" t="n">
-        <v>27.2352066040039</v>
+        <v>27.2352046966553</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>30</v>
       </c>
       <c r="G677" t="n">
-        <v>27.0190525054932</v>
+        <v>27.0190544128418</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>26.7488651275635</v>
+        <v>26.7488632202148</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693737030029</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196910858154</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G681" t="n">
-        <v>27.5774478912354</v>
+        <v>27.577449798584</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G682" t="n">
-        <v>27.9377002716064</v>
+        <v>27.9377021789551</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>27.829626083374</v>
+        <v>27.8296241760254</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476371765137</v>
+        <v>27.847635269165</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>27.7936019897461</v>
+        <v>27.7936000823975</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693737030029</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>28.0097541809082</v>
+        <v>28.0097522735596</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.0097541809082</v>
+        <v>28.0097522735596</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>31.7600002288818</v>
       </c>
       <c r="G691" t="n">
-        <v>28.6041717529297</v>
+        <v>28.6041736602783</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>29.1805801391602</v>
+        <v>29.1805820465088</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762237548828</v>
+        <v>28.6762218475342</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G699" t="n">
-        <v>27.6675090789795</v>
+        <v>27.6675109863281</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196910858154</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196910858154</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.5594367980957</v>
+        <v>27.5594348907471</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>25.7581653594971</v>
+        <v>25.7581634521484</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G708" t="n">
-        <v>21.7413330078125</v>
+        <v>21.7413311004639</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>23.236385345459</v>
+        <v>23.2363872528076</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G715" t="n">
-        <v>23.4345283508301</v>
+        <v>23.4345264434814</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>21.7053070068359</v>
+        <v>21.7053089141846</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G719" t="n">
-        <v>21.3630638122559</v>
+        <v>21.3630619049072</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369766235352</v>
+        <v>21.2369747161865</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>21.5972290039062</v>
+        <v>21.5972309112549</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G724" t="n">
-        <v>18.3189182281494</v>
+        <v>18.318920135498</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G726" t="n">
-        <v>19.5437831878662</v>
+        <v>19.5437850952148</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.8773097991943</v>
+        <v>18.8773078918457</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G730" t="n">
-        <v>18.3189182281494</v>
+        <v>18.318920135498</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.003698348999</v>
+        <v>18.0036964416504</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.5</v>
       </c>
       <c r="G735" t="n">
-        <v>16.661750793457</v>
+        <v>16.6617527008057</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.716082572937</v>
+        <v>15.7160835266113</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6170139312744</v>
+        <v>15.6170129776001</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G741" t="n">
-        <v>16.1573963165283</v>
+        <v>16.1573944091797</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G743" t="n">
-        <v>16.4005680084229</v>
+        <v>16.4005661010742</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>17.4723205566406</v>
+        <v>17.4723224639893</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G745" t="n">
-        <v>17.5533809661865</v>
+        <v>17.5533790588379</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>16.4906272888184</v>
+        <v>16.490629196167</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G747" t="n">
-        <v>17.9406509399414</v>
+        <v>17.94065284729</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4906272888184</v>
+        <v>16.490629196167</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G752" t="n">
-        <v>16.0132923126221</v>
+        <v>16.0132942199707</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.9052171707153</v>
+        <v>15.905216217041</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250881195068</v>
+        <v>15.7250890731812</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>15.4008626937866</v>
+        <v>15.4008636474609</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496139526367</v>
+        <v>15.0496110916138</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G760" t="n">
-        <v>14.752402305603</v>
+        <v>14.7524042129517</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639024734497</v>
+        <v>15.4639053344727</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>19.75</v>
       </c>
       <c r="G765" t="n">
-        <v>17.7875461578369</v>
+        <v>17.7875442504883</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G767" t="n">
-        <v>17.643440246582</v>
+        <v>17.6434440612793</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.3912620544434</v>
+        <v>17.391263961792</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G770" t="n">
-        <v>18.0487289428711</v>
+        <v>18.0487270355225</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>17.9226379394531</v>
+        <v>17.9226398468018</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.4543075561523</v>
+        <v>17.454309463501</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791725158691</v>
+        <v>18.6791706085205</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G782" t="n">
-        <v>18.9493656158447</v>
+        <v>18.9493637084961</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G783" t="n">
-        <v>18.7872486114502</v>
+        <v>18.7872505187988</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>18.354944229126</v>
+        <v>18.3549404144287</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G788" t="n">
-        <v>18.4269924163818</v>
+        <v>18.4269962310791</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>17.3552417755127</v>
+        <v>17.3552398681641</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G792" t="n">
-        <v>17.7244987487793</v>
+        <v>17.7245006561279</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>18.3009052276611</v>
+        <v>18.3009071350098</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698703765869</v>
+        <v>19.6698722839355</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G798" t="n">
-        <v>20.0661506652832</v>
+        <v>20.0661525726318</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G799" t="n">
-        <v>19.9220523834229</v>
+        <v>19.9220504760742</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>19.4176921844482</v>
+        <v>19.4176959991455</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537200927734</v>
+        <v>19.4537181854248</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>17.7515163421631</v>
+        <v>17.7515182495117</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>17.7965526580811</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G809" t="n">
-        <v>17.418285369873</v>
+        <v>17.4182834625244</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508834838867</v>
+        <v>16.8508815765381</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G811" t="n">
-        <v>16.9859809875488</v>
+        <v>16.9859790802002</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490245819092</v>
+        <v>17.0490226745605</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G815" t="n">
-        <v>16.9409446716309</v>
+        <v>16.9409484863281</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462352752686</v>
+        <v>17.3462333679199</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2831878662109</v>
+        <v>17.2831897735596</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9766750335693</v>
+        <v>17.976676940918</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.4272918701172</v>
+        <v>17.4272880554199</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.4543075561523</v>
+        <v>17.454309463501</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G827" t="n">
-        <v>18.1387901306152</v>
+        <v>18.1387920379639</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1928291320801</v>
+        <v>18.1928310394287</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496555328369</v>
+        <v>17.9496593475342</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2381572723389</v>
+        <v>17.2381534576416</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300792694092</v>
+        <v>17.1300811767578</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676685333252</v>
+        <v>17.9676723480225</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667419433594</v>
+        <v>18.0667381286621</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>17.7965526580811</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>18.6365566253662</v>
+        <v>18.6365585327148</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G850" t="n">
-        <v>16.6621894836426</v>
+        <v>16.6621875762939</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>16.1916599273682</v>
+        <v>16.1916618347168</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021240234375</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>13.3131446838379</v>
+        <v>13.3131456375122</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G860" t="n">
-        <v>13.8943843841553</v>
+        <v>13.894383430481</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G864" t="n">
-        <v>13.0732688903809</v>
+        <v>13.0732679367065</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G865" t="n">
-        <v>13.0732688903809</v>
+        <v>13.0732679367065</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G866" t="n">
-        <v>13.0179119110107</v>
+        <v>13.0179128646851</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G867" t="n">
-        <v>13.303918838501</v>
+        <v>13.3039197921753</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009454727173</v>
+        <v>13.1009473800659</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G870" t="n">
-        <v>13.1378507614136</v>
+        <v>13.1378498077393</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>13.7006387710571</v>
+        <v>13.7006378173828</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4756231307983</v>
+        <v>14.4756240844727</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>14.4202671051025</v>
+        <v>14.4202680587769</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G879" t="n">
-        <v>13.6914129257202</v>
+        <v>13.6914119720459</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G889" t="n">
-        <v>10.4161748886108</v>
+        <v>10.4161758422852</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>10.5914688110352</v>
+        <v>10.5914697647095</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.9236059188843</v>
+        <v>10.9236068725586</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G894" t="n">
-        <v>10.4807558059692</v>
+        <v>10.4807567596436</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G896" t="n">
-        <v>10.5361137390137</v>
+        <v>10.5361127853394</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.3700437545776</v>
+        <v>10.370044708252</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762971878052</v>
+        <v>10.1762981414795</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964221954346</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G908" t="n">
-        <v>10.5176610946655</v>
+        <v>10.5176601409912</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438543319702</v>
+        <v>10.4438524246216</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G912" t="n">
-        <v>10.6652784347534</v>
+        <v>10.6652774810791</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.9640998840332</v>
+        <v>9.96410083770752</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G917" t="n">
-        <v>10.120943069458</v>
+        <v>10.1209421157837</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G921" t="n">
-        <v>9.21217918395996</v>
+        <v>9.21218013763428</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964221954346</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G927" t="n">
-        <v>9.20295333862305</v>
+        <v>9.20295429229736</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.625</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88004398345947</v>
+        <v>8.88004302978516</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447154998779</v>
+        <v>9.24447059631348</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G935" t="n">
-        <v>9.21217918395996</v>
+        <v>9.21218013763428</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>9.88106632232666</v>
+        <v>9.88106536865234</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G937" t="n">
-        <v>9.97332668304443</v>
+        <v>9.97332572937012</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G942" t="n">
-        <v>10.4346284866333</v>
+        <v>10.434627532959</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>10.5176610946655</v>
+        <v>10.5176601409912</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>10.084038734436</v>
+        <v>10.0840396881104</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G954" t="n">
-        <v>9.56738185882568</v>
+        <v>9.56738090515137</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>9.39208793640137</v>
+        <v>9.39208698272705</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G958" t="n">
-        <v>9.65041637420654</v>
+        <v>9.65041542053223</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>9.31827831268311</v>
+        <v>9.31827926635742</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G962" t="n">
-        <v>9.81648445129395</v>
+        <v>9.81648349761963</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G964" t="n">
-        <v>9.88106632232666</v>
+        <v>9.88106536865234</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G966" t="n">
-        <v>9.75190162658691</v>
+        <v>9.7519006729126</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G967" t="n">
-        <v>9.49357223510742</v>
+        <v>9.49357318878174</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655851364136</v>
+        <v>10.0655860900879</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822439193726</v>
+        <v>10.5822429656982</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G971" t="n">
-        <v>10.7298612594604</v>
+        <v>10.7298593521118</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>10.2870101928711</v>
+        <v>10.2870111465454</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G973" t="n">
-        <v>10.5084352493286</v>
+        <v>10.5084362030029</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G975" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>10.3515930175781</v>
+        <v>10.3515939712524</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G977" t="n">
-        <v>11.431037902832</v>
+        <v>11.4310369491577</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337007522583</v>
+        <v>12.2337017059326</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>12.0860843658447</v>
+        <v>12.086085319519</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G983" t="n">
-        <v>12.1414413452148</v>
+        <v>12.1414403915405</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>12.1875705718994</v>
+        <v>12.1875715255737</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G986" t="n">
-        <v>11.9661474227905</v>
+        <v>11.9661464691162</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>11.8277559280396</v>
+        <v>11.8277568817139</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G990" t="n">
-        <v>11.8277559280396</v>
+        <v>11.8277568817139</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G991" t="n">
-        <v>11.7354955673218</v>
+        <v>11.7354965209961</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G992" t="n">
-        <v>12.0676326751709</v>
+        <v>12.0676317214966</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>13.5</v>
       </c>
       <c r="G993" t="n">
-        <v>12.4551248550415</v>
+        <v>12.4551258087158</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G995" t="n">
-        <v>13.2485628128052</v>
+        <v>13.2485637664795</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G999" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283153533936</v>
+        <v>13.7283163070679</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.0143213272095</v>
+        <v>14.0143232345581</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.682186126709</v>
+        <v>13.6821851730347</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.7006387710571</v>
+        <v>13.7006378173828</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.4571714401245</v>
+        <v>14.4571704864502</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.1158084869385</v>
+        <v>14.1158094406128</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.682186126709</v>
+        <v>13.6821851730347</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1020" t="n">
-        <v>13.8482542037964</v>
+        <v>13.8482532501221</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>14.1158084869385</v>
+        <v>14.1158094406128</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.9312887191772</v>
+        <v>13.9312896728516</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.64732837677</v>
+        <v>15.6473274230957</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303609848022</v>
+        <v>15.7303619384766</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.791353225708</v>
+        <v>16.7913551330566</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.8651638031006</v>
+        <v>16.865161895752</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.8190326690674</v>
+        <v>16.8190307617188</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.997917175293</v>
+        <v>15.9979162216187</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333333969116</v>
+        <v>15.9333362579346</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.678596496582</v>
+        <v>14.6785955429077</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.3187808990479</v>
+        <v>14.3187818527222</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247257232666</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247257232666</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.8538913726807</v>
+        <v>14.8538904190063</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506084442139</v>
+        <v>15.2506113052368</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.9830551147461</v>
+        <v>14.9830541610718</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.1583480834961</v>
+        <v>15.1583490371704</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.0753145217896</v>
+        <v>15.0753154754639</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.8538913726807</v>
+        <v>14.8538904190063</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>12.6027412414551</v>
+        <v>12.6027421951294</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399541854858</v>
+        <v>12.0399551391602</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>12.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>11.3018732070923</v>
+        <v>11.301872253418</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.6006946563721</v>
+        <v>10.6006956100464</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.97589349746704</v>
+        <v>7.97589445114136</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285945892334</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.55047273635864</v>
+        <v>6.55047369003296</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.01177358627319</v>
+        <v>7.01177453994751</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.47307538986206</v>
+        <v>7.47307586669922</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697746276855</v>
+        <v>8.85697937011719</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.33673095703125</v>
+        <v>9.33673000335693</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.01382160186768</v>
+        <v>9.01382064819336</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1077" t="n">
-        <v>8.395676612854</v>
+        <v>8.39567756652832</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.34954643249512</v>
+        <v>8.34954738616943</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.25728607177734</v>
+        <v>8.25728702545166</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.11889743804932</v>
+        <v>8.118896484375</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.929762840271</v>
+        <v>7.92976331710815</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675937652588</v>
+        <v>7.78675985336304</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285945892334</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1088" t="n">
-        <v>7.47307538986206</v>
+        <v>7.47307586669922</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>7.42694568634033</v>
+        <v>7.42694520950317</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.42694568634033</v>
+        <v>7.42694520950317</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.3346848487854</v>
+        <v>7.33468437194824</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.11326026916504</v>
+        <v>7.1132607460022</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.93437719345093</v>
+        <v>7.93437576293945</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.33929824829102</v>
+        <v>7.33929777145386</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920461654663</v>
+        <v>7.51920509338379</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.30700635910034</v>
+        <v>7.3070068359375</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403394699097</v>
+        <v>7.10403442382812</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.15939044952393</v>
+        <v>7.15939092636108</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.30700635910034</v>
+        <v>7.3070068359375</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874050140381</v>
+        <v>6.92874002456665</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533432006836</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533432006836</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217798233032</v>
+        <v>7.72217750549316</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.69091033935547</v>
+        <v>8.69090843200684</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420576095581</v>
+        <v>10.9420566558838</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.82570934295654</v>
+        <v>9.82571029663086</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.82570934295654</v>
+        <v>9.82571029663086</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.74267768859863</v>
+        <v>9.74267578125</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.4623050689697</v>
+        <v>10.462306022644</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5084352493286</v>
+        <v>10.5084362030029</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.1947498321533</v>
+        <v>10.194751739502</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1134" t="n">
-        <v>10.019455909729</v>
+        <v>10.0194549560547</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1135" t="n">
-        <v>9.89029121398926</v>
+        <v>9.89029216766357</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1136" t="n">
-        <v>10.5361137390137</v>
+        <v>10.5361127853394</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792715072632</v>
+        <v>10.3792695999146</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.5176610946655</v>
+        <v>10.5176601409912</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.3700437545776</v>
+        <v>10.370044708252</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.5361137390137</v>
+        <v>10.5361127853394</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.5453395843506</v>
+        <v>10.5453405380249</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667636871338</v>
+        <v>10.7667646408081</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1147" t="n">
-        <v>12.0215015411377</v>
+        <v>12.021502494812</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.4402637481689</v>
+        <v>11.4402627944946</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>11.8093042373657</v>
+        <v>11.8093032836914</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.8185300827026</v>
+        <v>11.818531036377</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.7078170776367</v>
+        <v>11.7078161239624</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.8185300827026</v>
+        <v>11.818531036377</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616888046265</v>
+        <v>11.6616868972778</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.5694284439087</v>
+        <v>11.5694274902344</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.2741947174072</v>
+        <v>11.2741956710815</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.1450309753418</v>
+        <v>11.1450300216675</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961782455444</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.2854681015015</v>
+        <v>13.2854661941528</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4423093795776</v>
+        <v>13.4423084259033</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.1286249160767</v>
+        <v>13.1286239624023</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.5437955856323</v>
+        <v>13.543794631958</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500499725342</v>
+        <v>13.3500490188599</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714750289917</v>
+        <v>13.5714731216431</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>13.3685007095337</v>
+        <v>13.368501663208</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>14.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.1470766067505</v>
+        <v>13.1470775604248</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.1101732254028</v>
+        <v>13.1101722717285</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>13.1286249160767</v>
+        <v>13.1286239624023</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1192" t="n">
-        <v>13.2670154571533</v>
+        <v>13.267014503479</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1195" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.3869533538818</v>
+        <v>13.3869543075562</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.5104808807373</v>
+        <v>12.5104818344116</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1204" t="n">
-        <v>12.335186958313</v>
+        <v>12.3351879119873</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1206" t="n">
-        <v>13.3869533538818</v>
+        <v>13.3869543075562</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1208" t="n">
-        <v>13.5068912506104</v>
+        <v>13.5068922042847</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330835342407</v>
+        <v>13.433084487915</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.4515342712402</v>
+        <v>13.4515361785889</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1211" t="n">
-        <v>14.1158084869385</v>
+        <v>14.1158094406128</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735197067261</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>15.3613204956055</v>
+        <v>15.3613214492798</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>16</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.7616300582886</v>
+        <v>14.7616291046143</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1223" t="n">
-        <v>14.7154998779297</v>
+        <v>14.7154989242554</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1226" t="n">
-        <v>13.9128351211548</v>
+        <v>13.9128360748291</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1227" t="n">
-        <v>13.3869533538818</v>
+        <v>13.3869543075562</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1228" t="n">
-        <v>13.8482542037964</v>
+        <v>13.8482532501221</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>13.6545076370239</v>
+        <v>13.6545085906982</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735197067261</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1235" t="n">
-        <v>15.6750068664551</v>
+        <v>15.6750059127808</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.4166774749756</v>
+        <v>15.416675567627</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G1237" t="n">
-        <v>15.1029939651489</v>
+        <v>15.1029949188232</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.582745552063</v>
+        <v>15.5827445983887</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.8133945465088</v>
+        <v>15.8133964538574</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410720825195</v>
+        <v>15.8410749435425</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>15.924108505249</v>
+        <v>15.9241094589233</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.1178550720215</v>
+        <v>16.1178531646729</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>15.8502988815308</v>
+        <v>15.8502998352051</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351291656494</v>
+        <v>15.4351282119751</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919704437256</v>
+        <v>15.5919713973999</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>15.8133945465088</v>
+        <v>15.8133964538574</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517869949341</v>
+        <v>15.9517889022827</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>16.0717258453369</v>
+        <v>16.0717239379883</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>16.5145721435547</v>
+        <v>16.5145740509033</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.4648532867432</v>
+        <v>17.4648551940918</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1267" t="n">
-        <v>17.5386619567871</v>
+        <v>17.5386600494385</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.4464015960693</v>
+        <v>17.4463996887207</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.621696472168</v>
+        <v>17.6216983795166</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.036865234375</v>
+        <v>18.0368671417236</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.7657203674316</v>
+        <v>18.7657222747803</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1279" t="n">
-        <v>19.4484481811523</v>
+        <v>19.448450088501</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1282" t="n">
-        <v>19.1901187896729</v>
+        <v>19.1901206970215</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="n">
-        <v>18.2029342651367</v>
+        <v>18.2029361724854</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.1829376220703</v>
+        <v>21.1829395294189</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G1303" t="n">
-        <v>22.2900619506836</v>
+        <v>22.290060043335</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="n">
-        <v>21.2013893127441</v>
+        <v>21.2013912200928</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4633102416992</v>
+        <v>20.4633083343506</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.8728446960449</v>
+        <v>19.8728466033936</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>20.8508033752441</v>
+        <v>20.8508014678955</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1318" t="n">
-        <v>21.0906791687012</v>
+        <v>21.0906810760498</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.1091327667236</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.1091327667236</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.9466533660889</v>
+        <v>19.9466514587402</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="n">
-        <v>19.6145172119141</v>
+        <v>19.6145153045654</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.8543930053711</v>
+        <v>19.8543910980225</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1331" t="n">
-        <v>20.8323497772217</v>
+        <v>20.8323516845703</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="n">
-        <v>22.5483894348145</v>
+        <v>22.5483913421631</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317344665527</v>
+        <v>22.0317325592041</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846755981445</v>
+        <v>23.7846775054932</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="n">
-        <v>23.729320526123</v>
+        <v>23.7293186187744</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1343" t="n">
-        <v>24.3935928344727</v>
+        <v>24.3935947418213</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>23.8953895568848</v>
+        <v>23.8953876495361</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>22.9174308776855</v>
+        <v>22.9174327850342</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1347" t="n">
-        <v>23.3049221038818</v>
+        <v>23.3049240112305</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.1388568878174</v>
+        <v>23.1388549804688</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="n">
-        <v>22.5852928161621</v>
+        <v>22.5852909088135</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>23.8953895568848</v>
+        <v>23.8953876495361</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662220001221</v>
+        <v>23.7662258148193</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="n">
-        <v>23.6370601654053</v>
+        <v>23.6370620727539</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="n">
-        <v>23.729320526123</v>
+        <v>23.7293186187744</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>27.1614017486572</v>
+        <v>27.1613998413086</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="n">
-        <v>27.3828258514404</v>
+        <v>27.3828239440918</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935359954834</v>
+        <v>27.4935340881348</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>28.0470943450928</v>
+        <v>28.04709815979</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="n">
-        <v>28.0470943450928</v>
+        <v>28.04709815979</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721118927002</v>
+        <v>27.2721099853516</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>27.3828258514404</v>
+        <v>27.3828239440918</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>27.4012775421143</v>
+        <v>27.4012756347656</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="n">
-        <v>26.9030685424805</v>
+        <v>26.9030723571777</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="n">
-        <v>26.4971256256104</v>
+        <v>26.497127532959</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.4971256256104</v>
+        <v>26.497127532959</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1384" t="n">
-        <v>26.644739151001</v>
+        <v>26.6447410583496</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>25.5007133483887</v>
+        <v>25.5007152557373</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1392" t="n">
-        <v>26.2572498321533</v>
+        <v>26.2572479248047</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>25.9620170593262</v>
+        <v>25.9620132446289</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="n">
-        <v>25.4453601837158</v>
+        <v>25.4453582763672</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1403" t="n">
-        <v>26.7370014190674</v>
+        <v>26.737003326416</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>26.8292636871338</v>
+        <v>26.8292617797852</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G1408" t="n">
-        <v>26.5340309143066</v>
+        <v>26.534029006958</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1409" t="n">
-        <v>25.426908493042</v>
+        <v>25.4269065856934</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>27.5</v>
       </c>
       <c r="G1410" t="n">
-        <v>25.3715515136719</v>
+        <v>25.3715534210205</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750823974609</v>
+        <v>27.4750862121582</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="n">
-        <v>28.914342880249</v>
+        <v>28.9143409729004</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>30.4643115997314</v>
+        <v>30.4643154144287</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="n">
-        <v>30.9625225067139</v>
+        <v>30.9625205993652</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>29.2999992370605</v>
       </c>
       <c r="G1419" t="n">
-        <v>27.0322341918945</v>
+        <v>27.0322360992432</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>26.8846187591553</v>
+        <v>26.8846168518066</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923583984375</v>
+        <v>26.7923564910889</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="n">
-        <v>27.1798515319824</v>
+        <v>27.1798496246338</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167530059814</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="n">
-        <v>27.364372253418</v>
+        <v>27.3643703460693</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="n">
-        <v>26.6262893676758</v>
+        <v>26.6262912750244</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167530059814</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="n">
-        <v>27.2536582946777</v>
+        <v>27.2536602020264</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>27.3090152740479</v>
+        <v>27.3090171813965</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.6744651794434</v>
+        <v>28.674467086792</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286464691162</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286464691162</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G1445" t="n">
-        <v>27.6965084075928</v>
+        <v>27.6965065002441</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.8256702423096</v>
+        <v>27.8256721496582</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732913970947</v>
+        <v>27.9732875823975</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="n">
-        <v>27.7887687683105</v>
+        <v>27.7887668609619</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>26.294153213501</v>
+        <v>26.2941551208496</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="n">
-        <v>26.8846187591553</v>
+        <v>26.8846168518066</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>26.2203464508057</v>
+        <v>26.220344543457</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191688537598</v>
+        <v>25.5191669464111</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="n">
-        <v>24.9656066894531</v>
+        <v>24.9656047821045</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.7108707427979</v>
+        <v>23.7108669281006</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="n">
-        <v>23.729320526123</v>
+        <v>23.7293186187744</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1469" t="n">
-        <v>23.3049221038818</v>
+        <v>23.3049240112305</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="n">
-        <v>24.2090721130371</v>
+        <v>24.2090740203857</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>25.0947723388672</v>
+        <v>25.0947704315186</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="n">
-        <v>24.910249710083</v>
+        <v>24.9102516174316</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179893493652</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="n">
-        <v>25.1870288848877</v>
+        <v>25.1870307922363</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>25.1870288848877</v>
+        <v>25.1870307922363</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179893493652</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G1483" t="n">
-        <v>24.670373916626</v>
+        <v>24.6703758239746</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="n">
-        <v>25.5376205444336</v>
+        <v>25.537618637085</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="n">
-        <v>24.910249710083</v>
+        <v>24.9102516174316</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.9287014007568</v>
+        <v>24.9287033081055</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.8364429473877</v>
+        <v>24.8364410400391</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="n">
-        <v>23.8769340515137</v>
+        <v>23.8769359588623</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>23.8769340515137</v>
+        <v>23.8769359588623</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>21.865665435791</v>
+        <v>21.8656635284424</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287601470947</v>
+        <v>21.8287620544434</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841152191162</v>
+        <v>21.8841133117676</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.8508033752441</v>
+        <v>20.8508014678955</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>21.0353221893311</v>
+        <v>21.0353202819824</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="n">
-        <v>20.7031860351562</v>
+        <v>20.7031879425049</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="n">
-        <v>21.4597225189209</v>
+        <v>21.4597187042236</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>21.0353221893311</v>
+        <v>21.0353202819824</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="n">
-        <v>22.6591014862061</v>
+        <v>22.6591033935547</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287601470947</v>
+        <v>21.8287620544434</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.1091327667236</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.7031860351562</v>
+        <v>20.7031879425049</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.3525943756104</v>
+        <v>20.352596282959</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.8323497772217</v>
+        <v>20.8323516845703</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.3525943756104</v>
+        <v>20.352596282959</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="n">
-        <v>22.8620758056641</v>
+        <v>22.8620738983154</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>24.8600006103516</v>
       </c>
       <c r="G1529" t="n">
-        <v>22.9358825683594</v>
+        <v>22.935884475708</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>22.3085155487061</v>
+        <v>22.3085136413574</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>21.0353221893311</v>
+        <v>21.0353202819824</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.9281997680664</v>
+        <v>19.928201675415</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877086639404</v>
+        <v>20.8877048492432</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="n">
-        <v>20.5002136230469</v>
+        <v>20.5002117156982</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.7585430145264</v>
+        <v>20.7585391998291</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="n">
-        <v>20.3710479736328</v>
+        <v>20.3710498809814</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.9871444702148</v>
+        <v>18.9871463775635</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.9871444702148</v>
+        <v>18.9871463775635</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770534515381</v>
+        <v>17.6770496368408</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.1291255950928</v>
+        <v>18.1291275024414</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.06813621521</v>
+        <v>17.0681343078613</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633651733398</v>
+        <v>17.3633670806885</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>15.2321557998657</v>
+        <v>15.2321577072144</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.1583480834961</v>
+        <v>15.1583490371704</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3705463409424</v>
+        <v>15.3705472946167</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.2377948760986</v>
+        <v>16.23779296875</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.3372325897217</v>
+        <v>14.337233543396</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634248733521</v>
+        <v>14.2634239196777</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.6565532684326</v>
+        <v>15.6565542221069</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.0753145217896</v>
+        <v>15.0753154754639</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.4571714401245</v>
+        <v>14.4571704864502</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021240234375</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.9958715438843</v>
+        <v>13.99587059021</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247257232666</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8482542037964</v>
+        <v>13.8482532501221</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.682186126709</v>
+        <v>13.6821851730347</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.2854681015015</v>
+        <v>13.2854661941528</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1614" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.8057136535645</v>
+        <v>12.8057146072388</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1616" t="n">
-        <v>12.713454246521</v>
+        <v>12.7134532928467</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961782455444</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1619" t="n">
-        <v>14.9461507797241</v>
+        <v>14.9461517333984</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.305965423584</v>
+        <v>15.3059644699097</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="n">
-        <v>15.3428678512573</v>
+        <v>15.342869758606</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384092330933</v>
+        <v>15.0384101867676</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>14.7736358642578</v>
+        <v>14.7736368179321</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.9367218017578</v>
+        <v>14.9367227554321</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="n">
-        <v>15.9823875427246</v>
+        <v>15.9823894500732</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>15.5410985946655</v>
+        <v>15.5410995483398</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9823875427246</v>
+        <v>15.9823894500732</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.7809314727783</v>
+        <v>15.780930519104</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.0303554534912</v>
+        <v>16.0303535461426</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.8576755523682</v>
+        <v>15.8576774597168</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="n">
-        <v>13.5456972122192</v>
+        <v>13.5456981658936</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.1427793502808</v>
+        <v>13.1427803039551</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.0180673599243</v>
+        <v>13.0180683135986</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="n">
-        <v>12.7590503692627</v>
+        <v>12.7590494155884</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="n">
-        <v>12.5959634780884</v>
+        <v>12.5959644317627</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="n">
-        <v>12.6247444152832</v>
+        <v>12.6247434616089</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>13.0468482971191</v>
+        <v>13.0468473434448</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="n">
-        <v>12.7974224090576</v>
+        <v>12.7974233627319</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="n">
-        <v>12.2026395797729</v>
+        <v>12.2026405334473</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="n">
-        <v>12.8933544158936</v>
+        <v>12.8933553695679</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1666" t="n">
-        <v>13.1715602874756</v>
+        <v>13.1715593338013</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1667" t="n">
-        <v>13.1715602874756</v>
+        <v>13.1715593338013</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="n">
-        <v>13.0468482971191</v>
+        <v>13.0468473434448</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="n">
-        <v>12.4712514877319</v>
+        <v>12.4712505340576</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1673" t="n">
-        <v>12.7782354354858</v>
+        <v>12.7782363891602</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="n">
-        <v>13.3058652877808</v>
+        <v>13.3058662414551</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="n">
-        <v>12.8933544158936</v>
+        <v>12.8933553695679</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="n">
-        <v>12.480845451355</v>
+        <v>12.4808444976807</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1683" t="n">
-        <v>12.7782354354858</v>
+        <v>12.7782363891602</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="n">
-        <v>12.6247444152832</v>
+        <v>12.6247434616089</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="n">
-        <v>12.2793865203857</v>
+        <v>12.2793855667114</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="n">
-        <v>12.154673576355</v>
+        <v>12.1546745300293</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="n">
-        <v>12.2218255996704</v>
+        <v>12.2218265533447</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1694" t="n">
-        <v>12.3081665039062</v>
+        <v>12.3081655502319</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.1162996292114</v>
+        <v>12.1163005828857</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1697" t="n">
-        <v>11.8476896286011</v>
+        <v>11.8476886749268</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="n">
-        <v>11.4927368164062</v>
+        <v>11.4927377700806</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="n">
-        <v>11.3296518325806</v>
+        <v>11.3296527862549</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1706" t="n">
-        <v>11.7709426879883</v>
+        <v>11.7709436416626</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1711" t="n">
-        <v>11.3680257797241</v>
+        <v>11.3680248260498</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="n">
-        <v>11.2720937728882</v>
+        <v>11.2720928192139</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="n">
-        <v>10.9363279342651</v>
+        <v>10.9363269805908</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>11.4159917831421</v>
+        <v>11.4159908294678</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.2720937728882</v>
+        <v>11.2720928192139</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.8764696121216</v>
+        <v>11.8764686584473</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="n">
-        <v>12.0491485595703</v>
+        <v>12.049147605896</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="n">
-        <v>12.154673576355</v>
+        <v>12.1546745300293</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="n">
-        <v>12.9413223266602</v>
+        <v>12.9413213729858</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="n">
-        <v>10.9267349243164</v>
+        <v>10.9267358779907</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="n">
-        <v>11.895655632019</v>
+        <v>11.8956546783447</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="n">
-        <v>11.7229766845703</v>
+        <v>11.7229776382446</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="n">
-        <v>12.2026395797729</v>
+        <v>12.2026405334473</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.7398633956909</v>
+        <v>12.7398624420166</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.5959634780884</v>
+        <v>12.5959644317627</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.260199546814</v>
+        <v>12.2601985931396</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930475234985</v>
+        <v>12.1930465698242</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="n">
-        <v>12.4136905670166</v>
+        <v>12.4136915206909</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="n">
-        <v>12.7398633956909</v>
+        <v>12.7398624420166</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>12.327353477478</v>
+        <v>12.3273525238037</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1768" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1769" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1772" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="n">
-        <v>12.1162996292114</v>
+        <v>12.1163005828857</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1777" t="n">
-        <v>11.9244346618652</v>
+        <v>11.9244356155396</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.0395545959473</v>
+        <v>12.0395536422729</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1781" t="n">
-        <v>12.3081665039062</v>
+        <v>12.3081655502319</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="n">
-        <v>12.4712514877319</v>
+        <v>12.4712505340576</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1785" t="n">
-        <v>12.8262023925781</v>
+        <v>12.8262033462524</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1787" t="n">
-        <v>13.0852222442627</v>
+        <v>13.0852212905884</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.2364139556885</v>
+        <v>14.2364130020142</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.8143100738525</v>
+        <v>13.8143091201782</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1798" t="n">
-        <v>13.8143100738525</v>
+        <v>13.8143091201782</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1799" t="n">
-        <v>14.1404800415039</v>
+        <v>14.1404809951782</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1800" t="n">
-        <v>14.1980400085449</v>
+        <v>14.1980409622192</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1802" t="n">
-        <v>14.3707189559937</v>
+        <v>14.3707180023193</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1804" t="n">
-        <v>14.1692600250244</v>
+        <v>14.1692609786987</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463148117065</v>
+        <v>14.9463157653809</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="n">
-        <v>14.7736358642578</v>
+        <v>14.7736368179321</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>14.3131589889526</v>
+        <v>14.313159942627</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.3323450088501</v>
+        <v>14.3323459625244</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.3515319824219</v>
+        <v>14.3515329360962</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1821" t="n">
-        <v>16.0879154205322</v>
+        <v>16.0879135131836</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.8288955688477</v>
+        <v>15.8288974761963</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1823" t="n">
-        <v>16.2509994506836</v>
+        <v>16.2510013580322</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1825" t="n">
-        <v>16.7210693359375</v>
+        <v>16.7210712432861</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="n">
-        <v>15.9823875427246</v>
+        <v>15.9823894500732</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1827" t="n">
-        <v>16.3277473449707</v>
+        <v>16.3277454376221</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1830" t="n">
-        <v>16.1454734802246</v>
+        <v>16.1454753875732</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1832" t="n">
-        <v>16.0207633972168</v>
+        <v>16.0207614898682</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>15.25</v>
       </c>
       <c r="G1835" t="n">
-        <v>14.6297369003296</v>
+        <v>14.6297378540039</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1838" t="n">
-        <v>14.1980400085449</v>
+        <v>14.1980409622192</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1844" t="n">
-        <v>13.948616027832</v>
+        <v>13.9486150741577</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1846" t="n">
-        <v>13.939022064209</v>
+        <v>13.9390211105347</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="n">
-        <v>13.5456972122192</v>
+        <v>13.5456981658936</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1853" t="n">
-        <v>13.555290222168</v>
+        <v>13.5552911758423</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>14</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4305782318115</v>
+        <v>13.4305791854858</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1858" t="n">
-        <v>13.3538331985474</v>
+        <v>13.353832244873</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1859" t="n">
-        <v>13.2195272445679</v>
+        <v>13.2195262908936</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>13.75</v>
       </c>
       <c r="G1862" t="n">
-        <v>13.190746307373</v>
+        <v>13.1907472610474</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>13.75</v>
       </c>
       <c r="G1864" t="n">
-        <v>13.190746307373</v>
+        <v>13.1907472610474</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2578983306885</v>
+        <v>13.2579002380371</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1866" t="n">
-        <v>13.0180673599243</v>
+        <v>13.0180683135986</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="n">
-        <v>12.9413223266602</v>
+        <v>12.9413213729858</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1873" t="n">
-        <v>12.8862733840942</v>
+        <v>12.8862724304199</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1874" t="n">
-        <v>12.2768526077271</v>
+        <v>12.2768535614014</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1878" t="n">
-        <v>12.2080488204956</v>
+        <v>12.2080478668213</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1880" t="n">
-        <v>12.7093458175659</v>
+        <v>12.7093448638916</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1885" t="n">
-        <v>11.7165803909302</v>
+        <v>11.7165813446045</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1888" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1894" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1895" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1898" t="n">
-        <v>11.9524850845337</v>
+        <v>11.9524841308594</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1902" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1906" t="n">
-        <v>11.5887994766235</v>
+        <v>11.5887985229492</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1911" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1917" t="n">
-        <v>11.4217004776001</v>
+        <v>11.4216995239258</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1919" t="n">
-        <v>11.4217004776001</v>
+        <v>11.4216995239258</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1922" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>12</v>
       </c>
       <c r="G1923" t="n">
-        <v>11.7952156066895</v>
+        <v>11.7952146530151</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1924" t="n">
-        <v>11.7460689544678</v>
+        <v>11.7460680007935</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1927" t="n">
-        <v>11.7264108657837</v>
+        <v>11.7264099121094</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1929" t="n">
-        <v>11.8738508224487</v>
+        <v>11.8738498687744</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1931" t="n">
-        <v>12.1097545623779</v>
+        <v>12.1097536087036</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1934" t="n">
-        <v>11.5986280441284</v>
+        <v>11.5986289978027</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1935" t="n">
-        <v>11.4020414352417</v>
+        <v>11.402042388916</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1939" t="n">
-        <v>11.2251129150391</v>
+        <v>11.2251138687134</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1941" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1943" t="n">
-        <v>11.8345336914062</v>
+        <v>11.8345327377319</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1945" t="n">
-        <v>12.2473659515381</v>
+        <v>12.2473649978638</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1948" t="n">
-        <v>11.8345336914062</v>
+        <v>11.8345327377319</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1950" t="n">
-        <v>12.2375354766846</v>
+        <v>12.2375364303589</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1951" t="n">
-        <v>12.2670240402222</v>
+        <v>12.2670230865479</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="n">
-        <v>11.8935098648071</v>
+        <v>11.8935089111328</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1962" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1964" t="n">
-        <v>11.3725538253784</v>
+        <v>11.3725528717041</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1965" t="n">
-        <v>11.2251129150391</v>
+        <v>11.2251138687134</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1966" t="n">
-        <v>11.3823823928833</v>
+        <v>11.3823833465576</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1968" t="n">
-        <v>11.0481853485107</v>
+        <v>11.0481843948364</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1973" t="n">
-        <v>10.8614273071289</v>
+        <v>10.8614282608032</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51719,7 +51719,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1975" t="n">
-        <v>10.6746702194214</v>
+        <v>10.6746692657471</v>
       </c>
       <c r="H1975" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1977" t="n">
-        <v>10.6746702194214</v>
+        <v>10.6746692657471</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1981" t="n">
-        <v>11.1563091278076</v>
+        <v>11.1563081741333</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -51901,7 +51901,7 @@
         <v>11.25</v>
       </c>
       <c r="G1982" t="n">
-        <v>11.0580148696899</v>
+        <v>11.0580139160156</v>
       </c>
       <c r="H1982" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1990" t="n">
-        <v>10.0455913543701</v>
+        <v>10.0455923080444</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1992" t="n">
-        <v>9.79985904693604</v>
+        <v>9.79985809326172</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G1993" t="n">
-        <v>9.53938007354736</v>
+        <v>9.53938102722168</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1997" t="n">
-        <v>10.0161037445068</v>
+        <v>10.0161027908325</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2015" t="n">
-        <v>11.1563091278076</v>
+        <v>11.1563081741333</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>11</v>
       </c>
       <c r="G2019" t="n">
-        <v>10.8122806549072</v>
+        <v>10.8122816085815</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G2021" t="n">
-        <v>11.1366500854492</v>
+        <v>11.1366491317749</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2022" t="n">
-        <v>11.0285263061523</v>
+        <v>11.0285272598267</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2024" t="n">
-        <v>11.2742605209351</v>
+        <v>11.2742595672607</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2028" t="n">
-        <v>11.8738508224487</v>
+        <v>11.8738498687744</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2029" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2030" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2032" t="n">
-        <v>11.8935098648071</v>
+        <v>11.8935089111328</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G2034" t="n">
-        <v>12.4341220855713</v>
+        <v>12.4341230392456</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2043" t="n">
-        <v>12.0507793426514</v>
+        <v>12.0507783889771</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>12</v>
       </c>
       <c r="G2046" t="n">
-        <v>11.7952156066895</v>
+        <v>11.7952146530151</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>12</v>
       </c>
       <c r="G2049" t="n">
-        <v>11.7952156066895</v>
+        <v>11.7952146530151</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2050" t="n">
-        <v>11.5887994766235</v>
+        <v>11.5887985229492</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2051" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G2054" t="n">
-        <v>12.0802659988403</v>
+        <v>12.0802669525146</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2061" t="n">
-        <v>11.7264108657837</v>
+        <v>11.7264099121094</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2062" t="n">
-        <v>11.7264108657837</v>
+        <v>11.7264099121094</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2064" t="n">
-        <v>11.706750869751</v>
+        <v>11.7067518234253</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2066" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G2068" t="n">
-        <v>11.7460689544678</v>
+        <v>11.7460680007935</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G2078" t="n">
-        <v>12.2768526077271</v>
+        <v>12.2768535614014</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54423,7 +54423,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2079" t="n">
-        <v>11.9524850845337</v>
+        <v>11.9524841308594</v>
       </c>
       <c r="H2079" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2081" t="n">
-        <v>11.8345336914062</v>
+        <v>11.8345327377319</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2084" t="n">
-        <v>11.5396518707275</v>
+        <v>11.5396528244019</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G2088" t="n">
-        <v>11.5298233032227</v>
+        <v>11.5298223495483</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2090" t="n">
-        <v>10.9695501327515</v>
+        <v>10.9695510864258</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2091" t="n">
-        <v>11.1563091278076</v>
+        <v>11.1563081741333</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2092" t="n">
-        <v>11.2152843475342</v>
+        <v>11.2152833938599</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2094" t="n">
-        <v>11.4315299987793</v>
+        <v>11.431529045105</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -54891,7 +54891,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2097" t="n">
-        <v>12.2080488204956</v>
+        <v>12.2080478668213</v>
       </c>
       <c r="H2097" t="s">
         <v>8</v>
@@ -54917,7 +54917,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2098" t="n">
-        <v>12.1687307357788</v>
+        <v>12.1687316894531</v>
       </c>
       <c r="H2098" t="s">
         <v>8</v>
@@ -54969,7 +54969,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2100" t="n">
-        <v>11.8935098648071</v>
+        <v>11.8935089111328</v>
       </c>
       <c r="H2100" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2109" t="n">
-        <v>11.5986280441284</v>
+        <v>11.5986289978027</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G2110" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55255,7 +55255,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2111" t="n">
-        <v>11.3430652618408</v>
+        <v>11.3430662155151</v>
       </c>
       <c r="H2111" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G2112" t="n">
-        <v>11.3725538253784</v>
+        <v>11.3725528717041</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2116" t="n">
-        <v>11.5396518707275</v>
+        <v>11.5396528244019</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55437,7 +55437,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2118" t="n">
-        <v>11.3430652618408</v>
+        <v>11.3430662155151</v>
       </c>
       <c r="H2118" t="s">
         <v>8</v>
@@ -55463,7 +55463,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2119" t="n">
-        <v>11.8738508224487</v>
+        <v>11.8738498687744</v>
       </c>
       <c r="H2119" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>5.1100001335144</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>35130</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>5.05000019073486</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>4.89499998092651</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>4.8899998664856</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>92598</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>4.96500015258789</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>4.84499979019165</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>4.84999990463257</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>4.84999990463257</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>4.90000009536743</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>78182</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>4.84999990463257</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>4.96500015258789</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>4.96500015258789</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>4.86499977111816</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>114071</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>4.84000015258789</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>4.66499996185303</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>4.84000015258789</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>4.84000015258789</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>4.69999980926514</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>62118</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>4.78999996185303</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>4.66499996185303</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>4.71999979019165</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>97398</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>4.70499992370605</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>4.67999982833862</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>4.6100001335144</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2523965835571</v>
+        <v>13.2523984909058</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G3" t="n">
-        <v>12.9788007736206</v>
+        <v>12.9787998199463</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>12.9788007736206</v>
+        <v>12.9787998199463</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G5" t="n">
-        <v>12.7479524612427</v>
+        <v>12.747950553894</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12.397403717041</v>
+        <v>12.3974046707153</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>12.2606048583984</v>
+        <v>12.2606058120728</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4825611114502</v>
+        <v>11.4825620651245</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>9.79822444915771</v>
+        <v>9.7982234954834</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G14" t="n">
-        <v>9.84952449798584</v>
+        <v>9.84952354431152</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941207885742</v>
+        <v>10.2941217422485</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G17" t="n">
-        <v>10.7814655303955</v>
+        <v>10.7814664840698</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G20" t="n">
-        <v>10.576268196106</v>
+        <v>10.5762691497803</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361179351807</v>
+        <v>10.6361169815063</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1915216445923</v>
+        <v>10.191520690918</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4565696716309</v>
+        <v>10.4565687179565</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0205221176147</v>
+        <v>10.0205240249634</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03728008270264</v>
+        <v>9.03728103637695</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743129730225</v>
+        <v>8.97743225097656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842891693115</v>
+        <v>9.14842987060547</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057823181152</v>
+        <v>9.43057727813721</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082454681396</v>
+        <v>9.90082359313965</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142654418945</v>
+        <v>9.66142463684082</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3454208374023</v>
+        <v>10.3454217910767</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506200790405</v>
+        <v>10.5506191253662</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257213592529</v>
+        <v>10.2257204055786</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0379638671875</v>
+        <v>11.0379648208618</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097156524658</v>
+        <v>10.9097166061401</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442567825317</v>
+        <v>11.9442577362061</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732601165771</v>
+        <v>11.7732582092285</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3799629211426</v>
+        <v>11.3799619674683</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6621122360229</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416585922241</v>
+        <v>11.8416595458984</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.9186067581177</v>
+        <v>11.918607711792</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922063827515</v>
+        <v>12.1922054290771</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>12.1323556900024</v>
+        <v>12.1323566436768</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665554046631</v>
+        <v>12.1665544509888</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178554534912</v>
+        <v>12.2178544998169</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>11.9015083312988</v>
+        <v>11.9015092849731</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5680618286133</v>
+        <v>11.568060874939</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.2859134674072</v>
+        <v>11.2859125137329</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5680618286133</v>
+        <v>11.568060874939</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6621122360229</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160085678101</v>
+        <v>11.8160095214844</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048606872559</v>
+        <v>11.7048587799072</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.6621122360229</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364603042603</v>
+        <v>11.6364593505859</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G78" t="n">
-        <v>11.4740114212036</v>
+        <v>11.4740123748779</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918640136719</v>
+        <v>11.1918630599976</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G80" t="n">
-        <v>11.1063642501831</v>
+        <v>11.1063652038574</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3799629211426</v>
+        <v>11.3799619674683</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G84" t="n">
-        <v>11.3457632064819</v>
+        <v>11.3457641601562</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.055064201355</v>
+        <v>11.0550661087036</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.9866647720337</v>
+        <v>10.9866666793823</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>10.6019172668457</v>
+        <v>10.60191822052</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G92" t="n">
-        <v>10.3553619384766</v>
+        <v>10.3553609848022</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G95" t="n">
-        <v>10.2673063278198</v>
+        <v>10.2673053741455</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92388916015625</v>
+        <v>9.92389011383057</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.003137588501</v>
+        <v>10.0031385421753</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3025274276733</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496938705444</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120302200317</v>
+        <v>11.4120311737061</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302528381348</v>
+        <v>11.1302537918091</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189176559448</v>
+        <v>10.9189186096191</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>11.2359189987183</v>
+        <v>11.2359199523926</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302528381348</v>
+        <v>11.1302537918091</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0069742202759</v>
+        <v>11.0069751739502</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396701812744</v>
+        <v>10.8396692276001</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.9277229309082</v>
+        <v>10.9277238845825</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G112" t="n">
-        <v>10.9101133346558</v>
+        <v>10.9101142883301</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G114" t="n">
-        <v>10.513861656189</v>
+        <v>10.5138626098633</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647783279419</v>
+        <v>10.0647792816162</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.99433326721191</v>
+        <v>9.99433422088623</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G117" t="n">
-        <v>9.9503059387207</v>
+        <v>9.95030498504639</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>11</v>
       </c>
       <c r="G118" t="n">
-        <v>9.68613719940186</v>
+        <v>9.68613815307617</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.0383596420288</v>
+        <v>10.0383605957031</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522228240967</v>
+        <v>10.452223777771</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843076705933</v>
+        <v>10.5843067169189</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G124" t="n">
-        <v>9.87985992431641</v>
+        <v>9.87986087799072</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733097076416</v>
+        <v>9.67733192443848</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>9.93269348144531</v>
+        <v>9.932692527771</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G130" t="n">
-        <v>9.9855260848999</v>
+        <v>9.98552703857422</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>9.68613719940186</v>
+        <v>9.68613815307617</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019298553467</v>
+        <v>9.14019203186035</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G134" t="n">
-        <v>9.72135925292969</v>
+        <v>9.721360206604</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0823879241943</v>
+        <v>10.082389831543</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G136" t="n">
-        <v>10.3817777633667</v>
+        <v>10.381778717041</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496938705444</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496938705444</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G144" t="n">
-        <v>10.2673063278198</v>
+        <v>10.2673053741455</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.3025274276733</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893636703491</v>
+        <v>10.9893627166748</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9277229309082</v>
+        <v>10.9277238845825</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.0950298309326</v>
+        <v>11.0950307846069</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>11.3151693344116</v>
+        <v>11.3151702880859</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>10.9013071060181</v>
+        <v>10.9013090133667</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654758453369</v>
+        <v>11.1654739379883</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G167" t="n">
-        <v>11.1214466094971</v>
+        <v>11.1214456558228</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302528381348</v>
+        <v>11.1302537918091</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>11.1830854415894</v>
+        <v>11.183084487915</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>11.5265045166016</v>
+        <v>11.5265035629272</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.7994775772095</v>
+        <v>11.7994756698608</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>13.25</v>
       </c>
       <c r="G178" t="n">
-        <v>11.6673946380615</v>
+        <v>11.6673936843872</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472541809082</v>
+        <v>11.4472532272339</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>11.3239765167236</v>
+        <v>11.3239755630493</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680019378662</v>
+        <v>11.3680038452148</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>11.1390571594238</v>
+        <v>11.1390562057495</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472541809082</v>
+        <v>11.4472532272339</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G187" t="n">
-        <v>11.8258934020996</v>
+        <v>11.8258943557739</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>12.0548391342163</v>
+        <v>12.054838180542</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303392410278</v>
+        <v>12.5303382873535</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837839126587</v>
+        <v>12.283784866333</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G195" t="n">
-        <v>12.6007852554321</v>
+        <v>12.6007843017578</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>12.9177846908569</v>
+        <v>12.9177856445312</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>12.8561477661133</v>
+        <v>12.856146812439</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>13.4108982086182</v>
+        <v>13.4108972549438</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782032012939</v>
+        <v>13.5782041549683</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G202" t="n">
-        <v>13.6838703155518</v>
+        <v>13.6838693618774</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285097122192</v>
+        <v>13.4285087585449</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>14.3707065582275</v>
+        <v>14.3707056045532</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G206" t="n">
-        <v>14.256233215332</v>
+        <v>14.2562341690063</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.1329545974731</v>
+        <v>14.1329555511475</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241502761841</v>
+        <v>14.1241512298584</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>13.7807321548462</v>
+        <v>13.7807312011719</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G216" t="n">
-        <v>13.1995639801025</v>
+        <v>13.1995649337769</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>13.3756761550903</v>
+        <v>13.375675201416</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486473083496</v>
+        <v>13.6486492156982</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285097122192</v>
+        <v>13.4285087585449</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>13.8775939941406</v>
+        <v>13.8775930404663</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>14.176983833313</v>
+        <v>14.1769847869873</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>14.0977325439453</v>
+        <v>14.0977334976196</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G226" t="n">
-        <v>14.7845668792725</v>
+        <v>14.7845697402954</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040962219238</v>
+        <v>15.3040981292725</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.277681350708</v>
+        <v>15.2776794433594</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657379150391</v>
+        <v>15.3657369613647</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G232" t="n">
-        <v>15.4449863433838</v>
+        <v>15.4449872970581</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G235" t="n">
-        <v>15.6651277542114</v>
+        <v>15.6651248931885</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>15.2424573898315</v>
+        <v>15.2424564361572</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.277681350708</v>
+        <v>15.2776794433594</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G241" t="n">
-        <v>16.3695735931396</v>
+        <v>16.369571685791</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.4664363861084</v>
+        <v>16.4664325714111</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.5104637145996</v>
+        <v>16.510461807251</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.5104637145996</v>
+        <v>16.510461807251</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387992858887</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G247" t="n">
-        <v>17.1532688140869</v>
+        <v>17.1532669067383</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>16.2374877929688</v>
+        <v>16.237491607666</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947681427002</v>
+        <v>16.9947700500488</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538761138916</v>
+        <v>16.8538780212402</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.0123767852783</v>
+        <v>17.0123825073242</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>17.1532688140869</v>
+        <v>17.1532669067383</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G260" t="n">
-        <v>17.2941570281982</v>
+        <v>17.2941589355469</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G261" t="n">
-        <v>17.1268501281738</v>
+        <v>17.1268520355225</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387992858887</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>16.8626823425293</v>
+        <v>16.8626842498779</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>17.3469924926758</v>
+        <v>17.3469944000244</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551876068115</v>
+        <v>17.6551895141602</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G271" t="n">
-        <v>17.7168273925781</v>
+        <v>17.7168254852295</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>17.55832862854</v>
+        <v>17.5583248138428</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432422637939</v>
+        <v>17.7432441711426</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>17.8401031494141</v>
+        <v>17.8401050567627</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>17.5759334564209</v>
+        <v>17.5759353637695</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482147216797</v>
+        <v>16.7482109069824</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G279" t="n">
-        <v>16.7658195495605</v>
+        <v>16.7658252716064</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G281" t="n">
-        <v>17.1620750427246</v>
+        <v>17.162073135376</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>16.6865730285645</v>
+        <v>16.6865749359131</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092433929443</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>16.8626823425293</v>
+        <v>16.8626842498779</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G290" t="n">
-        <v>17.2325172424316</v>
+        <v>17.2325210571289</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>17.2853527069092</v>
+        <v>17.2853507995605</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.391019821167</v>
+        <v>17.3910217285156</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092433929443</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G295" t="n">
-        <v>17.2853527069092</v>
+        <v>17.2853507995605</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734073638916</v>
+        <v>17.3734092712402</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G299" t="n">
-        <v>17.6463832855225</v>
+        <v>17.6463813781738</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>22</v>
       </c>
       <c r="G301" t="n">
-        <v>19.3722743988037</v>
+        <v>19.3722763061523</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962505340576</v>
+        <v>20.5962524414062</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8340034484863</v>
+        <v>20.8340015411377</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>21.0453357696533</v>
+        <v>21.0453338623047</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>21.0893650054932</v>
+        <v>21.0893630981445</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>21.327112197876</v>
+        <v>21.3271141052246</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G311" t="n">
-        <v>21.6529178619385</v>
+        <v>21.6529197692871</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>21.917085647583</v>
+        <v>21.9170875549316</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>25</v>
       </c>
       <c r="G315" t="n">
-        <v>22.0139484405518</v>
+        <v>22.0139503479004</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.2869205474854</v>
+        <v>22.286922454834</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605056762695</v>
+        <v>22.2605075836182</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221435546875</v>
+        <v>22.3221454620361</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>22.1900596618652</v>
+        <v>22.1900615692139</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>22.6303386688232</v>
+        <v>22.6303405761719</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G323" t="n">
-        <v>22.4806423187256</v>
+        <v>22.4806461334229</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G325" t="n">
-        <v>22.4806423187256</v>
+        <v>22.4806461334229</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743679046631</v>
+        <v>22.6743659973145</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945083618164</v>
+        <v>22.8945064544678</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G329" t="n">
-        <v>23.0970363616943</v>
+        <v>23.0970344543457</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>22.3749771118164</v>
+        <v>22.374979019165</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>25</v>
       </c>
       <c r="G332" t="n">
-        <v>22.0139484405518</v>
+        <v>22.0139503479004</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>23.9159545898438</v>
+        <v>23.9159526824951</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417602539062</v>
+        <v>24.2417621612549</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>24.7084560394287</v>
+        <v>24.7084541320801</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>28</v>
       </c>
       <c r="G339" t="n">
-        <v>24.6556224822998</v>
+        <v>24.6556243896484</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.9197902679443</v>
+        <v>24.919792175293</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870971679688</v>
+        <v>25.0870952606201</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>24.9638175964355</v>
+        <v>24.9638195037842</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255428314209</v>
+        <v>26.4255466461182</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>31</v>
       </c>
       <c r="G347" t="n">
-        <v>27.6287307739258</v>
+        <v>27.6287326812744</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G349" t="n">
-        <v>27.6732921600342</v>
+        <v>27.6732940673828</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>29.3666725158691</v>
+        <v>29.3666706085205</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>32.560001373291</v>
       </c>
       <c r="G354" t="n">
-        <v>29.0190830230713</v>
+        <v>29.0190811157227</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>33.0900001525879</v>
       </c>
       <c r="G355" t="n">
-        <v>29.4914455413818</v>
+        <v>29.4914436340332</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746795654297</v>
+        <v>29.8746776580811</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024787902832</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400913238525</v>
+        <v>30.2400951385498</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G361" t="n">
-        <v>30.6678943634033</v>
+        <v>30.6678981781006</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283157348633</v>
+        <v>30.8283195495605</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996181488037</v>
+        <v>30.8996200561523</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154819488525</v>
+        <v>31.0154800415039</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.9976539611816</v>
+        <v>30.9976501464844</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.9352626800537</v>
+        <v>30.9352684020996</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.685718536377</v>
+        <v>30.6857223510742</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G370" t="n">
-        <v>29.3577556610107</v>
+        <v>29.3577537536621</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>29.5003528594971</v>
+        <v>29.5003547668457</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G372" t="n">
-        <v>29.3131942749023</v>
+        <v>29.3131923675537</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.1687889099121</v>
+        <v>30.168794631958</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331424713135</v>
+        <v>30.1331462860107</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G377" t="n">
-        <v>29.9281539916992</v>
+        <v>29.9281578063965</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.4825325012207</v>
+        <v>29.4825344085693</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>29.8122959136963</v>
+        <v>29.8122940063477</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.126033782959</v>
+        <v>29.1260318756104</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544059753418</v>
+        <v>27.2544097900391</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>27.4861316680908</v>
+        <v>27.4861335754395</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>28.11891746521</v>
+        <v>28.1189155578613</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178573608398</v>
+        <v>27.7178554534912</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734577178955</v>
+        <v>28.5734596252441</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>32</v>
       </c>
       <c r="G394" t="n">
-        <v>28.5199794769287</v>
+        <v>28.5199813842773</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855529785156</v>
+        <v>29.7855548858643</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G398" t="n">
-        <v>29.5360069274902</v>
+        <v>29.536003112793</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.1705951690674</v>
+        <v>29.1705932617188</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221092224121</v>
+        <v>29.3221054077148</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>32.5</v>
       </c>
       <c r="G404" t="n">
-        <v>28.9656085968018</v>
+        <v>28.9656028747559</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>32.5</v>
       </c>
       <c r="G406" t="n">
-        <v>28.9656085968018</v>
+        <v>28.9656028747559</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477825164795</v>
+        <v>28.9477787017822</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>33</v>
       </c>
       <c r="G413" t="n">
-        <v>29.4112281799316</v>
+        <v>29.4112319946289</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>33</v>
       </c>
       <c r="G415" t="n">
-        <v>29.4112281799316</v>
+        <v>29.4112319946289</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.687520980835</v>
+        <v>29.6875190734863</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>29.6162185668945</v>
+        <v>29.6162204742432</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>29.6786079406738</v>
+        <v>29.6786041259766</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964321136475</v>
+        <v>29.6964282989502</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390293121338</v>
+        <v>29.8390350341797</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>33.8699989318848</v>
       </c>
       <c r="G422" t="n">
-        <v>30.1866130828857</v>
+        <v>30.1866188049316</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>29.8122959136963</v>
+        <v>29.8122940063477</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.5181789398193</v>
+        <v>29.518180847168</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G425" t="n">
-        <v>29.1795101165771</v>
+        <v>29.1795063018799</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648662567139</v>
+        <v>30.3648643493652</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629039764404</v>
+        <v>30.4629096984863</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024787902832</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G430" t="n">
-        <v>30.4718151092529</v>
+        <v>30.4718170166016</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.061840057373</v>
+        <v>30.0618457794189</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>36</v>
       </c>
       <c r="G435" t="n">
-        <v>32.0849800109863</v>
+        <v>32.0849838256836</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>36</v>
       </c>
       <c r="G436" t="n">
-        <v>32.0849800109863</v>
+        <v>32.0849838256836</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>31.4967555999756</v>
+        <v>31.4967517852783</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G438" t="n">
-        <v>30.819408416748</v>
+        <v>30.8194046020508</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>31.9958610534668</v>
+        <v>31.9958553314209</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G440" t="n">
-        <v>31.7730407714844</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G441" t="n">
-        <v>31.7730407714844</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928310394287</v>
+        <v>31.6928272247314</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>35.9900016784668</v>
       </c>
       <c r="G444" t="n">
-        <v>32.0760650634766</v>
+        <v>32.0760688781738</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>36.25</v>
       </c>
       <c r="G446" t="n">
-        <v>32.3077926635742</v>
+        <v>32.3077964782715</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>39</v>
       </c>
       <c r="G449" t="n">
-        <v>34.7587280273438</v>
+        <v>34.7587242126465</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.7319946289062</v>
+        <v>34.731990814209</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>34.2239761352539</v>
+        <v>34.2239799499512</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.4378700256348</v>
+        <v>34.4378814697266</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.4378700256348</v>
+        <v>34.4378814697266</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G457" t="n">
-        <v>34.5448226928711</v>
+        <v>34.5448265075684</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>39.75</v>
       </c>
       <c r="G458" t="n">
-        <v>35.4271697998047</v>
+        <v>35.4271621704102</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>38.8899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>34.6606864929199</v>
+        <v>34.6606903076172</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>38.5699996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>34.37548828125</v>
+        <v>34.3754844665527</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>38</v>
       </c>
       <c r="G462" t="n">
-        <v>33.8674812316895</v>
+        <v>33.8674736022949</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G463" t="n">
-        <v>33.8496513366699</v>
+        <v>33.8496475219727</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G464" t="n">
-        <v>34.1437721252441</v>
+        <v>34.1437683105469</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>38</v>
       </c>
       <c r="G465" t="n">
-        <v>33.8674812316895</v>
+        <v>33.8674736022949</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>38.6199989318848</v>
       </c>
       <c r="G471" t="n">
-        <v>34.4200477600098</v>
+        <v>34.420051574707</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>38.8400001525879</v>
       </c>
       <c r="G474" t="n">
-        <v>34.6161270141602</v>
+        <v>34.6161308288574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041915893555</v>
+        <v>34.3041877746582</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081237792969</v>
+        <v>34.1081161499023</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>38.25</v>
       </c>
       <c r="G478" t="n">
-        <v>34.0902900695801</v>
+        <v>34.0902862548828</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>36.4966583251953</v>
+        <v>36.4966621398926</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G484" t="n">
-        <v>37.4146537780762</v>
+        <v>37.4146499633789</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.858470916748</v>
+        <v>38.8584747314453</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>43.3300018310547</v>
       </c>
       <c r="G487" t="n">
-        <v>38.6178359985352</v>
+        <v>38.6178398132324</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>44</v>
       </c>
       <c r="G491" t="n">
-        <v>39.214973449707</v>
+        <v>39.2149772644043</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.805004119873</v>
+        <v>38.8050003051758</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>43.0299987792969</v>
       </c>
       <c r="G494" t="n">
-        <v>38.3504600524902</v>
+        <v>38.3504638671875</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>38.0563545227051</v>
+        <v>38.0563507080078</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>38.3682823181152</v>
+        <v>38.3682861328125</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.3415489196777</v>
+        <v>38.341552734375</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>43.2200012207031</v>
       </c>
       <c r="G498" t="n">
-        <v>38.5198059082031</v>
+        <v>38.5198020935059</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.6891403198242</v>
+        <v>38.689136505127</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>44.25</v>
       </c>
       <c r="G504" t="n">
-        <v>39.4377861022949</v>
+        <v>39.4377899169922</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>39.0812873840332</v>
+        <v>39.0812835693359</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545425415039</v>
+        <v>39.0545539855957</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>44.1199989318848</v>
       </c>
       <c r="G507" t="n">
-        <v>39.3219261169434</v>
+        <v>39.3219223022461</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>43.2599983215332</v>
       </c>
       <c r="G508" t="n">
-        <v>38.5554466247559</v>
+        <v>38.5554542541504</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>42.9599990844727</v>
       </c>
       <c r="G509" t="n">
-        <v>38.2880783081055</v>
+        <v>38.2880744934082</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G510" t="n">
-        <v>38.3772087097168</v>
+        <v>38.3772048950195</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G512" t="n">
-        <v>36.6125335693359</v>
+        <v>36.6125259399414</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G514" t="n">
-        <v>38.4663276672363</v>
+        <v>38.4663238525391</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>47.1199989318848</v>
       </c>
       <c r="G515" t="n">
-        <v>41.9956703186035</v>
+        <v>41.9956665039062</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.4234733581543</v>
+        <v>42.423469543457</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G520" t="n">
-        <v>42.0847969055176</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G521" t="n">
-        <v>41.924373626709</v>
+        <v>41.9243698120117</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G525" t="n">
-        <v>42.0847969055176</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G527" t="n">
-        <v>41.924373626709</v>
+        <v>41.9243698120117</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G528" t="n">
-        <v>41.6926460266113</v>
+        <v>41.6926498413086</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G536" t="n">
-        <v>39.143669128418</v>
+        <v>39.1436729431152</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>48</v>
       </c>
       <c r="G538" t="n">
-        <v>42.7799682617188</v>
+        <v>42.779972076416</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>38.6802291870117</v>
+        <v>38.6802253723145</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>42.1599998474121</v>
       </c>
       <c r="G541" t="n">
-        <v>37.5750732421875</v>
+        <v>37.5750770568848</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>41.8400001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>37.2898712158203</v>
+        <v>37.2898788452148</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>43.2599983215332</v>
       </c>
       <c r="G543" t="n">
-        <v>38.5554466247559</v>
+        <v>38.5554542541504</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>40.1953468322754</v>
+        <v>40.1953506469727</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>45</v>
       </c>
       <c r="G546" t="n">
-        <v>40.1062202453613</v>
+        <v>40.1062278747559</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>45.5200004577637</v>
       </c>
       <c r="G547" t="n">
-        <v>40.5696716308594</v>
+        <v>40.5696754455566</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G548" t="n">
-        <v>40.801399230957</v>
+        <v>40.8013954162598</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>45.939998626709</v>
       </c>
       <c r="G549" t="n">
-        <v>40.9439964294434</v>
+        <v>40.9439926147461</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G550" t="n">
-        <v>40.801399230957</v>
+        <v>40.8013954162598</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400756835938</v>
+        <v>41.1400718688965</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G553" t="n">
-        <v>40.5161933898926</v>
+        <v>40.5161972045898</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>45.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>40.9618225097656</v>
+        <v>40.9618263244629</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793212890625</v>
+        <v>39.1793251037598</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131690979004</v>
+        <v>40.2131729125977</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914222717285</v>
+        <v>40.3914260864258</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>42.6017265319824</v>
+        <v>42.6017189025879</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446434020996</v>
+        <v>44.5446472167969</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G563" t="n">
-        <v>43.9029502868652</v>
+        <v>43.9029426574707</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>50.75</v>
       </c>
       <c r="G564" t="n">
-        <v>45.2309112548828</v>
+        <v>45.2309074401855</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>46.0330352783203</v>
+        <v>46.0330390930176</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253440856934</v>
+        <v>47.3253479003906</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874099731445</v>
+        <v>45.5874061584473</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>50.1500015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>44.6961631774902</v>
+        <v>44.696159362793</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>49.3800010681152</v>
       </c>
       <c r="G572" t="n">
-        <v>44.0099029541016</v>
+        <v>44.0098991394043</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494720458984</v>
+        <v>43.8494758605957</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>41.175724029541</v>
+        <v>41.1757202148438</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G579" t="n">
-        <v>41.157901763916</v>
+        <v>41.1578941345215</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>46.0200004577637</v>
       </c>
       <c r="G580" t="n">
-        <v>41.0153007507324</v>
+        <v>41.0152969360352</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675514221191</v>
+        <v>39.7675476074219</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.108024597168</v>
+        <v>39.1080284118652</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479286193848</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>44.6399993896484</v>
       </c>
       <c r="G585" t="n">
-        <v>39.7853736877441</v>
+        <v>39.7853775024414</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>45.5</v>
       </c>
       <c r="G586" t="n">
-        <v>40.5518455505371</v>
+        <v>40.5518493652344</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7319030761719</v>
+        <v>39.7318992614746</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3040962219238</v>
+        <v>39.3041000366211</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675514221191</v>
+        <v>39.7675476074219</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488212585449</v>
+        <v>40.2488250732422</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G592" t="n">
-        <v>39.4288787841797</v>
+        <v>39.4288749694824</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G593" t="n">
-        <v>39.143669128418</v>
+        <v>39.1436729431152</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479286193848</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.050952911377</v>
+        <v>41.0509452819824</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G601" t="n">
-        <v>40.6366539001465</v>
+        <v>40.6366577148438</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>45</v>
       </c>
       <c r="G602" t="n">
-        <v>40.5285797119141</v>
+        <v>40.5285835266113</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.484432220459</v>
+        <v>37.4844360351562</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316230773926</v>
+        <v>36.3316192626953</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G607" t="n">
-        <v>37.0521278381348</v>
+        <v>37.052131652832</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>40.6399993896484</v>
       </c>
       <c r="G609" t="n">
-        <v>36.6018142700195</v>
+        <v>36.6018104553223</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.0073928833008</v>
+        <v>36.007396697998</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>37.3800010681152</v>
       </c>
       <c r="G615" t="n">
-        <v>33.6657447814941</v>
+        <v>33.6657409667969</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924667358398</v>
+        <v>34.6924705505371</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>38.560001373291</v>
       </c>
       <c r="G620" t="n">
-        <v>34.7284965515137</v>
+        <v>34.7284889221191</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>38.3600006103516</v>
       </c>
       <c r="G621" t="n">
-        <v>34.5483665466309</v>
+        <v>34.5483627319336</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>38.2400016784668</v>
       </c>
       <c r="G626" t="n">
-        <v>34.4402923583984</v>
+        <v>34.4402885437012</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247711181641</v>
+        <v>35.1247749328613</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>33.5036239624023</v>
+        <v>33.5036277770996</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>32.3868446350098</v>
+        <v>32.3868370056152</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G631" t="n">
-        <v>31.4681911468506</v>
+        <v>31.4681930541992</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.4867973327637</v>
+        <v>29.4867935180664</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371128082275</v>
+        <v>29.9371147155762</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.1532649993896</v>
+        <v>30.1532669067383</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G638" t="n">
-        <v>29.2166004180908</v>
+        <v>29.2166042327881</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G641" t="n">
-        <v>29.1265411376953</v>
+        <v>29.1265392303467</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>33.9799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>30.6035804748535</v>
+        <v>30.6035842895508</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520408630371</v>
+        <v>31.2520389556885</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551239013672</v>
+        <v>29.9551219940186</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.6663303375244</v>
+        <v>31.666332244873</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>31.6483211517334</v>
+        <v>31.6483192443848</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601188659668</v>
+        <v>31.3601131439209</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>30.9818496704102</v>
+        <v>30.9818477630615</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G656" t="n">
-        <v>31.7383823394775</v>
+        <v>31.7383861541748</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520408630371</v>
+        <v>31.2520389556885</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G661" t="n">
-        <v>29.9191017150879</v>
+        <v>29.9190998077393</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.901086807251</v>
+        <v>29.9010887145996</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6669216156006</v>
+        <v>29.666919708252</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>29.0905132293701</v>
+        <v>29.0905151367188</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>29.1800003051758</v>
       </c>
       <c r="G670" t="n">
-        <v>26.2805309295654</v>
+        <v>26.2805347442627</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.0550804138184</v>
+        <v>27.055082321167</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>27.1091194152832</v>
+        <v>27.1091175079346</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>27.1091194152832</v>
+        <v>27.1091175079346</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693717956543</v>
+        <v>27.4693698883057</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G682" t="n">
-        <v>27.9377021789551</v>
+        <v>27.9377002716064</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476409912109</v>
+        <v>27.8476390838623</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693717956543</v>
+        <v>27.4693698883057</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>31.1399993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>28.0457763671875</v>
+        <v>28.0457782745361</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G689" t="n">
-        <v>27.7755870819092</v>
+        <v>27.7755889892578</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>28.5501346588135</v>
+        <v>28.5501327514648</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G695" t="n">
-        <v>29.1625652313232</v>
+        <v>29.1625671386719</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G696" t="n">
-        <v>29.2166004180908</v>
+        <v>29.2166042327881</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401977539062</v>
+        <v>28.6401958465576</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762218475342</v>
+        <v>28.6762237548828</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G699" t="n">
-        <v>27.6675090789795</v>
+        <v>27.6675128936768</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.0550804138184</v>
+        <v>27.055082321167</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G703" t="n">
-        <v>27.4513568878174</v>
+        <v>27.4513607025146</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.5594348907471</v>
+        <v>27.5594367980957</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>25.7581653594971</v>
+        <v>25.7581634521484</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320327758789</v>
+        <v>22.7320308685303</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G708" t="n">
-        <v>21.7413330078125</v>
+        <v>21.7413311004639</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233200073242</v>
+        <v>21.7233238220215</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860698699951</v>
+        <v>22.7860660552979</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>26</v>
       </c>
       <c r="G711" t="n">
-        <v>23.4165153503418</v>
+        <v>23.4165134429932</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606155395508</v>
+        <v>23.5606136322021</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>25</v>
       </c>
       <c r="G716" t="n">
-        <v>22.5158786773682</v>
+        <v>22.5158805847168</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369766235352</v>
+        <v>21.2369747161865</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>21.5972290039062</v>
+        <v>21.5972309112549</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>18.2828922271729</v>
+        <v>18.2828941345215</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>18.3909683227539</v>
+        <v>18.3909702301025</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.0036964416504</v>
+        <v>18.003698348999</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2651767730713</v>
+        <v>17.2651748657227</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9502487182617</v>
+        <v>15.9502477645874</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.7160835266113</v>
+        <v>15.716082572937</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800594329834</v>
+        <v>15.6800565719604</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6170148849487</v>
+        <v>15.6170129776001</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077098846436</v>
+        <v>16.6077136993408</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G743" t="n">
-        <v>16.4005641937256</v>
+        <v>16.4005661010742</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>17.4723224639893</v>
+        <v>17.4723205566406</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>16.4906272888184</v>
+        <v>16.490629196167</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G749" t="n">
-        <v>17.6614551544189</v>
+        <v>17.6614570617676</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968444824219</v>
+        <v>16.7968425750732</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4906272888184</v>
+        <v>16.490629196167</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G752" t="n">
-        <v>16.0132942199707</v>
+        <v>16.0132923126221</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.905216217041</v>
+        <v>15.9052171707153</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>16.1934223175049</v>
+        <v>16.1934185028076</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250900268555</v>
+        <v>15.7250890731812</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>15.4008617401123</v>
+        <v>15.400860786438</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496110916138</v>
+        <v>15.0496120452881</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800594329834</v>
+        <v>15.6800565719604</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G760" t="n">
-        <v>14.7524032592773</v>
+        <v>14.7524042129517</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899934768677</v>
+        <v>15.5899925231934</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>15.1486825942993</v>
+        <v>15.1486835479736</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639053344727</v>
+        <v>15.4639043807983</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G767" t="n">
-        <v>17.643440246582</v>
+        <v>17.6434421539307</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.3912620544434</v>
+        <v>17.391263961792</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G771" t="n">
-        <v>18.2288570404053</v>
+        <v>18.2288551330566</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G772" t="n">
-        <v>18.0307159423828</v>
+        <v>18.0307178497314</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G774" t="n">
-        <v>17.9226379394531</v>
+        <v>17.9226398468018</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.454309463501</v>
+        <v>17.4543075561523</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791725158691</v>
+        <v>18.6791706085205</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G783" t="n">
-        <v>18.7872467041016</v>
+        <v>18.7872486114502</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G784" t="n">
-        <v>18.6971874237061</v>
+        <v>18.6971855163574</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>19.9699993133545</v>
       </c>
       <c r="G790" t="n">
-        <v>17.9856834411621</v>
+        <v>17.9856815338135</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G792" t="n">
-        <v>17.7245006561279</v>
+        <v>17.7244987487793</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>18.3009071350098</v>
+        <v>18.3009052276611</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6071224212646</v>
+        <v>18.607120513916</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>19.3996829986572</v>
+        <v>19.3996810913086</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698722839355</v>
+        <v>19.6698741912842</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>20.2462787628174</v>
+        <v>20.2462768554688</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>19.4176921844482</v>
+        <v>19.4176940917969</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537200927734</v>
+        <v>19.4537220001221</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G808" t="n">
-        <v>17.5083465576172</v>
+        <v>17.5083446502686</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508815765381</v>
+        <v>16.8508834838867</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490245819092</v>
+        <v>17.0490226745605</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462333679199</v>
+        <v>17.3462352752686</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G817" t="n">
-        <v>17.2741832733154</v>
+        <v>17.2741813659668</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>17.3822555541992</v>
+        <v>17.3822593688965</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.976676940918</v>
+        <v>17.9766750335693</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G823" t="n">
-        <v>17.6164207458496</v>
+        <v>17.6164226531982</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6614551544189</v>
+        <v>17.6614570617676</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.454309463501</v>
+        <v>17.4543075561523</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G827" t="n">
-        <v>18.1387901306152</v>
+        <v>18.1387920379639</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496593475342</v>
+        <v>17.9496574401855</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3822555541992</v>
+        <v>17.3822593688965</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667419433594</v>
+        <v>18.0667400360107</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G844" t="n">
-        <v>17.5894069671631</v>
+        <v>17.5894050598145</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>18.6365566253662</v>
+        <v>18.6365585327148</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G850" t="n">
-        <v>16.6621894836426</v>
+        <v>16.6621913909912</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G851" t="n">
-        <v>17.2249755859375</v>
+        <v>17.2249774932861</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G852" t="n">
-        <v>16.5330257415771</v>
+        <v>16.5330276489258</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>16.1916618347168</v>
+        <v>16.1916599273682</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.684232711792</v>
+        <v>15.6842317581177</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232385635376</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021240234375</v>
+        <v>13.8021230697632</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G857" t="n">
-        <v>13.9405145645142</v>
+        <v>13.9405136108398</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G860" t="n">
-        <v>13.894383430481</v>
+        <v>13.8943843841553</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>15</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G864" t="n">
-        <v>13.0732679367065</v>
+        <v>13.0732688903809</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G865" t="n">
-        <v>13.0732679367065</v>
+        <v>13.0732688903809</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G866" t="n">
-        <v>13.0179128646851</v>
+        <v>13.0179119110107</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009464263916</v>
+        <v>13.1009454727173</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G873" t="n">
-        <v>14.475622177124</v>
+        <v>14.4756231307983</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>14.5771102905273</v>
+        <v>14.577109336853</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G876" t="n">
-        <v>13.8298025131226</v>
+        <v>13.8298015594482</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>13.7928981781006</v>
+        <v>13.7928991317749</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15</v>
       </c>
       <c r="G880" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.5125274658203</v>
+        <v>14.512526512146</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G887" t="n">
-        <v>10.2132015228271</v>
+        <v>10.2132024765015</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G888" t="n">
-        <v>10.4069480895996</v>
+        <v>10.4069490432739</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G890" t="n">
-        <v>10.4069480895996</v>
+        <v>10.4069490432739</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.9236068725586</v>
+        <v>10.9236059188843</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837291717529</v>
+        <v>10.6837282180786</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G897" t="n">
-        <v>10.296236038208</v>
+        <v>10.2962369918823</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>10.0471343994141</v>
+        <v>10.0471353530884</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762981414795</v>
+        <v>10.1762971878052</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964221954346</v>
+        <v>9.65964126586914</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G906" t="n">
-        <v>10.5730171203613</v>
+        <v>10.573016166687</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3054628372192</v>
+        <v>10.3054618835449</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438524246216</v>
+        <v>10.4438533782959</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>10.056360244751</v>
+        <v>10.0563611984253</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964221954346</v>
+        <v>9.65964126586914</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G927" t="n">
-        <v>9.20295333862305</v>
+        <v>9.20295429229736</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>8.9861421585083</v>
+        <v>8.98614120483398</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447059631348</v>
+        <v>9.24447154998779</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G933" t="n">
-        <v>9.28137588500977</v>
+        <v>9.28137493133545</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G937" t="n">
-        <v>9.97332668304443</v>
+        <v>9.97332572937012</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>10.2408819198608</v>
+        <v>10.2408809661865</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>10.2132015228271</v>
+        <v>10.2132024765015</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G942" t="n">
-        <v>10.434627532959</v>
+        <v>10.4346284866333</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>10.084038734436</v>
+        <v>10.0840377807617</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G945" t="n">
-        <v>10.1024904251099</v>
+        <v>10.1024894714355</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886806488037</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886806488037</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G953" t="n">
-        <v>9.79803276062012</v>
+        <v>9.7980318069458</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G954" t="n">
-        <v>9.56738185882568</v>
+        <v>9.56738090515137</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G956" t="n">
-        <v>9.26292324066162</v>
+        <v>9.2629222869873</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G959" t="n">
-        <v>9.28137588500977</v>
+        <v>9.28137493133545</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>9.31827831268311</v>
+        <v>9.31827926635742</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G966" t="n">
-        <v>9.7519006729126</v>
+        <v>9.75190162658691</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G968" t="n">
-        <v>10.2777843475342</v>
+        <v>10.2777853012085</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655860900879</v>
+        <v>10.0655851364136</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G973" t="n">
-        <v>10.5084362030029</v>
+        <v>10.5084352493286</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G975" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G977" t="n">
-        <v>11.431037902832</v>
+        <v>11.4310369491577</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>12.1875715255737</v>
+        <v>12.1875705718994</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>11.8277559280396</v>
+        <v>11.8277549743652</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G990" t="n">
-        <v>11.8277559280396</v>
+        <v>11.8277549743652</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G991" t="n">
-        <v>11.7354965209961</v>
+        <v>11.7354955673218</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G992" t="n">
-        <v>12.0676317214966</v>
+        <v>12.0676326751709</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G994" t="n">
-        <v>13.2577886581421</v>
+        <v>13.2577877044678</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G996" t="n">
-        <v>13.0824956893921</v>
+        <v>13.0824947357178</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G998" t="n">
-        <v>13.40540599823</v>
+        <v>13.4054050445557</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.0143213272095</v>
+        <v>14.0143222808838</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.1342611312866</v>
+        <v>14.1342601776123</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.6821870803833</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.6821870803833</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.0512266159058</v>
+        <v>14.0512256622314</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0327739715576</v>
+        <v>14.0327749252319</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.9312887191772</v>
+        <v>13.9312877655029</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6473255157471</v>
+        <v>15.6473264694214</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303619384766</v>
+        <v>15.7303609848022</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.0865879058838</v>
+        <v>17.0865859985352</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.7452220916748</v>
+        <v>16.7452239990234</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1033" t="n">
-        <v>16.1086292266846</v>
+        <v>16.1086273193359</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.997917175293</v>
+        <v>15.9979152679443</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333343505859</v>
+        <v>15.9333333969116</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720344543457</v>
+        <v>15.4720325469971</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.6785945892334</v>
+        <v>14.6785955429077</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247257232666</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247257232666</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506093978882</v>
+        <v>15.2506084442139</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399560928345</v>
+        <v>12.0399551391602</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.6006946563721</v>
+        <v>10.6006956100464</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.4254007339478</v>
+        <v>10.4254016876221</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.79803276062012</v>
+        <v>9.7980318069458</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G1062" t="n">
-        <v>9.30905246734619</v>
+        <v>9.30905342102051</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.9758939743042</v>
+        <v>7.97589349746704</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.5504732131958</v>
+        <v>6.55047273635864</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.93796586990356</v>
+        <v>6.93796634674072</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409605026245</v>
+        <v>6.98409652709961</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>8.72999954223633</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.05431461334229</v>
+        <v>8.05431365966797</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697841644287</v>
+        <v>8.85697746276855</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.40029048919678</v>
+        <v>8.40028953552246</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.11889553070068</v>
+        <v>8.118896484375</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.92976331710815</v>
+        <v>7.92976379394531</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675889968872</v>
+        <v>7.78675937652588</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.10966968536377</v>
+        <v>8.10967063903809</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.842116355896</v>
+        <v>7.84211587905884</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.28855514526367</v>
+        <v>7.28855466842651</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1092" t="n">
-        <v>7.26087713241577</v>
+        <v>7.26087665557861</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1093" t="n">
-        <v>7.32545948028564</v>
+        <v>7.32545900344849</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.33468532562256</v>
+        <v>7.3346848487854</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.1132607460022</v>
+        <v>7.11326026916504</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.77753400802612</v>
+        <v>7.77753353118896</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.3392972946167</v>
+        <v>7.33929777145386</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920557022095</v>
+        <v>7.51920509338379</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403490066528</v>
+        <v>7.10403442382812</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.06713056564331</v>
+        <v>7.06713008880615</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874002456665</v>
+        <v>6.92874050140381</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1109" t="n">
-        <v>7.26087713241577</v>
+        <v>7.26087665557861</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533479690552</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533479690552</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.54227018356323</v>
+        <v>7.54227066040039</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010250091553</v>
+        <v>7.27010297775269</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217750549316</v>
+        <v>7.72217798233032</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948623657227</v>
+        <v>8.46948528289795</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.66784477233887</v>
+        <v>8.66784572601318</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310764312744</v>
+        <v>8.90310859680176</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.54329395294189</v>
+        <v>8.54329299926758</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.8754301071167</v>
+        <v>8.87542915344238</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1122" t="n">
-        <v>9.32750415802002</v>
+        <v>9.32750511169434</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.4956197738647</v>
+        <v>11.4956188201904</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>11.2557420730591</v>
+        <v>11.2557430267334</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.74267673492432</v>
+        <v>9.74267768859863</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.462306022644</v>
+        <v>10.4623050689697</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5084362030029</v>
+        <v>10.5084352493286</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.1947507858276</v>
+        <v>10.1947498321533</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792724609375</v>
+        <v>10.3792715072632</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.360818862915</v>
+        <v>10.3608198165894</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.2224283218384</v>
+        <v>10.2224292755127</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.5453395843506</v>
+        <v>10.5453405380249</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667646408081</v>
+        <v>10.7667636871338</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616878509521</v>
+        <v>11.6616888046265</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.5694274902344</v>
+        <v>11.5694284439087</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.3480033874512</v>
+        <v>11.3480043411255</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.7042284011841</v>
+        <v>12.7042274475098</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.0548152923584</v>
+        <v>13.0548162460327</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.0548152923584</v>
+        <v>13.0548162460327</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961801528931</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4423084259033</v>
+        <v>13.4423093795776</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.2577886581421</v>
+        <v>13.2577877044678</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.0086879730225</v>
+        <v>13.0086870193481</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.5437965393066</v>
+        <v>13.5437955856323</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>15</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714731216431</v>
+        <v>13.5714740753174</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>14.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.1470766067505</v>
+        <v>13.1470756530762</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1191" t="n">
-        <v>13.1655282974243</v>
+        <v>13.1655292510986</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.0455904006958</v>
+        <v>13.0455913543701</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.1747541427612</v>
+        <v>13.1747550964355</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.3813161849976</v>
+        <v>12.3813180923462</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6304197311401</v>
+        <v>12.6304187774658</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.40540599823</v>
+        <v>13.4054050445557</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330825805664</v>
+        <v>13.4330835342407</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1211" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>15.2690601348877</v>
+        <v>15.269061088562</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735177993774</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628067016602</v>
+        <v>15.4628057479858</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232385635376</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.5125274658203</v>
+        <v>14.512526512146</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1221" t="n">
-        <v>14.5217542648315</v>
+        <v>14.5217533111572</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>14.3556861877441</v>
+        <v>14.3556852340698</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1226" t="n">
-        <v>13.9128360748291</v>
+        <v>13.9128351211548</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1231" t="n">
-        <v>14.4110403060913</v>
+        <v>14.4110412597656</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1232" t="n">
-        <v>14.6509189605713</v>
+        <v>14.650918006897</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735177993774</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1234" t="n">
-        <v>15.1860275268555</v>
+        <v>15.1860265731812</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1235" t="n">
-        <v>15.6750049591064</v>
+        <v>15.6750068664551</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184722900391</v>
+        <v>14.9184713363647</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1239" t="n">
-        <v>15.3889989852905</v>
+        <v>15.3889999389648</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764921188354</v>
+        <v>15.7764911651611</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827465057373</v>
+        <v>15.5827474594116</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547565460205</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.8133974075317</v>
+        <v>15.8133964538574</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410749435425</v>
+        <v>15.8410739898682</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G1249" t="n">
-        <v>15.8779783248901</v>
+        <v>15.8779773712158</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>15.6381015777588</v>
+        <v>15.6381034851074</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351282119751</v>
+        <v>15.4351272583008</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919713973999</v>
+        <v>15.5919723510742</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>15.8133974075317</v>
+        <v>15.8133964538574</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>15.6381015777588</v>
+        <v>15.6381034851074</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517879486084</v>
+        <v>15.9517869949341</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.0994052886963</v>
+        <v>16.0994033813477</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.3910465240479</v>
+        <v>17.3910446166992</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.0865879058838</v>
+        <v>17.0865859985352</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.446403503418</v>
+        <v>17.4464015960693</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1270" t="n">
-        <v>17.3725929260254</v>
+        <v>17.372594833374</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.621696472168</v>
+        <v>17.6216945648193</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.5478858947754</v>
+        <v>17.547887802124</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.0368671417236</v>
+        <v>18.036865234375</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.415132522583</v>
+        <v>18.4151306152344</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="n">
-        <v>19.2454738616943</v>
+        <v>19.245475769043</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377361297607</v>
+        <v>19.3377342224121</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>18.5443000793457</v>
+        <v>18.5442981719971</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1287" t="n">
-        <v>18.5627517700195</v>
+        <v>18.5627498626709</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>18.4704895019531</v>
+        <v>18.4704914093018</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="n">
-        <v>17.9722843170166</v>
+        <v>17.972282409668</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.1844825744629</v>
+        <v>18.1844844818115</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.6109256744385</v>
+        <v>20.6109237670898</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>22.7698154449463</v>
+        <v>22.7698135375977</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745826721191</v>
+        <v>22.4745845794678</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="n">
-        <v>20.7216377258301</v>
+        <v>20.7216396331787</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>20.6847343444824</v>
+        <v>20.6847362518311</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="n">
-        <v>21.2013893127441</v>
+        <v>21.2013912200928</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1315" t="n">
-        <v>19.8728466033936</v>
+        <v>19.8728446960449</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>20.8508014678955</v>
+        <v>20.8508033752441</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1318" t="n">
-        <v>21.0906791687012</v>
+        <v>21.0906810760498</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.1091289520264</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.1091289520264</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="n">
-        <v>20.2234344482422</v>
+        <v>20.2234325408936</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.9466533660889</v>
+        <v>19.9466514587402</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.112720489502</v>
+        <v>20.1127223968506</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.2162532806396</v>
+        <v>22.2162551879883</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="n">
-        <v>22.1424465179443</v>
+        <v>22.1424446105957</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="n">
-        <v>22.2531585693359</v>
+        <v>22.2531604766846</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317306518555</v>
+        <v>22.0317325592041</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846794128418</v>
+        <v>23.7846755981445</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="n">
-        <v>23.7293186187744</v>
+        <v>23.729320526123</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>23.8953876495361</v>
+        <v>23.8953895568848</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>23.0465927124023</v>
+        <v>23.046594619751</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>22.9174308776855</v>
+        <v>22.9174327850342</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817012786865</v>
+        <v>23.5817031860352</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.1388549804688</v>
+        <v>23.1388568878174</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="n">
-        <v>22.5852947235107</v>
+        <v>22.5852928161621</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>23.8953876495361</v>
+        <v>23.8953895568848</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662258148193</v>
+        <v>23.7662239074707</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G1361" t="n">
-        <v>22.7144603729248</v>
+        <v>22.7144584655762</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="n">
-        <v>23.7293186187744</v>
+        <v>23.729320526123</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>27.16139793396</v>
+        <v>27.1613998413086</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935340881348</v>
+        <v>27.4935359954834</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="n">
-        <v>28.1578102111816</v>
+        <v>28.1578121185303</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721099853516</v>
+        <v>27.2721118927002</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="n">
-        <v>27.1060447692871</v>
+        <v>27.1060428619385</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>25.9251117706299</v>
+        <v>25.9251136779785</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="n">
-        <v>25.7221412658691</v>
+        <v>25.7221393585205</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="n">
-        <v>25.9989223480225</v>
+        <v>25.9989204406738</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="n">
-        <v>25.7221412658691</v>
+        <v>25.7221393585205</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="n">
-        <v>26.1280841827393</v>
+        <v>26.1280860900879</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>25.9620151519775</v>
+        <v>25.9620170593262</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>25.9989223480225</v>
+        <v>25.9989204406738</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="n">
-        <v>26.3310565948486</v>
+        <v>26.3310585021973</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="n">
-        <v>26.5155773162842</v>
+        <v>26.5155754089355</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="n">
-        <v>25.9251117706299</v>
+        <v>25.9251136779785</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="n">
-        <v>26.1280841827393</v>
+        <v>26.1280860900879</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="n">
-        <v>25.4453601837158</v>
+        <v>25.4453582763672</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>26.7185478210449</v>
+        <v>26.7185497283936</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>26.8292636871338</v>
+        <v>26.8292617797852</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="n">
-        <v>26.5155773162842</v>
+        <v>26.5155754089355</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>30.4643135070801</v>
+        <v>30.4643154144287</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>26.8846168518066</v>
+        <v>26.8846187591553</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1421" t="n">
-        <v>27.3459205627441</v>
+        <v>27.3459186553955</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923603057861</v>
+        <v>26.7923583984375</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="n">
-        <v>27.1798496246338</v>
+        <v>27.1798534393311</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994789123535</v>
+        <v>27.8994808197021</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>27.5857963562012</v>
+        <v>27.5857982635498</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="n">
-        <v>27.2352085113525</v>
+        <v>27.2352066040039</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="n">
-        <v>27.3643741607666</v>
+        <v>27.364372253418</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>27.7703151702881</v>
+        <v>27.7703170776367</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>27.9548377990723</v>
+        <v>27.9548358917236</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.674467086792</v>
+        <v>28.6744651794434</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.3423290252686</v>
+        <v>28.3423309326172</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="n">
-        <v>27.050687789917</v>
+        <v>27.0506858825684</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="n">
-        <v>27.7518634796143</v>
+        <v>27.7518653869629</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.8256721496582</v>
+        <v>27.8256702423096</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732875823975</v>
+        <v>27.9732894897461</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="n">
-        <v>27.7887668609619</v>
+        <v>27.7887687683105</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>26.294153213501</v>
+        <v>26.2941513061523</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="n">
-        <v>26.8846168518066</v>
+        <v>26.8846187591553</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191669464111</v>
+        <v>25.5191688537598</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.7108688354492</v>
+        <v>23.7108707427979</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="n">
-        <v>23.7293186187744</v>
+        <v>23.729320526123</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="n">
-        <v>24.0614585876465</v>
+        <v>24.0614566802979</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="n">
-        <v>24.2090740203857</v>
+        <v>24.2090721130371</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="n">
-        <v>24.7441806793213</v>
+        <v>24.7441825866699</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179893493652</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="n">
-        <v>25.1870307922363</v>
+        <v>25.1870288848877</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>25.1870307922363</v>
+        <v>25.1870288848877</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179893493652</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="n">
-        <v>25.537618637085</v>
+        <v>25.5376205444336</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1486" t="n">
-        <v>24.8733463287354</v>
+        <v>24.8733444213867</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.8364429473877</v>
+        <v>24.8364410400391</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>23.1573085784912</v>
+        <v>23.1573047637939</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="n">
-        <v>22.7698154449463</v>
+        <v>22.7698135375977</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.8508014678955</v>
+        <v>20.8508033752441</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.7364978790283</v>
+        <v>21.736499786377</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="n">
-        <v>22.6591014862061</v>
+        <v>22.6591033935547</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.1091289520264</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525943756104</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525943756104</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.529935836792</v>
+        <v>22.5299396514893</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>22.5114841461182</v>
+        <v>22.5114860534668</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.529935836792</v>
+        <v>22.5299396514893</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="n">
-        <v>22.8620758056641</v>
+        <v>22.8620738983154</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>22.5114841461182</v>
+        <v>22.5114860534668</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674583435059</v>
+        <v>21.3674564361572</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877048492432</v>
+        <v>20.8877067565918</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="n">
-        <v>20.7216377258301</v>
+        <v>20.7216396331787</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1551" t="n">
-        <v>20.4448566436768</v>
+        <v>20.4448585510254</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1552" t="n">
-        <v>20.278787612915</v>
+        <v>20.2787895202637</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="n">
-        <v>20.8138961791992</v>
+        <v>20.8138980865479</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>20.2049808502197</v>
+        <v>20.2049789428711</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.758544921875</v>
+        <v>20.7585430145264</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="n">
-        <v>20.0204601287842</v>
+        <v>20.0204620361328</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.5073947906494</v>
+        <v>18.5073909759521</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770515441895</v>
+        <v>17.6770534515381</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.0681343078613</v>
+        <v>17.06813621521</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633670806885</v>
+        <v>17.3633651733398</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.0845403671265</v>
+        <v>15.0845413208008</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>15.23215675354</v>
+        <v>15.2321577072144</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3705472946167</v>
+        <v>15.3705463409424</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.2377910614014</v>
+        <v>16.23779296875</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.337233543396</v>
+        <v>14.3372325897217</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878213882446</v>
+        <v>14.6878223419189</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G1584" t="n">
-        <v>14.6509189605713</v>
+        <v>14.650918006897</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1587" t="n">
-        <v>14.6601448059082</v>
+        <v>14.6601438522339</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.1860275268555</v>
+        <v>15.1860265731812</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1591" t="n">
-        <v>15.1860275268555</v>
+        <v>15.1860265731812</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021240234375</v>
+        <v>13.8021230697632</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G1595" t="n">
-        <v>13.8298025131226</v>
+        <v>13.8298015594482</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.0327739715576</v>
+        <v>14.0327749252319</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247257232666</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="n">
-        <v>13.6176042556763</v>
+        <v>13.617603302002</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.8298025131226</v>
+        <v>13.8298015594482</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>15</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.6821870803833</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1617" t="n">
-        <v>13.3592739105225</v>
+        <v>13.3592748641968</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961801528931</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476369857788</v>
+        <v>15.0476360321045</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="n">
-        <v>15.3428688049316</v>
+        <v>15.3428678512573</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384111404419</v>
+        <v>15.0384101867676</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="n">
-        <v>15.9823884963989</v>
+        <v>15.9823875427246</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>15.5410995483398</v>
+        <v>15.5410985946655</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9823884963989</v>
+        <v>15.9823875427246</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.8576765060425</v>
+        <v>15.8576755523682</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1637" t="n">
-        <v>15.6466245651245</v>
+        <v>15.6466236114502</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="n">
-        <v>14.5529918670654</v>
+        <v>14.5529909133911</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1646" t="n">
-        <v>13.0660352706909</v>
+        <v>13.0660343170166</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="n">
-        <v>12.7590494155884</v>
+        <v>12.7590503692627</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1657" t="n">
-        <v>11.9724016189575</v>
+        <v>11.9724006652832</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1662" t="n">
-        <v>12.6823043823242</v>
+        <v>12.6823034286499</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="n">
-        <v>12.2026405334473</v>
+        <v>12.2026395797729</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="n">
-        <v>12.8933553695679</v>
+        <v>12.8933544158936</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="n">
-        <v>12.4712505340576</v>
+        <v>12.4712514877319</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1675" t="n">
-        <v>13.0372543334961</v>
+        <v>13.0372552871704</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="n">
-        <v>12.8933553695679</v>
+        <v>12.8933544158936</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1681" t="n">
-        <v>12.1738586425781</v>
+        <v>12.1738595962524</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="n">
-        <v>12.2793855667114</v>
+        <v>12.2793865203857</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="n">
-        <v>12.2506065368652</v>
+        <v>12.2506055831909</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="n">
-        <v>12.1546726226807</v>
+        <v>12.154673576355</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.1163005828857</v>
+        <v>12.1162996292114</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1700" t="n">
-        <v>11.4639587402344</v>
+        <v>11.4639577865601</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1701" t="n">
-        <v>11.4639587402344</v>
+        <v>11.4639577865601</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>12.1354866027832</v>
+        <v>12.1354856491089</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1705" t="n">
-        <v>11.7421636581421</v>
+        <v>11.7421627044678</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1707" t="n">
-        <v>11.7421636581421</v>
+        <v>11.7421627044678</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="n">
-        <v>10.9363269805908</v>
+        <v>10.9363279342651</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.9459218978882</v>
+        <v>10.9459209442139</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>10.8499889373779</v>
+        <v>10.8499898910522</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1716" t="n">
-        <v>10.9459218978882</v>
+        <v>10.9459209442139</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.9555139541626</v>
+        <v>10.9555149078369</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="n">
-        <v>11.1090068817139</v>
+        <v>11.1090059280396</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1722" t="n">
-        <v>11.6558237075806</v>
+        <v>11.6558227539062</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1725" t="n">
-        <v>11.5311126708984</v>
+        <v>11.5311117172241</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1727" t="n">
-        <v>11.7613506317139</v>
+        <v>11.7613496780396</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="n">
-        <v>12.049147605896</v>
+        <v>12.0491485595703</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1731" t="n">
-        <v>11.9724016189575</v>
+        <v>11.9724006652832</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1732" t="n">
-        <v>11.9628076553345</v>
+        <v>11.9628086090088</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="n">
-        <v>12.1546726226807</v>
+        <v>12.154673576355</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1736" t="n">
-        <v>13.0372543334961</v>
+        <v>13.0372552871704</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="n">
-        <v>12.9413213729858</v>
+        <v>12.9413223266602</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="n">
-        <v>13.2003402709961</v>
+        <v>13.2003412246704</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="n">
-        <v>11.6941967010498</v>
+        <v>11.6941957473755</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="n">
-        <v>10.9267358779907</v>
+        <v>10.9267349243164</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="n">
-        <v>11.8956546783447</v>
+        <v>11.895655632019</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="n">
-        <v>11.7229776382446</v>
+        <v>11.7229766845703</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="n">
-        <v>12.2026405334473</v>
+        <v>12.2026395797729</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.2601985931396</v>
+        <v>12.260199546814</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930456161499</v>
+        <v>12.1930465698242</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.2506065368652</v>
+        <v>12.2506055831909</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="n">
-        <v>12.4136915206909</v>
+        <v>12.4136905670166</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G1762" t="n">
-        <v>12.7686443328857</v>
+        <v>12.7686433792114</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="n">
-        <v>12.1163005828857</v>
+        <v>12.1162996292114</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.0395545959473</v>
+        <v>12.0395536422729</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1780" t="n">
-        <v>12.1738586425781</v>
+        <v>12.1738595962524</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="n">
-        <v>12.4712505340576</v>
+        <v>12.4712514877319</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1794" t="n">
-        <v>14.2172269821167</v>
+        <v>14.2172260284424</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.7855291366577</v>
+        <v>13.7855281829834</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1800" t="n">
-        <v>14.1980409622192</v>
+        <v>14.1980400085449</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>14.2939720153809</v>
+        <v>14.2939729690552</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463148117065</v>
+        <v>14.9463157653809</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>15</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.3899059295654</v>
+        <v>14.3899049758911</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1811" t="n">
-        <v>14.4474658966064</v>
+        <v>14.4474649429321</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1812" t="n">
-        <v>14.2172269821167</v>
+        <v>14.2172260284424</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1816" t="n">
-        <v>14.5242109298706</v>
+        <v>14.5242118835449</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1818" t="n">
-        <v>14.6009588241577</v>
+        <v>14.6009578704834</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G1820" t="n">
-        <v>14.3611259460449</v>
+        <v>14.3611268997192</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.828896522522</v>
+        <v>15.8288974761963</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1824" t="n">
-        <v>16.3373413085938</v>
+        <v>16.3373394012451</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="n">
-        <v>15.9823884963989</v>
+        <v>15.9823875427246</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1827" t="n">
-        <v>16.3277454376221</v>
+        <v>16.3277473449707</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1834" t="n">
-        <v>16.0783214569092</v>
+        <v>16.0783195495605</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1836" t="n">
-        <v>14.5242109298706</v>
+        <v>14.5242118835449</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48157,7 +48157,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1838" t="n">
-        <v>14.1980409622192</v>
+        <v>14.1980400085449</v>
       </c>
       <c r="H1838" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="n">
-        <v>14.5529918670654</v>
+        <v>14.5529909133911</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.1308870315552</v>
+        <v>14.1308879852295</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1853" t="n">
-        <v>13.5552911758423</v>
+        <v>13.555290222168</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>13.459358215332</v>
+        <v>13.4593572616577</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>14</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4305782318115</v>
+        <v>13.4305791854858</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1858" t="n">
-        <v>13.353832244873</v>
+        <v>13.3538331985474</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1859" t="n">
-        <v>13.2195262908936</v>
+        <v>13.2195272445679</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>13.75</v>
       </c>
       <c r="G1862" t="n">
-        <v>13.1907472610474</v>
+        <v>13.190746307373</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>13.75</v>
       </c>
       <c r="G1864" t="n">
-        <v>13.1907472610474</v>
+        <v>13.190746307373</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2579002380371</v>
+        <v>13.2578992843628</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="n">
-        <v>12.9413213729858</v>
+        <v>12.9413223266602</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -71652,7 +71652,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="D2742" t="n">
-        <v>4.59999990463257</v>
+        <v>4.58500003814697</v>
       </c>
       <c r="E2742" t="n">
         <v>4.67000007629395</v>
@@ -71664,6 +71664,32 @@
         <v>4.58500003814697</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>109163</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>4.57999992370605</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2523984909058</v>
+        <v>13.2523975372314</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G5" t="n">
-        <v>12.747950553894</v>
+        <v>12.747953414917</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12.3974046707153</v>
+        <v>12.397403717041</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G7" t="n">
-        <v>12.2435054779053</v>
+        <v>12.2435064315796</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>12.2606058120728</v>
+        <v>12.2606067657471</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409063339233</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4825620651245</v>
+        <v>11.4825630187988</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>12.25</v>
       </c>
       <c r="G15" t="n">
-        <v>10.473669052124</v>
+        <v>10.4736680984497</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941217422485</v>
+        <v>10.2941207885742</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G17" t="n">
-        <v>10.7814664840698</v>
+        <v>10.7814655303955</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>10.8156652450562</v>
+        <v>10.8156661987305</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>10.7301664352417</v>
+        <v>10.7301654815674</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5762691497803</v>
+        <v>10.5762672424316</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361169815063</v>
+        <v>10.636118888855</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8156652450562</v>
+        <v>10.8156661987305</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0205240249634</v>
+        <v>10.0205211639404</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03728103637695</v>
+        <v>9.03727912902832</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743225097656</v>
+        <v>8.97743129730225</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9.40492725372314</v>
+        <v>9.40492630004883</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842987060547</v>
+        <v>9.14842891693115</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057727813721</v>
+        <v>9.43057537078857</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082359313965</v>
+        <v>9.90082263946533</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142463684082</v>
+        <v>9.66142654418945</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G34" t="n">
-        <v>10.4394702911377</v>
+        <v>10.4394683837891</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3454217910767</v>
+        <v>10.3454208374023</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>10.2000722885132</v>
+        <v>10.2000732421875</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0037651062012</v>
+        <v>11.0037660598755</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506191253662</v>
+        <v>10.5506181716919</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257204055786</v>
+        <v>10.2257194519043</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G40" t="n">
-        <v>10.1829710006714</v>
+        <v>10.1829700469971</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097166061401</v>
+        <v>10.9097156524658</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732582092285</v>
+        <v>11.7732601165771</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3799619674683</v>
+        <v>11.3799629211426</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6621112823486</v>
+        <v>11.6621103286743</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.918607711792</v>
+        <v>11.9186086654663</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>12.046856880188</v>
+        <v>12.0468559265137</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922054290771</v>
+        <v>12.1922063827515</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G57" t="n">
-        <v>12.200756072998</v>
+        <v>12.2007551193237</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375549316406</v>
+        <v>12.3375558853149</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409063339233</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665544509888</v>
+        <v>12.1665563583374</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178544998169</v>
+        <v>12.2178554534912</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409063339233</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.568060874939</v>
+        <v>11.5680618286133</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>11.8844079971313</v>
+        <v>11.8844089508057</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.568060874939</v>
+        <v>11.5680618286133</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6621112823486</v>
+        <v>11.6621103286743</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160095214844</v>
+        <v>11.8160104751587</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048587799072</v>
+        <v>11.7048597335815</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G75" t="n">
-        <v>11.6022596359253</v>
+        <v>11.6022605895996</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.6621112823486</v>
+        <v>11.6621103286743</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364593505859</v>
+        <v>11.6364603042603</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G78" t="n">
-        <v>11.4740123748779</v>
+        <v>11.4740114212036</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918630599976</v>
+        <v>11.1918649673462</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G80" t="n">
-        <v>11.1063652038574</v>
+        <v>11.1063642501831</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.114914894104</v>
+        <v>11.1149129867554</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3799619674683</v>
+        <v>11.3799629211426</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G84" t="n">
-        <v>11.3457641601562</v>
+        <v>11.3457622528076</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0550661087036</v>
+        <v>11.055064201355</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.9866666793823</v>
+        <v>10.986665725708</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>10.60191822052</v>
+        <v>10.6019172668457</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.4346113204956</v>
+        <v>10.4346122741699</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G92" t="n">
-        <v>10.3553609848022</v>
+        <v>10.3553628921509</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>10.4346113204956</v>
+        <v>10.4346122741699</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G94" t="n">
-        <v>10.22327709198</v>
+        <v>10.2232780456543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92389011383057</v>
+        <v>9.92388916015625</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G97" t="n">
-        <v>10.3201389312744</v>
+        <v>10.3201398849487</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.0031385421753</v>
+        <v>10.003137588501</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>10.6107234954834</v>
+        <v>10.6107244491577</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120311737061</v>
+        <v>11.4120302200317</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189186096191</v>
+        <v>10.9189195632935</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>11.2359199523926</v>
+        <v>11.2359209060669</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0069751739502</v>
+        <v>11.0069742202759</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8308639526367</v>
+        <v>10.8308629989624</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.9277238845825</v>
+        <v>10.9277248382568</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G112" t="n">
-        <v>10.9101142883301</v>
+        <v>10.9101133346558</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G114" t="n">
-        <v>10.5138626098633</v>
+        <v>10.513861656189</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647792816162</v>
+        <v>10.0647783279419</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.99433422088623</v>
+        <v>9.99433135986328</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G117" t="n">
-        <v>9.95030498504639</v>
+        <v>9.9503059387207</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>11</v>
       </c>
       <c r="G118" t="n">
-        <v>9.68613815307617</v>
+        <v>9.68613719940186</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962511062622</v>
+        <v>10.4962501525879</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.75</v>
       </c>
       <c r="G121" t="n">
-        <v>10.3465557098389</v>
+        <v>10.3465566635132</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.452223777771</v>
+        <v>10.4522228240967</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843067169189</v>
+        <v>10.5843076705933</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G125" t="n">
-        <v>9.12258052825928</v>
+        <v>9.12257957458496</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733192443848</v>
+        <v>9.67733287811279</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1880559921265</v>
+        <v>10.1880550384521</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G130" t="n">
-        <v>9.98552703857422</v>
+        <v>9.98552799224854</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>9.68613815307617</v>
+        <v>9.68613719940186</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019203186035</v>
+        <v>9.14019107818604</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>10.082389831543</v>
+        <v>10.0823888778687</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G137" t="n">
-        <v>10.3201389312744</v>
+        <v>10.3201398849487</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>10.2849178314209</v>
+        <v>10.2849168777466</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1528339385986</v>
+        <v>10.1528329849243</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987791061401</v>
+        <v>10.6987781524658</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G148" t="n">
-        <v>11.0157794952393</v>
+        <v>11.0157804489136</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>10.8308639526367</v>
+        <v>10.8308629989624</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893627166748</v>
+        <v>10.9893636703491</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748912811279</v>
+        <v>10.8748922348022</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748912811279</v>
+        <v>10.8748922348022</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9277238845825</v>
+        <v>10.9277248382568</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G157" t="n">
-        <v>11.2535305023193</v>
+        <v>11.253529548645</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>11.3151702880859</v>
+        <v>11.3151712417603</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>11.2535305023193</v>
+        <v>11.253529548645</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G160" t="n">
-        <v>11.0157794952393</v>
+        <v>11.0157804489136</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>11.0510015487671</v>
+        <v>11.0510025024414</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>10.9013090133667</v>
+        <v>10.9013080596924</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654739379883</v>
+        <v>11.1654758453369</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G165" t="n">
-        <v>11.0598077774048</v>
+        <v>11.0598087310791</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>11.183084487915</v>
+        <v>11.1830854415894</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>11.5265035629272</v>
+        <v>11.5265045166016</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>11.7466440200806</v>
+        <v>11.7466430664062</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G174" t="n">
-        <v>11.773060798645</v>
+        <v>11.7730598449707</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G177" t="n">
-        <v>11.6497821807861</v>
+        <v>11.6497812271118</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>13.25</v>
       </c>
       <c r="G178" t="n">
-        <v>11.6673936843872</v>
+        <v>11.6673946380615</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>11.6497821807861</v>
+        <v>11.6497812271118</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680038452148</v>
+        <v>11.3680047988892</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>11.1390562057495</v>
+        <v>11.1390581130981</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G187" t="n">
-        <v>11.8258943557739</v>
+        <v>11.8258934020996</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303382873535</v>
+        <v>12.5303392410278</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.283784866333</v>
+        <v>12.2837839126587</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8121194839478</v>
+        <v>12.8121185302734</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>12.856146812439</v>
+        <v>12.8561477661133</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782041549683</v>
+        <v>13.5782032012939</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G202" t="n">
-        <v>13.6838693618774</v>
+        <v>13.6838712692261</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210102081299</v>
+        <v>14.2210111618042</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241512298584</v>
+        <v>14.1241502761841</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>13.6046199798584</v>
+        <v>13.6046209335327</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631196975708</v>
+        <v>13.7631216049194</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7278985977173</v>
+        <v>13.727897644043</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G216" t="n">
-        <v>13.1995649337769</v>
+        <v>13.1995630264282</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605926513672</v>
+        <v>13.5605936050415</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>13.8775930404663</v>
+        <v>13.877592086792</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>14.1769847869873</v>
+        <v>14.176983833313</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>14.0977334976196</v>
+        <v>14.0977344512939</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G226" t="n">
-        <v>14.7845697402954</v>
+        <v>14.7845678329468</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040981292725</v>
+        <v>15.3040971755981</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.2776794433594</v>
+        <v>15.277681350708</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978199005127</v>
+        <v>15.4978179931641</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G232" t="n">
-        <v>15.4449872970581</v>
+        <v>15.4449892044067</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418472290039</v>
+        <v>15.5418481826782</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>15.2424564361572</v>
+        <v>15.2424573898315</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.2776794433594</v>
+        <v>15.277681350708</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>15.8060169219971</v>
+        <v>15.8060159683228</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G240" t="n">
-        <v>16.1934604644775</v>
+        <v>16.1934585571289</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.4664325714111</v>
+        <v>16.4664363861084</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.510461807251</v>
+        <v>16.5104637145996</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.510461807251</v>
+        <v>16.5104637145996</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.0387992858887</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.889102935791</v>
+        <v>16.8891010284424</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G248" t="n">
-        <v>16.7746276855469</v>
+        <v>16.7746295928955</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>16.237491607666</v>
+        <v>16.2374877929688</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G251" t="n">
-        <v>16.5897121429443</v>
+        <v>16.589714050293</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G252" t="n">
-        <v>16.6513519287109</v>
+        <v>16.6513538360596</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>16.5721015930176</v>
+        <v>16.5720996856689</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947700500488</v>
+        <v>16.9947681427002</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538780212402</v>
+        <v>16.8538799285889</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.0123825073242</v>
+        <v>17.012378692627</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.0387992858887</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>17.2061023712158</v>
+        <v>17.2061061859131</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551895141602</v>
+        <v>17.6551876068115</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G271" t="n">
-        <v>17.7168254852295</v>
+        <v>17.7168273925781</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G272" t="n">
-        <v>17.4526596069336</v>
+        <v>17.452657699585</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>17.5583248138428</v>
+        <v>17.5583267211914</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>17.8401050567627</v>
+        <v>17.8401069641113</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>17.5759353637695</v>
+        <v>17.5759372711182</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482109069824</v>
+        <v>16.7482128143311</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>19.25</v>
       </c>
       <c r="G280" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507427215576</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G281" t="n">
-        <v>17.162073135376</v>
+        <v>17.1620750427246</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G282" t="n">
-        <v>17.2765464782715</v>
+        <v>17.2765483856201</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>16.6865749359131</v>
+        <v>16.6865730285645</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.889102935791</v>
+        <v>16.8891010284424</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G287" t="n">
-        <v>16.8186569213867</v>
+        <v>16.8186550140381</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>19.25</v>
       </c>
       <c r="G288" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507427215576</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>19.25</v>
       </c>
       <c r="G289" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507427215576</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G290" t="n">
-        <v>17.2325210571289</v>
+        <v>17.2325191497803</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3910217285156</v>
+        <v>17.391019821167</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>17.250129699707</v>
+        <v>17.2501335144043</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350471496582</v>
+        <v>17.4350452423096</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>17.9457702636719</v>
+        <v>17.9457721710205</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>22</v>
       </c>
       <c r="G301" t="n">
-        <v>19.3722763061523</v>
+        <v>19.3722743988037</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962524414062</v>
+        <v>20.5962505340576</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>20.3408889770508</v>
+        <v>20.340892791748</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8340015411377</v>
+        <v>20.8340034484863</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824756622314</v>
+        <v>21.5824775695801</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G311" t="n">
-        <v>21.6529197692871</v>
+        <v>21.6529216766357</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497825622559</v>
+        <v>21.7497844696045</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>21.9170875549316</v>
+        <v>21.917085647583</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>25</v>
       </c>
       <c r="G315" t="n">
-        <v>22.0139503479004</v>
+        <v>22.0139484405518</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605075836182</v>
+        <v>22.2605056762695</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G318" t="n">
-        <v>22.348560333252</v>
+        <v>22.3485622406006</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221454620361</v>
+        <v>22.3221473693848</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>22.6303405761719</v>
+        <v>22.6303424835205</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G323" t="n">
-        <v>22.4806461334229</v>
+        <v>22.4806480407715</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G324" t="n">
-        <v>22.6655616760254</v>
+        <v>22.665563583374</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G325" t="n">
-        <v>22.4806461334229</v>
+        <v>22.4806480407715</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>25.6900005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>22.6215343475342</v>
+        <v>22.6215362548828</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743659973145</v>
+        <v>22.6743679046631</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945064544678</v>
+        <v>22.8945083618164</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>25</v>
       </c>
       <c r="G332" t="n">
-        <v>22.0139503479004</v>
+        <v>22.0139484405518</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G333" t="n">
-        <v>23.1938972473145</v>
+        <v>23.1938991546631</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>24.7084541320801</v>
+        <v>24.7084560394287</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.919792175293</v>
+        <v>24.9197883605957</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>24.9638195037842</v>
+        <v>24.9638175964355</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G345" t="n">
-        <v>26.4879302978516</v>
+        <v>26.4879322052002</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>28.1545696258545</v>
+        <v>28.1545677185059</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>29.3666706085205</v>
+        <v>29.3666687011719</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>27.8069820404053</v>
+        <v>27.8069839477539</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665050506592</v>
+        <v>28.4665069580078</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>29.7677364349365</v>
+        <v>29.7677345275879</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746776580811</v>
+        <v>29.8746814727783</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024806976318</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400951385498</v>
+        <v>30.2400932312012</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G361" t="n">
-        <v>30.6678981781006</v>
+        <v>30.6678924560547</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996200561523</v>
+        <v>30.8996162414551</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.9976501464844</v>
+        <v>30.9976539611816</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.9352684020996</v>
+        <v>30.935266494751</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.748104095459</v>
+        <v>30.7481079101562</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857223510742</v>
+        <v>30.685718536377</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G372" t="n">
-        <v>29.3131923675537</v>
+        <v>29.3131904602051</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.168794631958</v>
+        <v>30.1687889099121</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331462860107</v>
+        <v>30.1331443786621</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G377" t="n">
-        <v>29.9281578063965</v>
+        <v>29.9281558990479</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G378" t="n">
-        <v>30.0529327392578</v>
+        <v>30.0529289245605</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.4825344085693</v>
+        <v>29.4825325012207</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>29.8122940063477</v>
+        <v>29.812292098999</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G381" t="n">
-        <v>28.912130355835</v>
+        <v>28.9121322631836</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.1260318756104</v>
+        <v>29.126033782959</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544097900391</v>
+        <v>27.2544059753418</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>27.4861335754395</v>
+        <v>27.4861316680908</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>28.1189155578613</v>
+        <v>28.1189193725586</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>31.8099994659424</v>
       </c>
       <c r="G390" t="n">
-        <v>28.350643157959</v>
+        <v>28.3506450653076</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178554534912</v>
+        <v>27.7178592681885</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G393" t="n">
-        <v>28.6180191040039</v>
+        <v>28.6180210113525</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>28.7873554229736</v>
+        <v>28.7873573303223</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665050506592</v>
+        <v>28.4665069580078</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855548858643</v>
+        <v>29.7855529785156</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>32.9099998474121</v>
       </c>
       <c r="G399" t="n">
-        <v>29.331018447876</v>
+        <v>29.3310203552246</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.1705932617188</v>
+        <v>29.1705913543701</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>29.2329807281494</v>
+        <v>29.2329788208008</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>29.1438579559326</v>
+        <v>29.1438541412354</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>32.5</v>
       </c>
       <c r="G404" t="n">
-        <v>28.9656028747559</v>
+        <v>28.9656066894531</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>32.5</v>
       </c>
       <c r="G406" t="n">
-        <v>28.9656028747559</v>
+        <v>28.9656066894531</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477787017822</v>
+        <v>28.9477825164795</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>29.7677364349365</v>
+        <v>29.7677345275879</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G410" t="n">
-        <v>29.607307434082</v>
+        <v>29.6073055267334</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>33.5</v>
       </c>
       <c r="G411" t="n">
-        <v>29.8568553924561</v>
+        <v>29.8568572998047</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>32.9900016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>29.4023208618164</v>
+        <v>29.402322769165</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G414" t="n">
-        <v>28.814094543457</v>
+        <v>28.8140964508057</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.6875190734863</v>
+        <v>29.687520980835</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>29.6162204742432</v>
+        <v>29.6162185668945</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964282989502</v>
+        <v>29.6964321136475</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>30.142053604126</v>
+        <v>30.1420574188232</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390350341797</v>
+        <v>29.8390293121338</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>29.8122940063477</v>
+        <v>29.812292098999</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.518180847168</v>
+        <v>29.5181789398193</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>29.437967300415</v>
+        <v>29.4379653930664</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648643493652</v>
+        <v>30.3648662567139</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629096984863</v>
+        <v>30.4629039764404</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024806976318</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G430" t="n">
-        <v>30.4718170166016</v>
+        <v>30.4718189239502</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974903106689</v>
+        <v>30.0974922180176</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.0618457794189</v>
+        <v>30.0618438720703</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>36</v>
       </c>
       <c r="G435" t="n">
-        <v>32.0849838256836</v>
+        <v>32.0849800109863</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>36</v>
       </c>
       <c r="G436" t="n">
-        <v>32.0849838256836</v>
+        <v>32.0849800109863</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G438" t="n">
-        <v>30.8194046020508</v>
+        <v>30.819408416748</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928272247314</v>
+        <v>31.6928329467773</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>36.1100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>32.1830139160156</v>
+        <v>32.1830177307129</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>35.9900016784668</v>
       </c>
       <c r="G444" t="n">
-        <v>32.0760688781738</v>
+        <v>32.0760650634766</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.9512882232666</v>
+        <v>31.9512920379639</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>36.25</v>
       </c>
       <c r="G446" t="n">
-        <v>32.3077964782715</v>
+        <v>32.307788848877</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>39</v>
       </c>
       <c r="G449" t="n">
-        <v>34.7587242126465</v>
+        <v>34.7587280273438</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.731990814209</v>
+        <v>34.7319869995117</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>34.5804748535156</v>
+        <v>34.5804786682129</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.4378814697266</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.4378814697266</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>34.5804748535156</v>
+        <v>34.5804786682129</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G457" t="n">
-        <v>34.5448265075684</v>
+        <v>34.5448341369629</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>39.75</v>
       </c>
       <c r="G458" t="n">
-        <v>35.4271621704102</v>
+        <v>35.4271659851074</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>38.5699996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>34.3754844665527</v>
+        <v>34.3754920959473</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G463" t="n">
-        <v>33.8496475219727</v>
+        <v>33.8496551513672</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G466" t="n">
-        <v>33.7159652709961</v>
+        <v>33.7159729003906</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>38.5</v>
       </c>
       <c r="G468" t="n">
-        <v>34.3130989074707</v>
+        <v>34.313102722168</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>38.5</v>
       </c>
       <c r="G469" t="n">
-        <v>34.3130989074707</v>
+        <v>34.313102722168</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G470" t="n">
-        <v>34.1170234680176</v>
+        <v>34.1170310974121</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G472" t="n">
-        <v>34.1170234680176</v>
+        <v>34.1170310974121</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G473" t="n">
-        <v>34.776554107666</v>
+        <v>34.7765502929688</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041877746582</v>
+        <v>34.3041915893555</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081161499023</v>
+        <v>34.1081123352051</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8425407409668</v>
+        <v>32.8425369262695</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>39.3899993896484</v>
       </c>
       <c r="G479" t="n">
-        <v>35.1063117980957</v>
+        <v>35.106315612793</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>40.7299995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>36.3005905151367</v>
+        <v>36.3005867004395</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G482" t="n">
-        <v>36.1847267150879</v>
+        <v>36.1847229003906</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G484" t="n">
-        <v>37.4146499633789</v>
+        <v>37.4146461486816</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.8584747314453</v>
+        <v>38.8584785461426</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>43.3300018310547</v>
       </c>
       <c r="G487" t="n">
-        <v>38.6178398132324</v>
+        <v>38.6178359985352</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>43.2900009155273</v>
       </c>
       <c r="G488" t="n">
-        <v>38.5821876525879</v>
+        <v>38.5821914672852</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>44</v>
       </c>
       <c r="G491" t="n">
-        <v>39.2149772644043</v>
+        <v>39.2149696350098</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G493" t="n">
-        <v>37.8068008422852</v>
+        <v>37.8067970275879</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>38.0563507080078</v>
+        <v>38.0563468933105</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.341552734375</v>
+        <v>38.3415489196777</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089248657227</v>
+        <v>38.6089210510254</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.689136505127</v>
+        <v>38.6891403198242</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>43.4599990844727</v>
       </c>
       <c r="G503" t="n">
-        <v>38.733699798584</v>
+        <v>38.7337036132812</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545539855957</v>
+        <v>39.0545501708984</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G510" t="n">
-        <v>38.3772048950195</v>
+        <v>38.3772010803223</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>37.6998519897461</v>
+        <v>37.6998481750488</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G512" t="n">
-        <v>36.6125259399414</v>
+        <v>36.6125297546387</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G513" t="n">
-        <v>37.6820259094238</v>
+        <v>37.6820220947266</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>47.1199989318848</v>
       </c>
       <c r="G515" t="n">
-        <v>41.9956665039062</v>
+        <v>41.9956703186035</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.423469543457</v>
+        <v>42.4234733581543</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G521" t="n">
-        <v>41.9243698120117</v>
+        <v>41.924373626709</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>41.6213493347168</v>
+        <v>41.6213455200195</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>46.8600006103516</v>
       </c>
       <c r="G524" t="n">
-        <v>41.7639503479004</v>
+        <v>41.7639465332031</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>47.2799987792969</v>
       </c>
       <c r="G526" t="n">
-        <v>42.1382713317871</v>
+        <v>42.1382751464844</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G527" t="n">
-        <v>41.9243698120117</v>
+        <v>41.924373626709</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G528" t="n">
-        <v>41.6926498413086</v>
+        <v>41.6926460266113</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>40.8192253112793</v>
+        <v>40.819221496582</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G536" t="n">
-        <v>39.1436729431152</v>
+        <v>39.1436767578125</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784248352051</v>
+        <v>39.6784286499023</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G539" t="n">
-        <v>41.4787483215332</v>
+        <v>41.4787521362305</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>38.6802253723145</v>
+        <v>38.6802215576172</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>44.4199981689453</v>
       </c>
       <c r="G544" t="n">
-        <v>39.5892944335938</v>
+        <v>39.589298248291</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>45.5200004577637</v>
       </c>
       <c r="G547" t="n">
-        <v>40.5696754455566</v>
+        <v>40.5696716308594</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G548" t="n">
-        <v>40.8013954162598</v>
+        <v>40.801399230957</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>45.939998626709</v>
       </c>
       <c r="G549" t="n">
-        <v>40.9439926147461</v>
+        <v>40.9439964294434</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G550" t="n">
-        <v>40.8013954162598</v>
+        <v>40.801399230957</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400718688965</v>
+        <v>41.1400756835938</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>46</v>
       </c>
       <c r="G552" t="n">
-        <v>40.9974746704102</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131729125977</v>
+        <v>40.2131690979004</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>46</v>
       </c>
       <c r="G559" t="n">
-        <v>40.9974746704102</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>46.439998626709</v>
       </c>
       <c r="G560" t="n">
-        <v>41.3896179199219</v>
+        <v>41.3896255493164</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446472167969</v>
+        <v>44.5446510314941</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G565" t="n">
-        <v>43.885124206543</v>
+        <v>43.8851203918457</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>44.9635353088379</v>
+        <v>44.9635314941406</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>46.0330390930176</v>
+        <v>46.0330352783203</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253479003906</v>
+        <v>47.3253402709961</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494758605957</v>
+        <v>43.8494720458984</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G574" t="n">
-        <v>42.9582214355469</v>
+        <v>42.9582252502441</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>46.5200004577637</v>
       </c>
       <c r="G576" t="n">
-        <v>41.4609222412109</v>
+        <v>41.4609260559082</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>41.4787483215332</v>
+        <v>41.4787521362305</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>41.1757202148438</v>
+        <v>41.1757278442383</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675552368164</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.1080284118652</v>
+        <v>39.108024597168</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479286193848</v>
+        <v>40.7479248046875</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>44.6399993896484</v>
       </c>
       <c r="G585" t="n">
-        <v>39.7853775024414</v>
+        <v>39.7853736877441</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3041000366211</v>
+        <v>39.3040962219238</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675552368164</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488250732422</v>
+        <v>40.2488212585449</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G592" t="n">
-        <v>39.4288749694824</v>
+        <v>39.4288787841797</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G593" t="n">
-        <v>39.1436729431152</v>
+        <v>39.1436767578125</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>39.0367202758789</v>
+        <v>39.0367240905762</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479286193848</v>
+        <v>40.7479248046875</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.0509452819824</v>
+        <v>41.050952911377</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>46.560001373291</v>
       </c>
       <c r="G598" t="n">
-        <v>41.9335708618164</v>
+        <v>41.9335746765137</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G599" t="n">
-        <v>41.0149269104004</v>
+        <v>41.0149230957031</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G601" t="n">
-        <v>40.6366577148438</v>
+        <v>40.6366539001465</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.4844360351562</v>
+        <v>37.484432220459</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316192626953</v>
+        <v>36.3316230773926</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G607" t="n">
-        <v>37.052131652832</v>
+        <v>37.0521278381348</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>40.5</v>
       </c>
       <c r="G608" t="n">
-        <v>36.4757232666016</v>
+        <v>36.4757270812988</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.007396697998</v>
+        <v>36.0073890686035</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G611" t="n">
-        <v>35.6651496887207</v>
+        <v>35.6651458740234</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>33.4135627746582</v>
+        <v>33.4135665893555</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>37.6199989318848</v>
       </c>
       <c r="G616" t="n">
-        <v>33.881893157959</v>
+        <v>33.8818893432617</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G617" t="n">
-        <v>34.4763069152832</v>
+        <v>34.4763145446777</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924705505371</v>
+        <v>34.6924743652344</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G619" t="n">
-        <v>35.1427841186523</v>
+        <v>35.1427803039551</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>37.7400016784668</v>
       </c>
       <c r="G622" t="n">
-        <v>33.9899711608887</v>
+        <v>33.9899749755859</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>37.6199989318848</v>
       </c>
       <c r="G624" t="n">
-        <v>33.881893157959</v>
+        <v>33.8818893432617</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>37.560001373291</v>
       </c>
       <c r="G625" t="n">
-        <v>33.8278579711914</v>
+        <v>33.8278541564941</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247749328613</v>
+        <v>35.1247711181641</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.4048538208008</v>
+        <v>32.4048500061035</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G631" t="n">
-        <v>31.4681930541992</v>
+        <v>31.468189239502</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G632" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744064331055</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5315341949463</v>
+        <v>30.531530380249</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.4867935180664</v>
+        <v>29.486795425415</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371147155762</v>
+        <v>29.9371128082275</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346153259277</v>
+        <v>29.2346172332764</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.1532669067383</v>
+        <v>30.153263092041</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147434234619</v>
+        <v>29.4147415161133</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G641" t="n">
-        <v>29.1265392303467</v>
+        <v>29.1265411376953</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>29.5408325195312</v>
+        <v>29.5408306121826</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>33.9799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>30.6035842895508</v>
+        <v>30.6035823822021</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520389556885</v>
+        <v>31.2520408630371</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172351837158</v>
+        <v>30.1172370910645</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054412841797</v>
+        <v>30.4054393768311</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>30.5315341949463</v>
+        <v>30.531530380249</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.666332244873</v>
+        <v>31.6663284301758</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>35.6199989318848</v>
       </c>
       <c r="G652" t="n">
-        <v>32.080623626709</v>
+        <v>32.0806198120117</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>31.1079368591309</v>
+        <v>31.1079387664795</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601131439209</v>
+        <v>31.3601150512695</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>30.9818477630615</v>
+        <v>30.9818496704102</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G656" t="n">
-        <v>31.7383861541748</v>
+        <v>31.7383823394775</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520389556885</v>
+        <v>31.2520408630371</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122894287109</v>
+        <v>31.6122913360596</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G659" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744064331055</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.9010887145996</v>
+        <v>29.901086807251</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346153259277</v>
+        <v>29.2346172332764</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G668" t="n">
-        <v>27.5954608917236</v>
+        <v>27.5954627990723</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>26.0463676452637</v>
+        <v>26.0463695526123</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>26.5146980285645</v>
+        <v>26.5146999359131</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G673" t="n">
-        <v>27.2352066040039</v>
+        <v>27.2352046966553</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>26.7488651275635</v>
+        <v>26.7488632202148</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693717956543</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G682" t="n">
-        <v>27.9377002716064</v>
+        <v>27.9377021789551</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476390838623</v>
+        <v>27.8476409912109</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>27.7936019897461</v>
+        <v>27.7936000823975</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693717956543</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G689" t="n">
-        <v>27.7755889892578</v>
+        <v>27.7755870819092</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401958465576</v>
+        <v>28.6401996612549</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762237548828</v>
+        <v>28.6762218475342</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G699" t="n">
-        <v>27.6675128936768</v>
+        <v>27.6675109863281</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>27.5954608917236</v>
+        <v>27.5954627990723</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G703" t="n">
-        <v>27.4513607025146</v>
+        <v>27.451358795166</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>25.7581634521484</v>
+        <v>25.7581672668457</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320308685303</v>
+        <v>22.7320327758789</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233238220215</v>
+        <v>21.7233200073242</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860660552979</v>
+        <v>22.7860679626465</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606136322021</v>
+        <v>23.5606155395508</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G715" t="n">
-        <v>23.4345283508301</v>
+        <v>23.4345264434814</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>25</v>
       </c>
       <c r="G716" t="n">
-        <v>22.5158805847168</v>
+        <v>22.5158786773682</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>21.7053070068359</v>
+        <v>21.7053089141846</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G718" t="n">
-        <v>20.8226852416992</v>
+        <v>20.8226833343506</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G719" t="n">
-        <v>21.3630638122559</v>
+        <v>21.3630619049072</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369747161865</v>
+        <v>21.2369766235352</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>19.7239074707031</v>
+        <v>19.7239093780518</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G724" t="n">
-        <v>18.318920135498</v>
+        <v>18.3189182281494</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>18.2828941345215</v>
+        <v>18.2828922271729</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G726" t="n">
-        <v>19.5437831878662</v>
+        <v>19.5437812805176</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.877311706543</v>
+        <v>18.8773136138916</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>19.0034008026123</v>
+        <v>19.0034027099609</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G730" t="n">
-        <v>18.318920135498</v>
+        <v>18.3189182281494</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.003698348999</v>
+        <v>18.0036945343018</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>18.5</v>
       </c>
       <c r="G735" t="n">
-        <v>16.661750793457</v>
+        <v>16.6617488861084</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.2024269104004</v>
+        <v>16.2024250030518</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9502477645874</v>
+        <v>15.9502487182617</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.716082572937</v>
+        <v>15.7160835266113</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800565719604</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6170129776001</v>
+        <v>15.6170139312744</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077136993408</v>
+        <v>16.6077098846436</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>17.4723205566406</v>
+        <v>17.4723224639893</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>18.8232727050781</v>
+        <v>18.8232746124268</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G749" t="n">
-        <v>17.6614570617676</v>
+        <v>17.6614551544189</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968425750732</v>
+        <v>16.7968444824219</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G752" t="n">
-        <v>16.0132923126221</v>
+        <v>16.0132942199707</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250890731812</v>
+        <v>15.7250881195068</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>15.400860786438</v>
+        <v>15.4008617401123</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800565719604</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G760" t="n">
-        <v>14.7524042129517</v>
+        <v>14.7524032592773</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899925231934</v>
+        <v>15.5899934768677</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>15.1486835479736</v>
+        <v>15.1486845016479</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639043807983</v>
+        <v>15.4639072418213</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568012237549</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G767" t="n">
-        <v>17.6434421539307</v>
+        <v>17.6434440612793</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>20</v>
       </c>
       <c r="G769" t="n">
-        <v>18.0127029418945</v>
+        <v>18.0127010345459</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G770" t="n">
-        <v>18.0487289428711</v>
+        <v>18.0487270355225</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G772" t="n">
-        <v>18.0307178497314</v>
+        <v>18.0307159423828</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>20</v>
       </c>
       <c r="G773" t="n">
-        <v>18.0127029418945</v>
+        <v>18.0127010345459</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.4543075561523</v>
+        <v>17.4543113708496</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791706085205</v>
+        <v>18.6791725158691</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G778" t="n">
-        <v>18.6251335144043</v>
+        <v>18.6251354217529</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G780" t="n">
-        <v>18.6251335144043</v>
+        <v>18.6251354217529</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>19.0034008026123</v>
+        <v>19.0034027099609</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G782" t="n">
-        <v>18.9493656158447</v>
+        <v>18.9493637084961</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>20</v>
       </c>
       <c r="G786" t="n">
-        <v>18.0127029418945</v>
+        <v>18.0127010345459</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>20</v>
       </c>
       <c r="G787" t="n">
-        <v>18.0127029418945</v>
+        <v>18.0127010345459</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G788" t="n">
-        <v>18.4269943237305</v>
+        <v>18.4269924163818</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>19.0034008026123</v>
+        <v>19.0034027099609</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>17.3552398681641</v>
+        <v>17.3552379608154</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G794" t="n">
-        <v>18.607120513916</v>
+        <v>18.6071224212646</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698741912842</v>
+        <v>19.6698703765869</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>20.2462768554688</v>
+        <v>20.2462787628174</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G798" t="n">
-        <v>20.0661506652832</v>
+        <v>20.0661525726318</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537220001221</v>
+        <v>19.4537200927734</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>18.8232727050781</v>
+        <v>18.8232746124268</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G808" t="n">
-        <v>17.5083446502686</v>
+        <v>17.5083465576172</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G815" t="n">
-        <v>16.9409465789795</v>
+        <v>16.9409446716309</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462352752686</v>
+        <v>17.3462371826172</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>17.3822593688965</v>
+        <v>17.3822574615479</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2831878662109</v>
+        <v>17.2831897735596</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9766750335693</v>
+        <v>17.976676940918</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6614570617676</v>
+        <v>17.6614551544189</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.4543075561523</v>
+        <v>17.4543113708496</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G827" t="n">
-        <v>18.1387920379639</v>
+        <v>18.1387901306152</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G828" t="n">
-        <v>17.913631439209</v>
+        <v>17.9136333465576</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>20</v>
       </c>
       <c r="G829" t="n">
-        <v>18.0127029418945</v>
+        <v>18.0127010345459</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>17.6974792480469</v>
+        <v>17.6974773406982</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1928291320801</v>
+        <v>18.1928310394287</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3822593688965</v>
+        <v>17.3822574615479</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2381534576416</v>
+        <v>17.2381572723389</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300811767578</v>
+        <v>17.1300792694092</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676723480225</v>
+        <v>17.9676704406738</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G838" t="n">
-        <v>18.084753036499</v>
+        <v>18.0847549438477</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667400360107</v>
+        <v>18.0667419433594</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G840" t="n">
-        <v>17.8686008453369</v>
+        <v>17.8686027526855</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6074161529541</v>
+        <v>17.6074180603027</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G844" t="n">
-        <v>17.5894050598145</v>
+        <v>17.5894031524658</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G846" t="n">
-        <v>17.8686008453369</v>
+        <v>17.8686027526855</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568012237549</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G850" t="n">
-        <v>16.6621913909912</v>
+        <v>16.6621894836426</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G852" t="n">
-        <v>16.5330276489258</v>
+        <v>16.5330257415771</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>16.1916599273682</v>
+        <v>16.1916618347168</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.6842317581177</v>
+        <v>15.684232711792</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>14.6232385635376</v>
+        <v>14.6232395172119</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021240234375</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G857" t="n">
-        <v>13.9405136108398</v>
+        <v>13.9405145645142</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>14.5</v>
       </c>
       <c r="G868" t="n">
-        <v>13.3777275085449</v>
+        <v>13.3777265548706</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009454727173</v>
+        <v>13.1009464263916</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>13.7006387710571</v>
+        <v>13.7006378173828</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4756231307983</v>
+        <v>14.475622177124</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>14.4202661514282</v>
+        <v>14.4202671051025</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>14.577109336853</v>
+        <v>14.5771102905273</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>13.7928991317749</v>
+        <v>13.7928981781006</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G879" t="n">
-        <v>13.6914119720459</v>
+        <v>13.6914110183716</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486206054688</v>
+        <v>10.1486196517944</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G888" t="n">
-        <v>10.4069490432739</v>
+        <v>10.4069480895996</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G890" t="n">
-        <v>10.4069490432739</v>
+        <v>10.4069480895996</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>10.5914688110352</v>
+        <v>10.5914697647095</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.9236059188843</v>
+        <v>10.9236068725586</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837282180786</v>
+        <v>10.6837291717529</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G896" t="n">
-        <v>10.5361137390137</v>
+        <v>10.5361127853394</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.370044708252</v>
+        <v>10.3700456619263</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>10.0471353530884</v>
+        <v>10.0471343994141</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762971878052</v>
+        <v>10.1762981414795</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964221954346</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G904" t="n">
-        <v>10.0932645797729</v>
+        <v>10.0932636260986</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G906" t="n">
-        <v>10.573016166687</v>
+        <v>10.5730171203613</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286827087402</v>
+        <v>10.0286817550659</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486206054688</v>
+        <v>10.1486196517944</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G919" t="n">
-        <v>9.29060077667236</v>
+        <v>9.29059982299805</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G920" t="n">
-        <v>9.57660675048828</v>
+        <v>9.5766077041626</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964221954346</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>9.29060077667236</v>
+        <v>9.29059982299805</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G925" t="n">
-        <v>9.43821716308594</v>
+        <v>9.43821620941162</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>9.47512149810791</v>
+        <v>9.47512245178223</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G927" t="n">
-        <v>9.20295429229736</v>
+        <v>9.20295333862305</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G928" t="n">
-        <v>8.94001197814941</v>
+        <v>8.94001293182373</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447154998779</v>
+        <v>9.24447059631348</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G937" t="n">
-        <v>9.97332572937012</v>
+        <v>9.97332668304443</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486206054688</v>
+        <v>10.1486196517944</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G945" t="n">
-        <v>10.1024894714355</v>
+        <v>10.1024904251099</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286827087402</v>
+        <v>10.0286817550659</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886711120605</v>
+        <v>9.66886806488037</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886711120605</v>
+        <v>9.66886806488037</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G953" t="n">
-        <v>9.7980318069458</v>
+        <v>9.79803276062012</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>9.57660675048828</v>
+        <v>9.5766077041626</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G956" t="n">
-        <v>9.2629222869873</v>
+        <v>9.26292324066162</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G966" t="n">
-        <v>9.75190162658691</v>
+        <v>9.7519006729126</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655851364136</v>
+        <v>10.0655860900879</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822439193726</v>
+        <v>10.5822448730469</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>10.2870092391968</v>
+        <v>10.2870101928711</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G973" t="n">
-        <v>10.5084352493286</v>
+        <v>10.5084362030029</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G977" t="n">
-        <v>11.4310369491577</v>
+        <v>11.431037902832</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G978" t="n">
-        <v>11.6340093612671</v>
+        <v>11.6340084075928</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337007522583</v>
+        <v>12.2337017059326</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>12.0860843658447</v>
+        <v>12.086085319519</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G987" t="n">
-        <v>11.9569206237793</v>
+        <v>11.956919670105</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>11.8277549743652</v>
+        <v>11.8277559280396</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G990" t="n">
-        <v>11.8277549743652</v>
+        <v>11.8277559280396</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G994" t="n">
-        <v>13.2577877044678</v>
+        <v>13.2577886581421</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G996" t="n">
-        <v>13.0824947357178</v>
+        <v>13.0824956893921</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G997" t="n">
-        <v>13.5991516113281</v>
+        <v>13.5991506576538</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G998" t="n">
-        <v>13.4054050445557</v>
+        <v>13.40540599823</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7559938430786</v>
+        <v>13.7559928894043</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.7098627090454</v>
+        <v>13.7098636627197</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.3408231735229</v>
+        <v>13.3408241271973</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7190895080566</v>
+        <v>13.719090461731</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283153533936</v>
+        <v>13.7283163070679</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.0143222808838</v>
+        <v>14.0143213272095</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.1342601776123</v>
+        <v>14.1342620849609</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497394561768</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.6637344360352</v>
+        <v>13.6637353897095</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.6637344360352</v>
+        <v>13.6637353897095</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.7006387710571</v>
+        <v>13.7006378173828</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.1158084869385</v>
+        <v>14.1158094406128</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>13.7190895080566</v>
+        <v>13.719090461731</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.0512256622314</v>
+        <v>14.0512266159058</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>14.1158084869385</v>
+        <v>14.1158094406128</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497394561768</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.9312877655029</v>
+        <v>13.9312887191772</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303609848022</v>
+        <v>15.7303628921509</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.0865859985352</v>
+        <v>17.0865879058838</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.8651638031006</v>
+        <v>16.865161895752</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.7452239990234</v>
+        <v>16.7452220916748</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.9979152679443</v>
+        <v>15.997917175293</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333333969116</v>
+        <v>15.9333353042603</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720325469971</v>
+        <v>15.4720335006714</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247257232666</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247257232666</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.1491231918335</v>
+        <v>15.1491241455078</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506084442139</v>
+        <v>15.2506093978882</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.9830541610718</v>
+        <v>14.9830551147461</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.1301679611206</v>
+        <v>10.1301689147949</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.7980318069458</v>
+        <v>9.79803276062012</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.97589349746704</v>
+        <v>7.9758939743042</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.55047273635864</v>
+        <v>6.5504732131958</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409652709961</v>
+        <v>6.98409605026245</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.91028738021851</v>
+        <v>6.91028785705566</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697746276855</v>
+        <v>8.85697841644287</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.40028953552246</v>
+        <v>8.40029048919678</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.25728607177734</v>
+        <v>8.25728702545166</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.118896484375</v>
+        <v>8.11889553070068</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.74985551834106</v>
+        <v>7.74985504150391</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.92976379394531</v>
+        <v>7.92976331710815</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675937652588</v>
+        <v>7.78675889968872</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.10967063903809</v>
+        <v>8.10966968536377</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>8.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.84211587905884</v>
+        <v>7.842116355896</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.28855466842651</v>
+        <v>7.28855514526367</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1092" t="n">
-        <v>7.26087665557861</v>
+        <v>7.26087713241577</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.3346848487854</v>
+        <v>7.33468532562256</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920509338379</v>
+        <v>7.51920557022095</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G1103" t="n">
-        <v>7.1455512046814</v>
+        <v>7.14555168151855</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403442382812</v>
+        <v>7.10403490066528</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.06713008880615</v>
+        <v>7.06713104248047</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874050140381</v>
+        <v>6.92874002456665</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1109" t="n">
-        <v>7.26087665557861</v>
+        <v>7.26087713241577</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533479690552</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533479690552</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.54227066040039</v>
+        <v>7.54227018356323</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010297775269</v>
+        <v>7.27010250091553</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217798233032</v>
+        <v>7.72217750549316</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948528289795</v>
+        <v>8.46948623657227</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.66784572601318</v>
+        <v>8.66784477233887</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310859680176</v>
+        <v>8.90310764312744</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.54329299926758</v>
+        <v>8.54329395294189</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.87542915344238</v>
+        <v>8.8754301071167</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.4956188201904</v>
+        <v>11.4956197738647</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>11.2557430267334</v>
+        <v>11.2557420730591</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420576095581</v>
+        <v>10.9420566558838</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5084352493286</v>
+        <v>10.5084362030029</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.1947498321533</v>
+        <v>10.1947507858276</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1136" t="n">
-        <v>10.5361137390137</v>
+        <v>10.5361127853394</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.1301679611206</v>
+        <v>10.1301689147949</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.370044708252</v>
+        <v>10.3700456619263</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.3608198165894</v>
+        <v>10.360818862915</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.2224292755127</v>
+        <v>10.2224283218384</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.5361137390137</v>
+        <v>10.5361127853394</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G1145" t="n">
-        <v>10.5453405380249</v>
+        <v>10.5453395843506</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667636871338</v>
+        <v>10.7667646408081</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.5417490005493</v>
+        <v>11.5417499542236</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.7078170776367</v>
+        <v>11.707818031311</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616888046265</v>
+        <v>11.6616878509521</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.5694284439087</v>
+        <v>11.5694274902344</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.3480043411255</v>
+        <v>11.3480033874512</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.2741947174072</v>
+        <v>11.2741956710815</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.7042274475098</v>
+        <v>12.7042284011841</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.0548162460327</v>
+        <v>13.0548152923584</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.0548162460327</v>
+        <v>13.0548152923584</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961801528931</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4423093795776</v>
+        <v>13.4423084259033</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.2577877044678</v>
+        <v>13.2577886581421</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.2301111221313</v>
+        <v>13.230110168457</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.1932067871094</v>
+        <v>13.1932077407837</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500499725342</v>
+        <v>13.3500509262085</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>14.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.1470756530762</v>
+        <v>13.1470766067505</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.4976654052734</v>
+        <v>13.4976663589478</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>13.1932067871094</v>
+        <v>13.1932077407837</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1191" t="n">
-        <v>13.1655292510986</v>
+        <v>13.1655282974243</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1193" t="n">
-        <v>13.2301111221313</v>
+        <v>13.230110168457</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.2762413024902</v>
+        <v>13.2762403488159</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.0455913543701</v>
+        <v>13.0455904006958</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.1747550964355</v>
+        <v>13.1747541427612</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.3869543075562</v>
+        <v>13.3869533538818</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.3813180923462</v>
+        <v>12.3813161849976</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6304187774658</v>
+        <v>12.6304197311401</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1206" t="n">
-        <v>13.3869543075562</v>
+        <v>13.3869533538818</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.4054050445557</v>
+        <v>13.40540599823</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1208" t="n">
-        <v>13.5068912506104</v>
+        <v>13.5068922042847</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330835342407</v>
+        <v>13.4330825805664</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1211" t="n">
-        <v>14.1158084869385</v>
+        <v>14.1158094406128</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>15.269061088562</v>
+        <v>15.2690601348877</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735177993774</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1214" t="n">
-        <v>15.8318471908569</v>
+        <v>15.8318462371826</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628057479858</v>
+        <v>15.4628076553345</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>14.6232385635376</v>
+        <v>14.6232395172119</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1221" t="n">
-        <v>14.5217533111572</v>
+        <v>14.5217542648315</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1223" t="n">
-        <v>14.7154989242554</v>
+        <v>14.7154998779297</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>14.3556852340698</v>
+        <v>14.3556861877441</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1227" t="n">
-        <v>13.3869543075562</v>
+        <v>13.3869533538818</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735177993774</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1235" t="n">
-        <v>15.6750068664551</v>
+        <v>15.6750059127808</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184713363647</v>
+        <v>14.9184722900391</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1239" t="n">
-        <v>15.3889999389648</v>
+        <v>15.3889989852905</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764911651611</v>
+        <v>15.7764930725098</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827474594116</v>
+        <v>15.5827465057373</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410739898682</v>
+        <v>15.8410758972168</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>15.924108505249</v>
+        <v>15.9241094589233</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.1178550720215</v>
+        <v>16.1178531646729</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>15.8503007888794</v>
+        <v>15.8502998352051</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G1249" t="n">
-        <v>15.8779773712158</v>
+        <v>15.8779783248901</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>15.6381034851074</v>
+        <v>15.6381015777588</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351272583008</v>
+        <v>15.4351282119751</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919723510742</v>
+        <v>15.5919713973999</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>15.6381034851074</v>
+        <v>15.6381015777588</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517869949341</v>
+        <v>15.9517879486084</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>16.5145721435547</v>
+        <v>16.5145740509033</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.0865859985352</v>
+        <v>17.0865879058838</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.4464015960693</v>
+        <v>17.446403503418</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1269" t="n">
-        <v>17.5663394927979</v>
+        <v>17.5663414001465</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1270" t="n">
-        <v>17.372594833374</v>
+        <v>17.3725929260254</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.547887802124</v>
+        <v>17.5478858947754</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.036865234375</v>
+        <v>18.0368671417236</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.4151306152344</v>
+        <v>18.415132522583</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1276" t="n">
-        <v>19.6698722839355</v>
+        <v>19.6698703765869</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="n">
-        <v>19.245475769043</v>
+        <v>19.2454738616943</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377342224121</v>
+        <v>19.3377361297607</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>18.5442981719971</v>
+        <v>18.5443000793457</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>18.4704914093018</v>
+        <v>18.4704895019531</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.1844844818115</v>
+        <v>18.1844825744629</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="n">
-        <v>20.9430637359619</v>
+        <v>20.9430618286133</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="n">
-        <v>21.2567481994629</v>
+        <v>21.2567462921143</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.1829376220703</v>
+        <v>21.1829395294189</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.2567481994629</v>
+        <v>21.2567462921143</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1301" t="n">
-        <v>22.7513618469238</v>
+        <v>22.7513637542725</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>22.7698135375977</v>
+        <v>22.7698173522949</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.5371170043945</v>
+        <v>20.5371189117432</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.6293792724609</v>
+        <v>20.6293773651123</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="n">
-        <v>20.7216396331787</v>
+        <v>20.7216377258301</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.1865291595459</v>
+        <v>20.1865272521973</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>20.6847362518311</v>
+        <v>20.6847343444824</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4633102416992</v>
+        <v>20.4633083343506</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G1318" t="n">
-        <v>21.0906810760498</v>
+        <v>21.0906791687012</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.109130859375</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.109130859375</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="n">
-        <v>20.2234325408936</v>
+        <v>20.2234344482422</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.9466514587402</v>
+        <v>19.9466533660889</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="n">
-        <v>22.5483894348145</v>
+        <v>22.5483913421631</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.2162551879883</v>
+        <v>22.2162532806396</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="n">
-        <v>22.1424446105957</v>
+        <v>22.1424465179443</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="n">
-        <v>22.2531604766846</v>
+        <v>22.2531585693359</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317325592041</v>
+        <v>22.0317306518555</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846755981445</v>
+        <v>23.7846775054932</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>23.8953895568848</v>
+        <v>23.8953876495361</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>23.046594619751</v>
+        <v>23.0465927124023</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>24.8400001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>22.9174327850342</v>
+        <v>22.9174308776855</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817031860352</v>
+        <v>23.5817012786865</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.1388568878174</v>
+        <v>23.1388549804688</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1352" t="n">
-        <v>22.7513618469238</v>
+        <v>22.7513637542725</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="n">
-        <v>22.5852928161621</v>
+        <v>22.5852947235107</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.4894428253174</v>
+        <v>23.4894409179688</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>23.8953895568848</v>
+        <v>23.8953876495361</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763206481934</v>
+        <v>25.0763187408447</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>29</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7554550170898</v>
+        <v>26.7554531097412</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="n">
-        <v>27.3828239440918</v>
+        <v>27.3828220367432</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935359954834</v>
+        <v>27.4935340881348</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="n">
-        <v>28.1578121185303</v>
+        <v>28.157808303833</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721118927002</v>
+        <v>27.2721099853516</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>27.3828239440918</v>
+        <v>27.3828220367432</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>27.4012775421143</v>
+        <v>27.4012756347656</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="n">
-        <v>27.1060428619385</v>
+        <v>27.1060447692871</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>25.9251136779785</v>
+        <v>25.9251098632812</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="n">
-        <v>25.7221393585205</v>
+        <v>25.7221412658691</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="n">
-        <v>26.4602222442627</v>
+        <v>26.4602203369141</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>26.3864135742188</v>
+        <v>26.3864154815674</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="n">
-        <v>25.7221393585205</v>
+        <v>25.7221412658691</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="n">
-        <v>26.1280860900879</v>
+        <v>26.1280841827393</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>25.9620170593262</v>
+        <v>25.9620151519775</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="n">
-        <v>26.3310585021973</v>
+        <v>26.3310565948486</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="n">
-        <v>26.4602222442627</v>
+        <v>26.4602203369141</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="n">
-        <v>26.5155754089355</v>
+        <v>26.5155773162842</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="n">
-        <v>25.9251136779785</v>
+        <v>25.9251098632812</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="n">
-        <v>26.1280860900879</v>
+        <v>26.1280841827393</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="n">
-        <v>25.4453582763672</v>
+        <v>25.4453601837158</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>26.7185497283936</v>
+        <v>26.7185478210449</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>26.8292617797852</v>
+        <v>26.8292636871338</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>29</v>
       </c>
       <c r="G1406" t="n">
-        <v>26.7554550170898</v>
+        <v>26.7554531097412</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="n">
-        <v>26.5155754089355</v>
+        <v>26.5155773162842</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>29.4799995422363</v>
       </c>
       <c r="G1413" t="n">
-        <v>27.1983032226562</v>
+        <v>27.1983013153076</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750843048096</v>
+        <v>27.4750862121582</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>30.4643154144287</v>
+        <v>30.4643135070801</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="n">
-        <v>30.9625225067139</v>
+        <v>30.9625205993652</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="n">
-        <v>29.5970706939697</v>
+        <v>29.5970687866211</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>26.8846187591553</v>
+        <v>26.8846168518066</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923583984375</v>
+        <v>26.7923603057861</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="n">
-        <v>27.1798534393311</v>
+        <v>27.1798496246338</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994808197021</v>
+        <v>27.8994789123535</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>27.5857982635498</v>
+        <v>27.5857963562012</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="n">
-        <v>27.2352066040039</v>
+        <v>27.2352085113525</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37549,7 +37549,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167549133301</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1430" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167549133301</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>27.9548358917236</v>
+        <v>27.9548377990723</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.6744651794434</v>
+        <v>28.674467086792</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="n">
-        <v>28.0286445617676</v>
+        <v>28.0286426544189</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.8072204589844</v>
+        <v>27.8072185516357</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1442" t="n">
-        <v>28.3423309326172</v>
+        <v>28.3423290252686</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="n">
-        <v>28.0286445617676</v>
+        <v>28.0286426544189</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732894897461</v>
+        <v>27.9732875823975</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="n">
-        <v>28.0840015411377</v>
+        <v>28.0840034484863</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>26.2941513061523</v>
+        <v>26.294153213501</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="n">
-        <v>26.8846187591553</v>
+        <v>26.8846168518066</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.9953308105469</v>
+        <v>26.9953327178955</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1461" t="n">
-        <v>24.0983619689941</v>
+        <v>24.0983600616455</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1467" t="n">
-        <v>23.2680187225342</v>
+        <v>23.2680168151855</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="n">
-        <v>24.7441825866699</v>
+        <v>24.7441806793213</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.2423877716064</v>
+        <v>25.2423896789551</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>25.0947704315186</v>
+        <v>25.0947723388672</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763206481934</v>
+        <v>25.0763187408447</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179893493652</v>
+        <v>24.8179912567139</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179893493652</v>
+        <v>24.8179912567139</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1486" t="n">
-        <v>24.8733444213867</v>
+        <v>24.8733463287354</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="n">
-        <v>23.8769340515137</v>
+        <v>23.8769359588623</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>23.8769340515137</v>
+        <v>23.8769359588623</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>23.1573047637939</v>
+        <v>23.1573066711426</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="n">
-        <v>22.7698135375977</v>
+        <v>22.7698173522949</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>21.865665435791</v>
+        <v>21.8656635284424</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287601470947</v>
+        <v>21.8287620544434</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841152191162</v>
+        <v>21.8841133117676</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.736499786377</v>
+        <v>21.7364978790283</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="n">
-        <v>22.6591033935547</v>
+        <v>22.6591014862061</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287601470947</v>
+        <v>21.8287620544434</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.109130859375</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.3525943756104</v>
+        <v>20.352596282959</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.3525943756104</v>
+        <v>20.352596282959</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1522" t="n">
-        <v>22.7513618469238</v>
+        <v>22.7513637542725</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.5299396514893</v>
+        <v>22.529935836792</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>22.5114860534668</v>
+        <v>22.5114841461182</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.5299396514893</v>
+        <v>22.529935836792</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="n">
-        <v>22.8620738983154</v>
+        <v>22.8620758056641</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>22.5114860534668</v>
+        <v>22.5114841461182</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674564361572</v>
+        <v>21.3674583435059</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="n">
-        <v>20.7216396331787</v>
+        <v>20.7216377258301</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1551" t="n">
-        <v>20.4448585510254</v>
+        <v>20.4448566436768</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="n">
-        <v>20.8138980865479</v>
+        <v>20.8138961791992</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="n">
-        <v>20.5371170043945</v>
+        <v>20.5371189117432</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>20.2049789428711</v>
+        <v>20.2049808502197</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="n">
-        <v>20.5002136230469</v>
+        <v>20.5002117156982</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="n">
-        <v>20.0204620361328</v>
+        <v>20.0204601287842</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.5073909759521</v>
+        <v>18.5073947906494</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770534515381</v>
+        <v>17.6770515441895</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.1291255950928</v>
+        <v>18.1291236877441</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.06813621521</v>
+        <v>17.0681343078613</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633651733398</v>
+        <v>17.3633670806885</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.0845413208008</v>
+        <v>15.0845403671265</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>15.2321577072144</v>
+        <v>15.23215675354</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3705463409424</v>
+        <v>15.370548248291</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.23779296875</v>
+        <v>16.2377910614014</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.2172946929932</v>
+        <v>14.2172937393188</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.060453414917</v>
+        <v>14.0604524612427</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.3372325897217</v>
+        <v>14.337233543396</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878223419189</v>
+        <v>14.6878213882446</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634248733521</v>
+        <v>14.2634258270264</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.82262134552</v>
+        <v>15.8226222991943</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021240234375</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0420007705688</v>
+        <v>14.0420017242432</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.820574760437</v>
+        <v>13.8205757141113</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497394561768</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247257232666</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="n">
-        <v>13.617603302002</v>
+        <v>13.6176042556763</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.8057146072388</v>
+        <v>12.8057136535645</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1617" t="n">
-        <v>13.3592748641968</v>
+        <v>13.3592739105225</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961801528931</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476360321045</v>
+        <v>15.0476369857788</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1621" t="n">
-        <v>15.8318471908569</v>
+        <v>15.8318462371826</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.305965423584</v>
+        <v>15.3059663772583</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384101867676</v>
+        <v>15.0384111404419</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>4.46000003814697</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>111527</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>4.4850001335144</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>4.4850001335144</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G3" t="n">
-        <v>12.9787998199463</v>
+        <v>12.9788007736206</v>
       </c>
       <c r="H3" t="n">
         <v>55009</v>
@@ -485,7 +485,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>12.9787998199463</v>
+        <v>12.9788007736206</v>
       </c>
       <c r="H4" t="n">
         <v>53738</v>
@@ -514,7 +514,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G5" t="n">
-        <v>12.7479515075684</v>
+        <v>12.7479524612427</v>
       </c>
       <c r="H5" t="n">
         <v>96757</v>
@@ -543,7 +543,7 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12.3974046707153</v>
+        <v>12.3974056243896</v>
       </c>
       <c r="H6" t="n">
         <v>125048</v>
@@ -601,7 +601,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>12.2606039047241</v>
+        <v>12.2606048583984</v>
       </c>
       <c r="H8" t="n">
         <v>54531</v>
@@ -688,7 +688,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>10.858416557312</v>
+        <v>10.8584156036377</v>
       </c>
       <c r="H11" t="n">
         <v>191378</v>
@@ -775,7 +775,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G14" t="n">
-        <v>9.84952354431152</v>
+        <v>9.84952449798584</v>
       </c>
       <c r="H14" t="n">
         <v>191837</v>
@@ -804,7 +804,7 @@
         <v>12.25</v>
       </c>
       <c r="G15" t="n">
-        <v>10.4736700057983</v>
+        <v>10.4736709594727</v>
       </c>
       <c r="H15" t="n">
         <v>204057</v>
@@ -833,7 +833,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941207885742</v>
+        <v>10.2941217422485</v>
       </c>
       <c r="H16" t="n">
         <v>136366</v>
@@ -891,7 +891,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156671524048</v>
       </c>
       <c r="H18" t="n">
         <v>109866</v>
@@ -920,7 +920,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>10.7301683425903</v>
+        <v>10.7301664352417</v>
       </c>
       <c r="H19" t="n">
         <v>71825</v>
@@ -949,7 +949,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5762691497803</v>
+        <v>10.5762672424316</v>
       </c>
       <c r="H20" t="n">
         <v>57072</v>
@@ -978,7 +978,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361179351807</v>
+        <v>10.636118888855</v>
       </c>
       <c r="H21" t="n">
         <v>72208</v>
@@ -1007,7 +1007,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156671524048</v>
       </c>
       <c r="H22" t="n">
         <v>43477</v>
@@ -1036,7 +1036,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1915197372437</v>
+        <v>10.191520690918</v>
       </c>
       <c r="H23" t="n">
         <v>90616</v>
@@ -1065,7 +1065,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4565696716309</v>
+        <v>10.4565687179565</v>
       </c>
       <c r="H24" t="n">
         <v>157219</v>
@@ -1094,7 +1094,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907693862915</v>
+        <v>10.4907703399658</v>
       </c>
       <c r="H25" t="n">
         <v>150192</v>
@@ -1152,7 +1152,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03728103637695</v>
+        <v>9.03728008270264</v>
       </c>
       <c r="H27" t="n">
         <v>127617</v>
@@ -1181,7 +1181,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743034362793</v>
+        <v>8.97743129730225</v>
       </c>
       <c r="H28" t="n">
         <v>172224</v>
@@ -1268,7 +1268,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057632446289</v>
+        <v>9.43057823181152</v>
       </c>
       <c r="H31" t="n">
         <v>72178</v>
@@ -1326,7 +1326,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142559051514</v>
+        <v>9.66142749786377</v>
       </c>
       <c r="H33" t="n">
         <v>39366</v>
@@ -1384,7 +1384,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3454217910767</v>
+        <v>10.3454208374023</v>
       </c>
       <c r="H35" t="n">
         <v>81482</v>
@@ -1413,7 +1413,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>10.2000722885132</v>
+        <v>10.2000713348389</v>
       </c>
       <c r="H36" t="n">
         <v>73300</v>
@@ -1442,7 +1442,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0037660598755</v>
+        <v>11.0037651062012</v>
       </c>
       <c r="H37" t="n">
         <v>86253</v>
@@ -1471,7 +1471,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506191253662</v>
+        <v>10.5506200790405</v>
       </c>
       <c r="H38" t="n">
         <v>97952</v>
@@ -1529,7 +1529,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G40" t="n">
-        <v>10.1829719543457</v>
+        <v>10.1829710006714</v>
       </c>
       <c r="H40" t="n">
         <v>68122</v>
@@ -1558,7 +1558,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0379657745361</v>
+        <v>11.0379638671875</v>
       </c>
       <c r="H41" t="n">
         <v>191057</v>
@@ -1587,7 +1587,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097166061401</v>
+        <v>10.9097146987915</v>
       </c>
       <c r="H42" t="n">
         <v>105720</v>
@@ -1616,7 +1616,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8074588775635</v>
+        <v>11.8074598312378</v>
       </c>
       <c r="H43" t="n">
         <v>146558</v>
@@ -1645,7 +1645,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442577362061</v>
+        <v>11.9442586898804</v>
       </c>
       <c r="H44" t="n">
         <v>175966</v>
@@ -1703,7 +1703,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732591629028</v>
+        <v>11.7732582092285</v>
       </c>
       <c r="H46" t="n">
         <v>75412</v>
@@ -1761,7 +1761,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.6279106140137</v>
+        <v>11.627911567688</v>
       </c>
       <c r="H48" t="n">
         <v>125028</v>
@@ -1790,7 +1790,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>11.3714122772217</v>
+        <v>11.371413230896</v>
       </c>
       <c r="H49" t="n">
         <v>73494</v>
@@ -1819,7 +1819,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3799629211426</v>
+        <v>11.3799619674683</v>
       </c>
       <c r="H50" t="n">
         <v>138699</v>
@@ -1877,7 +1877,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416595458984</v>
+        <v>11.8416576385498</v>
       </c>
       <c r="H52" t="n">
         <v>101508</v>
@@ -1906,7 +1906,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.918607711792</v>
+        <v>11.9186067581177</v>
       </c>
       <c r="H53" t="n">
         <v>56813</v>
@@ -1964,7 +1964,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>12.0468578338623</v>
+        <v>12.0468587875366</v>
       </c>
       <c r="H55" t="n">
         <v>93874</v>
@@ -1993,7 +1993,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922073364258</v>
+        <v>12.1922063827515</v>
       </c>
       <c r="H56" t="n">
         <v>88317</v>
@@ -2051,7 +2051,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375549316406</v>
+        <v>12.3375558853149</v>
       </c>
       <c r="H58" t="n">
         <v>61525</v>
@@ -2109,7 +2109,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>12.1323556900024</v>
+        <v>12.1323566436768</v>
       </c>
       <c r="H60" t="n">
         <v>36904</v>
@@ -2196,7 +2196,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178544998169</v>
+        <v>12.2178564071655</v>
       </c>
       <c r="H63" t="n">
         <v>42659</v>
@@ -2341,7 +2341,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.2859125137329</v>
+        <v>11.2859134674072</v>
       </c>
       <c r="H68" t="n">
         <v>33579</v>
@@ -2486,7 +2486,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160085678101</v>
+        <v>11.8160095214844</v>
       </c>
       <c r="H73" t="n">
         <v>56893</v>
@@ -2515,7 +2515,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048606872559</v>
+        <v>11.7048597335815</v>
       </c>
       <c r="H74" t="n">
         <v>28658</v>
@@ -2544,7 +2544,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G75" t="n">
-        <v>11.6022605895996</v>
+        <v>11.6022615432739</v>
       </c>
       <c r="H75" t="n">
         <v>40113</v>
@@ -2602,7 +2602,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364603042603</v>
+        <v>11.6364612579346</v>
       </c>
       <c r="H77" t="n">
         <v>21274</v>
@@ -2660,7 +2660,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918649673462</v>
+        <v>11.1918640136719</v>
       </c>
       <c r="H79" t="n">
         <v>107247</v>
@@ -2718,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.114914894104</v>
+        <v>11.1149139404297</v>
       </c>
       <c r="H81" t="n">
         <v>44600</v>
@@ -2747,7 +2747,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3799629211426</v>
+        <v>11.3799619674683</v>
       </c>
       <c r="H82" t="n">
         <v>42005</v>
@@ -2776,7 +2776,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3201112747192</v>
+        <v>11.3201122283936</v>
       </c>
       <c r="H83" t="n">
         <v>33223</v>
@@ -2834,7 +2834,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1576633453369</v>
+        <v>11.1576642990112</v>
       </c>
       <c r="H85" t="n">
         <v>20515</v>
@@ -2863,7 +2863,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0550651550293</v>
+        <v>11.055064201355</v>
       </c>
       <c r="H86" t="n">
         <v>64749</v>
@@ -2892,7 +2892,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.9866676330566</v>
+        <v>10.986665725708</v>
       </c>
       <c r="H87" t="n">
         <v>18020</v>
@@ -2979,7 +2979,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>10.954140663147</v>
+        <v>10.9541425704956</v>
       </c>
       <c r="H90" t="n">
         <v>55438</v>
@@ -3008,7 +3008,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.4346122741699</v>
+        <v>10.4346132278442</v>
       </c>
       <c r="H91" t="n">
         <v>102250</v>
@@ -3037,7 +3037,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G92" t="n">
-        <v>10.3553609848022</v>
+        <v>10.3553619384766</v>
       </c>
       <c r="H92" t="n">
         <v>41348</v>
@@ -3066,7 +3066,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>10.4346122741699</v>
+        <v>10.4346132278442</v>
       </c>
       <c r="H93" t="n">
         <v>49691</v>
@@ -3095,7 +3095,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G94" t="n">
-        <v>10.22327709198</v>
+        <v>10.2232780456543</v>
       </c>
       <c r="H94" t="n">
         <v>77351</v>
@@ -3153,7 +3153,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92389011383057</v>
+        <v>9.92388916015625</v>
       </c>
       <c r="H96" t="n">
         <v>101148</v>
@@ -3182,7 +3182,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G97" t="n">
-        <v>10.3201389312744</v>
+        <v>10.3201398849487</v>
       </c>
       <c r="H97" t="n">
         <v>37803</v>
@@ -3211,7 +3211,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.0031385421753</v>
+        <v>10.003137588501</v>
       </c>
       <c r="H98" t="n">
         <v>56636</v>
@@ -3298,7 +3298,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>10.6107225418091</v>
+        <v>10.6107234954834</v>
       </c>
       <c r="H101" t="n">
         <v>49594</v>
@@ -3327,7 +3327,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120321273804</v>
+        <v>11.4120302200317</v>
       </c>
       <c r="H102" t="n">
         <v>156693</v>
@@ -3356,7 +3356,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H103" t="n">
         <v>70319</v>
@@ -3385,7 +3385,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189195632935</v>
+        <v>10.9189186096191</v>
       </c>
       <c r="H104" t="n">
         <v>30153</v>
@@ -3443,7 +3443,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>11.2799482345581</v>
+        <v>11.2799472808838</v>
       </c>
       <c r="H106" t="n">
         <v>56529</v>
@@ -3472,7 +3472,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H107" t="n">
         <v>63256</v>
@@ -3559,7 +3559,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396682739258</v>
+        <v>10.8396692276001</v>
       </c>
       <c r="H110" t="n">
         <v>35136</v>
@@ -3588,7 +3588,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.9277248382568</v>
+        <v>10.9277229309082</v>
       </c>
       <c r="H111" t="n">
         <v>58146</v>
@@ -3646,7 +3646,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G113" t="n">
-        <v>10.813250541687</v>
+        <v>10.8132514953613</v>
       </c>
       <c r="H113" t="n">
         <v>12086</v>
@@ -3675,7 +3675,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G114" t="n">
-        <v>10.5138607025146</v>
+        <v>10.513861656189</v>
       </c>
       <c r="H114" t="n">
         <v>43277</v>
@@ -3820,7 +3820,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.0383605957031</v>
+        <v>10.0383596420288</v>
       </c>
       <c r="H119" t="n">
         <v>59338</v>
@@ -3878,7 +3878,7 @@
         <v>11.75</v>
       </c>
       <c r="G121" t="n">
-        <v>10.3465557098389</v>
+        <v>10.3465566635132</v>
       </c>
       <c r="H121" t="n">
         <v>50694</v>
@@ -3907,7 +3907,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522228240967</v>
+        <v>10.452223777771</v>
       </c>
       <c r="H122" t="n">
         <v>40375</v>
@@ -3965,7 +3965,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G124" t="n">
-        <v>9.87986087799072</v>
+        <v>9.87986183166504</v>
       </c>
       <c r="H124" t="n">
         <v>94289</v>
@@ -3994,7 +3994,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G125" t="n">
-        <v>9.12257957458496</v>
+        <v>9.12258052825928</v>
       </c>
       <c r="H125" t="n">
         <v>55022</v>
@@ -4023,7 +4023,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733192443848</v>
+        <v>9.67733097076416</v>
       </c>
       <c r="H126" t="n">
         <v>56824</v>
@@ -4052,7 +4052,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G127" t="n">
-        <v>9.57166481018066</v>
+        <v>9.57166576385498</v>
       </c>
       <c r="H127" t="n">
         <v>24263</v>
@@ -4110,7 +4110,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1880559921265</v>
+        <v>10.1880550384521</v>
       </c>
       <c r="H129" t="n">
         <v>25733</v>
@@ -4139,7 +4139,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G130" t="n">
-        <v>9.98552703857422</v>
+        <v>9.98552799224854</v>
       </c>
       <c r="H130" t="n">
         <v>15581</v>
@@ -4197,7 +4197,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.18421840667725</v>
+        <v>9.1842212677002</v>
       </c>
       <c r="H132" t="n">
         <v>96061</v>
@@ -4255,7 +4255,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G134" t="n">
-        <v>9.721360206604</v>
+        <v>9.72135925292969</v>
       </c>
       <c r="H134" t="n">
         <v>37896</v>
@@ -4284,7 +4284,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0823888778687</v>
+        <v>10.0823879241943</v>
       </c>
       <c r="H135" t="n">
         <v>34424</v>
@@ -4313,7 +4313,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G136" t="n">
-        <v>10.3817777633667</v>
+        <v>10.381778717041</v>
       </c>
       <c r="H136" t="n">
         <v>45362</v>
@@ -4342,7 +4342,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G137" t="n">
-        <v>10.3201389312744</v>
+        <v>10.3201398849487</v>
       </c>
       <c r="H137" t="n">
         <v>22891</v>
@@ -4429,7 +4429,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>10.2144718170166</v>
+        <v>10.2144727706909</v>
       </c>
       <c r="H140" t="n">
         <v>22528</v>
@@ -4458,7 +4458,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1528348922729</v>
+        <v>10.15283203125</v>
       </c>
       <c r="H141" t="n">
         <v>23520</v>
@@ -4603,7 +4603,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987791061401</v>
+        <v>10.6987800598145</v>
       </c>
       <c r="H146" t="n">
         <v>35625</v>
@@ -4632,7 +4632,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G147" t="n">
-        <v>11.0774202346802</v>
+        <v>11.0774183273315</v>
       </c>
       <c r="H147" t="n">
         <v>53666</v>
@@ -4661,7 +4661,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G148" t="n">
-        <v>11.0157794952393</v>
+        <v>11.0157804489136</v>
       </c>
       <c r="H148" t="n">
         <v>49513</v>
@@ -4690,7 +4690,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>11.0333909988403</v>
+        <v>11.0333919525146</v>
       </c>
       <c r="H149" t="n">
         <v>32061</v>
@@ -4719,7 +4719,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>11.0333909988403</v>
+        <v>11.0333919525146</v>
       </c>
       <c r="H150" t="n">
         <v>31452</v>
@@ -4777,7 +4777,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893617630005</v>
+        <v>10.9893627166748</v>
       </c>
       <c r="H152" t="n">
         <v>42127</v>
@@ -4864,7 +4864,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9277248382568</v>
+        <v>10.9277229309082</v>
       </c>
       <c r="H155" t="n">
         <v>22842</v>
@@ -4922,7 +4922,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G157" t="n">
-        <v>11.2535305023193</v>
+        <v>11.2535314559937</v>
       </c>
       <c r="H157" t="n">
         <v>72265</v>
@@ -4951,7 +4951,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>11.3151702880859</v>
+        <v>11.3151712417603</v>
       </c>
       <c r="H158" t="n">
         <v>45498</v>
@@ -4980,7 +4980,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>11.2535305023193</v>
+        <v>11.2535314559937</v>
       </c>
       <c r="H159" t="n">
         <v>20029</v>
@@ -5009,7 +5009,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G160" t="n">
-        <v>11.0157794952393</v>
+        <v>11.0157804489136</v>
       </c>
       <c r="H160" t="n">
         <v>57012</v>
@@ -5067,7 +5067,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>11.0510025024414</v>
+        <v>11.0510015487671</v>
       </c>
       <c r="H162" t="n">
         <v>19081</v>
@@ -5096,7 +5096,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>10.9013080596924</v>
+        <v>10.9013061523438</v>
       </c>
       <c r="H163" t="n">
         <v>12830</v>
@@ -5183,7 +5183,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G166" t="n">
-        <v>11.2183074951172</v>
+        <v>11.2183084487915</v>
       </c>
       <c r="H166" t="n">
         <v>21084</v>
@@ -5212,7 +5212,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G167" t="n">
-        <v>11.1214466094971</v>
+        <v>11.1214475631714</v>
       </c>
       <c r="H167" t="n">
         <v>45450</v>
@@ -5241,7 +5241,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>11.0774202346802</v>
+        <v>11.0774183273315</v>
       </c>
       <c r="H168" t="n">
         <v>45236</v>
@@ -5270,7 +5270,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H169" t="n">
         <v>50121</v>
@@ -5299,7 +5299,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>11.1830854415894</v>
+        <v>11.183087348938</v>
       </c>
       <c r="H170" t="n">
         <v>34325</v>
@@ -5328,7 +5328,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G171" t="n">
-        <v>11.2623348236084</v>
+        <v>11.2623357772827</v>
       </c>
       <c r="H171" t="n">
         <v>27441</v>
@@ -5357,7 +5357,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G172" t="n">
-        <v>11.5265035629272</v>
+        <v>11.5265045166016</v>
       </c>
       <c r="H172" t="n">
         <v>102494</v>
@@ -5386,7 +5386,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>11.7466440200806</v>
+        <v>11.7466430664062</v>
       </c>
       <c r="H173" t="n">
         <v>47129</v>
@@ -5415,7 +5415,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G174" t="n">
-        <v>11.7730598449707</v>
+        <v>11.773060798645</v>
       </c>
       <c r="H174" t="n">
         <v>30007</v>
@@ -5531,7 +5531,7 @@
         <v>13.25</v>
       </c>
       <c r="G178" t="n">
-        <v>11.6673936843872</v>
+        <v>11.6673927307129</v>
       </c>
       <c r="H178" t="n">
         <v>36341</v>
@@ -5676,7 +5676,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>11.1390571594238</v>
+        <v>11.1390581130981</v>
       </c>
       <c r="H183" t="n">
         <v>30268</v>
@@ -5705,7 +5705,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G184" t="n">
-        <v>11.6938095092773</v>
+        <v>11.693811416626</v>
       </c>
       <c r="H184" t="n">
         <v>56844</v>
@@ -5821,7 +5821,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G188" t="n">
-        <v>12.0372266769409</v>
+        <v>12.0372257232666</v>
       </c>
       <c r="H188" t="n">
         <v>83675</v>
@@ -5850,7 +5850,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>12.0548391342163</v>
+        <v>12.0548372268677</v>
       </c>
       <c r="H189" t="n">
         <v>61757</v>
@@ -5879,7 +5879,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.0636444091797</v>
+        <v>12.0636434555054</v>
       </c>
       <c r="H190" t="n">
         <v>38989</v>
@@ -5908,7 +5908,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>12.5039234161377</v>
+        <v>12.503924369812</v>
       </c>
       <c r="H191" t="n">
         <v>102776</v>
@@ -5966,7 +5966,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070606231689</v>
+        <v>12.4070615768433</v>
       </c>
       <c r="H193" t="n">
         <v>92196</v>
@@ -5995,7 +5995,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837829589844</v>
+        <v>12.2837839126587</v>
       </c>
       <c r="H194" t="n">
         <v>42892</v>
@@ -6082,7 +6082,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8121194839478</v>
+        <v>12.8121175765991</v>
       </c>
       <c r="H197" t="n">
         <v>94007</v>
@@ -6111,7 +6111,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>12.8561458587646</v>
+        <v>12.8561477661133</v>
       </c>
       <c r="H198" t="n">
         <v>56736</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>13.0322570800781</v>
+        <v>13.0322580337524</v>
       </c>
       <c r="H199" t="n">
         <v>85136</v>
@@ -6198,7 +6198,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782051086426</v>
+        <v>13.5782041549683</v>
       </c>
       <c r="H201" t="n">
         <v>145739</v>
@@ -6227,7 +6227,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G202" t="n">
-        <v>13.6838712692261</v>
+        <v>13.6838703155518</v>
       </c>
       <c r="H202" t="n">
         <v>145564</v>
@@ -6256,7 +6256,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285087585449</v>
+        <v>13.4285078048706</v>
       </c>
       <c r="H203" t="n">
         <v>304187</v>
@@ -6314,7 +6314,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210111618042</v>
+        <v>14.2210121154785</v>
       </c>
       <c r="H205" t="n">
         <v>191135</v>
@@ -6343,7 +6343,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G206" t="n">
-        <v>14.2562341690063</v>
+        <v>14.256233215332</v>
       </c>
       <c r="H206" t="n">
         <v>116903</v>
@@ -6372,7 +6372,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.1329545974731</v>
+        <v>14.1329555511475</v>
       </c>
       <c r="H207" t="n">
         <v>75250</v>
@@ -6401,7 +6401,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241502761841</v>
+        <v>14.1241512298584</v>
       </c>
       <c r="H208" t="n">
         <v>50427</v>
@@ -6430,7 +6430,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0713157653809</v>
+        <v>14.0713148117065</v>
       </c>
       <c r="H209" t="n">
         <v>70266</v>
@@ -6546,7 +6546,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631196975708</v>
+        <v>13.7631216049194</v>
       </c>
       <c r="H213" t="n">
         <v>75863</v>
@@ -6633,7 +6633,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G216" t="n">
-        <v>13.1995639801025</v>
+        <v>13.1995630264282</v>
       </c>
       <c r="H216" t="n">
         <v>212327</v>
@@ -6691,7 +6691,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>13.155535697937</v>
+        <v>13.1555347442627</v>
       </c>
       <c r="H218" t="n">
         <v>60112</v>
@@ -6720,7 +6720,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486482620239</v>
+        <v>13.6486492156982</v>
       </c>
       <c r="H219" t="n">
         <v>47806</v>
@@ -6749,7 +6749,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605926513672</v>
+        <v>13.5605916976929</v>
       </c>
       <c r="H220" t="n">
         <v>47022</v>
@@ -6778,7 +6778,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285087585449</v>
+        <v>13.4285078048706</v>
       </c>
       <c r="H221" t="n">
         <v>144794</v>
@@ -6807,7 +6807,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>13.7367038726807</v>
+        <v>13.736704826355</v>
       </c>
       <c r="H222" t="n">
         <v>115544</v>
@@ -6894,7 +6894,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>14.0977334976196</v>
+        <v>14.0977344512939</v>
       </c>
       <c r="H225" t="n">
         <v>147489</v>
@@ -6923,7 +6923,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G226" t="n">
-        <v>14.7845697402954</v>
+        <v>14.7845687866211</v>
       </c>
       <c r="H226" t="n">
         <v>325482</v>
@@ -6952,7 +6952,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040971755981</v>
+        <v>15.3040981292725</v>
       </c>
       <c r="H227" t="n">
         <v>258275</v>
@@ -6981,7 +6981,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.2776794433594</v>
+        <v>15.277681350708</v>
       </c>
       <c r="H228" t="n">
         <v>398968</v>
@@ -7010,7 +7010,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G229" t="n">
-        <v>15.4890127182007</v>
+        <v>15.4890146255493</v>
       </c>
       <c r="H229" t="n">
         <v>247524</v>
@@ -7039,7 +7039,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978199005127</v>
+        <v>15.497820854187</v>
       </c>
       <c r="H230" t="n">
         <v>289822</v>
@@ -7068,7 +7068,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657388687134</v>
+        <v>15.3657360076904</v>
       </c>
       <c r="H231" t="n">
         <v>110362</v>
@@ -7126,7 +7126,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3393201828003</v>
+        <v>15.3393211364746</v>
       </c>
       <c r="H233" t="n">
         <v>71686</v>
@@ -7155,7 +7155,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5330419540405</v>
+        <v>15.5330400466919</v>
       </c>
       <c r="H234" t="n">
         <v>122396</v>
@@ -7184,7 +7184,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G235" t="n">
-        <v>15.6651268005371</v>
+        <v>15.6651258468628</v>
       </c>
       <c r="H235" t="n">
         <v>210948</v>
@@ -7213,7 +7213,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418491363525</v>
+        <v>15.5418481826782</v>
       </c>
       <c r="H236" t="n">
         <v>99490</v>
@@ -7242,7 +7242,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>15.2424573898315</v>
+        <v>15.2424602508545</v>
       </c>
       <c r="H237" t="n">
         <v>98091</v>
@@ -7271,7 +7271,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.2776794433594</v>
+        <v>15.277681350708</v>
       </c>
       <c r="H238" t="n">
         <v>97203</v>
@@ -7300,7 +7300,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>15.8060169219971</v>
+        <v>15.8060159683228</v>
       </c>
       <c r="H239" t="n">
         <v>125335</v>
@@ -7329,7 +7329,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G240" t="n">
-        <v>16.1934585571289</v>
+        <v>16.1934604644775</v>
       </c>
       <c r="H240" t="n">
         <v>378003</v>
@@ -7387,7 +7387,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.4664325714111</v>
+        <v>16.4664344787598</v>
       </c>
       <c r="H242" t="n">
         <v>118582</v>
@@ -7474,7 +7474,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.0387992858887</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H245" t="n">
         <v>177039</v>
@@ -7503,7 +7503,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.8891010284424</v>
+        <v>16.889102935791</v>
       </c>
       <c r="H246" t="n">
         <v>240701</v>
@@ -7590,7 +7590,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>16.5544891357422</v>
+        <v>16.5544872283936</v>
       </c>
       <c r="H249" t="n">
         <v>545131</v>
@@ -7619,7 +7619,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>16.2374897003174</v>
+        <v>16.2374858856201</v>
       </c>
       <c r="H250" t="n">
         <v>353155</v>
@@ -7677,7 +7677,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G252" t="n">
-        <v>16.6513519287109</v>
+        <v>16.6513500213623</v>
       </c>
       <c r="H252" t="n">
         <v>93094</v>
@@ -7706,7 +7706,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>16.5720996856689</v>
+        <v>16.5721015930176</v>
       </c>
       <c r="H253" t="n">
         <v>93811</v>
@@ -7735,7 +7735,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947700500488</v>
+        <v>16.9947681427002</v>
       </c>
       <c r="H254" t="n">
         <v>161135</v>
@@ -7764,7 +7764,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G255" t="n">
-        <v>16.7041835784912</v>
+        <v>16.7041873931885</v>
       </c>
       <c r="H255" t="n">
         <v>52207</v>
@@ -7793,7 +7793,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.8802967071533</v>
+        <v>16.8802947998047</v>
       </c>
       <c r="H256" t="n">
         <v>74391</v>
@@ -7822,7 +7822,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538799285889</v>
+        <v>16.8538818359375</v>
       </c>
       <c r="H257" t="n">
         <v>23740</v>
@@ -7851,7 +7851,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.012378692627</v>
+        <v>17.0123805999756</v>
       </c>
       <c r="H258" t="n">
         <v>25398</v>
@@ -7967,7 +7967,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.0387992858887</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H262" t="n">
         <v>26170</v>
@@ -7996,7 +7996,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G263" t="n">
-        <v>16.5368804931641</v>
+        <v>16.5368785858154</v>
       </c>
       <c r="H263" t="n">
         <v>65318</v>
@@ -8083,7 +8083,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>17.2061042785645</v>
+        <v>17.2061004638672</v>
       </c>
       <c r="H266" t="n">
         <v>93971</v>
@@ -8112,7 +8112,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>17.3469924926758</v>
+        <v>17.3469944000244</v>
       </c>
       <c r="H267" t="n">
         <v>96917</v>
@@ -8141,7 +8141,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551895141602</v>
+        <v>17.6551856994629</v>
       </c>
       <c r="H268" t="n">
         <v>75995</v>
@@ -8286,7 +8286,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>17.55832862854</v>
+        <v>17.5583267211914</v>
       </c>
       <c r="H273" t="n">
         <v>24496</v>
@@ -8315,7 +8315,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432422637939</v>
+        <v>17.7432441711426</v>
       </c>
       <c r="H274" t="n">
         <v>80664</v>
@@ -8402,7 +8402,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>17.5759372711182</v>
+        <v>17.5759353637695</v>
       </c>
       <c r="H277" t="n">
         <v>65783</v>
@@ -8431,7 +8431,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482109069824</v>
+        <v>16.7482128143311</v>
       </c>
       <c r="H278" t="n">
         <v>113676</v>
@@ -8460,7 +8460,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G279" t="n">
-        <v>16.7658252716064</v>
+        <v>16.7658214569092</v>
       </c>
       <c r="H279" t="n">
         <v>82633</v>
@@ -8605,7 +8605,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>17.1092433929443</v>
+        <v>17.1092395782471</v>
       </c>
       <c r="H284" t="n">
         <v>50524</v>
@@ -8663,7 +8663,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.8891010284424</v>
+        <v>16.889102935791</v>
       </c>
       <c r="H286" t="n">
         <v>33722</v>
@@ -8692,7 +8692,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G287" t="n">
-        <v>16.8186550140381</v>
+        <v>16.8186588287354</v>
       </c>
       <c r="H287" t="n">
         <v>24250</v>
@@ -8779,7 +8779,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G290" t="n">
-        <v>17.2325191497803</v>
+        <v>17.2325172424316</v>
       </c>
       <c r="H290" t="n">
         <v>110900</v>
@@ -8866,7 +8866,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3910217285156</v>
+        <v>17.391019821167</v>
       </c>
       <c r="H293" t="n">
         <v>29528</v>
@@ -8895,7 +8895,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>17.1092433929443</v>
+        <v>17.1092395782471</v>
       </c>
       <c r="H294" t="n">
         <v>52387</v>
@@ -8982,7 +8982,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350452423096</v>
+        <v>17.4350471496582</v>
       </c>
       <c r="H297" t="n">
         <v>105130</v>
@@ -9011,7 +9011,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734073638916</v>
+        <v>17.3734092712402</v>
       </c>
       <c r="H298" t="n">
         <v>48083</v>
@@ -9127,7 +9127,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G302" t="n">
-        <v>19.9358310699463</v>
+        <v>19.9358329772949</v>
       </c>
       <c r="H302" t="n">
         <v>140384</v>
@@ -9185,7 +9185,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962505340576</v>
+        <v>20.5962524414062</v>
       </c>
       <c r="H304" t="n">
         <v>71698</v>
@@ -9214,7 +9214,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>20.3408908843994</v>
+        <v>20.3408889770508</v>
       </c>
       <c r="H305" t="n">
         <v>87911</v>
@@ -9243,7 +9243,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8340015411377</v>
+        <v>20.8339996337891</v>
       </c>
       <c r="H306" t="n">
         <v>87962</v>
@@ -9301,7 +9301,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824756622314</v>
+        <v>21.5824794769287</v>
       </c>
       <c r="H308" t="n">
         <v>115604</v>
@@ -9330,7 +9330,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>21.0893630981445</v>
+        <v>21.0893650054932</v>
       </c>
       <c r="H309" t="n">
         <v>116636</v>
@@ -9388,7 +9388,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G311" t="n">
-        <v>21.6529197692871</v>
+        <v>21.6529178619385</v>
       </c>
       <c r="H311" t="n">
         <v>78484</v>
@@ -9446,7 +9446,7 @@
         <v>24.8899993896484</v>
       </c>
       <c r="G313" t="n">
-        <v>21.9170875549316</v>
+        <v>21.917085647583</v>
       </c>
       <c r="H313" t="n">
         <v>91167</v>
@@ -9475,7 +9475,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>21.8114223480225</v>
+        <v>21.8114204406738</v>
       </c>
       <c r="H314" t="n">
         <v>83092</v>
@@ -9533,7 +9533,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.286922454834</v>
+        <v>22.2869205474854</v>
       </c>
       <c r="H316" t="n">
         <v>115542</v>
@@ -9562,7 +9562,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605075836182</v>
+        <v>22.2605056762695</v>
       </c>
       <c r="H317" t="n">
         <v>83792</v>
@@ -9591,7 +9591,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G318" t="n">
-        <v>22.3485622406006</v>
+        <v>22.3485584259033</v>
       </c>
       <c r="H318" t="n">
         <v>54563</v>
@@ -9620,7 +9620,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221454620361</v>
+        <v>22.3221473693848</v>
       </c>
       <c r="H319" t="n">
         <v>60853</v>
@@ -9678,7 +9678,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>22.6303405761719</v>
+        <v>22.6303424835205</v>
       </c>
       <c r="H321" t="n">
         <v>84960</v>
@@ -9707,7 +9707,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>22.4366149902344</v>
+        <v>22.436616897583</v>
       </c>
       <c r="H322" t="n">
         <v>60620</v>
@@ -9736,7 +9736,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G323" t="n">
-        <v>22.4806461334229</v>
+        <v>22.4806442260742</v>
       </c>
       <c r="H323" t="n">
         <v>98956</v>
@@ -9794,7 +9794,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G325" t="n">
-        <v>22.4806461334229</v>
+        <v>22.4806442260742</v>
       </c>
       <c r="H325" t="n">
         <v>36599</v>
@@ -9823,7 +9823,7 @@
         <v>25.6900005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>22.6215343475342</v>
+        <v>22.6215324401855</v>
       </c>
       <c r="H326" t="n">
         <v>41825</v>
@@ -10055,7 +10055,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G334" t="n">
-        <v>23.3876190185547</v>
+        <v>23.387622833252</v>
       </c>
       <c r="H334" t="n">
         <v>64034</v>
@@ -10113,7 +10113,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>23.9159526824951</v>
+        <v>23.9159545898438</v>
       </c>
       <c r="H336" t="n">
         <v>100966</v>
@@ -10171,7 +10171,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G338" t="n">
-        <v>24.7084560394287</v>
+        <v>24.7084541320801</v>
       </c>
       <c r="H338" t="n">
         <v>103140</v>
@@ -10258,7 +10258,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870952606201</v>
+        <v>25.0870971679688</v>
       </c>
       <c r="H341" t="n">
         <v>113660</v>
@@ -10316,7 +10316,7 @@
         <v>28.2700004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>24.8933753967285</v>
+        <v>24.8933734893799</v>
       </c>
       <c r="H343" t="n">
         <v>72745</v>
@@ -10345,7 +10345,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255466461182</v>
+        <v>26.4255447387695</v>
       </c>
       <c r="H344" t="n">
         <v>323645</v>
@@ -10403,7 +10403,7 @@
         <v>30.7399997711182</v>
       </c>
       <c r="G346" t="n">
-        <v>27.3970069885254</v>
+        <v>27.3970050811768</v>
       </c>
       <c r="H346" t="n">
         <v>110655</v>
@@ -10461,7 +10461,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>28.1545677185059</v>
+        <v>28.1545696258545</v>
       </c>
       <c r="H348" t="n">
         <v>94775</v>
@@ -10548,7 +10548,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>29.3666706085205</v>
+        <v>29.3666687011719</v>
       </c>
       <c r="H351" t="n">
         <v>132004</v>
@@ -10577,7 +10577,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>27.8069801330566</v>
+        <v>27.8069839477539</v>
       </c>
       <c r="H352" t="n">
         <v>138482</v>
@@ -10606,7 +10606,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665050506592</v>
+        <v>28.4665069580078</v>
       </c>
       <c r="H353" t="n">
         <v>149589</v>
@@ -10693,7 +10693,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>29.7677364349365</v>
+        <v>29.7677326202393</v>
       </c>
       <c r="H356" t="n">
         <v>96078</v>
@@ -10722,7 +10722,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746814727783</v>
+        <v>29.874683380127</v>
       </c>
       <c r="H357" t="n">
         <v>77270</v>
@@ -10751,7 +10751,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024806976318</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H358" t="n">
         <v>94582</v>
@@ -10780,7 +10780,7 @@
         <v>34.5299987792969</v>
       </c>
       <c r="G359" t="n">
-        <v>30.774845123291</v>
+        <v>30.7748413085938</v>
       </c>
       <c r="H359" t="n">
         <v>96091</v>
@@ -10809,7 +10809,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400932312012</v>
+        <v>30.2400913238525</v>
       </c>
       <c r="H360" t="n">
         <v>60227</v>
@@ -10838,7 +10838,7 @@
         <v>34.4099998474121</v>
       </c>
       <c r="G361" t="n">
-        <v>30.6678943634033</v>
+        <v>30.6678905487061</v>
       </c>
       <c r="H361" t="n">
         <v>129532</v>
@@ -10867,7 +10867,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283157348633</v>
+        <v>30.8283195495605</v>
       </c>
       <c r="H362" t="n">
         <v>119866</v>
@@ -10896,7 +10896,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996200561523</v>
+        <v>30.8996162414551</v>
       </c>
       <c r="H363" t="n">
         <v>56630</v>
@@ -10925,7 +10925,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154800415039</v>
+        <v>31.0154781341553</v>
       </c>
       <c r="H364" t="n">
         <v>62681</v>
@@ -10954,7 +10954,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.9976539611816</v>
+        <v>30.997652053833</v>
       </c>
       <c r="H365" t="n">
         <v>39009</v>
@@ -10983,7 +10983,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.9352684020996</v>
+        <v>30.9352645874023</v>
       </c>
       <c r="H366" t="n">
         <v>57384</v>
@@ -11012,7 +11012,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G367" t="n">
-        <v>30.6500625610352</v>
+        <v>30.6500663757324</v>
       </c>
       <c r="H367" t="n">
         <v>49692</v>
@@ -11041,7 +11041,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.7481079101562</v>
+        <v>30.7481060028076</v>
       </c>
       <c r="H368" t="n">
         <v>76769</v>
@@ -11070,7 +11070,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857204437256</v>
+        <v>30.6857166290283</v>
       </c>
       <c r="H369" t="n">
         <v>81969</v>
@@ -11099,7 +11099,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G370" t="n">
-        <v>29.3577537536621</v>
+        <v>29.3577556610107</v>
       </c>
       <c r="H370" t="n">
         <v>121414</v>
@@ -11157,7 +11157,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G372" t="n">
-        <v>29.3131923675537</v>
+        <v>29.3131942749023</v>
       </c>
       <c r="H372" t="n">
         <v>62583</v>
@@ -11186,7 +11186,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>29.2775459289551</v>
+        <v>29.2775440216064</v>
       </c>
       <c r="H373" t="n">
         <v>103705</v>
@@ -11215,7 +11215,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.1687889099121</v>
+        <v>30.1687908172607</v>
       </c>
       <c r="H374" t="n">
         <v>129825</v>
@@ -11244,7 +11244,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331462860107</v>
+        <v>30.1331443786621</v>
       </c>
       <c r="H375" t="n">
         <v>53130</v>
@@ -11302,7 +11302,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G377" t="n">
-        <v>29.9281597137451</v>
+        <v>29.9281558990479</v>
       </c>
       <c r="H377" t="n">
         <v>47170</v>
@@ -11360,7 +11360,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.482536315918</v>
+        <v>29.4825305938721</v>
       </c>
       <c r="H379" t="n">
         <v>44022</v>
@@ -11418,7 +11418,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G381" t="n">
-        <v>28.9121322631836</v>
+        <v>28.912130355835</v>
       </c>
       <c r="H381" t="n">
         <v>56347</v>
@@ -11447,7 +11447,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.1260299682617</v>
+        <v>29.1260318756104</v>
       </c>
       <c r="H382" t="n">
         <v>60542</v>
@@ -11476,7 +11476,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>27.7713298797607</v>
+        <v>27.771333694458</v>
       </c>
       <c r="H383" t="n">
         <v>57971</v>
@@ -11534,7 +11534,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544078826904</v>
+        <v>27.2544097900391</v>
       </c>
       <c r="H385" t="n">
         <v>71103</v>
@@ -11563,7 +11563,7 @@
         <v>31.0699996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>27.6911182403564</v>
+        <v>27.6911201477051</v>
       </c>
       <c r="H386" t="n">
         <v>94629</v>
@@ -11708,7 +11708,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178554534912</v>
+        <v>27.7178573608398</v>
       </c>
       <c r="H391" t="n">
         <v>37483</v>
@@ -11737,7 +11737,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734577178955</v>
+        <v>28.5734596252441</v>
       </c>
       <c r="H392" t="n">
         <v>75319</v>
@@ -11824,7 +11824,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>28.7873554229736</v>
+        <v>28.7873573303223</v>
       </c>
       <c r="H395" t="n">
         <v>65931</v>
@@ -11853,7 +11853,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665050506592</v>
+        <v>28.4665069580078</v>
       </c>
       <c r="H396" t="n">
         <v>45353</v>
@@ -11882,7 +11882,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855548858643</v>
+        <v>29.7855529785156</v>
       </c>
       <c r="H397" t="n">
         <v>145142</v>
@@ -11969,7 +11969,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.1705951690674</v>
+        <v>29.1705932617188</v>
       </c>
       <c r="H400" t="n">
         <v>60603</v>
@@ -12056,7 +12056,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221092224121</v>
+        <v>29.3221073150635</v>
       </c>
       <c r="H403" t="n">
         <v>93384</v>
@@ -12172,7 +12172,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G407" t="n">
-        <v>28.9923439025879</v>
+        <v>28.9923419952393</v>
       </c>
       <c r="H407" t="n">
         <v>32363</v>
@@ -12201,7 +12201,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477787017822</v>
+        <v>28.9477806091309</v>
       </c>
       <c r="H408" t="n">
         <v>25669</v>
@@ -12230,7 +12230,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>29.7677364349365</v>
+        <v>29.7677326202393</v>
       </c>
       <c r="H409" t="n">
         <v>74517</v>
@@ -12317,7 +12317,7 @@
         <v>32.9900016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>29.402322769165</v>
+        <v>29.4023189544678</v>
       </c>
       <c r="H412" t="n">
         <v>67361</v>
@@ -12491,7 +12491,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>29.6786003112793</v>
+        <v>29.6786022186279</v>
       </c>
       <c r="H418" t="n">
         <v>29416</v>
@@ -12549,7 +12549,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>30.1420574188232</v>
+        <v>30.142053604126</v>
       </c>
       <c r="H420" t="n">
         <v>33779</v>
@@ -12578,7 +12578,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390312194824</v>
+        <v>29.8390293121338</v>
       </c>
       <c r="H421" t="n">
         <v>26190</v>
@@ -12665,7 +12665,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.5181789398193</v>
+        <v>29.518180847168</v>
       </c>
       <c r="H424" t="n">
         <v>23018</v>
@@ -12723,7 +12723,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>29.437967300415</v>
+        <v>29.4379692077637</v>
       </c>
       <c r="H426" t="n">
         <v>57589</v>
@@ -12752,7 +12752,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648681640625</v>
+        <v>30.3648700714111</v>
       </c>
       <c r="H427" t="n">
         <v>64685</v>
@@ -12781,7 +12781,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629077911377</v>
+        <v>30.4629039764404</v>
       </c>
       <c r="H428" t="n">
         <v>65836</v>
@@ -12810,7 +12810,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024806976318</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H429" t="n">
         <v>35077</v>
@@ -12839,7 +12839,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G430" t="n">
-        <v>30.4718189239502</v>
+        <v>30.4718170166016</v>
       </c>
       <c r="H430" t="n">
         <v>35469</v>
@@ -12868,7 +12868,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G431" t="n">
-        <v>30.2935676574707</v>
+        <v>30.293571472168</v>
       </c>
       <c r="H431" t="n">
         <v>27202</v>
@@ -12897,7 +12897,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974979400635</v>
+        <v>30.0974941253662</v>
       </c>
       <c r="H432" t="n">
         <v>12531</v>
@@ -12955,7 +12955,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.2311763763428</v>
+        <v>30.2311782836914</v>
       </c>
       <c r="H434" t="n">
         <v>24161</v>
@@ -12984,7 +12984,7 @@
         <v>36</v>
       </c>
       <c r="G435" t="n">
-        <v>32.0849838256836</v>
+        <v>32.0849800109863</v>
       </c>
       <c r="H435" t="n">
         <v>209022</v>
@@ -13013,7 +13013,7 @@
         <v>36</v>
       </c>
       <c r="G436" t="n">
-        <v>32.0849838256836</v>
+        <v>32.0849800109863</v>
       </c>
       <c r="H436" t="n">
         <v>73331</v>
@@ -13042,7 +13042,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>31.4967517852783</v>
+        <v>31.496753692627</v>
       </c>
       <c r="H437" t="n">
         <v>105328</v>
@@ -13071,7 +13071,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G438" t="n">
-        <v>30.819408416748</v>
+        <v>30.8194065093994</v>
       </c>
       <c r="H438" t="n">
         <v>80310</v>
@@ -13129,7 +13129,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G440" t="n">
-        <v>31.773042678833</v>
+        <v>31.7730464935303</v>
       </c>
       <c r="H440" t="n">
         <v>27909</v>
@@ -13158,7 +13158,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G441" t="n">
-        <v>31.773042678833</v>
+        <v>31.7730464935303</v>
       </c>
       <c r="H441" t="n">
         <v>20121</v>
@@ -13187,7 +13187,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928272247314</v>
+        <v>31.6928310394287</v>
       </c>
       <c r="H442" t="n">
         <v>33799</v>
@@ -13274,7 +13274,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.9512958526611</v>
+        <v>31.9512882232666</v>
       </c>
       <c r="H445" t="n">
         <v>54557</v>
@@ -13332,7 +13332,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990394592285</v>
+        <v>33.1990432739258</v>
       </c>
       <c r="H447" t="n">
         <v>128921</v>
@@ -13361,7 +13361,7 @@
         <v>37.4700012207031</v>
       </c>
       <c r="G448" t="n">
-        <v>33.3951187133789</v>
+        <v>33.3951225280762</v>
       </c>
       <c r="H448" t="n">
         <v>44537</v>
@@ -13419,7 +13419,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>34.6963386535645</v>
+        <v>34.6963424682617</v>
       </c>
       <c r="H450" t="n">
         <v>96401</v>
@@ -13448,7 +13448,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.7319869995117</v>
+        <v>34.7319946289062</v>
       </c>
       <c r="H451" t="n">
         <v>72300</v>
@@ -13506,7 +13506,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>34.2239761352539</v>
+        <v>34.2239837646484</v>
       </c>
       <c r="H453" t="n">
         <v>40089</v>
@@ -13535,7 +13535,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.437873840332</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H454" t="n">
         <v>22990</v>
@@ -13564,7 +13564,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.437873840332</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H455" t="n">
         <v>25085</v>
@@ -13651,7 +13651,7 @@
         <v>39.75</v>
       </c>
       <c r="G458" t="n">
-        <v>35.4271621704102</v>
+        <v>35.4271659851074</v>
       </c>
       <c r="H458" t="n">
         <v>72239</v>
@@ -13680,7 +13680,7 @@
         <v>39.5200004577637</v>
       </c>
       <c r="G459" t="n">
-        <v>35.2221755981445</v>
+        <v>35.2221832275391</v>
       </c>
       <c r="H459" t="n">
         <v>35360</v>
@@ -13709,7 +13709,7 @@
         <v>38.8899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>34.6606903076172</v>
+        <v>34.6606864929199</v>
       </c>
       <c r="H460" t="n">
         <v>44719</v>
@@ -13738,7 +13738,7 @@
         <v>38.5699996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>34.37548828125</v>
+        <v>34.3754920959473</v>
       </c>
       <c r="H461" t="n">
         <v>28779</v>
@@ -13767,7 +13767,7 @@
         <v>38</v>
       </c>
       <c r="G462" t="n">
-        <v>33.8674736022949</v>
+        <v>33.8674774169922</v>
       </c>
       <c r="H462" t="n">
         <v>58890</v>
@@ -13825,7 +13825,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G464" t="n">
-        <v>34.1437644958496</v>
+        <v>34.1437683105469</v>
       </c>
       <c r="H464" t="n">
         <v>21788</v>
@@ -13854,7 +13854,7 @@
         <v>38</v>
       </c>
       <c r="G465" t="n">
-        <v>33.8674736022949</v>
+        <v>33.8674774169922</v>
       </c>
       <c r="H465" t="n">
         <v>19781</v>
@@ -13941,7 +13941,7 @@
         <v>38.5</v>
       </c>
       <c r="G468" t="n">
-        <v>34.3130989074707</v>
+        <v>34.313102722168</v>
       </c>
       <c r="H468" t="n">
         <v>152768</v>
@@ -13970,7 +13970,7 @@
         <v>38.5</v>
       </c>
       <c r="G469" t="n">
-        <v>34.3130989074707</v>
+        <v>34.313102722168</v>
       </c>
       <c r="H469" t="n">
         <v>119331</v>
@@ -13999,7 +13999,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G470" t="n">
-        <v>34.1170234680176</v>
+        <v>34.1170310974121</v>
       </c>
       <c r="H470" t="n">
         <v>74592</v>
@@ -14028,7 +14028,7 @@
         <v>38.6199989318848</v>
       </c>
       <c r="G471" t="n">
-        <v>34.420051574707</v>
+        <v>34.4200553894043</v>
       </c>
       <c r="H471" t="n">
         <v>26257</v>
@@ -14057,7 +14057,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G472" t="n">
-        <v>34.1170234680176</v>
+        <v>34.1170310974121</v>
       </c>
       <c r="H472" t="n">
         <v>63699</v>
@@ -14086,7 +14086,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G473" t="n">
-        <v>34.7765502929688</v>
+        <v>34.776554107666</v>
       </c>
       <c r="H473" t="n">
         <v>35970</v>
@@ -14115,7 +14115,7 @@
         <v>38.8400001525879</v>
       </c>
       <c r="G474" t="n">
-        <v>34.6161270141602</v>
+        <v>34.6161308288574</v>
       </c>
       <c r="H474" t="n">
         <v>28179</v>
@@ -14144,7 +14144,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041877746582</v>
+        <v>34.3041954040527</v>
       </c>
       <c r="H475" t="n">
         <v>35545</v>
@@ -14173,7 +14173,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081161499023</v>
+        <v>34.1081123352051</v>
       </c>
       <c r="H476" t="n">
         <v>84787</v>
@@ -14260,7 +14260,7 @@
         <v>39.3899993896484</v>
       </c>
       <c r="G479" t="n">
-        <v>35.106315612793</v>
+        <v>35.1063194274902</v>
       </c>
       <c r="H479" t="n">
         <v>154448</v>
@@ -14318,7 +14318,7 @@
         <v>40.7299995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>36.3005905151367</v>
+        <v>36.3005867004395</v>
       </c>
       <c r="H481" t="n">
         <v>83025</v>
@@ -14347,7 +14347,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G482" t="n">
-        <v>36.1847267150879</v>
+        <v>36.1847305297852</v>
       </c>
       <c r="H482" t="n">
         <v>68855</v>
@@ -14405,7 +14405,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G484" t="n">
-        <v>37.4146499633789</v>
+        <v>37.4146537780762</v>
       </c>
       <c r="H484" t="n">
         <v>96543</v>
@@ -14434,7 +14434,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.8584785461426</v>
+        <v>38.858470916748</v>
       </c>
       <c r="H485" t="n">
         <v>114697</v>
@@ -14463,7 +14463,7 @@
         <v>43.6699981689453</v>
       </c>
       <c r="G486" t="n">
-        <v>38.9208641052246</v>
+        <v>38.9208602905273</v>
       </c>
       <c r="H486" t="n">
         <v>113917</v>
@@ -14521,7 +14521,7 @@
         <v>43.2900009155273</v>
       </c>
       <c r="G488" t="n">
-        <v>38.5821914672852</v>
+        <v>38.5821876525879</v>
       </c>
       <c r="H488" t="n">
         <v>84905</v>
@@ -14550,7 +14550,7 @@
         <v>42.939998626709</v>
       </c>
       <c r="G489" t="n">
-        <v>38.2702522277832</v>
+        <v>38.2702484130859</v>
       </c>
       <c r="H489" t="n">
         <v>42520</v>
@@ -14579,7 +14579,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G490" t="n">
-        <v>38.4306755065918</v>
+        <v>38.4306716918945</v>
       </c>
       <c r="H490" t="n">
         <v>37738</v>
@@ -14637,7 +14637,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.805004119873</v>
+        <v>38.8049964904785</v>
       </c>
       <c r="H492" t="n">
         <v>92161</v>
@@ -14666,7 +14666,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G493" t="n">
-        <v>37.8068008422852</v>
+        <v>37.8067970275879</v>
       </c>
       <c r="H493" t="n">
         <v>73604</v>
@@ -14695,7 +14695,7 @@
         <v>43.0299987792969</v>
       </c>
       <c r="G494" t="n">
-        <v>38.3504638671875</v>
+        <v>38.350456237793</v>
       </c>
       <c r="H494" t="n">
         <v>72056</v>
@@ -14782,7 +14782,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.3415489196777</v>
+        <v>38.341552734375</v>
       </c>
       <c r="H497" t="n">
         <v>44383</v>
@@ -14811,7 +14811,7 @@
         <v>43.2200012207031</v>
       </c>
       <c r="G498" t="n">
-        <v>38.5198059082031</v>
+        <v>38.5198020935059</v>
       </c>
       <c r="H498" t="n">
         <v>61880</v>
@@ -14869,7 +14869,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G500" t="n">
-        <v>38.4306755065918</v>
+        <v>38.4306716918945</v>
       </c>
       <c r="H500" t="n">
         <v>89203</v>
@@ -14898,7 +14898,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089248657227</v>
+        <v>38.6089210510254</v>
       </c>
       <c r="H501" t="n">
         <v>39100</v>
@@ -14985,7 +14985,7 @@
         <v>44.25</v>
       </c>
       <c r="G504" t="n">
-        <v>39.4377899169922</v>
+        <v>39.4377861022949</v>
       </c>
       <c r="H504" t="n">
         <v>47066</v>
@@ -15043,7 +15043,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545539855957</v>
+        <v>39.0545501708984</v>
       </c>
       <c r="H506" t="n">
         <v>27453</v>
@@ -15072,7 +15072,7 @@
         <v>44.1199989318848</v>
       </c>
       <c r="G507" t="n">
-        <v>39.3219223022461</v>
+        <v>39.3219261169434</v>
       </c>
       <c r="H507" t="n">
         <v>32415</v>
@@ -15246,7 +15246,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G513" t="n">
-        <v>37.6820220947266</v>
+        <v>37.6820259094238</v>
       </c>
       <c r="H513" t="n">
         <v>41367</v>
@@ -15275,7 +15275,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G514" t="n">
-        <v>38.4663238525391</v>
+        <v>38.4663276672363</v>
       </c>
       <c r="H514" t="n">
         <v>46576</v>
@@ -15362,7 +15362,7 @@
         <v>48.0400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>42.8156204223633</v>
+        <v>42.8156280517578</v>
       </c>
       <c r="H517" t="n">
         <v>52703</v>
@@ -15391,7 +15391,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.4234657287598</v>
+        <v>42.4234733581543</v>
       </c>
       <c r="H518" t="n">
         <v>40840</v>
@@ -15420,7 +15420,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G519" t="n">
-        <v>42.0313186645508</v>
+        <v>42.031322479248</v>
       </c>
       <c r="H519" t="n">
         <v>42498</v>
@@ -15478,7 +15478,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G521" t="n">
-        <v>41.9243698120117</v>
+        <v>41.924373626709</v>
       </c>
       <c r="H521" t="n">
         <v>37652</v>
@@ -15507,7 +15507,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>41.6213455200195</v>
+        <v>41.6213493347168</v>
       </c>
       <c r="H522" t="n">
         <v>37738</v>
@@ -15536,7 +15536,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G523" t="n">
-        <v>42.0313186645508</v>
+        <v>42.031322479248</v>
       </c>
       <c r="H523" t="n">
         <v>38729</v>
@@ -15623,7 +15623,7 @@
         <v>47.2799987792969</v>
       </c>
       <c r="G526" t="n">
-        <v>42.1382713317871</v>
+        <v>42.1382675170898</v>
       </c>
       <c r="H526" t="n">
         <v>32130</v>
@@ -15652,7 +15652,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G527" t="n">
-        <v>41.9243698120117</v>
+        <v>41.924373626709</v>
       </c>
       <c r="H527" t="n">
         <v>25137</v>
@@ -15681,7 +15681,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G528" t="n">
-        <v>41.6926460266113</v>
+        <v>41.6926498413086</v>
       </c>
       <c r="H528" t="n">
         <v>21631</v>
@@ -15739,7 +15739,7 @@
         <v>46.8800010681152</v>
       </c>
       <c r="G530" t="n">
-        <v>41.7817726135254</v>
+        <v>41.7817764282227</v>
       </c>
       <c r="H530" t="n">
         <v>30670</v>
@@ -15826,7 +15826,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G533" t="n">
-        <v>40.355770111084</v>
+        <v>40.3557739257812</v>
       </c>
       <c r="H533" t="n">
         <v>51912</v>
@@ -15884,7 +15884,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G535" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H535" t="n">
         <v>40370</v>
@@ -15942,7 +15942,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784248352051</v>
+        <v>39.6784324645996</v>
       </c>
       <c r="H537" t="n">
         <v>153620</v>
@@ -16000,7 +16000,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G539" t="n">
-        <v>41.4787521362305</v>
+        <v>41.4787483215332</v>
       </c>
       <c r="H539" t="n">
         <v>164721</v>
@@ -16058,7 +16058,7 @@
         <v>42.1599998474121</v>
       </c>
       <c r="G541" t="n">
-        <v>37.5750770568848</v>
+        <v>37.5750732421875</v>
       </c>
       <c r="H541" t="n">
         <v>81858</v>
@@ -16145,7 +16145,7 @@
         <v>44.4199981689453</v>
       </c>
       <c r="G544" t="n">
-        <v>39.5893020629883</v>
+        <v>39.5892944335938</v>
       </c>
       <c r="H544" t="n">
         <v>70654</v>
@@ -16174,7 +16174,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>40.1953468322754</v>
+        <v>40.1953506469727</v>
       </c>
       <c r="H545" t="n">
         <v>42666</v>
@@ -16203,7 +16203,7 @@
         <v>45</v>
       </c>
       <c r="G546" t="n">
-        <v>40.1062278747559</v>
+        <v>40.1062240600586</v>
       </c>
       <c r="H546" t="n">
         <v>31017</v>
@@ -16290,7 +16290,7 @@
         <v>45.939998626709</v>
       </c>
       <c r="G549" t="n">
-        <v>40.9439926147461</v>
+        <v>40.9440002441406</v>
       </c>
       <c r="H549" t="n">
         <v>33774</v>
@@ -16348,7 +16348,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400718688965</v>
+        <v>41.1400680541992</v>
       </c>
       <c r="H551" t="n">
         <v>31765</v>
@@ -16377,7 +16377,7 @@
         <v>46</v>
       </c>
       <c r="G552" t="n">
-        <v>40.9974670410156</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H552" t="n">
         <v>62087</v>
@@ -16406,7 +16406,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G553" t="n">
-        <v>40.5161972045898</v>
+        <v>40.5162010192871</v>
       </c>
       <c r="H553" t="n">
         <v>34881</v>
@@ -16464,7 +16464,7 @@
         <v>44.0400009155273</v>
       </c>
       <c r="G555" t="n">
-        <v>39.2506256103516</v>
+        <v>39.2506294250488</v>
       </c>
       <c r="H555" t="n">
         <v>114926</v>
@@ -16493,7 +16493,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793251037598</v>
+        <v>39.1793212890625</v>
       </c>
       <c r="H556" t="n">
         <v>64193</v>
@@ -16522,7 +16522,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131767272949</v>
+        <v>40.2131729125977</v>
       </c>
       <c r="H557" t="n">
         <v>48880</v>
@@ -16551,7 +16551,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914260864258</v>
+        <v>40.3914222717285</v>
       </c>
       <c r="H558" t="n">
         <v>72029</v>
@@ -16580,7 +16580,7 @@
         <v>46</v>
       </c>
       <c r="G559" t="n">
-        <v>40.9974670410156</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H559" t="n">
         <v>66348</v>
@@ -16667,7 +16667,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446434020996</v>
+        <v>44.5446510314941</v>
       </c>
       <c r="H562" t="n">
         <v>242564</v>
@@ -16696,7 +16696,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G563" t="n">
-        <v>43.9029426574707</v>
+        <v>43.902946472168</v>
       </c>
       <c r="H563" t="n">
         <v>150547</v>
@@ -16754,7 +16754,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G565" t="n">
-        <v>43.8851203918457</v>
+        <v>43.885124206543</v>
       </c>
       <c r="H565" t="n">
         <v>305117</v>
@@ -16783,7 +16783,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>44.9635391235352</v>
+        <v>44.9635314941406</v>
       </c>
       <c r="H566" t="n">
         <v>112572</v>
@@ -16812,7 +16812,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>46.0330390930176</v>
+        <v>46.033031463623</v>
       </c>
       <c r="H567" t="n">
         <v>142610</v>
@@ -16841,7 +16841,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253440856934</v>
+        <v>47.3253402709961</v>
       </c>
       <c r="H568" t="n">
         <v>177354</v>
@@ -16870,7 +16870,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>45.9439125061035</v>
+        <v>45.943904876709</v>
       </c>
       <c r="H569" t="n">
         <v>178635</v>
@@ -16899,7 +16899,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874099731445</v>
+        <v>45.5874137878418</v>
       </c>
       <c r="H570" t="n">
         <v>120878</v>
@@ -16957,7 +16957,7 @@
         <v>49.3800010681152</v>
       </c>
       <c r="G572" t="n">
-        <v>44.009895324707</v>
+        <v>44.0098991394043</v>
       </c>
       <c r="H572" t="n">
         <v>64462</v>
@@ -16986,7 +16986,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494720458984</v>
+        <v>43.8494758605957</v>
       </c>
       <c r="H573" t="n">
         <v>65658</v>
@@ -17102,7 +17102,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>41.4787521362305</v>
+        <v>41.4787483215332</v>
       </c>
       <c r="H577" t="n">
         <v>76270</v>
@@ -17131,7 +17131,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>41.1757202148438</v>
+        <v>41.175724029541</v>
       </c>
       <c r="H578" t="n">
         <v>78204</v>
@@ -17160,7 +17160,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G579" t="n">
-        <v>41.1578979492188</v>
+        <v>41.157901763916</v>
       </c>
       <c r="H579" t="n">
         <v>52237</v>
@@ -17189,7 +17189,7 @@
         <v>46.0200004577637</v>
       </c>
       <c r="G580" t="n">
-        <v>41.0152931213379</v>
+        <v>41.0152969360352</v>
       </c>
       <c r="H580" t="n">
         <v>49188</v>
@@ -17247,7 +17247,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G582" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H582" t="n">
         <v>46802</v>
@@ -17305,7 +17305,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479286193848</v>
       </c>
       <c r="H584" t="n">
         <v>83788</v>
@@ -17392,7 +17392,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7319030761719</v>
+        <v>39.7318992614746</v>
       </c>
       <c r="H587" t="n">
         <v>42227</v>
@@ -17479,7 +17479,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488288879395</v>
+        <v>40.2488250732422</v>
       </c>
       <c r="H590" t="n">
         <v>41714</v>
@@ -17508,7 +17508,7 @@
         <v>44.7799987792969</v>
       </c>
       <c r="G591" t="n">
-        <v>39.9101524353027</v>
+        <v>39.9101486206055</v>
       </c>
       <c r="H591" t="n">
         <v>42778</v>
@@ -17537,7 +17537,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G592" t="n">
-        <v>39.4288749694824</v>
+        <v>39.4288787841797</v>
       </c>
       <c r="H592" t="n">
         <v>40222</v>
@@ -17595,7 +17595,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>39.0367240905762</v>
+        <v>39.0367202758789</v>
       </c>
       <c r="H594" t="n">
         <v>36577</v>
@@ -17624,7 +17624,7 @@
         <v>47.560001373291</v>
       </c>
       <c r="G595" t="n">
-        <v>42.3878211975098</v>
+        <v>42.3878288269043</v>
       </c>
       <c r="H595" t="n">
         <v>180787</v>
@@ -17653,7 +17653,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479286193848</v>
       </c>
       <c r="H596" t="n">
         <v>103803</v>
@@ -17682,7 +17682,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.0509452819824</v>
+        <v>41.050952911377</v>
       </c>
       <c r="H597" t="n">
         <v>57439</v>
@@ -17711,7 +17711,7 @@
         <v>46.560001373291</v>
       </c>
       <c r="G598" t="n">
-        <v>41.9335746765137</v>
+        <v>41.9335708618164</v>
       </c>
       <c r="H598" t="n">
         <v>41681</v>
@@ -17798,7 +17798,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G601" t="n">
-        <v>40.6366577148438</v>
+        <v>40.6366539001465</v>
       </c>
       <c r="H601" t="n">
         <v>31298</v>
@@ -17856,7 +17856,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G603" t="n">
-        <v>39.8441047668457</v>
+        <v>39.8441009521484</v>
       </c>
       <c r="H603" t="n">
         <v>60714</v>
@@ -17914,7 +17914,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.4844398498535</v>
+        <v>37.4844360351562</v>
       </c>
       <c r="H605" t="n">
         <v>87797</v>
@@ -17943,7 +17943,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316192626953</v>
+        <v>36.3316230773926</v>
       </c>
       <c r="H606" t="n">
         <v>66466</v>
@@ -18001,7 +18001,7 @@
         <v>40.5</v>
       </c>
       <c r="G608" t="n">
-        <v>36.4757270812988</v>
+        <v>36.4757194519043</v>
       </c>
       <c r="H608" t="n">
         <v>40866</v>
@@ -18146,7 +18146,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H613" t="n">
         <v>88495</v>
@@ -18175,7 +18175,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>33.4135627746582</v>
+        <v>33.4135665893555</v>
       </c>
       <c r="H614" t="n">
         <v>159133</v>
@@ -18204,7 +18204,7 @@
         <v>37.3800010681152</v>
       </c>
       <c r="G615" t="n">
-        <v>33.6657409667969</v>
+        <v>33.6657447814941</v>
       </c>
       <c r="H615" t="n">
         <v>56794</v>
@@ -18233,7 +18233,7 @@
         <v>37.6199989318848</v>
       </c>
       <c r="G616" t="n">
-        <v>33.8818969726562</v>
+        <v>33.8818893432617</v>
       </c>
       <c r="H616" t="n">
         <v>84050</v>
@@ -18262,7 +18262,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G617" t="n">
-        <v>34.4763107299805</v>
+        <v>34.4763145446777</v>
       </c>
       <c r="H617" t="n">
         <v>85349</v>
@@ -18291,7 +18291,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924667358398</v>
+        <v>34.6924629211426</v>
       </c>
       <c r="H618" t="n">
         <v>73867</v>
@@ -18320,7 +18320,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G619" t="n">
-        <v>35.1427879333496</v>
+        <v>35.1427803039551</v>
       </c>
       <c r="H619" t="n">
         <v>51349</v>
@@ -18349,7 +18349,7 @@
         <v>38.560001373291</v>
       </c>
       <c r="G620" t="n">
-        <v>34.7284965515137</v>
+        <v>34.7284927368164</v>
       </c>
       <c r="H620" t="n">
         <v>62523</v>
@@ -18378,7 +18378,7 @@
         <v>38.3600006103516</v>
       </c>
       <c r="G621" t="n">
-        <v>34.5483627319336</v>
+        <v>34.5483589172363</v>
       </c>
       <c r="H621" t="n">
         <v>32667</v>
@@ -18436,7 +18436,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H623" t="n">
         <v>21903</v>
@@ -18465,7 +18465,7 @@
         <v>37.6199989318848</v>
       </c>
       <c r="G624" t="n">
-        <v>33.8818969726562</v>
+        <v>33.8818893432617</v>
       </c>
       <c r="H624" t="n">
         <v>47834</v>
@@ -18523,7 +18523,7 @@
         <v>38.2400016784668</v>
       </c>
       <c r="G626" t="n">
-        <v>34.4402885437012</v>
+        <v>34.4402847290039</v>
       </c>
       <c r="H626" t="n">
         <v>46240</v>
@@ -18552,7 +18552,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247749328613</v>
+        <v>35.1247673034668</v>
       </c>
       <c r="H627" t="n">
         <v>103614</v>
@@ -18581,7 +18581,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>33.5036277770996</v>
+        <v>33.5036239624023</v>
       </c>
       <c r="H628" t="n">
         <v>53029</v>
@@ -18610,7 +18610,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.4048500061035</v>
+        <v>32.4048538208008</v>
       </c>
       <c r="H629" t="n">
         <v>77422</v>
@@ -18668,7 +18668,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G631" t="n">
-        <v>31.4681930541992</v>
+        <v>31.468189239502</v>
       </c>
       <c r="H631" t="n">
         <v>192630</v>
@@ -18697,7 +18697,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G632" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744045257568</v>
       </c>
       <c r="H632" t="n">
         <v>126471</v>
@@ -18726,7 +18726,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5315322875977</v>
+        <v>30.531530380249</v>
       </c>
       <c r="H633" t="n">
         <v>75764</v>
@@ -18755,7 +18755,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.4867935180664</v>
+        <v>29.486795425415</v>
       </c>
       <c r="H634" t="n">
         <v>160938</v>
@@ -18813,7 +18813,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H636" t="n">
         <v>86489</v>
@@ -18842,7 +18842,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.1532688140869</v>
+        <v>30.1532649993896</v>
       </c>
       <c r="H637" t="n">
         <v>47812</v>
@@ -18900,7 +18900,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147415161133</v>
+        <v>29.4147434234619</v>
       </c>
       <c r="H639" t="n">
         <v>66878</v>
@@ -18929,7 +18929,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>27.8296241760254</v>
+        <v>27.829626083374</v>
       </c>
       <c r="H640" t="n">
         <v>89099</v>
@@ -19016,7 +19016,7 @@
         <v>33.9799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>30.6035823822021</v>
+        <v>30.6035785675049</v>
       </c>
       <c r="H643" t="n">
         <v>77878</v>
@@ -19103,7 +19103,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551258087158</v>
+        <v>29.9551239013672</v>
       </c>
       <c r="H646" t="n">
         <v>48258</v>
@@ -19132,7 +19132,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172370910645</v>
+        <v>30.1172351837158</v>
       </c>
       <c r="H647" t="n">
         <v>44619</v>
@@ -19161,7 +19161,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054431915283</v>
+        <v>30.4054412841797</v>
       </c>
       <c r="H648" t="n">
         <v>33638</v>
@@ -19190,7 +19190,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>30.5315322875977</v>
+        <v>30.531530380249</v>
       </c>
       <c r="H649" t="n">
         <v>62064</v>
@@ -19219,7 +19219,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.666332244873</v>
+        <v>31.6663284301758</v>
       </c>
       <c r="H650" t="n">
         <v>110112</v>
@@ -19306,7 +19306,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>31.1079406738281</v>
+        <v>31.1079387664795</v>
       </c>
       <c r="H653" t="n">
         <v>70388</v>
@@ -19335,7 +19335,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601169586182</v>
+        <v>31.3601150512695</v>
       </c>
       <c r="H654" t="n">
         <v>42779</v>
@@ -19364,7 +19364,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>30.9818458557129</v>
+        <v>30.9818477630615</v>
       </c>
       <c r="H655" t="n">
         <v>44556</v>
@@ -19393,7 +19393,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G656" t="n">
-        <v>31.7383861541748</v>
+        <v>31.7383842468262</v>
       </c>
       <c r="H656" t="n">
         <v>58243</v>
@@ -19451,7 +19451,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122894287109</v>
+        <v>31.6122913360596</v>
       </c>
       <c r="H658" t="n">
         <v>29583</v>
@@ -19480,7 +19480,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G659" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744045257568</v>
       </c>
       <c r="H659" t="n">
         <v>43655</v>
@@ -19538,7 +19538,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G661" t="n">
-        <v>29.9190979003906</v>
+        <v>29.9190998077393</v>
       </c>
       <c r="H661" t="n">
         <v>36448</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.9010887145996</v>
+        <v>29.901086807251</v>
       </c>
       <c r="H662" t="n">
         <v>24019</v>
@@ -19596,7 +19596,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H663" t="n">
         <v>57598</v>
@@ -19712,7 +19712,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>28.0998191833496</v>
+        <v>28.099817276001</v>
       </c>
       <c r="H667" t="n">
         <v>106675</v>
@@ -19741,7 +19741,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G668" t="n">
-        <v>27.5954608917236</v>
+        <v>27.595458984375</v>
       </c>
       <c r="H668" t="n">
         <v>30813</v>
@@ -19770,7 +19770,7 @@
         <v>29.5799999237061</v>
       </c>
       <c r="G669" t="n">
-        <v>26.6407871246338</v>
+        <v>26.6407890319824</v>
       </c>
       <c r="H669" t="n">
         <v>54672</v>
@@ -19828,7 +19828,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>26.0463695526123</v>
+        <v>26.0463676452637</v>
       </c>
       <c r="H671" t="n">
         <v>28977</v>
@@ -19857,7 +19857,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>26.5146980285645</v>
+        <v>26.5146999359131</v>
       </c>
       <c r="H672" t="n">
         <v>22536</v>
@@ -19886,7 +19886,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G673" t="n">
-        <v>27.2352046966553</v>
+        <v>27.2352066040039</v>
       </c>
       <c r="H673" t="n">
         <v>40742</v>
@@ -19915,7 +19915,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.0550804138184</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H674" t="n">
         <v>59352</v>
@@ -19944,7 +19944,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>27.1091175079346</v>
+        <v>27.1091194152832</v>
       </c>
       <c r="H675" t="n">
         <v>14694</v>
@@ -19973,7 +19973,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>27.1091175079346</v>
+        <v>27.1091194152832</v>
       </c>
       <c r="H676" t="n">
         <v>21986</v>
@@ -20031,7 +20031,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>26.7488632202148</v>
+        <v>26.7488613128662</v>
       </c>
       <c r="H678" t="n">
         <v>33597</v>
@@ -20089,7 +20089,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196910858154</v>
       </c>
       <c r="H680" t="n">
         <v>46685</v>
@@ -20147,7 +20147,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G682" t="n">
-        <v>27.9377021789551</v>
+        <v>27.9377002716064</v>
       </c>
       <c r="H682" t="n">
         <v>34366</v>
@@ -20176,7 +20176,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G683" t="n">
-        <v>27.8296241760254</v>
+        <v>27.829626083374</v>
       </c>
       <c r="H683" t="n">
         <v>57040</v>
@@ -20205,7 +20205,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476409912109</v>
+        <v>27.8476390838623</v>
       </c>
       <c r="H684" t="n">
         <v>50842</v>
@@ -20234,7 +20234,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>27.7936019897461</v>
+        <v>27.7936038970947</v>
       </c>
       <c r="H685" t="n">
         <v>35760</v>
@@ -20321,7 +20321,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>28.0097541809082</v>
+        <v>28.0097522735596</v>
       </c>
       <c r="H688" t="n">
         <v>31923</v>
@@ -20350,7 +20350,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G689" t="n">
-        <v>27.7755889892578</v>
+        <v>27.7755870819092</v>
       </c>
       <c r="H689" t="n">
         <v>109737</v>
@@ -20379,7 +20379,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.0097541809082</v>
+        <v>28.0097522735596</v>
       </c>
       <c r="H690" t="n">
         <v>44005</v>
@@ -20466,7 +20466,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>28.5501327514648</v>
+        <v>28.5501346588135</v>
       </c>
       <c r="H693" t="n">
         <v>27520</v>
@@ -20524,7 +20524,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G695" t="n">
-        <v>29.1625671386719</v>
+        <v>29.1625652313232</v>
       </c>
       <c r="H695" t="n">
         <v>62299</v>
@@ -20582,7 +20582,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401958465576</v>
+        <v>28.6401977539062</v>
       </c>
       <c r="H697" t="n">
         <v>27160</v>
@@ -20611,7 +20611,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762237548828</v>
+        <v>28.6762218475342</v>
       </c>
       <c r="H698" t="n">
         <v>35302</v>
@@ -20669,7 +20669,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.0550804138184</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H700" t="n">
         <v>32431</v>
@@ -20698,7 +20698,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>27.5954608917236</v>
+        <v>27.595458984375</v>
       </c>
       <c r="H701" t="n">
         <v>221272</v>
@@ -20727,7 +20727,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196910858154</v>
       </c>
       <c r="H702" t="n">
         <v>26734</v>
@@ -20756,7 +20756,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G703" t="n">
-        <v>27.451358795166</v>
+        <v>27.4513607025146</v>
       </c>
       <c r="H703" t="n">
         <v>119469</v>
@@ -20785,7 +20785,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196910858154</v>
       </c>
       <c r="H704" t="n">
         <v>37755</v>
@@ -20814,7 +20814,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.5594367980957</v>
+        <v>27.5594348907471</v>
       </c>
       <c r="H705" t="n">
         <v>27627</v>
@@ -20872,7 +20872,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320308685303</v>
+        <v>22.7320289611816</v>
       </c>
       <c r="H707" t="n">
         <v>196682</v>
@@ -20930,7 +20930,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233238220215</v>
+        <v>21.7233200073242</v>
       </c>
       <c r="H709" t="n">
         <v>130761</v>
@@ -20959,7 +20959,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860660552979</v>
+        <v>22.7860698699951</v>
       </c>
       <c r="H710" t="n">
         <v>107966</v>
@@ -21017,7 +21017,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G712" t="n">
-        <v>23.7047157287598</v>
+        <v>23.7047176361084</v>
       </c>
       <c r="H712" t="n">
         <v>61152</v>
@@ -21046,7 +21046,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606136322021</v>
+        <v>23.5606174468994</v>
       </c>
       <c r="H713" t="n">
         <v>38427</v>
@@ -21075,7 +21075,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>23.236385345459</v>
+        <v>23.2363872528076</v>
       </c>
       <c r="H714" t="n">
         <v>56594</v>
@@ -21104,7 +21104,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G715" t="n">
-        <v>23.4345283508301</v>
+        <v>23.4345264434814</v>
       </c>
       <c r="H715" t="n">
         <v>56928</v>
@@ -21191,7 +21191,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G718" t="n">
-        <v>20.8226852416992</v>
+        <v>20.8226871490479</v>
       </c>
       <c r="H718" t="n">
         <v>40533</v>
@@ -21220,7 +21220,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G719" t="n">
-        <v>21.3630657196045</v>
+        <v>21.3630638122559</v>
       </c>
       <c r="H719" t="n">
         <v>42932</v>
@@ -21249,7 +21249,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369766235352</v>
+        <v>21.2369747161865</v>
       </c>
       <c r="H720" t="n">
         <v>38258</v>
@@ -21278,7 +21278,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.3450527191162</v>
+        <v>21.3450546264648</v>
       </c>
       <c r="H721" t="n">
         <v>38719</v>
@@ -21365,7 +21365,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G724" t="n">
-        <v>18.3189182281494</v>
+        <v>18.318920135498</v>
       </c>
       <c r="H724" t="n">
         <v>205787</v>
@@ -21452,7 +21452,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.877311706543</v>
+        <v>18.8773097991943</v>
       </c>
       <c r="H727" t="n">
         <v>78461</v>
@@ -21481,7 +21481,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>18.3909702301025</v>
+        <v>18.3909683227539</v>
       </c>
       <c r="H728" t="n">
         <v>70249</v>
@@ -21510,7 +21510,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H729" t="n">
         <v>46125</v>
@@ -21539,7 +21539,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G730" t="n">
-        <v>18.3189182281494</v>
+        <v>18.318920135498</v>
       </c>
       <c r="H730" t="n">
         <v>43093</v>
@@ -21597,7 +21597,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G732" t="n">
-        <v>17.139087677002</v>
+        <v>17.1390895843506</v>
       </c>
       <c r="H732" t="n">
         <v>49459</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H733" t="n">
         <v>71224</v>
@@ -21684,7 +21684,7 @@
         <v>18.5</v>
       </c>
       <c r="G735" t="n">
-        <v>16.6617488861084</v>
+        <v>16.661750793457</v>
       </c>
       <c r="H735" t="n">
         <v>70337</v>
@@ -21713,7 +21713,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.2024250030518</v>
+        <v>16.2024269104004</v>
       </c>
       <c r="H736" t="n">
         <v>53336</v>
@@ -21742,7 +21742,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9502458572388</v>
+        <v>15.9502477645874</v>
       </c>
       <c r="H737" t="n">
         <v>57508</v>
@@ -21800,7 +21800,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H739" t="n">
         <v>56603</v>
@@ -21829,7 +21829,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6170139312744</v>
+        <v>15.6170110702515</v>
       </c>
       <c r="H740" t="n">
         <v>28241</v>
@@ -21858,7 +21858,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G741" t="n">
-        <v>16.1573963165283</v>
+        <v>16.1573944091797</v>
       </c>
       <c r="H741" t="n">
         <v>30250</v>
@@ -21887,7 +21887,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077136993408</v>
+        <v>16.6077117919922</v>
       </c>
       <c r="H742" t="n">
         <v>126448</v>
@@ -21974,7 +21974,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G745" t="n">
-        <v>17.5533771514893</v>
+        <v>17.5533790588379</v>
       </c>
       <c r="H745" t="n">
         <v>76853</v>
@@ -22032,7 +22032,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G747" t="n">
-        <v>17.9406509399414</v>
+        <v>17.94065284729</v>
       </c>
       <c r="H747" t="n">
         <v>117827</v>
@@ -22119,7 +22119,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968444824219</v>
+        <v>16.7968463897705</v>
       </c>
       <c r="H750" t="n">
         <v>72692</v>
@@ -22206,7 +22206,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.9052152633667</v>
+        <v>15.905216217041</v>
       </c>
       <c r="H753" t="n">
         <v>55986</v>
@@ -22293,7 +22293,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250881195068</v>
+        <v>15.7250890731812</v>
       </c>
       <c r="H756" t="n">
         <v>68222</v>
@@ -22322,7 +22322,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>15.4008626937866</v>
+        <v>15.4008617401123</v>
       </c>
       <c r="H757" t="n">
         <v>46935</v>
@@ -22351,7 +22351,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496139526367</v>
+        <v>15.0496110916138</v>
       </c>
       <c r="H758" t="n">
         <v>39650</v>
@@ -22380,7 +22380,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H759" t="n">
         <v>53012</v>
@@ -22409,7 +22409,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G760" t="n">
-        <v>14.7524042129517</v>
+        <v>14.7524032592773</v>
       </c>
       <c r="H760" t="n">
         <v>54545</v>
@@ -22438,7 +22438,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899925231934</v>
+        <v>15.589994430542</v>
       </c>
       <c r="H761" t="n">
         <v>79930</v>
@@ -22467,7 +22467,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>15.1486835479736</v>
+        <v>15.1486825942993</v>
       </c>
       <c r="H762" t="n">
         <v>108666</v>
@@ -22496,7 +22496,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.463906288147</v>
+        <v>15.4639053344727</v>
       </c>
       <c r="H763" t="n">
         <v>62260</v>
@@ -22525,7 +22525,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G764" t="n">
-        <v>17.1661033630371</v>
+        <v>17.1661071777344</v>
       </c>
       <c r="H764" t="n">
         <v>136749</v>
@@ -22583,7 +22583,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568050384521</v>
       </c>
       <c r="H766" t="n">
         <v>115896</v>
@@ -22612,7 +22612,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G767" t="n">
-        <v>17.6434421539307</v>
+        <v>17.6434440612793</v>
       </c>
       <c r="H767" t="n">
         <v>54735</v>
@@ -22641,7 +22641,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.391263961792</v>
+        <v>17.3912658691406</v>
       </c>
       <c r="H768" t="n">
         <v>73850</v>
@@ -22670,7 +22670,7 @@
         <v>20</v>
       </c>
       <c r="G769" t="n">
-        <v>18.0127010345459</v>
+        <v>18.0127048492432</v>
       </c>
       <c r="H769" t="n">
         <v>95011</v>
@@ -22728,7 +22728,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G771" t="n">
-        <v>18.2288570404053</v>
+        <v>18.228853225708</v>
       </c>
       <c r="H771" t="n">
         <v>74008</v>
@@ -22757,7 +22757,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G772" t="n">
-        <v>18.0307178497314</v>
+        <v>18.0307140350342</v>
       </c>
       <c r="H772" t="n">
         <v>42586</v>
@@ -22786,7 +22786,7 @@
         <v>20</v>
       </c>
       <c r="G773" t="n">
-        <v>18.0127010345459</v>
+        <v>18.0127048492432</v>
       </c>
       <c r="H773" t="n">
         <v>24003</v>
@@ -22873,7 +22873,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791706085205</v>
+        <v>18.6791725158691</v>
       </c>
       <c r="H776" t="n">
         <v>84665</v>
@@ -22902,7 +22902,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G777" t="n">
-        <v>18.8052635192871</v>
+        <v>18.8052597045898</v>
       </c>
       <c r="H777" t="n">
         <v>56710</v>
@@ -22931,7 +22931,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G778" t="n">
-        <v>18.6251335144043</v>
+        <v>18.6251373291016</v>
       </c>
       <c r="H778" t="n">
         <v>52083</v>
@@ -22989,7 +22989,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G780" t="n">
-        <v>18.6251335144043</v>
+        <v>18.6251373291016</v>
       </c>
       <c r="H780" t="n">
         <v>25837</v>
@@ -23018,7 +23018,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H781" t="n">
         <v>52065</v>
@@ -23047,7 +23047,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G782" t="n">
-        <v>18.9493656158447</v>
+        <v>18.9493637084961</v>
       </c>
       <c r="H782" t="n">
         <v>40418</v>
@@ -23076,7 +23076,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G783" t="n">
-        <v>18.7872486114502</v>
+        <v>18.7872505187988</v>
       </c>
       <c r="H783" t="n">
         <v>33247</v>
@@ -23105,7 +23105,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G784" t="n">
-        <v>18.6971855163574</v>
+        <v>18.6971836090088</v>
       </c>
       <c r="H784" t="n">
         <v>38581</v>
@@ -23134,7 +23134,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>18.354944229126</v>
+        <v>18.3549423217773</v>
       </c>
       <c r="H785" t="n">
         <v>61250</v>
@@ -23163,7 +23163,7 @@
         <v>20</v>
       </c>
       <c r="G786" t="n">
-        <v>18.0127010345459</v>
+        <v>18.0127048492432</v>
       </c>
       <c r="H786" t="n">
         <v>32584</v>
@@ -23192,7 +23192,7 @@
         <v>20</v>
       </c>
       <c r="G787" t="n">
-        <v>18.0127010345459</v>
+        <v>18.0127048492432</v>
       </c>
       <c r="H787" t="n">
         <v>55807</v>
@@ -23221,7 +23221,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G788" t="n">
-        <v>18.4269924163818</v>
+        <v>18.4269943237305</v>
       </c>
       <c r="H788" t="n">
         <v>64191</v>
@@ -23250,7 +23250,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H789" t="n">
         <v>81539</v>
@@ -23279,7 +23279,7 @@
         <v>19.9699993133545</v>
       </c>
       <c r="G790" t="n">
-        <v>17.9856815338135</v>
+        <v>17.9856834411621</v>
       </c>
       <c r="H790" t="n">
         <v>73749</v>
@@ -23308,7 +23308,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>17.3552398681641</v>
+        <v>17.3552417755127</v>
       </c>
       <c r="H791" t="n">
         <v>65355</v>
@@ -23337,7 +23337,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G792" t="n">
-        <v>17.7245006561279</v>
+        <v>17.7244987487793</v>
       </c>
       <c r="H792" t="n">
         <v>29423</v>
@@ -23424,7 +23424,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G795" t="n">
-        <v>19.3996810913086</v>
+        <v>19.3996829986572</v>
       </c>
       <c r="H795" t="n">
         <v>121292</v>
@@ -23453,7 +23453,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698722839355</v>
+        <v>19.6698703765869</v>
       </c>
       <c r="H796" t="n">
         <v>111608</v>
@@ -23540,7 +23540,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G799" t="n">
-        <v>19.9220523834229</v>
+        <v>19.9220504760742</v>
       </c>
       <c r="H799" t="n">
         <v>43219</v>
@@ -23569,7 +23569,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>19.4176940917969</v>
+        <v>19.4176921844482</v>
       </c>
       <c r="H800" t="n">
         <v>43308</v>
@@ -23598,7 +23598,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537181854248</v>
+        <v>19.4537200927734</v>
       </c>
       <c r="H801" t="n">
         <v>38620</v>
@@ -23772,7 +23772,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>17.7965507507324</v>
+        <v>17.7965526580811</v>
       </c>
       <c r="H807" t="n">
         <v>48825</v>
@@ -23830,7 +23830,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G809" t="n">
-        <v>17.418285369873</v>
+        <v>17.4182834625244</v>
       </c>
       <c r="H809" t="n">
         <v>64382</v>
@@ -23859,7 +23859,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508853912354</v>
+        <v>16.8508815765381</v>
       </c>
       <c r="H810" t="n">
         <v>142958</v>
@@ -23888,7 +23888,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G811" t="n">
-        <v>16.9859771728516</v>
+        <v>16.9859809875488</v>
       </c>
       <c r="H811" t="n">
         <v>69819</v>
@@ -23917,7 +23917,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G812" t="n">
-        <v>16.8688945770264</v>
+        <v>16.868896484375</v>
       </c>
       <c r="H812" t="n">
         <v>61620</v>
@@ -23946,7 +23946,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H813" t="n">
         <v>36891</v>
@@ -23975,7 +23975,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490226745605</v>
+        <v>17.0490245819092</v>
       </c>
       <c r="H814" t="n">
         <v>19771</v>
@@ -24004,7 +24004,7 @@
         <v>18.8099994659424</v>
       </c>
       <c r="G815" t="n">
-        <v>16.9409484863281</v>
+        <v>16.9409446716309</v>
       </c>
       <c r="H815" t="n">
         <v>56118</v>
@@ -24033,7 +24033,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462333679199</v>
+        <v>17.3462314605713</v>
       </c>
       <c r="H816" t="n">
         <v>103910</v>
@@ -24062,7 +24062,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G817" t="n">
-        <v>17.2741813659668</v>
+        <v>17.2741794586182</v>
       </c>
       <c r="H817" t="n">
         <v>92869</v>
@@ -24120,7 +24120,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2831878662109</v>
+        <v>17.2831897735596</v>
       </c>
       <c r="H819" t="n">
         <v>39049</v>
@@ -24178,7 +24178,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9766750335693</v>
+        <v>17.976676940918</v>
       </c>
       <c r="H821" t="n">
         <v>368484</v>
@@ -24294,7 +24294,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.4272899627686</v>
+        <v>17.4272880554199</v>
       </c>
       <c r="H825" t="n">
         <v>44899</v>
@@ -24410,7 +24410,7 @@
         <v>20</v>
       </c>
       <c r="G829" t="n">
-        <v>18.0127010345459</v>
+        <v>18.0127048492432</v>
       </c>
       <c r="H829" t="n">
         <v>99973</v>
@@ -24439,7 +24439,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>17.6974792480469</v>
+        <v>17.6974811553955</v>
       </c>
       <c r="H830" t="n">
         <v>92252</v>
@@ -24497,7 +24497,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496555328369</v>
+        <v>17.9496593475342</v>
       </c>
       <c r="H832" t="n">
         <v>46935</v>
@@ -24555,7 +24555,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2381553649902</v>
+        <v>17.2381572723389</v>
       </c>
       <c r="H834" t="n">
         <v>111270</v>
@@ -24584,7 +24584,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300792694092</v>
+        <v>17.1300811767578</v>
       </c>
       <c r="H835" t="n">
         <v>63235</v>
@@ -24642,7 +24642,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676723480225</v>
+        <v>17.9676704406738</v>
       </c>
       <c r="H837" t="n">
         <v>49207</v>
@@ -24729,7 +24729,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G840" t="n">
-        <v>17.8686027526855</v>
+        <v>17.8686008453369</v>
       </c>
       <c r="H840" t="n">
         <v>52488</v>
@@ -24758,7 +24758,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>17.7965507507324</v>
+        <v>17.7965526580811</v>
       </c>
       <c r="H841" t="n">
         <v>59761</v>
@@ -24787,7 +24787,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G842" t="n">
-        <v>17.5173530578613</v>
+        <v>17.51735496521</v>
       </c>
       <c r="H842" t="n">
         <v>58040</v>
@@ -24845,7 +24845,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G844" t="n">
-        <v>17.5894031524658</v>
+        <v>17.5894050598145</v>
       </c>
       <c r="H844" t="n">
         <v>44622</v>
@@ -24903,7 +24903,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G846" t="n">
-        <v>17.8686027526855</v>
+        <v>17.8686008453369</v>
       </c>
       <c r="H846" t="n">
         <v>91137</v>
@@ -24932,7 +24932,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568050384521</v>
       </c>
       <c r="H847" t="n">
         <v>58676</v>
@@ -25019,7 +25019,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G850" t="n">
-        <v>16.6621894836426</v>
+        <v>16.6621875762939</v>
       </c>
       <c r="H850" t="n">
         <v>95173</v>
@@ -25193,7 +25193,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021240234375</v>
       </c>
       <c r="H856" t="n">
         <v>215640</v>
@@ -25222,7 +25222,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G857" t="n">
-        <v>13.9405145645142</v>
+        <v>13.9405136108398</v>
       </c>
       <c r="H857" t="n">
         <v>212931</v>
@@ -25309,7 +25309,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G860" t="n">
-        <v>13.8943853378296</v>
+        <v>13.894383430481</v>
       </c>
       <c r="H860" t="n">
         <v>100198</v>
@@ -25367,7 +25367,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G862" t="n">
-        <v>13.4792137145996</v>
+        <v>13.4792127609253</v>
       </c>
       <c r="H862" t="n">
         <v>74086</v>
@@ -25483,7 +25483,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G866" t="n">
-        <v>13.0179119110107</v>
+        <v>13.0179128646851</v>
       </c>
       <c r="H866" t="n">
         <v>46939</v>
@@ -25570,7 +25570,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009454727173</v>
+        <v>13.1009464263916</v>
       </c>
       <c r="H869" t="n">
         <v>110683</v>
@@ -25628,7 +25628,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G871" t="n">
-        <v>13.922061920166</v>
+        <v>13.9220628738403</v>
       </c>
       <c r="H871" t="n">
         <v>162028</v>
@@ -25686,7 +25686,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G873" t="n">
-        <v>14.4756231307983</v>
+        <v>14.4756240844727</v>
       </c>
       <c r="H873" t="n">
         <v>197201</v>
@@ -25744,7 +25744,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>14.5771102905273</v>
+        <v>14.577109336853</v>
       </c>
       <c r="H875" t="n">
         <v>145209</v>
@@ -25802,7 +25802,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G877" t="n">
-        <v>13.922061920166</v>
+        <v>13.9220628738403</v>
       </c>
       <c r="H877" t="n">
         <v>53138</v>
@@ -25947,7 +25947,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H882" t="n">
         <v>171512</v>
@@ -25976,7 +25976,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G883" t="n">
-        <v>14.1803913116455</v>
+        <v>14.1803903579712</v>
       </c>
       <c r="H883" t="n">
         <v>186740</v>
@@ -26005,7 +26005,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G884" t="n">
-        <v>11.0988998413086</v>
+        <v>11.0989007949829</v>
       </c>
       <c r="H884" t="n">
         <v>788071</v>
@@ -26034,7 +26034,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G885" t="n">
-        <v>10.7575378417969</v>
+        <v>10.7575368881226</v>
       </c>
       <c r="H885" t="n">
         <v>650354</v>
@@ -26092,7 +26092,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G887" t="n">
-        <v>10.2132015228271</v>
+        <v>10.2132024765015</v>
       </c>
       <c r="H887" t="n">
         <v>292038</v>
@@ -26150,7 +26150,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G889" t="n">
-        <v>10.4161748886108</v>
+        <v>10.4161758422852</v>
       </c>
       <c r="H889" t="n">
         <v>201324</v>
@@ -26208,7 +26208,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>10.5914688110352</v>
+        <v>10.5914697647095</v>
       </c>
       <c r="H891" t="n">
         <v>113923</v>
@@ -26237,7 +26237,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G892" t="n">
-        <v>10.8590250015259</v>
+        <v>10.8590240478516</v>
       </c>
       <c r="H892" t="n">
         <v>171193</v>
@@ -26324,7 +26324,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837291717529</v>
+        <v>10.6837301254272</v>
       </c>
       <c r="H895" t="n">
         <v>124644</v>
@@ -26411,7 +26411,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.370044708252</v>
+        <v>10.3700456619263</v>
       </c>
       <c r="H898" t="n">
         <v>110215</v>
@@ -26440,7 +26440,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>10.0471343994141</v>
+        <v>10.0471353530884</v>
       </c>
       <c r="H899" t="n">
         <v>182473</v>
@@ -26469,7 +26469,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762981414795</v>
+        <v>10.1762990951538</v>
       </c>
       <c r="H900" t="n">
         <v>261491</v>
@@ -26527,7 +26527,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964221954346</v>
       </c>
       <c r="H902" t="n">
         <v>198170</v>
@@ -26556,7 +26556,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G903" t="n">
-        <v>9.53047847747803</v>
+        <v>9.53047752380371</v>
       </c>
       <c r="H903" t="n">
         <v>177150</v>
@@ -26585,7 +26585,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G904" t="n">
-        <v>10.0932636260986</v>
+        <v>10.0932655334473</v>
       </c>
       <c r="H904" t="n">
         <v>154899</v>
@@ -26672,7 +26672,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H907" t="n">
         <v>168958</v>
@@ -26759,7 +26759,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438533782959</v>
+        <v>10.4438524246216</v>
       </c>
       <c r="H910" t="n">
         <v>188704</v>
@@ -26788,7 +26788,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H911" t="n">
         <v>88660</v>
@@ -26817,7 +26817,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G912" t="n">
-        <v>10.6652774810791</v>
+        <v>10.6652784347534</v>
       </c>
       <c r="H912" t="n">
         <v>140872</v>
@@ -26846,7 +26846,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H913" t="n">
         <v>207382</v>
@@ -26875,7 +26875,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.9640998840332</v>
+        <v>9.96410083770752</v>
       </c>
       <c r="H914" t="n">
         <v>253876</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>10.0563611984253</v>
+        <v>10.056360244751</v>
       </c>
       <c r="H915" t="n">
         <v>185001</v>
@@ -26962,7 +26962,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G917" t="n">
-        <v>10.120943069458</v>
+        <v>10.1209421157837</v>
       </c>
       <c r="H917" t="n">
         <v>79748</v>
@@ -26991,7 +26991,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G918" t="n">
-        <v>9.50279903411865</v>
+        <v>9.50279998779297</v>
       </c>
       <c r="H918" t="n">
         <v>261117</v>
@@ -27078,7 +27078,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G921" t="n">
-        <v>9.21217918395996</v>
+        <v>9.21218013763428</v>
       </c>
       <c r="H921" t="n">
         <v>72765</v>
@@ -27136,7 +27136,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964221954346</v>
       </c>
       <c r="H923" t="n">
         <v>86848</v>
@@ -27194,7 +27194,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G925" t="n">
-        <v>9.43821716308594</v>
+        <v>9.43821620941162</v>
       </c>
       <c r="H925" t="n">
         <v>137287</v>
@@ -27368,7 +27368,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G931" t="n">
-        <v>9.53970336914062</v>
+        <v>9.53970432281494</v>
       </c>
       <c r="H931" t="n">
         <v>325642</v>
@@ -27397,7 +27397,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447059631348</v>
+        <v>9.24447154998779</v>
       </c>
       <c r="H932" t="n">
         <v>161867</v>
@@ -27484,7 +27484,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G935" t="n">
-        <v>9.21217918395996</v>
+        <v>9.21218013763428</v>
       </c>
       <c r="H935" t="n">
         <v>132335</v>
@@ -27542,7 +27542,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G937" t="n">
-        <v>9.97332572937012</v>
+        <v>9.97332668304443</v>
       </c>
       <c r="H937" t="n">
         <v>202148</v>
@@ -27629,7 +27629,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>10.2408819198608</v>
+        <v>10.2408809661865</v>
       </c>
       <c r="H940" t="n">
         <v>178359</v>
@@ -27658,7 +27658,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G941" t="n">
-        <v>10.2132015228271</v>
+        <v>10.2132024765015</v>
       </c>
       <c r="H941" t="n">
         <v>109302</v>
@@ -27803,7 +27803,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H946" t="n">
         <v>131456</v>
@@ -27832,7 +27832,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G947" t="n">
-        <v>9.61351203918457</v>
+        <v>9.61351108551025</v>
       </c>
       <c r="H947" t="n">
         <v>385751</v>
@@ -27890,7 +27890,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>9.61351203918457</v>
+        <v>9.61351108551025</v>
       </c>
       <c r="H949" t="n">
         <v>82832</v>
@@ -27919,7 +27919,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G950" t="n">
-        <v>9.52125072479248</v>
+        <v>9.5212516784668</v>
       </c>
       <c r="H950" t="n">
         <v>59934</v>
@@ -27948,7 +27948,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G951" t="n">
-        <v>9.53047847747803</v>
+        <v>9.53047752380371</v>
       </c>
       <c r="H951" t="n">
         <v>116133</v>
@@ -28093,7 +28093,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G956" t="n">
-        <v>9.2629222869873</v>
+        <v>9.26292324066162</v>
       </c>
       <c r="H956" t="n">
         <v>124882</v>
@@ -28151,7 +28151,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G958" t="n">
-        <v>9.65041637420654</v>
+        <v>9.65041542053223</v>
       </c>
       <c r="H958" t="n">
         <v>160776</v>
@@ -28238,7 +28238,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G961" t="n">
-        <v>9.71499824523926</v>
+        <v>9.71499729156494</v>
       </c>
       <c r="H961" t="n">
         <v>136175</v>
@@ -28267,7 +28267,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G962" t="n">
-        <v>9.81648540496826</v>
+        <v>9.81648445129395</v>
       </c>
       <c r="H962" t="n">
         <v>117453</v>
@@ -28354,7 +28354,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G965" t="n">
-        <v>9.98255157470703</v>
+        <v>9.98255252838135</v>
       </c>
       <c r="H965" t="n">
         <v>181594</v>
@@ -28383,7 +28383,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G966" t="n">
-        <v>9.75190258026123</v>
+        <v>9.7519006729126</v>
       </c>
       <c r="H966" t="n">
         <v>167211</v>
@@ -28470,7 +28470,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655851364136</v>
+        <v>10.0655860900879</v>
       </c>
       <c r="H969" t="n">
         <v>218375</v>
@@ -28499,7 +28499,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822439193726</v>
+        <v>10.5822429656982</v>
       </c>
       <c r="H970" t="n">
         <v>229401</v>
@@ -28615,7 +28615,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G974" t="n">
-        <v>10.8590250015259</v>
+        <v>10.8590240478516</v>
       </c>
       <c r="H974" t="n">
         <v>430743</v>
@@ -28644,7 +28644,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G975" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H975" t="n">
         <v>397866</v>
@@ -28673,7 +28673,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>10.3515930175781</v>
+        <v>10.3515939712524</v>
       </c>
       <c r="H976" t="n">
         <v>149030</v>
@@ -28702,7 +28702,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G977" t="n">
-        <v>11.431037902832</v>
+        <v>11.4310369491577</v>
       </c>
       <c r="H977" t="n">
         <v>569005</v>
@@ -28731,7 +28731,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G978" t="n">
-        <v>11.6340093612671</v>
+        <v>11.6340103149414</v>
       </c>
       <c r="H978" t="n">
         <v>723041</v>
@@ -28760,7 +28760,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337007522583</v>
+        <v>12.2337017059326</v>
       </c>
       <c r="H979" t="n">
         <v>516034</v>
@@ -28789,7 +28789,7 @@
         <v>13</v>
       </c>
       <c r="G980" t="n">
-        <v>11.9938230514526</v>
+        <v>11.993824005127</v>
       </c>
       <c r="H980" t="n">
         <v>232872</v>
@@ -28847,7 +28847,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>12.0860843658447</v>
+        <v>12.086085319519</v>
       </c>
       <c r="H982" t="n">
         <v>247645</v>
@@ -28905,7 +28905,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>12.1875705718994</v>
+        <v>12.1875715255737</v>
       </c>
       <c r="H984" t="n">
         <v>154181</v>
@@ -28934,7 +28934,7 @@
         <v>13</v>
       </c>
       <c r="G985" t="n">
-        <v>11.9938230514526</v>
+        <v>11.993824005127</v>
       </c>
       <c r="H985" t="n">
         <v>104842</v>
@@ -29021,7 +29021,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>11.7539482116699</v>
+        <v>11.7539472579956</v>
       </c>
       <c r="H988" t="n">
         <v>186372</v>
@@ -29050,7 +29050,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G989" t="n">
-        <v>11.8277559280396</v>
+        <v>11.8277568817139</v>
       </c>
       <c r="H989" t="n">
         <v>232780</v>
@@ -29079,7 +29079,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G990" t="n">
-        <v>11.8277559280396</v>
+        <v>11.8277568817139</v>
       </c>
       <c r="H990" t="n">
         <v>151779</v>
@@ -29166,7 +29166,7 @@
         <v>13.5</v>
       </c>
       <c r="G993" t="n">
-        <v>12.4551248550415</v>
+        <v>12.4551258087158</v>
       </c>
       <c r="H993" t="n">
         <v>251556</v>
@@ -29224,7 +29224,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G995" t="n">
-        <v>13.2485628128052</v>
+        <v>13.2485637664795</v>
       </c>
       <c r="H995" t="n">
         <v>409482</v>
@@ -29311,7 +29311,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G998" t="n">
-        <v>13.4054050445557</v>
+        <v>13.4054040908813</v>
       </c>
       <c r="H998" t="n">
         <v>614560</v>
@@ -29340,7 +29340,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G999" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H999" t="n">
         <v>450784</v>
@@ -29369,7 +29369,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7559947967529</v>
+        <v>13.7559938430786</v>
       </c>
       <c r="H1000" t="n">
         <v>343538</v>
@@ -29398,7 +29398,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.7098627090454</v>
+        <v>13.7098636627197</v>
       </c>
       <c r="H1001" t="n">
         <v>329930</v>
@@ -29427,7 +29427,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7744474411011</v>
+        <v>13.7744464874268</v>
       </c>
       <c r="H1002" t="n">
         <v>214342</v>
@@ -29485,7 +29485,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.7744474411011</v>
+        <v>13.7744464874268</v>
       </c>
       <c r="H1004" t="n">
         <v>370057</v>
@@ -29514,7 +29514,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.7190895080566</v>
+        <v>13.7190885543823</v>
       </c>
       <c r="H1005" t="n">
         <v>92655</v>
@@ -29543,7 +29543,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283153533936</v>
+        <v>13.7283163070679</v>
       </c>
       <c r="H1006" t="n">
         <v>219263</v>
@@ -29572,7 +29572,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.0143213272095</v>
+        <v>14.0143222808838</v>
       </c>
       <c r="H1007" t="n">
         <v>371820</v>
@@ -29601,7 +29601,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.1342601776123</v>
+        <v>14.134259223938</v>
       </c>
       <c r="H1008" t="n">
         <v>148543</v>
@@ -29659,7 +29659,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.7744474411011</v>
+        <v>13.7744464874268</v>
       </c>
       <c r="H1010" t="n">
         <v>195269</v>
@@ -29688,7 +29688,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1011" t="n">
         <v>66991</v>
@@ -29833,7 +29833,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.4571704864502</v>
+        <v>14.4571714401245</v>
       </c>
       <c r="H1016" t="n">
         <v>517730</v>
@@ -29891,7 +29891,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>13.7190895080566</v>
+        <v>13.7190885543823</v>
       </c>
       <c r="H1018" t="n">
         <v>328396</v>
@@ -29949,7 +29949,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1020" t="n">
-        <v>13.8482542037964</v>
+        <v>13.8482532501221</v>
       </c>
       <c r="H1020" t="n">
         <v>167283</v>
@@ -30036,7 +30036,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1023" t="n">
         <v>109674</v>
@@ -30094,7 +30094,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.9312877655029</v>
+        <v>13.9312896728516</v>
       </c>
       <c r="H1025" t="n">
         <v>191887</v>
@@ -30123,7 +30123,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6473264694214</v>
+        <v>15.6473274230957</v>
       </c>
       <c r="H1026" t="n">
         <v>1111920</v>
@@ -30152,7 +30152,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303609848022</v>
+        <v>15.7303619384766</v>
       </c>
       <c r="H1027" t="n">
         <v>948892</v>
@@ -30239,7 +30239,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.8651638031006</v>
+        <v>16.865161895752</v>
       </c>
       <c r="H1030" t="n">
         <v>257560</v>
@@ -30355,7 +30355,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.997917175293</v>
+        <v>15.99791431427</v>
       </c>
       <c r="H1034" t="n">
         <v>308732</v>
@@ -30384,7 +30384,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333333969116</v>
+        <v>15.9333343505859</v>
       </c>
       <c r="H1035" t="n">
         <v>130687</v>
@@ -30413,7 +30413,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720325469971</v>
+        <v>15.4720344543457</v>
       </c>
       <c r="H1036" t="n">
         <v>234914</v>
@@ -30471,7 +30471,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.3187808990479</v>
+        <v>14.3187818527222</v>
       </c>
       <c r="H1038" t="n">
         <v>248886</v>
@@ -30500,7 +30500,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8446655273438</v>
+        <v>14.8446645736694</v>
       </c>
       <c r="H1039" t="n">
         <v>220373</v>
@@ -30558,7 +30558,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.2044773101807</v>
+        <v>15.2044792175293</v>
       </c>
       <c r="H1041" t="n">
         <v>120054</v>
@@ -30645,7 +30645,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.8538913726807</v>
+        <v>14.8538904190063</v>
       </c>
       <c r="H1044" t="n">
         <v>138232</v>
@@ -30674,7 +30674,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.1491241455078</v>
+        <v>15.1491222381592</v>
       </c>
       <c r="H1045" t="n">
         <v>133980</v>
@@ -30703,7 +30703,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506093978882</v>
+        <v>15.2506103515625</v>
       </c>
       <c r="H1046" t="n">
         <v>126441</v>
@@ -30790,7 +30790,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.2044773101807</v>
+        <v>15.2044792175293</v>
       </c>
       <c r="H1049" t="n">
         <v>166255</v>
@@ -30819,7 +30819,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.0753164291382</v>
+        <v>15.0753154754639</v>
       </c>
       <c r="H1050" t="n">
         <v>149710</v>
@@ -30848,7 +30848,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.8538913726807</v>
+        <v>14.8538904190063</v>
       </c>
       <c r="H1051" t="n">
         <v>129321</v>
@@ -30877,7 +30877,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.1065816879272</v>
+        <v>14.1065835952759</v>
       </c>
       <c r="H1052" t="n">
         <v>295239</v>
@@ -30935,7 +30935,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399551391602</v>
+        <v>12.0399541854858</v>
       </c>
       <c r="H1054" t="n">
         <v>314929</v>
@@ -30964,7 +30964,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G1055" t="n">
-        <v>11.9753723144531</v>
+        <v>11.9753713607788</v>
       </c>
       <c r="H1055" t="n">
         <v>399315</v>
@@ -30993,7 +30993,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1056" t="n">
-        <v>11.5878791809082</v>
+        <v>11.5878801345825</v>
       </c>
       <c r="H1056" t="n">
         <v>232809</v>
@@ -31022,7 +31022,7 @@
         <v>12.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>11.301872253418</v>
+        <v>11.3018732070923</v>
       </c>
       <c r="H1057" t="n">
         <v>355369</v>
@@ -31080,7 +31080,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H1059" t="n">
         <v>236701</v>
@@ -31196,7 +31196,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>8.06353950500488</v>
+        <v>8.0635404586792</v>
       </c>
       <c r="H1063" t="n">
         <v>362042</v>
@@ -31225,7 +31225,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.97589445114136</v>
+        <v>7.97589349746704</v>
       </c>
       <c r="H1064" t="n">
         <v>361762</v>
@@ -31254,7 +31254,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285945892334</v>
       </c>
       <c r="H1065" t="n">
         <v>433976</v>
@@ -31283,7 +31283,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.55047273635864</v>
+        <v>6.5504732131958</v>
       </c>
       <c r="H1066" t="n">
         <v>390315</v>
@@ -31312,7 +31312,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.93796634674072</v>
+        <v>6.93796586990356</v>
       </c>
       <c r="H1067" t="n">
         <v>314093</v>
@@ -31370,7 +31370,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409605026245</v>
+        <v>6.98409652709961</v>
       </c>
       <c r="H1069" t="n">
         <v>157083</v>
@@ -31399,7 +31399,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.91028738021851</v>
+        <v>6.91028833389282</v>
       </c>
       <c r="H1070" t="n">
         <v>106846</v>
@@ -31428,7 +31428,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.01177453994751</v>
+        <v>7.01177406311035</v>
       </c>
       <c r="H1071" t="n">
         <v>100213</v>
@@ -31515,7 +31515,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697746276855</v>
+        <v>8.85697937011719</v>
       </c>
       <c r="H1074" t="n">
         <v>167191</v>
@@ -31544,7 +31544,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.33673095703125</v>
+        <v>9.33673000335693</v>
       </c>
       <c r="H1075" t="n">
         <v>210439</v>
@@ -31573,7 +31573,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.01382160186768</v>
+        <v>9.01381969451904</v>
       </c>
       <c r="H1076" t="n">
         <v>132675</v>
@@ -31660,7 +31660,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.34954643249512</v>
+        <v>8.34954738616943</v>
       </c>
       <c r="H1079" t="n">
         <v>108596</v>
@@ -31718,7 +31718,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.118896484375</v>
+        <v>8.11889743804932</v>
       </c>
       <c r="H1081" t="n">
         <v>72725</v>
@@ -31747,7 +31747,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.74985456466675</v>
+        <v>7.74985551834106</v>
       </c>
       <c r="H1082" t="n">
         <v>71777</v>
@@ -31776,7 +31776,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.929762840271</v>
+        <v>7.92976331710815</v>
       </c>
       <c r="H1083" t="n">
         <v>60718</v>
@@ -31805,7 +31805,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675937652588</v>
+        <v>7.78675985336304</v>
       </c>
       <c r="H1084" t="n">
         <v>156268</v>
@@ -31834,7 +31834,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.10967063903809</v>
+        <v>8.10966968536377</v>
       </c>
       <c r="H1085" t="n">
         <v>65803</v>
@@ -31863,7 +31863,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285945892334</v>
       </c>
       <c r="H1086" t="n">
         <v>212254</v>
@@ -31950,7 +31950,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>7.42694568634033</v>
+        <v>7.42694520950317</v>
       </c>
       <c r="H1089" t="n">
         <v>94583</v>
@@ -31979,7 +31979,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.42694568634033</v>
+        <v>7.42694520950317</v>
       </c>
       <c r="H1090" t="n">
         <v>124531</v>
@@ -32008,7 +32008,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>7.28855514526367</v>
+        <v>7.28855466842651</v>
       </c>
       <c r="H1091" t="n">
         <v>92461</v>
@@ -32124,7 +32124,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.1132607460022</v>
+        <v>7.11326026916504</v>
       </c>
       <c r="H1095" t="n">
         <v>69984</v>
@@ -32153,7 +32153,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.55610942840576</v>
+        <v>7.5561089515686</v>
       </c>
       <c r="H1096" t="n">
         <v>241778</v>
@@ -32211,7 +32211,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.93437623977661</v>
+        <v>7.93437576293945</v>
       </c>
       <c r="H1098" t="n">
         <v>138770</v>
@@ -32240,7 +32240,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.60223865509033</v>
+        <v>7.60223960876465</v>
       </c>
       <c r="H1099" t="n">
         <v>152629</v>
@@ -32298,7 +32298,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920557022095</v>
+        <v>7.51920461654663</v>
       </c>
       <c r="H1101" t="n">
         <v>66663</v>
@@ -32327,7 +32327,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.3070068359375</v>
+        <v>7.30700731277466</v>
       </c>
       <c r="H1102" t="n">
         <v>85960</v>
@@ -32414,7 +32414,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.15939044952393</v>
+        <v>7.15939092636108</v>
       </c>
       <c r="H1105" t="n">
         <v>90167</v>
@@ -32443,7 +32443,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.3070068359375</v>
+        <v>7.30700731277466</v>
       </c>
       <c r="H1106" t="n">
         <v>150317</v>
@@ -32472,7 +32472,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.06713008880615</v>
+        <v>7.06712961196899</v>
       </c>
       <c r="H1107" t="n">
         <v>140089</v>
@@ -32501,7 +32501,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874050140381</v>
+        <v>6.92874002456665</v>
       </c>
       <c r="H1108" t="n">
         <v>182143</v>
@@ -32617,7 +32617,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.54227066040039</v>
+        <v>7.54227018356323</v>
       </c>
       <c r="H1112" t="n">
         <v>115707</v>
@@ -32646,7 +32646,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.44539737701416</v>
+        <v>7.445396900177</v>
       </c>
       <c r="H1113" t="n">
         <v>89200</v>
@@ -32675,7 +32675,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010250091553</v>
+        <v>7.27010297775269</v>
       </c>
       <c r="H1114" t="n">
         <v>241372</v>
@@ -32704,7 +32704,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217798233032</v>
+        <v>7.72217750549316</v>
       </c>
       <c r="H1115" t="n">
         <v>329478</v>
@@ -32733,7 +32733,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948528289795</v>
+        <v>8.46948432922363</v>
       </c>
       <c r="H1116" t="n">
         <v>379600</v>
@@ -32762,7 +32762,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.66784572601318</v>
+        <v>8.66784477233887</v>
       </c>
       <c r="H1117" t="n">
         <v>353840</v>
@@ -32791,7 +32791,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310859680176</v>
+        <v>8.90310764312744</v>
       </c>
       <c r="H1118" t="n">
         <v>292199</v>
@@ -32878,7 +32878,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.87542915344238</v>
+        <v>8.8754301071167</v>
       </c>
       <c r="H1121" t="n">
         <v>174840</v>
@@ -32936,7 +32936,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1123" t="n">
-        <v>11.0066413879395</v>
+        <v>11.0066404342651</v>
       </c>
       <c r="H1123" t="n">
         <v>911213</v>
@@ -33081,7 +33081,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.82570934295654</v>
+        <v>9.82571029663086</v>
       </c>
       <c r="H1128" t="n">
         <v>371295</v>
@@ -33110,7 +33110,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.82570934295654</v>
+        <v>9.82571029663086</v>
       </c>
       <c r="H1129" t="n">
         <v>254965</v>
@@ -33139,7 +33139,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.74267673492432</v>
+        <v>9.74267578125</v>
       </c>
       <c r="H1130" t="n">
         <v>168430</v>
@@ -33168,7 +33168,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.4623050689697</v>
+        <v>10.462306022644</v>
       </c>
       <c r="H1131" t="n">
         <v>404544</v>
@@ -33226,7 +33226,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.1947498321533</v>
+        <v>10.194751739502</v>
       </c>
       <c r="H1133" t="n">
         <v>166996</v>
@@ -33255,7 +33255,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1134" t="n">
-        <v>10.0194568634033</v>
+        <v>10.019455909729</v>
       </c>
       <c r="H1134" t="n">
         <v>151652</v>
@@ -33342,7 +33342,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792715072632</v>
+        <v>10.3792705535889</v>
       </c>
       <c r="H1137" t="n">
         <v>258796</v>
@@ -33429,7 +33429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.370044708252</v>
+        <v>10.3700456619263</v>
       </c>
       <c r="H1140" t="n">
         <v>116026</v>
@@ -33458,7 +33458,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.3608198165894</v>
+        <v>10.3608179092407</v>
       </c>
       <c r="H1141" t="n">
         <v>120220</v>
@@ -33603,7 +33603,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667636871338</v>
+        <v>10.7667646408081</v>
       </c>
       <c r="H1146" t="n">
         <v>215683</v>
@@ -33632,7 +33632,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1147" t="n">
-        <v>12.021502494812</v>
+        <v>12.0215015411377</v>
       </c>
       <c r="H1147" t="n">
         <v>726814</v>
@@ -33690,7 +33690,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.5417490005493</v>
+        <v>11.5417499542236</v>
       </c>
       <c r="H1149" t="n">
         <v>248313</v>
@@ -33748,7 +33748,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>11.8093032836914</v>
+        <v>11.8093042373657</v>
       </c>
       <c r="H1151" t="n">
         <v>223425</v>
@@ -33777,7 +33777,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.818531036377</v>
+        <v>11.8185300827026</v>
       </c>
       <c r="H1152" t="n">
         <v>187197</v>
@@ -33835,7 +33835,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.818531036377</v>
+        <v>11.8185300827026</v>
       </c>
       <c r="H1154" t="n">
         <v>76721</v>
@@ -33864,7 +33864,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.7539482116699</v>
+        <v>11.7539472579956</v>
       </c>
       <c r="H1155" t="n">
         <v>263178</v>
@@ -33893,7 +33893,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1156" t="n">
-        <v>11.5878791809082</v>
+        <v>11.5878801345825</v>
       </c>
       <c r="H1156" t="n">
         <v>179977</v>
@@ -33922,7 +33922,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616888046265</v>
+        <v>11.6616868972778</v>
       </c>
       <c r="H1157" t="n">
         <v>54063</v>
@@ -34009,7 +34009,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1160" t="n">
-        <v>11.5878791809082</v>
+        <v>11.5878801345825</v>
       </c>
       <c r="H1160" t="n">
         <v>78220</v>
@@ -34038,7 +34038,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.2741956710815</v>
+        <v>11.2741947174072</v>
       </c>
       <c r="H1161" t="n">
         <v>62971</v>
@@ -34125,7 +34125,7 @@
         <v>12.0299997329712</v>
       </c>
       <c r="G1164" t="n">
-        <v>11.0988998413086</v>
+        <v>11.0989007949829</v>
       </c>
       <c r="H1164" t="n">
         <v>191245</v>
@@ -34357,7 +34357,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.2854671478271</v>
+        <v>13.2854661941528</v>
       </c>
       <c r="H1172" t="n">
         <v>98903</v>
@@ -34386,7 +34386,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4423093795776</v>
+        <v>13.4423084259033</v>
       </c>
       <c r="H1173" t="n">
         <v>141586</v>
@@ -34473,7 +34473,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H1176" t="n">
         <v>96376</v>
@@ -34531,7 +34531,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1178" t="n">
-        <v>13.0086870193481</v>
+        <v>13.0086860656738</v>
       </c>
       <c r="H1178" t="n">
         <v>67273</v>
@@ -34560,7 +34560,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.1932067871094</v>
+        <v>13.1932077407837</v>
       </c>
       <c r="H1179" t="n">
         <v>142039</v>
@@ -34589,7 +34589,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1180" t="n">
-        <v>13.5437955856323</v>
+        <v>13.543794631958</v>
       </c>
       <c r="H1180" t="n">
         <v>208316</v>
@@ -34618,7 +34618,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500499725342</v>
+        <v>13.3500490188599</v>
       </c>
       <c r="H1181" t="n">
         <v>113455</v>
@@ -34676,7 +34676,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714750289917</v>
+        <v>13.5714731216431</v>
       </c>
       <c r="H1183" t="n">
         <v>86309</v>
@@ -34705,7 +34705,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>13.3685007095337</v>
+        <v>13.368501663208</v>
       </c>
       <c r="H1184" t="n">
         <v>145405</v>
@@ -34821,7 +34821,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.1101722717285</v>
+        <v>13.1101732254028</v>
       </c>
       <c r="H1188" t="n">
         <v>183776</v>
@@ -34850,7 +34850,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>13.1932067871094</v>
+        <v>13.1932077407837</v>
       </c>
       <c r="H1189" t="n">
         <v>112671</v>
@@ -35024,7 +35024,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1195" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H1195" t="n">
         <v>76764</v>
@@ -35053,7 +35053,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.0455913543701</v>
+        <v>13.0455904006958</v>
       </c>
       <c r="H1196" t="n">
         <v>83647</v>
@@ -35169,7 +35169,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.5104808807373</v>
+        <v>12.5104818344116</v>
       </c>
       <c r="H1200" t="n">
         <v>248470</v>
@@ -35227,7 +35227,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6304187774658</v>
+        <v>12.6304197311401</v>
       </c>
       <c r="H1202" t="n">
         <v>101665</v>
@@ -35314,7 +35314,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.7872619628906</v>
+        <v>12.7872610092163</v>
       </c>
       <c r="H1205" t="n">
         <v>90314</v>
@@ -35372,7 +35372,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.4054050445557</v>
+        <v>13.4054040908813</v>
       </c>
       <c r="H1207" t="n">
         <v>164570</v>
@@ -35401,7 +35401,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1208" t="n">
-        <v>13.5068912506104</v>
+        <v>13.5068922042847</v>
       </c>
       <c r="H1208" t="n">
         <v>135804</v>
@@ -35430,7 +35430,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330835342407</v>
+        <v>13.433084487915</v>
       </c>
       <c r="H1209" t="n">
         <v>134522</v>
@@ -35546,7 +35546,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735197067261</v>
       </c>
       <c r="H1213" t="n">
         <v>405514</v>
@@ -35633,7 +35633,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>15.3613195419312</v>
+        <v>15.3613204956055</v>
       </c>
       <c r="H1216" t="n">
         <v>206453</v>
@@ -35662,7 +35662,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628076553345</v>
+        <v>15.4628086090088</v>
       </c>
       <c r="H1217" t="n">
         <v>170488</v>
@@ -35720,7 +35720,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H1219" t="n">
         <v>194522</v>
@@ -35749,7 +35749,7 @@
         <v>16</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.7616300582886</v>
+        <v>14.7616291046143</v>
       </c>
       <c r="H1220" t="n">
         <v>90320</v>
@@ -35981,7 +35981,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1228" t="n">
-        <v>13.8482542037964</v>
+        <v>13.8482532501221</v>
       </c>
       <c r="H1228" t="n">
         <v>366547</v>
@@ -36010,7 +36010,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>13.6545085906982</v>
+        <v>13.6545076370239</v>
       </c>
       <c r="H1229" t="n">
         <v>211009</v>
@@ -36039,7 +36039,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1230" t="n">
         <v>232002</v>
@@ -36126,7 +36126,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735197067261</v>
       </c>
       <c r="H1233" t="n">
         <v>375133</v>
@@ -36184,7 +36184,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1235" t="n">
-        <v>15.6750068664551</v>
+        <v>15.6750040054321</v>
       </c>
       <c r="H1235" t="n">
         <v>412079</v>
@@ -36213,7 +36213,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.4166765213013</v>
+        <v>15.416675567627</v>
       </c>
       <c r="H1236" t="n">
         <v>175438</v>
@@ -36242,7 +36242,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G1237" t="n">
-        <v>15.1029920578003</v>
+        <v>15.1029939651489</v>
       </c>
       <c r="H1237" t="n">
         <v>167525</v>
@@ -36271,7 +36271,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184713363647</v>
+        <v>14.9184722900391</v>
       </c>
       <c r="H1238" t="n">
         <v>69332</v>
@@ -36300,7 +36300,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1239" t="n">
-        <v>15.3889999389648</v>
+        <v>15.3889989852905</v>
       </c>
       <c r="H1239" t="n">
         <v>152784</v>
@@ -36329,7 +36329,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764930725098</v>
+        <v>15.7764921188354</v>
       </c>
       <c r="H1240" t="n">
         <v>178894</v>
@@ -36358,7 +36358,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827474594116</v>
+        <v>15.5827445983887</v>
       </c>
       <c r="H1241" t="n">
         <v>78857</v>
@@ -36387,7 +36387,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547565460205</v>
       </c>
       <c r="H1242" t="n">
         <v>259846</v>
@@ -36445,7 +36445,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410739898682</v>
+        <v>15.8410749435425</v>
       </c>
       <c r="H1244" t="n">
         <v>51279</v>
@@ -36474,7 +36474,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>15.924108505249</v>
+        <v>15.9241094589233</v>
       </c>
       <c r="H1245" t="n">
         <v>72824</v>
@@ -36532,7 +36532,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.1178550720215</v>
+        <v>16.1178531646729</v>
       </c>
       <c r="H1247" t="n">
         <v>97235</v>
@@ -36561,7 +36561,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>15.8503007888794</v>
+        <v>15.8503017425537</v>
       </c>
       <c r="H1248" t="n">
         <v>38481</v>
@@ -36590,7 +36590,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G1249" t="n">
-        <v>15.8779792785645</v>
+        <v>15.8779773712158</v>
       </c>
       <c r="H1249" t="n">
         <v>70649</v>
@@ -36619,7 +36619,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1250" t="n">
-        <v>15.3520946502686</v>
+        <v>15.3520936965942</v>
       </c>
       <c r="H1250" t="n">
         <v>139263</v>
@@ -36677,7 +36677,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351272583008</v>
+        <v>15.4351291656494</v>
       </c>
       <c r="H1252" t="n">
         <v>60423</v>
@@ -36706,7 +36706,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919723510742</v>
+        <v>15.5919713973999</v>
       </c>
       <c r="H1253" t="n">
         <v>50800</v>
@@ -36793,7 +36793,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517889022827</v>
+        <v>15.9517869949341</v>
       </c>
       <c r="H1256" t="n">
         <v>77596</v>
@@ -36880,7 +36880,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>16.0717258453369</v>
+        <v>16.0717239379883</v>
       </c>
       <c r="H1259" t="n">
         <v>62766</v>
@@ -36967,7 +36967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.3910446166992</v>
+        <v>17.3910465240479</v>
       </c>
       <c r="H1262" t="n">
         <v>199105</v>
@@ -36996,7 +36996,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.4648532867432</v>
+        <v>17.4648551940918</v>
       </c>
       <c r="H1263" t="n">
         <v>97580</v>
@@ -37054,7 +37054,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>17.1142635345459</v>
+        <v>17.1142654418945</v>
       </c>
       <c r="H1265" t="n">
         <v>144721</v>
@@ -37083,7 +37083,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G1266" t="n">
-        <v>17.2618808746338</v>
+        <v>17.2618789672852</v>
       </c>
       <c r="H1266" t="n">
         <v>72275</v>
@@ -37112,7 +37112,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1267" t="n">
-        <v>17.5386619567871</v>
+        <v>17.5386600494385</v>
       </c>
       <c r="H1267" t="n">
         <v>99892</v>
@@ -37141,7 +37141,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.4464015960693</v>
+        <v>17.4463996887207</v>
       </c>
       <c r="H1268" t="n">
         <v>107802</v>
@@ -37170,7 +37170,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1269" t="n">
-        <v>17.5663414001465</v>
+        <v>17.5663394927979</v>
       </c>
       <c r="H1269" t="n">
         <v>89128</v>
@@ -37199,7 +37199,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1270" t="n">
-        <v>17.372594833374</v>
+        <v>17.3725929260254</v>
       </c>
       <c r="H1270" t="n">
         <v>76845</v>
@@ -37228,7 +37228,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.621696472168</v>
+        <v>17.6216983795166</v>
       </c>
       <c r="H1271" t="n">
         <v>125434</v>
@@ -37257,7 +37257,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.5478858947754</v>
+        <v>17.547887802124</v>
       </c>
       <c r="H1272" t="n">
         <v>81241</v>
@@ -37286,7 +37286,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.036865234375</v>
+        <v>18.0368671417236</v>
       </c>
       <c r="H1273" t="n">
         <v>111248</v>
@@ -37373,7 +37373,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1276" t="n">
-        <v>19.6698741912842</v>
+        <v>19.6698722839355</v>
       </c>
       <c r="H1276" t="n">
         <v>259555</v>
@@ -37431,7 +37431,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1278" t="n">
-        <v>19.4299964904785</v>
+        <v>19.4299945831299</v>
       </c>
       <c r="H1278" t="n">
         <v>92876</v>
@@ -37489,7 +37489,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>18.728816986084</v>
+        <v>18.7288188934326</v>
       </c>
       <c r="H1280" t="n">
         <v>138251</v>
@@ -37605,7 +37605,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.2639293670654</v>
+        <v>19.2639255523682</v>
       </c>
       <c r="H1284" t="n">
         <v>44320</v>
@@ -37634,7 +37634,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="n">
-        <v>19.2639293670654</v>
+        <v>19.2639255523682</v>
       </c>
       <c r="H1285" t="n">
         <v>59633</v>
@@ -37750,7 +37750,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>18.4704914093018</v>
+        <v>18.4704895019531</v>
       </c>
       <c r="H1289" t="n">
         <v>98728</v>
@@ -37808,7 +37808,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.1844825744629</v>
+        <v>18.1844806671143</v>
       </c>
       <c r="H1291" t="n">
         <v>67860</v>
@@ -37866,7 +37866,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>19.9651031494141</v>
+        <v>19.9651050567627</v>
       </c>
       <c r="H1293" t="n">
         <v>129783</v>
@@ -37924,7 +37924,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="n">
-        <v>20.9430637359619</v>
+        <v>20.9430618286133</v>
       </c>
       <c r="H1295" t="n">
         <v>142083</v>
@@ -38011,7 +38011,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>21.312105178833</v>
+        <v>21.3121032714844</v>
       </c>
       <c r="H1298" t="n">
         <v>54089</v>
@@ -38040,7 +38040,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.1829376220703</v>
+        <v>21.1829395294189</v>
       </c>
       <c r="H1299" t="n">
         <v>58252</v>
@@ -38214,7 +38214,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745826721191</v>
+        <v>22.4745845794678</v>
       </c>
       <c r="H1305" t="n">
         <v>45171</v>
@@ -38243,7 +38243,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1306" t="n">
-        <v>21.7180500030518</v>
+        <v>21.7180480957031</v>
       </c>
       <c r="H1306" t="n">
         <v>103170</v>
@@ -38272,7 +38272,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.5371170043945</v>
+        <v>20.5371189117432</v>
       </c>
       <c r="H1307" t="n">
         <v>221676</v>
@@ -38301,7 +38301,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.6293773651123</v>
+        <v>20.6293792724609</v>
       </c>
       <c r="H1308" t="n">
         <v>73684</v>
@@ -38330,7 +38330,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1309" t="n">
-        <v>20.7216396331787</v>
+        <v>20.7216358184814</v>
       </c>
       <c r="H1309" t="n">
         <v>77545</v>
@@ -38359,7 +38359,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.1865272521973</v>
+        <v>20.1865310668945</v>
       </c>
       <c r="H1310" t="n">
         <v>87245</v>
@@ -38388,7 +38388,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>21.1275825500488</v>
+        <v>21.1275806427002</v>
       </c>
       <c r="H1311" t="n">
         <v>86497</v>
@@ -38417,7 +38417,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>20.6847362518311</v>
+        <v>20.6847324371338</v>
       </c>
       <c r="H1312" t="n">
         <v>43411</v>
@@ -38475,7 +38475,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4633083343506</v>
+        <v>20.4633102416992</v>
       </c>
       <c r="H1314" t="n">
         <v>180543</v>
@@ -38562,7 +38562,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>20.8508033752441</v>
+        <v>20.8508014678955</v>
       </c>
       <c r="H1317" t="n">
         <v>68057</v>
@@ -38678,7 +38678,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="n">
-        <v>20.2234325408936</v>
+        <v>20.2234344482422</v>
       </c>
       <c r="H1321" t="n">
         <v>160358</v>
@@ -38736,7 +38736,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.9466514587402</v>
+        <v>19.9466533660889</v>
       </c>
       <c r="H1323" t="n">
         <v>137347</v>
@@ -38765,7 +38765,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1324" t="n">
         <v>133244</v>
@@ -38794,7 +38794,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.1127223968506</v>
+        <v>20.112720489502</v>
       </c>
       <c r="H1325" t="n">
         <v>134502</v>
@@ -38823,7 +38823,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="n">
-        <v>19.6145153045654</v>
+        <v>19.6145172119141</v>
       </c>
       <c r="H1326" t="n">
         <v>83270</v>
@@ -38852,7 +38852,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>19.8543930053711</v>
+        <v>19.8543910980225</v>
       </c>
       <c r="H1327" t="n">
         <v>141734</v>
@@ -38881,7 +38881,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1328" t="n">
         <v>213744</v>
@@ -38939,7 +38939,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1330" t="n">
         <v>74044</v>
@@ -38968,7 +38968,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1331" t="n">
-        <v>20.8323497772217</v>
+        <v>20.8323516845703</v>
       </c>
       <c r="H1331" t="n">
         <v>115400</v>
@@ -38997,7 +38997,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G1332" t="n">
-        <v>22.1793518066406</v>
+        <v>22.179349899292</v>
       </c>
       <c r="H1332" t="n">
         <v>248716</v>
@@ -39026,7 +39026,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="n">
-        <v>22.5483913421631</v>
+        <v>22.5483894348145</v>
       </c>
       <c r="H1333" t="n">
         <v>168907</v>
@@ -39084,7 +39084,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.2162551879883</v>
+        <v>22.2162532806396</v>
       </c>
       <c r="H1335" t="n">
         <v>78096</v>
@@ -39142,7 +39142,7 @@
         <v>23.8600006103516</v>
       </c>
       <c r="G1337" t="n">
-        <v>22.0132827758789</v>
+        <v>22.0132808685303</v>
       </c>
       <c r="H1337" t="n">
         <v>60244</v>
@@ -39171,7 +39171,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1338" t="n">
-        <v>22.2531604766846</v>
+        <v>22.2531585693359</v>
       </c>
       <c r="H1338" t="n">
         <v>63147</v>
@@ -39200,7 +39200,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317306518555</v>
+        <v>22.0317325592041</v>
       </c>
       <c r="H1339" t="n">
         <v>111019</v>
@@ -39258,7 +39258,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846755981445</v>
+        <v>23.7846775054932</v>
       </c>
       <c r="H1341" t="n">
         <v>181858</v>
@@ -39287,7 +39287,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1342" t="n">
-        <v>23.729320526123</v>
+        <v>23.7293186187744</v>
       </c>
       <c r="H1342" t="n">
         <v>145478</v>
@@ -39374,7 +39374,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>23.0465927124023</v>
+        <v>23.046594619751</v>
       </c>
       <c r="H1345" t="n">
         <v>113640</v>
@@ -39432,7 +39432,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1347" t="n">
-        <v>23.3049240112305</v>
+        <v>23.3049259185791</v>
       </c>
       <c r="H1347" t="n">
         <v>128596</v>
@@ -39490,7 +39490,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1349" t="n">
         <v>78530</v>
@@ -39519,7 +39519,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817012786865</v>
+        <v>23.5817050933838</v>
       </c>
       <c r="H1350" t="n">
         <v>51355</v>
@@ -39606,7 +39606,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="n">
-        <v>22.5852947235107</v>
+        <v>22.5852909088135</v>
       </c>
       <c r="H1353" t="n">
         <v>208215</v>
@@ -39722,7 +39722,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1357" t="n">
         <v>131691</v>
@@ -39867,7 +39867,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="n">
-        <v>23.6370620727539</v>
+        <v>23.6370601654053</v>
       </c>
       <c r="H1362" t="n">
         <v>264460</v>
@@ -39896,7 +39896,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1363" t="n">
-        <v>23.729320526123</v>
+        <v>23.7293186187744</v>
       </c>
       <c r="H1363" t="n">
         <v>182308</v>
@@ -39925,7 +39925,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1364" t="n">
         <v>236072</v>
@@ -39983,7 +39983,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>26.4786739349365</v>
+        <v>26.4786758422852</v>
       </c>
       <c r="H1366" t="n">
         <v>262217</v>
@@ -40099,7 +40099,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935340881348</v>
+        <v>27.4935359954834</v>
       </c>
       <c r="H1370" t="n">
         <v>201422</v>
@@ -40128,7 +40128,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="n">
-        <v>28.1578121185303</v>
+        <v>28.1578102111816</v>
       </c>
       <c r="H1371" t="n">
         <v>113890</v>
@@ -40157,7 +40157,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>28.04709815979</v>
+        <v>28.0470962524414</v>
       </c>
       <c r="H1372" t="n">
         <v>81326</v>
@@ -40186,7 +40186,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="n">
-        <v>28.04709815979</v>
+        <v>28.0470962524414</v>
       </c>
       <c r="H1373" t="n">
         <v>74572</v>
@@ -40389,7 +40389,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="n">
-        <v>26.4971256256104</v>
+        <v>26.497127532959</v>
       </c>
       <c r="H1380" t="n">
         <v>98446</v>
@@ -40418,7 +40418,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>25.9251117706299</v>
+        <v>25.9251136779785</v>
       </c>
       <c r="H1381" t="n">
         <v>64116</v>
@@ -40476,7 +40476,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.4971256256104</v>
+        <v>26.497127532959</v>
       </c>
       <c r="H1383" t="n">
         <v>165675</v>
@@ -40563,7 +40563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>26.3864135742188</v>
+        <v>26.3864154815674</v>
       </c>
       <c r="H1386" t="n">
         <v>54044</v>
@@ -40592,7 +40592,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="n">
-        <v>25.9989185333252</v>
+        <v>25.9989223480225</v>
       </c>
       <c r="H1387" t="n">
         <v>84386</v>
@@ -40621,7 +40621,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>25.5007171630859</v>
+        <v>25.5007133483887</v>
       </c>
       <c r="H1388" t="n">
         <v>89097</v>
@@ -40766,7 +40766,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="n">
-        <v>26.1280841827393</v>
+        <v>26.1280860900879</v>
       </c>
       <c r="H1393" t="n">
         <v>32484</v>
@@ -40853,7 +40853,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>25.9989185333252</v>
+        <v>25.9989223480225</v>
       </c>
       <c r="H1396" t="n">
         <v>59600</v>
@@ -40969,7 +40969,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="n">
-        <v>25.9251117706299</v>
+        <v>25.9251136779785</v>
       </c>
       <c r="H1400" t="n">
         <v>40818</v>
@@ -40998,7 +40998,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="n">
-        <v>26.1280841827393</v>
+        <v>26.1280860900879</v>
       </c>
       <c r="H1401" t="n">
         <v>44132</v>
@@ -41027,7 +41027,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="n">
-        <v>25.4453601837158</v>
+        <v>25.4453582763672</v>
       </c>
       <c r="H1402" t="n">
         <v>72975</v>
@@ -41056,7 +41056,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1403" t="n">
-        <v>26.7370014190674</v>
+        <v>26.737003326416</v>
       </c>
       <c r="H1403" t="n">
         <v>119012</v>
@@ -41404,7 +41404,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="n">
-        <v>28.9143409729004</v>
+        <v>28.914342880249</v>
       </c>
       <c r="H1415" t="n">
         <v>409404</v>
@@ -41433,7 +41433,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>30.4643135070801</v>
+        <v>30.4643154144287</v>
       </c>
       <c r="H1416" t="n">
         <v>215821</v>
@@ -41462,7 +41462,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="n">
-        <v>30.9625225067139</v>
+        <v>30.9625205993652</v>
       </c>
       <c r="H1417" t="n">
         <v>144420</v>
@@ -41549,7 +41549,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>26.8846187591553</v>
+        <v>26.8846168518066</v>
       </c>
       <c r="H1420" t="n">
         <v>277218</v>
@@ -41578,7 +41578,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1421" t="n">
-        <v>27.3459205627441</v>
+        <v>27.3459186553955</v>
       </c>
       <c r="H1421" t="n">
         <v>113087</v>
@@ -41665,7 +41665,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>26.9399757385254</v>
+        <v>26.939977645874</v>
       </c>
       <c r="H1424" t="n">
         <v>66230</v>
@@ -41694,7 +41694,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="n">
-        <v>27.1798515319824</v>
+        <v>27.1798496246338</v>
       </c>
       <c r="H1425" t="n">
         <v>50534</v>
@@ -41723,7 +41723,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994789123535</v>
+        <v>27.8994808197021</v>
       </c>
       <c r="H1426" t="n">
         <v>102901</v>
@@ -41839,7 +41839,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167549133301</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1430" t="n">
         <v>75930</v>
@@ -41955,7 +41955,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167549133301</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1434" t="n">
         <v>37007</v>
@@ -42013,7 +42013,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>27.7703170776367</v>
+        <v>27.7703189849854</v>
       </c>
       <c r="H1436" t="n">
         <v>77299</v>
@@ -42042,7 +42042,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>27.3090171813965</v>
+        <v>27.3090152740479</v>
       </c>
       <c r="H1437" t="n">
         <v>40719</v>
@@ -42100,7 +42100,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.6744651794434</v>
+        <v>28.674467086792</v>
       </c>
       <c r="H1439" t="n">
         <v>107729</v>
@@ -42129,7 +42129,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1440" t="n">
         <v>83693</v>
@@ -42158,7 +42158,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1441" t="n">
-        <v>27.8072185516357</v>
+        <v>27.8072204589844</v>
       </c>
       <c r="H1441" t="n">
         <v>74738</v>
@@ -42216,7 +42216,7 @@
         <v>30.2600002288818</v>
       </c>
       <c r="G1443" t="n">
-        <v>27.9179344177246</v>
+        <v>27.917932510376</v>
       </c>
       <c r="H1443" t="n">
         <v>30488</v>
@@ -42245,7 +42245,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1444" t="n">
         <v>25013</v>
@@ -42274,7 +42274,7 @@
         <v>30.0200004577637</v>
       </c>
       <c r="G1445" t="n">
-        <v>27.6965084075928</v>
+        <v>27.6965065002441</v>
       </c>
       <c r="H1445" t="n">
         <v>29532</v>
@@ -42303,7 +42303,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="n">
-        <v>27.0506858825684</v>
+        <v>27.050687789917</v>
       </c>
       <c r="H1446" t="n">
         <v>113229</v>
@@ -42332,7 +42332,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="n">
-        <v>27.7518653869629</v>
+        <v>27.7518634796143</v>
       </c>
       <c r="H1447" t="n">
         <v>106881</v>
@@ -42477,7 +42477,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="n">
-        <v>28.0840034484863</v>
+        <v>28.0840015411377</v>
       </c>
       <c r="H1452" t="n">
         <v>49417</v>
@@ -42506,7 +42506,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1453" t="n">
-        <v>27.7887706756592</v>
+        <v>27.7887668609619</v>
       </c>
       <c r="H1453" t="n">
         <v>56815</v>
@@ -42593,7 +42593,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="n">
-        <v>26.8846187591553</v>
+        <v>26.8846168518066</v>
       </c>
       <c r="H1456" t="n">
         <v>46219</v>
@@ -42651,7 +42651,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>26.220344543457</v>
+        <v>26.2203464508057</v>
       </c>
       <c r="H1458" t="n">
         <v>92706</v>
@@ -42680,7 +42680,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191669464111</v>
+        <v>25.5191688537598</v>
       </c>
       <c r="H1459" t="n">
         <v>176751</v>
@@ -42767,7 +42767,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="n">
-        <v>24.9656085968018</v>
+        <v>24.9656047821045</v>
       </c>
       <c r="H1462" t="n">
         <v>161733</v>
@@ -42796,7 +42796,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>24.356689453125</v>
+        <v>24.3566875457764</v>
       </c>
       <c r="H1463" t="n">
         <v>92597</v>
@@ -42825,7 +42825,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.7108707427979</v>
+        <v>23.7108688354492</v>
       </c>
       <c r="H1464" t="n">
         <v>124786</v>
@@ -42854,7 +42854,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1465" t="n">
-        <v>23.729320526123</v>
+        <v>23.7293186187744</v>
       </c>
       <c r="H1465" t="n">
         <v>226930</v>
@@ -42912,7 +42912,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1467" t="n">
-        <v>23.2680187225342</v>
+        <v>23.2680206298828</v>
       </c>
       <c r="H1467" t="n">
         <v>94425</v>
@@ -42941,7 +42941,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1468" t="n">
         <v>76657</v>
@@ -42970,7 +42970,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1469" t="n">
-        <v>23.3049240112305</v>
+        <v>23.3049259185791</v>
       </c>
       <c r="H1469" t="n">
         <v>97191</v>
@@ -43028,7 +43028,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1471" t="n">
-        <v>24.2090721130371</v>
+        <v>24.2090740203857</v>
       </c>
       <c r="H1471" t="n">
         <v>89896</v>
@@ -43173,7 +43173,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="n">
-        <v>24.910249710083</v>
+        <v>24.9102516174316</v>
       </c>
       <c r="H1476" t="n">
         <v>51659</v>
@@ -43202,7 +43202,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1477" t="n">
-        <v>24.9840564727783</v>
+        <v>24.984058380127</v>
       </c>
       <c r="H1477" t="n">
         <v>45457</v>
@@ -43231,7 +43231,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1478" t="n">
         <v>36215</v>
@@ -43260,7 +43260,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179893493652</v>
+        <v>24.8179912567139</v>
       </c>
       <c r="H1479" t="n">
         <v>40510</v>
@@ -43347,7 +43347,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179893493652</v>
+        <v>24.8179912567139</v>
       </c>
       <c r="H1482" t="n">
         <v>79431</v>
@@ -43405,7 +43405,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="n">
-        <v>25.5376224517822</v>
+        <v>25.537618637085</v>
       </c>
       <c r="H1484" t="n">
         <v>157497</v>
@@ -43434,7 +43434,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="n">
-        <v>24.910249710083</v>
+        <v>24.9102516174316</v>
       </c>
       <c r="H1485" t="n">
         <v>209407</v>
@@ -43492,7 +43492,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1487" t="n">
-        <v>24.9840564727783</v>
+        <v>24.984058380127</v>
       </c>
       <c r="H1487" t="n">
         <v>69067</v>
@@ -43521,7 +43521,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.9287052154541</v>
+        <v>24.9287033081055</v>
       </c>
       <c r="H1488" t="n">
         <v>107665</v>
@@ -43666,7 +43666,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1493" t="n">
         <v>64503</v>
@@ -43695,7 +43695,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1494" t="n">
         <v>81730</v>
@@ -43956,7 +43956,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.8508033752441</v>
+        <v>20.8508014678955</v>
       </c>
       <c r="H1503" t="n">
         <v>98505</v>
@@ -44014,7 +44014,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="n">
-        <v>20.7031860351562</v>
+        <v>20.7031879425049</v>
       </c>
       <c r="H1505" t="n">
         <v>133575</v>
@@ -44130,7 +44130,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1509" t="n">
         <v>177120</v>
@@ -44275,7 +44275,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.7031860351562</v>
+        <v>20.7031879425049</v>
       </c>
       <c r="H1514" t="n">
         <v>46863</v>
@@ -44304,7 +44304,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525981903076</v>
       </c>
       <c r="H1515" t="n">
         <v>74574</v>
@@ -44333,7 +44333,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1516" t="n">
         <v>83075</v>
@@ -44362,7 +44362,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1517" t="n">
-        <v>20.8323497772217</v>
+        <v>20.8323516845703</v>
       </c>
       <c r="H1517" t="n">
         <v>102046</v>
@@ -44420,7 +44420,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525981903076</v>
       </c>
       <c r="H1519" t="n">
         <v>105798</v>
@@ -44478,7 +44478,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.9948272705078</v>
+        <v>21.9948291778564</v>
       </c>
       <c r="H1521" t="n">
         <v>112637</v>
@@ -44681,7 +44681,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G1528" t="n">
-        <v>22.8620758056641</v>
+        <v>22.8620738983154</v>
       </c>
       <c r="H1528" t="n">
         <v>99627</v>
@@ -44739,7 +44739,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>22.3085136413574</v>
+        <v>22.3085117340088</v>
       </c>
       <c r="H1530" t="n">
         <v>64510</v>
@@ -44826,7 +44826,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674583435059</v>
+        <v>21.3674602508545</v>
       </c>
       <c r="H1533" t="n">
         <v>40625</v>
@@ -45000,7 +45000,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1539" t="n">
         <v>67442</v>
@@ -45087,7 +45087,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.9281997680664</v>
+        <v>19.928201675415</v>
       </c>
       <c r="H1542" t="n">
         <v>354066</v>
@@ -45116,7 +45116,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1543" t="n">
-        <v>20.0758190155029</v>
+        <v>20.0758171081543</v>
       </c>
       <c r="H1543" t="n">
         <v>220064</v>
@@ -45145,7 +45145,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1544" t="n">
         <v>73711</v>
@@ -45174,7 +45174,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877067565918</v>
+        <v>20.8877048492432</v>
       </c>
       <c r="H1545" t="n">
         <v>65560</v>
@@ -45203,7 +45203,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G1546" t="n">
-        <v>20.7216396331787</v>
+        <v>20.7216358184814</v>
       </c>
       <c r="H1546" t="n">
         <v>73272</v>
@@ -45232,7 +45232,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1547" t="n">
-        <v>21.1275825500488</v>
+        <v>21.1275806427002</v>
       </c>
       <c r="H1547" t="n">
         <v>50975</v>
@@ -45261,7 +45261,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.312105178833</v>
+        <v>21.3121032714844</v>
       </c>
       <c r="H1548" t="n">
         <v>71843</v>
@@ -45319,7 +45319,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1550" t="n">
-        <v>21.1275825500488</v>
+        <v>21.1275806427002</v>
       </c>
       <c r="H1550" t="n">
         <v>113684</v>
@@ -45377,7 +45377,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1552" t="n">
-        <v>20.2787895202637</v>
+        <v>20.278787612915</v>
       </c>
       <c r="H1552" t="n">
         <v>50610</v>
@@ -45464,7 +45464,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="n">
-        <v>20.5371170043945</v>
+        <v>20.5371189117432</v>
       </c>
       <c r="H1555" t="n">
         <v>162022</v>
@@ -45580,7 +45580,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.7585430145264</v>
+        <v>20.7585411071777</v>
       </c>
       <c r="H1559" t="n">
         <v>34621</v>
@@ -45609,7 +45609,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="n">
-        <v>20.3710498809814</v>
+        <v>20.3710479736328</v>
       </c>
       <c r="H1560" t="n">
         <v>107999</v>
@@ -45754,7 +45754,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770515441895</v>
+        <v>17.6770496368408</v>
       </c>
       <c r="H1565" t="n">
         <v>135742</v>
@@ -45870,7 +45870,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633670806885</v>
+        <v>17.3633689880371</v>
       </c>
       <c r="H1569" t="n">
         <v>50964</v>
@@ -45928,7 +45928,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1571" t="n">
         <v>197519</v>
@@ -45957,7 +45957,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.0845413208008</v>
+        <v>15.0845403671265</v>
       </c>
       <c r="H1572" t="n">
         <v>244822</v>
@@ -45986,7 +45986,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>15.23215675354</v>
+        <v>15.2321577072144</v>
       </c>
       <c r="H1573" t="n">
         <v>154625</v>
@@ -46102,7 +46102,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.23779296875</v>
+        <v>16.2377948760986</v>
       </c>
       <c r="H1577" t="n">
         <v>111126</v>
@@ -46131,7 +46131,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1578" t="n">
-        <v>13.4699878692627</v>
+        <v>13.469988822937</v>
       </c>
       <c r="H1578" t="n">
         <v>921508</v>
@@ -46160,7 +46160,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.2172937393188</v>
+        <v>14.2172946929932</v>
       </c>
       <c r="H1579" t="n">
         <v>614742</v>
@@ -46218,7 +46218,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.3372325897217</v>
+        <v>14.337233543396</v>
       </c>
       <c r="H1581" t="n">
         <v>304440</v>
@@ -46247,7 +46247,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878223419189</v>
+        <v>14.6878213882446</v>
       </c>
       <c r="H1582" t="n">
         <v>163036</v>
@@ -46276,7 +46276,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1583" t="n">
-        <v>14.8169851303101</v>
+        <v>14.8169860839844</v>
       </c>
       <c r="H1583" t="n">
         <v>106388</v>
@@ -46334,7 +46334,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634258270264</v>
+        <v>14.2634248733521</v>
       </c>
       <c r="H1585" t="n">
         <v>112266</v>
@@ -46363,7 +46363,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1586" t="n">
-        <v>14.2541980743408</v>
+        <v>14.2541999816895</v>
       </c>
       <c r="H1586" t="n">
         <v>187789</v>
@@ -46392,7 +46392,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G1587" t="n">
-        <v>14.6601438522339</v>
+        <v>14.6601448059082</v>
       </c>
       <c r="H1587" t="n">
         <v>182343</v>
@@ -46450,7 +46450,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.6565532684326</v>
+        <v>15.6565542221069</v>
       </c>
       <c r="H1589" t="n">
         <v>213894</v>
@@ -46537,7 +46537,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.0753164291382</v>
+        <v>15.0753154754639</v>
       </c>
       <c r="H1592" t="n">
         <v>140875</v>
@@ -46566,7 +46566,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.4571704864502</v>
+        <v>14.4571714401245</v>
       </c>
       <c r="H1593" t="n">
         <v>111492</v>
@@ -46595,7 +46595,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021240234375</v>
       </c>
       <c r="H1594" t="n">
         <v>167595</v>
@@ -46682,7 +46682,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0420017242432</v>
+        <v>14.0420007705688</v>
       </c>
       <c r="H1597" t="n">
         <v>49196</v>
@@ -46711,7 +46711,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.9958715438843</v>
+        <v>13.99587059021</v>
       </c>
       <c r="H1598" t="n">
         <v>55239</v>
@@ -46740,7 +46740,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.820574760437</v>
+        <v>13.8205766677856</v>
       </c>
       <c r="H1599" t="n">
         <v>68975</v>
@@ -46769,7 +46769,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G1600" t="n">
-        <v>13.922061920166</v>
+        <v>13.9220628738403</v>
       </c>
       <c r="H1600" t="n">
         <v>50011</v>
@@ -46798,7 +46798,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1601" t="n">
         <v>45680</v>
@@ -46827,7 +46827,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.2541980743408</v>
+        <v>14.2541999816895</v>
       </c>
       <c r="H1602" t="n">
         <v>61148</v>
@@ -46914,7 +46914,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.8667058944702</v>
+        <v>13.8667068481445</v>
       </c>
       <c r="H1605" t="n">
         <v>46964</v>
@@ -46972,7 +46972,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.8482542037964</v>
+        <v>13.8482532501221</v>
       </c>
       <c r="H1607" t="n">
         <v>59001</v>
@@ -47146,7 +47146,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.2854671478271</v>
+        <v>13.2854661941528</v>
       </c>
       <c r="H1613" t="n">
         <v>58779</v>
@@ -47175,7 +47175,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1614" t="n">
-        <v>13.2024326324463</v>
+        <v>13.2024335861206</v>
       </c>
       <c r="H1614" t="n">
         <v>61686</v>
@@ -47349,7 +47349,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476369857788</v>
+        <v>15.0476360321045</v>
       </c>
       <c r="H1620" t="n">
         <v>154501</v>
@@ -47407,7 +47407,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3059663772583</v>
+        <v>15.3059644699097</v>
       </c>
       <c r="H1622" t="n">
         <v>88717</v>
@@ -47436,7 +47436,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="n">
-        <v>15.3428688049316</v>
+        <v>15.342869758606</v>
       </c>
       <c r="H1623" t="n">
         <v>75173</v>
@@ -47465,7 +47465,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384111404419</v>
+        <v>15.0384092330933</v>
       </c>
       <c r="H1624" t="n">
         <v>74404</v>
@@ -47552,7 +47552,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.9367218017578</v>
+        <v>14.9367227554321</v>
       </c>
       <c r="H1627" t="n">
         <v>47766</v>
@@ -47639,7 +47639,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="n">
-        <v>15.9823884963989</v>
+        <v>15.9823894500732</v>
       </c>
       <c r="H1630" t="n">
         <v>64691</v>
@@ -47697,7 +47697,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.7137775421143</v>
+        <v>15.7137765884399</v>
       </c>
       <c r="H1632" t="n">
         <v>66096</v>
@@ -47726,7 +47726,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9823884963989</v>
+        <v>15.9823894500732</v>
       </c>
       <c r="H1633" t="n">
         <v>27898</v>
@@ -47813,7 +47813,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.8576765060425</v>
+        <v>15.8576774597168</v>
       </c>
       <c r="H1636" t="n">
         <v>45854</v>
@@ -47842,7 +47842,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1637" t="n">
-        <v>15.6466245651245</v>
+        <v>15.6466236114502</v>
       </c>
       <c r="H1637" t="n">
         <v>47026</v>
@@ -47987,7 +47987,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>13.843090057373</v>
+        <v>13.8430891036987</v>
       </c>
       <c r="H1642" t="n">
         <v>116898</v>
@@ -48074,7 +48074,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.0180673599243</v>
+        <v>13.0180683135986</v>
       </c>
       <c r="H1645" t="n">
         <v>44723</v>
@@ -48103,7 +48103,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1646" t="n">
-        <v>13.0660352706909</v>
+        <v>13.0660343170166</v>
       </c>
       <c r="H1646" t="n">
         <v>48895</v>
@@ -48161,7 +48161,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="n">
-        <v>12.4040994644165</v>
+        <v>12.4040985107422</v>
       </c>
       <c r="H1648" t="n">
         <v>78173</v>
@@ -48364,7 +48364,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.7805366516113</v>
+        <v>11.780535697937</v>
       </c>
       <c r="H1655" t="n">
         <v>68390</v>
@@ -48393,7 +48393,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="n">
-        <v>11.5502986907959</v>
+        <v>11.5502977371216</v>
       </c>
       <c r="H1656" t="n">
         <v>106176</v>
@@ -48422,7 +48422,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1657" t="n">
-        <v>11.9724016189575</v>
+        <v>11.9724006652832</v>
       </c>
       <c r="H1657" t="n">
         <v>85513</v>
@@ -48509,7 +48509,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="n">
-        <v>12.7974224090576</v>
+        <v>12.7974233627319</v>
       </c>
       <c r="H1660" t="n">
         <v>30618</v>
@@ -48567,7 +48567,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G1662" t="n">
-        <v>12.6823043823242</v>
+        <v>12.6823034286499</v>
       </c>
       <c r="H1662" t="n">
         <v>62896</v>
@@ -48683,7 +48683,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1666" t="n">
-        <v>13.1715602874756</v>
+        <v>13.1715593338013</v>
       </c>
       <c r="H1666" t="n">
         <v>26112</v>
@@ -48712,7 +48712,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1667" t="n">
-        <v>13.1715602874756</v>
+        <v>13.1715593338013</v>
       </c>
       <c r="H1667" t="n">
         <v>43945</v>
@@ -48770,7 +48770,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>13.1044082641602</v>
+        <v>13.1044073104858</v>
       </c>
       <c r="H1669" t="n">
         <v>22290</v>
@@ -48886,7 +48886,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1673" t="n">
-        <v>12.7782354354858</v>
+        <v>12.7782363891602</v>
       </c>
       <c r="H1673" t="n">
         <v>79863</v>
@@ -48915,7 +48915,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="n">
-        <v>13.3058652877808</v>
+        <v>13.3058662414551</v>
       </c>
       <c r="H1674" t="n">
         <v>153447</v>
@@ -48944,7 +48944,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1675" t="n">
-        <v>13.0372543334961</v>
+        <v>13.0372552871704</v>
       </c>
       <c r="H1675" t="n">
         <v>84357</v>
@@ -49002,7 +49002,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.3154602050781</v>
+        <v>13.3154592514038</v>
       </c>
       <c r="H1677" t="n">
         <v>61589</v>
@@ -49031,7 +49031,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.1044082641602</v>
+        <v>13.1044073104858</v>
       </c>
       <c r="H1678" t="n">
         <v>78688</v>
@@ -49060,7 +49060,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="n">
-        <v>12.480845451355</v>
+        <v>12.4808444976807</v>
       </c>
       <c r="H1679" t="n">
         <v>126884</v>
@@ -49089,7 +49089,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.6055574417114</v>
+        <v>12.6055583953857</v>
       </c>
       <c r="H1680" t="n">
         <v>65707</v>
@@ -49118,7 +49118,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1681" t="n">
-        <v>12.1738586425781</v>
+        <v>12.1738595962524</v>
       </c>
       <c r="H1681" t="n">
         <v>68306</v>
@@ -49176,7 +49176,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1683" t="n">
-        <v>12.7782354354858</v>
+        <v>12.7782363891602</v>
       </c>
       <c r="H1683" t="n">
         <v>46182</v>
@@ -49350,7 +49350,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>11.7805366516113</v>
+        <v>11.780535697937</v>
       </c>
       <c r="H1689" t="n">
         <v>75821</v>
@@ -49437,7 +49437,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1692" t="n">
-        <v>12.1546726226807</v>
+        <v>12.1546745300293</v>
       </c>
       <c r="H1692" t="n">
         <v>63596</v>
@@ -49495,7 +49495,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1694" t="n">
-        <v>12.3081665039062</v>
+        <v>12.3081655502319</v>
       </c>
       <c r="H1694" t="n">
         <v>52687</v>
@@ -49553,7 +49553,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1696" t="n">
         <v>51664</v>
@@ -49582,7 +49582,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1697" t="n">
-        <v>11.8476896286011</v>
+        <v>11.8476886749268</v>
       </c>
       <c r="H1697" t="n">
         <v>50586</v>
@@ -49640,7 +49640,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="n">
-        <v>11.4927368164062</v>
+        <v>11.4927377700806</v>
       </c>
       <c r="H1699" t="n">
         <v>80053</v>
@@ -49669,7 +49669,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1700" t="n">
-        <v>11.4639587402344</v>
+        <v>11.4639577865601</v>
       </c>
       <c r="H1700" t="n">
         <v>62951</v>
@@ -49698,7 +49698,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1701" t="n">
-        <v>11.4639587402344</v>
+        <v>11.4639577865601</v>
       </c>
       <c r="H1701" t="n">
         <v>58588</v>
@@ -49814,7 +49814,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1705" t="n">
-        <v>11.7421636581421</v>
+        <v>11.7421627044678</v>
       </c>
       <c r="H1705" t="n">
         <v>64648</v>
@@ -49843,7 +49843,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1706" t="n">
-        <v>11.7709426879883</v>
+        <v>11.7709436416626</v>
       </c>
       <c r="H1706" t="n">
         <v>57056</v>
@@ -49872,7 +49872,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G1707" t="n">
-        <v>11.7421636581421</v>
+        <v>11.7421627044678</v>
       </c>
       <c r="H1707" t="n">
         <v>40647</v>
@@ -49988,7 +49988,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1711" t="n">
-        <v>11.3680257797241</v>
+        <v>11.3680248260498</v>
       </c>
       <c r="H1711" t="n">
         <v>37939</v>
@@ -50075,7 +50075,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1714" t="n">
-        <v>10.9459218978882</v>
+        <v>10.9459209442139</v>
       </c>
       <c r="H1714" t="n">
         <v>22338</v>
@@ -50104,7 +50104,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>10.8499889373779</v>
+        <v>10.8499898910522</v>
       </c>
       <c r="H1715" t="n">
         <v>25660</v>
@@ -50133,7 +50133,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G1716" t="n">
-        <v>10.9459218978882</v>
+        <v>10.9459209442139</v>
       </c>
       <c r="H1716" t="n">
         <v>55086</v>
@@ -50162,7 +50162,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.754056930542</v>
+        <v>10.7540559768677</v>
       </c>
       <c r="H1717" t="n">
         <v>47037</v>
@@ -50191,7 +50191,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1718" t="n">
-        <v>10.9555139541626</v>
+        <v>10.9555149078369</v>
       </c>
       <c r="H1718" t="n">
         <v>35414</v>
@@ -50307,7 +50307,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1722" t="n">
-        <v>11.6558237075806</v>
+        <v>11.6558227539062</v>
       </c>
       <c r="H1722" t="n">
         <v>48221</v>
@@ -50336,7 +50336,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.5694856643677</v>
+        <v>11.5694847106934</v>
       </c>
       <c r="H1723" t="n">
         <v>30512</v>
@@ -50365,7 +50365,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>11.5790767669678</v>
+        <v>11.5790777206421</v>
       </c>
       <c r="H1724" t="n">
         <v>33530</v>
@@ -50394,7 +50394,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1725" t="n">
-        <v>11.5311126708984</v>
+        <v>11.5311117172241</v>
       </c>
       <c r="H1725" t="n">
         <v>20586</v>
@@ -50452,7 +50452,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1727" t="n">
-        <v>11.7613506317139</v>
+        <v>11.7613496780396</v>
       </c>
       <c r="H1727" t="n">
         <v>44721</v>
@@ -50568,7 +50568,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1731" t="n">
-        <v>11.9724016189575</v>
+        <v>11.9724006652832</v>
       </c>
       <c r="H1731" t="n">
         <v>31016</v>
@@ -50597,7 +50597,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1732" t="n">
-        <v>11.9628076553345</v>
+        <v>11.9628086090088</v>
       </c>
       <c r="H1732" t="n">
         <v>17425</v>
@@ -50626,7 +50626,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G1733" t="n">
-        <v>12.1546726226807</v>
+        <v>12.1546745300293</v>
       </c>
       <c r="H1733" t="n">
         <v>45975</v>
@@ -50713,7 +50713,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1736" t="n">
-        <v>13.0372543334961</v>
+        <v>13.0372552871704</v>
       </c>
       <c r="H1736" t="n">
         <v>188772</v>
@@ -50945,7 +50945,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.5790767669678</v>
+        <v>11.5790777206421</v>
       </c>
       <c r="H1744" t="n">
         <v>105065</v>
@@ -51148,7 +51148,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.2889804840088</v>
+        <v>12.2889795303345</v>
       </c>
       <c r="H1751" t="n">
         <v>103263</v>
@@ -51235,7 +51235,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930456161499</v>
+        <v>12.1930465698242</v>
       </c>
       <c r="H1754" t="n">
         <v>93258</v>
@@ -51467,7 +51467,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G1762" t="n">
-        <v>12.7686443328857</v>
+        <v>12.7686433792114</v>
       </c>
       <c r="H1762" t="n">
         <v>180370</v>
@@ -51612,7 +51612,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>12.327353477478</v>
+        <v>12.3273525238037</v>
       </c>
       <c r="H1767" t="n">
         <v>48990</v>
@@ -51641,7 +51641,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1768" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1768" t="n">
         <v>41157</v>
@@ -51670,7 +51670,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1769" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1769" t="n">
         <v>40933</v>
@@ -51757,7 +51757,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1772" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1772" t="n">
         <v>56609</v>
@@ -51786,7 +51786,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1773" t="n">
         <v>45619</v>
@@ -51844,7 +51844,7 @@
         <v>12.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.9915885925293</v>
+        <v>11.991587638855</v>
       </c>
       <c r="H1775" t="n">
         <v>63441</v>
@@ -51902,7 +51902,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1777" t="n">
-        <v>11.9244346618652</v>
+        <v>11.9244356155396</v>
       </c>
       <c r="H1777" t="n">
         <v>44998</v>
@@ -51931,7 +51931,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.0395545959473</v>
+        <v>12.0395536422729</v>
       </c>
       <c r="H1778" t="n">
         <v>24126</v>
@@ -51989,7 +51989,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1780" t="n">
-        <v>12.1738586425781</v>
+        <v>12.1738595962524</v>
       </c>
       <c r="H1780" t="n">
         <v>29284</v>
@@ -52018,7 +52018,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1781" t="n">
-        <v>12.3081665039062</v>
+        <v>12.3081655502319</v>
       </c>
       <c r="H1781" t="n">
         <v>134819</v>
@@ -52105,7 +52105,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.5000314712524</v>
+        <v>12.5000305175781</v>
       </c>
       <c r="H1784" t="n">
         <v>49900</v>
@@ -52134,7 +52134,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1785" t="n">
-        <v>12.8262023925781</v>
+        <v>12.8262033462524</v>
       </c>
       <c r="H1785" t="n">
         <v>43708</v>
@@ -52192,7 +52192,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1787" t="n">
-        <v>13.0852222442627</v>
+        <v>13.0852212905884</v>
       </c>
       <c r="H1787" t="n">
         <v>34405</v>
@@ -52308,7 +52308,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.7663431167603</v>
+        <v>13.7663440704346</v>
       </c>
       <c r="H1791" t="n">
         <v>71163</v>
@@ -52395,7 +52395,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1794" t="n">
-        <v>14.2172269821167</v>
+        <v>14.2172260284424</v>
       </c>
       <c r="H1794" t="n">
         <v>68949</v>
@@ -52540,7 +52540,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1799" t="n">
-        <v>14.1404800415039</v>
+        <v>14.1404809951782</v>
       </c>
       <c r="H1799" t="n">
         <v>78517</v>
@@ -52656,7 +52656,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>14.2939720153809</v>
+        <v>14.2939729690552</v>
       </c>
       <c r="H1803" t="n">
         <v>84411</v>
@@ -52743,7 +52743,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463148117065</v>
+        <v>14.9463157653809</v>
       </c>
       <c r="H1806" t="n">
         <v>121708</v>
@@ -52859,7 +52859,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G1810" t="n">
-        <v>14.3131589889526</v>
+        <v>14.313159942627</v>
       </c>
       <c r="H1810" t="n">
         <v>59576</v>
@@ -52888,7 +52888,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1811" t="n">
-        <v>14.4474658966064</v>
+        <v>14.4474649429321</v>
       </c>
       <c r="H1811" t="n">
         <v>60232</v>
@@ -52917,7 +52917,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1812" t="n">
-        <v>14.2172269821167</v>
+        <v>14.2172260284424</v>
       </c>
       <c r="H1812" t="n">
         <v>66566</v>
@@ -52946,7 +52946,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.3323450088501</v>
+        <v>14.3323459625244</v>
       </c>
       <c r="H1813" t="n">
         <v>56523</v>
@@ -52975,7 +52975,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.3515319824219</v>
+        <v>14.3515329360962</v>
       </c>
       <c r="H1814" t="n">
         <v>36760</v>
@@ -53004,7 +53004,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1815" t="n">
         <v>43434</v>
@@ -53033,7 +53033,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1816" t="n">
-        <v>14.5242109298706</v>
+        <v>14.5242118835449</v>
       </c>
       <c r="H1816" t="n">
         <v>68875</v>
@@ -53062,7 +53062,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1817" t="n">
         <v>85926</v>
@@ -53091,7 +53091,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1818" t="n">
-        <v>14.6009588241577</v>
+        <v>14.6009578704834</v>
       </c>
       <c r="H1818" t="n">
         <v>47487</v>
@@ -53120,7 +53120,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1819" t="n">
         <v>79210</v>
@@ -53149,7 +53149,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G1820" t="n">
-        <v>14.3611259460449</v>
+        <v>14.3611268997192</v>
       </c>
       <c r="H1820" t="n">
         <v>69943</v>
@@ -53207,7 +53207,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.828896522522</v>
+        <v>15.8288974761963</v>
       </c>
       <c r="H1822" t="n">
         <v>177332</v>
@@ -53265,7 +53265,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1824" t="n">
-        <v>16.3373413085938</v>
+        <v>16.3373394012451</v>
       </c>
       <c r="H1824" t="n">
         <v>103940</v>
@@ -53323,7 +53323,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="n">
-        <v>15.9823884963989</v>
+        <v>15.9823894500732</v>
       </c>
       <c r="H1826" t="n">
         <v>183104</v>
@@ -53381,7 +53381,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1828" t="n">
-        <v>16.2030353546143</v>
+        <v>16.2030334472656</v>
       </c>
       <c r="H1828" t="n">
         <v>59759</v>
@@ -53439,7 +53439,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1830" t="n">
-        <v>16.1454734802246</v>
+        <v>16.1454753875732</v>
       </c>
       <c r="H1830" t="n">
         <v>33085</v>
@@ -53468,7 +53468,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1831" t="n">
-        <v>16.2030353546143</v>
+        <v>16.2030334472656</v>
       </c>
       <c r="H1831" t="n">
         <v>39708</v>
@@ -53497,7 +53497,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1832" t="n">
-        <v>16.0207633972168</v>
+        <v>16.0207614898682</v>
       </c>
       <c r="H1832" t="n">
         <v>60293</v>
@@ -53526,7 +53526,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.3588266372681</v>
+        <v>15.3588256835938</v>
       </c>
       <c r="H1833" t="n">
         <v>142239</v>
@@ -53584,7 +53584,7 @@
         <v>15.25</v>
       </c>
       <c r="G1835" t="n">
-        <v>14.6297369003296</v>
+        <v>14.6297378540039</v>
       </c>
       <c r="H1835" t="n">
         <v>390715</v>
@@ -53613,7 +53613,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1836" t="n">
-        <v>14.5242109298706</v>
+        <v>14.5242118835449</v>
       </c>
       <c r="H1836" t="n">
         <v>276851</v>
@@ -53729,7 +53729,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1840" t="n">
-        <v>14.639331817627</v>
+        <v>14.6393308639526</v>
       </c>
       <c r="H1840" t="n">
         <v>102978</v>
@@ -53903,7 +53903,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1846" t="n">
-        <v>13.939022064209</v>
+        <v>13.9390211105347</v>
       </c>
       <c r="H1846" t="n">
         <v>59999</v>
@@ -54222,7 +54222,7 @@
         <v>14</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4305782318115</v>
+        <v>13.4305791854858</v>
       </c>
       <c r="H1857" t="n">
         <v>134657</v>
@@ -54396,7 +54396,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1863" t="n">
-        <v>12.9701013565063</v>
+        <v>12.9701023101807</v>
       </c>
       <c r="H1863" t="n">
         <v>106326</v>
@@ -54483,7 +54483,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G1866" t="n">
-        <v>13.0180673599243</v>
+        <v>13.0180683135986</v>
       </c>
       <c r="H1866" t="n">
         <v>84225</v>
@@ -54512,7 +54512,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1867" t="n">
-        <v>13.027660369873</v>
+        <v>13.0276613235474</v>
       </c>
       <c r="H1867" t="n">
         <v>39070</v>
@@ -54686,7 +54686,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1873" t="n">
-        <v>12.8862733840942</v>
+        <v>12.8862724304199</v>
       </c>
       <c r="H1873" t="n">
         <v>74352</v>
@@ -54715,7 +54715,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1874" t="n">
-        <v>12.2768526077271</v>
+        <v>12.2768535614014</v>
       </c>
       <c r="H1874" t="n">
         <v>337436</v>
@@ -54831,7 +54831,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1878" t="n">
-        <v>12.2080488204956</v>
+        <v>12.2080478668213</v>
       </c>
       <c r="H1878" t="n">
         <v>74114</v>
@@ -54889,7 +54889,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1880" t="n">
-        <v>12.7093458175659</v>
+        <v>12.7093448638916</v>
       </c>
       <c r="H1880" t="n">
         <v>114865</v>
@@ -55034,7 +55034,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1885" t="n">
-        <v>11.7165803909302</v>
+        <v>11.7165813446045</v>
       </c>
       <c r="H1885" t="n">
         <v>61095</v>
@@ -55121,7 +55121,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1888" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1888" t="n">
         <v>49130</v>
@@ -55295,7 +55295,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1894" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H1894" t="n">
         <v>62454</v>
@@ -55324,7 +55324,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1895" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H1895" t="n">
         <v>45711</v>
@@ -55411,7 +55411,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1898" t="n">
-        <v>11.9524850845337</v>
+        <v>11.9524841308594</v>
       </c>
       <c r="H1898" t="n">
         <v>50728</v>
@@ -55527,7 +55527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1902" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1902" t="n">
         <v>60178</v>
@@ -55643,7 +55643,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1906" t="n">
-        <v>11.5887994766235</v>
+        <v>11.5887985229492</v>
       </c>
       <c r="H1906" t="n">
         <v>66958</v>
@@ -55788,7 +55788,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1911" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1911" t="n">
         <v>39057</v>
@@ -55962,7 +55962,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1917" t="n">
-        <v>11.4217004776001</v>
+        <v>11.4216995239258</v>
       </c>
       <c r="H1917" t="n">
         <v>57508</v>
@@ -56020,7 +56020,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1919" t="n">
-        <v>11.4217004776001</v>
+        <v>11.4216995239258</v>
       </c>
       <c r="H1919" t="n">
         <v>35438</v>
@@ -56107,7 +56107,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1922" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H1922" t="n">
         <v>107825</v>
@@ -56136,7 +56136,7 @@
         <v>12</v>
       </c>
       <c r="G1923" t="n">
-        <v>11.7952156066895</v>
+        <v>11.7952146530151</v>
       </c>
       <c r="H1923" t="n">
         <v>109237</v>
@@ -56165,7 +56165,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1924" t="n">
-        <v>11.7460689544678</v>
+        <v>11.7460680007935</v>
       </c>
       <c r="H1924" t="n">
         <v>44422</v>
@@ -56252,7 +56252,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1927" t="n">
-        <v>11.7264108657837</v>
+        <v>11.7264099121094</v>
       </c>
       <c r="H1927" t="n">
         <v>47219</v>
@@ -56310,7 +56310,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1929" t="n">
-        <v>11.8738508224487</v>
+        <v>11.8738498687744</v>
       </c>
       <c r="H1929" t="n">
         <v>167696</v>
@@ -56368,7 +56368,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1931" t="n">
-        <v>12.1097545623779</v>
+        <v>12.1097536087036</v>
       </c>
       <c r="H1931" t="n">
         <v>133586</v>
@@ -56455,7 +56455,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1934" t="n">
-        <v>11.5986280441284</v>
+        <v>11.5986289978027</v>
       </c>
       <c r="H1934" t="n">
         <v>54866</v>
@@ -56484,7 +56484,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1935" t="n">
-        <v>11.4020414352417</v>
+        <v>11.402042388916</v>
       </c>
       <c r="H1935" t="n">
         <v>69816</v>
@@ -56600,7 +56600,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1939" t="n">
-        <v>11.2251129150391</v>
+        <v>11.2251138687134</v>
       </c>
       <c r="H1939" t="n">
         <v>45479</v>
@@ -56658,7 +56658,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1941" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H1941" t="n">
         <v>126662</v>
@@ -56716,7 +56716,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1943" t="n">
-        <v>11.8345336914062</v>
+        <v>11.8345327377319</v>
       </c>
       <c r="H1943" t="n">
         <v>125912</v>
@@ -56774,7 +56774,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1945" t="n">
-        <v>12.2473659515381</v>
+        <v>12.2473649978638</v>
       </c>
       <c r="H1945" t="n">
         <v>112071</v>
@@ -56861,7 +56861,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1948" t="n">
-        <v>11.8345336914062</v>
+        <v>11.8345327377319</v>
       </c>
       <c r="H1948" t="n">
         <v>69300</v>
@@ -56919,7 +56919,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1950" t="n">
-        <v>12.2375354766846</v>
+        <v>12.2375364303589</v>
       </c>
       <c r="H1950" t="n">
         <v>44747</v>
@@ -56948,7 +56948,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1951" t="n">
-        <v>12.2670240402222</v>
+        <v>12.2670230865479</v>
       </c>
       <c r="H1951" t="n">
         <v>66899</v>
@@ -57122,7 +57122,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1957" t="n">
-        <v>11.8935098648071</v>
+        <v>11.8935089111328</v>
       </c>
       <c r="H1957" t="n">
         <v>84287</v>
@@ -57267,7 +57267,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1962" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1962" t="n">
         <v>65978</v>
@@ -57325,7 +57325,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1964" t="n">
-        <v>11.3725538253784</v>
+        <v>11.3725528717041</v>
       </c>
       <c r="H1964" t="n">
         <v>95068</v>
@@ -57354,7 +57354,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1965" t="n">
-        <v>11.2251129150391</v>
+        <v>11.2251138687134</v>
       </c>
       <c r="H1965" t="n">
         <v>85683</v>
@@ -57383,7 +57383,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1966" t="n">
-        <v>11.3823823928833</v>
+        <v>11.3823833465576</v>
       </c>
       <c r="H1966" t="n">
         <v>97120</v>
@@ -57441,7 +57441,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1968" t="n">
-        <v>11.0481853485107</v>
+        <v>11.0481843948364</v>
       </c>
       <c r="H1968" t="n">
         <v>56453</v>
@@ -57586,7 +57586,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1973" t="n">
-        <v>10.8614273071289</v>
+        <v>10.8614282608032</v>
       </c>
       <c r="H1973" t="n">
         <v>71442</v>
@@ -57644,7 +57644,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1975" t="n">
-        <v>10.6746702194214</v>
+        <v>10.6746692657471</v>
       </c>
       <c r="H1975" t="n">
         <v>43738</v>
@@ -57702,7 +57702,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1977" t="n">
-        <v>10.6746702194214</v>
+        <v>10.6746692657471</v>
       </c>
       <c r="H1977" t="n">
         <v>52690</v>
@@ -57818,7 +57818,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1981" t="n">
-        <v>11.1563091278076</v>
+        <v>11.1563081741333</v>
       </c>
       <c r="H1981" t="n">
         <v>67840</v>
@@ -57847,7 +57847,7 @@
         <v>11.25</v>
       </c>
       <c r="G1982" t="n">
-        <v>11.0580148696899</v>
+        <v>11.0580139160156</v>
       </c>
       <c r="H1982" t="n">
         <v>91613</v>
@@ -58079,7 +58079,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1990" t="n">
-        <v>10.0455913543701</v>
+        <v>10.0455923080444</v>
       </c>
       <c r="H1990" t="n">
         <v>69361</v>
@@ -58137,7 +58137,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1992" t="n">
-        <v>9.79985904693604</v>
+        <v>9.79985809326172</v>
       </c>
       <c r="H1992" t="n">
         <v>156565</v>
@@ -58166,7 +58166,7 @@
         <v>9.70499992370605</v>
       </c>
       <c r="G1993" t="n">
-        <v>9.53938007354736</v>
+        <v>9.53938102722168</v>
       </c>
       <c r="H1993" t="n">
         <v>147157</v>
@@ -58282,7 +58282,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1997" t="n">
-        <v>10.0161037445068</v>
+        <v>10.0161027908325</v>
       </c>
       <c r="H1997" t="n">
         <v>95490</v>
@@ -58804,7 +58804,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2015" t="n">
-        <v>11.1563091278076</v>
+        <v>11.1563081741333</v>
       </c>
       <c r="H2015" t="n">
         <v>79198</v>
@@ -58920,7 +58920,7 @@
         <v>11</v>
       </c>
       <c r="G2019" t="n">
-        <v>10.8122806549072</v>
+        <v>10.8122816085815</v>
       </c>
       <c r="H2019" t="n">
         <v>137497</v>
@@ -58978,7 +58978,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G2021" t="n">
-        <v>11.1366500854492</v>
+        <v>11.1366491317749</v>
       </c>
       <c r="H2021" t="n">
         <v>58974</v>
@@ -59007,7 +59007,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G2022" t="n">
-        <v>11.0285263061523</v>
+        <v>11.0285272598267</v>
       </c>
       <c r="H2022" t="n">
         <v>36863</v>
@@ -59065,7 +59065,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G2024" t="n">
-        <v>11.2742605209351</v>
+        <v>11.2742595672607</v>
       </c>
       <c r="H2024" t="n">
         <v>50950</v>
@@ -59181,7 +59181,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2028" t="n">
-        <v>11.8738508224487</v>
+        <v>11.8738498687744</v>
       </c>
       <c r="H2028" t="n">
         <v>182332</v>
@@ -59210,7 +59210,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2029" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H2029" t="n">
         <v>87835</v>
@@ -59239,7 +59239,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2030" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H2030" t="n">
         <v>69686</v>
@@ -59297,7 +59297,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2032" t="n">
-        <v>11.8935098648071</v>
+        <v>11.8935089111328</v>
       </c>
       <c r="H2032" t="n">
         <v>140876</v>
@@ -59355,7 +59355,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G2034" t="n">
-        <v>12.4341220855713</v>
+        <v>12.4341230392456</v>
       </c>
       <c r="H2034" t="n">
         <v>131198</v>
@@ -59616,7 +59616,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G2043" t="n">
-        <v>12.0507793426514</v>
+        <v>12.0507783889771</v>
       </c>
       <c r="H2043" t="n">
         <v>63638</v>
@@ -59703,7 +59703,7 @@
         <v>12</v>
       </c>
       <c r="G2046" t="n">
-        <v>11.7952156066895</v>
+        <v>11.7952146530151</v>
       </c>
       <c r="H2046" t="n">
         <v>50591</v>
@@ -59790,7 +59790,7 @@
         <v>12</v>
       </c>
       <c r="G2049" t="n">
-        <v>11.7952156066895</v>
+        <v>11.7952146530151</v>
       </c>
       <c r="H2049" t="n">
         <v>47703</v>
@@ -59819,7 +59819,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G2050" t="n">
-        <v>11.5887994766235</v>
+        <v>11.5887985229492</v>
       </c>
       <c r="H2050" t="n">
         <v>56560</v>
@@ -59848,7 +59848,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2051" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H2051" t="n">
         <v>39050</v>
@@ -59935,7 +59935,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G2054" t="n">
-        <v>12.0802659988403</v>
+        <v>12.0802669525146</v>
       </c>
       <c r="H2054" t="n">
         <v>81294</v>
@@ -60138,7 +60138,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2061" t="n">
-        <v>11.7264108657837</v>
+        <v>11.7264099121094</v>
       </c>
       <c r="H2061" t="n">
         <v>60902</v>
@@ -60167,7 +60167,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G2062" t="n">
-        <v>11.7264108657837</v>
+        <v>11.7264099121094</v>
       </c>
       <c r="H2062" t="n">
         <v>68363</v>
@@ -60225,7 +60225,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G2064" t="n">
-        <v>11.706750869751</v>
+        <v>11.7067518234253</v>
       </c>
       <c r="H2064" t="n">
         <v>37008</v>
@@ -60283,7 +60283,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2066" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H2066" t="n">
         <v>86522</v>
@@ -60341,7 +60341,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G2068" t="n">
-        <v>11.7460689544678</v>
+        <v>11.7460680007935</v>
       </c>
       <c r="H2068" t="n">
         <v>32303</v>
@@ -60631,7 +60631,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G2078" t="n">
-        <v>12.2768526077271</v>
+        <v>12.2768535614014</v>
       </c>
       <c r="H2078" t="n">
         <v>81249</v>
@@ -60660,7 +60660,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2079" t="n">
-        <v>11.9524850845337</v>
+        <v>11.9524841308594</v>
       </c>
       <c r="H2079" t="n">
         <v>106131</v>
@@ -60718,7 +60718,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2081" t="n">
-        <v>11.8345336914062</v>
+        <v>11.8345327377319</v>
       </c>
       <c r="H2081" t="n">
         <v>232407</v>
@@ -60805,7 +60805,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2084" t="n">
-        <v>11.5396518707275</v>
+        <v>11.5396528244019</v>
       </c>
       <c r="H2084" t="n">
         <v>37347</v>
@@ -60921,7 +60921,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G2088" t="n">
-        <v>11.5298233032227</v>
+        <v>11.5298223495483</v>
       </c>
       <c r="H2088" t="n">
         <v>46352</v>
@@ -60979,7 +60979,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2090" t="n">
-        <v>10.9695501327515</v>
+        <v>10.9695510864258</v>
       </c>
       <c r="H2090" t="n">
         <v>236266</v>
@@ -61008,7 +61008,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G2091" t="n">
-        <v>11.1563091278076</v>
+        <v>11.1563081741333</v>
       </c>
       <c r="H2091" t="n">
         <v>137660</v>
@@ -61037,7 +61037,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G2092" t="n">
-        <v>11.2152843475342</v>
+        <v>11.2152833938599</v>
       </c>
       <c r="H2092" t="n">
         <v>73117</v>
@@ -61095,7 +61095,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G2094" t="n">
-        <v>11.4315299987793</v>
+        <v>11.431529045105</v>
       </c>
       <c r="H2094" t="n">
         <v>86868</v>
@@ -61182,7 +61182,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2097" t="n">
-        <v>12.2080488204956</v>
+        <v>12.2080478668213</v>
       </c>
       <c r="H2097" t="n">
         <v>142973</v>
@@ -61211,7 +61211,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2098" t="n">
-        <v>12.1687307357788</v>
+        <v>12.1687316894531</v>
       </c>
       <c r="H2098" t="n">
         <v>68322</v>
@@ -61269,7 +61269,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2100" t="n">
-        <v>11.8935098648071</v>
+        <v>11.8935089111328</v>
       </c>
       <c r="H2100" t="n">
         <v>178736</v>
@@ -61530,7 +61530,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G2109" t="n">
-        <v>11.5986280441284</v>
+        <v>11.5986289978027</v>
       </c>
       <c r="H2109" t="n">
         <v>46564</v>
@@ -61559,7 +61559,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G2110" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H2110" t="n">
         <v>41342</v>
@@ -61588,7 +61588,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2111" t="n">
-        <v>11.3430652618408</v>
+        <v>11.3430662155151</v>
       </c>
       <c r="H2111" t="n">
         <v>44459</v>
@@ -61617,7 +61617,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G2112" t="n">
-        <v>11.3725538253784</v>
+        <v>11.3725528717041</v>
       </c>
       <c r="H2112" t="n">
         <v>65930</v>
@@ -61733,7 +61733,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G2116" t="n">
-        <v>11.5396518707275</v>
+        <v>11.5396528244019</v>
       </c>
       <c r="H2116" t="n">
         <v>45312</v>
@@ -61791,7 +61791,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2118" t="n">
-        <v>11.3430652618408</v>
+        <v>11.3430662155151</v>
       </c>
       <c r="H2118" t="n">
         <v>31523</v>
@@ -61820,7 +61820,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2119" t="n">
-        <v>11.8738508224487</v>
+        <v>11.8738498687744</v>
       </c>
       <c r="H2119" t="n">
         <v>62356</v>
@@ -79980,6 +79980,35 @@
         <v>50070</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>4.42000007629395</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>4.44500017166138</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>4.34999990463257</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>105918</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G3" t="n">
-        <v>12.978798866272</v>
+        <v>12.9787998199463</v>
       </c>
       <c r="H3" t="n">
         <v>55009</v>
@@ -485,7 +485,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>12.978798866272</v>
+        <v>12.9787998199463</v>
       </c>
       <c r="H4" t="n">
         <v>53738</v>
@@ -514,7 +514,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G5" t="n">
-        <v>12.7479524612427</v>
+        <v>12.7479515075684</v>
       </c>
       <c r="H5" t="n">
         <v>96757</v>
@@ -601,7 +601,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>12.2606048583984</v>
+        <v>12.2606058120728</v>
       </c>
       <c r="H8" t="n">
         <v>54531</v>
@@ -659,7 +659,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4825630187988</v>
+        <v>11.4825611114502</v>
       </c>
       <c r="H10" t="n">
         <v>137481</v>
@@ -717,7 +717,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>9.79822540283203</v>
+        <v>9.79822444915771</v>
       </c>
       <c r="H12" t="n">
         <v>322059</v>
@@ -746,7 +746,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3539695739746</v>
+        <v>10.3539705276489</v>
       </c>
       <c r="H13" t="n">
         <v>237289</v>
@@ -833,7 +833,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941198348999</v>
+        <v>10.2941207885742</v>
       </c>
       <c r="H16" t="n">
         <v>136366</v>
@@ -891,7 +891,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156652450562</v>
       </c>
       <c r="H18" t="n">
         <v>109866</v>
@@ -920,7 +920,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>10.7301664352417</v>
+        <v>10.730167388916</v>
       </c>
       <c r="H19" t="n">
         <v>71825</v>
@@ -978,7 +978,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361169815063</v>
+        <v>10.6361179351807</v>
       </c>
       <c r="H21" t="n">
         <v>72208</v>
@@ -1007,7 +1007,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8156661987305</v>
+        <v>10.8156652450562</v>
       </c>
       <c r="H22" t="n">
         <v>43477</v>
@@ -1036,7 +1036,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.191520690918</v>
+        <v>10.1915216445923</v>
       </c>
       <c r="H23" t="n">
         <v>90616</v>
@@ -1065,7 +1065,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4565696716309</v>
+        <v>10.4565687179565</v>
       </c>
       <c r="H24" t="n">
         <v>157219</v>
@@ -1094,7 +1094,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907693862915</v>
+        <v>10.4907703399658</v>
       </c>
       <c r="H25" t="n">
         <v>150192</v>
@@ -1123,7 +1123,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0205230712891</v>
+        <v>10.0205221176147</v>
       </c>
       <c r="H26" t="n">
         <v>55946</v>
@@ -1152,7 +1152,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03728008270264</v>
+        <v>9.03727912902832</v>
       </c>
       <c r="H27" t="n">
         <v>127617</v>
@@ -1181,7 +1181,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743034362793</v>
+        <v>8.97743129730225</v>
       </c>
       <c r="H28" t="n">
         <v>172224</v>
@@ -1210,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9.40492725372314</v>
+        <v>9.40492820739746</v>
       </c>
       <c r="H29" t="n">
         <v>104278</v>
@@ -1239,7 +1239,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842891693115</v>
+        <v>9.14842987060547</v>
       </c>
       <c r="H30" t="n">
         <v>114215</v>
@@ -1268,7 +1268,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057537078857</v>
+        <v>9.43057727813721</v>
       </c>
       <c r="H31" t="n">
         <v>72178</v>
@@ -1297,7 +1297,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082359313965</v>
+        <v>9.90082454681396</v>
       </c>
       <c r="H32" t="n">
         <v>70762</v>
@@ -1326,7 +1326,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142654418945</v>
+        <v>9.66142463684082</v>
       </c>
       <c r="H33" t="n">
         <v>39366</v>
@@ -1355,7 +1355,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G34" t="n">
-        <v>10.4394693374634</v>
+        <v>10.4394702911377</v>
       </c>
       <c r="H34" t="n">
         <v>73399</v>
@@ -1384,7 +1384,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3454208374023</v>
+        <v>10.3454217910767</v>
       </c>
       <c r="H35" t="n">
         <v>81482</v>
@@ -1442,7 +1442,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0037660598755</v>
+        <v>11.0037641525269</v>
       </c>
       <c r="H37" t="n">
         <v>86253</v>
@@ -1471,7 +1471,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506181716919</v>
+        <v>10.5506191253662</v>
       </c>
       <c r="H38" t="n">
         <v>97952</v>
@@ -1500,7 +1500,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257194519043</v>
+        <v>10.2257204055786</v>
       </c>
       <c r="H39" t="n">
         <v>73018</v>
@@ -1558,7 +1558,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0379648208618</v>
+        <v>11.0379638671875</v>
       </c>
       <c r="H41" t="n">
         <v>191057</v>
@@ -1587,7 +1587,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097166061401</v>
+        <v>10.9097156524658</v>
       </c>
       <c r="H42" t="n">
         <v>105720</v>
@@ -1616,7 +1616,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8074598312378</v>
+        <v>11.8074588775635</v>
       </c>
       <c r="H43" t="n">
         <v>146558</v>
@@ -1645,7 +1645,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442586898804</v>
+        <v>11.9442567825317</v>
       </c>
       <c r="H44" t="n">
         <v>175966</v>
@@ -1906,7 +1906,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.9186086654663</v>
+        <v>11.9186067581177</v>
       </c>
       <c r="H53" t="n">
         <v>56813</v>
@@ -1993,7 +1993,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922054290771</v>
+        <v>12.1922063827515</v>
       </c>
       <c r="H56" t="n">
         <v>88317</v>
@@ -2051,7 +2051,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375558853149</v>
+        <v>12.3375549316406</v>
       </c>
       <c r="H58" t="n">
         <v>61525</v>
@@ -2196,7 +2196,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178554534912</v>
+        <v>12.2178564071655</v>
       </c>
       <c r="H63" t="n">
         <v>42659</v>
@@ -2225,7 +2225,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>11.9015083312988</v>
+        <v>11.9015092849731</v>
       </c>
       <c r="H64" t="n">
         <v>46495</v>
@@ -2312,7 +2312,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.568060874939</v>
+        <v>11.5680599212646</v>
       </c>
       <c r="H67" t="n">
         <v>44037</v>
@@ -2341,7 +2341,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.2859134674072</v>
+        <v>11.2859125137329</v>
       </c>
       <c r="H68" t="n">
         <v>33579</v>
@@ -2428,7 +2428,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.568060874939</v>
+        <v>11.5680599212646</v>
       </c>
       <c r="H71" t="n">
         <v>41497</v>
@@ -2544,7 +2544,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G75" t="n">
-        <v>11.6022605895996</v>
+        <v>11.6022596359253</v>
       </c>
       <c r="H75" t="n">
         <v>40113</v>
@@ -2602,7 +2602,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364593505859</v>
+        <v>11.6364612579346</v>
       </c>
       <c r="H77" t="n">
         <v>21274</v>
@@ -2631,7 +2631,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G78" t="n">
-        <v>11.4740114212036</v>
+        <v>11.4740123748779</v>
       </c>
       <c r="H78" t="n">
         <v>51888</v>
@@ -2660,7 +2660,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918659210205</v>
+        <v>11.1918630599976</v>
       </c>
       <c r="H79" t="n">
         <v>107247</v>
@@ -2689,7 +2689,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G80" t="n">
-        <v>11.1063652038574</v>
+        <v>11.1063642501831</v>
       </c>
       <c r="H80" t="n">
         <v>44115</v>
@@ -2718,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.114914894104</v>
+        <v>11.1149129867554</v>
       </c>
       <c r="H81" t="n">
         <v>44600</v>
@@ -2834,7 +2834,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1576642990112</v>
+        <v>11.1576633453369</v>
       </c>
       <c r="H85" t="n">
         <v>20515</v>
@@ -2863,7 +2863,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.0550661087036</v>
+        <v>11.055064201355</v>
       </c>
       <c r="H86" t="n">
         <v>64749</v>
@@ -2921,7 +2921,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1405649185181</v>
+        <v>11.1405639648438</v>
       </c>
       <c r="H88" t="n">
         <v>30374</v>
@@ -2979,7 +2979,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9541416168213</v>
+        <v>10.954140663147</v>
       </c>
       <c r="H90" t="n">
         <v>55438</v>
@@ -3008,7 +3008,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.4346132278442</v>
+        <v>10.4346122741699</v>
       </c>
       <c r="H91" t="n">
         <v>102250</v>
@@ -3066,7 +3066,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>10.4346132278442</v>
+        <v>10.4346122741699</v>
       </c>
       <c r="H93" t="n">
         <v>49691</v>
@@ -3153,7 +3153,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92389011383057</v>
+        <v>9.92388820648193</v>
       </c>
       <c r="H96" t="n">
         <v>101148</v>
@@ -3211,7 +3211,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G98" t="n">
-        <v>10.0031385421753</v>
+        <v>10.003137588501</v>
       </c>
       <c r="H98" t="n">
         <v>56636</v>
@@ -3240,7 +3240,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.302526473999</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H99" t="n">
         <v>48962</v>
@@ -3269,7 +3269,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496938705444</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H100" t="n">
         <v>39045</v>
@@ -3298,7 +3298,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>10.6107225418091</v>
+        <v>10.6107234954834</v>
       </c>
       <c r="H101" t="n">
         <v>49594</v>
@@ -3327,7 +3327,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120321273804</v>
+        <v>11.4120330810547</v>
       </c>
       <c r="H102" t="n">
         <v>156693</v>
@@ -3356,7 +3356,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302518844604</v>
       </c>
       <c r="H103" t="n">
         <v>70319</v>
@@ -3385,7 +3385,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189176559448</v>
+        <v>10.9189186096191</v>
       </c>
       <c r="H104" t="n">
         <v>30153</v>
@@ -3472,7 +3472,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302518844604</v>
       </c>
       <c r="H107" t="n">
         <v>63256</v>
@@ -3559,7 +3559,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396682739258</v>
+        <v>10.8396701812744</v>
       </c>
       <c r="H110" t="n">
         <v>35136</v>
@@ -3617,7 +3617,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G112" t="n">
-        <v>10.9101123809814</v>
+        <v>10.9101133346558</v>
       </c>
       <c r="H112" t="n">
         <v>37578</v>
@@ -3704,7 +3704,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647783279419</v>
+        <v>10.0647773742676</v>
       </c>
       <c r="H115" t="n">
         <v>60966</v>
@@ -3791,7 +3791,7 @@
         <v>11</v>
       </c>
       <c r="G118" t="n">
-        <v>9.68613910675049</v>
+        <v>9.68613815307617</v>
       </c>
       <c r="H118" t="n">
         <v>96012</v>
@@ -3849,7 +3849,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962511062622</v>
+        <v>10.4962501525879</v>
       </c>
       <c r="H120" t="n">
         <v>43223</v>
@@ -3907,7 +3907,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522218704224</v>
+        <v>10.4522228240967</v>
       </c>
       <c r="H122" t="n">
         <v>40375</v>
@@ -3936,7 +3936,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843076705933</v>
+        <v>10.5843067169189</v>
       </c>
       <c r="H123" t="n">
         <v>36459</v>
@@ -3965,7 +3965,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G124" t="n">
-        <v>9.87986087799072</v>
+        <v>9.87985992431641</v>
       </c>
       <c r="H124" t="n">
         <v>94289</v>
@@ -3994,7 +3994,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G125" t="n">
-        <v>9.12258052825928</v>
+        <v>9.12257957458496</v>
       </c>
       <c r="H125" t="n">
         <v>55022</v>
@@ -4023,7 +4023,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733097076416</v>
+        <v>9.67733192443848</v>
       </c>
       <c r="H126" t="n">
         <v>56824</v>
@@ -4110,7 +4110,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1880559921265</v>
+        <v>10.1880550384521</v>
       </c>
       <c r="H129" t="n">
         <v>25733</v>
@@ -4168,7 +4168,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>9.68613910675049</v>
+        <v>9.68613815307617</v>
       </c>
       <c r="H131" t="n">
         <v>15874</v>
@@ -4197,7 +4197,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.18421840667725</v>
+        <v>9.1842212677002</v>
       </c>
       <c r="H132" t="n">
         <v>96061</v>
@@ -4226,7 +4226,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019012451172</v>
+        <v>9.14019203186035</v>
       </c>
       <c r="H133" t="n">
         <v>64369</v>
@@ -4284,7 +4284,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0823888778687</v>
+        <v>10.0823879241943</v>
       </c>
       <c r="H135" t="n">
         <v>34424</v>
@@ -4313,7 +4313,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G136" t="n">
-        <v>10.3817777633667</v>
+        <v>10.381778717041</v>
       </c>
       <c r="H136" t="n">
         <v>45362</v>
@@ -4371,7 +4371,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>10.2849178314209</v>
+        <v>10.2849168777466</v>
       </c>
       <c r="H138" t="n">
         <v>15768</v>
@@ -4429,7 +4429,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>10.2144718170166</v>
+        <v>10.2144727706909</v>
       </c>
       <c r="H140" t="n">
         <v>22528</v>
@@ -4458,7 +4458,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1528339385986</v>
+        <v>10.15283203125</v>
       </c>
       <c r="H141" t="n">
         <v>23520</v>
@@ -4487,7 +4487,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496938705444</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H142" t="n">
         <v>53624</v>
@@ -4516,7 +4516,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496938705444</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H143" t="n">
         <v>15986</v>
@@ -4574,7 +4574,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.302526473999</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H145" t="n">
         <v>26846</v>
@@ -4690,7 +4690,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>11.033390045166</v>
+        <v>11.0333909988403</v>
       </c>
       <c r="H149" t="n">
         <v>32061</v>
@@ -4719,7 +4719,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>11.033390045166</v>
+        <v>11.0333909988403</v>
       </c>
       <c r="H150" t="n">
         <v>31452</v>
@@ -4806,7 +4806,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748922348022</v>
+        <v>10.8748912811279</v>
       </c>
       <c r="H153" t="n">
         <v>39269</v>
@@ -4835,7 +4835,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748922348022</v>
+        <v>10.8748912811279</v>
       </c>
       <c r="H154" t="n">
         <v>23378</v>
@@ -4893,7 +4893,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.0950288772583</v>
+        <v>11.0950298309326</v>
       </c>
       <c r="H156" t="n">
         <v>40839</v>
@@ -5038,7 +5038,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7251977920532</v>
+        <v>10.7251958847046</v>
       </c>
       <c r="H161" t="n">
         <v>58715</v>
@@ -5096,7 +5096,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>10.9013080596924</v>
+        <v>10.9013071060181</v>
       </c>
       <c r="H163" t="n">
         <v>12830</v>
@@ -5125,7 +5125,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654748916626</v>
+        <v>11.1654739379883</v>
       </c>
       <c r="H164" t="n">
         <v>19684</v>
@@ -5154,7 +5154,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G165" t="n">
-        <v>11.0598087310791</v>
+        <v>11.0598077774048</v>
       </c>
       <c r="H165" t="n">
         <v>40339</v>
@@ -5183,7 +5183,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G166" t="n">
-        <v>11.2183074951172</v>
+        <v>11.2183084487915</v>
       </c>
       <c r="H166" t="n">
         <v>21084</v>
@@ -5212,7 +5212,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G167" t="n">
-        <v>11.1214475631714</v>
+        <v>11.1214466094971</v>
       </c>
       <c r="H167" t="n">
         <v>45450</v>
@@ -5270,7 +5270,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302518844604</v>
       </c>
       <c r="H169" t="n">
         <v>50121</v>
@@ -5328,7 +5328,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G171" t="n">
-        <v>11.2623357772827</v>
+        <v>11.262336730957</v>
       </c>
       <c r="H171" t="n">
         <v>27441</v>
@@ -5415,7 +5415,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G174" t="n">
-        <v>11.773060798645</v>
+        <v>11.7730598449707</v>
       </c>
       <c r="H174" t="n">
         <v>30007</v>
@@ -5473,7 +5473,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.7994766235352</v>
+        <v>11.7994775772095</v>
       </c>
       <c r="H176" t="n">
         <v>51577</v>
@@ -5531,7 +5531,7 @@
         <v>13.25</v>
       </c>
       <c r="G178" t="n">
-        <v>11.6673946380615</v>
+        <v>11.6673936843872</v>
       </c>
       <c r="H178" t="n">
         <v>36341</v>
@@ -5589,7 +5589,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H180" t="n">
         <v>64823</v>
@@ -5647,7 +5647,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680028915405</v>
+        <v>11.3680038452148</v>
       </c>
       <c r="H182" t="n">
         <v>62143</v>
@@ -5676,7 +5676,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>11.1390562057495</v>
+        <v>11.1390590667725</v>
       </c>
       <c r="H183" t="n">
         <v>30268</v>
@@ -5734,7 +5734,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H185" t="n">
         <v>43283</v>
@@ -5763,7 +5763,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G186" t="n">
-        <v>11.614559173584</v>
+        <v>11.6145582199097</v>
       </c>
       <c r="H186" t="n">
         <v>25730</v>
@@ -5792,7 +5792,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G187" t="n">
-        <v>11.8258943557739</v>
+        <v>11.8258934020996</v>
       </c>
       <c r="H187" t="n">
         <v>136773</v>
@@ -5821,7 +5821,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G188" t="n">
-        <v>12.0372266769409</v>
+        <v>12.0372276306152</v>
       </c>
       <c r="H188" t="n">
         <v>83675</v>
@@ -5850,7 +5850,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>12.054838180542</v>
+        <v>12.0548372268677</v>
       </c>
       <c r="H189" t="n">
         <v>61757</v>
@@ -5879,7 +5879,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.063645362854</v>
+        <v>12.0636425018311</v>
       </c>
       <c r="H190" t="n">
         <v>38989</v>
@@ -5908,7 +5908,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>12.5039234161377</v>
+        <v>12.5039224624634</v>
       </c>
       <c r="H191" t="n">
         <v>102776</v>
@@ -5937,7 +5937,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303392410278</v>
+        <v>12.5303401947021</v>
       </c>
       <c r="H192" t="n">
         <v>109655</v>
@@ -5966,7 +5966,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070606231689</v>
+        <v>12.4070615768433</v>
       </c>
       <c r="H193" t="n">
         <v>92196</v>
@@ -5995,7 +5995,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837829589844</v>
+        <v>12.2837820053101</v>
       </c>
       <c r="H194" t="n">
         <v>42892</v>
@@ -6024,7 +6024,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G195" t="n">
-        <v>12.6007862091064</v>
+        <v>12.6007852554321</v>
       </c>
       <c r="H195" t="n">
         <v>62641</v>
@@ -6053,7 +6053,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>12.9177856445312</v>
+        <v>12.9177865982056</v>
       </c>
       <c r="H196" t="n">
         <v>155030</v>
@@ -6082,7 +6082,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8121194839478</v>
+        <v>12.8121185302734</v>
       </c>
       <c r="H197" t="n">
         <v>94007</v>
@@ -6111,7 +6111,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>12.8561477661133</v>
+        <v>12.856146812439</v>
       </c>
       <c r="H198" t="n">
         <v>56736</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>13.0322580337524</v>
+        <v>13.0322570800781</v>
       </c>
       <c r="H199" t="n">
         <v>85136</v>
@@ -6169,7 +6169,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>13.4108963012695</v>
+        <v>13.4108972549438</v>
       </c>
       <c r="H200" t="n">
         <v>211127</v>
@@ -6256,7 +6256,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285097122192</v>
+        <v>13.4285087585449</v>
       </c>
       <c r="H203" t="n">
         <v>304187</v>
@@ -6285,7 +6285,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>14.3707065582275</v>
+        <v>14.3707046508789</v>
       </c>
       <c r="H204" t="n">
         <v>401338</v>
@@ -6314,7 +6314,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210111618042</v>
+        <v>14.2210092544556</v>
       </c>
       <c r="H205" t="n">
         <v>191135</v>
@@ -6401,7 +6401,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241493225098</v>
+        <v>14.1241512298584</v>
       </c>
       <c r="H208" t="n">
         <v>50427</v>
@@ -6517,7 +6517,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>13.6046209335327</v>
+        <v>13.6046199798584</v>
       </c>
       <c r="H212" t="n">
         <v>48829</v>
@@ -6575,7 +6575,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G214" t="n">
-        <v>13.8335666656494</v>
+        <v>13.8335647583008</v>
       </c>
       <c r="H214" t="n">
         <v>23394</v>
@@ -6604,7 +6604,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7278995513916</v>
+        <v>13.7278985977173</v>
       </c>
       <c r="H215" t="n">
         <v>17418</v>
@@ -6691,7 +6691,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>13.1555337905884</v>
+        <v>13.155535697937</v>
       </c>
       <c r="H218" t="n">
         <v>60112</v>
@@ -6720,7 +6720,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486492156982</v>
+        <v>13.6486482620239</v>
       </c>
       <c r="H219" t="n">
         <v>47806</v>
@@ -6749,7 +6749,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605926513672</v>
+        <v>13.5605916976929</v>
       </c>
       <c r="H220" t="n">
         <v>47022</v>
@@ -6778,7 +6778,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285097122192</v>
+        <v>13.4285087585449</v>
       </c>
       <c r="H221" t="n">
         <v>144794</v>
@@ -6865,7 +6865,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>14.1769828796387</v>
+        <v>14.176983833313</v>
       </c>
       <c r="H224" t="n">
         <v>125262</v>
@@ -6894,7 +6894,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>14.0977334976196</v>
+        <v>14.0977325439453</v>
       </c>
       <c r="H225" t="n">
         <v>147489</v>
@@ -6952,7 +6952,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040952682495</v>
+        <v>15.3040971755981</v>
       </c>
       <c r="H227" t="n">
         <v>258275</v>
@@ -6981,7 +6981,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.2776794433594</v>
+        <v>15.277681350708</v>
       </c>
       <c r="H228" t="n">
         <v>398968</v>
@@ -7010,7 +7010,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G229" t="n">
-        <v>15.489013671875</v>
+        <v>15.4890155792236</v>
       </c>
       <c r="H229" t="n">
         <v>247524</v>
@@ -7039,7 +7039,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.497820854187</v>
+        <v>15.4978218078613</v>
       </c>
       <c r="H230" t="n">
         <v>289822</v>
@@ -7068,7 +7068,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657369613647</v>
+        <v>15.3657360076904</v>
       </c>
       <c r="H231" t="n">
         <v>110362</v>
@@ -7097,7 +7097,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G232" t="n">
-        <v>15.4449863433838</v>
+        <v>15.4449872970581</v>
       </c>
       <c r="H232" t="n">
         <v>68856</v>
@@ -7126,7 +7126,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3393201828003</v>
+        <v>15.3393173217773</v>
       </c>
       <c r="H233" t="n">
         <v>71686</v>
@@ -7155,7 +7155,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5330419540405</v>
+        <v>15.5330438613892</v>
       </c>
       <c r="H234" t="n">
         <v>122396</v>
@@ -7213,7 +7213,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418491363525</v>
+        <v>15.5418472290039</v>
       </c>
       <c r="H236" t="n">
         <v>99490</v>
@@ -7271,7 +7271,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.2776794433594</v>
+        <v>15.277681350708</v>
       </c>
       <c r="H238" t="n">
         <v>97203</v>
@@ -7300,7 +7300,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>15.8060159683228</v>
+        <v>15.8060169219971</v>
       </c>
       <c r="H239" t="n">
         <v>125335</v>
@@ -7358,7 +7358,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G241" t="n">
-        <v>16.3695735931396</v>
+        <v>16.3695755004883</v>
       </c>
       <c r="H241" t="n">
         <v>106538</v>
@@ -7474,7 +7474,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H245" t="n">
         <v>177039</v>
@@ -7503,7 +7503,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.8891010284424</v>
+        <v>16.889102935791</v>
       </c>
       <c r="H246" t="n">
         <v>240701</v>
@@ -7590,7 +7590,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>16.5544910430908</v>
+        <v>16.5544891357422</v>
       </c>
       <c r="H249" t="n">
         <v>545131</v>
@@ -7619,7 +7619,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>16.2374897003174</v>
+        <v>16.2374877929688</v>
       </c>
       <c r="H250" t="n">
         <v>353155</v>
@@ -7648,7 +7648,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G251" t="n">
-        <v>16.5897121429443</v>
+        <v>16.589714050293</v>
       </c>
       <c r="H251" t="n">
         <v>110433</v>
@@ -7677,7 +7677,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G252" t="n">
-        <v>16.6513519287109</v>
+        <v>16.6513481140137</v>
       </c>
       <c r="H252" t="n">
         <v>93094</v>
@@ -7735,7 +7735,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947681427002</v>
+        <v>16.9947662353516</v>
       </c>
       <c r="H254" t="n">
         <v>161135</v>
@@ -7793,7 +7793,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.8802947998047</v>
+        <v>16.8802928924561</v>
       </c>
       <c r="H256" t="n">
         <v>74391</v>
@@ -7822,7 +7822,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538780212402</v>
+        <v>16.8538818359375</v>
       </c>
       <c r="H257" t="n">
         <v>23740</v>
@@ -7851,7 +7851,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.0123825073242</v>
+        <v>17.012378692627</v>
       </c>
       <c r="H258" t="n">
         <v>25398</v>
@@ -7967,7 +7967,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H262" t="n">
         <v>26170</v>
@@ -7996,7 +7996,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G263" t="n">
-        <v>16.5368785858154</v>
+        <v>16.5368766784668</v>
       </c>
       <c r="H263" t="n">
         <v>65318</v>
@@ -8025,7 +8025,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>17.0828247070312</v>
+        <v>17.0828266143799</v>
       </c>
       <c r="H264" t="n">
         <v>180948</v>
@@ -8054,7 +8054,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>16.8626823425293</v>
+        <v>16.8626842498779</v>
       </c>
       <c r="H265" t="n">
         <v>51846</v>
@@ -8170,7 +8170,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>17.5407161712646</v>
+        <v>17.540714263916</v>
       </c>
       <c r="H269" t="n">
         <v>197725</v>
@@ -8228,7 +8228,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G271" t="n">
-        <v>17.7168273925781</v>
+        <v>17.7168254852295</v>
       </c>
       <c r="H271" t="n">
         <v>75032</v>
@@ -8257,7 +8257,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G272" t="n">
-        <v>17.4526596069336</v>
+        <v>17.4526557922363</v>
       </c>
       <c r="H272" t="n">
         <v>52750</v>
@@ -8315,7 +8315,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432422637939</v>
+        <v>17.7432441711426</v>
       </c>
       <c r="H274" t="n">
         <v>80664</v>
@@ -8431,7 +8431,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482147216797</v>
+        <v>16.7482128143311</v>
       </c>
       <c r="H278" t="n">
         <v>113676</v>
@@ -8460,7 +8460,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G279" t="n">
-        <v>16.7658252716064</v>
+        <v>16.7658233642578</v>
       </c>
       <c r="H279" t="n">
         <v>82633</v>
@@ -8489,7 +8489,7 @@
         <v>19.25</v>
       </c>
       <c r="G280" t="n">
-        <v>16.9507369995117</v>
+        <v>16.950740814209</v>
       </c>
       <c r="H280" t="n">
         <v>60029</v>
@@ -8518,7 +8518,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G281" t="n">
-        <v>17.162073135376</v>
+        <v>17.1620750427246</v>
       </c>
       <c r="H281" t="n">
         <v>28651</v>
@@ -8547,7 +8547,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G282" t="n">
-        <v>17.2765502929688</v>
+        <v>17.2765483856201</v>
       </c>
       <c r="H282" t="n">
         <v>41713</v>
@@ -8576,7 +8576,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>16.6865730285645</v>
+        <v>16.6865749359131</v>
       </c>
       <c r="H283" t="n">
         <v>41016</v>
@@ -8634,7 +8634,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>16.8626823425293</v>
+        <v>16.8626842498779</v>
       </c>
       <c r="H285" t="n">
         <v>37497</v>
@@ -8663,7 +8663,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.8891010284424</v>
+        <v>16.889102935791</v>
       </c>
       <c r="H286" t="n">
         <v>33722</v>
@@ -8721,7 +8721,7 @@
         <v>19.25</v>
       </c>
       <c r="G288" t="n">
-        <v>16.9507369995117</v>
+        <v>16.950740814209</v>
       </c>
       <c r="H288" t="n">
         <v>47872</v>
@@ -8750,7 +8750,7 @@
         <v>19.25</v>
       </c>
       <c r="G289" t="n">
-        <v>16.9507369995117</v>
+        <v>16.950740814209</v>
       </c>
       <c r="H289" t="n">
         <v>32145</v>
@@ -8808,7 +8808,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>17.0828247070312</v>
+        <v>17.0828266143799</v>
       </c>
       <c r="H291" t="n">
         <v>122243</v>
@@ -8866,7 +8866,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.391019821167</v>
+        <v>17.3910217285156</v>
       </c>
       <c r="H293" t="n">
         <v>29528</v>
@@ -8953,7 +8953,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2501316070557</v>
+        <v>17.250129699707</v>
       </c>
       <c r="H296" t="n">
         <v>53304</v>
@@ -8982,7 +8982,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350471496582</v>
+        <v>17.4350452423096</v>
       </c>
       <c r="H297" t="n">
         <v>105130</v>
@@ -9011,7 +9011,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734092712402</v>
+        <v>17.3734073638916</v>
       </c>
       <c r="H298" t="n">
         <v>48083</v>
@@ -9040,7 +9040,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G299" t="n">
-        <v>17.6463813781738</v>
+        <v>17.6463832855225</v>
       </c>
       <c r="H299" t="n">
         <v>74706</v>
@@ -9069,7 +9069,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>17.9457702636719</v>
+        <v>17.9457721710205</v>
       </c>
       <c r="H300" t="n">
         <v>68868</v>
@@ -9098,7 +9098,7 @@
         <v>22</v>
       </c>
       <c r="G301" t="n">
-        <v>19.372278213501</v>
+        <v>19.3722763061523</v>
       </c>
       <c r="H301" t="n">
         <v>221346</v>
@@ -9185,7 +9185,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962505340576</v>
+        <v>20.5962524414062</v>
       </c>
       <c r="H304" t="n">
         <v>71698</v>
@@ -9214,7 +9214,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>20.3408889770508</v>
+        <v>20.3408908843994</v>
       </c>
       <c r="H305" t="n">
         <v>87911</v>
@@ -9243,7 +9243,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8340034484863</v>
+        <v>20.8339996337891</v>
       </c>
       <c r="H306" t="n">
         <v>87962</v>
@@ -9272,7 +9272,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>21.0453357696533</v>
+        <v>21.045337677002</v>
       </c>
       <c r="H307" t="n">
         <v>88135</v>
@@ -9301,7 +9301,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824737548828</v>
+        <v>21.5824775695801</v>
       </c>
       <c r="H308" t="n">
         <v>115604</v>
@@ -9330,7 +9330,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>21.0893630981445</v>
+        <v>21.0893611907959</v>
       </c>
       <c r="H309" t="n">
         <v>116636</v>
@@ -9359,7 +9359,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>21.3271160125732</v>
+        <v>21.3271141052246</v>
       </c>
       <c r="H310" t="n">
         <v>59333</v>
@@ -9388,7 +9388,7 @@
         <v>24.5900001525879</v>
       </c>
       <c r="G311" t="n">
-        <v>21.6529178619385</v>
+        <v>21.6529216766357</v>
       </c>
       <c r="H311" t="n">
         <v>78484</v>
@@ -9417,7 +9417,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497844696045</v>
+        <v>21.7497825622559</v>
       </c>
       <c r="H312" t="n">
         <v>78215</v>
@@ -9475,7 +9475,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>21.8114223480225</v>
+        <v>21.8114204406738</v>
       </c>
       <c r="H314" t="n">
         <v>83092</v>
@@ -9533,7 +9533,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.286922454834</v>
+        <v>22.2869205474854</v>
       </c>
       <c r="H316" t="n">
         <v>115542</v>
@@ -9562,7 +9562,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605075836182</v>
+        <v>22.2605037689209</v>
       </c>
       <c r="H317" t="n">
         <v>83792</v>
@@ -9591,7 +9591,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G318" t="n">
-        <v>22.348560333252</v>
+        <v>22.3485584259033</v>
       </c>
       <c r="H318" t="n">
         <v>54563</v>
@@ -9620,7 +9620,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221454620361</v>
+        <v>22.3221473693848</v>
       </c>
       <c r="H319" t="n">
         <v>60853</v>
@@ -9649,7 +9649,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>22.1900577545166</v>
+        <v>22.1900596618652</v>
       </c>
       <c r="H320" t="n">
         <v>84678</v>
@@ -9707,7 +9707,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>22.4366149902344</v>
+        <v>22.436616897583</v>
       </c>
       <c r="H322" t="n">
         <v>60620</v>
@@ -9736,7 +9736,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G323" t="n">
-        <v>22.4806461334229</v>
+        <v>22.4806480407715</v>
       </c>
       <c r="H323" t="n">
         <v>98956</v>
@@ -9765,7 +9765,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G324" t="n">
-        <v>22.665563583374</v>
+        <v>22.6655616760254</v>
       </c>
       <c r="H324" t="n">
         <v>95912</v>
@@ -9794,7 +9794,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G325" t="n">
-        <v>22.4806461334229</v>
+        <v>22.4806480407715</v>
       </c>
       <c r="H325" t="n">
         <v>36599</v>
@@ -9852,7 +9852,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743679046631</v>
+        <v>22.6743659973145</v>
       </c>
       <c r="H327" t="n">
         <v>33968</v>
@@ -9881,7 +9881,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945064544678</v>
+        <v>22.8945083618164</v>
       </c>
       <c r="H328" t="n">
         <v>89327</v>
@@ -10113,7 +10113,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G336" t="n">
-        <v>23.9159526824951</v>
+        <v>23.9159545898438</v>
       </c>
       <c r="H336" t="n">
         <v>100966</v>
@@ -10142,7 +10142,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417621612549</v>
+        <v>24.2417640686035</v>
       </c>
       <c r="H337" t="n">
         <v>94347</v>
@@ -10200,7 +10200,7 @@
         <v>28</v>
       </c>
       <c r="G339" t="n">
-        <v>24.6556243896484</v>
+        <v>24.6556205749512</v>
       </c>
       <c r="H339" t="n">
         <v>63031</v>
@@ -10229,7 +10229,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.9197883605957</v>
+        <v>24.919792175293</v>
       </c>
       <c r="H340" t="n">
         <v>76611</v>
@@ -10258,7 +10258,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870971679688</v>
+        <v>25.0870933532715</v>
       </c>
       <c r="H341" t="n">
         <v>113660</v>
@@ -10345,7 +10345,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255466461182</v>
+        <v>26.4255447387695</v>
       </c>
       <c r="H344" t="n">
         <v>323645</v>
@@ -10374,7 +10374,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G345" t="n">
-        <v>26.4879341125488</v>
+        <v>26.4879322052002</v>
       </c>
       <c r="H345" t="n">
         <v>116456</v>
@@ -10432,7 +10432,7 @@
         <v>31</v>
       </c>
       <c r="G347" t="n">
-        <v>27.628734588623</v>
+        <v>27.6287326812744</v>
       </c>
       <c r="H347" t="n">
         <v>144983</v>
@@ -10490,7 +10490,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G349" t="n">
-        <v>27.6732921600342</v>
+        <v>27.6732902526855</v>
       </c>
       <c r="H349" t="n">
         <v>144929</v>
@@ -10519,7 +10519,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G350" t="n">
-        <v>28.6804084777832</v>
+        <v>28.6804065704346</v>
       </c>
       <c r="H350" t="n">
         <v>101430</v>
@@ -10577,7 +10577,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>27.8069820404053</v>
+        <v>27.8069839477539</v>
       </c>
       <c r="H352" t="n">
         <v>138482</v>
@@ -10606,7 +10606,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665088653564</v>
+        <v>28.4665069580078</v>
       </c>
       <c r="H353" t="n">
         <v>149589</v>
@@ -10664,7 +10664,7 @@
         <v>33.0900001525879</v>
       </c>
       <c r="G355" t="n">
-        <v>29.4914455413818</v>
+        <v>29.4914436340332</v>
       </c>
       <c r="H355" t="n">
         <v>77343</v>
@@ -10722,7 +10722,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746814727783</v>
+        <v>29.8746795654297</v>
       </c>
       <c r="H357" t="n">
         <v>77270</v>
@@ -10751,7 +10751,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024806976318</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H358" t="n">
         <v>94582</v>
@@ -10780,7 +10780,7 @@
         <v>34.5299987792969</v>
       </c>
       <c r="G359" t="n">
-        <v>30.7748413085938</v>
+        <v>30.7748432159424</v>
       </c>
       <c r="H359" t="n">
         <v>96091</v>
@@ -10809,7 +10809,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400932312012</v>
+        <v>30.2400951385498</v>
       </c>
       <c r="H360" t="n">
         <v>60227</v>
@@ -10867,7 +10867,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283157348633</v>
+        <v>30.8283176422119</v>
       </c>
       <c r="H362" t="n">
         <v>119866</v>
@@ -10896,7 +10896,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996162414551</v>
+        <v>30.8996181488037</v>
       </c>
       <c r="H363" t="n">
         <v>56630</v>
@@ -10925,7 +10925,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154800415039</v>
+        <v>31.0154819488525</v>
       </c>
       <c r="H364" t="n">
         <v>62681</v>
@@ -10954,7 +10954,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.9976539611816</v>
+        <v>30.9976558685303</v>
       </c>
       <c r="H365" t="n">
         <v>39009</v>
@@ -10983,7 +10983,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.9352684020996</v>
+        <v>30.935266494751</v>
       </c>
       <c r="H366" t="n">
         <v>57384</v>
@@ -11012,7 +11012,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G367" t="n">
-        <v>30.6500663757324</v>
+        <v>30.6500644683838</v>
       </c>
       <c r="H367" t="n">
         <v>49692</v>
@@ -11041,7 +11041,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.7481060028076</v>
+        <v>30.748104095459</v>
       </c>
       <c r="H368" t="n">
         <v>76769</v>
@@ -11070,7 +11070,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857204437256</v>
+        <v>30.6857223510742</v>
       </c>
       <c r="H369" t="n">
         <v>81969</v>
@@ -11128,7 +11128,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G371" t="n">
-        <v>29.5003566741943</v>
+        <v>29.5003528594971</v>
       </c>
       <c r="H371" t="n">
         <v>139607</v>
@@ -11157,7 +11157,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G372" t="n">
-        <v>29.3131923675537</v>
+        <v>29.3131942749023</v>
       </c>
       <c r="H372" t="n">
         <v>62583</v>
@@ -11186,7 +11186,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>29.2775440216064</v>
+        <v>29.2775402069092</v>
       </c>
       <c r="H373" t="n">
         <v>103705</v>
@@ -11215,7 +11215,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.1687870025635</v>
+        <v>30.1687927246094</v>
       </c>
       <c r="H374" t="n">
         <v>129825</v>
@@ -11244,7 +11244,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331443786621</v>
+        <v>30.1331462860107</v>
       </c>
       <c r="H375" t="n">
         <v>53130</v>
@@ -11273,7 +11273,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G376" t="n">
-        <v>29.9994525909424</v>
+        <v>29.999454498291</v>
       </c>
       <c r="H376" t="n">
         <v>56145</v>
@@ -11302,7 +11302,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G377" t="n">
-        <v>29.9281578063965</v>
+        <v>29.9281558990479</v>
       </c>
       <c r="H377" t="n">
         <v>47170</v>
@@ -11331,7 +11331,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G378" t="n">
-        <v>30.0529327392578</v>
+        <v>30.0529308319092</v>
       </c>
       <c r="H378" t="n">
         <v>73018</v>
@@ -11360,7 +11360,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.4825344085693</v>
+        <v>29.4825305938721</v>
       </c>
       <c r="H379" t="n">
         <v>44022</v>
@@ -11389,7 +11389,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G380" t="n">
-        <v>29.8122940063477</v>
+        <v>29.812292098999</v>
       </c>
       <c r="H380" t="n">
         <v>103731</v>
@@ -11418,7 +11418,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G381" t="n">
-        <v>28.9121322631836</v>
+        <v>28.912130355835</v>
       </c>
       <c r="H381" t="n">
         <v>56347</v>
@@ -11447,7 +11447,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.1260318756104</v>
+        <v>29.1260299682617</v>
       </c>
       <c r="H382" t="n">
         <v>60542</v>
@@ -11534,7 +11534,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544040679932</v>
+        <v>27.2544097900391</v>
       </c>
       <c r="H385" t="n">
         <v>71103</v>
@@ -11563,7 +11563,7 @@
         <v>31.0699996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>27.6911182403564</v>
+        <v>27.6911201477051</v>
       </c>
       <c r="H386" t="n">
         <v>94629</v>
@@ -11592,7 +11592,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>27.4861335754395</v>
+        <v>27.4861316680908</v>
       </c>
       <c r="H387" t="n">
         <v>60669</v>
@@ -11621,7 +11621,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G388" t="n">
-        <v>27.5752582550049</v>
+        <v>27.5752601623535</v>
       </c>
       <c r="H388" t="n">
         <v>39274</v>
@@ -11650,7 +11650,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>28.1189212799072</v>
+        <v>28.11891746521</v>
       </c>
       <c r="H389" t="n">
         <v>62724</v>
@@ -11737,7 +11737,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734596252441</v>
+        <v>28.5734558105469</v>
       </c>
       <c r="H392" t="n">
         <v>75319</v>
@@ -11766,7 +11766,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G393" t="n">
-        <v>28.6180210113525</v>
+        <v>28.6180191040039</v>
       </c>
       <c r="H393" t="n">
         <v>25940</v>
@@ -11795,7 +11795,7 @@
         <v>32</v>
       </c>
       <c r="G394" t="n">
-        <v>28.519983291626</v>
+        <v>28.5199813842773</v>
       </c>
       <c r="H394" t="n">
         <v>36963</v>
@@ -11824,7 +11824,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>28.7873573303223</v>
+        <v>28.787353515625</v>
       </c>
       <c r="H395" t="n">
         <v>65931</v>
@@ -11853,7 +11853,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665088653564</v>
+        <v>28.4665069580078</v>
       </c>
       <c r="H396" t="n">
         <v>45353</v>
@@ -11882,7 +11882,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855529785156</v>
+        <v>29.7855587005615</v>
       </c>
       <c r="H397" t="n">
         <v>145142</v>
@@ -11911,7 +11911,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G398" t="n">
-        <v>29.536003112793</v>
+        <v>29.5360069274902</v>
       </c>
       <c r="H398" t="n">
         <v>60276</v>
@@ -11969,7 +11969,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.1705932617188</v>
+        <v>29.1705951690674</v>
       </c>
       <c r="H400" t="n">
         <v>60603</v>
@@ -11998,7 +11998,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>29.2329769134521</v>
+        <v>29.2329807281494</v>
       </c>
       <c r="H401" t="n">
         <v>46478</v>
@@ -12056,7 +12056,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221073150635</v>
+        <v>29.3221092224121</v>
       </c>
       <c r="H403" t="n">
         <v>93384</v>
@@ -12172,7 +12172,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G407" t="n">
-        <v>28.9923439025879</v>
+        <v>28.9923419952393</v>
       </c>
       <c r="H407" t="n">
         <v>32363</v>
@@ -12201,7 +12201,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477787017822</v>
+        <v>28.9477825164795</v>
       </c>
       <c r="H408" t="n">
         <v>25669</v>
@@ -12259,7 +12259,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G410" t="n">
-        <v>29.607307434082</v>
+        <v>29.6073093414307</v>
       </c>
       <c r="H410" t="n">
         <v>24264</v>
@@ -12288,7 +12288,7 @@
         <v>33.5</v>
       </c>
       <c r="G411" t="n">
-        <v>29.8568572998047</v>
+        <v>29.8568553924561</v>
       </c>
       <c r="H411" t="n">
         <v>92243</v>
@@ -12317,7 +12317,7 @@
         <v>32.9900016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>29.4023208618164</v>
+        <v>29.4023189544678</v>
       </c>
       <c r="H412" t="n">
         <v>67361</v>
@@ -12346,7 +12346,7 @@
         <v>33</v>
       </c>
       <c r="G413" t="n">
-        <v>29.4112319946289</v>
+        <v>29.4112281799316</v>
       </c>
       <c r="H413" t="n">
         <v>55788</v>
@@ -12375,7 +12375,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G414" t="n">
-        <v>28.814094543457</v>
+        <v>28.8140983581543</v>
       </c>
       <c r="H414" t="n">
         <v>37331</v>
@@ -12404,7 +12404,7 @@
         <v>33</v>
       </c>
       <c r="G415" t="n">
-        <v>29.4112319946289</v>
+        <v>29.4112281799316</v>
       </c>
       <c r="H415" t="n">
         <v>48065</v>
@@ -12433,7 +12433,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.687520980835</v>
+        <v>29.6875152587891</v>
       </c>
       <c r="H416" t="n">
         <v>61558</v>
@@ -12462,7 +12462,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>29.6162185668945</v>
+        <v>29.6162223815918</v>
       </c>
       <c r="H417" t="n">
         <v>37108</v>
@@ -12491,7 +12491,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>29.6786041259766</v>
+        <v>29.6786060333252</v>
       </c>
       <c r="H418" t="n">
         <v>29416</v>
@@ -12520,7 +12520,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964302062988</v>
+        <v>29.6964282989502</v>
       </c>
       <c r="H419" t="n">
         <v>28781</v>
@@ -12549,7 +12549,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>30.1420555114746</v>
+        <v>30.142053604126</v>
       </c>
       <c r="H420" t="n">
         <v>33779</v>
@@ -12578,7 +12578,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390293121338</v>
+        <v>29.8390350341797</v>
       </c>
       <c r="H421" t="n">
         <v>26190</v>
@@ -12636,7 +12636,7 @@
         <v>33.4500007629395</v>
       </c>
       <c r="G423" t="n">
-        <v>29.8122940063477</v>
+        <v>29.812292098999</v>
       </c>
       <c r="H423" t="n">
         <v>44745</v>
@@ -12665,7 +12665,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.5181789398193</v>
+        <v>29.5181770324707</v>
       </c>
       <c r="H424" t="n">
         <v>23018</v>
@@ -12694,7 +12694,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G425" t="n">
-        <v>29.1795043945312</v>
+        <v>29.1795082092285</v>
       </c>
       <c r="H425" t="n">
         <v>93713</v>
@@ -12723,7 +12723,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>29.4379692077637</v>
+        <v>29.437967300415</v>
       </c>
       <c r="H426" t="n">
         <v>57589</v>
@@ -12752,7 +12752,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648681640625</v>
+        <v>30.3648662567139</v>
       </c>
       <c r="H427" t="n">
         <v>64685</v>
@@ -12781,7 +12781,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629058837891</v>
+        <v>30.4629096984863</v>
       </c>
       <c r="H428" t="n">
         <v>65836</v>
@@ -12810,7 +12810,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024806976318</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H429" t="n">
         <v>35077</v>
@@ -12839,7 +12839,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G430" t="n">
-        <v>30.4718189239502</v>
+        <v>30.4718170166016</v>
       </c>
       <c r="H430" t="n">
         <v>35469</v>
@@ -12897,7 +12897,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974922180176</v>
+        <v>30.0974941253662</v>
       </c>
       <c r="H432" t="n">
         <v>12531</v>
@@ -12926,7 +12926,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.0618419647217</v>
+        <v>30.0618457794189</v>
       </c>
       <c r="H433" t="n">
         <v>32928</v>
@@ -12955,7 +12955,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.2311763763428</v>
+        <v>30.23118019104</v>
       </c>
       <c r="H434" t="n">
         <v>24161</v>
@@ -13071,7 +13071,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G438" t="n">
-        <v>30.819408416748</v>
+        <v>30.8194065093994</v>
       </c>
       <c r="H438" t="n">
         <v>80310</v>
@@ -13129,7 +13129,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G440" t="n">
-        <v>31.7730464935303</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H440" t="n">
         <v>27909</v>
@@ -13158,7 +13158,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G441" t="n">
-        <v>31.7730464935303</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H441" t="n">
         <v>20121</v>
@@ -13216,7 +13216,7 @@
         <v>36.1100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>32.1830139160156</v>
+        <v>32.1830177307129</v>
       </c>
       <c r="H443" t="n">
         <v>74880</v>
@@ -13245,7 +13245,7 @@
         <v>35.9900016784668</v>
       </c>
       <c r="G444" t="n">
-        <v>32.0760612487793</v>
+        <v>32.0760688781738</v>
       </c>
       <c r="H444" t="n">
         <v>50553</v>
@@ -13274,7 +13274,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.9512901306152</v>
+        <v>31.951286315918</v>
       </c>
       <c r="H445" t="n">
         <v>54557</v>
@@ -13332,7 +13332,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990394592285</v>
+        <v>33.1990432739258</v>
       </c>
       <c r="H447" t="n">
         <v>128921</v>
@@ -13361,7 +13361,7 @@
         <v>37.4700012207031</v>
       </c>
       <c r="G448" t="n">
-        <v>33.3951148986816</v>
+        <v>33.3951225280762</v>
       </c>
       <c r="H448" t="n">
         <v>44537</v>
@@ -13390,7 +13390,7 @@
         <v>39</v>
       </c>
       <c r="G449" t="n">
-        <v>34.758731842041</v>
+        <v>34.7587280273438</v>
       </c>
       <c r="H449" t="n">
         <v>134623</v>
@@ -13448,7 +13448,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.7319869995117</v>
+        <v>34.731990814209</v>
       </c>
       <c r="H451" t="n">
         <v>72300</v>
@@ -13506,7 +13506,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>34.2239837646484</v>
+        <v>34.2239799499512</v>
       </c>
       <c r="H453" t="n">
         <v>40089</v>
@@ -13535,7 +13535,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.4378814697266</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H454" t="n">
         <v>22990</v>
@@ -13564,7 +13564,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.4378814697266</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H455" t="n">
         <v>25085</v>
@@ -13680,7 +13680,7 @@
         <v>39.5200004577637</v>
       </c>
       <c r="G459" t="n">
-        <v>35.2221755981445</v>
+        <v>35.2221794128418</v>
       </c>
       <c r="H459" t="n">
         <v>35360</v>
@@ -13738,7 +13738,7 @@
         <v>38.5699996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>34.3754920959473</v>
+        <v>34.37548828125</v>
       </c>
       <c r="H461" t="n">
         <v>28779</v>
@@ -13796,7 +13796,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G463" t="n">
-        <v>33.8496551513672</v>
+        <v>33.8496513366699</v>
       </c>
       <c r="H463" t="n">
         <v>26614</v>
@@ -13883,7 +13883,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G466" t="n">
-        <v>33.7159690856934</v>
+        <v>33.7159652709961</v>
       </c>
       <c r="H466" t="n">
         <v>30408</v>
@@ -13912,7 +13912,7 @@
         <v>38.2200012207031</v>
       </c>
       <c r="G467" t="n">
-        <v>34.0635528564453</v>
+        <v>34.0635566711426</v>
       </c>
       <c r="H467" t="n">
         <v>45044</v>
@@ -13941,7 +13941,7 @@
         <v>38.5</v>
       </c>
       <c r="G468" t="n">
-        <v>34.3130989074707</v>
+        <v>34.3131065368652</v>
       </c>
       <c r="H468" t="n">
         <v>152768</v>
@@ -13970,7 +13970,7 @@
         <v>38.5</v>
       </c>
       <c r="G469" t="n">
-        <v>34.3130989074707</v>
+        <v>34.3131065368652</v>
       </c>
       <c r="H469" t="n">
         <v>119331</v>
@@ -14086,7 +14086,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G473" t="n">
-        <v>34.7765579223633</v>
+        <v>34.776554107666</v>
       </c>
       <c r="H473" t="n">
         <v>35970</v>
@@ -14173,7 +14173,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081161499023</v>
+        <v>34.1081199645996</v>
       </c>
       <c r="H476" t="n">
         <v>84787</v>
@@ -14231,7 +14231,7 @@
         <v>38.25</v>
       </c>
       <c r="G478" t="n">
-        <v>34.0902900695801</v>
+        <v>34.0902938842773</v>
       </c>
       <c r="H478" t="n">
         <v>89938</v>
@@ -14260,7 +14260,7 @@
         <v>39.3899993896484</v>
       </c>
       <c r="G479" t="n">
-        <v>35.1063194274902</v>
+        <v>35.106315612793</v>
       </c>
       <c r="H479" t="n">
         <v>154448</v>
@@ -14289,7 +14289,7 @@
         <v>40.6699981689453</v>
       </c>
       <c r="G480" t="n">
-        <v>36.2471160888672</v>
+        <v>36.2471122741699</v>
       </c>
       <c r="H480" t="n">
         <v>192485</v>
@@ -14405,7 +14405,7 @@
         <v>41.9799995422363</v>
       </c>
       <c r="G484" t="n">
-        <v>37.4146461486816</v>
+        <v>37.4146499633789</v>
       </c>
       <c r="H484" t="n">
         <v>96543</v>
@@ -14434,7 +14434,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.8584747314453</v>
+        <v>38.858470916748</v>
       </c>
       <c r="H485" t="n">
         <v>114697</v>
@@ -14492,7 +14492,7 @@
         <v>43.3300018310547</v>
       </c>
       <c r="G487" t="n">
-        <v>38.6178359985352</v>
+        <v>38.6178436279297</v>
       </c>
       <c r="H487" t="n">
         <v>81528</v>
@@ -14521,7 +14521,7 @@
         <v>43.2900009155273</v>
       </c>
       <c r="G488" t="n">
-        <v>38.5821914672852</v>
+        <v>38.5821876525879</v>
       </c>
       <c r="H488" t="n">
         <v>84905</v>
@@ -14579,7 +14579,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G490" t="n">
-        <v>38.4306755065918</v>
+        <v>38.4306716918945</v>
       </c>
       <c r="H490" t="n">
         <v>37738</v>
@@ -14637,7 +14637,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.805004119873</v>
+        <v>38.8050003051758</v>
       </c>
       <c r="H492" t="n">
         <v>92161</v>
@@ -14724,7 +14724,7 @@
         <v>42.7000007629395</v>
       </c>
       <c r="G495" t="n">
-        <v>38.0563468933105</v>
+        <v>38.0563507080078</v>
       </c>
       <c r="H495" t="n">
         <v>40596</v>
@@ -14782,7 +14782,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.3415451049805</v>
+        <v>38.341552734375</v>
       </c>
       <c r="H497" t="n">
         <v>44383</v>
@@ -14811,7 +14811,7 @@
         <v>43.2200012207031</v>
       </c>
       <c r="G498" t="n">
-        <v>38.5197982788086</v>
+        <v>38.5198020935059</v>
       </c>
       <c r="H498" t="n">
         <v>61880</v>
@@ -14869,7 +14869,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G500" t="n">
-        <v>38.4306755065918</v>
+        <v>38.4306716918945</v>
       </c>
       <c r="H500" t="n">
         <v>89203</v>
@@ -14898,7 +14898,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089248657227</v>
+        <v>38.6089286804199</v>
       </c>
       <c r="H501" t="n">
         <v>39100</v>
@@ -15014,7 +15014,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>39.0812911987305</v>
+        <v>39.0812835693359</v>
       </c>
       <c r="H505" t="n">
         <v>45135</v>
@@ -15043,7 +15043,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545539855957</v>
+        <v>39.0545501708984</v>
       </c>
       <c r="H506" t="n">
         <v>27453</v>
@@ -15072,7 +15072,7 @@
         <v>44.1199989318848</v>
       </c>
       <c r="G507" t="n">
-        <v>39.3219261169434</v>
+        <v>39.3219223022461</v>
       </c>
       <c r="H507" t="n">
         <v>32415</v>
@@ -15130,7 +15130,7 @@
         <v>42.9599990844727</v>
       </c>
       <c r="G509" t="n">
-        <v>38.2880744934082</v>
+        <v>38.2880706787109</v>
       </c>
       <c r="H509" t="n">
         <v>18466</v>
@@ -15217,7 +15217,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G512" t="n">
-        <v>36.6125335693359</v>
+        <v>36.6125259399414</v>
       </c>
       <c r="H512" t="n">
         <v>50757</v>
@@ -15246,7 +15246,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G513" t="n">
-        <v>37.6820220947266</v>
+        <v>37.6820259094238</v>
       </c>
       <c r="H513" t="n">
         <v>41367</v>
@@ -15275,7 +15275,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G514" t="n">
-        <v>38.4663238525391</v>
+        <v>38.4663276672363</v>
       </c>
       <c r="H514" t="n">
         <v>46576</v>
@@ -15333,7 +15333,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G516" t="n">
-        <v>42.655200958252</v>
+        <v>42.6551971435547</v>
       </c>
       <c r="H516" t="n">
         <v>71031</v>
@@ -15391,7 +15391,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.423469543457</v>
+        <v>42.4234733581543</v>
       </c>
       <c r="H518" t="n">
         <v>40840</v>
@@ -15449,7 +15449,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G520" t="n">
-        <v>42.0848007202148</v>
+        <v>42.0847969055176</v>
       </c>
       <c r="H520" t="n">
         <v>21408</v>
@@ -15565,7 +15565,7 @@
         <v>46.8600006103516</v>
       </c>
       <c r="G524" t="n">
-        <v>41.7639465332031</v>
+        <v>41.7639503479004</v>
       </c>
       <c r="H524" t="n">
         <v>22587</v>
@@ -15594,7 +15594,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G525" t="n">
-        <v>42.0848007202148</v>
+        <v>42.0847969055176</v>
       </c>
       <c r="H525" t="n">
         <v>27575</v>
@@ -15623,7 +15623,7 @@
         <v>47.2799987792969</v>
       </c>
       <c r="G526" t="n">
-        <v>42.1382713317871</v>
+        <v>42.1382675170898</v>
       </c>
       <c r="H526" t="n">
         <v>32130</v>
@@ -15710,7 +15710,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>41.5322227478027</v>
+        <v>41.5322189331055</v>
       </c>
       <c r="H529" t="n">
         <v>36997</v>
@@ -15739,7 +15739,7 @@
         <v>46.8800010681152</v>
       </c>
       <c r="G530" t="n">
-        <v>41.7817687988281</v>
+        <v>41.7817726135254</v>
       </c>
       <c r="H530" t="n">
         <v>30670</v>
@@ -15797,7 +15797,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>40.8192291259766</v>
+        <v>40.8192253112793</v>
       </c>
       <c r="H532" t="n">
         <v>43823</v>
@@ -15826,7 +15826,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G533" t="n">
-        <v>40.355770111084</v>
+        <v>40.3557739257812</v>
       </c>
       <c r="H533" t="n">
         <v>51912</v>
@@ -15884,7 +15884,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G535" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H535" t="n">
         <v>40370</v>
@@ -15942,7 +15942,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784210205078</v>
+        <v>39.6784248352051</v>
       </c>
       <c r="H537" t="n">
         <v>153620</v>
@@ -15971,7 +15971,7 @@
         <v>48</v>
       </c>
       <c r="G538" t="n">
-        <v>42.7799758911133</v>
+        <v>42.779972076416</v>
       </c>
       <c r="H538" t="n">
         <v>151081</v>
@@ -16000,7 +16000,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G539" t="n">
-        <v>41.4787483215332</v>
+        <v>41.4787521362305</v>
       </c>
       <c r="H539" t="n">
         <v>164721</v>
@@ -16029,7 +16029,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>38.6802215576172</v>
+        <v>38.6802253723145</v>
       </c>
       <c r="H540" t="n">
         <v>153076</v>
@@ -16087,7 +16087,7 @@
         <v>41.8400001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>37.2898788452148</v>
+        <v>37.2898750305176</v>
       </c>
       <c r="H542" t="n">
         <v>58757</v>
@@ -16174,7 +16174,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>40.1953468322754</v>
+        <v>40.1953506469727</v>
       </c>
       <c r="H545" t="n">
         <v>42666</v>
@@ -16261,7 +16261,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G548" t="n">
-        <v>40.8013954162598</v>
+        <v>40.801399230957</v>
       </c>
       <c r="H548" t="n">
         <v>30062</v>
@@ -16290,7 +16290,7 @@
         <v>45.939998626709</v>
       </c>
       <c r="G549" t="n">
-        <v>40.9439964294434</v>
+        <v>40.9440002441406</v>
       </c>
       <c r="H549" t="n">
         <v>33774</v>
@@ -16319,7 +16319,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G550" t="n">
-        <v>40.8013954162598</v>
+        <v>40.801399230957</v>
       </c>
       <c r="H550" t="n">
         <v>59354</v>
@@ -16464,7 +16464,7 @@
         <v>44.0400009155273</v>
       </c>
       <c r="G555" t="n">
-        <v>39.2506256103516</v>
+        <v>39.2506294250488</v>
       </c>
       <c r="H555" t="n">
         <v>114926</v>
@@ -16493,7 +16493,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793212890625</v>
+        <v>39.1793251037598</v>
       </c>
       <c r="H556" t="n">
         <v>64193</v>
@@ -16522,7 +16522,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131729125977</v>
+        <v>40.2131690979004</v>
       </c>
       <c r="H557" t="n">
         <v>48880</v>
@@ -16638,7 +16638,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>42.6017227172852</v>
+        <v>42.6017189025879</v>
       </c>
       <c r="H561" t="n">
         <v>139514</v>
@@ -16667,7 +16667,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446472167969</v>
+        <v>44.5446434020996</v>
       </c>
       <c r="H562" t="n">
         <v>242564</v>
@@ -16696,7 +16696,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G563" t="n">
-        <v>43.9029426574707</v>
+        <v>43.902946472168</v>
       </c>
       <c r="H563" t="n">
         <v>150547</v>
@@ -16725,7 +16725,7 @@
         <v>50.75</v>
       </c>
       <c r="G564" t="n">
-        <v>45.2309112548828</v>
+        <v>45.2309074401855</v>
       </c>
       <c r="H564" t="n">
         <v>99680</v>
@@ -16812,7 +16812,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>46.0330352783203</v>
+        <v>46.0330390930176</v>
       </c>
       <c r="H567" t="n">
         <v>142610</v>
@@ -16841,7 +16841,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253402709961</v>
+        <v>47.3253440856934</v>
       </c>
       <c r="H568" t="n">
         <v>177354</v>
@@ -16870,7 +16870,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>45.943904876709</v>
+        <v>45.9439086914062</v>
       </c>
       <c r="H569" t="n">
         <v>178635</v>
@@ -16899,7 +16899,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874061584473</v>
+        <v>45.5874099731445</v>
       </c>
       <c r="H570" t="n">
         <v>120878</v>
@@ -16928,7 +16928,7 @@
         <v>50.1500015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>44.6961631774902</v>
+        <v>44.696159362793</v>
       </c>
       <c r="H571" t="n">
         <v>63427</v>
@@ -16986,7 +16986,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494720458984</v>
+        <v>43.8494682312012</v>
       </c>
       <c r="H573" t="n">
         <v>65658</v>
@@ -17015,7 +17015,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G574" t="n">
-        <v>42.9582176208496</v>
+        <v>42.9582214355469</v>
       </c>
       <c r="H574" t="n">
         <v>88622</v>
@@ -17044,7 +17044,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>42.655200958252</v>
+        <v>42.6551971435547</v>
       </c>
       <c r="H575" t="n">
         <v>111110</v>
@@ -17073,7 +17073,7 @@
         <v>46.5200004577637</v>
       </c>
       <c r="G576" t="n">
-        <v>41.4609222412109</v>
+        <v>41.4609260559082</v>
       </c>
       <c r="H576" t="n">
         <v>100832</v>
@@ -17102,7 +17102,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>41.4787483215332</v>
+        <v>41.4787521362305</v>
       </c>
       <c r="H577" t="n">
         <v>76270</v>
@@ -17160,7 +17160,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G579" t="n">
-        <v>41.157901763916</v>
+        <v>41.1578979492188</v>
       </c>
       <c r="H579" t="n">
         <v>52237</v>
@@ -17218,7 +17218,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675514221191</v>
+        <v>39.7675476074219</v>
       </c>
       <c r="H581" t="n">
         <v>81341</v>
@@ -17247,7 +17247,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G582" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H582" t="n">
         <v>46802</v>
@@ -17276,7 +17276,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.1080207824707</v>
+        <v>39.108024597168</v>
       </c>
       <c r="H583" t="n">
         <v>48182</v>
@@ -17392,7 +17392,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7318992614746</v>
+        <v>39.7319030761719</v>
       </c>
       <c r="H587" t="n">
         <v>42227</v>
@@ -17421,7 +17421,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3041000366211</v>
+        <v>39.3040962219238</v>
       </c>
       <c r="H588" t="n">
         <v>50438</v>
@@ -17450,7 +17450,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675514221191</v>
+        <v>39.7675476074219</v>
       </c>
       <c r="H589" t="n">
         <v>23775</v>
@@ -17537,7 +17537,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G592" t="n">
-        <v>39.4288787841797</v>
+        <v>39.4288749694824</v>
       </c>
       <c r="H592" t="n">
         <v>40222</v>
@@ -17769,7 +17769,7 @@
         <v>45.2000007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>40.7087059020996</v>
+        <v>40.7087097167969</v>
       </c>
       <c r="H600" t="n">
         <v>23543</v>
@@ -17856,7 +17856,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G603" t="n">
-        <v>39.8440971374512</v>
+        <v>39.8441009521484</v>
       </c>
       <c r="H603" t="n">
         <v>60714</v>
@@ -17914,7 +17914,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.484432220459</v>
+        <v>37.4844360351562</v>
       </c>
       <c r="H605" t="n">
         <v>87797</v>
@@ -17943,7 +17943,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316230773926</v>
+        <v>36.3316192626953</v>
       </c>
       <c r="H606" t="n">
         <v>66466</v>
@@ -17972,7 +17972,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G607" t="n">
-        <v>37.0521278381348</v>
+        <v>37.0521240234375</v>
       </c>
       <c r="H607" t="n">
         <v>93918</v>
@@ -18059,7 +18059,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.0073890686035</v>
+        <v>36.0073928833008</v>
       </c>
       <c r="H610" t="n">
         <v>71270</v>
@@ -18146,7 +18146,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241401672363</v>
+        <v>34.2241363525391</v>
       </c>
       <c r="H613" t="n">
         <v>88495</v>
@@ -18262,7 +18262,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G617" t="n">
-        <v>34.4763107299805</v>
+        <v>34.4763145446777</v>
       </c>
       <c r="H617" t="n">
         <v>85349</v>
@@ -18291,7 +18291,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924629211426</v>
+        <v>34.6924667358398</v>
       </c>
       <c r="H618" t="n">
         <v>73867</v>
@@ -18436,7 +18436,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241401672363</v>
+        <v>34.2241363525391</v>
       </c>
       <c r="H623" t="n">
         <v>21903</v>
@@ -18552,7 +18552,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247711181641</v>
+        <v>35.1247749328613</v>
       </c>
       <c r="H627" t="n">
         <v>103614</v>
@@ -18581,7 +18581,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>33.5036239624023</v>
+        <v>33.5036277770996</v>
       </c>
       <c r="H628" t="n">
         <v>53029</v>
@@ -18610,7 +18610,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.4048500061035</v>
+        <v>32.4048538208008</v>
       </c>
       <c r="H629" t="n">
         <v>77422</v>
@@ -18639,7 +18639,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>32.3868370056152</v>
+        <v>32.3868408203125</v>
       </c>
       <c r="H630" t="n">
         <v>57634</v>
@@ -18726,7 +18726,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5315341949463</v>
+        <v>30.5315361022949</v>
       </c>
       <c r="H633" t="n">
         <v>75764</v>
@@ -18755,7 +18755,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.4867935180664</v>
+        <v>29.486795425415</v>
       </c>
       <c r="H634" t="n">
         <v>160938</v>
@@ -18784,7 +18784,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371166229248</v>
+        <v>29.9371128082275</v>
       </c>
       <c r="H635" t="n">
         <v>311338</v>
@@ -18813,7 +18813,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H636" t="n">
         <v>86489</v>
@@ -18842,7 +18842,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.153263092041</v>
+        <v>30.1532649993896</v>
       </c>
       <c r="H637" t="n">
         <v>47812</v>
@@ -18900,7 +18900,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147415161133</v>
+        <v>29.4147434234619</v>
       </c>
       <c r="H639" t="n">
         <v>66878</v>
@@ -18958,7 +18958,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G641" t="n">
-        <v>29.1265392303467</v>
+        <v>29.1265411376953</v>
       </c>
       <c r="H641" t="n">
         <v>126609</v>
@@ -19016,7 +19016,7 @@
         <v>33.9799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>30.6035804748535</v>
+        <v>30.6035823822021</v>
       </c>
       <c r="H643" t="n">
         <v>77878</v>
@@ -19045,7 +19045,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520408630371</v>
+        <v>31.2520427703857</v>
       </c>
       <c r="H644" t="n">
         <v>161628</v>
@@ -19074,7 +19074,7 @@
         <v>32.9199981689453</v>
       </c>
       <c r="G645" t="n">
-        <v>29.6489067077637</v>
+        <v>29.6489086151123</v>
       </c>
       <c r="H645" t="n">
         <v>97694</v>
@@ -19103,7 +19103,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551239013672</v>
+        <v>29.9551219940186</v>
       </c>
       <c r="H646" t="n">
         <v>48258</v>
@@ -19132,7 +19132,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172351837158</v>
+        <v>30.1172389984131</v>
       </c>
       <c r="H647" t="n">
         <v>44619</v>
@@ -19161,7 +19161,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054374694824</v>
+        <v>30.4054393768311</v>
       </c>
       <c r="H648" t="n">
         <v>33638</v>
@@ -19190,7 +19190,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>30.5315341949463</v>
+        <v>30.5315361022949</v>
       </c>
       <c r="H649" t="n">
         <v>62064</v>
@@ -19219,7 +19219,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.666332244873</v>
+        <v>31.6663360595703</v>
       </c>
       <c r="H650" t="n">
         <v>110112</v>
@@ -19248,7 +19248,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>31.6483211517334</v>
+        <v>31.6483173370361</v>
       </c>
       <c r="H651" t="n">
         <v>95229</v>
@@ -19277,7 +19277,7 @@
         <v>35.6199989318848</v>
       </c>
       <c r="G652" t="n">
-        <v>32.080623626709</v>
+        <v>32.0806159973145</v>
       </c>
       <c r="H652" t="n">
         <v>85998</v>
@@ -19335,7 +19335,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601169586182</v>
+        <v>31.3601150512695</v>
       </c>
       <c r="H654" t="n">
         <v>42779</v>
@@ -19422,7 +19422,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520408630371</v>
+        <v>31.2520427703857</v>
       </c>
       <c r="H657" t="n">
         <v>35703</v>
@@ -19451,7 +19451,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122875213623</v>
+        <v>31.6122894287109</v>
       </c>
       <c r="H658" t="n">
         <v>29583</v>
@@ -19509,7 +19509,7 @@
         <v>34.2400016784668</v>
       </c>
       <c r="G660" t="n">
-        <v>30.8377475738525</v>
+        <v>30.8377456665039</v>
       </c>
       <c r="H660" t="n">
         <v>41227</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.901086807251</v>
+        <v>29.9010887145996</v>
       </c>
       <c r="H662" t="n">
         <v>24019</v>
@@ -19596,7 +19596,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H663" t="n">
         <v>57598</v>
@@ -19654,7 +19654,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>29.0905151367188</v>
+        <v>29.0905132293701</v>
       </c>
       <c r="H665" t="n">
         <v>24107</v>
@@ -19712,7 +19712,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>28.099817276001</v>
+        <v>28.0998191833496</v>
       </c>
       <c r="H667" t="n">
         <v>106675</v>
@@ -19741,7 +19741,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G668" t="n">
-        <v>27.5954608917236</v>
+        <v>27.595458984375</v>
       </c>
       <c r="H668" t="n">
         <v>30813</v>
@@ -19770,7 +19770,7 @@
         <v>29.5799999237061</v>
       </c>
       <c r="G669" t="n">
-        <v>26.6407890319824</v>
+        <v>26.6407871246338</v>
       </c>
       <c r="H669" t="n">
         <v>54672</v>
@@ -19828,7 +19828,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>26.0463695526123</v>
+        <v>26.0463676452637</v>
       </c>
       <c r="H671" t="n">
         <v>28977</v>
@@ -19857,7 +19857,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>26.5146980285645</v>
+        <v>26.5146999359131</v>
       </c>
       <c r="H672" t="n">
         <v>22536</v>
@@ -19915,7 +19915,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.0550804138184</v>
+        <v>27.055082321167</v>
       </c>
       <c r="H674" t="n">
         <v>59352</v>
@@ -20031,7 +20031,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>26.7488651275635</v>
+        <v>26.7488632202148</v>
       </c>
       <c r="H678" t="n">
         <v>33597</v>
@@ -20060,7 +20060,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693717956543</v>
+        <v>27.4693698883057</v>
       </c>
       <c r="H679" t="n">
         <v>30485</v>
@@ -20089,7 +20089,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196872711182</v>
       </c>
       <c r="H680" t="n">
         <v>46685</v>
@@ -20118,7 +20118,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G681" t="n">
-        <v>27.5774478912354</v>
+        <v>27.577449798584</v>
       </c>
       <c r="H681" t="n">
         <v>43724</v>
@@ -20205,7 +20205,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476409912109</v>
+        <v>27.8476371765137</v>
       </c>
       <c r="H684" t="n">
         <v>50842</v>
@@ -20263,7 +20263,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693717956543</v>
+        <v>27.4693698883057</v>
       </c>
       <c r="H686" t="n">
         <v>52867</v>
@@ -20292,7 +20292,7 @@
         <v>31.1399993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>28.0457782745361</v>
+        <v>28.0457763671875</v>
       </c>
       <c r="H687" t="n">
         <v>23832</v>
@@ -20321,7 +20321,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>28.0097522735596</v>
+        <v>28.0097541809082</v>
       </c>
       <c r="H688" t="n">
         <v>31923</v>
@@ -20379,7 +20379,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.0097522735596</v>
+        <v>28.0097541809082</v>
       </c>
       <c r="H690" t="n">
         <v>44005</v>
@@ -20466,7 +20466,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>28.5501327514648</v>
+        <v>28.5501346588135</v>
       </c>
       <c r="H693" t="n">
         <v>27520</v>
@@ -20495,7 +20495,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>29.1805820465088</v>
+        <v>29.1805801391602</v>
       </c>
       <c r="H694" t="n">
         <v>37376</v>
@@ -20582,7 +20582,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401977539062</v>
+        <v>28.6401958465576</v>
       </c>
       <c r="H697" t="n">
         <v>27160</v>
@@ -20611,7 +20611,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762218475342</v>
+        <v>28.6762237548828</v>
       </c>
       <c r="H698" t="n">
         <v>35302</v>
@@ -20640,7 +20640,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G699" t="n">
-        <v>27.6675109863281</v>
+        <v>27.6675090789795</v>
       </c>
       <c r="H699" t="n">
         <v>42864</v>
@@ -20669,7 +20669,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.0550804138184</v>
+        <v>27.055082321167</v>
       </c>
       <c r="H700" t="n">
         <v>32431</v>
@@ -20698,7 +20698,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>27.5954608917236</v>
+        <v>27.595458984375</v>
       </c>
       <c r="H701" t="n">
         <v>221272</v>
@@ -20727,7 +20727,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196872711182</v>
       </c>
       <c r="H702" t="n">
         <v>26734</v>
@@ -20756,7 +20756,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G703" t="n">
-        <v>27.4513607025146</v>
+        <v>27.451358795166</v>
       </c>
       <c r="H703" t="n">
         <v>119469</v>
@@ -20785,7 +20785,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196872711182</v>
       </c>
       <c r="H704" t="n">
         <v>37755</v>
@@ -20872,7 +20872,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320308685303</v>
+        <v>22.7320289611816</v>
       </c>
       <c r="H707" t="n">
         <v>196682</v>
@@ -20930,7 +20930,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233200073242</v>
+        <v>21.7233180999756</v>
       </c>
       <c r="H709" t="n">
         <v>130761</v>
@@ -20959,7 +20959,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860679626465</v>
+        <v>22.7860698699951</v>
       </c>
       <c r="H710" t="n">
         <v>107966</v>
@@ -21017,7 +21017,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G712" t="n">
-        <v>23.7047157287598</v>
+        <v>23.7047176361084</v>
       </c>
       <c r="H712" t="n">
         <v>61152</v>
@@ -21046,7 +21046,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606174468994</v>
+        <v>23.5606155395508</v>
       </c>
       <c r="H713" t="n">
         <v>38427</v>
@@ -21075,7 +21075,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>23.236385345459</v>
+        <v>23.2363872528076</v>
       </c>
       <c r="H714" t="n">
         <v>56594</v>
@@ -21162,7 +21162,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>21.7053070068359</v>
+        <v>21.7053089141846</v>
       </c>
       <c r="H717" t="n">
         <v>31552</v>
@@ -21249,7 +21249,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369747161865</v>
+        <v>21.2369766235352</v>
       </c>
       <c r="H720" t="n">
         <v>38258</v>
@@ -21278,7 +21278,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.3450546264648</v>
+        <v>21.3450527191162</v>
       </c>
       <c r="H721" t="n">
         <v>38719</v>
@@ -21307,7 +21307,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>21.5972309112549</v>
+        <v>21.5972270965576</v>
       </c>
       <c r="H722" t="n">
         <v>28389</v>
@@ -21336,7 +21336,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>19.7239074707031</v>
+        <v>19.7239093780518</v>
       </c>
       <c r="H723" t="n">
         <v>114037</v>
@@ -21394,7 +21394,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>18.2828941345215</v>
+        <v>18.2828922271729</v>
       </c>
       <c r="H725" t="n">
         <v>49521</v>
@@ -21452,7 +21452,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.8773136138916</v>
+        <v>18.877311706543</v>
       </c>
       <c r="H727" t="n">
         <v>78461</v>
@@ -21481,7 +21481,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>18.3909683227539</v>
+        <v>18.3909702301025</v>
       </c>
       <c r="H728" t="n">
         <v>70249</v>
@@ -21568,7 +21568,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.0036945343018</v>
+        <v>18.0036964416504</v>
       </c>
       <c r="H731" t="n">
         <v>90396</v>
@@ -21597,7 +21597,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G732" t="n">
-        <v>17.139087677002</v>
+        <v>17.1390857696533</v>
       </c>
       <c r="H732" t="n">
         <v>49459</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120700836182</v>
+        <v>17.1120681762695</v>
       </c>
       <c r="H733" t="n">
         <v>71224</v>
@@ -21713,7 +21713,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.2024250030518</v>
+        <v>16.2024269104004</v>
       </c>
       <c r="H736" t="n">
         <v>53336</v>
@@ -21742,7 +21742,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9502458572388</v>
+        <v>15.950249671936</v>
       </c>
       <c r="H737" t="n">
         <v>57508</v>
@@ -21771,7 +21771,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.7160844802856</v>
+        <v>15.7160835266113</v>
       </c>
       <c r="H738" t="n">
         <v>81701</v>
@@ -21800,7 +21800,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H739" t="n">
         <v>56603</v>
@@ -21858,7 +21858,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G741" t="n">
-        <v>16.1573925018311</v>
+        <v>16.1573963165283</v>
       </c>
       <c r="H741" t="n">
         <v>30250</v>
@@ -21887,7 +21887,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077117919922</v>
+        <v>16.6077136993408</v>
       </c>
       <c r="H742" t="n">
         <v>126448</v>
@@ -21916,7 +21916,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G743" t="n">
-        <v>16.4005641937256</v>
+        <v>16.4005661010742</v>
       </c>
       <c r="H743" t="n">
         <v>110085</v>
@@ -21945,7 +21945,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>17.4723224639893</v>
+        <v>17.4723205566406</v>
       </c>
       <c r="H744" t="n">
         <v>93088</v>
@@ -22032,7 +22032,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G747" t="n">
-        <v>17.9406490325928</v>
+        <v>17.9406509399414</v>
       </c>
       <c r="H747" t="n">
         <v>117827</v>
@@ -22119,7 +22119,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968444824219</v>
+        <v>16.7968463897705</v>
       </c>
       <c r="H750" t="n">
         <v>72692</v>
@@ -22206,7 +22206,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.905216217041</v>
+        <v>15.9052181243896</v>
       </c>
       <c r="H753" t="n">
         <v>55986</v>
@@ -22235,7 +22235,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G754" t="n">
-        <v>16.2654705047607</v>
+        <v>16.2654685974121</v>
       </c>
       <c r="H754" t="n">
         <v>85504</v>
@@ -22264,7 +22264,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>16.1934185028076</v>
+        <v>16.1934204101562</v>
       </c>
       <c r="H755" t="n">
         <v>54198</v>
@@ -22351,7 +22351,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496129989624</v>
+        <v>15.0496139526367</v>
       </c>
       <c r="H758" t="n">
         <v>39650</v>
@@ -22380,7 +22380,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800575256348</v>
       </c>
       <c r="H759" t="n">
         <v>53012</v>
@@ -22438,7 +22438,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899934768677</v>
+        <v>15.5899925231934</v>
       </c>
       <c r="H761" t="n">
         <v>79930</v>
@@ -22467,7 +22467,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>15.1486825942993</v>
+        <v>15.1486835479736</v>
       </c>
       <c r="H762" t="n">
         <v>108666</v>
@@ -22496,7 +22496,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639053344727</v>
+        <v>15.463903427124</v>
       </c>
       <c r="H763" t="n">
         <v>62260</v>
@@ -22583,7 +22583,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568050384521</v>
       </c>
       <c r="H766" t="n">
         <v>115896</v>
@@ -22641,7 +22641,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.3912658691406</v>
+        <v>17.391263961792</v>
       </c>
       <c r="H768" t="n">
         <v>73850</v>
@@ -22728,7 +22728,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G771" t="n">
-        <v>18.228853225708</v>
+        <v>18.2288551330566</v>
       </c>
       <c r="H771" t="n">
         <v>74008</v>
@@ -22844,7 +22844,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.4543113708496</v>
+        <v>17.454309463501</v>
       </c>
       <c r="H775" t="n">
         <v>38968</v>
@@ -22873,7 +22873,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791725158691</v>
+        <v>18.6791744232178</v>
       </c>
       <c r="H776" t="n">
         <v>84665</v>
@@ -22902,7 +22902,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G777" t="n">
-        <v>18.8052635192871</v>
+        <v>18.8052616119385</v>
       </c>
       <c r="H777" t="n">
         <v>56710</v>
@@ -22960,7 +22960,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G779" t="n">
-        <v>18.3369312286377</v>
+        <v>18.3369331359863</v>
       </c>
       <c r="H779" t="n">
         <v>51138</v>
@@ -23047,7 +23047,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G782" t="n">
-        <v>18.9493656158447</v>
+        <v>18.9493637084961</v>
       </c>
       <c r="H782" t="n">
         <v>40418</v>
@@ -23105,7 +23105,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G784" t="n">
-        <v>18.6971855163574</v>
+        <v>18.6971874237061</v>
       </c>
       <c r="H784" t="n">
         <v>38581</v>
@@ -23221,7 +23221,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G788" t="n">
-        <v>18.4269943237305</v>
+        <v>18.4269924163818</v>
       </c>
       <c r="H788" t="n">
         <v>64191</v>
@@ -23453,7 +23453,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698703765869</v>
+        <v>19.6698684692383</v>
       </c>
       <c r="H796" t="n">
         <v>111608</v>
@@ -23482,7 +23482,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>20.2462787628174</v>
+        <v>20.2462749481201</v>
       </c>
       <c r="H797" t="n">
         <v>77155</v>
@@ -23511,7 +23511,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G798" t="n">
-        <v>20.0661506652832</v>
+        <v>20.0661525726318</v>
       </c>
       <c r="H798" t="n">
         <v>47640</v>
@@ -23540,7 +23540,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G799" t="n">
-        <v>19.9220485687256</v>
+        <v>19.9220504760742</v>
       </c>
       <c r="H799" t="n">
         <v>43219</v>
@@ -23569,7 +23569,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>19.4176940917969</v>
+        <v>19.4176921844482</v>
       </c>
       <c r="H800" t="n">
         <v>43308</v>
@@ -23598,7 +23598,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537220001221</v>
+        <v>19.4537200927734</v>
       </c>
       <c r="H801" t="n">
         <v>38620</v>
@@ -23627,7 +23627,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G802" t="n">
-        <v>20.2823028564453</v>
+        <v>20.2823047637939</v>
       </c>
       <c r="H802" t="n">
         <v>63858</v>
@@ -23685,7 +23685,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>17.7515201568604</v>
+        <v>17.7515182495117</v>
       </c>
       <c r="H804" t="n">
         <v>362073</v>
@@ -23772,7 +23772,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>17.7965488433838</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H807" t="n">
         <v>48825</v>
@@ -23801,7 +23801,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G808" t="n">
-        <v>17.5083484649658</v>
+        <v>17.5083465576172</v>
       </c>
       <c r="H808" t="n">
         <v>79412</v>
@@ -23859,7 +23859,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508815765381</v>
+        <v>16.8508834838867</v>
       </c>
       <c r="H810" t="n">
         <v>142958</v>
@@ -23888,7 +23888,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G811" t="n">
-        <v>16.9859771728516</v>
+        <v>16.9859809875488</v>
       </c>
       <c r="H811" t="n">
         <v>69819</v>
@@ -23946,7 +23946,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120700836182</v>
+        <v>17.1120681762695</v>
       </c>
       <c r="H813" t="n">
         <v>36891</v>
@@ -23975,7 +23975,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490207672119</v>
+        <v>17.0490245819092</v>
       </c>
       <c r="H814" t="n">
         <v>19771</v>
@@ -24033,7 +24033,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462314605713</v>
+        <v>17.3462333679199</v>
       </c>
       <c r="H816" t="n">
         <v>103910</v>
@@ -24091,7 +24091,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>17.3822574615479</v>
+        <v>17.3822555541992</v>
       </c>
       <c r="H818" t="n">
         <v>52262</v>
@@ -24178,7 +24178,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.976676940918</v>
+        <v>17.9766750335693</v>
       </c>
       <c r="H821" t="n">
         <v>368484</v>
@@ -24294,7 +24294,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.4272899627686</v>
+        <v>17.4272918701172</v>
       </c>
       <c r="H825" t="n">
         <v>44899</v>
@@ -24323,7 +24323,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.4543113708496</v>
+        <v>17.454309463501</v>
       </c>
       <c r="H826" t="n">
         <v>48981</v>
@@ -24381,7 +24381,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G828" t="n">
-        <v>17.9136333465576</v>
+        <v>17.913631439209</v>
       </c>
       <c r="H828" t="n">
         <v>52651</v>
@@ -24497,7 +24497,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496593475342</v>
+        <v>17.9496574401855</v>
       </c>
       <c r="H832" t="n">
         <v>46935</v>
@@ -24526,7 +24526,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3822574615479</v>
+        <v>17.3822555541992</v>
       </c>
       <c r="H833" t="n">
         <v>127471</v>
@@ -24555,7 +24555,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2381553649902</v>
+        <v>17.2381572723389</v>
       </c>
       <c r="H834" t="n">
         <v>111270</v>
@@ -24584,7 +24584,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300792694092</v>
+        <v>17.1300811767578</v>
       </c>
       <c r="H835" t="n">
         <v>63235</v>
@@ -24642,7 +24642,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676723480225</v>
+        <v>17.9676704406738</v>
       </c>
       <c r="H837" t="n">
         <v>49207</v>
@@ -24700,7 +24700,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667419433594</v>
+        <v>18.0667400360107</v>
       </c>
       <c r="H839" t="n">
         <v>64387</v>
@@ -24758,7 +24758,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>17.7965488433838</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H841" t="n">
         <v>59761</v>
@@ -24816,7 +24816,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6074180603027</v>
+        <v>17.6074161529541</v>
       </c>
       <c r="H843" t="n">
         <v>31630</v>
@@ -24932,7 +24932,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568050384521</v>
       </c>
       <c r="H847" t="n">
         <v>58676</v>
@@ -24961,7 +24961,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>18.6365585327148</v>
+        <v>18.6365566253662</v>
       </c>
       <c r="H848" t="n">
         <v>152183</v>
@@ -25048,7 +25048,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G851" t="n">
-        <v>17.2249774932861</v>
+        <v>17.2249755859375</v>
       </c>
       <c r="H851" t="n">
         <v>61198</v>
@@ -25077,7 +25077,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G852" t="n">
-        <v>16.5330257415771</v>
+        <v>16.5330238342285</v>
       </c>
       <c r="H852" t="n">
         <v>79775</v>
@@ -25164,7 +25164,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232404708862</v>
       </c>
       <c r="H855" t="n">
         <v>212131</v>
@@ -25280,7 +25280,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>13.3131456375122</v>
+        <v>13.3131446838379</v>
       </c>
       <c r="H859" t="n">
         <v>77696</v>
@@ -25338,7 +25338,7 @@
         <v>15</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H861" t="n">
         <v>78115</v>
@@ -25367,7 +25367,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G862" t="n">
-        <v>13.4792137145996</v>
+        <v>13.4792127609253</v>
       </c>
       <c r="H862" t="n">
         <v>74086</v>
@@ -25657,7 +25657,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>13.7006378173828</v>
+        <v>13.7006387710571</v>
       </c>
       <c r="H872" t="n">
         <v>150643</v>
@@ -25715,7 +25715,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>14.4202671051025</v>
+        <v>14.4202680587769</v>
       </c>
       <c r="H874" t="n">
         <v>118791</v>
@@ -25831,7 +25831,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>13.7928981781006</v>
+        <v>13.7928972244263</v>
       </c>
       <c r="H878" t="n">
         <v>33517</v>
@@ -25860,7 +25860,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G879" t="n">
-        <v>13.6914110183716</v>
+        <v>13.6914119720459</v>
       </c>
       <c r="H879" t="n">
         <v>39249</v>
@@ -25889,7 +25889,7 @@
         <v>15</v>
       </c>
       <c r="G880" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H880" t="n">
         <v>70407</v>
@@ -26063,7 +26063,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H886" t="n">
         <v>520891</v>
@@ -26121,7 +26121,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G888" t="n">
-        <v>10.4069480895996</v>
+        <v>10.4069490432739</v>
       </c>
       <c r="H888" t="n">
         <v>237022</v>
@@ -26179,7 +26179,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G890" t="n">
-        <v>10.4069480895996</v>
+        <v>10.4069490432739</v>
       </c>
       <c r="H890" t="n">
         <v>125493</v>
@@ -26295,7 +26295,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G894" t="n">
-        <v>10.4807567596436</v>
+        <v>10.4807558059692</v>
       </c>
       <c r="H894" t="n">
         <v>222824</v>
@@ -26324,7 +26324,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837291717529</v>
+        <v>10.6837301254272</v>
       </c>
       <c r="H895" t="n">
         <v>124644</v>
@@ -26411,7 +26411,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.3700456619263</v>
+        <v>10.370044708252</v>
       </c>
       <c r="H898" t="n">
         <v>110215</v>
@@ -26556,7 +26556,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G903" t="n">
-        <v>9.53047752380371</v>
+        <v>9.53047657012939</v>
       </c>
       <c r="H903" t="n">
         <v>177150</v>
@@ -26585,7 +26585,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G904" t="n">
-        <v>10.0932636260986</v>
+        <v>10.0932645797729</v>
       </c>
       <c r="H904" t="n">
         <v>154899</v>
@@ -26643,7 +26643,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G906" t="n">
-        <v>10.5730171203613</v>
+        <v>10.5730180740356</v>
       </c>
       <c r="H906" t="n">
         <v>224050</v>
@@ -26730,7 +26730,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3054618835449</v>
+        <v>10.3054628372192</v>
       </c>
       <c r="H909" t="n">
         <v>167262</v>
@@ -26759,7 +26759,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438533782959</v>
+        <v>10.4438543319702</v>
       </c>
       <c r="H910" t="n">
         <v>188704</v>
@@ -26817,7 +26817,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G912" t="n">
-        <v>10.6652774810791</v>
+        <v>10.6652784347534</v>
       </c>
       <c r="H912" t="n">
         <v>140872</v>
@@ -26846,7 +26846,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H913" t="n">
         <v>207382</v>
@@ -26875,7 +26875,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.96410083770752</v>
+        <v>9.9640998840332</v>
       </c>
       <c r="H914" t="n">
         <v>253876</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>10.0563611984253</v>
+        <v>10.056360244751</v>
       </c>
       <c r="H915" t="n">
         <v>185001</v>
@@ -26933,7 +26933,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H916" t="n">
         <v>218887</v>
@@ -26991,7 +26991,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G918" t="n">
-        <v>9.50279903411865</v>
+        <v>9.50279998779297</v>
       </c>
       <c r="H918" t="n">
         <v>261117</v>
@@ -27020,7 +27020,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G919" t="n">
-        <v>9.29059982299805</v>
+        <v>9.29060077667236</v>
       </c>
       <c r="H919" t="n">
         <v>131607</v>
@@ -27049,7 +27049,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G920" t="n">
-        <v>9.5766077041626</v>
+        <v>9.57660865783691</v>
       </c>
       <c r="H920" t="n">
         <v>214640</v>
@@ -27078,7 +27078,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G921" t="n">
-        <v>9.21217823028564</v>
+        <v>9.21217918395996</v>
       </c>
       <c r="H921" t="n">
         <v>72765</v>
@@ -27165,7 +27165,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>9.29059982299805</v>
+        <v>9.29060077667236</v>
       </c>
       <c r="H924" t="n">
         <v>94925</v>
@@ -27223,7 +27223,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>9.47512245178223</v>
+        <v>9.47512149810791</v>
       </c>
       <c r="H926" t="n">
         <v>155843</v>
@@ -27281,7 +27281,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G928" t="n">
-        <v>8.94001293182373</v>
+        <v>8.94001197814941</v>
       </c>
       <c r="H928" t="n">
         <v>231622</v>
@@ -27310,7 +27310,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>8.98614120483398</v>
+        <v>8.9861421585083</v>
       </c>
       <c r="H929" t="n">
         <v>131407</v>
@@ -27339,7 +27339,7 @@
         <v>9.625</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88004302978516</v>
+        <v>8.88004398345947</v>
       </c>
       <c r="H930" t="n">
         <v>287237</v>
@@ -27397,7 +27397,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447059631348</v>
+        <v>9.24447154998779</v>
       </c>
       <c r="H932" t="n">
         <v>161867</v>
@@ -27484,7 +27484,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G935" t="n">
-        <v>9.21217823028564</v>
+        <v>9.21217918395996</v>
       </c>
       <c r="H935" t="n">
         <v>132335</v>
@@ -27513,7 +27513,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>9.88106536865234</v>
+        <v>9.88106632232666</v>
       </c>
       <c r="H936" t="n">
         <v>328350</v>
@@ -27542,7 +27542,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G937" t="n">
-        <v>9.97332668304443</v>
+        <v>9.97332763671875</v>
       </c>
       <c r="H937" t="n">
         <v>202148</v>
@@ -27571,7 +27571,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G938" t="n">
-        <v>9.99177742004395</v>
+        <v>9.99177837371826</v>
       </c>
       <c r="H938" t="n">
         <v>283851</v>
@@ -27600,7 +27600,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H939" t="n">
         <v>195612</v>
@@ -27745,7 +27745,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>10.0840377807617</v>
+        <v>10.084038734436</v>
       </c>
       <c r="H944" t="n">
         <v>156292</v>
@@ -27803,7 +27803,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H946" t="n">
         <v>131456</v>
@@ -27832,7 +27832,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G947" t="n">
-        <v>9.61351203918457</v>
+        <v>9.61351108551025</v>
       </c>
       <c r="H947" t="n">
         <v>385751</v>
@@ -27861,7 +27861,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886806488037</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H948" t="n">
         <v>129728</v>
@@ -27890,7 +27890,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>9.61351203918457</v>
+        <v>9.61351108551025</v>
       </c>
       <c r="H949" t="n">
         <v>82832</v>
@@ -27948,7 +27948,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G951" t="n">
-        <v>9.53047752380371</v>
+        <v>9.53047657012939</v>
       </c>
       <c r="H951" t="n">
         <v>116133</v>
@@ -27977,7 +27977,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886806488037</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H952" t="n">
         <v>80416</v>
@@ -28006,7 +28006,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G953" t="n">
-        <v>9.79803276062012</v>
+        <v>9.7980318069458</v>
       </c>
       <c r="H953" t="n">
         <v>64831</v>
@@ -28035,7 +28035,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G954" t="n">
-        <v>9.56738090515137</v>
+        <v>9.56738185882568</v>
       </c>
       <c r="H954" t="n">
         <v>113957</v>
@@ -28064,7 +28064,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>9.5766077041626</v>
+        <v>9.57660865783691</v>
       </c>
       <c r="H955" t="n">
         <v>120004</v>
@@ -28122,7 +28122,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>9.39208698272705</v>
+        <v>9.39208793640137</v>
       </c>
       <c r="H957" t="n">
         <v>68256</v>
@@ -28151,7 +28151,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G958" t="n">
-        <v>9.65041637420654</v>
+        <v>9.65041542053223</v>
       </c>
       <c r="H958" t="n">
         <v>160776</v>
@@ -28209,7 +28209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>9.31827926635742</v>
+        <v>9.31827831268311</v>
       </c>
       <c r="H960" t="n">
         <v>109157</v>
@@ -28325,7 +28325,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G964" t="n">
-        <v>9.88106536865234</v>
+        <v>9.88106632232666</v>
       </c>
       <c r="H964" t="n">
         <v>91898</v>
@@ -28441,7 +28441,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G968" t="n">
-        <v>10.2777853012085</v>
+        <v>10.2777862548828</v>
       </c>
       <c r="H968" t="n">
         <v>321790</v>
@@ -28470,7 +28470,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655860900879</v>
+        <v>10.0655851364136</v>
       </c>
       <c r="H969" t="n">
         <v>218375</v>
@@ -28499,7 +28499,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822448730469</v>
+        <v>10.5822439193726</v>
       </c>
       <c r="H970" t="n">
         <v>229401</v>
@@ -28557,7 +28557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>10.2870101928711</v>
+        <v>10.2870111465454</v>
       </c>
       <c r="H972" t="n">
         <v>436417</v>
@@ -28760,7 +28760,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337017059326</v>
+        <v>12.2337007522583</v>
       </c>
       <c r="H979" t="n">
         <v>516034</v>
@@ -28876,7 +28876,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G983" t="n">
-        <v>12.1414403915405</v>
+        <v>12.1414413452148</v>
       </c>
       <c r="H983" t="n">
         <v>156365</v>
@@ -28963,7 +28963,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G986" t="n">
-        <v>11.9661474227905</v>
+        <v>11.9661464691162</v>
       </c>
       <c r="H986" t="n">
         <v>115543</v>
@@ -28992,7 +28992,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G987" t="n">
-        <v>11.956919670105</v>
+        <v>11.9569206237793</v>
       </c>
       <c r="H987" t="n">
         <v>141835</v>
@@ -29021,7 +29021,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>11.7539482116699</v>
+        <v>11.7539472579956</v>
       </c>
       <c r="H988" t="n">
         <v>186372</v>
@@ -29195,7 +29195,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G994" t="n">
-        <v>13.2577886581421</v>
+        <v>13.2577896118164</v>
       </c>
       <c r="H994" t="n">
         <v>641567</v>
@@ -29253,7 +29253,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G996" t="n">
-        <v>13.0824956893921</v>
+        <v>13.0824947357178</v>
       </c>
       <c r="H996" t="n">
         <v>236235</v>
@@ -29369,7 +29369,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7559928894043</v>
+        <v>13.7559938430786</v>
       </c>
       <c r="H1000" t="n">
         <v>343538</v>
@@ -29543,7 +29543,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283163070679</v>
+        <v>13.7283153533936</v>
       </c>
       <c r="H1006" t="n">
         <v>219263</v>
@@ -29601,7 +29601,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.1342620849609</v>
+        <v>14.1342611312866</v>
       </c>
       <c r="H1008" t="n">
         <v>148543</v>
@@ -29688,7 +29688,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1011" t="n">
         <v>66991</v>
@@ -29717,7 +29717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.6637353897095</v>
+        <v>13.6637344360352</v>
       </c>
       <c r="H1012" t="n">
         <v>165683</v>
@@ -29746,7 +29746,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.6637353897095</v>
+        <v>13.6637344360352</v>
       </c>
       <c r="H1013" t="n">
         <v>84386</v>
@@ -29775,7 +29775,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.682186126709</v>
+        <v>13.6821851730347</v>
       </c>
       <c r="H1014" t="n">
         <v>59957</v>
@@ -29804,7 +29804,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.7006378173828</v>
+        <v>13.7006387710571</v>
       </c>
       <c r="H1015" t="n">
         <v>89461</v>
@@ -29920,7 +29920,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.682186126709</v>
+        <v>13.6821851730347</v>
       </c>
       <c r="H1019" t="n">
         <v>108242</v>
@@ -30036,7 +30036,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1023" t="n">
         <v>109674</v>
@@ -30065,7 +30065,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0327749252319</v>
+        <v>14.0327739715576</v>
       </c>
       <c r="H1024" t="n">
         <v>138602</v>
@@ -30123,7 +30123,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6473264694214</v>
+        <v>15.6473274230957</v>
       </c>
       <c r="H1026" t="n">
         <v>1111920</v>
@@ -30152,7 +30152,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303628921509</v>
+        <v>15.7303609848022</v>
       </c>
       <c r="H1027" t="n">
         <v>948892</v>
@@ -30268,7 +30268,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.7452220916748</v>
+        <v>16.7452239990234</v>
       </c>
       <c r="H1031" t="n">
         <v>202159</v>
@@ -30297,7 +30297,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.8190307617188</v>
+        <v>16.8190326690674</v>
       </c>
       <c r="H1032" t="n">
         <v>152525</v>
@@ -30413,7 +30413,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720335006714</v>
+        <v>15.4720344543457</v>
       </c>
       <c r="H1036" t="n">
         <v>234914</v>
@@ -30442,7 +30442,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.6785955429077</v>
+        <v>14.678596496582</v>
       </c>
       <c r="H1037" t="n">
         <v>251460</v>
@@ -30471,7 +30471,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.3187818527222</v>
+        <v>14.3187808990479</v>
       </c>
       <c r="H1038" t="n">
         <v>248886</v>
@@ -30500,7 +30500,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8446645736694</v>
+        <v>14.8446636199951</v>
       </c>
       <c r="H1039" t="n">
         <v>220373</v>
@@ -30558,7 +30558,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.204478263855</v>
+        <v>15.2044792175293</v>
       </c>
       <c r="H1041" t="n">
         <v>120054</v>
@@ -30587,7 +30587,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247247695923</v>
       </c>
       <c r="H1042" t="n">
         <v>250873</v>
@@ -30616,7 +30616,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247247695923</v>
       </c>
       <c r="H1043" t="n">
         <v>139842</v>
@@ -30674,7 +30674,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.1491241455078</v>
+        <v>15.1491231918335</v>
       </c>
       <c r="H1045" t="n">
         <v>133980</v>
@@ -30703,7 +30703,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506093978882</v>
+        <v>15.2506084442139</v>
       </c>
       <c r="H1046" t="n">
         <v>126441</v>
@@ -30761,7 +30761,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.1583490371704</v>
+        <v>15.1583471298218</v>
       </c>
       <c r="H1048" t="n">
         <v>75769</v>
@@ -30790,7 +30790,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.204478263855</v>
+        <v>15.2044792175293</v>
       </c>
       <c r="H1049" t="n">
         <v>166255</v>
@@ -30819,7 +30819,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.0753154754639</v>
+        <v>15.0753145217896</v>
       </c>
       <c r="H1050" t="n">
         <v>149710</v>
@@ -30877,7 +30877,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.1065826416016</v>
+        <v>14.1065835952759</v>
       </c>
       <c r="H1052" t="n">
         <v>295239</v>
@@ -30906,7 +30906,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>12.6027421951294</v>
+        <v>12.6027412414551</v>
       </c>
       <c r="H1053" t="n">
         <v>435284</v>
@@ -30935,7 +30935,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399551391602</v>
+        <v>12.0399541854858</v>
       </c>
       <c r="H1054" t="n">
         <v>314929</v>
@@ -31051,7 +31051,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.6006956100464</v>
+        <v>10.6006946563721</v>
       </c>
       <c r="H1058" t="n">
         <v>282297</v>
@@ -31109,7 +31109,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.1301689147949</v>
+        <v>10.1301679611206</v>
       </c>
       <c r="H1060" t="n">
         <v>421008</v>
@@ -31138,7 +31138,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.79803276062012</v>
+        <v>9.7980318069458</v>
       </c>
       <c r="H1061" t="n">
         <v>252887</v>
@@ -31196,7 +31196,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>8.06353950500488</v>
+        <v>8.0635404586792</v>
       </c>
       <c r="H1063" t="n">
         <v>362042</v>
@@ -31225,7 +31225,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.9758939743042</v>
+        <v>7.97589302062988</v>
       </c>
       <c r="H1064" t="n">
         <v>361762</v>
@@ -31254,7 +31254,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.89285898208618</v>
+        <v>7.8928599357605</v>
       </c>
       <c r="H1065" t="n">
         <v>433976</v>
@@ -31312,7 +31312,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.93796634674072</v>
+        <v>6.93796586990356</v>
       </c>
       <c r="H1067" t="n">
         <v>314093</v>
@@ -31370,7 +31370,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409605026245</v>
+        <v>6.98409652709961</v>
       </c>
       <c r="H1069" t="n">
         <v>157083</v>
@@ -31399,7 +31399,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.91028785705566</v>
+        <v>6.91028833389282</v>
       </c>
       <c r="H1070" t="n">
         <v>106846</v>
@@ -31573,7 +31573,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.01382160186768</v>
+        <v>9.01382064819336</v>
       </c>
       <c r="H1076" t="n">
         <v>132675</v>
@@ -31718,7 +31718,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.11889553070068</v>
+        <v>8.118896484375</v>
       </c>
       <c r="H1081" t="n">
         <v>72725</v>
@@ -31747,7 +31747,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.74985504150391</v>
+        <v>7.74985551834106</v>
       </c>
       <c r="H1082" t="n">
         <v>71777</v>
@@ -31776,7 +31776,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.92976331710815</v>
+        <v>7.929762840271</v>
       </c>
       <c r="H1083" t="n">
         <v>60718</v>
@@ -31805,7 +31805,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675889968872</v>
+        <v>7.78675937652588</v>
       </c>
       <c r="H1084" t="n">
         <v>156268</v>
@@ -31834,7 +31834,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.10966968536377</v>
+        <v>8.10967063903809</v>
       </c>
       <c r="H1085" t="n">
         <v>65803</v>
@@ -31863,7 +31863,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.89285898208618</v>
+        <v>7.8928599357605</v>
       </c>
       <c r="H1086" t="n">
         <v>212254</v>
@@ -32095,7 +32095,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.33468532562256</v>
+        <v>7.3346848487854</v>
       </c>
       <c r="H1094" t="n">
         <v>117087</v>
@@ -32153,7 +32153,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.55610942840576</v>
+        <v>7.5561089515686</v>
       </c>
       <c r="H1096" t="n">
         <v>241778</v>
@@ -32182,7 +32182,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.77753353118896</v>
+        <v>7.77753400802612</v>
       </c>
       <c r="H1097" t="n">
         <v>226363</v>
@@ -32240,7 +32240,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.60223913192749</v>
+        <v>7.60223960876465</v>
       </c>
       <c r="H1099" t="n">
         <v>152629</v>
@@ -32269,7 +32269,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.33929777145386</v>
+        <v>7.33929824829102</v>
       </c>
       <c r="H1100" t="n">
         <v>190738</v>
@@ -32298,7 +32298,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920557022095</v>
+        <v>7.51920509338379</v>
       </c>
       <c r="H1101" t="n">
         <v>66663</v>
@@ -32327,7 +32327,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.3070068359375</v>
+        <v>7.30700635910034</v>
       </c>
       <c r="H1102" t="n">
         <v>85960</v>
@@ -32385,7 +32385,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403490066528</v>
+        <v>7.10403442382812</v>
       </c>
       <c r="H1104" t="n">
         <v>88763</v>
@@ -32414,7 +32414,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.15939092636108</v>
+        <v>7.15939044952393</v>
       </c>
       <c r="H1105" t="n">
         <v>90167</v>
@@ -32443,7 +32443,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.3070068359375</v>
+        <v>7.30700635910034</v>
       </c>
       <c r="H1106" t="n">
         <v>150317</v>
@@ -32472,7 +32472,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.06713104248047</v>
+        <v>7.06713056564331</v>
       </c>
       <c r="H1107" t="n">
         <v>140089</v>
@@ -32501,7 +32501,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874002456665</v>
+        <v>6.92874050140381</v>
       </c>
       <c r="H1108" t="n">
         <v>182143</v>
@@ -32559,7 +32559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533479690552</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1110" t="n">
         <v>160774</v>
@@ -32588,7 +32588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533479690552</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1111" t="n">
         <v>124418</v>
@@ -32617,7 +32617,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.54227018356323</v>
+        <v>7.54227066040039</v>
       </c>
       <c r="H1112" t="n">
         <v>115707</v>
@@ -32646,7 +32646,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.44539737701416</v>
+        <v>7.445396900177</v>
       </c>
       <c r="H1113" t="n">
         <v>89200</v>
@@ -32675,7 +32675,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010250091553</v>
+        <v>7.27010297775269</v>
       </c>
       <c r="H1114" t="n">
         <v>241372</v>
@@ -32704,7 +32704,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217750549316</v>
+        <v>7.72217798233032</v>
       </c>
       <c r="H1115" t="n">
         <v>329478</v>
@@ -32733,7 +32733,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948623657227</v>
+        <v>8.46948528289795</v>
       </c>
       <c r="H1116" t="n">
         <v>379600</v>
@@ -32791,7 +32791,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310764312744</v>
+        <v>8.90310668945312</v>
       </c>
       <c r="H1118" t="n">
         <v>292199</v>
@@ -32878,7 +32878,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.8754301071167</v>
+        <v>8.87543106079102</v>
       </c>
       <c r="H1121" t="n">
         <v>174840</v>
@@ -32994,7 +32994,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.4956197738647</v>
+        <v>11.4956188201904</v>
       </c>
       <c r="H1125" t="n">
         <v>412132</v>
@@ -33023,7 +33023,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>11.2557420730591</v>
+        <v>11.2557430267334</v>
       </c>
       <c r="H1126" t="n">
         <v>312966</v>
@@ -33052,7 +33052,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420566558838</v>
+        <v>10.9420576095581</v>
       </c>
       <c r="H1127" t="n">
         <v>171397</v>
@@ -33081,7 +33081,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.82570934295654</v>
+        <v>9.82571029663086</v>
       </c>
       <c r="H1128" t="n">
         <v>371295</v>
@@ -33110,7 +33110,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.82570934295654</v>
+        <v>9.82571029663086</v>
       </c>
       <c r="H1129" t="n">
         <v>254965</v>
@@ -33342,7 +33342,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792715072632</v>
+        <v>10.3792705535889</v>
       </c>
       <c r="H1137" t="n">
         <v>258796</v>
@@ -33400,7 +33400,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.1301689147949</v>
+        <v>10.1301679611206</v>
       </c>
       <c r="H1139" t="n">
         <v>131328</v>
@@ -33429,7 +33429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.3700456619263</v>
+        <v>10.370044708252</v>
       </c>
       <c r="H1140" t="n">
         <v>116026</v>
@@ -33516,7 +33516,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1143" t="n">
-        <v>10.674503326416</v>
+        <v>10.6745042800903</v>
       </c>
       <c r="H1143" t="n">
         <v>240355</v>
@@ -33603,7 +33603,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667646408081</v>
+        <v>10.7667636871338</v>
       </c>
       <c r="H1146" t="n">
         <v>215683</v>
@@ -33690,7 +33690,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.5417499542236</v>
+        <v>11.5417509078979</v>
       </c>
       <c r="H1149" t="n">
         <v>248313</v>
@@ -33777,7 +33777,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.818531036377</v>
+        <v>11.8185300827026</v>
       </c>
       <c r="H1152" t="n">
         <v>187197</v>
@@ -33835,7 +33835,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.818531036377</v>
+        <v>11.8185300827026</v>
       </c>
       <c r="H1154" t="n">
         <v>76721</v>
@@ -33864,7 +33864,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.7539482116699</v>
+        <v>11.7539472579956</v>
       </c>
       <c r="H1155" t="n">
         <v>263178</v>
@@ -33980,7 +33980,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.3480033874512</v>
+        <v>11.3480024337769</v>
       </c>
       <c r="H1159" t="n">
         <v>167840</v>
@@ -34154,7 +34154,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0030508041382</v>
+        <v>12.0030517578125</v>
       </c>
       <c r="H1165" t="n">
         <v>386906</v>
@@ -34241,7 +34241,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.7042284011841</v>
+        <v>12.7042293548584</v>
       </c>
       <c r="H1168" t="n">
         <v>224535</v>
@@ -34270,7 +34270,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.0548152923584</v>
+        <v>13.0548162460327</v>
       </c>
       <c r="H1169" t="n">
         <v>208552</v>
@@ -34299,7 +34299,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.0548152923584</v>
+        <v>13.0548162460327</v>
       </c>
       <c r="H1170" t="n">
         <v>98947</v>
@@ -34328,7 +34328,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961801528931</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1171" t="n">
         <v>197304</v>
@@ -34415,7 +34415,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.2577886581421</v>
+        <v>13.2577896118164</v>
       </c>
       <c r="H1174" t="n">
         <v>91618</v>
@@ -34502,7 +34502,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.230110168457</v>
+        <v>13.2301111221313</v>
       </c>
       <c r="H1177" t="n">
         <v>59759</v>
@@ -34560,7 +34560,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.1932077407837</v>
+        <v>13.1932067871094</v>
       </c>
       <c r="H1179" t="n">
         <v>142039</v>
@@ -34618,7 +34618,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500509262085</v>
+        <v>13.3500499725342</v>
       </c>
       <c r="H1181" t="n">
         <v>113455</v>
@@ -34647,7 +34647,7 @@
         <v>15</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H1182" t="n">
         <v>172704</v>
@@ -34676,7 +34676,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714740753174</v>
+        <v>13.5714750289917</v>
       </c>
       <c r="H1183" t="n">
         <v>86309</v>
@@ -34792,7 +34792,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.4976663589478</v>
+        <v>13.4976654052734</v>
       </c>
       <c r="H1187" t="n">
         <v>194560</v>
@@ -34821,7 +34821,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.1101722717285</v>
+        <v>13.1101732254028</v>
       </c>
       <c r="H1188" t="n">
         <v>183776</v>
@@ -34850,7 +34850,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>13.1932077407837</v>
+        <v>13.1932067871094</v>
       </c>
       <c r="H1189" t="n">
         <v>112671</v>
@@ -34908,7 +34908,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1191" t="n">
-        <v>13.1655282974243</v>
+        <v>13.1655292510986</v>
       </c>
       <c r="H1191" t="n">
         <v>114078</v>
@@ -34966,7 +34966,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1193" t="n">
-        <v>13.230110168457</v>
+        <v>13.2301111221313</v>
       </c>
       <c r="H1193" t="n">
         <v>90522</v>
@@ -35053,7 +35053,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.0455904006958</v>
+        <v>13.0455894470215</v>
       </c>
       <c r="H1196" t="n">
         <v>83647</v>
@@ -35082,7 +35082,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.1747541427612</v>
+        <v>13.1747550964355</v>
       </c>
       <c r="H1197" t="n">
         <v>81797</v>
@@ -35111,7 +35111,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.331597328186</v>
+        <v>13.3315963745117</v>
       </c>
       <c r="H1198" t="n">
         <v>81183</v>
@@ -35198,7 +35198,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.3813161849976</v>
+        <v>12.3813171386719</v>
       </c>
       <c r="H1201" t="n">
         <v>204999</v>
@@ -35227,7 +35227,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6304197311401</v>
+        <v>12.6304187774658</v>
       </c>
       <c r="H1202" t="n">
         <v>101665</v>
@@ -35430,7 +35430,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330825805664</v>
+        <v>13.4330835342407</v>
       </c>
       <c r="H1209" t="n">
         <v>134522</v>
@@ -35459,7 +35459,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.4515352249146</v>
+        <v>13.4515342712402</v>
       </c>
       <c r="H1210" t="n">
         <v>167243</v>
@@ -35517,7 +35517,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>15.2690601348877</v>
+        <v>15.2690591812134</v>
       </c>
       <c r="H1212" t="n">
         <v>617005</v>
@@ -35546,7 +35546,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735177993774</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1213" t="n">
         <v>405514</v>
@@ -35662,7 +35662,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628076553345</v>
+        <v>15.4628086090088</v>
       </c>
       <c r="H1217" t="n">
         <v>170488</v>
@@ -35691,7 +35691,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232404708862</v>
       </c>
       <c r="H1218" t="n">
         <v>281974</v>
@@ -35807,7 +35807,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>14.5955619812012</v>
+        <v>14.5955610275269</v>
       </c>
       <c r="H1222" t="n">
         <v>167540</v>
@@ -36010,7 +36010,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>13.6545076370239</v>
+        <v>13.6545085906982</v>
       </c>
       <c r="H1229" t="n">
         <v>211009</v>
@@ -36039,7 +36039,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033016204834</v>
+        <v>14.5033025741577</v>
       </c>
       <c r="H1230" t="n">
         <v>232002</v>
@@ -36126,7 +36126,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735177993774</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1233" t="n">
         <v>375133</v>
@@ -36213,7 +36213,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.4166765213013</v>
+        <v>15.4166774749756</v>
       </c>
       <c r="H1236" t="n">
         <v>175438</v>
@@ -36242,7 +36242,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G1237" t="n">
-        <v>15.1029930114746</v>
+        <v>15.1029939651489</v>
       </c>
       <c r="H1237" t="n">
         <v>167525</v>
@@ -36271,7 +36271,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184722900391</v>
+        <v>14.9184732437134</v>
       </c>
       <c r="H1238" t="n">
         <v>69332</v>
@@ -36329,7 +36329,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764930725098</v>
+        <v>15.7764940261841</v>
       </c>
       <c r="H1240" t="n">
         <v>178894</v>
@@ -36358,7 +36358,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827465057373</v>
+        <v>15.5827445983887</v>
       </c>
       <c r="H1241" t="n">
         <v>78857</v>
@@ -36416,7 +36416,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.8133964538574</v>
+        <v>15.8133945465088</v>
       </c>
       <c r="H1243" t="n">
         <v>116062</v>
@@ -36445,7 +36445,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410758972168</v>
+        <v>15.8410739898682</v>
       </c>
       <c r="H1244" t="n">
         <v>51279</v>
@@ -36648,7 +36648,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>15.6381015777588</v>
+        <v>15.6381034851074</v>
       </c>
       <c r="H1251" t="n">
         <v>64739</v>
@@ -36677,7 +36677,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351282119751</v>
+        <v>15.4351301193237</v>
       </c>
       <c r="H1252" t="n">
         <v>60423</v>
@@ -36706,7 +36706,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919713973999</v>
+        <v>15.5919704437256</v>
       </c>
       <c r="H1253" t="n">
         <v>50800</v>
@@ -36735,7 +36735,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>15.8133964538574</v>
+        <v>15.8133945465088</v>
       </c>
       <c r="H1254" t="n">
         <v>89575</v>
@@ -36764,7 +36764,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>15.6381015777588</v>
+        <v>15.6381034851074</v>
       </c>
       <c r="H1255" t="n">
         <v>69044</v>
@@ -36793,7 +36793,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517879486084</v>
+        <v>15.9517860412598</v>
       </c>
       <c r="H1256" t="n">
         <v>77596</v>
@@ -36822,7 +36822,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.0994033813477</v>
+        <v>16.099401473999</v>
       </c>
       <c r="H1257" t="n">
         <v>135906</v>
@@ -36880,7 +36880,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>16.0717258453369</v>
+        <v>16.0717239379883</v>
       </c>
       <c r="H1259" t="n">
         <v>62766</v>
@@ -36967,7 +36967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.3910446166992</v>
+        <v>17.3910465240479</v>
       </c>
       <c r="H1262" t="n">
         <v>199105</v>
@@ -37054,7 +37054,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>17.1142654418945</v>
+        <v>17.1142635345459</v>
       </c>
       <c r="H1265" t="n">
         <v>144721</v>
@@ -37141,7 +37141,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.446403503418</v>
+        <v>17.4464015960693</v>
       </c>
       <c r="H1268" t="n">
         <v>107802</v>
@@ -37170,7 +37170,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1269" t="n">
-        <v>17.5663414001465</v>
+        <v>17.5663394927979</v>
       </c>
       <c r="H1269" t="n">
         <v>89128</v>
@@ -37228,7 +37228,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.6216945648193</v>
+        <v>17.621696472168</v>
       </c>
       <c r="H1271" t="n">
         <v>125434</v>
@@ -37257,7 +37257,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.5478858947754</v>
+        <v>17.547887802124</v>
       </c>
       <c r="H1272" t="n">
         <v>81241</v>
@@ -37315,7 +37315,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.415132522583</v>
+        <v>18.4151306152344</v>
       </c>
       <c r="H1274" t="n">
         <v>123597</v>
@@ -37344,7 +37344,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.7657222747803</v>
+        <v>18.7657203674316</v>
       </c>
       <c r="H1275" t="n">
         <v>142765</v>
@@ -37402,7 +37402,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>19.9835548400879</v>
+        <v>19.9835567474365</v>
       </c>
       <c r="H1277" t="n">
         <v>153145</v>
@@ -37489,7 +37489,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>18.728816986084</v>
+        <v>18.7288150787354</v>
       </c>
       <c r="H1280" t="n">
         <v>138251</v>
@@ -37518,7 +37518,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="n">
-        <v>19.2454738616943</v>
+        <v>19.245475769043</v>
       </c>
       <c r="H1281" t="n">
         <v>104819</v>
@@ -37576,7 +37576,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377361297607</v>
+        <v>19.3377342224121</v>
       </c>
       <c r="H1283" t="n">
         <v>45421</v>
@@ -37605,7 +37605,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.2639274597168</v>
+        <v>19.2639255523682</v>
       </c>
       <c r="H1284" t="n">
         <v>44320</v>
@@ -37634,7 +37634,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="n">
-        <v>19.2639274597168</v>
+        <v>19.2639255523682</v>
       </c>
       <c r="H1285" t="n">
         <v>59633</v>
@@ -37721,7 +37721,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="n">
-        <v>18.2029342651367</v>
+        <v>18.2029361724854</v>
       </c>
       <c r="H1288" t="n">
         <v>161850</v>
@@ -37779,7 +37779,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="n">
-        <v>17.972282409668</v>
+        <v>17.9722843170166</v>
       </c>
       <c r="H1290" t="n">
         <v>74769</v>
@@ -37808,7 +37808,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.1844825744629</v>
+        <v>18.1844806671143</v>
       </c>
       <c r="H1291" t="n">
         <v>67860</v>
@@ -37895,7 +37895,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.6109237670898</v>
+        <v>20.6109256744385</v>
       </c>
       <c r="H1294" t="n">
         <v>103797</v>
@@ -37953,7 +37953,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="n">
-        <v>21.2567462921143</v>
+        <v>21.2567481994629</v>
       </c>
       <c r="H1296" t="n">
         <v>150867</v>
@@ -37982,7 +37982,7 @@
         <v>23</v>
       </c>
       <c r="G1297" t="n">
-        <v>21.2198429107666</v>
+        <v>21.2198448181152</v>
       </c>
       <c r="H1297" t="n">
         <v>87493</v>
@@ -38011,7 +38011,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>21.312105178833</v>
+        <v>21.3121032714844</v>
       </c>
       <c r="H1298" t="n">
         <v>54089</v>
@@ -38069,7 +38069,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.2567462921143</v>
+        <v>21.2567481994629</v>
       </c>
       <c r="H1300" t="n">
         <v>61853</v>
@@ -38127,7 +38127,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>22.7698173522949</v>
+        <v>22.7698154449463</v>
       </c>
       <c r="H1302" t="n">
         <v>125679</v>
@@ -38214,7 +38214,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745845794678</v>
+        <v>22.4745826721191</v>
       </c>
       <c r="H1305" t="n">
         <v>45171</v>
@@ -38301,7 +38301,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.6293773651123</v>
+        <v>20.6293754577637</v>
       </c>
       <c r="H1308" t="n">
         <v>73684</v>
@@ -38359,7 +38359,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.1865272521973</v>
+        <v>20.1865291595459</v>
       </c>
       <c r="H1310" t="n">
         <v>87245</v>
@@ -38446,7 +38446,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="n">
-        <v>21.2013912200928</v>
+        <v>21.2013893127441</v>
       </c>
       <c r="H1313" t="n">
         <v>97639</v>
@@ -38620,7 +38620,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.1091289520264</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1319" t="n">
         <v>59299</v>
@@ -38649,7 +38649,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.1091289520264</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1320" t="n">
         <v>52297</v>
@@ -38707,7 +38707,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.9835548400879</v>
+        <v>19.9835567474365</v>
       </c>
       <c r="H1322" t="n">
         <v>182976</v>
@@ -38736,7 +38736,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.9466533660889</v>
+        <v>19.9466552734375</v>
       </c>
       <c r="H1323" t="n">
         <v>137347</v>
@@ -38765,7 +38765,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1324" t="n">
         <v>133244</v>
@@ -38794,7 +38794,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.1127223968506</v>
+        <v>20.112720489502</v>
       </c>
       <c r="H1325" t="n">
         <v>134502</v>
@@ -38881,7 +38881,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1328" t="n">
         <v>213744</v>
@@ -38910,7 +38910,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1329" t="n">
         <v>111615</v>
@@ -38939,7 +38939,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1330" t="n">
         <v>74044</v>
@@ -39113,7 +39113,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="n">
-        <v>22.1424465179443</v>
+        <v>22.1424446105957</v>
       </c>
       <c r="H1336" t="n">
         <v>58817</v>
@@ -39200,7 +39200,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317306518555</v>
+        <v>22.0317325592041</v>
       </c>
       <c r="H1339" t="n">
         <v>111019</v>
@@ -39374,7 +39374,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>23.0465927124023</v>
+        <v>23.046594619751</v>
       </c>
       <c r="H1345" t="n">
         <v>113640</v>
@@ -39490,7 +39490,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971862792969</v>
+        <v>23.3971843719482</v>
       </c>
       <c r="H1349" t="n">
         <v>78530</v>
@@ -39519,7 +39519,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817012786865</v>
+        <v>23.5817031860352</v>
       </c>
       <c r="H1350" t="n">
         <v>51355</v>
@@ -39664,7 +39664,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.3454170227051</v>
+        <v>22.3454151153564</v>
       </c>
       <c r="H1355" t="n">
         <v>127437</v>
@@ -39693,7 +39693,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.4894409179688</v>
+        <v>23.4894428253174</v>
       </c>
       <c r="H1356" t="n">
         <v>126113</v>
@@ -39780,7 +39780,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662239074707</v>
+        <v>23.7662220001221</v>
       </c>
       <c r="H1359" t="n">
         <v>240302</v>
@@ -39867,7 +39867,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="n">
-        <v>23.6370620727539</v>
+        <v>23.6370601654053</v>
       </c>
       <c r="H1362" t="n">
         <v>264460</v>
@@ -39925,7 +39925,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1364" t="n">
         <v>236072</v>
@@ -39983,7 +39983,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>26.4786739349365</v>
+        <v>26.4786758422852</v>
       </c>
       <c r="H1366" t="n">
         <v>262217</v>
@@ -40012,7 +40012,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1367" t="n">
         <v>280231</v>
@@ -40041,7 +40041,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>27.1613998413086</v>
+        <v>27.1614017486572</v>
       </c>
       <c r="H1368" t="n">
         <v>189145</v>
@@ -40070,7 +40070,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="n">
-        <v>27.3828220367432</v>
+        <v>27.3828239440918</v>
       </c>
       <c r="H1369" t="n">
         <v>120408</v>
@@ -40215,7 +40215,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721099853516</v>
+        <v>27.2721118927002</v>
       </c>
       <c r="H1374" t="n">
         <v>176103</v>
@@ -40273,7 +40273,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>27.3828220367432</v>
+        <v>27.3828239440918</v>
       </c>
       <c r="H1376" t="n">
         <v>44639</v>
@@ -40302,7 +40302,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>27.4012756347656</v>
+        <v>27.4012775421143</v>
       </c>
       <c r="H1377" t="n">
         <v>73760</v>
@@ -40331,7 +40331,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="n">
-        <v>27.1060447692871</v>
+        <v>27.1060428619385</v>
       </c>
       <c r="H1378" t="n">
         <v>74735</v>
@@ -40360,7 +40360,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="n">
-        <v>26.9030704498291</v>
+        <v>26.9030685424805</v>
       </c>
       <c r="H1379" t="n">
         <v>72804</v>
@@ -40418,7 +40418,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>25.9251098632812</v>
+        <v>25.9251117706299</v>
       </c>
       <c r="H1381" t="n">
         <v>64116</v>
@@ -40447,7 +40447,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="n">
-        <v>25.7221412658691</v>
+        <v>25.7221393585205</v>
       </c>
       <c r="H1382" t="n">
         <v>121764</v>
@@ -40534,7 +40534,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="n">
-        <v>26.4602203369141</v>
+        <v>26.4602222442627</v>
       </c>
       <c r="H1385" t="n">
         <v>51146</v>
@@ -40563,7 +40563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>26.3864154815674</v>
+        <v>26.3864135742188</v>
       </c>
       <c r="H1386" t="n">
         <v>54044</v>
@@ -40592,7 +40592,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="n">
-        <v>25.9989204406738</v>
+        <v>25.9989223480225</v>
       </c>
       <c r="H1387" t="n">
         <v>84386</v>
@@ -40621,7 +40621,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>25.5007152557373</v>
+        <v>25.5007133483887</v>
       </c>
       <c r="H1388" t="n">
         <v>89097</v>
@@ -40708,7 +40708,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="n">
-        <v>25.7221412658691</v>
+        <v>25.7221393585205</v>
       </c>
       <c r="H1391" t="n">
         <v>36786</v>
@@ -40824,7 +40824,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>26.6631946563721</v>
+        <v>26.6631927490234</v>
       </c>
       <c r="H1395" t="n">
         <v>88982</v>
@@ -40853,7 +40853,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>25.9989204406738</v>
+        <v>25.9989223480225</v>
       </c>
       <c r="H1396" t="n">
         <v>59600</v>
@@ -40882,7 +40882,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="n">
-        <v>26.3310565948486</v>
+        <v>26.3310585021973</v>
       </c>
       <c r="H1397" t="n">
         <v>52161</v>
@@ -40911,7 +40911,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="n">
-        <v>26.4602203369141</v>
+        <v>26.4602222442627</v>
       </c>
       <c r="H1398" t="n">
         <v>26653</v>
@@ -40940,7 +40940,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="n">
-        <v>26.5155773162842</v>
+        <v>26.5155792236328</v>
       </c>
       <c r="H1399" t="n">
         <v>89298</v>
@@ -40969,7 +40969,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="n">
-        <v>25.9251098632812</v>
+        <v>25.9251117706299</v>
       </c>
       <c r="H1400" t="n">
         <v>40818</v>
@@ -41027,7 +41027,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="n">
-        <v>25.4453601837158</v>
+        <v>25.4453620910645</v>
       </c>
       <c r="H1402" t="n">
         <v>72975</v>
@@ -41288,7 +41288,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="n">
-        <v>26.5155773162842</v>
+        <v>26.5155792236328</v>
       </c>
       <c r="H1411" t="n">
         <v>78798</v>
@@ -41375,7 +41375,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750862121582</v>
+        <v>27.4750843048096</v>
       </c>
       <c r="H1414" t="n">
         <v>54200</v>
@@ -41491,7 +41491,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="n">
-        <v>29.5970687866211</v>
+        <v>29.5970706939697</v>
       </c>
       <c r="H1418" t="n">
         <v>191826</v>
@@ -41636,7 +41636,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923603057861</v>
+        <v>26.7923583984375</v>
       </c>
       <c r="H1423" t="n">
         <v>119595</v>
@@ -41723,7 +41723,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994789123535</v>
+        <v>27.8994808197021</v>
       </c>
       <c r="H1426" t="n">
         <v>102901</v>
@@ -41752,7 +41752,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>27.5857963562012</v>
+        <v>27.5857944488525</v>
       </c>
       <c r="H1427" t="n">
         <v>51172</v>
@@ -41781,7 +41781,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="n">
-        <v>27.2352085113525</v>
+        <v>27.2352066040039</v>
       </c>
       <c r="H1428" t="n">
         <v>56869</v>
@@ -41810,7 +41810,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1429" t="n">
         <v>76852</v>
@@ -41839,7 +41839,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1430" t="n">
         <v>75930</v>
@@ -41868,7 +41868,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="n">
-        <v>27.364372253418</v>
+        <v>27.3643703460693</v>
       </c>
       <c r="H1431" t="n">
         <v>81630</v>
@@ -41897,7 +41897,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1432" t="n">
         <v>58614</v>
@@ -41926,7 +41926,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="n">
-        <v>26.6262912750244</v>
+        <v>26.6262893676758</v>
       </c>
       <c r="H1433" t="n">
         <v>47937</v>
@@ -41955,7 +41955,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1434" t="n">
         <v>37007</v>
@@ -41984,7 +41984,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="n">
-        <v>27.2536602020264</v>
+        <v>27.2536582946777</v>
       </c>
       <c r="H1435" t="n">
         <v>71855</v>
@@ -42042,7 +42042,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>27.3090152740479</v>
+        <v>27.3090171813965</v>
       </c>
       <c r="H1437" t="n">
         <v>40719</v>
@@ -42332,7 +42332,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="n">
-        <v>27.7518653869629</v>
+        <v>27.7518634796143</v>
       </c>
       <c r="H1447" t="n">
         <v>106881</v>
@@ -42390,7 +42390,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732875823975</v>
+        <v>27.9732894897461</v>
       </c>
       <c r="H1449" t="n">
         <v>79612</v>
@@ -42448,7 +42448,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1451" t="n">
-        <v>28.2869739532471</v>
+        <v>28.2869720458984</v>
       </c>
       <c r="H1451" t="n">
         <v>74987</v>
@@ -42477,7 +42477,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="n">
-        <v>28.0840034484863</v>
+        <v>28.0840015411377</v>
       </c>
       <c r="H1452" t="n">
         <v>49417</v>
@@ -42622,7 +42622,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.9953327178955</v>
+        <v>26.9953308105469</v>
       </c>
       <c r="H1457" t="n">
         <v>157384</v>
@@ -42651,7 +42651,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>26.220344543457</v>
+        <v>26.2203464508057</v>
       </c>
       <c r="H1458" t="n">
         <v>92706</v>
@@ -42680,7 +42680,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191688537598</v>
+        <v>25.5191669464111</v>
       </c>
       <c r="H1459" t="n">
         <v>176751</v>
@@ -42709,7 +42709,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1460" t="n">
-        <v>24.6150169372559</v>
+        <v>24.6150188446045</v>
       </c>
       <c r="H1460" t="n">
         <v>154714</v>
@@ -42883,7 +42883,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="n">
-        <v>23.3418254852295</v>
+        <v>23.3418273925781</v>
       </c>
       <c r="H1466" t="n">
         <v>110737</v>
@@ -42941,7 +42941,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971862792969</v>
+        <v>23.3971843719482</v>
       </c>
       <c r="H1468" t="n">
         <v>76657</v>
@@ -42999,7 +42999,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="n">
-        <v>24.0614566802979</v>
+        <v>24.0614547729492</v>
       </c>
       <c r="H1470" t="n">
         <v>127573</v>
@@ -43057,7 +43057,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="n">
-        <v>24.7441806793213</v>
+        <v>24.7441825866699</v>
       </c>
       <c r="H1472" t="n">
         <v>100651</v>
@@ -43115,7 +43115,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.2423896789551</v>
+        <v>25.2423877716064</v>
       </c>
       <c r="H1474" t="n">
         <v>98494</v>
@@ -43231,7 +43231,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1478" t="n">
         <v>36215</v>
@@ -43260,7 +43260,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179931640625</v>
       </c>
       <c r="H1479" t="n">
         <v>40510</v>
@@ -43347,7 +43347,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179931640625</v>
       </c>
       <c r="H1482" t="n">
         <v>79431</v>
@@ -43521,7 +43521,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.9287033081055</v>
+        <v>24.9287014007568</v>
       </c>
       <c r="H1488" t="n">
         <v>107665</v>
@@ -43550,7 +43550,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.8364410400391</v>
+        <v>24.8364429473877</v>
       </c>
       <c r="H1489" t="n">
         <v>76383</v>
@@ -43753,7 +43753,7 @@
         <v>25.5</v>
       </c>
       <c r="G1496" t="n">
-        <v>23.5263481140137</v>
+        <v>23.526346206665</v>
       </c>
       <c r="H1496" t="n">
         <v>49797</v>
@@ -43811,7 +43811,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="n">
-        <v>22.7698173522949</v>
+        <v>22.7698154449463</v>
       </c>
       <c r="H1498" t="n">
         <v>145644</v>
@@ -43898,7 +43898,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1501" t="n">
         <v>112882</v>
@@ -43927,7 +43927,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841133117676</v>
+        <v>21.8841152191162</v>
       </c>
       <c r="H1502" t="n">
         <v>111017</v>
@@ -44043,7 +44043,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.7364978790283</v>
+        <v>21.736499786377</v>
       </c>
       <c r="H1506" t="n">
         <v>138194</v>
@@ -44130,7 +44130,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1509" t="n">
         <v>177120</v>
@@ -44159,7 +44159,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="n">
-        <v>22.6591014862061</v>
+        <v>22.6590995788574</v>
       </c>
       <c r="H1510" t="n">
         <v>92110</v>
@@ -44188,7 +44188,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1511" t="n">
         <v>119930</v>
@@ -44246,7 +44246,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.1091289520264</v>
+        <v>21.109130859375</v>
       </c>
       <c r="H1513" t="n">
         <v>30601</v>
@@ -44333,7 +44333,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1516" t="n">
         <v>83075</v>
@@ -44391,7 +44391,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1518" t="n">
         <v>87616</v>
@@ -44478,7 +44478,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.9948272705078</v>
+        <v>21.9948291778564</v>
       </c>
       <c r="H1521" t="n">
         <v>112637</v>
@@ -44536,7 +44536,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.529935836792</v>
+        <v>22.5299377441406</v>
       </c>
       <c r="H1523" t="n">
         <v>282491</v>
@@ -44565,7 +44565,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>22.5114841461182</v>
+        <v>22.5114860534668</v>
       </c>
       <c r="H1524" t="n">
         <v>72450</v>
@@ -44623,7 +44623,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.529935836792</v>
+        <v>22.5299377441406</v>
       </c>
       <c r="H1526" t="n">
         <v>35005</v>
@@ -44652,7 +44652,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="n">
-        <v>23.1204013824463</v>
+        <v>23.1204032897949</v>
       </c>
       <c r="H1527" t="n">
         <v>87054</v>
@@ -44739,7 +44739,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>22.3085136413574</v>
+        <v>22.3085155487061</v>
       </c>
       <c r="H1530" t="n">
         <v>64510</v>
@@ -44768,7 +44768,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>22.5114841461182</v>
+        <v>22.5114860534668</v>
       </c>
       <c r="H1531" t="n">
         <v>40554</v>
@@ -44826,7 +44826,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674583435059</v>
+        <v>21.3674602508545</v>
       </c>
       <c r="H1533" t="n">
         <v>40625</v>
@@ -45000,7 +45000,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1539" t="n">
         <v>67442</v>
@@ -45087,7 +45087,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.928201675415</v>
+        <v>19.9281997680664</v>
       </c>
       <c r="H1542" t="n">
         <v>354066</v>
@@ -45145,7 +45145,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1544" t="n">
         <v>73711</v>
@@ -45174,7 +45174,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877067565918</v>
+        <v>20.8877086639404</v>
       </c>
       <c r="H1545" t="n">
         <v>65560</v>
@@ -45261,7 +45261,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.312105178833</v>
+        <v>21.3121032714844</v>
       </c>
       <c r="H1548" t="n">
         <v>71843</v>
@@ -45290,7 +45290,7 @@
         <v>23</v>
       </c>
       <c r="G1549" t="n">
-        <v>21.2198429107666</v>
+        <v>21.2198448181152</v>
       </c>
       <c r="H1549" t="n">
         <v>44418</v>
@@ -45435,7 +45435,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="n">
-        <v>20.8138961791992</v>
+        <v>20.8138980865479</v>
       </c>
       <c r="H1554" t="n">
         <v>258855</v>
@@ -45522,7 +45522,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.9835548400879</v>
+        <v>19.9835567474365</v>
       </c>
       <c r="H1557" t="n">
         <v>232143</v>
@@ -45580,7 +45580,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.7585430145264</v>
+        <v>20.7585411071777</v>
       </c>
       <c r="H1559" t="n">
         <v>34621</v>
@@ -45609,7 +45609,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="n">
-        <v>20.3710498809814</v>
+        <v>20.3710479736328</v>
       </c>
       <c r="H1560" t="n">
         <v>107999</v>
@@ -45638,7 +45638,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="n">
-        <v>20.0204601287842</v>
+        <v>20.0204620361328</v>
       </c>
       <c r="H1561" t="n">
         <v>57646</v>
@@ -45725,7 +45725,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.5073947906494</v>
+        <v>18.5073928833008</v>
       </c>
       <c r="H1564" t="n">
         <v>48417</v>
@@ -45783,7 +45783,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.1291236877441</v>
+        <v>18.1291255950928</v>
       </c>
       <c r="H1566" t="n">
         <v>145527</v>
@@ -45870,7 +45870,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633670806885</v>
+        <v>17.3633651733398</v>
       </c>
       <c r="H1569" t="n">
         <v>50964</v>
@@ -45928,7 +45928,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033016204834</v>
+        <v>14.5033025741577</v>
       </c>
       <c r="H1571" t="n">
         <v>197519</v>
@@ -45957,7 +45957,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.0845403671265</v>
+        <v>15.0845413208008</v>
       </c>
       <c r="H1572" t="n">
         <v>244822</v>
@@ -46044,7 +46044,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.1583490371704</v>
+        <v>15.1583471298218</v>
       </c>
       <c r="H1575" t="n">
         <v>113410</v>
@@ -46073,7 +46073,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.370548248291</v>
+        <v>15.3705472946167</v>
       </c>
       <c r="H1576" t="n">
         <v>128639</v>
@@ -46102,7 +46102,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.2377910614014</v>
+        <v>16.23779296875</v>
       </c>
       <c r="H1577" t="n">
         <v>111126</v>
@@ -46160,7 +46160,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.2172937393188</v>
+        <v>14.2172946929932</v>
       </c>
       <c r="H1579" t="n">
         <v>614742</v>
@@ -46189,7 +46189,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.0604524612427</v>
+        <v>14.0604515075684</v>
       </c>
       <c r="H1580" t="n">
         <v>242362</v>
@@ -46247,7 +46247,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878213882446</v>
+        <v>14.6878223419189</v>
       </c>
       <c r="H1582" t="n">
         <v>163036</v>
@@ -46276,7 +46276,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1583" t="n">
-        <v>14.8169851303101</v>
+        <v>14.8169860839844</v>
       </c>
       <c r="H1583" t="n">
         <v>106388</v>
@@ -46334,7 +46334,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634258270264</v>
+        <v>14.2634248733521</v>
       </c>
       <c r="H1585" t="n">
         <v>112266</v>
@@ -46421,7 +46421,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8226222991943</v>
+        <v>15.8226203918457</v>
       </c>
       <c r="H1588" t="n">
         <v>261661</v>
@@ -46537,7 +46537,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.0753154754639</v>
+        <v>15.0753145217896</v>
       </c>
       <c r="H1592" t="n">
         <v>140875</v>
@@ -46653,7 +46653,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.0327749252319</v>
+        <v>14.0327739715576</v>
       </c>
       <c r="H1596" t="n">
         <v>72466</v>
@@ -46682,7 +46682,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0420017242432</v>
+        <v>14.0420007705688</v>
       </c>
       <c r="H1597" t="n">
         <v>49196</v>
@@ -46740,7 +46740,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.8205757141113</v>
+        <v>13.8205766677856</v>
       </c>
       <c r="H1599" t="n">
         <v>68975</v>
@@ -46798,7 +46798,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1601" t="n">
         <v>45680</v>
@@ -46856,7 +46856,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247247695923</v>
       </c>
       <c r="H1603" t="n">
         <v>73059</v>
@@ -46914,7 +46914,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.8667058944702</v>
+        <v>13.8667068481445</v>
       </c>
       <c r="H1605" t="n">
         <v>46964</v>
@@ -46943,7 +46943,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="n">
-        <v>13.6176042556763</v>
+        <v>13.617603302002</v>
       </c>
       <c r="H1606" t="n">
         <v>94220</v>
@@ -47059,7 +47059,7 @@
         <v>15</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H1610" t="n">
         <v>78749</v>
@@ -47117,7 +47117,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.682186126709</v>
+        <v>13.6821851730347</v>
       </c>
       <c r="H1612" t="n">
         <v>65954</v>
@@ -47291,7 +47291,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961801528931</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1618" t="n">
         <v>99070</v>
@@ -47349,7 +47349,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476369857788</v>
+        <v>15.0476360321045</v>
       </c>
       <c r="H1620" t="n">
         <v>154501</v>
@@ -47465,7 +47465,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384111404419</v>
+        <v>15.0384101867676</v>
       </c>
       <c r="H1624" t="n">
         <v>74404</v>
@@ -47523,7 +47523,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>14.7736368179321</v>
+        <v>14.7736358642578</v>
       </c>
       <c r="H1626" t="n">
         <v>61617</v>
@@ -47697,7 +47697,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.7137775421143</v>
+        <v>15.7137765884399</v>
       </c>
       <c r="H1632" t="n">
         <v>66096</v>
@@ -47755,7 +47755,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.780930519104</v>
+        <v>15.7809314727783</v>
       </c>
       <c r="H1634" t="n">
         <v>37135</v>
@@ -47784,7 +47784,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.0303535461426</v>
+        <v>16.0303554534912</v>
       </c>
       <c r="H1635" t="n">
         <v>43698</v>
@@ -47900,7 +47900,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="n">
-        <v>14.5529909133911</v>
+        <v>14.5529918670654</v>
       </c>
       <c r="H1639" t="n">
         <v>89694</v>
@@ -47958,7 +47958,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="n">
-        <v>13.5456981658936</v>
+        <v>13.5456972122192</v>
       </c>
       <c r="H1641" t="n">
         <v>86532</v>
@@ -47987,7 +47987,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>13.843090057373</v>
+        <v>13.8430891036987</v>
       </c>
       <c r="H1642" t="n">
         <v>116898</v>
@@ -48045,7 +48045,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.1427803039551</v>
+        <v>13.1427793502808</v>
       </c>
       <c r="H1644" t="n">
         <v>169292</v>
@@ -48161,7 +48161,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="n">
-        <v>12.4040994644165</v>
+        <v>12.4040985107422</v>
       </c>
       <c r="H1648" t="n">
         <v>78173</v>
@@ -48277,7 +48277,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="n">
-        <v>12.5959644317627</v>
+        <v>12.5959634780884</v>
       </c>
       <c r="H1652" t="n">
         <v>94645</v>
@@ -48364,7 +48364,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.7805366516113</v>
+        <v>11.780535697937</v>
       </c>
       <c r="H1655" t="n">
         <v>68390</v>
@@ -48393,7 +48393,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="n">
-        <v>11.5502986907959</v>
+        <v>11.5502977371216</v>
       </c>
       <c r="H1656" t="n">
         <v>106176</v>
@@ -48451,7 +48451,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="n">
-        <v>12.6247434616089</v>
+        <v>12.6247444152832</v>
       </c>
       <c r="H1658" t="n">
         <v>79138</v>
@@ -48480,7 +48480,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>13.0468473434448</v>
+        <v>13.0468482971191</v>
       </c>
       <c r="H1659" t="n">
         <v>65276</v>
@@ -48741,7 +48741,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="n">
-        <v>13.0468473434448</v>
+        <v>13.0468482971191</v>
       </c>
       <c r="H1668" t="n">
         <v>63442</v>
@@ -48770,7 +48770,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>13.1044082641602</v>
+        <v>13.1044073104858</v>
       </c>
       <c r="H1669" t="n">
         <v>22290</v>
@@ -49002,7 +49002,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.3154602050781</v>
+        <v>13.3154592514038</v>
       </c>
       <c r="H1677" t="n">
         <v>61589</v>
@@ -49031,7 +49031,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.1044082641602</v>
+        <v>13.1044073104858</v>
       </c>
       <c r="H1678" t="n">
         <v>78688</v>
@@ -49089,7 +49089,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.6055574417114</v>
+        <v>12.6055583953857</v>
       </c>
       <c r="H1680" t="n">
         <v>65707</v>
@@ -49205,7 +49205,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="n">
-        <v>12.6247434616089</v>
+        <v>12.6247444152832</v>
       </c>
       <c r="H1684" t="n">
         <v>34970</v>
@@ -49321,7 +49321,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="n">
-        <v>12.2506055831909</v>
+        <v>12.2506065368652</v>
       </c>
       <c r="H1688" t="n">
         <v>46659</v>
@@ -49350,7 +49350,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>11.7805366516113</v>
+        <v>11.780535697937</v>
       </c>
       <c r="H1689" t="n">
         <v>75821</v>
@@ -49466,7 +49466,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="n">
-        <v>12.2218265533447</v>
+        <v>12.2218255996704</v>
       </c>
       <c r="H1693" t="n">
         <v>114156</v>
@@ -49553,7 +49553,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="n">
-        <v>12.1834526062012</v>
+        <v>12.1834535598755</v>
       </c>
       <c r="H1696" t="n">
         <v>51664</v>
@@ -49727,7 +49727,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="n">
-        <v>11.3296527862549</v>
+        <v>11.3296518325806</v>
       </c>
       <c r="H1702" t="n">
         <v>48994</v>
@@ -49756,7 +49756,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="n">
-        <v>11.6654176712036</v>
+        <v>11.6654167175293</v>
       </c>
       <c r="H1703" t="n">
         <v>48478</v>
@@ -49785,7 +49785,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>12.1354856491089</v>
+        <v>12.1354866027832</v>
       </c>
       <c r="H1704" t="n">
         <v>69346</v>
@@ -50017,7 +50017,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="n">
-        <v>11.2720928192139</v>
+        <v>11.2720937728882</v>
       </c>
       <c r="H1712" t="n">
         <v>57229</v>
@@ -50162,7 +50162,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.754056930542</v>
+        <v>10.7540559768677</v>
       </c>
       <c r="H1717" t="n">
         <v>47037</v>
@@ -50220,7 +50220,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="n">
-        <v>11.1090059280396</v>
+        <v>11.1090068817139</v>
       </c>
       <c r="H1719" t="n">
         <v>38067</v>
@@ -50249,7 +50249,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.6654176712036</v>
+        <v>11.6654167175293</v>
       </c>
       <c r="H1720" t="n">
         <v>60827</v>
@@ -50278,7 +50278,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>11.4159908294678</v>
+        <v>11.4159917831421</v>
       </c>
       <c r="H1721" t="n">
         <v>31311</v>
@@ -50336,7 +50336,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.5694856643677</v>
+        <v>11.5694847106934</v>
       </c>
       <c r="H1723" t="n">
         <v>30512</v>
@@ -50365,7 +50365,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>11.5790767669678</v>
+        <v>11.5790777206421</v>
       </c>
       <c r="H1724" t="n">
         <v>33530</v>
@@ -50423,7 +50423,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.2720928192139</v>
+        <v>11.2720937728882</v>
       </c>
       <c r="H1726" t="n">
         <v>45721</v>
@@ -50481,7 +50481,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.6654176712036</v>
+        <v>11.6654167175293</v>
       </c>
       <c r="H1728" t="n">
         <v>31281</v>
@@ -50510,7 +50510,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.8764686584473</v>
+        <v>11.8764696121216</v>
       </c>
       <c r="H1729" t="n">
         <v>26291</v>
@@ -50771,7 +50771,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="n">
-        <v>13.2003412246704</v>
+        <v>13.2003402709961</v>
       </c>
       <c r="H1738" t="n">
         <v>77128</v>
@@ -50800,7 +50800,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="n">
-        <v>11.6941957473755</v>
+        <v>11.6941967010498</v>
       </c>
       <c r="H1739" t="n">
         <v>447229</v>
@@ -50945,7 +50945,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.5790767669678</v>
+        <v>11.5790777206421</v>
       </c>
       <c r="H1744" t="n">
         <v>105065</v>
@@ -51061,7 +51061,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.7398624420166</v>
+        <v>12.7398633956909</v>
       </c>
       <c r="H1748" t="n">
         <v>160134</v>
@@ -51119,7 +51119,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.5959644317627</v>
+        <v>12.5959634780884</v>
       </c>
       <c r="H1750" t="n">
         <v>92825</v>
@@ -51148,7 +51148,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.2889804840088</v>
+        <v>12.2889795303345</v>
       </c>
       <c r="H1751" t="n">
         <v>103263</v>
@@ -51235,7 +51235,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930465698242</v>
+        <v>12.1930475234985</v>
       </c>
       <c r="H1754" t="n">
         <v>93258</v>
@@ -51264,7 +51264,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.2506055831909</v>
+        <v>12.2506065368652</v>
       </c>
       <c r="H1755" t="n">
         <v>28199</v>
@@ -51409,7 +51409,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H1760" t="n">
         <v>57784</v>
@@ -51496,7 +51496,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="n">
-        <v>12.7398624420166</v>
+        <v>12.7398633956909</v>
       </c>
       <c r="H1763" t="n">
         <v>76238</v>
@@ -51786,7 +51786,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.1834526062012</v>
+        <v>12.1834535598755</v>
       </c>
       <c r="H1773" t="n">
         <v>45619</v>
@@ -51815,7 +51815,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H1774" t="n">
         <v>28745</v>
@@ -51844,7 +51844,7 @@
         <v>12.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.9915885925293</v>
+        <v>11.991587638855</v>
       </c>
       <c r="H1775" t="n">
         <v>63441</v>
@@ -51931,7 +51931,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.0395536422729</v>
+        <v>12.0395545959473</v>
       </c>
       <c r="H1778" t="n">
         <v>24126</v>
@@ -52105,7 +52105,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.5000314712524</v>
+        <v>12.5000305175781</v>
       </c>
       <c r="H1784" t="n">
         <v>49900</v>
@@ -52308,7 +52308,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.7663431167603</v>
+        <v>13.7663440704346</v>
       </c>
       <c r="H1791" t="n">
         <v>71163</v>
@@ -52424,7 +52424,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.2364130020142</v>
+        <v>14.2364139556885</v>
       </c>
       <c r="H1795" t="n">
         <v>65651</v>
@@ -52453,7 +52453,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.7855281829834</v>
+        <v>13.7855291366577</v>
       </c>
       <c r="H1796" t="n">
         <v>52655</v>
@@ -52482,7 +52482,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.8143091201782</v>
+        <v>13.8143100738525</v>
       </c>
       <c r="H1797" t="n">
         <v>40053</v>
@@ -52511,7 +52511,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1798" t="n">
-        <v>13.8143091201782</v>
+        <v>13.8143100738525</v>
       </c>
       <c r="H1798" t="n">
         <v>44811</v>
@@ -52627,7 +52627,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1802" t="n">
-        <v>14.3707180023193</v>
+        <v>14.3707189559937</v>
       </c>
       <c r="H1802" t="n">
         <v>61789</v>
@@ -52685,7 +52685,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1804" t="n">
-        <v>14.1692609786987</v>
+        <v>14.1692600250244</v>
       </c>
       <c r="H1804" t="n">
         <v>86857</v>
@@ -52743,7 +52743,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463157653809</v>
+        <v>14.9463148117065</v>
       </c>
       <c r="H1806" t="n">
         <v>121708</v>
@@ -52772,7 +52772,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="n">
-        <v>14.7736368179321</v>
+        <v>14.7736358642578</v>
       </c>
       <c r="H1807" t="n">
         <v>83586</v>
@@ -52830,7 +52830,7 @@
         <v>15</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.3899049758911</v>
+        <v>14.3899059295654</v>
       </c>
       <c r="H1809" t="n">
         <v>55734</v>
@@ -53004,7 +53004,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.5721778869629</v>
+        <v>14.5721769332886</v>
       </c>
       <c r="H1815" t="n">
         <v>43434</v>
@@ -53062,7 +53062,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.5721778869629</v>
+        <v>14.5721769332886</v>
       </c>
       <c r="H1817" t="n">
         <v>85926</v>
@@ -53120,7 +53120,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.5721778869629</v>
+        <v>14.5721769332886</v>
       </c>
       <c r="H1819" t="n">
         <v>79210</v>
@@ -53178,7 +53178,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1821" t="n">
-        <v>16.0879135131836</v>
+        <v>16.0879154205322</v>
       </c>
       <c r="H1821" t="n">
         <v>460810</v>
@@ -53207,7 +53207,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.8288974761963</v>
+        <v>15.8288955688477</v>
       </c>
       <c r="H1822" t="n">
         <v>177332</v>
@@ -53236,7 +53236,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1823" t="n">
-        <v>16.2510013580322</v>
+        <v>16.2509994506836</v>
       </c>
       <c r="H1823" t="n">
         <v>168955</v>
@@ -53294,7 +53294,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1825" t="n">
-        <v>16.7210712432861</v>
+        <v>16.7210693359375</v>
       </c>
       <c r="H1825" t="n">
         <v>176367</v>
@@ -53381,7 +53381,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1828" t="n">
-        <v>16.2030353546143</v>
+        <v>16.2030334472656</v>
       </c>
       <c r="H1828" t="n">
         <v>59759</v>
@@ -53468,7 +53468,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1831" t="n">
-        <v>16.2030353546143</v>
+        <v>16.2030334472656</v>
       </c>
       <c r="H1831" t="n">
         <v>39708</v>
@@ -53526,7 +53526,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.3588266372681</v>
+        <v>15.3588256835938</v>
       </c>
       <c r="H1833" t="n">
         <v>142239</v>
@@ -53555,7 +53555,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1834" t="n">
-        <v>16.0783195495605</v>
+        <v>16.0783214569092</v>
       </c>
       <c r="H1834" t="n">
         <v>161635</v>
@@ -53729,7 +53729,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1840" t="n">
-        <v>14.639331817627</v>
+        <v>14.6393308639526</v>
       </c>
       <c r="H1840" t="n">
         <v>102978</v>
@@ -53758,7 +53758,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="n">
-        <v>14.5529909133911</v>
+        <v>14.5529918670654</v>
       </c>
       <c r="H1841" t="n">
         <v>102046</v>
@@ -53787,7 +53787,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.1308879852295</v>
+        <v>14.1308870315552</v>
       </c>
       <c r="H1842" t="n">
         <v>109542</v>
@@ -53845,7 +53845,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1844" t="n">
-        <v>13.9486150741577</v>
+        <v>13.948616027832</v>
       </c>
       <c r="H1844" t="n">
         <v>54799</v>
@@ -54019,7 +54019,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="n">
-        <v>13.5456981658936</v>
+        <v>13.5456972122192</v>
       </c>
       <c r="H1850" t="n">
         <v>60451</v>
@@ -54135,7 +54135,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>13.4593572616577</v>
+        <v>13.459358215332</v>
       </c>
       <c r="H1854" t="n">
         <v>46148</v>
@@ -54222,7 +54222,7 @@
         <v>14</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4305791854858</v>
+        <v>13.4305782318115</v>
       </c>
       <c r="H1857" t="n">
         <v>134657</v>
@@ -54396,7 +54396,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1863" t="n">
-        <v>12.9701013565063</v>
+        <v>12.9701023101807</v>
       </c>
       <c r="H1863" t="n">
         <v>106326</v>
@@ -54454,7 +54454,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2578992843628</v>
+        <v>13.2578983306885</v>
       </c>
       <c r="H1865" t="n">
         <v>39502</v>
@@ -54512,7 +54512,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1867" t="n">
-        <v>13.027660369873</v>
+        <v>13.0276613235474</v>
       </c>
       <c r="H1867" t="n">
         <v>39070</v>
@@ -80026,7 +80026,7 @@
         <v>4.41499996185303</v>
       </c>
       <c r="E2747" t="n">
-        <v>4.1100001335144</v>
+        <v>4.06500005722046</v>
       </c>
       <c r="F2747" t="n">
         <v>4.06500005722046</v>
@@ -80038,6 +80038,35 @@
         <v>204831</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>4.04500007629395</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>4.15500020980835</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>4.04500007629395</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>4.04500007629395</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>193765</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2523975372314</v>
+        <v>13.2523984909058</v>
       </c>
       <c r="H2" t="n">
         <v>87173</v>
@@ -514,7 +514,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G5" t="n">
-        <v>12.7479515075684</v>
+        <v>12.747950553894</v>
       </c>
       <c r="H5" t="n">
         <v>96757</v>
@@ -572,7 +572,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G7" t="n">
-        <v>12.2435054779053</v>
+        <v>12.243504524231</v>
       </c>
       <c r="H7" t="n">
         <v>86270</v>
@@ -601,7 +601,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>12.2606058120728</v>
+        <v>12.2606067657471</v>
       </c>
       <c r="H8" t="n">
         <v>54531</v>
@@ -630,7 +630,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409072875977</v>
       </c>
       <c r="H9" t="n">
         <v>34417</v>
@@ -688,7 +688,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>10.858416557312</v>
+        <v>10.8584156036377</v>
       </c>
       <c r="H11" t="n">
         <v>191378</v>
@@ -746,7 +746,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3539705276489</v>
+        <v>10.3539695739746</v>
       </c>
       <c r="H13" t="n">
         <v>237289</v>
@@ -775,7 +775,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G14" t="n">
-        <v>9.84952354431152</v>
+        <v>9.84952449798584</v>
       </c>
       <c r="H14" t="n">
         <v>191837</v>
@@ -804,7 +804,7 @@
         <v>12.25</v>
       </c>
       <c r="G15" t="n">
-        <v>10.473669052124</v>
+        <v>10.4736680984497</v>
       </c>
       <c r="H15" t="n">
         <v>204057</v>
@@ -833,7 +833,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941207885742</v>
+        <v>10.2941198348999</v>
       </c>
       <c r="H16" t="n">
         <v>136366</v>
@@ -891,7 +891,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>10.8156652450562</v>
+        <v>10.8156661987305</v>
       </c>
       <c r="H18" t="n">
         <v>109866</v>
@@ -920,7 +920,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>10.730167388916</v>
+        <v>10.7301683425903</v>
       </c>
       <c r="H19" t="n">
         <v>71825</v>
@@ -949,7 +949,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5762691497803</v>
+        <v>10.576268196106</v>
       </c>
       <c r="H20" t="n">
         <v>57072</v>
@@ -978,7 +978,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361179351807</v>
+        <v>10.6361169815063</v>
       </c>
       <c r="H21" t="n">
         <v>72208</v>
@@ -1007,7 +1007,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8156652450562</v>
+        <v>10.8156661987305</v>
       </c>
       <c r="H22" t="n">
         <v>43477</v>
@@ -1036,7 +1036,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1915216445923</v>
+        <v>10.191520690918</v>
       </c>
       <c r="H23" t="n">
         <v>90616</v>
@@ -1094,7 +1094,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907703399658</v>
+        <v>10.4907693862915</v>
       </c>
       <c r="H25" t="n">
         <v>150192</v>
@@ -1123,7 +1123,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0205221176147</v>
+        <v>10.0205230712891</v>
       </c>
       <c r="H26" t="n">
         <v>55946</v>
@@ -1152,7 +1152,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03727912902832</v>
+        <v>9.03728008270264</v>
       </c>
       <c r="H27" t="n">
         <v>127617</v>
@@ -1181,7 +1181,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743129730225</v>
+        <v>8.97743034362793</v>
       </c>
       <c r="H28" t="n">
         <v>172224</v>
@@ -1210,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9.40492820739746</v>
+        <v>9.40492725372314</v>
       </c>
       <c r="H29" t="n">
         <v>104278</v>
@@ -1239,7 +1239,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842987060547</v>
+        <v>9.14842891693115</v>
       </c>
       <c r="H30" t="n">
         <v>114215</v>
@@ -1268,7 +1268,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057727813721</v>
+        <v>9.43057632446289</v>
       </c>
       <c r="H31" t="n">
         <v>72178</v>
@@ -1297,7 +1297,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082454681396</v>
+        <v>9.90082263946533</v>
       </c>
       <c r="H32" t="n">
         <v>70762</v>
@@ -1326,7 +1326,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142463684082</v>
+        <v>9.66142654418945</v>
       </c>
       <c r="H33" t="n">
         <v>39366</v>
@@ -1384,7 +1384,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3454217910767</v>
+        <v>10.3454208374023</v>
       </c>
       <c r="H35" t="n">
         <v>81482</v>
@@ -1442,7 +1442,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>11.0037641525269</v>
+        <v>11.0037651062012</v>
       </c>
       <c r="H37" t="n">
         <v>86253</v>
@@ -1500,7 +1500,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257204055786</v>
+        <v>10.2257213592529</v>
       </c>
       <c r="H39" t="n">
         <v>73018</v>
@@ -1529,7 +1529,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G40" t="n">
-        <v>10.1829719543457</v>
+        <v>10.1829710006714</v>
       </c>
       <c r="H40" t="n">
         <v>68122</v>
@@ -1645,7 +1645,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442567825317</v>
+        <v>11.9442577362061</v>
       </c>
       <c r="H44" t="n">
         <v>175966</v>
@@ -1674,7 +1674,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G45" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H45" t="n">
         <v>110221</v>
@@ -1703,7 +1703,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732601165771</v>
+        <v>11.7732591629028</v>
       </c>
       <c r="H46" t="n">
         <v>75412</v>
@@ -1790,7 +1790,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>11.3714122772217</v>
+        <v>11.371413230896</v>
       </c>
       <c r="H49" t="n">
         <v>73494</v>
@@ -1848,7 +1848,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6621103286743</v>
+        <v>11.662109375</v>
       </c>
       <c r="H51" t="n">
         <v>99643</v>
@@ -1877,7 +1877,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416595458984</v>
+        <v>11.8416585922241</v>
       </c>
       <c r="H52" t="n">
         <v>101508</v>
@@ -1906,7 +1906,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.9186067581177</v>
+        <v>11.9186086654663</v>
       </c>
       <c r="H53" t="n">
         <v>56813</v>
@@ -1993,7 +1993,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922063827515</v>
+        <v>12.1922054290771</v>
       </c>
       <c r="H56" t="n">
         <v>88317</v>
@@ -2051,7 +2051,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375549316406</v>
+        <v>12.3375558853149</v>
       </c>
       <c r="H58" t="n">
         <v>61525</v>
@@ -2080,7 +2080,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409072875977</v>
       </c>
       <c r="H59" t="n">
         <v>40540</v>
@@ -2109,7 +2109,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>12.1323556900024</v>
+        <v>12.1323566436768</v>
       </c>
       <c r="H60" t="n">
         <v>36904</v>
@@ -2138,7 +2138,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665563583374</v>
+        <v>12.1665544509888</v>
       </c>
       <c r="H61" t="n">
         <v>40779</v>
@@ -2167,7 +2167,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H62" t="n">
         <v>55469</v>
@@ -2196,7 +2196,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178564071655</v>
+        <v>12.2178554534912</v>
       </c>
       <c r="H63" t="n">
         <v>42659</v>
@@ -2225,7 +2225,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>11.9015092849731</v>
+        <v>11.9015083312988</v>
       </c>
       <c r="H64" t="n">
         <v>46495</v>
@@ -2254,7 +2254,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409072875977</v>
       </c>
       <c r="H65" t="n">
         <v>58858</v>
@@ -2312,7 +2312,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5680599212646</v>
+        <v>11.5680618286133</v>
       </c>
       <c r="H67" t="n">
         <v>44037</v>
@@ -2399,7 +2399,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>11.8844079971313</v>
+        <v>11.8844089508057</v>
       </c>
       <c r="H70" t="n">
         <v>38060</v>
@@ -2428,7 +2428,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5680599212646</v>
+        <v>11.5680618286133</v>
       </c>
       <c r="H71" t="n">
         <v>41497</v>
@@ -2457,7 +2457,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6621103286743</v>
+        <v>11.662109375</v>
       </c>
       <c r="H72" t="n">
         <v>25570</v>
@@ -2486,7 +2486,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160085678101</v>
+        <v>11.8160095214844</v>
       </c>
       <c r="H73" t="n">
         <v>56893</v>
@@ -2573,7 +2573,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.6621103286743</v>
+        <v>11.662109375</v>
       </c>
       <c r="H76" t="n">
         <v>47170</v>
@@ -2602,7 +2602,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364612579346</v>
+        <v>11.6364603042603</v>
       </c>
       <c r="H77" t="n">
         <v>21274</v>
@@ -2631,7 +2631,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G78" t="n">
-        <v>11.4740123748779</v>
+        <v>11.4740114212036</v>
       </c>
       <c r="H78" t="n">
         <v>51888</v>
@@ -2660,7 +2660,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918630599976</v>
+        <v>11.1918659210205</v>
       </c>
       <c r="H79" t="n">
         <v>107247</v>
@@ -2718,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.1149129867554</v>
+        <v>11.1149158477783</v>
       </c>
       <c r="H81" t="n">
         <v>44600</v>
@@ -2776,7 +2776,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3201122283936</v>
+        <v>11.3201112747192</v>
       </c>
       <c r="H83" t="n">
         <v>33223</v>
@@ -2805,7 +2805,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G84" t="n">
-        <v>11.3457622528076</v>
+        <v>11.3457632064819</v>
       </c>
       <c r="H84" t="n">
         <v>35206</v>
@@ -2834,7 +2834,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1576633453369</v>
+        <v>11.1576642990112</v>
       </c>
       <c r="H85" t="n">
         <v>20515</v>
@@ -2863,7 +2863,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G86" t="n">
-        <v>11.055064201355</v>
+        <v>11.0550651550293</v>
       </c>
       <c r="H86" t="n">
         <v>64749</v>
@@ -2892,7 +2892,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.9866647720337</v>
+        <v>10.986665725708</v>
       </c>
       <c r="H87" t="n">
         <v>18020</v>
@@ -2921,7 +2921,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1405639648438</v>
+        <v>11.1405630111694</v>
       </c>
       <c r="H88" t="n">
         <v>30374</v>
@@ -2979,7 +2979,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>10.954140663147</v>
+        <v>10.9541397094727</v>
       </c>
       <c r="H90" t="n">
         <v>55438</v>
@@ -3095,7 +3095,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G94" t="n">
-        <v>10.22327709198</v>
+        <v>10.2232780456543</v>
       </c>
       <c r="H94" t="n">
         <v>77351</v>
@@ -3240,7 +3240,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3025283813477</v>
+        <v>10.3025274276733</v>
       </c>
       <c r="H99" t="n">
         <v>48962</v>
@@ -3269,7 +3269,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496957778931</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H100" t="n">
         <v>39045</v>
@@ -3327,7 +3327,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120330810547</v>
+        <v>11.4120311737061</v>
       </c>
       <c r="H102" t="n">
         <v>156693</v>
@@ -3356,7 +3356,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302518844604</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H103" t="n">
         <v>70319</v>
@@ -3472,7 +3472,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302518844604</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H107" t="n">
         <v>63256</v>
@@ -3501,7 +3501,7 @@
         <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0069742202759</v>
+        <v>11.0069732666016</v>
       </c>
       <c r="H108" t="n">
         <v>22280</v>
@@ -3559,7 +3559,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396701812744</v>
+        <v>10.8396711349487</v>
       </c>
       <c r="H110" t="n">
         <v>35136</v>
@@ -3588,7 +3588,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.9277238845825</v>
+        <v>10.9277229309082</v>
       </c>
       <c r="H111" t="n">
         <v>58146</v>
@@ -3617,7 +3617,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G112" t="n">
-        <v>10.9101133346558</v>
+        <v>10.9101123809814</v>
       </c>
       <c r="H112" t="n">
         <v>37578</v>
@@ -3733,7 +3733,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.9943323135376</v>
+        <v>9.99433326721191</v>
       </c>
       <c r="H116" t="n">
         <v>83790</v>
@@ -3762,7 +3762,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G117" t="n">
-        <v>9.95030498504639</v>
+        <v>9.95030403137207</v>
       </c>
       <c r="H117" t="n">
         <v>51985</v>
@@ -3820,7 +3820,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.0383596420288</v>
+        <v>10.0383605957031</v>
       </c>
       <c r="H119" t="n">
         <v>59338</v>
@@ -3849,7 +3849,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962501525879</v>
+        <v>10.4962511062622</v>
       </c>
       <c r="H120" t="n">
         <v>43223</v>
@@ -3907,7 +3907,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522228240967</v>
+        <v>10.4522247314453</v>
       </c>
       <c r="H122" t="n">
         <v>40375</v>
@@ -3936,7 +3936,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843067169189</v>
+        <v>10.5843076705933</v>
       </c>
       <c r="H123" t="n">
         <v>36459</v>
@@ -4023,7 +4023,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733192443848</v>
+        <v>9.67733097076416</v>
       </c>
       <c r="H126" t="n">
         <v>56824</v>
@@ -4052,7 +4052,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G127" t="n">
-        <v>9.57166576385498</v>
+        <v>9.57166481018066</v>
       </c>
       <c r="H127" t="n">
         <v>24263</v>
@@ -4110,7 +4110,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1880550384521</v>
+        <v>10.1880559921265</v>
       </c>
       <c r="H129" t="n">
         <v>25733</v>
@@ -4139,7 +4139,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G130" t="n">
-        <v>9.98552703857422</v>
+        <v>9.9855260848999</v>
       </c>
       <c r="H130" t="n">
         <v>15581</v>
@@ -4197,7 +4197,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.1842212677002</v>
+        <v>9.18421936035156</v>
       </c>
       <c r="H132" t="n">
         <v>96061</v>
@@ -4226,7 +4226,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019203186035</v>
+        <v>9.14019107818604</v>
       </c>
       <c r="H133" t="n">
         <v>64369</v>
@@ -4284,7 +4284,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0823879241943</v>
+        <v>10.0823888778687</v>
       </c>
       <c r="H135" t="n">
         <v>34424</v>
@@ -4458,7 +4458,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.15283203125</v>
+        <v>10.1528329849243</v>
       </c>
       <c r="H141" t="n">
         <v>23520</v>
@@ -4487,7 +4487,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496957778931</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H142" t="n">
         <v>53624</v>
@@ -4516,7 +4516,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496957778931</v>
+        <v>10.2496948242188</v>
       </c>
       <c r="H143" t="n">
         <v>15986</v>
@@ -4574,7 +4574,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.3025283813477</v>
+        <v>10.3025274276733</v>
       </c>
       <c r="H145" t="n">
         <v>26846</v>
@@ -4603,7 +4603,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987791061401</v>
+        <v>10.6987800598145</v>
       </c>
       <c r="H146" t="n">
         <v>35625</v>
@@ -4632,7 +4632,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G147" t="n">
-        <v>11.0774192810059</v>
+        <v>11.0774183273315</v>
       </c>
       <c r="H147" t="n">
         <v>53666</v>
@@ -4690,7 +4690,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>11.0333909988403</v>
+        <v>11.033390045166</v>
       </c>
       <c r="H149" t="n">
         <v>32061</v>
@@ -4719,7 +4719,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>11.0333909988403</v>
+        <v>11.033390045166</v>
       </c>
       <c r="H150" t="n">
         <v>31452</v>
@@ -4777,7 +4777,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893627166748</v>
+        <v>10.9893636703491</v>
       </c>
       <c r="H152" t="n">
         <v>42127</v>
@@ -4806,7 +4806,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748912811279</v>
+        <v>10.8748922348022</v>
       </c>
       <c r="H153" t="n">
         <v>39269</v>
@@ -4835,7 +4835,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748912811279</v>
+        <v>10.8748922348022</v>
       </c>
       <c r="H154" t="n">
         <v>23378</v>
@@ -4864,7 +4864,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9277238845825</v>
+        <v>10.9277229309082</v>
       </c>
       <c r="H155" t="n">
         <v>22842</v>
@@ -4893,7 +4893,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.0950298309326</v>
+        <v>11.0950307846069</v>
       </c>
       <c r="H156" t="n">
         <v>40839</v>
@@ -4922,7 +4922,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G157" t="n">
-        <v>11.2535305023193</v>
+        <v>11.253529548645</v>
       </c>
       <c r="H157" t="n">
         <v>72265</v>
@@ -4951,7 +4951,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>11.3151702880859</v>
+        <v>11.3151712417603</v>
       </c>
       <c r="H158" t="n">
         <v>45498</v>
@@ -4980,7 +4980,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>11.2535305023193</v>
+        <v>11.253529548645</v>
       </c>
       <c r="H159" t="n">
         <v>20029</v>
@@ -5038,7 +5038,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7251958847046</v>
+        <v>10.7251977920532</v>
       </c>
       <c r="H161" t="n">
         <v>58715</v>
@@ -5067,7 +5067,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>11.0510025024414</v>
+        <v>11.0510015487671</v>
       </c>
       <c r="H162" t="n">
         <v>19081</v>
@@ -5125,7 +5125,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654739379883</v>
+        <v>11.1654758453369</v>
       </c>
       <c r="H164" t="n">
         <v>19684</v>
@@ -5183,7 +5183,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G166" t="n">
-        <v>11.2183084487915</v>
+        <v>11.2183074951172</v>
       </c>
       <c r="H166" t="n">
         <v>21084</v>
@@ -5241,7 +5241,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G168" t="n">
-        <v>11.0774192810059</v>
+        <v>11.0774183273315</v>
       </c>
       <c r="H168" t="n">
         <v>45236</v>
@@ -5270,7 +5270,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302518844604</v>
+        <v>11.1302528381348</v>
       </c>
       <c r="H169" t="n">
         <v>50121</v>
@@ -5328,7 +5328,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G171" t="n">
-        <v>11.262336730957</v>
+        <v>11.2623357772827</v>
       </c>
       <c r="H171" t="n">
         <v>27441</v>
@@ -5473,7 +5473,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.7994775772095</v>
+        <v>11.7994766235352</v>
       </c>
       <c r="H176" t="n">
         <v>51577</v>
@@ -5502,7 +5502,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G177" t="n">
-        <v>11.6497821807861</v>
+        <v>11.6497812271118</v>
       </c>
       <c r="H177" t="n">
         <v>41874</v>
@@ -5560,7 +5560,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>11.6497821807861</v>
+        <v>11.6497812271118</v>
       </c>
       <c r="H179" t="n">
         <v>69100</v>
@@ -5618,7 +5618,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>11.3239736557007</v>
+        <v>11.323974609375</v>
       </c>
       <c r="H181" t="n">
         <v>72041</v>
@@ -5647,7 +5647,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680038452148</v>
+        <v>11.3680028915405</v>
       </c>
       <c r="H182" t="n">
         <v>62143</v>
@@ -5676,7 +5676,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>11.1390590667725</v>
+        <v>11.1390571594238</v>
       </c>
       <c r="H183" t="n">
         <v>30268</v>
@@ -5763,7 +5763,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G186" t="n">
-        <v>11.6145582199097</v>
+        <v>11.6145601272583</v>
       </c>
       <c r="H186" t="n">
         <v>25730</v>
@@ -5792,7 +5792,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G187" t="n">
-        <v>11.8258934020996</v>
+        <v>11.8258943557739</v>
       </c>
       <c r="H187" t="n">
         <v>136773</v>
@@ -5821,7 +5821,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G188" t="n">
-        <v>12.0372276306152</v>
+        <v>12.0372266769409</v>
       </c>
       <c r="H188" t="n">
         <v>83675</v>
@@ -5850,7 +5850,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>12.0548372268677</v>
+        <v>12.054838180542</v>
       </c>
       <c r="H189" t="n">
         <v>61757</v>
@@ -5879,7 +5879,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.0636425018311</v>
+        <v>12.0636444091797</v>
       </c>
       <c r="H190" t="n">
         <v>38989</v>
@@ -5937,7 +5937,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303401947021</v>
+        <v>12.5303382873535</v>
       </c>
       <c r="H192" t="n">
         <v>109655</v>
@@ -5966,7 +5966,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070615768433</v>
+        <v>12.4070606231689</v>
       </c>
       <c r="H193" t="n">
         <v>92196</v>
@@ -5995,7 +5995,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837820053101</v>
+        <v>12.2837829589844</v>
       </c>
       <c r="H194" t="n">
         <v>42892</v>
@@ -6024,7 +6024,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G195" t="n">
-        <v>12.6007852554321</v>
+        <v>12.6007843017578</v>
       </c>
       <c r="H195" t="n">
         <v>62641</v>
@@ -6053,7 +6053,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G196" t="n">
-        <v>12.9177865982056</v>
+        <v>12.9177856445312</v>
       </c>
       <c r="H196" t="n">
         <v>155030</v>
@@ -6082,7 +6082,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G197" t="n">
-        <v>12.8121185302734</v>
+        <v>12.8121194839478</v>
       </c>
       <c r="H197" t="n">
         <v>94007</v>
@@ -6140,7 +6140,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>13.0322570800781</v>
+        <v>13.0322580337524</v>
       </c>
       <c r="H199" t="n">
         <v>85136</v>
@@ -6169,7 +6169,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>13.4108972549438</v>
+        <v>13.4108982086182</v>
       </c>
       <c r="H200" t="n">
         <v>211127</v>
@@ -6198,7 +6198,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782051086426</v>
+        <v>13.5782041549683</v>
       </c>
       <c r="H201" t="n">
         <v>145739</v>
@@ -6256,7 +6256,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285087585449</v>
+        <v>13.4285097122192</v>
       </c>
       <c r="H203" t="n">
         <v>304187</v>
@@ -6285,7 +6285,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G204" t="n">
-        <v>14.3707046508789</v>
+        <v>14.3707056045532</v>
       </c>
       <c r="H204" t="n">
         <v>401338</v>
@@ -6314,7 +6314,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210092544556</v>
+        <v>14.2210111618042</v>
       </c>
       <c r="H205" t="n">
         <v>191135</v>
@@ -6372,7 +6372,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.1329545974731</v>
+        <v>14.1329536437988</v>
       </c>
       <c r="H207" t="n">
         <v>75250</v>
@@ -6401,7 +6401,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241512298584</v>
+        <v>14.1241502761841</v>
       </c>
       <c r="H208" t="n">
         <v>50427</v>
@@ -6430,7 +6430,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0713148117065</v>
+        <v>14.0713157653809</v>
       </c>
       <c r="H209" t="n">
         <v>70266</v>
@@ -6459,7 +6459,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9216213226318</v>
+        <v>13.9216222763062</v>
       </c>
       <c r="H210" t="n">
         <v>55040</v>
@@ -6517,7 +6517,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G212" t="n">
-        <v>13.6046199798584</v>
+        <v>13.6046209335327</v>
       </c>
       <c r="H212" t="n">
         <v>48829</v>
@@ -6546,7 +6546,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631206512451</v>
+        <v>13.7631196975708</v>
       </c>
       <c r="H213" t="n">
         <v>75863</v>
@@ -6575,7 +6575,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G214" t="n">
-        <v>13.8335647583008</v>
+        <v>13.8335657119751</v>
       </c>
       <c r="H214" t="n">
         <v>23394</v>
@@ -6633,7 +6633,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G216" t="n">
-        <v>13.1995639801025</v>
+        <v>13.1995630264282</v>
       </c>
       <c r="H216" t="n">
         <v>212327</v>
@@ -6720,7 +6720,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486482620239</v>
+        <v>13.6486492156982</v>
       </c>
       <c r="H219" t="n">
         <v>47806</v>
@@ -6749,7 +6749,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605916976929</v>
+        <v>13.5605926513672</v>
       </c>
       <c r="H220" t="n">
         <v>47022</v>
@@ -6778,7 +6778,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285087585449</v>
+        <v>13.4285097122192</v>
       </c>
       <c r="H221" t="n">
         <v>144794</v>
@@ -6894,7 +6894,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>14.0977325439453</v>
+        <v>14.0977334976196</v>
       </c>
       <c r="H225" t="n">
         <v>147489</v>
@@ -6952,7 +6952,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040971755981</v>
+        <v>15.3040952682495</v>
       </c>
       <c r="H227" t="n">
         <v>258275</v>
@@ -7039,7 +7039,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978218078613</v>
+        <v>15.4978199005127</v>
       </c>
       <c r="H230" t="n">
         <v>289822</v>
@@ -7068,7 +7068,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657360076904</v>
+        <v>15.3657369613647</v>
       </c>
       <c r="H231" t="n">
         <v>110362</v>
@@ -7126,7 +7126,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3393173217773</v>
+        <v>15.339319229126</v>
       </c>
       <c r="H233" t="n">
         <v>71686</v>
@@ -7155,7 +7155,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5330438613892</v>
+        <v>15.5330429077148</v>
       </c>
       <c r="H234" t="n">
         <v>122396</v>
@@ -7213,7 +7213,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418472290039</v>
+        <v>15.5418481826782</v>
       </c>
       <c r="H236" t="n">
         <v>99490</v>
@@ -7329,7 +7329,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G240" t="n">
-        <v>16.1934604644775</v>
+        <v>16.1934623718262</v>
       </c>
       <c r="H240" t="n">
         <v>378003</v>
@@ -7416,7 +7416,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.5104637145996</v>
+        <v>16.5104656219482</v>
       </c>
       <c r="H243" t="n">
         <v>85459</v>
@@ -7445,7 +7445,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.5104637145996</v>
+        <v>16.5104656219482</v>
       </c>
       <c r="H244" t="n">
         <v>184405</v>
@@ -7503,7 +7503,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.889102935791</v>
+        <v>16.8890991210938</v>
       </c>
       <c r="H246" t="n">
         <v>240701</v>
@@ -7648,7 +7648,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G251" t="n">
-        <v>16.589714050293</v>
+        <v>16.5897121429443</v>
       </c>
       <c r="H251" t="n">
         <v>110433</v>
@@ -7677,7 +7677,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G252" t="n">
-        <v>16.6513481140137</v>
+        <v>16.6513500213623</v>
       </c>
       <c r="H252" t="n">
         <v>93094</v>
@@ -7706,7 +7706,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>16.5720996856689</v>
+        <v>16.5721015930176</v>
       </c>
       <c r="H253" t="n">
         <v>93811</v>
@@ -7735,7 +7735,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G254" t="n">
-        <v>16.9947662353516</v>
+        <v>16.9947681427002</v>
       </c>
       <c r="H254" t="n">
         <v>161135</v>
@@ -7764,7 +7764,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G255" t="n">
-        <v>16.7041835784912</v>
+        <v>16.7041816711426</v>
       </c>
       <c r="H255" t="n">
         <v>52207</v>
@@ -7793,7 +7793,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.8802928924561</v>
+        <v>16.8802947998047</v>
       </c>
       <c r="H256" t="n">
         <v>74391</v>
@@ -7822,7 +7822,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538818359375</v>
+        <v>16.8538780212402</v>
       </c>
       <c r="H257" t="n">
         <v>23740</v>
@@ -7851,7 +7851,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.012378692627</v>
+        <v>17.0123805999756</v>
       </c>
       <c r="H258" t="n">
         <v>25398</v>
@@ -7938,7 +7938,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G261" t="n">
-        <v>17.1268539428711</v>
+        <v>17.1268520355225</v>
       </c>
       <c r="H261" t="n">
         <v>64080</v>
@@ -7996,7 +7996,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G263" t="n">
-        <v>16.5368766784668</v>
+        <v>16.5368804931641</v>
       </c>
       <c r="H263" t="n">
         <v>65318</v>
@@ -8025,7 +8025,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>17.0828266143799</v>
+        <v>17.0828247070312</v>
       </c>
       <c r="H264" t="n">
         <v>180948</v>
@@ -8112,7 +8112,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>17.3469924926758</v>
+        <v>17.3469944000244</v>
       </c>
       <c r="H267" t="n">
         <v>96917</v>
@@ -8141,7 +8141,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551856994629</v>
+        <v>17.6551876068115</v>
       </c>
       <c r="H268" t="n">
         <v>75995</v>
@@ -8170,7 +8170,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>17.540714263916</v>
+        <v>17.5407123565674</v>
       </c>
       <c r="H269" t="n">
         <v>197725</v>
@@ -8257,7 +8257,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G272" t="n">
-        <v>17.4526557922363</v>
+        <v>17.4526596069336</v>
       </c>
       <c r="H272" t="n">
         <v>52750</v>
@@ -8315,7 +8315,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432441711426</v>
+        <v>17.7432422637939</v>
       </c>
       <c r="H274" t="n">
         <v>80664</v>
@@ -8344,7 +8344,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>17.8401050567627</v>
+        <v>17.8401031494141</v>
       </c>
       <c r="H275" t="n">
         <v>58976</v>
@@ -8402,7 +8402,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>17.5759353637695</v>
+        <v>17.5759372711182</v>
       </c>
       <c r="H277" t="n">
         <v>65783</v>
@@ -8431,7 +8431,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482128143311</v>
+        <v>16.7482109069824</v>
       </c>
       <c r="H278" t="n">
         <v>113676</v>
@@ -8489,7 +8489,7 @@
         <v>19.25</v>
       </c>
       <c r="G280" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507369995117</v>
       </c>
       <c r="H280" t="n">
         <v>60029</v>
@@ -8605,7 +8605,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092395782471</v>
       </c>
       <c r="H284" t="n">
         <v>50524</v>
@@ -8663,7 +8663,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.889102935791</v>
+        <v>16.8890991210938</v>
       </c>
       <c r="H286" t="n">
         <v>33722</v>
@@ -8692,7 +8692,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G287" t="n">
-        <v>16.8186569213867</v>
+        <v>16.8186550140381</v>
       </c>
       <c r="H287" t="n">
         <v>24250</v>
@@ -8721,7 +8721,7 @@
         <v>19.25</v>
       </c>
       <c r="G288" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507369995117</v>
       </c>
       <c r="H288" t="n">
         <v>47872</v>
@@ -8750,7 +8750,7 @@
         <v>19.25</v>
       </c>
       <c r="G289" t="n">
-        <v>16.950740814209</v>
+        <v>16.9507369995117</v>
       </c>
       <c r="H289" t="n">
         <v>32145</v>
@@ -8779,7 +8779,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G290" t="n">
-        <v>17.2325172424316</v>
+        <v>17.2325191497803</v>
       </c>
       <c r="H290" t="n">
         <v>110900</v>
@@ -8808,7 +8808,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>17.0828266143799</v>
+        <v>17.0828247070312</v>
       </c>
       <c r="H291" t="n">
         <v>122243</v>
@@ -8866,7 +8866,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3910217285156</v>
+        <v>17.3910179138184</v>
       </c>
       <c r="H293" t="n">
         <v>29528</v>
@@ -8895,7 +8895,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092395782471</v>
       </c>
       <c r="H294" t="n">
         <v>52387</v>
@@ -8982,7 +8982,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350452423096</v>
+        <v>17.4350471496582</v>
       </c>
       <c r="H297" t="n">
         <v>105130</v>
@@ -9011,7 +9011,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734073638916</v>
+        <v>17.3734092712402</v>
       </c>
       <c r="H298" t="n">
         <v>48083</v>
@@ -9040,7 +9040,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G299" t="n">
-        <v>17.6463832855225</v>
+        <v>17.6463813781738</v>
       </c>
       <c r="H299" t="n">
         <v>74706</v>
@@ -9127,7 +9127,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G302" t="n">
-        <v>19.9358291625977</v>
+        <v>19.9358310699463</v>
       </c>
       <c r="H302" t="n">
         <v>140384</v>
@@ -9185,7 +9185,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962524414062</v>
+        <v>20.5962505340576</v>
       </c>
       <c r="H304" t="n">
         <v>71698</v>
@@ -9214,7 +9214,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G305" t="n">
-        <v>20.3408908843994</v>
+        <v>20.3408889770508</v>
       </c>
       <c r="H305" t="n">
         <v>87911</v>
@@ -9301,7 +9301,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824775695801</v>
+        <v>21.5824756622314</v>
       </c>
       <c r="H308" t="n">
         <v>115604</v>
@@ -9330,7 +9330,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G309" t="n">
-        <v>21.0893611907959</v>
+        <v>21.0893630981445</v>
       </c>
       <c r="H309" t="n">
         <v>116636</v>
@@ -9417,7 +9417,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497825622559</v>
+        <v>21.7497844696045</v>
       </c>
       <c r="H312" t="n">
         <v>78215</v>
@@ -9504,7 +9504,7 @@
         <v>25</v>
       </c>
       <c r="G315" t="n">
-        <v>22.0139484405518</v>
+        <v>22.0139465332031</v>
       </c>
       <c r="H315" t="n">
         <v>69244</v>
@@ -9562,7 +9562,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605037689209</v>
+        <v>22.2605056762695</v>
       </c>
       <c r="H317" t="n">
         <v>83792</v>
@@ -9591,7 +9591,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G318" t="n">
-        <v>22.3485584259033</v>
+        <v>22.3485565185547</v>
       </c>
       <c r="H318" t="n">
         <v>54563</v>
@@ -9620,7 +9620,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221473693848</v>
+        <v>22.3221454620361</v>
       </c>
       <c r="H319" t="n">
         <v>60853</v>
@@ -9649,7 +9649,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>22.1900596618652</v>
+        <v>22.1900615692139</v>
       </c>
       <c r="H320" t="n">
         <v>84678</v>
@@ -9678,7 +9678,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>22.6303405761719</v>
+        <v>22.6303424835205</v>
       </c>
       <c r="H321" t="n">
         <v>84960</v>
@@ -9707,7 +9707,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>22.436616897583</v>
+        <v>22.4366149902344</v>
       </c>
       <c r="H322" t="n">
         <v>60620</v>
@@ -9736,7 +9736,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G323" t="n">
-        <v>22.4806480407715</v>
+        <v>22.4806461334229</v>
       </c>
       <c r="H323" t="n">
         <v>98956</v>
@@ -9765,7 +9765,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G324" t="n">
-        <v>22.6655616760254</v>
+        <v>22.665563583374</v>
       </c>
       <c r="H324" t="n">
         <v>95912</v>
@@ -9794,7 +9794,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G325" t="n">
-        <v>22.4806480407715</v>
+        <v>22.4806461334229</v>
       </c>
       <c r="H325" t="n">
         <v>36599</v>
@@ -9823,7 +9823,7 @@
         <v>25.6900005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>22.6215362548828</v>
+        <v>22.6215343475342</v>
       </c>
       <c r="H326" t="n">
         <v>41825</v>
@@ -9852,7 +9852,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743659973145</v>
+        <v>22.6743679046631</v>
       </c>
       <c r="H327" t="n">
         <v>33968</v>
@@ -9968,7 +9968,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>22.374979019165</v>
+        <v>22.3749771118164</v>
       </c>
       <c r="H331" t="n">
         <v>41506</v>
@@ -9997,7 +9997,7 @@
         <v>25</v>
       </c>
       <c r="G332" t="n">
-        <v>22.0139484405518</v>
+        <v>22.0139465332031</v>
       </c>
       <c r="H332" t="n">
         <v>63890</v>
@@ -10026,7 +10026,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G333" t="n">
-        <v>23.1938972473145</v>
+        <v>23.1938991546631</v>
       </c>
       <c r="H333" t="n">
         <v>56151</v>
@@ -10142,7 +10142,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417640686035</v>
+        <v>24.2417621612549</v>
       </c>
       <c r="H337" t="n">
         <v>94347</v>
@@ -10200,7 +10200,7 @@
         <v>28</v>
       </c>
       <c r="G339" t="n">
-        <v>24.6556205749512</v>
+        <v>24.6556224822998</v>
       </c>
       <c r="H339" t="n">
         <v>63031</v>
@@ -10229,7 +10229,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.919792175293</v>
+        <v>24.9197883605957</v>
       </c>
       <c r="H340" t="n">
         <v>76611</v>
@@ -10461,7 +10461,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>28.1545715332031</v>
+        <v>28.1545696258545</v>
       </c>
       <c r="H348" t="n">
         <v>94775</v>
@@ -10490,7 +10490,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G349" t="n">
-        <v>27.6732902526855</v>
+        <v>27.6732921600342</v>
       </c>
       <c r="H349" t="n">
         <v>144929</v>
@@ -10519,7 +10519,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G350" t="n">
-        <v>28.6804065704346</v>
+        <v>28.6804084777832</v>
       </c>
       <c r="H350" t="n">
         <v>101430</v>
@@ -10548,7 +10548,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>29.3666687011719</v>
+        <v>29.3666706085205</v>
       </c>
       <c r="H351" t="n">
         <v>132004</v>
@@ -10577,7 +10577,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>27.8069839477539</v>
+        <v>27.8069820404053</v>
       </c>
       <c r="H352" t="n">
         <v>138482</v>
@@ -10635,7 +10635,7 @@
         <v>32.560001373291</v>
       </c>
       <c r="G354" t="n">
-        <v>29.0190811157227</v>
+        <v>29.0190849304199</v>
       </c>
       <c r="H354" t="n">
         <v>134928</v>
@@ -10664,7 +10664,7 @@
         <v>33.0900001525879</v>
       </c>
       <c r="G355" t="n">
-        <v>29.4914436340332</v>
+        <v>29.4914474487305</v>
       </c>
       <c r="H355" t="n">
         <v>77343</v>
@@ -10751,7 +10751,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024787902832</v>
       </c>
       <c r="H358" t="n">
         <v>94582</v>
@@ -10809,7 +10809,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400951385498</v>
+        <v>30.2400913238525</v>
       </c>
       <c r="H360" t="n">
         <v>60227</v>
@@ -10867,7 +10867,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283176422119</v>
+        <v>30.8283157348633</v>
       </c>
       <c r="H362" t="n">
         <v>119866</v>
@@ -10896,7 +10896,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996181488037</v>
+        <v>30.8996200561523</v>
       </c>
       <c r="H363" t="n">
         <v>56630</v>
@@ -10925,7 +10925,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154819488525</v>
+        <v>31.0154800415039</v>
       </c>
       <c r="H364" t="n">
         <v>62681</v>
@@ -10954,7 +10954,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.9976558685303</v>
+        <v>30.9976501464844</v>
       </c>
       <c r="H365" t="n">
         <v>39009</v>
@@ -10983,7 +10983,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.935266494751</v>
+        <v>30.9352684020996</v>
       </c>
       <c r="H366" t="n">
         <v>57384</v>
@@ -11012,7 +11012,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G367" t="n">
-        <v>30.6500644683838</v>
+        <v>30.6500663757324</v>
       </c>
       <c r="H367" t="n">
         <v>49692</v>
@@ -11041,7 +11041,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.748104095459</v>
+        <v>30.7481060028076</v>
       </c>
       <c r="H368" t="n">
         <v>76769</v>
@@ -11070,7 +11070,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857223510742</v>
+        <v>30.685718536377</v>
       </c>
       <c r="H369" t="n">
         <v>81969</v>
@@ -11099,7 +11099,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G370" t="n">
-        <v>29.3577537536621</v>
+        <v>29.3577556610107</v>
       </c>
       <c r="H370" t="n">
         <v>121414</v>
@@ -11186,7 +11186,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>29.2775402069092</v>
+        <v>29.2775440216064</v>
       </c>
       <c r="H373" t="n">
         <v>103705</v>
@@ -11215,7 +11215,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.1687927246094</v>
+        <v>30.1687889099121</v>
       </c>
       <c r="H374" t="n">
         <v>129825</v>
@@ -11244,7 +11244,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331462860107</v>
+        <v>30.1331443786621</v>
       </c>
       <c r="H375" t="n">
         <v>53130</v>
@@ -11302,7 +11302,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G377" t="n">
-        <v>29.9281558990479</v>
+        <v>29.9281578063965</v>
       </c>
       <c r="H377" t="n">
         <v>47170</v>
@@ -11331,7 +11331,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G378" t="n">
-        <v>30.0529308319092</v>
+        <v>30.0529327392578</v>
       </c>
       <c r="H378" t="n">
         <v>73018</v>
@@ -11360,7 +11360,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.4825305938721</v>
+        <v>29.482536315918</v>
       </c>
       <c r="H379" t="n">
         <v>44022</v>
@@ -11447,7 +11447,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.1260299682617</v>
+        <v>29.126033782959</v>
       </c>
       <c r="H382" t="n">
         <v>60542</v>
@@ -11476,7 +11476,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>27.7713317871094</v>
+        <v>27.771333694458</v>
       </c>
       <c r="H383" t="n">
         <v>57971</v>
@@ -11534,7 +11534,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544097900391</v>
+        <v>27.2544059753418</v>
       </c>
       <c r="H385" t="n">
         <v>71103</v>
@@ -11563,7 +11563,7 @@
         <v>31.0699996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>27.6911201477051</v>
+        <v>27.6911182403564</v>
       </c>
       <c r="H386" t="n">
         <v>94629</v>
@@ -11621,7 +11621,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G388" t="n">
-        <v>27.5752601623535</v>
+        <v>27.5752563476562</v>
       </c>
       <c r="H388" t="n">
         <v>39274</v>
@@ -11650,7 +11650,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>28.11891746521</v>
+        <v>28.1189193725586</v>
       </c>
       <c r="H389" t="n">
         <v>62724</v>
@@ -11679,7 +11679,7 @@
         <v>31.8099994659424</v>
       </c>
       <c r="G390" t="n">
-        <v>28.350643157959</v>
+        <v>28.3506450653076</v>
       </c>
       <c r="H390" t="n">
         <v>37980</v>
@@ -11737,7 +11737,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734558105469</v>
+        <v>28.5734596252441</v>
       </c>
       <c r="H392" t="n">
         <v>75319</v>
@@ -11824,7 +11824,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>28.787353515625</v>
+        <v>28.7873573303223</v>
       </c>
       <c r="H395" t="n">
         <v>65931</v>
@@ -11882,7 +11882,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855587005615</v>
+        <v>29.7855567932129</v>
       </c>
       <c r="H397" t="n">
         <v>145142</v>
@@ -11911,7 +11911,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G398" t="n">
-        <v>29.5360069274902</v>
+        <v>29.536003112793</v>
       </c>
       <c r="H398" t="n">
         <v>60276</v>
@@ -11969,7 +11969,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.1705951690674</v>
+        <v>29.1705932617188</v>
       </c>
       <c r="H400" t="n">
         <v>60603</v>
@@ -12056,7 +12056,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221092224121</v>
+        <v>29.3221073150635</v>
       </c>
       <c r="H403" t="n">
         <v>93384</v>
@@ -12172,7 +12172,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G407" t="n">
-        <v>28.9923419952393</v>
+        <v>28.9923439025879</v>
       </c>
       <c r="H407" t="n">
         <v>32363</v>
@@ -12201,7 +12201,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477825164795</v>
+        <v>28.9477806091309</v>
       </c>
       <c r="H408" t="n">
         <v>25669</v>
@@ -12259,7 +12259,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G410" t="n">
-        <v>29.6073093414307</v>
+        <v>29.607307434082</v>
       </c>
       <c r="H410" t="n">
         <v>24264</v>
@@ -12317,7 +12317,7 @@
         <v>32.9900016784668</v>
       </c>
       <c r="G412" t="n">
-        <v>29.4023189544678</v>
+        <v>29.4023208618164</v>
       </c>
       <c r="H412" t="n">
         <v>67361</v>
@@ -12346,7 +12346,7 @@
         <v>33</v>
       </c>
       <c r="G413" t="n">
-        <v>29.4112281799316</v>
+        <v>29.4112319946289</v>
       </c>
       <c r="H413" t="n">
         <v>55788</v>
@@ -12375,7 +12375,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G414" t="n">
-        <v>28.8140983581543</v>
+        <v>28.814094543457</v>
       </c>
       <c r="H414" t="n">
         <v>37331</v>
@@ -12404,7 +12404,7 @@
         <v>33</v>
       </c>
       <c r="G415" t="n">
-        <v>29.4112281799316</v>
+        <v>29.4112319946289</v>
       </c>
       <c r="H415" t="n">
         <v>48065</v>
@@ -12433,7 +12433,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.6875152587891</v>
+        <v>29.687520980835</v>
       </c>
       <c r="H416" t="n">
         <v>61558</v>
@@ -12491,7 +12491,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>29.6786060333252</v>
+        <v>29.6786041259766</v>
       </c>
       <c r="H418" t="n">
         <v>29416</v>
@@ -12520,7 +12520,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964282989502</v>
+        <v>29.6964302062988</v>
       </c>
       <c r="H419" t="n">
         <v>28781</v>
@@ -12578,7 +12578,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390350341797</v>
+        <v>29.8390293121338</v>
       </c>
       <c r="H421" t="n">
         <v>26190</v>
@@ -12665,7 +12665,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.5181770324707</v>
+        <v>29.5181789398193</v>
       </c>
       <c r="H424" t="n">
         <v>23018</v>
@@ -12694,7 +12694,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G425" t="n">
-        <v>29.1795082092285</v>
+        <v>29.1795063018799</v>
       </c>
       <c r="H425" t="n">
         <v>93713</v>
@@ -12723,7 +12723,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>29.437967300415</v>
+        <v>29.4379692077637</v>
       </c>
       <c r="H426" t="n">
         <v>57589</v>
@@ -12752,7 +12752,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648662567139</v>
+        <v>30.3648681640625</v>
       </c>
       <c r="H427" t="n">
         <v>64685</v>
@@ -12781,7 +12781,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629096984863</v>
+        <v>30.4629077911377</v>
       </c>
       <c r="H428" t="n">
         <v>65836</v>
@@ -12810,7 +12810,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024787902832</v>
       </c>
       <c r="H429" t="n">
         <v>35077</v>
@@ -12868,7 +12868,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G431" t="n">
-        <v>30.2935676574707</v>
+        <v>30.2935695648193</v>
       </c>
       <c r="H431" t="n">
         <v>27202</v>
@@ -12897,7 +12897,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974941253662</v>
+        <v>30.0974903106689</v>
       </c>
       <c r="H432" t="n">
         <v>12531</v>
@@ -12926,7 +12926,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.0618457794189</v>
+        <v>30.0618438720703</v>
       </c>
       <c r="H433" t="n">
         <v>32928</v>
@@ -12955,7 +12955,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.23118019104</v>
+        <v>30.2311744689941</v>
       </c>
       <c r="H434" t="n">
         <v>24161</v>
@@ -13042,7 +13042,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>31.4967517852783</v>
+        <v>31.4967555999756</v>
       </c>
       <c r="H437" t="n">
         <v>105328</v>
@@ -13071,7 +13071,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G438" t="n">
-        <v>30.8194065093994</v>
+        <v>30.819408416748</v>
       </c>
       <c r="H438" t="n">
         <v>80310</v>
@@ -13187,7 +13187,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928272247314</v>
+        <v>31.6928310394287</v>
       </c>
       <c r="H442" t="n">
         <v>33799</v>
@@ -13216,7 +13216,7 @@
         <v>36.1100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>32.1830177307129</v>
+        <v>32.1830139160156</v>
       </c>
       <c r="H443" t="n">
         <v>74880</v>
@@ -13245,7 +13245,7 @@
         <v>35.9900016784668</v>
       </c>
       <c r="G444" t="n">
-        <v>32.0760688781738</v>
+        <v>32.0760650634766</v>
       </c>
       <c r="H444" t="n">
         <v>50553</v>
@@ -13274,7 +13274,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.951286315918</v>
+        <v>31.9512901306152</v>
       </c>
       <c r="H445" t="n">
         <v>54557</v>
@@ -13303,7 +13303,7 @@
         <v>36.25</v>
       </c>
       <c r="G446" t="n">
-        <v>32.3077926635742</v>
+        <v>32.307788848877</v>
       </c>
       <c r="H446" t="n">
         <v>79657</v>
@@ -13332,7 +13332,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990432739258</v>
+        <v>33.1990356445312</v>
       </c>
       <c r="H447" t="n">
         <v>128921</v>
@@ -13361,7 +13361,7 @@
         <v>37.4700012207031</v>
       </c>
       <c r="G448" t="n">
-        <v>33.3951225280762</v>
+        <v>33.3951148986816</v>
       </c>
       <c r="H448" t="n">
         <v>44537</v>
@@ -13419,7 +13419,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>34.6963386535645</v>
+        <v>34.6963424682617</v>
       </c>
       <c r="H450" t="n">
         <v>96401</v>
@@ -13680,7 +13680,7 @@
         <v>39.5200004577637</v>
       </c>
       <c r="G459" t="n">
-        <v>35.2221794128418</v>
+        <v>35.2221755981445</v>
       </c>
       <c r="H459" t="n">
         <v>35360</v>
@@ -13767,7 +13767,7 @@
         <v>38</v>
       </c>
       <c r="G462" t="n">
-        <v>33.8674774169922</v>
+        <v>33.8674812316895</v>
       </c>
       <c r="H462" t="n">
         <v>58890</v>
@@ -13825,7 +13825,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G464" t="n">
-        <v>34.1437644958496</v>
+        <v>34.1437683105469</v>
       </c>
       <c r="H464" t="n">
         <v>21788</v>
@@ -13854,7 +13854,7 @@
         <v>38</v>
       </c>
       <c r="G465" t="n">
-        <v>33.8674774169922</v>
+        <v>33.8674812316895</v>
       </c>
       <c r="H465" t="n">
         <v>19781</v>
@@ -13883,7 +13883,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G466" t="n">
-        <v>33.7159652709961</v>
+        <v>33.7159729003906</v>
       </c>
       <c r="H466" t="n">
         <v>30408</v>
@@ -13912,7 +13912,7 @@
         <v>38.2200012207031</v>
       </c>
       <c r="G467" t="n">
-        <v>34.0635566711426</v>
+        <v>34.0635528564453</v>
       </c>
       <c r="H467" t="n">
         <v>45044</v>
@@ -13941,7 +13941,7 @@
         <v>38.5</v>
       </c>
       <c r="G468" t="n">
-        <v>34.3131065368652</v>
+        <v>34.3130989074707</v>
       </c>
       <c r="H468" t="n">
         <v>152768</v>
@@ -13970,7 +13970,7 @@
         <v>38.5</v>
       </c>
       <c r="G469" t="n">
-        <v>34.3131065368652</v>
+        <v>34.3130989074707</v>
       </c>
       <c r="H469" t="n">
         <v>119331</v>
@@ -14144,7 +14144,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041915893555</v>
+        <v>34.3041954040527</v>
       </c>
       <c r="H475" t="n">
         <v>35545</v>
@@ -14231,7 +14231,7 @@
         <v>38.25</v>
       </c>
       <c r="G478" t="n">
-        <v>34.0902938842773</v>
+        <v>34.0902900695801</v>
       </c>
       <c r="H478" t="n">
         <v>89938</v>
@@ -14260,7 +14260,7 @@
         <v>39.3899993896484</v>
       </c>
       <c r="G479" t="n">
-        <v>35.106315612793</v>
+        <v>35.1063194274902</v>
       </c>
       <c r="H479" t="n">
         <v>154448</v>
@@ -14376,7 +14376,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>36.4966659545898</v>
+        <v>36.4966621398926</v>
       </c>
       <c r="H483" t="n">
         <v>94288</v>
@@ -14434,7 +14434,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.858470916748</v>
+        <v>38.8584747314453</v>
       </c>
       <c r="H485" t="n">
         <v>114697</v>
@@ -14492,7 +14492,7 @@
         <v>43.3300018310547</v>
       </c>
       <c r="G487" t="n">
-        <v>38.6178436279297</v>
+        <v>38.6178359985352</v>
       </c>
       <c r="H487" t="n">
         <v>81528</v>
@@ -14579,7 +14579,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G490" t="n">
-        <v>38.4306716918945</v>
+        <v>38.4306755065918</v>
       </c>
       <c r="H490" t="n">
         <v>37738</v>
@@ -14608,7 +14608,7 @@
         <v>44</v>
       </c>
       <c r="G491" t="n">
-        <v>39.2149772644043</v>
+        <v>39.214973449707</v>
       </c>
       <c r="H491" t="n">
         <v>80819</v>
@@ -14637,7 +14637,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.8050003051758</v>
+        <v>38.805004119873</v>
       </c>
       <c r="H492" t="n">
         <v>92161</v>
@@ -14782,7 +14782,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.341552734375</v>
+        <v>38.3415489196777</v>
       </c>
       <c r="H497" t="n">
         <v>44383</v>
@@ -14869,7 +14869,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G500" t="n">
-        <v>38.4306716918945</v>
+        <v>38.4306755065918</v>
       </c>
       <c r="H500" t="n">
         <v>89203</v>
@@ -14927,7 +14927,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.689136505127</v>
+        <v>38.6891326904297</v>
       </c>
       <c r="H502" t="n">
         <v>37927</v>
@@ -15014,7 +15014,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>39.0812835693359</v>
+        <v>39.0812873840332</v>
       </c>
       <c r="H505" t="n">
         <v>45135</v>
@@ -15130,7 +15130,7 @@
         <v>42.9599990844727</v>
       </c>
       <c r="G509" t="n">
-        <v>38.2880706787109</v>
+        <v>38.2880744934082</v>
       </c>
       <c r="H509" t="n">
         <v>18466</v>
@@ -15159,7 +15159,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G510" t="n">
-        <v>38.3772048950195</v>
+        <v>38.3772087097168</v>
       </c>
       <c r="H510" t="n">
         <v>23866</v>
@@ -15217,7 +15217,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G512" t="n">
-        <v>36.6125259399414</v>
+        <v>36.6125335693359</v>
       </c>
       <c r="H512" t="n">
         <v>50757</v>
@@ -15246,7 +15246,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G513" t="n">
-        <v>37.6820259094238</v>
+        <v>37.6820220947266</v>
       </c>
       <c r="H513" t="n">
         <v>41367</v>
@@ -15275,7 +15275,7 @@
         <v>43.1599998474121</v>
       </c>
       <c r="G514" t="n">
-        <v>38.4663276672363</v>
+        <v>38.4663238525391</v>
       </c>
       <c r="H514" t="n">
         <v>46576</v>
@@ -15333,7 +15333,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G516" t="n">
-        <v>42.6551971435547</v>
+        <v>42.655200958252</v>
       </c>
       <c r="H516" t="n">
         <v>71031</v>
@@ -15362,7 +15362,7 @@
         <v>48.0400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>42.8156204223633</v>
+        <v>42.8156242370605</v>
       </c>
       <c r="H517" t="n">
         <v>52703</v>
@@ -15449,7 +15449,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G520" t="n">
-        <v>42.0847969055176</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H520" t="n">
         <v>21408</v>
@@ -15565,7 +15565,7 @@
         <v>46.8600006103516</v>
       </c>
       <c r="G524" t="n">
-        <v>41.7639503479004</v>
+        <v>41.7639465332031</v>
       </c>
       <c r="H524" t="n">
         <v>22587</v>
@@ -15594,7 +15594,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G525" t="n">
-        <v>42.0847969055176</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H525" t="n">
         <v>27575</v>
@@ -15623,7 +15623,7 @@
         <v>47.2799987792969</v>
       </c>
       <c r="G526" t="n">
-        <v>42.1382675170898</v>
+        <v>42.1382713317871</v>
       </c>
       <c r="H526" t="n">
         <v>32130</v>
@@ -15710,7 +15710,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>41.5322189331055</v>
+        <v>41.5322227478027</v>
       </c>
       <c r="H529" t="n">
         <v>36997</v>
@@ -15739,7 +15739,7 @@
         <v>46.8800010681152</v>
       </c>
       <c r="G530" t="n">
-        <v>41.7817726135254</v>
+        <v>41.7817687988281</v>
       </c>
       <c r="H530" t="n">
         <v>30670</v>
@@ -15855,7 +15855,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G534" t="n">
-        <v>40.5875015258789</v>
+        <v>40.5874977111816</v>
       </c>
       <c r="H534" t="n">
         <v>32810</v>
@@ -15884,7 +15884,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G535" t="n">
-        <v>39.8031997680664</v>
+        <v>39.8031959533691</v>
       </c>
       <c r="H535" t="n">
         <v>40370</v>
@@ -15913,7 +15913,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G536" t="n">
-        <v>39.1436729431152</v>
+        <v>39.143669128418</v>
       </c>
       <c r="H536" t="n">
         <v>97085</v>
@@ -15942,7 +15942,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784248352051</v>
+        <v>39.6784210205078</v>
       </c>
       <c r="H537" t="n">
         <v>153620</v>
@@ -16000,7 +16000,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G539" t="n">
-        <v>41.4787521362305</v>
+        <v>41.4787483215332</v>
       </c>
       <c r="H539" t="n">
         <v>164721</v>
@@ -16174,7 +16174,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>40.1953506469727</v>
+        <v>40.1953468322754</v>
       </c>
       <c r="H545" t="n">
         <v>42666</v>
@@ -16232,7 +16232,7 @@
         <v>45.5200004577637</v>
       </c>
       <c r="G547" t="n">
-        <v>40.5696754455566</v>
+        <v>40.5696716308594</v>
       </c>
       <c r="H547" t="n">
         <v>75371</v>
@@ -16261,7 +16261,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G548" t="n">
-        <v>40.801399230957</v>
+        <v>40.8013954162598</v>
       </c>
       <c r="H548" t="n">
         <v>30062</v>
@@ -16319,7 +16319,7 @@
         <v>45.7799987792969</v>
       </c>
       <c r="G550" t="n">
-        <v>40.801399230957</v>
+        <v>40.8013954162598</v>
       </c>
       <c r="H550" t="n">
         <v>59354</v>
@@ -16348,7 +16348,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400718688965</v>
+        <v>41.1400756835938</v>
       </c>
       <c r="H551" t="n">
         <v>31765</v>
@@ -16435,7 +16435,7 @@
         <v>45.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>40.9618186950684</v>
+        <v>40.9618225097656</v>
       </c>
       <c r="H554" t="n">
         <v>94078</v>
@@ -16464,7 +16464,7 @@
         <v>44.0400009155273</v>
       </c>
       <c r="G555" t="n">
-        <v>39.2506294250488</v>
+        <v>39.2506217956543</v>
       </c>
       <c r="H555" t="n">
         <v>114926</v>
@@ -16493,7 +16493,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793251037598</v>
+        <v>39.1793212890625</v>
       </c>
       <c r="H556" t="n">
         <v>64193</v>
@@ -16522,7 +16522,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131690979004</v>
+        <v>40.2131729125977</v>
       </c>
       <c r="H557" t="n">
         <v>48880</v>
@@ -16551,7 +16551,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914260864258</v>
+        <v>40.3914222717285</v>
       </c>
       <c r="H558" t="n">
         <v>72029</v>
@@ -16609,7 +16609,7 @@
         <v>46.439998626709</v>
       </c>
       <c r="G560" t="n">
-        <v>41.3896217346191</v>
+        <v>41.3896255493164</v>
       </c>
       <c r="H560" t="n">
         <v>94283</v>
@@ -16638,7 +16638,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>42.6017189025879</v>
+        <v>42.6017265319824</v>
       </c>
       <c r="H561" t="n">
         <v>139514</v>
@@ -16725,7 +16725,7 @@
         <v>50.75</v>
       </c>
       <c r="G564" t="n">
-        <v>45.2309074401855</v>
+        <v>45.2309112548828</v>
       </c>
       <c r="H564" t="n">
         <v>99680</v>
@@ -16754,7 +16754,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G565" t="n">
-        <v>43.8851203918457</v>
+        <v>43.8851280212402</v>
       </c>
       <c r="H565" t="n">
         <v>305117</v>
@@ -16870,7 +16870,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>45.9439086914062</v>
+        <v>45.943904876709</v>
       </c>
       <c r="H569" t="n">
         <v>178635</v>
@@ -16899,7 +16899,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874099731445</v>
+        <v>45.5874061584473</v>
       </c>
       <c r="H570" t="n">
         <v>120878</v>
@@ -16986,7 +16986,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494682312012</v>
+        <v>43.8494720458984</v>
       </c>
       <c r="H573" t="n">
         <v>65658</v>
@@ -17044,7 +17044,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>42.6551971435547</v>
+        <v>42.655200958252</v>
       </c>
       <c r="H575" t="n">
         <v>111110</v>
@@ -17073,7 +17073,7 @@
         <v>46.5200004577637</v>
       </c>
       <c r="G576" t="n">
-        <v>41.4609260559082</v>
+        <v>41.4609222412109</v>
       </c>
       <c r="H576" t="n">
         <v>100832</v>
@@ -17102,7 +17102,7 @@
         <v>46.5400009155273</v>
       </c>
       <c r="G577" t="n">
-        <v>41.4787521362305</v>
+        <v>41.4787483215332</v>
       </c>
       <c r="H577" t="n">
         <v>76270</v>
@@ -17189,7 +17189,7 @@
         <v>46.0200004577637</v>
       </c>
       <c r="G580" t="n">
-        <v>41.0152969360352</v>
+        <v>41.0152931213379</v>
       </c>
       <c r="H580" t="n">
         <v>49188</v>
@@ -17218,7 +17218,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675514221191</v>
       </c>
       <c r="H581" t="n">
         <v>81341</v>
@@ -17247,7 +17247,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G582" t="n">
-        <v>39.8031997680664</v>
+        <v>39.8031959533691</v>
       </c>
       <c r="H582" t="n">
         <v>46802</v>
@@ -17363,7 +17363,7 @@
         <v>45.5</v>
       </c>
       <c r="G586" t="n">
-        <v>40.5518493652344</v>
+        <v>40.5518531799316</v>
       </c>
       <c r="H586" t="n">
         <v>51926</v>
@@ -17392,7 +17392,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7319030761719</v>
+        <v>39.7318954467773</v>
       </c>
       <c r="H587" t="n">
         <v>42227</v>
@@ -17450,7 +17450,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675514221191</v>
       </c>
       <c r="H589" t="n">
         <v>23775</v>
@@ -17479,7 +17479,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488250732422</v>
+        <v>40.2488288879395</v>
       </c>
       <c r="H590" t="n">
         <v>41714</v>
@@ -17566,7 +17566,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G593" t="n">
-        <v>39.1436729431152</v>
+        <v>39.143669128418</v>
       </c>
       <c r="H593" t="n">
         <v>46759</v>
@@ -17595,7 +17595,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>39.0367240905762</v>
+        <v>39.0367202758789</v>
       </c>
       <c r="H594" t="n">
         <v>36577</v>
@@ -17682,7 +17682,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.0509490966797</v>
+        <v>41.050952911377</v>
       </c>
       <c r="H597" t="n">
         <v>57439</v>
@@ -17769,7 +17769,7 @@
         <v>45.2000007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>40.7087097167969</v>
+        <v>40.7087059020996</v>
       </c>
       <c r="H600" t="n">
         <v>23543</v>
@@ -17856,7 +17856,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G603" t="n">
-        <v>39.8441009521484</v>
+        <v>39.8440971374512</v>
       </c>
       <c r="H603" t="n">
         <v>60714</v>
@@ -17914,7 +17914,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.4844360351562</v>
+        <v>37.484432220459</v>
       </c>
       <c r="H605" t="n">
         <v>87797</v>
@@ -17943,7 +17943,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316192626953</v>
+        <v>36.3316230773926</v>
       </c>
       <c r="H606" t="n">
         <v>66466</v>
@@ -17972,7 +17972,7 @@
         <v>41.1399993896484</v>
       </c>
       <c r="G607" t="n">
-        <v>37.0521240234375</v>
+        <v>37.0521278381348</v>
       </c>
       <c r="H607" t="n">
         <v>93918</v>
@@ -18059,7 +18059,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.0073928833008</v>
+        <v>36.0073890686035</v>
       </c>
       <c r="H610" t="n">
         <v>71270</v>
@@ -18146,7 +18146,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241401672363</v>
       </c>
       <c r="H613" t="n">
         <v>88495</v>
@@ -18262,7 +18262,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G617" t="n">
-        <v>34.4763145446777</v>
+        <v>34.4763107299805</v>
       </c>
       <c r="H617" t="n">
         <v>85349</v>
@@ -18291,7 +18291,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924667358398</v>
+        <v>34.6924629211426</v>
       </c>
       <c r="H618" t="n">
         <v>73867</v>
@@ -18436,7 +18436,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241401672363</v>
       </c>
       <c r="H623" t="n">
         <v>21903</v>
@@ -18552,7 +18552,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247749328613</v>
+        <v>35.1247711181641</v>
       </c>
       <c r="H627" t="n">
         <v>103614</v>
@@ -18581,7 +18581,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>33.5036277770996</v>
+        <v>33.5036239624023</v>
       </c>
       <c r="H628" t="n">
         <v>53029</v>
@@ -18610,7 +18610,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.4048538208008</v>
+        <v>32.4048500061035</v>
       </c>
       <c r="H629" t="n">
         <v>77422</v>
@@ -18639,7 +18639,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>32.3868408203125</v>
+        <v>32.3868370056152</v>
       </c>
       <c r="H630" t="n">
         <v>57634</v>
@@ -18726,7 +18726,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G633" t="n">
-        <v>30.5315361022949</v>
+        <v>30.5315341949463</v>
       </c>
       <c r="H633" t="n">
         <v>75764</v>
@@ -18755,7 +18755,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.486795425415</v>
+        <v>29.4867935180664</v>
       </c>
       <c r="H634" t="n">
         <v>160938</v>
@@ -18784,7 +18784,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371128082275</v>
+        <v>29.9371166229248</v>
       </c>
       <c r="H635" t="n">
         <v>311338</v>
@@ -18813,7 +18813,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346153259277</v>
+        <v>29.2346172332764</v>
       </c>
       <c r="H636" t="n">
         <v>86489</v>
@@ -18842,7 +18842,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.1532649993896</v>
+        <v>30.153263092041</v>
       </c>
       <c r="H637" t="n">
         <v>47812</v>
@@ -18900,7 +18900,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147434234619</v>
+        <v>29.4147415161133</v>
       </c>
       <c r="H639" t="n">
         <v>66878</v>
@@ -18958,7 +18958,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G641" t="n">
-        <v>29.1265411376953</v>
+        <v>29.1265392303467</v>
       </c>
       <c r="H641" t="n">
         <v>126609</v>
@@ -19016,7 +19016,7 @@
         <v>33.9799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>30.6035823822021</v>
+        <v>30.6035804748535</v>
       </c>
       <c r="H643" t="n">
         <v>77878</v>
@@ -19045,7 +19045,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520427703857</v>
+        <v>31.2520408630371</v>
       </c>
       <c r="H644" t="n">
         <v>161628</v>
@@ -19074,7 +19074,7 @@
         <v>32.9199981689453</v>
       </c>
       <c r="G645" t="n">
-        <v>29.6489086151123</v>
+        <v>29.6489067077637</v>
       </c>
       <c r="H645" t="n">
         <v>97694</v>
@@ -19103,7 +19103,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551219940186</v>
+        <v>29.9551239013672</v>
       </c>
       <c r="H646" t="n">
         <v>48258</v>
@@ -19132,7 +19132,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172389984131</v>
+        <v>30.1172351837158</v>
       </c>
       <c r="H647" t="n">
         <v>44619</v>
@@ -19161,7 +19161,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054393768311</v>
+        <v>30.4054374694824</v>
       </c>
       <c r="H648" t="n">
         <v>33638</v>
@@ -19190,7 +19190,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>30.5315361022949</v>
+        <v>30.5315341949463</v>
       </c>
       <c r="H649" t="n">
         <v>62064</v>
@@ -19219,7 +19219,7 @@
         <v>35.1599998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>31.6663360595703</v>
+        <v>31.666332244873</v>
       </c>
       <c r="H650" t="n">
         <v>110112</v>
@@ -19248,7 +19248,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>31.6483173370361</v>
+        <v>31.6483211517334</v>
       </c>
       <c r="H651" t="n">
         <v>95229</v>
@@ -19277,7 +19277,7 @@
         <v>35.6199989318848</v>
       </c>
       <c r="G652" t="n">
-        <v>32.0806159973145</v>
+        <v>32.080623626709</v>
       </c>
       <c r="H652" t="n">
         <v>85998</v>
@@ -19335,7 +19335,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601150512695</v>
+        <v>31.3601169586182</v>
       </c>
       <c r="H654" t="n">
         <v>42779</v>
@@ -19422,7 +19422,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520427703857</v>
+        <v>31.2520408630371</v>
       </c>
       <c r="H657" t="n">
         <v>35703</v>
@@ -19451,7 +19451,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122894287109</v>
+        <v>31.6122875213623</v>
       </c>
       <c r="H658" t="n">
         <v>29583</v>
@@ -19509,7 +19509,7 @@
         <v>34.2400016784668</v>
       </c>
       <c r="G660" t="n">
-        <v>30.8377456665039</v>
+        <v>30.8377475738525</v>
       </c>
       <c r="H660" t="n">
         <v>41227</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.9010887145996</v>
+        <v>29.901086807251</v>
       </c>
       <c r="H662" t="n">
         <v>24019</v>
@@ -19596,7 +19596,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346153259277</v>
+        <v>29.2346172332764</v>
       </c>
       <c r="H663" t="n">
         <v>57598</v>
@@ -19654,7 +19654,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>29.0905132293701</v>
+        <v>29.0905151367188</v>
       </c>
       <c r="H665" t="n">
         <v>24107</v>
@@ -19712,7 +19712,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G667" t="n">
-        <v>28.0998191833496</v>
+        <v>28.099817276001</v>
       </c>
       <c r="H667" t="n">
         <v>106675</v>
@@ -19741,7 +19741,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G668" t="n">
-        <v>27.595458984375</v>
+        <v>27.5954608917236</v>
       </c>
       <c r="H668" t="n">
         <v>30813</v>
@@ -19770,7 +19770,7 @@
         <v>29.5799999237061</v>
       </c>
       <c r="G669" t="n">
-        <v>26.6407871246338</v>
+        <v>26.6407890319824</v>
       </c>
       <c r="H669" t="n">
         <v>54672</v>
@@ -19828,7 +19828,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>26.0463676452637</v>
+        <v>26.0463695526123</v>
       </c>
       <c r="H671" t="n">
         <v>28977</v>
@@ -19857,7 +19857,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>26.5146999359131</v>
+        <v>26.5146980285645</v>
       </c>
       <c r="H672" t="n">
         <v>22536</v>
@@ -19915,7 +19915,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550804138184</v>
       </c>
       <c r="H674" t="n">
         <v>59352</v>
@@ -20031,7 +20031,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G678" t="n">
-        <v>26.7488632202148</v>
+        <v>26.7488651275635</v>
       </c>
       <c r="H678" t="n">
         <v>33597</v>
@@ -20060,7 +20060,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693717956543</v>
       </c>
       <c r="H679" t="n">
         <v>30485</v>
@@ -20089,7 +20089,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H680" t="n">
         <v>46685</v>
@@ -20118,7 +20118,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G681" t="n">
-        <v>27.577449798584</v>
+        <v>27.5774478912354</v>
       </c>
       <c r="H681" t="n">
         <v>43724</v>
@@ -20205,7 +20205,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476371765137</v>
+        <v>27.8476409912109</v>
       </c>
       <c r="H684" t="n">
         <v>50842</v>
@@ -20263,7 +20263,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693717956543</v>
       </c>
       <c r="H686" t="n">
         <v>52867</v>
@@ -20292,7 +20292,7 @@
         <v>31.1399993896484</v>
       </c>
       <c r="G687" t="n">
-        <v>28.0457763671875</v>
+        <v>28.0457782745361</v>
       </c>
       <c r="H687" t="n">
         <v>23832</v>
@@ -20321,7 +20321,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>28.0097541809082</v>
+        <v>28.0097522735596</v>
       </c>
       <c r="H688" t="n">
         <v>31923</v>
@@ -20379,7 +20379,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.0097541809082</v>
+        <v>28.0097522735596</v>
       </c>
       <c r="H690" t="n">
         <v>44005</v>
@@ -20466,7 +20466,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>28.5501346588135</v>
+        <v>28.5501327514648</v>
       </c>
       <c r="H693" t="n">
         <v>27520</v>
@@ -20495,7 +20495,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>29.1805801391602</v>
+        <v>29.1805820465088</v>
       </c>
       <c r="H694" t="n">
         <v>37376</v>
@@ -20582,7 +20582,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401958465576</v>
+        <v>28.6401977539062</v>
       </c>
       <c r="H697" t="n">
         <v>27160</v>
@@ -20611,7 +20611,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762237548828</v>
+        <v>28.6762218475342</v>
       </c>
       <c r="H698" t="n">
         <v>35302</v>
@@ -20640,7 +20640,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G699" t="n">
-        <v>27.6675090789795</v>
+        <v>27.6675109863281</v>
       </c>
       <c r="H699" t="n">
         <v>42864</v>
@@ -20669,7 +20669,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550804138184</v>
       </c>
       <c r="H700" t="n">
         <v>32431</v>
@@ -20698,7 +20698,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>27.595458984375</v>
+        <v>27.5954608917236</v>
       </c>
       <c r="H701" t="n">
         <v>221272</v>
@@ -20727,7 +20727,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H702" t="n">
         <v>26734</v>
@@ -20756,7 +20756,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G703" t="n">
-        <v>27.451358795166</v>
+        <v>27.4513607025146</v>
       </c>
       <c r="H703" t="n">
         <v>119469</v>
@@ -20785,7 +20785,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H704" t="n">
         <v>37755</v>
@@ -20872,7 +20872,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320289611816</v>
+        <v>22.7320308685303</v>
       </c>
       <c r="H707" t="n">
         <v>196682</v>
@@ -20930,7 +20930,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233180999756</v>
+        <v>21.7233200073242</v>
       </c>
       <c r="H709" t="n">
         <v>130761</v>
@@ -20959,7 +20959,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860698699951</v>
+        <v>22.7860679626465</v>
       </c>
       <c r="H710" t="n">
         <v>107966</v>
@@ -21017,7 +21017,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G712" t="n">
-        <v>23.7047176361084</v>
+        <v>23.7047157287598</v>
       </c>
       <c r="H712" t="n">
         <v>61152</v>
@@ -21046,7 +21046,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606155395508</v>
+        <v>23.5606174468994</v>
       </c>
       <c r="H713" t="n">
         <v>38427</v>
@@ -21075,7 +21075,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>23.2363872528076</v>
+        <v>23.236385345459</v>
       </c>
       <c r="H714" t="n">
         <v>56594</v>
@@ -21162,7 +21162,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G717" t="n">
-        <v>21.7053089141846</v>
+        <v>21.7053070068359</v>
       </c>
       <c r="H717" t="n">
         <v>31552</v>
@@ -21249,7 +21249,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369766235352</v>
+        <v>21.2369747161865</v>
       </c>
       <c r="H720" t="n">
         <v>38258</v>
@@ -21278,7 +21278,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.3450527191162</v>
+        <v>21.3450546264648</v>
       </c>
       <c r="H721" t="n">
         <v>38719</v>
@@ -21307,7 +21307,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>21.5972270965576</v>
+        <v>21.5972309112549</v>
       </c>
       <c r="H722" t="n">
         <v>28389</v>
@@ -21336,7 +21336,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>19.7239093780518</v>
+        <v>19.7239074707031</v>
       </c>
       <c r="H723" t="n">
         <v>114037</v>
@@ -21394,7 +21394,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>18.2828922271729</v>
+        <v>18.2828941345215</v>
       </c>
       <c r="H725" t="n">
         <v>49521</v>
@@ -21452,7 +21452,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.877311706543</v>
+        <v>18.8773136138916</v>
       </c>
       <c r="H727" t="n">
         <v>78461</v>
@@ -21481,7 +21481,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>18.3909702301025</v>
+        <v>18.3909683227539</v>
       </c>
       <c r="H728" t="n">
         <v>70249</v>
@@ -21568,7 +21568,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.0036964416504</v>
+        <v>18.0036945343018</v>
       </c>
       <c r="H731" t="n">
         <v>90396</v>
@@ -21597,7 +21597,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G732" t="n">
-        <v>17.1390857696533</v>
+        <v>17.139087677002</v>
       </c>
       <c r="H732" t="n">
         <v>49459</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120700836182</v>
       </c>
       <c r="H733" t="n">
         <v>71224</v>
@@ -21713,7 +21713,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.2024269104004</v>
+        <v>16.2024250030518</v>
       </c>
       <c r="H736" t="n">
         <v>53336</v>
@@ -21742,7 +21742,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.950249671936</v>
+        <v>15.9502458572388</v>
       </c>
       <c r="H737" t="n">
         <v>57508</v>
@@ -21771,7 +21771,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.7160835266113</v>
+        <v>15.7160844802856</v>
       </c>
       <c r="H738" t="n">
         <v>81701</v>
@@ -21800,7 +21800,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800575256348</v>
+        <v>15.6800584793091</v>
       </c>
       <c r="H739" t="n">
         <v>56603</v>
@@ -21858,7 +21858,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G741" t="n">
-        <v>16.1573963165283</v>
+        <v>16.1573925018311</v>
       </c>
       <c r="H741" t="n">
         <v>30250</v>
@@ -21887,7 +21887,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077136993408</v>
+        <v>16.6077117919922</v>
       </c>
       <c r="H742" t="n">
         <v>126448</v>
@@ -21916,7 +21916,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G743" t="n">
-        <v>16.4005661010742</v>
+        <v>16.4005641937256</v>
       </c>
       <c r="H743" t="n">
         <v>110085</v>
@@ -21945,7 +21945,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>17.4723205566406</v>
+        <v>17.4723224639893</v>
       </c>
       <c r="H744" t="n">
         <v>93088</v>
@@ -22032,7 +22032,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G747" t="n">
-        <v>17.9406509399414</v>
+        <v>17.9406490325928</v>
       </c>
       <c r="H747" t="n">
         <v>117827</v>
@@ -22119,7 +22119,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968463897705</v>
+        <v>16.7968444824219</v>
       </c>
       <c r="H750" t="n">
         <v>72692</v>
@@ -22206,7 +22206,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.9052181243896</v>
+        <v>15.905216217041</v>
       </c>
       <c r="H753" t="n">
         <v>55986</v>
@@ -22235,7 +22235,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G754" t="n">
-        <v>16.2654685974121</v>
+        <v>16.2654705047607</v>
       </c>
       <c r="H754" t="n">
         <v>85504</v>
@@ -22264,7 +22264,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>16.1934204101562</v>
+        <v>16.1934185028076</v>
       </c>
       <c r="H755" t="n">
         <v>54198</v>
@@ -22351,7 +22351,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496139526367</v>
+        <v>15.0496129989624</v>
       </c>
       <c r="H758" t="n">
         <v>39650</v>
@@ -22380,7 +22380,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800575256348</v>
+        <v>15.6800584793091</v>
       </c>
       <c r="H759" t="n">
         <v>53012</v>
@@ -22438,7 +22438,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899925231934</v>
+        <v>15.5899934768677</v>
       </c>
       <c r="H761" t="n">
         <v>79930</v>
@@ -22467,7 +22467,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>15.1486835479736</v>
+        <v>15.1486825942993</v>
       </c>
       <c r="H762" t="n">
         <v>108666</v>
@@ -22496,7 +22496,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.463903427124</v>
+        <v>15.4639053344727</v>
       </c>
       <c r="H763" t="n">
         <v>62260</v>
@@ -22583,7 +22583,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H766" t="n">
         <v>115896</v>
@@ -22641,7 +22641,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.391263961792</v>
+        <v>17.3912658691406</v>
       </c>
       <c r="H768" t="n">
         <v>73850</v>
@@ -22728,7 +22728,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G771" t="n">
-        <v>18.2288551330566</v>
+        <v>18.228853225708</v>
       </c>
       <c r="H771" t="n">
         <v>74008</v>
@@ -22844,7 +22844,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.454309463501</v>
+        <v>17.4543113708496</v>
       </c>
       <c r="H775" t="n">
         <v>38968</v>
@@ -22873,7 +22873,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791744232178</v>
+        <v>18.6791725158691</v>
       </c>
       <c r="H776" t="n">
         <v>84665</v>
@@ -22902,7 +22902,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G777" t="n">
-        <v>18.8052616119385</v>
+        <v>18.8052635192871</v>
       </c>
       <c r="H777" t="n">
         <v>56710</v>
@@ -22960,7 +22960,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G779" t="n">
-        <v>18.3369331359863</v>
+        <v>18.3369312286377</v>
       </c>
       <c r="H779" t="n">
         <v>51138</v>
@@ -23047,7 +23047,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G782" t="n">
-        <v>18.9493637084961</v>
+        <v>18.9493656158447</v>
       </c>
       <c r="H782" t="n">
         <v>40418</v>
@@ -23105,7 +23105,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G784" t="n">
-        <v>18.6971874237061</v>
+        <v>18.6971855163574</v>
       </c>
       <c r="H784" t="n">
         <v>38581</v>
@@ -23221,7 +23221,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G788" t="n">
-        <v>18.4269924163818</v>
+        <v>18.4269943237305</v>
       </c>
       <c r="H788" t="n">
         <v>64191</v>
@@ -23453,7 +23453,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698684692383</v>
+        <v>19.6698703765869</v>
       </c>
       <c r="H796" t="n">
         <v>111608</v>
@@ -23482,7 +23482,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>20.2462749481201</v>
+        <v>20.2462787628174</v>
       </c>
       <c r="H797" t="n">
         <v>77155</v>
@@ -23511,7 +23511,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G798" t="n">
-        <v>20.0661525726318</v>
+        <v>20.0661506652832</v>
       </c>
       <c r="H798" t="n">
         <v>47640</v>
@@ -23540,7 +23540,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G799" t="n">
-        <v>19.9220504760742</v>
+        <v>19.9220485687256</v>
       </c>
       <c r="H799" t="n">
         <v>43219</v>
@@ -23569,7 +23569,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G800" t="n">
-        <v>19.4176921844482</v>
+        <v>19.4176940917969</v>
       </c>
       <c r="H800" t="n">
         <v>43308</v>
@@ -23598,7 +23598,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537200927734</v>
+        <v>19.4537220001221</v>
       </c>
       <c r="H801" t="n">
         <v>38620</v>
@@ -23627,7 +23627,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G802" t="n">
-        <v>20.2823047637939</v>
+        <v>20.2823028564453</v>
       </c>
       <c r="H802" t="n">
         <v>63858</v>
@@ -23685,7 +23685,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>17.7515182495117</v>
+        <v>17.7515201568604</v>
       </c>
       <c r="H804" t="n">
         <v>362073</v>
@@ -23772,7 +23772,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>17.7965507507324</v>
+        <v>17.7965488433838</v>
       </c>
       <c r="H807" t="n">
         <v>48825</v>
@@ -23801,7 +23801,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G808" t="n">
-        <v>17.5083465576172</v>
+        <v>17.5083484649658</v>
       </c>
       <c r="H808" t="n">
         <v>79412</v>
@@ -23859,7 +23859,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508834838867</v>
+        <v>16.8508815765381</v>
       </c>
       <c r="H810" t="n">
         <v>142958</v>
@@ -23888,7 +23888,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G811" t="n">
-        <v>16.9859809875488</v>
+        <v>16.9859771728516</v>
       </c>
       <c r="H811" t="n">
         <v>69819</v>
@@ -23946,7 +23946,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120700836182</v>
       </c>
       <c r="H813" t="n">
         <v>36891</v>
@@ -23975,7 +23975,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490245819092</v>
+        <v>17.0490207672119</v>
       </c>
       <c r="H814" t="n">
         <v>19771</v>
@@ -24033,7 +24033,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462333679199</v>
+        <v>17.3462314605713</v>
       </c>
       <c r="H816" t="n">
         <v>103910</v>
@@ -24091,7 +24091,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>17.3822555541992</v>
+        <v>17.3822574615479</v>
       </c>
       <c r="H818" t="n">
         <v>52262</v>
@@ -24178,7 +24178,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.9766750335693</v>
+        <v>17.976676940918</v>
       </c>
       <c r="H821" t="n">
         <v>368484</v>
@@ -24294,7 +24294,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G825" t="n">
-        <v>17.4272918701172</v>
+        <v>17.4272899627686</v>
       </c>
       <c r="H825" t="n">
         <v>44899</v>
@@ -24323,7 +24323,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.454309463501</v>
+        <v>17.4543113708496</v>
       </c>
       <c r="H826" t="n">
         <v>48981</v>
@@ -24381,7 +24381,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G828" t="n">
-        <v>17.913631439209</v>
+        <v>17.9136333465576</v>
       </c>
       <c r="H828" t="n">
         <v>52651</v>
@@ -24497,7 +24497,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496574401855</v>
+        <v>17.9496593475342</v>
       </c>
       <c r="H832" t="n">
         <v>46935</v>
@@ -24526,7 +24526,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3822555541992</v>
+        <v>17.3822574615479</v>
       </c>
       <c r="H833" t="n">
         <v>127471</v>
@@ -24555,7 +24555,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2381572723389</v>
+        <v>17.2381553649902</v>
       </c>
       <c r="H834" t="n">
         <v>111270</v>
@@ -24584,7 +24584,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300811767578</v>
+        <v>17.1300792694092</v>
       </c>
       <c r="H835" t="n">
         <v>63235</v>
@@ -24642,7 +24642,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676704406738</v>
+        <v>17.9676723480225</v>
       </c>
       <c r="H837" t="n">
         <v>49207</v>
@@ -24700,7 +24700,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667400360107</v>
+        <v>18.0667419433594</v>
       </c>
       <c r="H839" t="n">
         <v>64387</v>
@@ -24758,7 +24758,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>17.7965507507324</v>
+        <v>17.7965488433838</v>
       </c>
       <c r="H841" t="n">
         <v>59761</v>
@@ -24816,7 +24816,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6074161529541</v>
+        <v>17.6074180603027</v>
       </c>
       <c r="H843" t="n">
         <v>31630</v>
@@ -24932,7 +24932,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H847" t="n">
         <v>58676</v>
@@ -24961,7 +24961,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>18.6365566253662</v>
+        <v>18.6365585327148</v>
       </c>
       <c r="H848" t="n">
         <v>152183</v>
@@ -25048,7 +25048,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G851" t="n">
-        <v>17.2249755859375</v>
+        <v>17.2249774932861</v>
       </c>
       <c r="H851" t="n">
         <v>61198</v>
@@ -25077,7 +25077,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G852" t="n">
-        <v>16.5330238342285</v>
+        <v>16.5330257415771</v>
       </c>
       <c r="H852" t="n">
         <v>79775</v>
@@ -25164,7 +25164,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>14.6232404708862</v>
+        <v>14.6232395172119</v>
       </c>
       <c r="H855" t="n">
         <v>212131</v>
@@ -25280,7 +25280,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>13.3131446838379</v>
+        <v>13.3131456375122</v>
       </c>
       <c r="H859" t="n">
         <v>77696</v>
@@ -25338,7 +25338,7 @@
         <v>15</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H861" t="n">
         <v>78115</v>
@@ -25367,7 +25367,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G862" t="n">
-        <v>13.4792127609253</v>
+        <v>13.4792137145996</v>
       </c>
       <c r="H862" t="n">
         <v>74086</v>
@@ -25657,7 +25657,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>13.7006387710571</v>
+        <v>13.7006378173828</v>
       </c>
       <c r="H872" t="n">
         <v>150643</v>
@@ -25715,7 +25715,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>14.4202680587769</v>
+        <v>14.4202671051025</v>
       </c>
       <c r="H874" t="n">
         <v>118791</v>
@@ -25831,7 +25831,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>13.7928972244263</v>
+        <v>13.7928981781006</v>
       </c>
       <c r="H878" t="n">
         <v>33517</v>
@@ -25860,7 +25860,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G879" t="n">
-        <v>13.6914119720459</v>
+        <v>13.6914110183716</v>
       </c>
       <c r="H879" t="n">
         <v>39249</v>
@@ -25889,7 +25889,7 @@
         <v>15</v>
       </c>
       <c r="G880" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H880" t="n">
         <v>70407</v>
@@ -26063,7 +26063,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486206054688</v>
+        <v>10.1486196517944</v>
       </c>
       <c r="H886" t="n">
         <v>520891</v>
@@ -26121,7 +26121,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G888" t="n">
-        <v>10.4069490432739</v>
+        <v>10.4069480895996</v>
       </c>
       <c r="H888" t="n">
         <v>237022</v>
@@ -26179,7 +26179,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G890" t="n">
-        <v>10.4069490432739</v>
+        <v>10.4069480895996</v>
       </c>
       <c r="H890" t="n">
         <v>125493</v>
@@ -26295,7 +26295,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G894" t="n">
-        <v>10.4807558059692</v>
+        <v>10.4807567596436</v>
       </c>
       <c r="H894" t="n">
         <v>222824</v>
@@ -26324,7 +26324,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837301254272</v>
+        <v>10.6837291717529</v>
       </c>
       <c r="H895" t="n">
         <v>124644</v>
@@ -26411,7 +26411,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.370044708252</v>
+        <v>10.3700456619263</v>
       </c>
       <c r="H898" t="n">
         <v>110215</v>
@@ -26556,7 +26556,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G903" t="n">
-        <v>9.53047657012939</v>
+        <v>9.53047752380371</v>
       </c>
       <c r="H903" t="n">
         <v>177150</v>
@@ -26585,7 +26585,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G904" t="n">
-        <v>10.0932645797729</v>
+        <v>10.0932636260986</v>
       </c>
       <c r="H904" t="n">
         <v>154899</v>
@@ -26643,7 +26643,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G906" t="n">
-        <v>10.5730180740356</v>
+        <v>10.5730171203613</v>
       </c>
       <c r="H906" t="n">
         <v>224050</v>
@@ -26730,7 +26730,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3054628372192</v>
+        <v>10.3054618835449</v>
       </c>
       <c r="H909" t="n">
         <v>167262</v>
@@ -26759,7 +26759,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438543319702</v>
+        <v>10.4438533782959</v>
       </c>
       <c r="H910" t="n">
         <v>188704</v>
@@ -26817,7 +26817,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G912" t="n">
-        <v>10.6652784347534</v>
+        <v>10.6652774810791</v>
       </c>
       <c r="H912" t="n">
         <v>140872</v>
@@ -26846,7 +26846,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286827087402</v>
+        <v>10.0286817550659</v>
       </c>
       <c r="H913" t="n">
         <v>207382</v>
@@ -26875,7 +26875,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.9640998840332</v>
+        <v>9.96410083770752</v>
       </c>
       <c r="H914" t="n">
         <v>253876</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>10.056360244751</v>
+        <v>10.0563611984253</v>
       </c>
       <c r="H915" t="n">
         <v>185001</v>
@@ -26933,7 +26933,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486206054688</v>
+        <v>10.1486196517944</v>
       </c>
       <c r="H916" t="n">
         <v>218887</v>
@@ -26991,7 +26991,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G918" t="n">
-        <v>9.50279998779297</v>
+        <v>9.50279903411865</v>
       </c>
       <c r="H918" t="n">
         <v>261117</v>
@@ -27020,7 +27020,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G919" t="n">
-        <v>9.29060077667236</v>
+        <v>9.29059982299805</v>
       </c>
       <c r="H919" t="n">
         <v>131607</v>
@@ -27049,7 +27049,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G920" t="n">
-        <v>9.57660865783691</v>
+        <v>9.5766077041626</v>
       </c>
       <c r="H920" t="n">
         <v>214640</v>
@@ -27078,7 +27078,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G921" t="n">
-        <v>9.21217918395996</v>
+        <v>9.21217823028564</v>
       </c>
       <c r="H921" t="n">
         <v>72765</v>
@@ -27165,7 +27165,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>9.29060077667236</v>
+        <v>9.29059982299805</v>
       </c>
       <c r="H924" t="n">
         <v>94925</v>
@@ -27223,7 +27223,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>9.47512149810791</v>
+        <v>9.47512245178223</v>
       </c>
       <c r="H926" t="n">
         <v>155843</v>
@@ -27281,7 +27281,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G928" t="n">
-        <v>8.94001197814941</v>
+        <v>8.94001293182373</v>
       </c>
       <c r="H928" t="n">
         <v>231622</v>
@@ -27310,7 +27310,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>8.9861421585083</v>
+        <v>8.98614120483398</v>
       </c>
       <c r="H929" t="n">
         <v>131407</v>
@@ -27339,7 +27339,7 @@
         <v>9.625</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88004398345947</v>
+        <v>8.88004302978516</v>
       </c>
       <c r="H930" t="n">
         <v>287237</v>
@@ -27397,7 +27397,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447154998779</v>
+        <v>9.24447059631348</v>
       </c>
       <c r="H932" t="n">
         <v>161867</v>
@@ -27484,7 +27484,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G935" t="n">
-        <v>9.21217918395996</v>
+        <v>9.21217823028564</v>
       </c>
       <c r="H935" t="n">
         <v>132335</v>
@@ -27513,7 +27513,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>9.88106632232666</v>
+        <v>9.88106536865234</v>
       </c>
       <c r="H936" t="n">
         <v>328350</v>
@@ -27542,7 +27542,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G937" t="n">
-        <v>9.97332763671875</v>
+        <v>9.97332668304443</v>
       </c>
       <c r="H937" t="n">
         <v>202148</v>
@@ -27571,7 +27571,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G938" t="n">
-        <v>9.99177837371826</v>
+        <v>9.99177742004395</v>
       </c>
       <c r="H938" t="n">
         <v>283851</v>
@@ -27600,7 +27600,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486206054688</v>
+        <v>10.1486196517944</v>
       </c>
       <c r="H939" t="n">
         <v>195612</v>
@@ -27745,7 +27745,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>10.084038734436</v>
+        <v>10.0840377807617</v>
       </c>
       <c r="H944" t="n">
         <v>156292</v>
@@ -27803,7 +27803,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286827087402</v>
+        <v>10.0286817550659</v>
       </c>
       <c r="H946" t="n">
         <v>131456</v>
@@ -27832,7 +27832,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G947" t="n">
-        <v>9.61351108551025</v>
+        <v>9.61351203918457</v>
       </c>
       <c r="H947" t="n">
         <v>385751</v>
@@ -27861,7 +27861,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886711120605</v>
+        <v>9.66886806488037</v>
       </c>
       <c r="H948" t="n">
         <v>129728</v>
@@ -27890,7 +27890,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>9.61351108551025</v>
+        <v>9.61351203918457</v>
       </c>
       <c r="H949" t="n">
         <v>82832</v>
@@ -27948,7 +27948,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G951" t="n">
-        <v>9.53047657012939</v>
+        <v>9.53047752380371</v>
       </c>
       <c r="H951" t="n">
         <v>116133</v>
@@ -27977,7 +27977,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886711120605</v>
+        <v>9.66886806488037</v>
       </c>
       <c r="H952" t="n">
         <v>80416</v>
@@ -28006,7 +28006,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G953" t="n">
-        <v>9.7980318069458</v>
+        <v>9.79803276062012</v>
       </c>
       <c r="H953" t="n">
         <v>64831</v>
@@ -28035,7 +28035,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G954" t="n">
-        <v>9.56738185882568</v>
+        <v>9.56738090515137</v>
       </c>
       <c r="H954" t="n">
         <v>113957</v>
@@ -28064,7 +28064,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G955" t="n">
-        <v>9.57660865783691</v>
+        <v>9.5766077041626</v>
       </c>
       <c r="H955" t="n">
         <v>120004</v>
@@ -28122,7 +28122,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>9.39208793640137</v>
+        <v>9.39208698272705</v>
       </c>
       <c r="H957" t="n">
         <v>68256</v>
@@ -28151,7 +28151,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G958" t="n">
-        <v>9.65041542053223</v>
+        <v>9.65041637420654</v>
       </c>
       <c r="H958" t="n">
         <v>160776</v>
@@ -28209,7 +28209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>9.31827831268311</v>
+        <v>9.31827926635742</v>
       </c>
       <c r="H960" t="n">
         <v>109157</v>
@@ -28325,7 +28325,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G964" t="n">
-        <v>9.88106632232666</v>
+        <v>9.88106536865234</v>
       </c>
       <c r="H964" t="n">
         <v>91898</v>
@@ -28441,7 +28441,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G968" t="n">
-        <v>10.2777862548828</v>
+        <v>10.2777853012085</v>
       </c>
       <c r="H968" t="n">
         <v>321790</v>
@@ -28470,7 +28470,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655851364136</v>
+        <v>10.0655860900879</v>
       </c>
       <c r="H969" t="n">
         <v>218375</v>
@@ -28499,7 +28499,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822439193726</v>
+        <v>10.5822448730469</v>
       </c>
       <c r="H970" t="n">
         <v>229401</v>
@@ -28557,7 +28557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G972" t="n">
-        <v>10.2870111465454</v>
+        <v>10.2870101928711</v>
       </c>
       <c r="H972" t="n">
         <v>436417</v>
@@ -28760,7 +28760,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337007522583</v>
+        <v>12.2337017059326</v>
       </c>
       <c r="H979" t="n">
         <v>516034</v>
@@ -28876,7 +28876,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G983" t="n">
-        <v>12.1414413452148</v>
+        <v>12.1414403915405</v>
       </c>
       <c r="H983" t="n">
         <v>156365</v>
@@ -28963,7 +28963,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G986" t="n">
-        <v>11.9661464691162</v>
+        <v>11.9661474227905</v>
       </c>
       <c r="H986" t="n">
         <v>115543</v>
@@ -28992,7 +28992,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G987" t="n">
-        <v>11.9569206237793</v>
+        <v>11.956919670105</v>
       </c>
       <c r="H987" t="n">
         <v>141835</v>
@@ -29021,7 +29021,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>11.7539472579956</v>
+        <v>11.7539482116699</v>
       </c>
       <c r="H988" t="n">
         <v>186372</v>
@@ -29195,7 +29195,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G994" t="n">
-        <v>13.2577896118164</v>
+        <v>13.2577886581421</v>
       </c>
       <c r="H994" t="n">
         <v>641567</v>
@@ -29253,7 +29253,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G996" t="n">
-        <v>13.0824947357178</v>
+        <v>13.0824956893921</v>
       </c>
       <c r="H996" t="n">
         <v>236235</v>
@@ -29369,7 +29369,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7559938430786</v>
+        <v>13.7559928894043</v>
       </c>
       <c r="H1000" t="n">
         <v>343538</v>
@@ -29543,7 +29543,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283153533936</v>
+        <v>13.7283163070679</v>
       </c>
       <c r="H1006" t="n">
         <v>219263</v>
@@ -29601,7 +29601,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.1342611312866</v>
+        <v>14.1342620849609</v>
       </c>
       <c r="H1008" t="n">
         <v>148543</v>
@@ -29688,7 +29688,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497394561768</v>
       </c>
       <c r="H1011" t="n">
         <v>66991</v>
@@ -29717,7 +29717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.6637344360352</v>
+        <v>13.6637353897095</v>
       </c>
       <c r="H1012" t="n">
         <v>165683</v>
@@ -29746,7 +29746,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.6637344360352</v>
+        <v>13.6637353897095</v>
       </c>
       <c r="H1013" t="n">
         <v>84386</v>
@@ -29775,7 +29775,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1014" t="n">
-        <v>13.6821851730347</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1014" t="n">
         <v>59957</v>
@@ -29804,7 +29804,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.7006387710571</v>
+        <v>13.7006378173828</v>
       </c>
       <c r="H1015" t="n">
         <v>89461</v>
@@ -29920,7 +29920,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1019" t="n">
-        <v>13.6821851730347</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1019" t="n">
         <v>108242</v>
@@ -30036,7 +30036,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497394561768</v>
       </c>
       <c r="H1023" t="n">
         <v>109674</v>
@@ -30065,7 +30065,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0327739715576</v>
+        <v>14.0327749252319</v>
       </c>
       <c r="H1024" t="n">
         <v>138602</v>
@@ -30123,7 +30123,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6473274230957</v>
+        <v>15.6473264694214</v>
       </c>
       <c r="H1026" t="n">
         <v>1111920</v>
@@ -30152,7 +30152,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303609848022</v>
+        <v>15.7303628921509</v>
       </c>
       <c r="H1027" t="n">
         <v>948892</v>
@@ -30268,7 +30268,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.7452239990234</v>
+        <v>16.7452220916748</v>
       </c>
       <c r="H1031" t="n">
         <v>202159</v>
@@ -30297,7 +30297,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.8190326690674</v>
+        <v>16.8190307617188</v>
       </c>
       <c r="H1032" t="n">
         <v>152525</v>
@@ -30413,7 +30413,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720344543457</v>
+        <v>15.4720335006714</v>
       </c>
       <c r="H1036" t="n">
         <v>234914</v>
@@ -30442,7 +30442,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.678596496582</v>
+        <v>14.6785955429077</v>
       </c>
       <c r="H1037" t="n">
         <v>251460</v>
@@ -30471,7 +30471,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.3187808990479</v>
+        <v>14.3187818527222</v>
       </c>
       <c r="H1038" t="n">
         <v>248886</v>
@@ -30500,7 +30500,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8446636199951</v>
+        <v>14.8446645736694</v>
       </c>
       <c r="H1039" t="n">
         <v>220373</v>
@@ -30558,7 +30558,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.2044792175293</v>
+        <v>15.204478263855</v>
       </c>
       <c r="H1041" t="n">
         <v>120054</v>
@@ -30587,7 +30587,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1042" t="n">
         <v>250873</v>
@@ -30616,7 +30616,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1043" t="n">
         <v>139842</v>
@@ -30674,7 +30674,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.1491231918335</v>
+        <v>15.1491241455078</v>
       </c>
       <c r="H1045" t="n">
         <v>133980</v>
@@ -30703,7 +30703,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506084442139</v>
+        <v>15.2506093978882</v>
       </c>
       <c r="H1046" t="n">
         <v>126441</v>
@@ -30761,7 +30761,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.1583471298218</v>
+        <v>15.1583490371704</v>
       </c>
       <c r="H1048" t="n">
         <v>75769</v>
@@ -30790,7 +30790,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.2044792175293</v>
+        <v>15.204478263855</v>
       </c>
       <c r="H1049" t="n">
         <v>166255</v>
@@ -30819,7 +30819,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.0753145217896</v>
+        <v>15.0753154754639</v>
       </c>
       <c r="H1050" t="n">
         <v>149710</v>
@@ -30877,7 +30877,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.1065835952759</v>
+        <v>14.1065826416016</v>
       </c>
       <c r="H1052" t="n">
         <v>295239</v>
@@ -30906,7 +30906,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>12.6027412414551</v>
+        <v>12.6027421951294</v>
       </c>
       <c r="H1053" t="n">
         <v>435284</v>
@@ -30935,7 +30935,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399541854858</v>
+        <v>12.0399551391602</v>
       </c>
       <c r="H1054" t="n">
         <v>314929</v>
@@ -31051,7 +31051,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.6006946563721</v>
+        <v>10.6006956100464</v>
       </c>
       <c r="H1058" t="n">
         <v>282297</v>
@@ -31109,7 +31109,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.1301679611206</v>
+        <v>10.1301689147949</v>
       </c>
       <c r="H1060" t="n">
         <v>421008</v>
@@ -31138,7 +31138,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.7980318069458</v>
+        <v>9.79803276062012</v>
       </c>
       <c r="H1061" t="n">
         <v>252887</v>
@@ -31196,7 +31196,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>8.0635404586792</v>
+        <v>8.06353950500488</v>
       </c>
       <c r="H1063" t="n">
         <v>362042</v>
@@ -31225,7 +31225,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.97589302062988</v>
+        <v>7.9758939743042</v>
       </c>
       <c r="H1064" t="n">
         <v>361762</v>
@@ -31254,7 +31254,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285898208618</v>
       </c>
       <c r="H1065" t="n">
         <v>433976</v>
@@ -31312,7 +31312,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.93796586990356</v>
+        <v>6.93796634674072</v>
       </c>
       <c r="H1067" t="n">
         <v>314093</v>
@@ -31370,7 +31370,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409652709961</v>
+        <v>6.98409605026245</v>
       </c>
       <c r="H1069" t="n">
         <v>157083</v>
@@ -31399,7 +31399,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.91028833389282</v>
+        <v>6.91028785705566</v>
       </c>
       <c r="H1070" t="n">
         <v>106846</v>
@@ -31573,7 +31573,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.01382064819336</v>
+        <v>9.01382160186768</v>
       </c>
       <c r="H1076" t="n">
         <v>132675</v>
@@ -31718,7 +31718,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.118896484375</v>
+        <v>8.11889553070068</v>
       </c>
       <c r="H1081" t="n">
         <v>72725</v>
@@ -31747,7 +31747,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.74985551834106</v>
+        <v>7.74985504150391</v>
       </c>
       <c r="H1082" t="n">
         <v>71777</v>
@@ -31776,7 +31776,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.929762840271</v>
+        <v>7.92976331710815</v>
       </c>
       <c r="H1083" t="n">
         <v>60718</v>
@@ -31805,7 +31805,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675937652588</v>
+        <v>7.78675889968872</v>
       </c>
       <c r="H1084" t="n">
         <v>156268</v>
@@ -31834,7 +31834,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.10967063903809</v>
+        <v>8.10966968536377</v>
       </c>
       <c r="H1085" t="n">
         <v>65803</v>
@@ -31863,7 +31863,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285898208618</v>
       </c>
       <c r="H1086" t="n">
         <v>212254</v>
@@ -32095,7 +32095,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.3346848487854</v>
+        <v>7.33468532562256</v>
       </c>
       <c r="H1094" t="n">
         <v>117087</v>
@@ -32153,7 +32153,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1096" t="n">
-        <v>7.5561089515686</v>
+        <v>7.55610942840576</v>
       </c>
       <c r="H1096" t="n">
         <v>241778</v>
@@ -32182,7 +32182,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G1097" t="n">
-        <v>7.77753400802612</v>
+        <v>7.77753353118896</v>
       </c>
       <c r="H1097" t="n">
         <v>226363</v>
@@ -32240,7 +32240,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.60223960876465</v>
+        <v>7.60223913192749</v>
       </c>
       <c r="H1099" t="n">
         <v>152629</v>
@@ -32269,7 +32269,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.33929824829102</v>
+        <v>7.33929777145386</v>
       </c>
       <c r="H1100" t="n">
         <v>190738</v>
@@ -32298,7 +32298,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920509338379</v>
+        <v>7.51920557022095</v>
       </c>
       <c r="H1101" t="n">
         <v>66663</v>
@@ -32327,7 +32327,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.30700635910034</v>
+        <v>7.3070068359375</v>
       </c>
       <c r="H1102" t="n">
         <v>85960</v>
@@ -32385,7 +32385,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403442382812</v>
+        <v>7.10403490066528</v>
       </c>
       <c r="H1104" t="n">
         <v>88763</v>
@@ -32414,7 +32414,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.15939044952393</v>
+        <v>7.15939092636108</v>
       </c>
       <c r="H1105" t="n">
         <v>90167</v>
@@ -32443,7 +32443,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.30700635910034</v>
+        <v>7.3070068359375</v>
       </c>
       <c r="H1106" t="n">
         <v>150317</v>
@@ -32472,7 +32472,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.06713056564331</v>
+        <v>7.06713104248047</v>
       </c>
       <c r="H1107" t="n">
         <v>140089</v>
@@ -32501,7 +32501,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874050140381</v>
+        <v>6.92874002456665</v>
       </c>
       <c r="H1108" t="n">
         <v>182143</v>
@@ -32559,7 +32559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533479690552</v>
       </c>
       <c r="H1110" t="n">
         <v>160774</v>
@@ -32588,7 +32588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533479690552</v>
       </c>
       <c r="H1111" t="n">
         <v>124418</v>
@@ -32617,7 +32617,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.54227066040039</v>
+        <v>7.54227018356323</v>
       </c>
       <c r="H1112" t="n">
         <v>115707</v>
@@ -32646,7 +32646,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.445396900177</v>
+        <v>7.44539737701416</v>
       </c>
       <c r="H1113" t="n">
         <v>89200</v>
@@ -32675,7 +32675,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010297775269</v>
+        <v>7.27010250091553</v>
       </c>
       <c r="H1114" t="n">
         <v>241372</v>
@@ -32704,7 +32704,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217798233032</v>
+        <v>7.72217750549316</v>
       </c>
       <c r="H1115" t="n">
         <v>329478</v>
@@ -32733,7 +32733,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948528289795</v>
+        <v>8.46948623657227</v>
       </c>
       <c r="H1116" t="n">
         <v>379600</v>
@@ -32791,7 +32791,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310668945312</v>
+        <v>8.90310764312744</v>
       </c>
       <c r="H1118" t="n">
         <v>292199</v>
@@ -32878,7 +32878,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.87543106079102</v>
+        <v>8.8754301071167</v>
       </c>
       <c r="H1121" t="n">
         <v>174840</v>
@@ -32994,7 +32994,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.4956188201904</v>
+        <v>11.4956197738647</v>
       </c>
       <c r="H1125" t="n">
         <v>412132</v>
@@ -33023,7 +33023,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>11.2557430267334</v>
+        <v>11.2557420730591</v>
       </c>
       <c r="H1126" t="n">
         <v>312966</v>
@@ -33052,7 +33052,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420576095581</v>
+        <v>10.9420566558838</v>
       </c>
       <c r="H1127" t="n">
         <v>171397</v>
@@ -33081,7 +33081,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.82571029663086</v>
+        <v>9.82570934295654</v>
       </c>
       <c r="H1128" t="n">
         <v>371295</v>
@@ -33110,7 +33110,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.82571029663086</v>
+        <v>9.82570934295654</v>
       </c>
       <c r="H1129" t="n">
         <v>254965</v>
@@ -33342,7 +33342,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792705535889</v>
+        <v>10.3792715072632</v>
       </c>
       <c r="H1137" t="n">
         <v>258796</v>
@@ -33400,7 +33400,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.1301679611206</v>
+        <v>10.1301689147949</v>
       </c>
       <c r="H1139" t="n">
         <v>131328</v>
@@ -33429,7 +33429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.370044708252</v>
+        <v>10.3700456619263</v>
       </c>
       <c r="H1140" t="n">
         <v>116026</v>
@@ -33516,7 +33516,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1143" t="n">
-        <v>10.6745042800903</v>
+        <v>10.674503326416</v>
       </c>
       <c r="H1143" t="n">
         <v>240355</v>
@@ -33603,7 +33603,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667636871338</v>
+        <v>10.7667646408081</v>
       </c>
       <c r="H1146" t="n">
         <v>215683</v>
@@ -33690,7 +33690,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.5417509078979</v>
+        <v>11.5417499542236</v>
       </c>
       <c r="H1149" t="n">
         <v>248313</v>
@@ -33777,7 +33777,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.8185300827026</v>
+        <v>11.818531036377</v>
       </c>
       <c r="H1152" t="n">
         <v>187197</v>
@@ -33835,7 +33835,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.8185300827026</v>
+        <v>11.818531036377</v>
       </c>
       <c r="H1154" t="n">
         <v>76721</v>
@@ -33864,7 +33864,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.7539472579956</v>
+        <v>11.7539482116699</v>
       </c>
       <c r="H1155" t="n">
         <v>263178</v>
@@ -33980,7 +33980,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.3480024337769</v>
+        <v>11.3480033874512</v>
       </c>
       <c r="H1159" t="n">
         <v>167840</v>
@@ -34154,7 +34154,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0030517578125</v>
+        <v>12.0030508041382</v>
       </c>
       <c r="H1165" t="n">
         <v>386906</v>
@@ -34241,7 +34241,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G1168" t="n">
-        <v>12.7042293548584</v>
+        <v>12.7042284011841</v>
       </c>
       <c r="H1168" t="n">
         <v>224535</v>
@@ -34270,7 +34270,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.0548162460327</v>
+        <v>13.0548152923584</v>
       </c>
       <c r="H1169" t="n">
         <v>208552</v>
@@ -34299,7 +34299,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.0548162460327</v>
+        <v>13.0548152923584</v>
       </c>
       <c r="H1170" t="n">
         <v>98947</v>
@@ -34328,7 +34328,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961801528931</v>
       </c>
       <c r="H1171" t="n">
         <v>197304</v>
@@ -34415,7 +34415,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1174" t="n">
-        <v>13.2577896118164</v>
+        <v>13.2577886581421</v>
       </c>
       <c r="H1174" t="n">
         <v>91618</v>
@@ -34502,7 +34502,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.2301111221313</v>
+        <v>13.230110168457</v>
       </c>
       <c r="H1177" t="n">
         <v>59759</v>
@@ -34560,7 +34560,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.1932067871094</v>
+        <v>13.1932077407837</v>
       </c>
       <c r="H1179" t="n">
         <v>142039</v>
@@ -34618,7 +34618,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500499725342</v>
+        <v>13.3500509262085</v>
       </c>
       <c r="H1181" t="n">
         <v>113455</v>
@@ -34647,7 +34647,7 @@
         <v>15</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H1182" t="n">
         <v>172704</v>
@@ -34676,7 +34676,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714750289917</v>
+        <v>13.5714740753174</v>
       </c>
       <c r="H1183" t="n">
         <v>86309</v>
@@ -34792,7 +34792,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.4976654052734</v>
+        <v>13.4976663589478</v>
       </c>
       <c r="H1187" t="n">
         <v>194560</v>
@@ -34821,7 +34821,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.1101732254028</v>
+        <v>13.1101722717285</v>
       </c>
       <c r="H1188" t="n">
         <v>183776</v>
@@ -34850,7 +34850,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>13.1932067871094</v>
+        <v>13.1932077407837</v>
       </c>
       <c r="H1189" t="n">
         <v>112671</v>
@@ -34908,7 +34908,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1191" t="n">
-        <v>13.1655292510986</v>
+        <v>13.1655282974243</v>
       </c>
       <c r="H1191" t="n">
         <v>114078</v>
@@ -34966,7 +34966,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1193" t="n">
-        <v>13.2301111221313</v>
+        <v>13.230110168457</v>
       </c>
       <c r="H1193" t="n">
         <v>90522</v>
@@ -35053,7 +35053,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1196" t="n">
-        <v>13.0455894470215</v>
+        <v>13.0455904006958</v>
       </c>
       <c r="H1196" t="n">
         <v>83647</v>
@@ -35082,7 +35082,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.1747550964355</v>
+        <v>13.1747541427612</v>
       </c>
       <c r="H1197" t="n">
         <v>81797</v>
@@ -35111,7 +35111,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.3315963745117</v>
+        <v>13.331597328186</v>
       </c>
       <c r="H1198" t="n">
         <v>81183</v>
@@ -35198,7 +35198,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.3813171386719</v>
+        <v>12.3813161849976</v>
       </c>
       <c r="H1201" t="n">
         <v>204999</v>
@@ -35227,7 +35227,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6304187774658</v>
+        <v>12.6304197311401</v>
       </c>
       <c r="H1202" t="n">
         <v>101665</v>
@@ -35430,7 +35430,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330835342407</v>
+        <v>13.4330825805664</v>
       </c>
       <c r="H1209" t="n">
         <v>134522</v>
@@ -35459,7 +35459,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.4515342712402</v>
+        <v>13.4515352249146</v>
       </c>
       <c r="H1210" t="n">
         <v>167243</v>
@@ -35517,7 +35517,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>15.2690591812134</v>
+        <v>15.2690601348877</v>
       </c>
       <c r="H1212" t="n">
         <v>617005</v>
@@ -35546,7 +35546,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735177993774</v>
       </c>
       <c r="H1213" t="n">
         <v>405514</v>
@@ -35662,7 +35662,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628086090088</v>
+        <v>15.4628076553345</v>
       </c>
       <c r="H1217" t="n">
         <v>170488</v>
@@ -35691,7 +35691,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>14.6232404708862</v>
+        <v>14.6232395172119</v>
       </c>
       <c r="H1218" t="n">
         <v>281974</v>
@@ -35807,7 +35807,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>14.5955610275269</v>
+        <v>14.5955619812012</v>
       </c>
       <c r="H1222" t="n">
         <v>167540</v>
@@ -36010,7 +36010,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>13.6545085906982</v>
+        <v>13.6545076370239</v>
       </c>
       <c r="H1229" t="n">
         <v>211009</v>
@@ -36039,7 +36039,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1230" t="n">
         <v>232002</v>
@@ -36126,7 +36126,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735177993774</v>
       </c>
       <c r="H1233" t="n">
         <v>375133</v>
@@ -36213,7 +36213,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.4166774749756</v>
+        <v>15.4166765213013</v>
       </c>
       <c r="H1236" t="n">
         <v>175438</v>
@@ -36242,7 +36242,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G1237" t="n">
-        <v>15.1029939651489</v>
+        <v>15.1029930114746</v>
       </c>
       <c r="H1237" t="n">
         <v>167525</v>
@@ -36271,7 +36271,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184732437134</v>
+        <v>14.9184722900391</v>
       </c>
       <c r="H1238" t="n">
         <v>69332</v>
@@ -36329,7 +36329,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764940261841</v>
+        <v>15.7764930725098</v>
       </c>
       <c r="H1240" t="n">
         <v>178894</v>
@@ -36358,7 +36358,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827445983887</v>
+        <v>15.5827465057373</v>
       </c>
       <c r="H1241" t="n">
         <v>78857</v>
@@ -36416,7 +36416,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.8133945465088</v>
+        <v>15.8133964538574</v>
       </c>
       <c r="H1243" t="n">
         <v>116062</v>
@@ -36445,7 +36445,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410739898682</v>
+        <v>15.8410758972168</v>
       </c>
       <c r="H1244" t="n">
         <v>51279</v>
@@ -36648,7 +36648,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>15.6381034851074</v>
+        <v>15.6381015777588</v>
       </c>
       <c r="H1251" t="n">
         <v>64739</v>
@@ -36677,7 +36677,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351301193237</v>
+        <v>15.4351282119751</v>
       </c>
       <c r="H1252" t="n">
         <v>60423</v>
@@ -36706,7 +36706,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919704437256</v>
+        <v>15.5919713973999</v>
       </c>
       <c r="H1253" t="n">
         <v>50800</v>
@@ -36735,7 +36735,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>15.8133945465088</v>
+        <v>15.8133964538574</v>
       </c>
       <c r="H1254" t="n">
         <v>89575</v>
@@ -36764,7 +36764,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>15.6381034851074</v>
+        <v>15.6381015777588</v>
       </c>
       <c r="H1255" t="n">
         <v>69044</v>
@@ -36793,7 +36793,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517860412598</v>
+        <v>15.9517879486084</v>
       </c>
       <c r="H1256" t="n">
         <v>77596</v>
@@ -36822,7 +36822,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.099401473999</v>
+        <v>16.0994033813477</v>
       </c>
       <c r="H1257" t="n">
         <v>135906</v>
@@ -36880,7 +36880,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>16.0717239379883</v>
+        <v>16.0717258453369</v>
       </c>
       <c r="H1259" t="n">
         <v>62766</v>
@@ -36967,7 +36967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.3910465240479</v>
+        <v>17.3910446166992</v>
       </c>
       <c r="H1262" t="n">
         <v>199105</v>
@@ -37054,7 +37054,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>17.1142635345459</v>
+        <v>17.1142654418945</v>
       </c>
       <c r="H1265" t="n">
         <v>144721</v>
@@ -37141,7 +37141,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.4464015960693</v>
+        <v>17.446403503418</v>
       </c>
       <c r="H1268" t="n">
         <v>107802</v>
@@ -37170,7 +37170,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1269" t="n">
-        <v>17.5663394927979</v>
+        <v>17.5663414001465</v>
       </c>
       <c r="H1269" t="n">
         <v>89128</v>
@@ -37228,7 +37228,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.621696472168</v>
+        <v>17.6216945648193</v>
       </c>
       <c r="H1271" t="n">
         <v>125434</v>
@@ -37257,7 +37257,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.547887802124</v>
+        <v>17.5478858947754</v>
       </c>
       <c r="H1272" t="n">
         <v>81241</v>
@@ -37315,7 +37315,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.4151306152344</v>
+        <v>18.415132522583</v>
       </c>
       <c r="H1274" t="n">
         <v>123597</v>
@@ -37344,7 +37344,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.7657203674316</v>
+        <v>18.7657222747803</v>
       </c>
       <c r="H1275" t="n">
         <v>142765</v>
@@ -37402,7 +37402,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1277" t="n">
         <v>153145</v>
@@ -37489,7 +37489,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>18.7288150787354</v>
+        <v>18.728816986084</v>
       </c>
       <c r="H1280" t="n">
         <v>138251</v>
@@ -37518,7 +37518,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="n">
-        <v>19.245475769043</v>
+        <v>19.2454738616943</v>
       </c>
       <c r="H1281" t="n">
         <v>104819</v>
@@ -37576,7 +37576,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377342224121</v>
+        <v>19.3377361297607</v>
       </c>
       <c r="H1283" t="n">
         <v>45421</v>
@@ -37605,7 +37605,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.2639255523682</v>
+        <v>19.2639274597168</v>
       </c>
       <c r="H1284" t="n">
         <v>44320</v>
@@ -37634,7 +37634,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="n">
-        <v>19.2639255523682</v>
+        <v>19.2639274597168</v>
       </c>
       <c r="H1285" t="n">
         <v>59633</v>
@@ -37721,7 +37721,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="n">
-        <v>18.2029361724854</v>
+        <v>18.2029342651367</v>
       </c>
       <c r="H1288" t="n">
         <v>161850</v>
@@ -37779,7 +37779,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="n">
-        <v>17.9722843170166</v>
+        <v>17.972282409668</v>
       </c>
       <c r="H1290" t="n">
         <v>74769</v>
@@ -37808,7 +37808,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1291" t="n">
-        <v>18.1844806671143</v>
+        <v>18.1844825744629</v>
       </c>
       <c r="H1291" t="n">
         <v>67860</v>
@@ -37895,7 +37895,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.6109256744385</v>
+        <v>20.6109237670898</v>
       </c>
       <c r="H1294" t="n">
         <v>103797</v>
@@ -37953,7 +37953,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="n">
-        <v>21.2567481994629</v>
+        <v>21.2567462921143</v>
       </c>
       <c r="H1296" t="n">
         <v>150867</v>
@@ -37982,7 +37982,7 @@
         <v>23</v>
       </c>
       <c r="G1297" t="n">
-        <v>21.2198448181152</v>
+        <v>21.2198429107666</v>
       </c>
       <c r="H1297" t="n">
         <v>87493</v>
@@ -38011,7 +38011,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>21.3121032714844</v>
+        <v>21.312105178833</v>
       </c>
       <c r="H1298" t="n">
         <v>54089</v>
@@ -38069,7 +38069,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.2567481994629</v>
+        <v>21.2567462921143</v>
       </c>
       <c r="H1300" t="n">
         <v>61853</v>
@@ -38127,7 +38127,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>22.7698154449463</v>
+        <v>22.7698173522949</v>
       </c>
       <c r="H1302" t="n">
         <v>125679</v>
@@ -38214,7 +38214,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745826721191</v>
+        <v>22.4745845794678</v>
       </c>
       <c r="H1305" t="n">
         <v>45171</v>
@@ -38301,7 +38301,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.6293754577637</v>
+        <v>20.6293773651123</v>
       </c>
       <c r="H1308" t="n">
         <v>73684</v>
@@ -38359,7 +38359,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.1865291595459</v>
+        <v>20.1865272521973</v>
       </c>
       <c r="H1310" t="n">
         <v>87245</v>
@@ -38446,7 +38446,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="n">
-        <v>21.2013893127441</v>
+        <v>21.2013912200928</v>
       </c>
       <c r="H1313" t="n">
         <v>97639</v>
@@ -38620,7 +38620,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.109130859375</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1319" t="n">
         <v>59299</v>
@@ -38649,7 +38649,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.109130859375</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1320" t="n">
         <v>52297</v>
@@ -38707,7 +38707,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1322" t="n">
         <v>182976</v>
@@ -38736,7 +38736,7 @@
         <v>21.6200008392334</v>
       </c>
       <c r="G1323" t="n">
-        <v>19.9466552734375</v>
+        <v>19.9466533660889</v>
       </c>
       <c r="H1323" t="n">
         <v>137347</v>
@@ -38765,7 +38765,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1324" t="n">
         <v>133244</v>
@@ -38794,7 +38794,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.112720489502</v>
+        <v>20.1127223968506</v>
       </c>
       <c r="H1325" t="n">
         <v>134502</v>
@@ -38881,7 +38881,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1328" t="n">
         <v>213744</v>
@@ -38910,7 +38910,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1329" t="n">
         <v>111615</v>
@@ -38939,7 +38939,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1330" t="n">
         <v>74044</v>
@@ -39113,7 +39113,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="n">
-        <v>22.1424446105957</v>
+        <v>22.1424465179443</v>
       </c>
       <c r="H1336" t="n">
         <v>58817</v>
@@ -39200,7 +39200,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317325592041</v>
+        <v>22.0317306518555</v>
       </c>
       <c r="H1339" t="n">
         <v>111019</v>
@@ -39374,7 +39374,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>23.046594619751</v>
+        <v>23.0465927124023</v>
       </c>
       <c r="H1345" t="n">
         <v>113640</v>
@@ -39490,7 +39490,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1349" t="n">
         <v>78530</v>
@@ -39519,7 +39519,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817031860352</v>
+        <v>23.5817012786865</v>
       </c>
       <c r="H1350" t="n">
         <v>51355</v>
@@ -39664,7 +39664,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.3454151153564</v>
+        <v>22.3454170227051</v>
       </c>
       <c r="H1355" t="n">
         <v>127437</v>
@@ -39693,7 +39693,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.4894428253174</v>
+        <v>23.4894409179688</v>
       </c>
       <c r="H1356" t="n">
         <v>126113</v>
@@ -39780,7 +39780,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662220001221</v>
+        <v>23.7662239074707</v>
       </c>
       <c r="H1359" t="n">
         <v>240302</v>
@@ -39867,7 +39867,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="n">
-        <v>23.6370601654053</v>
+        <v>23.6370620727539</v>
       </c>
       <c r="H1362" t="n">
         <v>264460</v>
@@ -39925,7 +39925,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763206481934</v>
+        <v>25.0763187408447</v>
       </c>
       <c r="H1364" t="n">
         <v>236072</v>
@@ -39983,7 +39983,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>26.4786758422852</v>
+        <v>26.4786739349365</v>
       </c>
       <c r="H1366" t="n">
         <v>262217</v>
@@ -40012,7 +40012,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1367" t="n">
         <v>280231</v>
@@ -40041,7 +40041,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>27.1614017486572</v>
+        <v>27.1613998413086</v>
       </c>
       <c r="H1368" t="n">
         <v>189145</v>
@@ -40070,7 +40070,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="n">
-        <v>27.3828239440918</v>
+        <v>27.3828220367432</v>
       </c>
       <c r="H1369" t="n">
         <v>120408</v>
@@ -40215,7 +40215,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721118927002</v>
+        <v>27.2721099853516</v>
       </c>
       <c r="H1374" t="n">
         <v>176103</v>
@@ -40273,7 +40273,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>27.3828239440918</v>
+        <v>27.3828220367432</v>
       </c>
       <c r="H1376" t="n">
         <v>44639</v>
@@ -40302,7 +40302,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>27.4012775421143</v>
+        <v>27.4012756347656</v>
       </c>
       <c r="H1377" t="n">
         <v>73760</v>
@@ -40331,7 +40331,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="n">
-        <v>27.1060428619385</v>
+        <v>27.1060447692871</v>
       </c>
       <c r="H1378" t="n">
         <v>74735</v>
@@ -40360,7 +40360,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="n">
-        <v>26.9030685424805</v>
+        <v>26.9030704498291</v>
       </c>
       <c r="H1379" t="n">
         <v>72804</v>
@@ -40418,7 +40418,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>25.9251117706299</v>
+        <v>25.9251098632812</v>
       </c>
       <c r="H1381" t="n">
         <v>64116</v>
@@ -40447,7 +40447,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="n">
-        <v>25.7221393585205</v>
+        <v>25.7221412658691</v>
       </c>
       <c r="H1382" t="n">
         <v>121764</v>
@@ -40534,7 +40534,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="n">
-        <v>26.4602222442627</v>
+        <v>26.4602203369141</v>
       </c>
       <c r="H1385" t="n">
         <v>51146</v>
@@ -40563,7 +40563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>26.3864135742188</v>
+        <v>26.3864154815674</v>
       </c>
       <c r="H1386" t="n">
         <v>54044</v>
@@ -40592,7 +40592,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="n">
-        <v>25.9989223480225</v>
+        <v>25.9989204406738</v>
       </c>
       <c r="H1387" t="n">
         <v>84386</v>
@@ -40621,7 +40621,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>25.5007133483887</v>
+        <v>25.5007152557373</v>
       </c>
       <c r="H1388" t="n">
         <v>89097</v>
@@ -40708,7 +40708,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="n">
-        <v>25.7221393585205</v>
+        <v>25.7221412658691</v>
       </c>
       <c r="H1391" t="n">
         <v>36786</v>
@@ -40824,7 +40824,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>26.6631927490234</v>
+        <v>26.6631946563721</v>
       </c>
       <c r="H1395" t="n">
         <v>88982</v>
@@ -40853,7 +40853,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>25.9989223480225</v>
+        <v>25.9989204406738</v>
       </c>
       <c r="H1396" t="n">
         <v>59600</v>
@@ -40882,7 +40882,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="n">
-        <v>26.3310585021973</v>
+        <v>26.3310565948486</v>
       </c>
       <c r="H1397" t="n">
         <v>52161</v>
@@ -40911,7 +40911,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="n">
-        <v>26.4602222442627</v>
+        <v>26.4602203369141</v>
       </c>
       <c r="H1398" t="n">
         <v>26653</v>
@@ -40940,7 +40940,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1399" t="n">
-        <v>26.5155792236328</v>
+        <v>26.5155773162842</v>
       </c>
       <c r="H1399" t="n">
         <v>89298</v>
@@ -40969,7 +40969,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="n">
-        <v>25.9251117706299</v>
+        <v>25.9251098632812</v>
       </c>
       <c r="H1400" t="n">
         <v>40818</v>
@@ -41027,7 +41027,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G1402" t="n">
-        <v>25.4453620910645</v>
+        <v>25.4453601837158</v>
       </c>
       <c r="H1402" t="n">
         <v>72975</v>
@@ -41288,7 +41288,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1411" t="n">
-        <v>26.5155792236328</v>
+        <v>26.5155773162842</v>
       </c>
       <c r="H1411" t="n">
         <v>78798</v>
@@ -41375,7 +41375,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750843048096</v>
+        <v>27.4750862121582</v>
       </c>
       <c r="H1414" t="n">
         <v>54200</v>
@@ -41491,7 +41491,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="n">
-        <v>29.5970706939697</v>
+        <v>29.5970687866211</v>
       </c>
       <c r="H1418" t="n">
         <v>191826</v>
@@ -41636,7 +41636,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923583984375</v>
+        <v>26.7923603057861</v>
       </c>
       <c r="H1423" t="n">
         <v>119595</v>
@@ -41723,7 +41723,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994808197021</v>
+        <v>27.8994789123535</v>
       </c>
       <c r="H1426" t="n">
         <v>102901</v>
@@ -41752,7 +41752,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G1427" t="n">
-        <v>27.5857944488525</v>
+        <v>27.5857963562012</v>
       </c>
       <c r="H1427" t="n">
         <v>51172</v>
@@ -41781,7 +41781,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="n">
-        <v>27.2352066040039</v>
+        <v>27.2352085113525</v>
       </c>
       <c r="H1428" t="n">
         <v>56869</v>
@@ -41810,7 +41810,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1429" t="n">
         <v>76852</v>
@@ -41839,7 +41839,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167549133301</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1430" t="n">
         <v>75930</v>
@@ -41868,7 +41868,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G1431" t="n">
-        <v>27.3643703460693</v>
+        <v>27.364372253418</v>
       </c>
       <c r="H1431" t="n">
         <v>81630</v>
@@ -41897,7 +41897,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.976879119873</v>
+        <v>26.9768772125244</v>
       </c>
       <c r="H1432" t="n">
         <v>58614</v>
@@ -41926,7 +41926,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="n">
-        <v>26.6262893676758</v>
+        <v>26.6262912750244</v>
       </c>
       <c r="H1433" t="n">
         <v>47937</v>
@@ -41955,7 +41955,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167549133301</v>
+        <v>27.2167568206787</v>
       </c>
       <c r="H1434" t="n">
         <v>37007</v>
@@ -41984,7 +41984,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="n">
-        <v>27.2536582946777</v>
+        <v>27.2536602020264</v>
       </c>
       <c r="H1435" t="n">
         <v>71855</v>
@@ -42042,7 +42042,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>27.3090171813965</v>
+        <v>27.3090152740479</v>
       </c>
       <c r="H1437" t="n">
         <v>40719</v>
@@ -42332,7 +42332,7 @@
         <v>30.0799999237061</v>
       </c>
       <c r="G1447" t="n">
-        <v>27.7518634796143</v>
+        <v>27.7518653869629</v>
       </c>
       <c r="H1447" t="n">
         <v>106881</v>
@@ -42390,7 +42390,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732894897461</v>
+        <v>27.9732875823975</v>
       </c>
       <c r="H1449" t="n">
         <v>79612</v>
@@ -42448,7 +42448,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1451" t="n">
-        <v>28.2869720458984</v>
+        <v>28.2869739532471</v>
       </c>
       <c r="H1451" t="n">
         <v>74987</v>
@@ -42477,7 +42477,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="n">
-        <v>28.0840015411377</v>
+        <v>28.0840034484863</v>
       </c>
       <c r="H1452" t="n">
         <v>49417</v>
@@ -42622,7 +42622,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.9953308105469</v>
+        <v>26.9953327178955</v>
       </c>
       <c r="H1457" t="n">
         <v>157384</v>
@@ -42651,7 +42651,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>26.2203464508057</v>
+        <v>26.220344543457</v>
       </c>
       <c r="H1458" t="n">
         <v>92706</v>
@@ -42680,7 +42680,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191669464111</v>
+        <v>25.5191688537598</v>
       </c>
       <c r="H1459" t="n">
         <v>176751</v>
@@ -42709,7 +42709,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1460" t="n">
-        <v>24.6150188446045</v>
+        <v>24.6150169372559</v>
       </c>
       <c r="H1460" t="n">
         <v>154714</v>
@@ -42883,7 +42883,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="n">
-        <v>23.3418273925781</v>
+        <v>23.3418254852295</v>
       </c>
       <c r="H1466" t="n">
         <v>110737</v>
@@ -42941,7 +42941,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971843719482</v>
+        <v>23.3971862792969</v>
       </c>
       <c r="H1468" t="n">
         <v>76657</v>
@@ -42999,7 +42999,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="n">
-        <v>24.0614547729492</v>
+        <v>24.0614566802979</v>
       </c>
       <c r="H1470" t="n">
         <v>127573</v>
@@ -43057,7 +43057,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="n">
-        <v>24.7441825866699</v>
+        <v>24.7441806793213</v>
       </c>
       <c r="H1472" t="n">
         <v>100651</v>
@@ -43115,7 +43115,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.2423877716064</v>
+        <v>25.2423896789551</v>
       </c>
       <c r="H1474" t="n">
         <v>98494</v>
@@ -43231,7 +43231,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763206481934</v>
+        <v>25.0763187408447</v>
       </c>
       <c r="H1478" t="n">
         <v>36215</v>
@@ -43260,7 +43260,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179931640625</v>
+        <v>24.8179912567139</v>
       </c>
       <c r="H1479" t="n">
         <v>40510</v>
@@ -43347,7 +43347,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179931640625</v>
+        <v>24.8179912567139</v>
       </c>
       <c r="H1482" t="n">
         <v>79431</v>
@@ -43521,7 +43521,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.9287014007568</v>
+        <v>24.9287033081055</v>
       </c>
       <c r="H1488" t="n">
         <v>107665</v>
@@ -43550,7 +43550,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.8364429473877</v>
+        <v>24.8364410400391</v>
       </c>
       <c r="H1489" t="n">
         <v>76383</v>
@@ -43753,7 +43753,7 @@
         <v>25.5</v>
       </c>
       <c r="G1496" t="n">
-        <v>23.526346206665</v>
+        <v>23.5263481140137</v>
       </c>
       <c r="H1496" t="n">
         <v>49797</v>
@@ -43811,7 +43811,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="n">
-        <v>22.7698154449463</v>
+        <v>22.7698173522949</v>
       </c>
       <c r="H1498" t="n">
         <v>145644</v>
@@ -43898,7 +43898,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287601470947</v>
+        <v>21.8287620544434</v>
       </c>
       <c r="H1501" t="n">
         <v>112882</v>
@@ -43927,7 +43927,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841152191162</v>
+        <v>21.8841133117676</v>
       </c>
       <c r="H1502" t="n">
         <v>111017</v>
@@ -44043,7 +44043,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.736499786377</v>
+        <v>21.7364978790283</v>
       </c>
       <c r="H1506" t="n">
         <v>138194</v>
@@ -44130,7 +44130,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1509" t="n">
         <v>177120</v>
@@ -44159,7 +44159,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="n">
-        <v>22.6590995788574</v>
+        <v>22.6591014862061</v>
       </c>
       <c r="H1510" t="n">
         <v>92110</v>
@@ -44188,7 +44188,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287601470947</v>
+        <v>21.8287620544434</v>
       </c>
       <c r="H1511" t="n">
         <v>119930</v>
@@ -44246,7 +44246,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.109130859375</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1513" t="n">
         <v>30601</v>
@@ -44333,7 +44333,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311721801758</v>
       </c>
       <c r="H1516" t="n">
         <v>83075</v>
@@ -44391,7 +44391,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1518" t="n">
         <v>87616</v>
@@ -44478,7 +44478,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.9948291778564</v>
+        <v>21.9948272705078</v>
       </c>
       <c r="H1521" t="n">
         <v>112637</v>
@@ -44536,7 +44536,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.5299377441406</v>
+        <v>22.529935836792</v>
       </c>
       <c r="H1523" t="n">
         <v>282491</v>
@@ -44565,7 +44565,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>22.5114860534668</v>
+        <v>22.5114841461182</v>
       </c>
       <c r="H1524" t="n">
         <v>72450</v>
@@ -44623,7 +44623,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.5299377441406</v>
+        <v>22.529935836792</v>
       </c>
       <c r="H1526" t="n">
         <v>35005</v>
@@ -44652,7 +44652,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="n">
-        <v>23.1204032897949</v>
+        <v>23.1204013824463</v>
       </c>
       <c r="H1527" t="n">
         <v>87054</v>
@@ -44739,7 +44739,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>22.3085155487061</v>
+        <v>22.3085136413574</v>
       </c>
       <c r="H1530" t="n">
         <v>64510</v>
@@ -44768,7 +44768,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>22.5114860534668</v>
+        <v>22.5114841461182</v>
       </c>
       <c r="H1531" t="n">
         <v>40554</v>
@@ -44826,7 +44826,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674602508545</v>
+        <v>21.3674583435059</v>
       </c>
       <c r="H1533" t="n">
         <v>40625</v>
@@ -45000,7 +45000,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335273742676</v>
+        <v>21.5335292816162</v>
       </c>
       <c r="H1539" t="n">
         <v>67442</v>
@@ -45087,7 +45087,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.9281997680664</v>
+        <v>19.928201675415</v>
       </c>
       <c r="H1542" t="n">
         <v>354066</v>
@@ -45145,7 +45145,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1544" t="n">
         <v>73711</v>
@@ -45174,7 +45174,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877086639404</v>
+        <v>20.8877067565918</v>
       </c>
       <c r="H1545" t="n">
         <v>65560</v>
@@ -45261,7 +45261,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.3121032714844</v>
+        <v>21.312105178833</v>
       </c>
       <c r="H1548" t="n">
         <v>71843</v>
@@ -45290,7 +45290,7 @@
         <v>23</v>
       </c>
       <c r="G1549" t="n">
-        <v>21.2198448181152</v>
+        <v>21.2198429107666</v>
       </c>
       <c r="H1549" t="n">
         <v>44418</v>
@@ -45435,7 +45435,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="n">
-        <v>20.8138980865479</v>
+        <v>20.8138961791992</v>
       </c>
       <c r="H1554" t="n">
         <v>258855</v>
@@ -45522,7 +45522,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1557" t="n">
         <v>232143</v>
@@ -45580,7 +45580,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.7585411071777</v>
+        <v>20.7585430145264</v>
       </c>
       <c r="H1559" t="n">
         <v>34621</v>
@@ -45609,7 +45609,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="n">
-        <v>20.3710479736328</v>
+        <v>20.3710498809814</v>
       </c>
       <c r="H1560" t="n">
         <v>107999</v>
@@ -45638,7 +45638,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="n">
-        <v>20.0204620361328</v>
+        <v>20.0204601287842</v>
       </c>
       <c r="H1561" t="n">
         <v>57646</v>
@@ -45725,7 +45725,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.5073928833008</v>
+        <v>18.5073947906494</v>
       </c>
       <c r="H1564" t="n">
         <v>48417</v>
@@ -45783,7 +45783,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.1291255950928</v>
+        <v>18.1291236877441</v>
       </c>
       <c r="H1566" t="n">
         <v>145527</v>
@@ -45870,7 +45870,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633651733398</v>
+        <v>17.3633670806885</v>
       </c>
       <c r="H1569" t="n">
         <v>50964</v>
@@ -45928,7 +45928,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1571" t="n">
         <v>197519</v>
@@ -45957,7 +45957,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.0845413208008</v>
+        <v>15.0845403671265</v>
       </c>
       <c r="H1572" t="n">
         <v>244822</v>
@@ -46044,7 +46044,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.1583471298218</v>
+        <v>15.1583490371704</v>
       </c>
       <c r="H1575" t="n">
         <v>113410</v>
@@ -46073,7 +46073,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.3705472946167</v>
+        <v>15.370548248291</v>
       </c>
       <c r="H1576" t="n">
         <v>128639</v>
@@ -46102,7 +46102,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.23779296875</v>
+        <v>16.2377910614014</v>
       </c>
       <c r="H1577" t="n">
         <v>111126</v>
@@ -46160,7 +46160,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.2172946929932</v>
+        <v>14.2172937393188</v>
       </c>
       <c r="H1579" t="n">
         <v>614742</v>
@@ -46189,7 +46189,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.0604515075684</v>
+        <v>14.0604524612427</v>
       </c>
       <c r="H1580" t="n">
         <v>242362</v>
@@ -46247,7 +46247,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878223419189</v>
+        <v>14.6878213882446</v>
       </c>
       <c r="H1582" t="n">
         <v>163036</v>
@@ -46276,7 +46276,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1583" t="n">
-        <v>14.8169860839844</v>
+        <v>14.8169851303101</v>
       </c>
       <c r="H1583" t="n">
         <v>106388</v>
@@ -46334,7 +46334,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634248733521</v>
+        <v>14.2634258270264</v>
       </c>
       <c r="H1585" t="n">
         <v>112266</v>
@@ -46421,7 +46421,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8226203918457</v>
+        <v>15.8226222991943</v>
       </c>
       <c r="H1588" t="n">
         <v>261661</v>
@@ -46537,7 +46537,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.0753145217896</v>
+        <v>15.0753154754639</v>
       </c>
       <c r="H1592" t="n">
         <v>140875</v>
@@ -46653,7 +46653,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.0327739715576</v>
+        <v>14.0327749252319</v>
       </c>
       <c r="H1596" t="n">
         <v>72466</v>
@@ -46682,7 +46682,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0420007705688</v>
+        <v>14.0420017242432</v>
       </c>
       <c r="H1597" t="n">
         <v>49196</v>
@@ -46740,7 +46740,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1599" t="n">
-        <v>13.8205766677856</v>
+        <v>13.8205757141113</v>
       </c>
       <c r="H1599" t="n">
         <v>68975</v>
@@ -46798,7 +46798,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497394561768</v>
       </c>
       <c r="H1601" t="n">
         <v>45680</v>
@@ -46856,7 +46856,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1603" t="n">
         <v>73059</v>
@@ -46914,7 +46914,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.8667068481445</v>
+        <v>13.8667058944702</v>
       </c>
       <c r="H1605" t="n">
         <v>46964</v>
@@ -46943,7 +46943,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="n">
-        <v>13.617603302002</v>
+        <v>13.6176042556763</v>
       </c>
       <c r="H1606" t="n">
         <v>94220</v>
@@ -47059,7 +47059,7 @@
         <v>15</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8390283584595</v>
+        <v>13.8390274047852</v>
       </c>
       <c r="H1610" t="n">
         <v>78749</v>
@@ -47117,7 +47117,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.6821851730347</v>
+        <v>13.682186126709</v>
       </c>
       <c r="H1612" t="n">
         <v>65954</v>
@@ -47291,7 +47291,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961801528931</v>
       </c>
       <c r="H1618" t="n">
         <v>99070</v>
@@ -47349,7 +47349,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476360321045</v>
+        <v>15.0476369857788</v>
       </c>
       <c r="H1620" t="n">
         <v>154501</v>
@@ -47465,7 +47465,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384101867676</v>
+        <v>15.0384111404419</v>
       </c>
       <c r="H1624" t="n">
         <v>74404</v>
@@ -47523,7 +47523,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>14.7736358642578</v>
+        <v>14.7736368179321</v>
       </c>
       <c r="H1626" t="n">
         <v>61617</v>
@@ -47697,7 +47697,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.7137765884399</v>
+        <v>15.7137775421143</v>
       </c>
       <c r="H1632" t="n">
         <v>66096</v>
@@ -47755,7 +47755,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.7809314727783</v>
+        <v>15.780930519104</v>
       </c>
       <c r="H1634" t="n">
         <v>37135</v>
@@ -47784,7 +47784,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.0303554534912</v>
+        <v>16.0303535461426</v>
       </c>
       <c r="H1635" t="n">
         <v>43698</v>
@@ -47900,7 +47900,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="n">
-        <v>14.5529918670654</v>
+        <v>14.5529909133911</v>
       </c>
       <c r="H1639" t="n">
         <v>89694</v>
@@ -47958,7 +47958,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="n">
-        <v>13.5456972122192</v>
+        <v>13.5456981658936</v>
       </c>
       <c r="H1641" t="n">
         <v>86532</v>
@@ -47987,7 +47987,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>13.8430891036987</v>
+        <v>13.843090057373</v>
       </c>
       <c r="H1642" t="n">
         <v>116898</v>
@@ -48045,7 +48045,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.1427793502808</v>
+        <v>13.1427803039551</v>
       </c>
       <c r="H1644" t="n">
         <v>169292</v>
@@ -48161,7 +48161,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="n">
-        <v>12.4040985107422</v>
+        <v>12.4040994644165</v>
       </c>
       <c r="H1648" t="n">
         <v>78173</v>
@@ -48277,7 +48277,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="n">
-        <v>12.5959634780884</v>
+        <v>12.5959644317627</v>
       </c>
       <c r="H1652" t="n">
         <v>94645</v>
@@ -48364,7 +48364,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.780535697937</v>
+        <v>11.7805366516113</v>
       </c>
       <c r="H1655" t="n">
         <v>68390</v>
@@ -48393,7 +48393,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="n">
-        <v>11.5502977371216</v>
+        <v>11.5502986907959</v>
       </c>
       <c r="H1656" t="n">
         <v>106176</v>
@@ -48451,7 +48451,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="n">
-        <v>12.6247444152832</v>
+        <v>12.6247434616089</v>
       </c>
       <c r="H1658" t="n">
         <v>79138</v>
@@ -48480,7 +48480,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>13.0468482971191</v>
+        <v>13.0468473434448</v>
       </c>
       <c r="H1659" t="n">
         <v>65276</v>
@@ -48741,7 +48741,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="n">
-        <v>13.0468482971191</v>
+        <v>13.0468473434448</v>
       </c>
       <c r="H1668" t="n">
         <v>63442</v>
@@ -48770,7 +48770,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>13.1044073104858</v>
+        <v>13.1044082641602</v>
       </c>
       <c r="H1669" t="n">
         <v>22290</v>
@@ -49002,7 +49002,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.3154592514038</v>
+        <v>13.3154602050781</v>
       </c>
       <c r="H1677" t="n">
         <v>61589</v>
@@ -49031,7 +49031,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.1044073104858</v>
+        <v>13.1044082641602</v>
       </c>
       <c r="H1678" t="n">
         <v>78688</v>
@@ -49089,7 +49089,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.6055583953857</v>
+        <v>12.6055574417114</v>
       </c>
       <c r="H1680" t="n">
         <v>65707</v>
@@ -49205,7 +49205,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="n">
-        <v>12.6247444152832</v>
+        <v>12.6247434616089</v>
       </c>
       <c r="H1684" t="n">
         <v>34970</v>
@@ -49321,7 +49321,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="n">
-        <v>12.2506065368652</v>
+        <v>12.2506055831909</v>
       </c>
       <c r="H1688" t="n">
         <v>46659</v>
@@ -49350,7 +49350,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>11.780535697937</v>
+        <v>11.7805366516113</v>
       </c>
       <c r="H1689" t="n">
         <v>75821</v>
@@ -49466,7 +49466,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="n">
-        <v>12.2218255996704</v>
+        <v>12.2218265533447</v>
       </c>
       <c r="H1693" t="n">
         <v>114156</v>
@@ -49553,7 +49553,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1696" t="n">
         <v>51664</v>
@@ -49727,7 +49727,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="n">
-        <v>11.3296518325806</v>
+        <v>11.3296527862549</v>
       </c>
       <c r="H1702" t="n">
         <v>48994</v>
@@ -49756,7 +49756,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1703" t="n">
         <v>48478</v>
@@ -49785,7 +49785,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>12.1354866027832</v>
+        <v>12.1354856491089</v>
       </c>
       <c r="H1704" t="n">
         <v>69346</v>
@@ -50017,7 +50017,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="n">
-        <v>11.2720937728882</v>
+        <v>11.2720928192139</v>
       </c>
       <c r="H1712" t="n">
         <v>57229</v>
@@ -50162,7 +50162,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.7540559768677</v>
+        <v>10.754056930542</v>
       </c>
       <c r="H1717" t="n">
         <v>47037</v>
@@ -50220,7 +50220,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="n">
-        <v>11.1090068817139</v>
+        <v>11.1090059280396</v>
       </c>
       <c r="H1719" t="n">
         <v>38067</v>
@@ -50249,7 +50249,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1720" t="n">
         <v>60827</v>
@@ -50278,7 +50278,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>11.4159917831421</v>
+        <v>11.4159908294678</v>
       </c>
       <c r="H1721" t="n">
         <v>31311</v>
@@ -50336,7 +50336,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.5694847106934</v>
+        <v>11.5694856643677</v>
       </c>
       <c r="H1723" t="n">
         <v>30512</v>
@@ -50365,7 +50365,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>11.5790777206421</v>
+        <v>11.5790767669678</v>
       </c>
       <c r="H1724" t="n">
         <v>33530</v>
@@ -50423,7 +50423,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.2720937728882</v>
+        <v>11.2720928192139</v>
       </c>
       <c r="H1726" t="n">
         <v>45721</v>
@@ -50481,7 +50481,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.6654167175293</v>
+        <v>11.6654176712036</v>
       </c>
       <c r="H1728" t="n">
         <v>31281</v>
@@ -50510,7 +50510,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.8764696121216</v>
+        <v>11.8764686584473</v>
       </c>
       <c r="H1729" t="n">
         <v>26291</v>
@@ -50771,7 +50771,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="n">
-        <v>13.2003402709961</v>
+        <v>13.2003412246704</v>
       </c>
       <c r="H1738" t="n">
         <v>77128</v>
@@ -50800,7 +50800,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="n">
-        <v>11.6941967010498</v>
+        <v>11.6941957473755</v>
       </c>
       <c r="H1739" t="n">
         <v>447229</v>
@@ -50945,7 +50945,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.5790777206421</v>
+        <v>11.5790767669678</v>
       </c>
       <c r="H1744" t="n">
         <v>105065</v>
@@ -51061,7 +51061,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.7398633956909</v>
+        <v>12.7398624420166</v>
       </c>
       <c r="H1748" t="n">
         <v>160134</v>
@@ -51119,7 +51119,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.5959634780884</v>
+        <v>12.5959644317627</v>
       </c>
       <c r="H1750" t="n">
         <v>92825</v>
@@ -51148,7 +51148,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.2889795303345</v>
+        <v>12.2889804840088</v>
       </c>
       <c r="H1751" t="n">
         <v>103263</v>
@@ -51235,7 +51235,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930475234985</v>
+        <v>12.1930465698242</v>
       </c>
       <c r="H1754" t="n">
         <v>93258</v>
@@ -51264,7 +51264,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.2506065368652</v>
+        <v>12.2506055831909</v>
       </c>
       <c r="H1755" t="n">
         <v>28199</v>
@@ -51409,7 +51409,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H1760" t="n">
         <v>57784</v>
@@ -51496,7 +51496,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="n">
-        <v>12.7398633956909</v>
+        <v>12.7398624420166</v>
       </c>
       <c r="H1763" t="n">
         <v>76238</v>
@@ -51786,7 +51786,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.1834535598755</v>
+        <v>12.1834526062012</v>
       </c>
       <c r="H1773" t="n">
         <v>45619</v>
@@ -51815,7 +51815,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H1774" t="n">
         <v>28745</v>
@@ -51844,7 +51844,7 @@
         <v>12.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.991587638855</v>
+        <v>11.9915885925293</v>
       </c>
       <c r="H1775" t="n">
         <v>63441</v>
@@ -51931,7 +51931,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.0395545959473</v>
+        <v>12.0395536422729</v>
       </c>
       <c r="H1778" t="n">
         <v>24126</v>
@@ -52105,7 +52105,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.5000305175781</v>
+        <v>12.5000314712524</v>
       </c>
       <c r="H1784" t="n">
         <v>49900</v>
@@ -52308,7 +52308,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.7663440704346</v>
+        <v>13.7663431167603</v>
       </c>
       <c r="H1791" t="n">
         <v>71163</v>
@@ -52424,7 +52424,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.2364139556885</v>
+        <v>14.2364130020142</v>
       </c>
       <c r="H1795" t="n">
         <v>65651</v>
@@ -52453,7 +52453,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.7855291366577</v>
+        <v>13.7855281829834</v>
       </c>
       <c r="H1796" t="n">
         <v>52655</v>
@@ -52482,7 +52482,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.8143100738525</v>
+        <v>13.8143091201782</v>
       </c>
       <c r="H1797" t="n">
         <v>40053</v>
@@ -52511,7 +52511,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1798" t="n">
-        <v>13.8143100738525</v>
+        <v>13.8143091201782</v>
       </c>
       <c r="H1798" t="n">
         <v>44811</v>
@@ -52627,7 +52627,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1802" t="n">
-        <v>14.3707189559937</v>
+        <v>14.3707180023193</v>
       </c>
       <c r="H1802" t="n">
         <v>61789</v>
@@ -52685,7 +52685,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1804" t="n">
-        <v>14.1692600250244</v>
+        <v>14.1692609786987</v>
       </c>
       <c r="H1804" t="n">
         <v>86857</v>
@@ -52743,7 +52743,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463148117065</v>
+        <v>14.9463157653809</v>
       </c>
       <c r="H1806" t="n">
         <v>121708</v>
@@ -52772,7 +52772,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="n">
-        <v>14.7736358642578</v>
+        <v>14.7736368179321</v>
       </c>
       <c r="H1807" t="n">
         <v>83586</v>
@@ -52830,7 +52830,7 @@
         <v>15</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.3899059295654</v>
+        <v>14.3899049758911</v>
       </c>
       <c r="H1809" t="n">
         <v>55734</v>
@@ -53004,7 +53004,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1815" t="n">
         <v>43434</v>
@@ -53062,7 +53062,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1817" t="n">
         <v>85926</v>
@@ -53120,7 +53120,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.5721769332886</v>
+        <v>14.5721778869629</v>
       </c>
       <c r="H1819" t="n">
         <v>79210</v>
@@ -53178,7 +53178,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1821" t="n">
-        <v>16.0879154205322</v>
+        <v>16.0879135131836</v>
       </c>
       <c r="H1821" t="n">
         <v>460810</v>
@@ -53207,7 +53207,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.8288955688477</v>
+        <v>15.8288974761963</v>
       </c>
       <c r="H1822" t="n">
         <v>177332</v>
@@ -53236,7 +53236,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1823" t="n">
-        <v>16.2509994506836</v>
+        <v>16.2510013580322</v>
       </c>
       <c r="H1823" t="n">
         <v>168955</v>
@@ -53294,7 +53294,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1825" t="n">
-        <v>16.7210693359375</v>
+        <v>16.7210712432861</v>
       </c>
       <c r="H1825" t="n">
         <v>176367</v>
@@ -53381,7 +53381,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1828" t="n">
-        <v>16.2030334472656</v>
+        <v>16.2030353546143</v>
       </c>
       <c r="H1828" t="n">
         <v>59759</v>
@@ -53468,7 +53468,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1831" t="n">
-        <v>16.2030334472656</v>
+        <v>16.2030353546143</v>
       </c>
       <c r="H1831" t="n">
         <v>39708</v>
@@ -53526,7 +53526,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.3588256835938</v>
+        <v>15.3588266372681</v>
       </c>
       <c r="H1833" t="n">
         <v>142239</v>
@@ -53555,7 +53555,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1834" t="n">
-        <v>16.0783214569092</v>
+        <v>16.0783195495605</v>
       </c>
       <c r="H1834" t="n">
         <v>161635</v>
@@ -53729,7 +53729,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1840" t="n">
-        <v>14.6393308639526</v>
+        <v>14.639331817627</v>
       </c>
       <c r="H1840" t="n">
         <v>102978</v>
@@ -53758,7 +53758,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="n">
-        <v>14.5529918670654</v>
+        <v>14.5529909133911</v>
       </c>
       <c r="H1841" t="n">
         <v>102046</v>
@@ -53787,7 +53787,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.1308870315552</v>
+        <v>14.1308879852295</v>
       </c>
       <c r="H1842" t="n">
         <v>109542</v>
@@ -53845,7 +53845,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1844" t="n">
-        <v>13.948616027832</v>
+        <v>13.9486150741577</v>
       </c>
       <c r="H1844" t="n">
         <v>54799</v>
@@ -54019,7 +54019,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="n">
-        <v>13.5456972122192</v>
+        <v>13.5456981658936</v>
       </c>
       <c r="H1850" t="n">
         <v>60451</v>
@@ -54135,7 +54135,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>13.459358215332</v>
+        <v>13.4593572616577</v>
       </c>
       <c r="H1854" t="n">
         <v>46148</v>
@@ -54222,7 +54222,7 @@
         <v>14</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4305782318115</v>
+        <v>13.4305791854858</v>
       </c>
       <c r="H1857" t="n">
         <v>134657</v>
@@ -54396,7 +54396,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1863" t="n">
-        <v>12.9701023101807</v>
+        <v>12.9701013565063</v>
       </c>
       <c r="H1863" t="n">
         <v>106326</v>
@@ -54454,7 +54454,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2578983306885</v>
+        <v>13.2578992843628</v>
       </c>
       <c r="H1865" t="n">
         <v>39502</v>
@@ -54512,7 +54512,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1867" t="n">
-        <v>13.0276613235474</v>
+        <v>13.027660369873</v>
       </c>
       <c r="H1867" t="n">
         <v>39070</v>
@@ -80064,9 +80064,38 @@
         <v>4.04500007629395</v>
       </c>
       <c r="H2748" t="n">
-        <v>193765</v>
+        <v>194174</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>4.03499984741211</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>4.09000015258789</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>3.95000004768372</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>116915</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -514,7 +514,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G5" t="n">
-        <v>12.747950553894</v>
+        <v>12.7479515075684</v>
       </c>
       <c r="H5" t="n">
         <v>96757</v>
@@ -543,7 +543,7 @@
         <v>14.5</v>
       </c>
       <c r="G6" t="n">
-        <v>12.397403717041</v>
+        <v>12.3974046707153</v>
       </c>
       <c r="H6" t="n">
         <v>125048</v>
@@ -601,7 +601,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>12.2606067657471</v>
+        <v>12.2606058120728</v>
       </c>
       <c r="H8" t="n">
         <v>54531</v>
@@ -630,7 +630,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>12.1409072875977</v>
+        <v>12.140905380249</v>
       </c>
       <c r="H9" t="n">
         <v>34417</v>
@@ -659,7 +659,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4825611114502</v>
+        <v>11.4825601577759</v>
       </c>
       <c r="H10" t="n">
         <v>137481</v>
@@ -804,7 +804,7 @@
         <v>12.25</v>
       </c>
       <c r="G15" t="n">
-        <v>10.4736680984497</v>
+        <v>10.473669052124</v>
       </c>
       <c r="H15" t="n">
         <v>204057</v>
@@ -978,7 +978,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6361169815063</v>
+        <v>10.6361179351807</v>
       </c>
       <c r="H21" t="n">
         <v>72208</v>
@@ -1036,7 +1036,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.191520690918</v>
+        <v>10.1915225982666</v>
       </c>
       <c r="H23" t="n">
         <v>90616</v>
@@ -1094,7 +1094,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907693862915</v>
+        <v>10.4907684326172</v>
       </c>
       <c r="H25" t="n">
         <v>150192</v>
@@ -1123,7 +1123,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0205230712891</v>
+        <v>10.0205221176147</v>
       </c>
       <c r="H26" t="n">
         <v>55946</v>
@@ -1152,7 +1152,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03728008270264</v>
+        <v>9.03728103637695</v>
       </c>
       <c r="H27" t="n">
         <v>127617</v>
@@ -1181,7 +1181,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743034362793</v>
+        <v>8.97743129730225</v>
       </c>
       <c r="H28" t="n">
         <v>172224</v>
@@ -1210,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9.40492725372314</v>
+        <v>9.40492820739746</v>
       </c>
       <c r="H29" t="n">
         <v>104278</v>
@@ -1239,7 +1239,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842891693115</v>
+        <v>9.14842987060547</v>
       </c>
       <c r="H30" t="n">
         <v>114215</v>
@@ -1268,7 +1268,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G31" t="n">
-        <v>9.43057632446289</v>
+        <v>9.43057727813721</v>
       </c>
       <c r="H31" t="n">
         <v>72178</v>
@@ -1297,7 +1297,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G32" t="n">
-        <v>9.90082263946533</v>
+        <v>9.90082359313965</v>
       </c>
       <c r="H32" t="n">
         <v>70762</v>
@@ -1326,7 +1326,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142654418945</v>
+        <v>9.66142559051514</v>
       </c>
       <c r="H33" t="n">
         <v>39366</v>
@@ -1384,7 +1384,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3454208374023</v>
+        <v>10.345419883728</v>
       </c>
       <c r="H35" t="n">
         <v>81482</v>
@@ -1413,7 +1413,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G36" t="n">
-        <v>10.2000722885132</v>
+        <v>10.2000713348389</v>
       </c>
       <c r="H36" t="n">
         <v>73300</v>
@@ -1471,7 +1471,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506191253662</v>
+        <v>10.5506172180176</v>
       </c>
       <c r="H38" t="n">
         <v>97952</v>
@@ -1500,7 +1500,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257213592529</v>
+        <v>10.2257204055786</v>
       </c>
       <c r="H39" t="n">
         <v>73018</v>
@@ -1558,7 +1558,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G41" t="n">
-        <v>11.0379638671875</v>
+        <v>11.0379648208618</v>
       </c>
       <c r="H41" t="n">
         <v>191057</v>
@@ -1587,7 +1587,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097156524658</v>
+        <v>10.9097166061401</v>
       </c>
       <c r="H42" t="n">
         <v>105720</v>
@@ -1645,7 +1645,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G44" t="n">
-        <v>11.9442577362061</v>
+        <v>11.9442586898804</v>
       </c>
       <c r="H44" t="n">
         <v>175966</v>
@@ -1674,7 +1674,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G45" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H45" t="n">
         <v>110221</v>
@@ -1703,7 +1703,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732591629028</v>
+        <v>11.7732601165771</v>
       </c>
       <c r="H46" t="n">
         <v>75412</v>
@@ -1761,7 +1761,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>11.627911567688</v>
+        <v>11.6279106140137</v>
       </c>
       <c r="H48" t="n">
         <v>125028</v>
@@ -1848,7 +1848,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.662109375</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H51" t="n">
         <v>99643</v>
@@ -1877,7 +1877,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416585922241</v>
+        <v>11.8416604995728</v>
       </c>
       <c r="H52" t="n">
         <v>101508</v>
@@ -1906,7 +1906,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.9186086654663</v>
+        <v>11.9186067581177</v>
       </c>
       <c r="H53" t="n">
         <v>56813</v>
@@ -1964,7 +1964,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>12.046856880188</v>
+        <v>12.0468587875366</v>
       </c>
       <c r="H55" t="n">
         <v>93874</v>
@@ -1993,7 +1993,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G56" t="n">
-        <v>12.1922054290771</v>
+        <v>12.1922063827515</v>
       </c>
       <c r="H56" t="n">
         <v>88317</v>
@@ -2051,7 +2051,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375558853149</v>
+        <v>12.3375549316406</v>
       </c>
       <c r="H58" t="n">
         <v>61525</v>
@@ -2080,7 +2080,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.1409072875977</v>
+        <v>12.140905380249</v>
       </c>
       <c r="H59" t="n">
         <v>40540</v>
@@ -2109,7 +2109,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>12.1323566436768</v>
+        <v>12.1323556900024</v>
       </c>
       <c r="H60" t="n">
         <v>36904</v>
@@ -2138,7 +2138,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665544509888</v>
+        <v>12.1665573120117</v>
       </c>
       <c r="H61" t="n">
         <v>40779</v>
@@ -2167,7 +2167,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H62" t="n">
         <v>55469</v>
@@ -2225,7 +2225,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>11.9015083312988</v>
+        <v>11.9015092849731</v>
       </c>
       <c r="H64" t="n">
         <v>46495</v>
@@ -2254,7 +2254,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1409072875977</v>
+        <v>12.140905380249</v>
       </c>
       <c r="H65" t="n">
         <v>58858</v>
@@ -2312,7 +2312,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5680618286133</v>
+        <v>11.5680599212646</v>
       </c>
       <c r="H67" t="n">
         <v>44037</v>
@@ -2341,7 +2341,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G68" t="n">
-        <v>11.2859125137329</v>
+        <v>11.2859134674072</v>
       </c>
       <c r="H68" t="n">
         <v>33579</v>
@@ -2399,7 +2399,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>11.8844089508057</v>
+        <v>11.8844079971313</v>
       </c>
       <c r="H70" t="n">
         <v>38060</v>
@@ -2428,7 +2428,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5680618286133</v>
+        <v>11.5680599212646</v>
       </c>
       <c r="H71" t="n">
         <v>41497</v>
@@ -2457,7 +2457,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.662109375</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H72" t="n">
         <v>25570</v>
@@ -2486,7 +2486,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160095214844</v>
+        <v>11.8160076141357</v>
       </c>
       <c r="H73" t="n">
         <v>56893</v>
@@ -2515,7 +2515,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048587799072</v>
+        <v>11.7048606872559</v>
       </c>
       <c r="H74" t="n">
         <v>28658</v>
@@ -2573,7 +2573,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.662109375</v>
+        <v>11.6621112823486</v>
       </c>
       <c r="H76" t="n">
         <v>47170</v>
@@ -2602,7 +2602,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364603042603</v>
+        <v>11.6364612579346</v>
       </c>
       <c r="H77" t="n">
         <v>21274</v>
@@ -2660,7 +2660,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1918659210205</v>
+        <v>11.1918640136719</v>
       </c>
       <c r="H79" t="n">
         <v>107247</v>
@@ -2718,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.1149158477783</v>
+        <v>11.1149139404297</v>
       </c>
       <c r="H81" t="n">
         <v>44600</v>
@@ -2776,7 +2776,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G83" t="n">
-        <v>11.3201112747192</v>
+        <v>11.3201122283936</v>
       </c>
       <c r="H83" t="n">
         <v>33223</v>
@@ -2834,7 +2834,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1576642990112</v>
+        <v>11.1576633453369</v>
       </c>
       <c r="H85" t="n">
         <v>20515</v>
@@ -2892,7 +2892,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G87" t="n">
-        <v>10.986665725708</v>
+        <v>10.9866666793823</v>
       </c>
       <c r="H87" t="n">
         <v>18020</v>
@@ -2921,7 +2921,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1405630111694</v>
+        <v>11.1405639648438</v>
       </c>
       <c r="H88" t="n">
         <v>30374</v>
@@ -2950,7 +2950,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>10.6019191741943</v>
+        <v>10.60191822052</v>
       </c>
       <c r="H89" t="n">
         <v>131898</v>
@@ -3124,7 +3124,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G95" t="n">
-        <v>10.2673053741455</v>
+        <v>10.2673063278198</v>
       </c>
       <c r="H95" t="n">
         <v>21248</v>
@@ -3153,7 +3153,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92388820648193</v>
+        <v>9.92388916015625</v>
       </c>
       <c r="H96" t="n">
         <v>101148</v>
@@ -3240,7 +3240,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3025274276733</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H99" t="n">
         <v>48962</v>
@@ -3356,7 +3356,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302528381348</v>
+        <v>11.1302537918091</v>
       </c>
       <c r="H103" t="n">
         <v>70319</v>
@@ -3385,7 +3385,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189186096191</v>
+        <v>10.9189195632935</v>
       </c>
       <c r="H104" t="n">
         <v>30153</v>
@@ -3472,7 +3472,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302528381348</v>
+        <v>11.1302537918091</v>
       </c>
       <c r="H107" t="n">
         <v>63256</v>
@@ -3501,7 +3501,7 @@
         <v>12.5</v>
       </c>
       <c r="G108" t="n">
-        <v>11.0069732666016</v>
+        <v>11.0069742202759</v>
       </c>
       <c r="H108" t="n">
         <v>22280</v>
@@ -3530,7 +3530,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>10.8308639526367</v>
+        <v>10.8308629989624</v>
       </c>
       <c r="H109" t="n">
         <v>32955</v>
@@ -3559,7 +3559,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396711349487</v>
+        <v>10.8396682739258</v>
       </c>
       <c r="H110" t="n">
         <v>35136</v>
@@ -3588,7 +3588,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G111" t="n">
-        <v>10.9277229309082</v>
+        <v>10.9277238845825</v>
       </c>
       <c r="H111" t="n">
         <v>58146</v>
@@ -3617,7 +3617,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G112" t="n">
-        <v>10.9101123809814</v>
+        <v>10.9101133346558</v>
       </c>
       <c r="H112" t="n">
         <v>37578</v>
@@ -3646,7 +3646,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G113" t="n">
-        <v>10.8132524490356</v>
+        <v>10.8132514953613</v>
       </c>
       <c r="H113" t="n">
         <v>12086</v>
@@ -3675,7 +3675,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G114" t="n">
-        <v>10.513861656189</v>
+        <v>10.5138635635376</v>
       </c>
       <c r="H114" t="n">
         <v>43277</v>
@@ -3704,7 +3704,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647773742676</v>
+        <v>10.0647764205933</v>
       </c>
       <c r="H115" t="n">
         <v>60966</v>
@@ -3762,7 +3762,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G117" t="n">
-        <v>9.95030403137207</v>
+        <v>9.95030498504639</v>
       </c>
       <c r="H117" t="n">
         <v>51985</v>
@@ -3849,7 +3849,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962511062622</v>
+        <v>10.4962520599365</v>
       </c>
       <c r="H120" t="n">
         <v>43223</v>
@@ -3878,7 +3878,7 @@
         <v>11.75</v>
       </c>
       <c r="G121" t="n">
-        <v>10.3465557098389</v>
+        <v>10.3465576171875</v>
       </c>
       <c r="H121" t="n">
         <v>50694</v>
@@ -3907,7 +3907,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522247314453</v>
+        <v>10.4522228240967</v>
       </c>
       <c r="H122" t="n">
         <v>40375</v>
@@ -3936,7 +3936,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843076705933</v>
+        <v>10.5843067169189</v>
       </c>
       <c r="H123" t="n">
         <v>36459</v>
@@ -3965,7 +3965,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G124" t="n">
-        <v>9.87985992431641</v>
+        <v>9.87986087799072</v>
       </c>
       <c r="H124" t="n">
         <v>94289</v>
@@ -3994,7 +3994,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G125" t="n">
-        <v>9.12257957458496</v>
+        <v>9.12257862091064</v>
       </c>
       <c r="H125" t="n">
         <v>55022</v>
@@ -4023,7 +4023,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G126" t="n">
-        <v>9.67733097076416</v>
+        <v>9.67733192443848</v>
       </c>
       <c r="H126" t="n">
         <v>56824</v>
@@ -4052,7 +4052,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G127" t="n">
-        <v>9.57166481018066</v>
+        <v>9.57166576385498</v>
       </c>
       <c r="H127" t="n">
         <v>24263</v>
@@ -4139,7 +4139,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G130" t="n">
-        <v>9.9855260848999</v>
+        <v>9.98552703857422</v>
       </c>
       <c r="H130" t="n">
         <v>15581</v>
@@ -4197,7 +4197,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.18421936035156</v>
+        <v>9.18421840667725</v>
       </c>
       <c r="H132" t="n">
         <v>96061</v>
@@ -4226,7 +4226,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019107818604</v>
+        <v>9.14019203186035</v>
       </c>
       <c r="H133" t="n">
         <v>64369</v>
@@ -4255,7 +4255,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G134" t="n">
-        <v>9.721360206604</v>
+        <v>9.72135925292969</v>
       </c>
       <c r="H134" t="n">
         <v>37896</v>
@@ -4371,7 +4371,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>10.2849168777466</v>
+        <v>10.2849178314209</v>
       </c>
       <c r="H138" t="n">
         <v>15768</v>
@@ -4400,7 +4400,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1352224349976</v>
+        <v>10.1352233886719</v>
       </c>
       <c r="H139" t="n">
         <v>7545</v>
@@ -4545,7 +4545,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G144" t="n">
-        <v>10.2673053741455</v>
+        <v>10.2673063278198</v>
       </c>
       <c r="H144" t="n">
         <v>23296</v>
@@ -4574,7 +4574,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.3025274276733</v>
+        <v>10.3025283813477</v>
       </c>
       <c r="H145" t="n">
         <v>26846</v>
@@ -4603,7 +4603,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987800598145</v>
+        <v>10.6987781524658</v>
       </c>
       <c r="H146" t="n">
         <v>35625</v>
@@ -4661,7 +4661,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G148" t="n">
-        <v>11.0157794952393</v>
+        <v>11.0157804489136</v>
       </c>
       <c r="H148" t="n">
         <v>49513</v>
@@ -4690,7 +4690,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>11.033390045166</v>
+        <v>11.0333919525146</v>
       </c>
       <c r="H149" t="n">
         <v>32061</v>
@@ -4719,7 +4719,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>11.033390045166</v>
+        <v>11.0333919525146</v>
       </c>
       <c r="H150" t="n">
         <v>31452</v>
@@ -4748,7 +4748,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G151" t="n">
-        <v>10.8308639526367</v>
+        <v>10.8308629989624</v>
       </c>
       <c r="H151" t="n">
         <v>42419</v>
@@ -4777,7 +4777,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893636703491</v>
+        <v>10.9893627166748</v>
       </c>
       <c r="H152" t="n">
         <v>42127</v>
@@ -4806,7 +4806,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748922348022</v>
+        <v>10.8748912811279</v>
       </c>
       <c r="H153" t="n">
         <v>39269</v>
@@ -4835,7 +4835,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748922348022</v>
+        <v>10.8748912811279</v>
       </c>
       <c r="H154" t="n">
         <v>23378</v>
@@ -4864,7 +4864,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>10.9277229309082</v>
+        <v>10.9277238845825</v>
       </c>
       <c r="H155" t="n">
         <v>22842</v>
@@ -4922,7 +4922,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G157" t="n">
-        <v>11.253529548645</v>
+        <v>11.2535305023193</v>
       </c>
       <c r="H157" t="n">
         <v>72265</v>
@@ -4980,7 +4980,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>11.253529548645</v>
+        <v>11.2535305023193</v>
       </c>
       <c r="H159" t="n">
         <v>20029</v>
@@ -5009,7 +5009,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G160" t="n">
-        <v>11.0157794952393</v>
+        <v>11.0157804489136</v>
       </c>
       <c r="H160" t="n">
         <v>57012</v>
@@ -5038,7 +5038,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>10.7251977920532</v>
+        <v>10.7251968383789</v>
       </c>
       <c r="H161" t="n">
         <v>58715</v>
@@ -5067,7 +5067,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>11.0510015487671</v>
+        <v>11.0510034561157</v>
       </c>
       <c r="H162" t="n">
         <v>19081</v>
@@ -5096,7 +5096,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>10.9013071060181</v>
+        <v>10.9013090133667</v>
       </c>
       <c r="H163" t="n">
         <v>12830</v>
@@ -5125,7 +5125,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654758453369</v>
+        <v>11.1654748916626</v>
       </c>
       <c r="H164" t="n">
         <v>19684</v>
@@ -5154,7 +5154,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G165" t="n">
-        <v>11.0598077774048</v>
+        <v>11.0598087310791</v>
       </c>
       <c r="H165" t="n">
         <v>40339</v>
@@ -5212,7 +5212,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G167" t="n">
-        <v>11.1214466094971</v>
+        <v>11.1214456558228</v>
       </c>
       <c r="H167" t="n">
         <v>45450</v>
@@ -5270,7 +5270,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302528381348</v>
+        <v>11.1302537918091</v>
       </c>
       <c r="H169" t="n">
         <v>50121</v>
@@ -5299,7 +5299,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>11.1830863952637</v>
+        <v>11.1830854415894</v>
       </c>
       <c r="H170" t="n">
         <v>34325</v>
@@ -5328,7 +5328,7 @@
         <v>12.789999961853</v>
       </c>
       <c r="G171" t="n">
-        <v>11.2623357772827</v>
+        <v>11.262336730957</v>
       </c>
       <c r="H171" t="n">
         <v>27441</v>
@@ -5386,7 +5386,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>11.7466440200806</v>
+        <v>11.7466430664062</v>
       </c>
       <c r="H173" t="n">
         <v>47129</v>
@@ -5473,7 +5473,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.7994766235352</v>
+        <v>11.7994756698608</v>
       </c>
       <c r="H176" t="n">
         <v>51577</v>
@@ -5502,7 +5502,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G177" t="n">
-        <v>11.6497812271118</v>
+        <v>11.6497821807861</v>
       </c>
       <c r="H177" t="n">
         <v>41874</v>
@@ -5531,7 +5531,7 @@
         <v>13.25</v>
       </c>
       <c r="G178" t="n">
-        <v>11.6673936843872</v>
+        <v>11.6673927307129</v>
       </c>
       <c r="H178" t="n">
         <v>36341</v>
@@ -5560,7 +5560,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G179" t="n">
-        <v>11.6497812271118</v>
+        <v>11.6497821807861</v>
       </c>
       <c r="H179" t="n">
         <v>69100</v>
@@ -5589,7 +5589,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472541809082</v>
+        <v>11.4472532272339</v>
       </c>
       <c r="H180" t="n">
         <v>64823</v>
@@ -5618,7 +5618,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>11.323974609375</v>
+        <v>11.3239755630493</v>
       </c>
       <c r="H181" t="n">
         <v>72041</v>
@@ -5647,7 +5647,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G182" t="n">
-        <v>11.3680028915405</v>
+        <v>11.3680038452148</v>
       </c>
       <c r="H182" t="n">
         <v>62143</v>
@@ -5676,7 +5676,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>11.1390571594238</v>
+        <v>11.1390581130981</v>
       </c>
       <c r="H183" t="n">
         <v>30268</v>
@@ -5734,7 +5734,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472541809082</v>
+        <v>11.4472532272339</v>
       </c>
       <c r="H185" t="n">
         <v>43283</v>
@@ -5763,7 +5763,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G186" t="n">
-        <v>11.6145601272583</v>
+        <v>11.6145582199097</v>
       </c>
       <c r="H186" t="n">
         <v>25730</v>
@@ -5792,7 +5792,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G187" t="n">
-        <v>11.8258943557739</v>
+        <v>11.8258934020996</v>
       </c>
       <c r="H187" t="n">
         <v>136773</v>
@@ -5821,7 +5821,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G188" t="n">
-        <v>12.0372266769409</v>
+        <v>12.0372276306152</v>
       </c>
       <c r="H188" t="n">
         <v>83675</v>
@@ -5879,7 +5879,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.0636444091797</v>
+        <v>12.0636425018311</v>
       </c>
       <c r="H190" t="n">
         <v>38989</v>
@@ -5937,7 +5937,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303382873535</v>
+        <v>12.5303392410278</v>
       </c>
       <c r="H192" t="n">
         <v>109655</v>
@@ -5966,7 +5966,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070606231689</v>
+        <v>12.4070634841919</v>
       </c>
       <c r="H193" t="n">
         <v>92196</v>
@@ -5995,7 +5995,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837829589844</v>
+        <v>12.2837839126587</v>
       </c>
       <c r="H194" t="n">
         <v>42892</v>
@@ -6111,7 +6111,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>12.856146812439</v>
+        <v>12.8561458587646</v>
       </c>
       <c r="H198" t="n">
         <v>56736</v>
@@ -6169,7 +6169,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G200" t="n">
-        <v>13.4108982086182</v>
+        <v>13.4108972549438</v>
       </c>
       <c r="H200" t="n">
         <v>211127</v>
@@ -6198,7 +6198,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782041549683</v>
+        <v>13.5782032012939</v>
       </c>
       <c r="H201" t="n">
         <v>145739</v>
@@ -6227,7 +6227,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G202" t="n">
-        <v>13.6838712692261</v>
+        <v>13.6838693618774</v>
       </c>
       <c r="H202" t="n">
         <v>145564</v>
@@ -6256,7 +6256,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285097122192</v>
+        <v>13.4285078048706</v>
       </c>
       <c r="H203" t="n">
         <v>304187</v>
@@ -6314,7 +6314,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210111618042</v>
+        <v>14.2210102081299</v>
       </c>
       <c r="H205" t="n">
         <v>191135</v>
@@ -6372,7 +6372,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.1329536437988</v>
+        <v>14.1329555511475</v>
       </c>
       <c r="H207" t="n">
         <v>75250</v>
@@ -6488,7 +6488,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>13.7807321548462</v>
+        <v>13.7807302474976</v>
       </c>
       <c r="H211" t="n">
         <v>83561</v>
@@ -6546,7 +6546,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631196975708</v>
+        <v>13.7631206512451</v>
       </c>
       <c r="H213" t="n">
         <v>75863</v>
@@ -6604,7 +6604,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7278985977173</v>
+        <v>13.7278995513916</v>
       </c>
       <c r="H215" t="n">
         <v>17418</v>
@@ -6633,7 +6633,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G216" t="n">
-        <v>13.1995630264282</v>
+        <v>13.1995639801025</v>
       </c>
       <c r="H216" t="n">
         <v>212327</v>
@@ -6662,7 +6662,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>13.375675201416</v>
+        <v>13.3756732940674</v>
       </c>
       <c r="H217" t="n">
         <v>67398</v>
@@ -6720,7 +6720,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486492156982</v>
+        <v>13.6486482620239</v>
       </c>
       <c r="H219" t="n">
         <v>47806</v>
@@ -6778,7 +6778,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285097122192</v>
+        <v>13.4285078048706</v>
       </c>
       <c r="H221" t="n">
         <v>144794</v>
@@ -6807,7 +6807,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>13.736704826355</v>
+        <v>13.7367038726807</v>
       </c>
       <c r="H222" t="n">
         <v>115544</v>
@@ -6865,7 +6865,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>14.176983833313</v>
+        <v>14.1769847869873</v>
       </c>
       <c r="H224" t="n">
         <v>125262</v>
@@ -6952,7 +6952,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040952682495</v>
+        <v>15.3040971755981</v>
       </c>
       <c r="H227" t="n">
         <v>258275</v>
@@ -6981,7 +6981,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.277681350708</v>
+        <v>15.2776823043823</v>
       </c>
       <c r="H228" t="n">
         <v>398968</v>
@@ -7010,7 +7010,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G229" t="n">
-        <v>15.4890155792236</v>
+        <v>15.4890165328979</v>
       </c>
       <c r="H229" t="n">
         <v>247524</v>
@@ -7039,7 +7039,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978199005127</v>
+        <v>15.4978218078613</v>
       </c>
       <c r="H230" t="n">
         <v>289822</v>
@@ -7068,7 +7068,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657369613647</v>
+        <v>15.3657350540161</v>
       </c>
       <c r="H231" t="n">
         <v>110362</v>
@@ -7126,7 +7126,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G233" t="n">
-        <v>15.339319229126</v>
+        <v>15.3393201828003</v>
       </c>
       <c r="H233" t="n">
         <v>71686</v>
@@ -7155,7 +7155,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5330429077148</v>
+        <v>15.5330419540405</v>
       </c>
       <c r="H234" t="n">
         <v>122396</v>
@@ -7184,7 +7184,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G235" t="n">
-        <v>15.6651268005371</v>
+        <v>15.6651248931885</v>
       </c>
       <c r="H235" t="n">
         <v>210948</v>
@@ -7213,7 +7213,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G236" t="n">
-        <v>15.5418481826782</v>
+        <v>15.5418472290039</v>
       </c>
       <c r="H236" t="n">
         <v>99490</v>
@@ -7242,7 +7242,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>15.2424573898315</v>
+        <v>15.2424564361572</v>
       </c>
       <c r="H237" t="n">
         <v>98091</v>
@@ -7271,7 +7271,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.277681350708</v>
+        <v>15.2776823043823</v>
       </c>
       <c r="H238" t="n">
         <v>97203</v>
@@ -7329,7 +7329,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G240" t="n">
-        <v>16.1934623718262</v>
+        <v>16.1934604644775</v>
       </c>
       <c r="H240" t="n">
         <v>378003</v>
@@ -7358,7 +7358,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G241" t="n">
-        <v>16.3695755004883</v>
+        <v>16.3695735931396</v>
       </c>
       <c r="H241" t="n">
         <v>106538</v>
@@ -7387,7 +7387,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.4664344787598</v>
+        <v>16.4664325714111</v>
       </c>
       <c r="H242" t="n">
         <v>118582</v>
@@ -7416,7 +7416,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.5104656219482</v>
+        <v>16.5104637145996</v>
       </c>
       <c r="H243" t="n">
         <v>85459</v>
@@ -7445,7 +7445,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.5104656219482</v>
+        <v>16.5104637145996</v>
       </c>
       <c r="H244" t="n">
         <v>184405</v>
@@ -7474,7 +7474,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.0387954711914</v>
+        <v>17.03879737854</v>
       </c>
       <c r="H245" t="n">
         <v>177039</v>
@@ -7503,7 +7503,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.8890991210938</v>
+        <v>16.8891010284424</v>
       </c>
       <c r="H246" t="n">
         <v>240701</v>
@@ -7532,7 +7532,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G247" t="n">
-        <v>17.1532688140869</v>
+        <v>17.1532707214355</v>
       </c>
       <c r="H247" t="n">
         <v>100453</v>
@@ -7590,7 +7590,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>16.5544891357422</v>
+        <v>16.5544872283936</v>
       </c>
       <c r="H249" t="n">
         <v>545131</v>
@@ -7706,7 +7706,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G253" t="n">
-        <v>16.5721015930176</v>
+        <v>16.5720996856689</v>
       </c>
       <c r="H253" t="n">
         <v>93811</v>
@@ -7764,7 +7764,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G255" t="n">
-        <v>16.7041816711426</v>
+        <v>16.7041835784912</v>
       </c>
       <c r="H255" t="n">
         <v>52207</v>
@@ -7793,7 +7793,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.8802947998047</v>
+        <v>16.8802967071533</v>
       </c>
       <c r="H256" t="n">
         <v>74391</v>
@@ -7822,7 +7822,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538780212402</v>
+        <v>16.8538799285889</v>
       </c>
       <c r="H257" t="n">
         <v>23740</v>
@@ -7851,7 +7851,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.0123805999756</v>
+        <v>17.0123767852783</v>
       </c>
       <c r="H258" t="n">
         <v>25398</v>
@@ -7880,7 +7880,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>17.1532688140869</v>
+        <v>17.1532707214355</v>
       </c>
       <c r="H259" t="n">
         <v>100834</v>
@@ -7909,7 +7909,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G260" t="n">
-        <v>17.2941570281982</v>
+        <v>17.2941589355469</v>
       </c>
       <c r="H260" t="n">
         <v>117775</v>
@@ -7967,7 +7967,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.0387954711914</v>
+        <v>17.03879737854</v>
       </c>
       <c r="H262" t="n">
         <v>26170</v>
@@ -8054,7 +8054,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>16.8626842498779</v>
+        <v>16.8626823425293</v>
       </c>
       <c r="H265" t="n">
         <v>51846</v>
@@ -8112,7 +8112,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>17.3469944000244</v>
+        <v>17.3469924926758</v>
       </c>
       <c r="H267" t="n">
         <v>96917</v>
@@ -8170,7 +8170,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G269" t="n">
-        <v>17.5407123565674</v>
+        <v>17.540714263916</v>
       </c>
       <c r="H269" t="n">
         <v>197725</v>
@@ -8228,7 +8228,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G271" t="n">
-        <v>17.7168254852295</v>
+        <v>17.7168273925781</v>
       </c>
       <c r="H271" t="n">
         <v>75032</v>
@@ -8286,7 +8286,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>17.55832862854</v>
+        <v>17.5583248138428</v>
       </c>
       <c r="H273" t="n">
         <v>24496</v>
@@ -8315,7 +8315,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>17.7432422637939</v>
+        <v>17.7432441711426</v>
       </c>
       <c r="H274" t="n">
         <v>80664</v>
@@ -8344,7 +8344,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G275" t="n">
-        <v>17.8401031494141</v>
+        <v>17.8401050567627</v>
       </c>
       <c r="H275" t="n">
         <v>58976</v>
@@ -8402,7 +8402,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G277" t="n">
-        <v>17.5759372711182</v>
+        <v>17.5759353637695</v>
       </c>
       <c r="H277" t="n">
         <v>65783</v>
@@ -8431,7 +8431,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G278" t="n">
-        <v>16.7482109069824</v>
+        <v>16.7482128143311</v>
       </c>
       <c r="H278" t="n">
         <v>113676</v>
@@ -8489,7 +8489,7 @@
         <v>19.25</v>
       </c>
       <c r="G280" t="n">
-        <v>16.9507369995117</v>
+        <v>16.9507427215576</v>
       </c>
       <c r="H280" t="n">
         <v>60029</v>
@@ -8605,7 +8605,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>17.1092395782471</v>
+        <v>17.1092414855957</v>
       </c>
       <c r="H284" t="n">
         <v>50524</v>
@@ -8634,7 +8634,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G285" t="n">
-        <v>16.8626842498779</v>
+        <v>16.8626823425293</v>
       </c>
       <c r="H285" t="n">
         <v>37497</v>
@@ -8663,7 +8663,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.8890991210938</v>
+        <v>16.8891010284424</v>
       </c>
       <c r="H286" t="n">
         <v>33722</v>
@@ -8692,7 +8692,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G287" t="n">
-        <v>16.8186550140381</v>
+        <v>16.8186569213867</v>
       </c>
       <c r="H287" t="n">
         <v>24250</v>
@@ -8721,7 +8721,7 @@
         <v>19.25</v>
       </c>
       <c r="G288" t="n">
-        <v>16.9507369995117</v>
+        <v>16.9507427215576</v>
       </c>
       <c r="H288" t="n">
         <v>47872</v>
@@ -8750,7 +8750,7 @@
         <v>19.25</v>
       </c>
       <c r="G289" t="n">
-        <v>16.9507369995117</v>
+        <v>16.9507427215576</v>
       </c>
       <c r="H289" t="n">
         <v>32145</v>
@@ -8779,7 +8779,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G290" t="n">
-        <v>17.2325191497803</v>
+        <v>17.2325210571289</v>
       </c>
       <c r="H290" t="n">
         <v>110900</v>
@@ -8837,7 +8837,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>17.2853527069092</v>
+        <v>17.2853488922119</v>
       </c>
       <c r="H292" t="n">
         <v>75503</v>
@@ -8866,7 +8866,7 @@
         <v>19.75</v>
       </c>
       <c r="G293" t="n">
-        <v>17.3910179138184</v>
+        <v>17.391019821167</v>
       </c>
       <c r="H293" t="n">
         <v>29528</v>
@@ -8895,7 +8895,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>17.1092395782471</v>
+        <v>17.1092414855957</v>
       </c>
       <c r="H294" t="n">
         <v>52387</v>
@@ -8924,7 +8924,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G295" t="n">
-        <v>17.2853527069092</v>
+        <v>17.2853488922119</v>
       </c>
       <c r="H295" t="n">
         <v>43544</v>
@@ -8953,7 +8953,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>17.250129699707</v>
+        <v>17.2501277923584</v>
       </c>
       <c r="H296" t="n">
         <v>53304</v>
@@ -8982,7 +8982,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350471496582</v>
+        <v>17.4350452423096</v>
       </c>
       <c r="H297" t="n">
         <v>105130</v>
@@ -9069,7 +9069,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>17.9457721710205</v>
+        <v>17.9457683563232</v>
       </c>
       <c r="H300" t="n">
         <v>68868</v>
@@ -9127,7 +9127,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G302" t="n">
-        <v>19.9358310699463</v>
+        <v>19.9358348846436</v>
       </c>
       <c r="H302" t="n">
         <v>140384</v>
@@ -9243,7 +9243,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G306" t="n">
-        <v>20.8339996337891</v>
+        <v>20.8340015411377</v>
       </c>
       <c r="H306" t="n">
         <v>87962</v>
@@ -9272,7 +9272,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G307" t="n">
-        <v>21.045337677002</v>
+        <v>21.0453357696533</v>
       </c>
       <c r="H307" t="n">
         <v>88135</v>
@@ -9301,7 +9301,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824756622314</v>
+        <v>21.5824775695801</v>
       </c>
       <c r="H308" t="n">
         <v>115604</v>
@@ -9359,7 +9359,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>21.3271141052246</v>
+        <v>21.327112197876</v>
       </c>
       <c r="H310" t="n">
         <v>59333</v>
@@ -9417,7 +9417,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497844696045</v>
+        <v>21.7497825622559</v>
       </c>
       <c r="H312" t="n">
         <v>78215</v>
@@ -9475,7 +9475,7 @@
         <v>24.7700004577637</v>
       </c>
       <c r="G314" t="n">
-        <v>21.8114204406738</v>
+        <v>21.8114223480225</v>
       </c>
       <c r="H314" t="n">
         <v>83092</v>
@@ -9504,7 +9504,7 @@
         <v>25</v>
       </c>
       <c r="G315" t="n">
-        <v>22.0139465332031</v>
+        <v>22.0139484405518</v>
       </c>
       <c r="H315" t="n">
         <v>69244</v>
@@ -9533,7 +9533,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.2869205474854</v>
+        <v>22.286922454834</v>
       </c>
       <c r="H316" t="n">
         <v>115542</v>
@@ -9562,7 +9562,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605056762695</v>
+        <v>22.2605075836182</v>
       </c>
       <c r="H317" t="n">
         <v>83792</v>
@@ -9591,7 +9591,7 @@
         <v>25.3799991607666</v>
       </c>
       <c r="G318" t="n">
-        <v>22.3485565185547</v>
+        <v>22.348560333252</v>
       </c>
       <c r="H318" t="n">
         <v>54563</v>
@@ -9765,7 +9765,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G324" t="n">
-        <v>22.665563583374</v>
+        <v>22.6655616760254</v>
       </c>
       <c r="H324" t="n">
         <v>95912</v>
@@ -9823,7 +9823,7 @@
         <v>25.6900005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>22.6215343475342</v>
+        <v>22.6215362548828</v>
       </c>
       <c r="H326" t="n">
         <v>41825</v>
@@ -9852,7 +9852,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743679046631</v>
+        <v>22.6743659973145</v>
       </c>
       <c r="H327" t="n">
         <v>33968</v>
@@ -9881,7 +9881,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945083618164</v>
+        <v>22.8945064544678</v>
       </c>
       <c r="H328" t="n">
         <v>89327</v>
@@ -9968,7 +9968,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>22.3749771118164</v>
+        <v>22.3749809265137</v>
       </c>
       <c r="H331" t="n">
         <v>41506</v>
@@ -9997,7 +9997,7 @@
         <v>25</v>
       </c>
       <c r="G332" t="n">
-        <v>22.0139465332031</v>
+        <v>22.0139484405518</v>
       </c>
       <c r="H332" t="n">
         <v>63890</v>
@@ -10026,7 +10026,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G333" t="n">
-        <v>23.1938991546631</v>
+        <v>23.1938972473145</v>
       </c>
       <c r="H333" t="n">
         <v>56151</v>
@@ -10142,7 +10142,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417621612549</v>
+        <v>24.2417640686035</v>
       </c>
       <c r="H337" t="n">
         <v>94347</v>
@@ -10229,7 +10229,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.9197883605957</v>
+        <v>24.9197902679443</v>
       </c>
       <c r="H340" t="n">
         <v>76611</v>
@@ -10258,7 +10258,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870933532715</v>
+        <v>25.0870971679688</v>
       </c>
       <c r="H341" t="n">
         <v>113660</v>
@@ -10287,7 +10287,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>24.9638175964355</v>
+        <v>24.9638195037842</v>
       </c>
       <c r="H342" t="n">
         <v>62731</v>
@@ -10316,7 +10316,7 @@
         <v>28.2700004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>24.8933753967285</v>
+        <v>24.8933734893799</v>
       </c>
       <c r="H343" t="n">
         <v>72745</v>
@@ -10345,7 +10345,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255447387695</v>
+        <v>26.4255466461182</v>
       </c>
       <c r="H344" t="n">
         <v>323645</v>
@@ -10374,7 +10374,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G345" t="n">
-        <v>26.4879322052002</v>
+        <v>26.4879341125488</v>
       </c>
       <c r="H345" t="n">
         <v>116456</v>
@@ -10490,7 +10490,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G349" t="n">
-        <v>27.6732921600342</v>
+        <v>27.6732940673828</v>
       </c>
       <c r="H349" t="n">
         <v>144929</v>
@@ -10635,7 +10635,7 @@
         <v>32.560001373291</v>
       </c>
       <c r="G354" t="n">
-        <v>29.0190849304199</v>
+        <v>29.019079208374</v>
       </c>
       <c r="H354" t="n">
         <v>134928</v>
@@ -10664,7 +10664,7 @@
         <v>33.0900001525879</v>
       </c>
       <c r="G355" t="n">
-        <v>29.4914474487305</v>
+        <v>29.4914436340332</v>
       </c>
       <c r="H355" t="n">
         <v>77343</v>
@@ -10693,7 +10693,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>29.7677364349365</v>
+        <v>29.7677345275879</v>
       </c>
       <c r="H356" t="n">
         <v>96078</v>
@@ -10722,7 +10722,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746795654297</v>
+        <v>29.8746814727783</v>
       </c>
       <c r="H357" t="n">
         <v>77270</v>
@@ -10751,7 +10751,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024787902832</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H358" t="n">
         <v>94582</v>
@@ -10780,7 +10780,7 @@
         <v>34.5299987792969</v>
       </c>
       <c r="G359" t="n">
-        <v>30.7748432159424</v>
+        <v>30.7748470306396</v>
       </c>
       <c r="H359" t="n">
         <v>96091</v>
@@ -10925,7 +10925,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154800415039</v>
+        <v>31.0154838562012</v>
       </c>
       <c r="H364" t="n">
         <v>62681</v>
@@ -10954,7 +10954,7 @@
         <v>34.7799987792969</v>
       </c>
       <c r="G365" t="n">
-        <v>30.9976501464844</v>
+        <v>30.9976539611816</v>
       </c>
       <c r="H365" t="n">
         <v>39009</v>
@@ -11012,7 +11012,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G367" t="n">
-        <v>30.6500663757324</v>
+        <v>30.6500701904297</v>
       </c>
       <c r="H367" t="n">
         <v>49692</v>
@@ -11041,7 +11041,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.7481060028076</v>
+        <v>30.748104095459</v>
       </c>
       <c r="H368" t="n">
         <v>76769</v>
@@ -11070,7 +11070,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.685718536377</v>
+        <v>30.6857223510742</v>
       </c>
       <c r="H369" t="n">
         <v>81969</v>
@@ -11099,7 +11099,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G370" t="n">
-        <v>29.3577556610107</v>
+        <v>29.3577537536621</v>
       </c>
       <c r="H370" t="n">
         <v>121414</v>
@@ -11186,7 +11186,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>29.2775440216064</v>
+        <v>29.2775402069092</v>
       </c>
       <c r="H373" t="n">
         <v>103705</v>
@@ -11215,7 +11215,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.1687889099121</v>
+        <v>30.168794631958</v>
       </c>
       <c r="H374" t="n">
         <v>129825</v>
@@ -11244,7 +11244,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331443786621</v>
+        <v>30.1331462860107</v>
       </c>
       <c r="H375" t="n">
         <v>53130</v>
@@ -11331,7 +11331,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G378" t="n">
-        <v>30.0529327392578</v>
+        <v>30.0529289245605</v>
       </c>
       <c r="H378" t="n">
         <v>73018</v>
@@ -11360,7 +11360,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G379" t="n">
-        <v>29.482536315918</v>
+        <v>29.4825286865234</v>
       </c>
       <c r="H379" t="n">
         <v>44022</v>
@@ -11447,7 +11447,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.126033782959</v>
+        <v>29.1260299682617</v>
       </c>
       <c r="H382" t="n">
         <v>60542</v>
@@ -11476,7 +11476,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>27.771333694458</v>
+        <v>27.7713298797607</v>
       </c>
       <c r="H383" t="n">
         <v>57971</v>
@@ -11534,7 +11534,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544059753418</v>
+        <v>27.2544078826904</v>
       </c>
       <c r="H385" t="n">
         <v>71103</v>
@@ -11563,7 +11563,7 @@
         <v>31.0699996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>27.6911182403564</v>
+        <v>27.6911201477051</v>
       </c>
       <c r="H386" t="n">
         <v>94629</v>
@@ -11621,7 +11621,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="G388" t="n">
-        <v>27.5752563476562</v>
+        <v>27.5752582550049</v>
       </c>
       <c r="H388" t="n">
         <v>39274</v>
@@ -11650,7 +11650,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G389" t="n">
-        <v>28.1189193725586</v>
+        <v>28.11891746521</v>
       </c>
       <c r="H389" t="n">
         <v>62724</v>
@@ -11679,7 +11679,7 @@
         <v>31.8099994659424</v>
       </c>
       <c r="G390" t="n">
-        <v>28.3506450653076</v>
+        <v>28.3506412506104</v>
       </c>
       <c r="H390" t="n">
         <v>37980</v>
@@ -11708,7 +11708,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178554534912</v>
+        <v>27.7178573608398</v>
       </c>
       <c r="H391" t="n">
         <v>37483</v>
@@ -11737,7 +11737,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734596252441</v>
+        <v>28.5734577178955</v>
       </c>
       <c r="H392" t="n">
         <v>75319</v>
@@ -11766,7 +11766,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G393" t="n">
-        <v>28.6180191040039</v>
+        <v>28.6180210113525</v>
       </c>
       <c r="H393" t="n">
         <v>25940</v>
@@ -11824,7 +11824,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G395" t="n">
-        <v>28.7873573303223</v>
+        <v>28.7873554229736</v>
       </c>
       <c r="H395" t="n">
         <v>65931</v>
@@ -11911,7 +11911,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G398" t="n">
-        <v>29.536003112793</v>
+        <v>29.5360069274902</v>
       </c>
       <c r="H398" t="n">
         <v>60276</v>
@@ -11940,7 +11940,7 @@
         <v>32.9099998474121</v>
       </c>
       <c r="G399" t="n">
-        <v>29.3310203552246</v>
+        <v>29.331018447876</v>
       </c>
       <c r="H399" t="n">
         <v>35491</v>
@@ -11969,7 +11969,7 @@
         <v>32.7299995422363</v>
       </c>
       <c r="G400" t="n">
-        <v>29.1705932617188</v>
+        <v>29.1705951690674</v>
       </c>
       <c r="H400" t="n">
         <v>60603</v>
@@ -12027,7 +12027,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G402" t="n">
-        <v>29.1438579559326</v>
+        <v>29.143856048584</v>
       </c>
       <c r="H402" t="n">
         <v>67166</v>
@@ -12056,7 +12056,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221073150635</v>
+        <v>29.3221092224121</v>
       </c>
       <c r="H403" t="n">
         <v>93384</v>
@@ -12085,7 +12085,7 @@
         <v>32.5</v>
       </c>
       <c r="G404" t="n">
-        <v>28.9656066894531</v>
+        <v>28.9656047821045</v>
       </c>
       <c r="H404" t="n">
         <v>28407</v>
@@ -12143,7 +12143,7 @@
         <v>32.5</v>
       </c>
       <c r="G406" t="n">
-        <v>28.9656066894531</v>
+        <v>28.9656047821045</v>
       </c>
       <c r="H406" t="n">
         <v>55695</v>
@@ -12172,7 +12172,7 @@
         <v>32.5299987792969</v>
       </c>
       <c r="G407" t="n">
-        <v>28.9923439025879</v>
+        <v>28.9923419952393</v>
       </c>
       <c r="H407" t="n">
         <v>32363</v>
@@ -12230,7 +12230,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>29.7677364349365</v>
+        <v>29.7677345275879</v>
       </c>
       <c r="H409" t="n">
         <v>74517</v>
@@ -12288,7 +12288,7 @@
         <v>33.5</v>
       </c>
       <c r="G411" t="n">
-        <v>29.8568553924561</v>
+        <v>29.8568592071533</v>
       </c>
       <c r="H411" t="n">
         <v>92243</v>
@@ -12346,7 +12346,7 @@
         <v>33</v>
       </c>
       <c r="G413" t="n">
-        <v>29.4112319946289</v>
+        <v>29.4112300872803</v>
       </c>
       <c r="H413" t="n">
         <v>55788</v>
@@ -12375,7 +12375,7 @@
         <v>32.3300018310547</v>
       </c>
       <c r="G414" t="n">
-        <v>28.814094543457</v>
+        <v>28.8140964508057</v>
       </c>
       <c r="H414" t="n">
         <v>37331</v>
@@ -12404,7 +12404,7 @@
         <v>33</v>
       </c>
       <c r="G415" t="n">
-        <v>29.4112319946289</v>
+        <v>29.4112300872803</v>
       </c>
       <c r="H415" t="n">
         <v>48065</v>
@@ -12433,7 +12433,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.687520980835</v>
+        <v>29.6875171661377</v>
       </c>
       <c r="H416" t="n">
         <v>61558</v>
@@ -12462,7 +12462,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>29.6162223815918</v>
+        <v>29.6162185668945</v>
       </c>
       <c r="H417" t="n">
         <v>37108</v>
@@ -12520,7 +12520,7 @@
         <v>33.3199996948242</v>
       </c>
       <c r="G419" t="n">
-        <v>29.6964302062988</v>
+        <v>29.6964282989502</v>
       </c>
       <c r="H419" t="n">
         <v>28781</v>
@@ -12578,7 +12578,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390293121338</v>
+        <v>29.8390331268311</v>
       </c>
       <c r="H421" t="n">
         <v>26190</v>
@@ -12607,7 +12607,7 @@
         <v>33.8699989318848</v>
       </c>
       <c r="G422" t="n">
-        <v>30.1866188049316</v>
+        <v>30.1866149902344</v>
       </c>
       <c r="H422" t="n">
         <v>29191</v>
@@ -12665,7 +12665,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.5181789398193</v>
+        <v>29.5181770324707</v>
       </c>
       <c r="H424" t="n">
         <v>23018</v>
@@ -12694,7 +12694,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G425" t="n">
-        <v>29.1795063018799</v>
+        <v>29.1795082092285</v>
       </c>
       <c r="H425" t="n">
         <v>93713</v>
@@ -12723,7 +12723,7 @@
         <v>33.0299987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>29.4379692077637</v>
+        <v>29.437967300415</v>
       </c>
       <c r="H426" t="n">
         <v>57589</v>
@@ -12752,7 +12752,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648681640625</v>
+        <v>30.3648643493652</v>
       </c>
       <c r="H427" t="n">
         <v>64685</v>
@@ -12781,7 +12781,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629077911377</v>
+        <v>30.4629096984863</v>
       </c>
       <c r="H428" t="n">
         <v>65836</v>
@@ -12810,7 +12810,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024787902832</v>
+        <v>30.3024826049805</v>
       </c>
       <c r="H429" t="n">
         <v>35077</v>
@@ -12839,7 +12839,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G430" t="n">
-        <v>30.4718170166016</v>
+        <v>30.4718208312988</v>
       </c>
       <c r="H430" t="n">
         <v>35469</v>
@@ -12868,7 +12868,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G431" t="n">
-        <v>30.2935695648193</v>
+        <v>30.2935676574707</v>
       </c>
       <c r="H431" t="n">
         <v>27202</v>
@@ -12897,7 +12897,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974903106689</v>
+        <v>30.0974941253662</v>
       </c>
       <c r="H432" t="n">
         <v>12531</v>
@@ -12926,7 +12926,7 @@
         <v>33.7299995422363</v>
       </c>
       <c r="G433" t="n">
-        <v>30.0618438720703</v>
+        <v>30.0618419647217</v>
       </c>
       <c r="H433" t="n">
         <v>32928</v>
@@ -12955,7 +12955,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.2311744689941</v>
+        <v>30.2311820983887</v>
       </c>
       <c r="H434" t="n">
         <v>24161</v>
@@ -13100,7 +13100,7 @@
         <v>35.9000015258789</v>
       </c>
       <c r="G439" t="n">
-        <v>31.9958572387695</v>
+        <v>31.9958553314209</v>
       </c>
       <c r="H439" t="n">
         <v>59390</v>
@@ -13129,7 +13129,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G440" t="n">
-        <v>31.773042678833</v>
+        <v>31.7730388641357</v>
       </c>
       <c r="H440" t="n">
         <v>27909</v>
@@ -13158,7 +13158,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G441" t="n">
-        <v>31.773042678833</v>
+        <v>31.7730388641357</v>
       </c>
       <c r="H441" t="n">
         <v>20121</v>
@@ -13187,7 +13187,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928310394287</v>
+        <v>31.6928272247314</v>
       </c>
       <c r="H442" t="n">
         <v>33799</v>
@@ -13216,7 +13216,7 @@
         <v>36.1100006103516</v>
       </c>
       <c r="G443" t="n">
-        <v>32.1830139160156</v>
+        <v>32.1830177307129</v>
       </c>
       <c r="H443" t="n">
         <v>74880</v>
@@ -13245,7 +13245,7 @@
         <v>35.9900016784668</v>
       </c>
       <c r="G444" t="n">
-        <v>32.0760650634766</v>
+        <v>32.0760688781738</v>
       </c>
       <c r="H444" t="n">
         <v>50553</v>
@@ -13274,7 +13274,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.9512901306152</v>
+        <v>31.9512844085693</v>
       </c>
       <c r="H445" t="n">
         <v>54557</v>
@@ -13303,7 +13303,7 @@
         <v>36.25</v>
       </c>
       <c r="G446" t="n">
-        <v>32.307788848877</v>
+        <v>32.3077964782715</v>
       </c>
       <c r="H446" t="n">
         <v>79657</v>
@@ -13332,7 +13332,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990356445312</v>
+        <v>33.1990394592285</v>
       </c>
       <c r="H447" t="n">
         <v>128921</v>
@@ -13361,7 +13361,7 @@
         <v>37.4700012207031</v>
       </c>
       <c r="G448" t="n">
-        <v>33.3951148986816</v>
+        <v>33.3951187133789</v>
       </c>
       <c r="H448" t="n">
         <v>44537</v>
@@ -13419,7 +13419,7 @@
         <v>38.9300003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>34.6963424682617</v>
+        <v>34.6963386535645</v>
       </c>
       <c r="H450" t="n">
         <v>96401</v>
@@ -13506,7 +13506,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>34.2239799499512</v>
+        <v>34.2239761352539</v>
       </c>
       <c r="H453" t="n">
         <v>40089</v>
@@ -13535,7 +13535,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.4378776550293</v>
+        <v>34.437873840332</v>
       </c>
       <c r="H454" t="n">
         <v>22990</v>
@@ -13564,7 +13564,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.4378776550293</v>
+        <v>34.437873840332</v>
       </c>
       <c r="H455" t="n">
         <v>25085</v>
@@ -13622,7 +13622,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G457" t="n">
-        <v>34.5448303222656</v>
+        <v>34.5448265075684</v>
       </c>
       <c r="H457" t="n">
         <v>38480</v>
@@ -13651,7 +13651,7 @@
         <v>39.75</v>
       </c>
       <c r="G458" t="n">
-        <v>35.4271659851074</v>
+        <v>35.4271621704102</v>
       </c>
       <c r="H458" t="n">
         <v>72239</v>
@@ -13709,7 +13709,7 @@
         <v>38.8899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>34.6606903076172</v>
+        <v>34.6606826782227</v>
       </c>
       <c r="H460" t="n">
         <v>44719</v>
@@ -13767,7 +13767,7 @@
         <v>38</v>
       </c>
       <c r="G462" t="n">
-        <v>33.8674812316895</v>
+        <v>33.8674774169922</v>
       </c>
       <c r="H462" t="n">
         <v>58890</v>
@@ -13825,7 +13825,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G464" t="n">
-        <v>34.1437683105469</v>
+        <v>34.1437644958496</v>
       </c>
       <c r="H464" t="n">
         <v>21788</v>
@@ -13854,7 +13854,7 @@
         <v>38</v>
       </c>
       <c r="G465" t="n">
-        <v>33.8674812316895</v>
+        <v>33.8674774169922</v>
       </c>
       <c r="H465" t="n">
         <v>19781</v>
@@ -13883,7 +13883,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G466" t="n">
-        <v>33.7159729003906</v>
+        <v>33.7159652709961</v>
       </c>
       <c r="H466" t="n">
         <v>30408</v>
@@ -13941,7 +13941,7 @@
         <v>38.5</v>
       </c>
       <c r="G468" t="n">
-        <v>34.3130989074707</v>
+        <v>34.313102722168</v>
       </c>
       <c r="H468" t="n">
         <v>152768</v>
@@ -13970,7 +13970,7 @@
         <v>38.5</v>
       </c>
       <c r="G469" t="n">
-        <v>34.3130989074707</v>
+        <v>34.313102722168</v>
       </c>
       <c r="H469" t="n">
         <v>119331</v>
@@ -13999,7 +13999,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G470" t="n">
-        <v>34.1170234680176</v>
+        <v>34.1170272827148</v>
       </c>
       <c r="H470" t="n">
         <v>74592</v>
@@ -14028,7 +14028,7 @@
         <v>38.6199989318848</v>
       </c>
       <c r="G471" t="n">
-        <v>34.420051574707</v>
+        <v>34.4200477600098</v>
       </c>
       <c r="H471" t="n">
         <v>26257</v>
@@ -14057,7 +14057,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G472" t="n">
-        <v>34.1170234680176</v>
+        <v>34.1170272827148</v>
       </c>
       <c r="H472" t="n">
         <v>63699</v>
@@ -14086,7 +14086,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G473" t="n">
-        <v>34.776554107666</v>
+        <v>34.7765502929688</v>
       </c>
       <c r="H473" t="n">
         <v>35970</v>
@@ -14115,7 +14115,7 @@
         <v>38.8400001525879</v>
       </c>
       <c r="G474" t="n">
-        <v>34.6161270141602</v>
+        <v>34.6161231994629</v>
       </c>
       <c r="H474" t="n">
         <v>28179</v>
@@ -14144,7 +14144,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041954040527</v>
+        <v>34.3041877746582</v>
       </c>
       <c r="H475" t="n">
         <v>35545</v>
@@ -14173,7 +14173,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081199645996</v>
+        <v>34.1081123352051</v>
       </c>
       <c r="H476" t="n">
         <v>84787</v>
@@ -14202,7 +14202,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8425369262695</v>
+        <v>32.8425407409668</v>
       </c>
       <c r="H477" t="n">
         <v>88388</v>
@@ -14231,7 +14231,7 @@
         <v>38.25</v>
       </c>
       <c r="G478" t="n">
-        <v>34.0902900695801</v>
+        <v>34.0902862548828</v>
       </c>
       <c r="H478" t="n">
         <v>89938</v>
@@ -14260,7 +14260,7 @@
         <v>39.3899993896484</v>
       </c>
       <c r="G479" t="n">
-        <v>35.1063194274902</v>
+        <v>35.106315612793</v>
       </c>
       <c r="H479" t="n">
         <v>154448</v>
@@ -14434,7 +14434,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.8584747314453</v>
+        <v>38.858470916748</v>
       </c>
       <c r="H485" t="n">
         <v>114697</v>
@@ -14463,7 +14463,7 @@
         <v>43.6699981689453</v>
       </c>
       <c r="G486" t="n">
-        <v>38.9208641052246</v>
+        <v>38.9208602905273</v>
       </c>
       <c r="H486" t="n">
         <v>113917</v>
@@ -14492,7 +14492,7 @@
         <v>43.3300018310547</v>
       </c>
       <c r="G487" t="n">
-        <v>38.6178359985352</v>
+        <v>38.6178398132324</v>
       </c>
       <c r="H487" t="n">
         <v>81528</v>
@@ -14579,7 +14579,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G490" t="n">
-        <v>38.4306755065918</v>
+        <v>38.4306716918945</v>
       </c>
       <c r="H490" t="n">
         <v>37738</v>
@@ -14608,7 +14608,7 @@
         <v>44</v>
       </c>
       <c r="G491" t="n">
-        <v>39.214973449707</v>
+        <v>39.2149772644043</v>
       </c>
       <c r="H491" t="n">
         <v>80819</v>
@@ -14666,7 +14666,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G493" t="n">
-        <v>37.8068008422852</v>
+        <v>37.8067970275879</v>
       </c>
       <c r="H493" t="n">
         <v>73604</v>
@@ -14840,7 +14840,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>38.5643615722656</v>
+        <v>38.5643653869629</v>
       </c>
       <c r="H499" t="n">
         <v>49640</v>
@@ -14869,7 +14869,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G500" t="n">
-        <v>38.4306755065918</v>
+        <v>38.4306716918945</v>
       </c>
       <c r="H500" t="n">
         <v>89203</v>
@@ -14898,7 +14898,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089286804199</v>
+        <v>38.6089248657227</v>
       </c>
       <c r="H501" t="n">
         <v>39100</v>
@@ -14927,7 +14927,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.6891326904297</v>
+        <v>38.689136505127</v>
       </c>
       <c r="H502" t="n">
         <v>37927</v>
@@ -14985,7 +14985,7 @@
         <v>44.25</v>
       </c>
       <c r="G504" t="n">
-        <v>39.4377899169922</v>
+        <v>39.4377937316895</v>
       </c>
       <c r="H504" t="n">
         <v>47066</v>
@@ -15014,7 +15014,7 @@
         <v>43.8499984741211</v>
       </c>
       <c r="G505" t="n">
-        <v>39.0812873840332</v>
+        <v>39.0812835693359</v>
       </c>
       <c r="H505" t="n">
         <v>45135</v>
@@ -15043,7 +15043,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545501708984</v>
+        <v>39.0545539855957</v>
       </c>
       <c r="H506" t="n">
         <v>27453</v>
@@ -15101,7 +15101,7 @@
         <v>43.2599983215332</v>
       </c>
       <c r="G508" t="n">
-        <v>38.5554504394531</v>
+        <v>38.5554542541504</v>
       </c>
       <c r="H508" t="n">
         <v>24711</v>
@@ -15159,7 +15159,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G510" t="n">
-        <v>38.3772087097168</v>
+        <v>38.3772048950195</v>
       </c>
       <c r="H510" t="n">
         <v>23866</v>
@@ -15188,7 +15188,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>37.6998519897461</v>
+        <v>37.6998481750488</v>
       </c>
       <c r="H511" t="n">
         <v>40470</v>
@@ -15217,7 +15217,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G512" t="n">
-        <v>36.6125335693359</v>
+        <v>36.6125297546387</v>
       </c>
       <c r="H512" t="n">
         <v>50757</v>
@@ -15246,7 +15246,7 @@
         <v>42.2799987792969</v>
       </c>
       <c r="G513" t="n">
-        <v>37.6820220947266</v>
+        <v>37.6820259094238</v>
       </c>
       <c r="H513" t="n">
         <v>41367</v>
@@ -15333,7 +15333,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G516" t="n">
-        <v>42.655200958252</v>
+        <v>42.6551971435547</v>
       </c>
       <c r="H516" t="n">
         <v>71031</v>
@@ -15362,7 +15362,7 @@
         <v>48.0400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>42.8156242370605</v>
+        <v>42.8156204223633</v>
       </c>
       <c r="H517" t="n">
         <v>52703</v>
@@ -15391,7 +15391,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.4234733581543</v>
+        <v>42.423469543457</v>
       </c>
       <c r="H518" t="n">
         <v>40840</v>
@@ -15449,7 +15449,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G520" t="n">
-        <v>42.0848007202148</v>
+        <v>42.0847930908203</v>
       </c>
       <c r="H520" t="n">
         <v>21408</v>
@@ -15507,7 +15507,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>41.6213493347168</v>
+        <v>41.6213455200195</v>
       </c>
       <c r="H522" t="n">
         <v>37738</v>
@@ -15565,7 +15565,7 @@
         <v>46.8600006103516</v>
       </c>
       <c r="G524" t="n">
-        <v>41.7639465332031</v>
+        <v>41.7639503479004</v>
       </c>
       <c r="H524" t="n">
         <v>22587</v>
@@ -15594,7 +15594,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G525" t="n">
-        <v>42.0848007202148</v>
+        <v>42.0847930908203</v>
       </c>
       <c r="H525" t="n">
         <v>27575</v>
@@ -15710,7 +15710,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>41.5322227478027</v>
+        <v>41.5322151184082</v>
       </c>
       <c r="H529" t="n">
         <v>36997</v>
@@ -15768,7 +15768,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G531" t="n">
-        <v>41.3539733886719</v>
+        <v>41.3539695739746</v>
       </c>
       <c r="H531" t="n">
         <v>26139</v>
@@ -15826,7 +15826,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G533" t="n">
-        <v>40.3557739257812</v>
+        <v>40.3557777404785</v>
       </c>
       <c r="H533" t="n">
         <v>51912</v>
@@ -15884,7 +15884,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G535" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H535" t="n">
         <v>40370</v>
@@ -15913,7 +15913,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G536" t="n">
-        <v>39.143669128418</v>
+        <v>39.1436729431152</v>
       </c>
       <c r="H536" t="n">
         <v>97085</v>
@@ -15942,7 +15942,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784210205078</v>
+        <v>39.6784286499023</v>
       </c>
       <c r="H537" t="n">
         <v>153620</v>
@@ -15971,7 +15971,7 @@
         <v>48</v>
       </c>
       <c r="G538" t="n">
-        <v>42.779972076416</v>
+        <v>42.7799682617188</v>
       </c>
       <c r="H538" t="n">
         <v>151081</v>
@@ -16029,7 +16029,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>38.6802253723145</v>
+        <v>38.6802291870117</v>
       </c>
       <c r="H540" t="n">
         <v>153076</v>
@@ -16087,7 +16087,7 @@
         <v>41.8400001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>37.2898750305176</v>
+        <v>37.2898788452148</v>
       </c>
       <c r="H542" t="n">
         <v>58757</v>
@@ -16116,7 +16116,7 @@
         <v>43.2599983215332</v>
       </c>
       <c r="G543" t="n">
-        <v>38.5554504394531</v>
+        <v>38.5554542541504</v>
       </c>
       <c r="H543" t="n">
         <v>52756</v>
@@ -16232,7 +16232,7 @@
         <v>45.5200004577637</v>
       </c>
       <c r="G547" t="n">
-        <v>40.5696716308594</v>
+        <v>40.5696754455566</v>
       </c>
       <c r="H547" t="n">
         <v>75371</v>
@@ -16290,7 +16290,7 @@
         <v>45.939998626709</v>
       </c>
       <c r="G549" t="n">
-        <v>40.9440002441406</v>
+        <v>40.9439964294434</v>
       </c>
       <c r="H549" t="n">
         <v>33774</v>
@@ -16348,7 +16348,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400756835938</v>
+        <v>41.1400718688965</v>
       </c>
       <c r="H551" t="n">
         <v>31765</v>
@@ -16406,7 +16406,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G553" t="n">
-        <v>40.5161933898926</v>
+        <v>40.5161972045898</v>
       </c>
       <c r="H553" t="n">
         <v>34881</v>
@@ -16435,7 +16435,7 @@
         <v>45.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>40.9618225097656</v>
+        <v>40.9618186950684</v>
       </c>
       <c r="H554" t="n">
         <v>94078</v>
@@ -16464,7 +16464,7 @@
         <v>44.0400009155273</v>
       </c>
       <c r="G555" t="n">
-        <v>39.2506217956543</v>
+        <v>39.2506294250488</v>
       </c>
       <c r="H555" t="n">
         <v>114926</v>
@@ -16493,7 +16493,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793212890625</v>
+        <v>39.1793251037598</v>
       </c>
       <c r="H556" t="n">
         <v>64193</v>
@@ -16522,7 +16522,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131729125977</v>
+        <v>40.2131767272949</v>
       </c>
       <c r="H557" t="n">
         <v>48880</v>
@@ -16551,7 +16551,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914222717285</v>
+        <v>40.3914260864258</v>
       </c>
       <c r="H558" t="n">
         <v>72029</v>
@@ -16609,7 +16609,7 @@
         <v>46.439998626709</v>
       </c>
       <c r="G560" t="n">
-        <v>41.3896255493164</v>
+        <v>41.3896217346191</v>
       </c>
       <c r="H560" t="n">
         <v>94283</v>
@@ -16638,7 +16638,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G561" t="n">
-        <v>42.6017265319824</v>
+        <v>42.6017189025879</v>
       </c>
       <c r="H561" t="n">
         <v>139514</v>
@@ -16725,7 +16725,7 @@
         <v>50.75</v>
       </c>
       <c r="G564" t="n">
-        <v>45.2309112548828</v>
+        <v>45.2309074401855</v>
       </c>
       <c r="H564" t="n">
         <v>99680</v>
@@ -16754,7 +16754,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G565" t="n">
-        <v>43.8851280212402</v>
+        <v>43.8851203918457</v>
       </c>
       <c r="H565" t="n">
         <v>305117</v>
@@ -16783,7 +16783,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>44.9635353088379</v>
+        <v>44.9635314941406</v>
       </c>
       <c r="H566" t="n">
         <v>112572</v>
@@ -16812,7 +16812,7 @@
         <v>51.6500015258789</v>
       </c>
       <c r="G567" t="n">
-        <v>46.0330390930176</v>
+        <v>46.0330352783203</v>
       </c>
       <c r="H567" t="n">
         <v>142610</v>
@@ -16870,7 +16870,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>45.943904876709</v>
+        <v>45.9439125061035</v>
       </c>
       <c r="H569" t="n">
         <v>178635</v>
@@ -16899,7 +16899,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874061584473</v>
+        <v>45.5874099731445</v>
       </c>
       <c r="H570" t="n">
         <v>120878</v>
@@ -16928,7 +16928,7 @@
         <v>50.1500015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>44.696159362793</v>
+        <v>44.6961631774902</v>
       </c>
       <c r="H571" t="n">
         <v>63427</v>
@@ -17044,7 +17044,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>42.655200958252</v>
+        <v>42.6551971435547</v>
       </c>
       <c r="H575" t="n">
         <v>111110</v>
@@ -17073,7 +17073,7 @@
         <v>46.5200004577637</v>
       </c>
       <c r="G576" t="n">
-        <v>41.4609222412109</v>
+        <v>41.4609260559082</v>
       </c>
       <c r="H576" t="n">
         <v>100832</v>
@@ -17131,7 +17131,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>41.175724029541</v>
+        <v>41.1757202148438</v>
       </c>
       <c r="H578" t="n">
         <v>78204</v>
@@ -17160,7 +17160,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G579" t="n">
-        <v>41.1578979492188</v>
+        <v>41.1578941345215</v>
       </c>
       <c r="H579" t="n">
         <v>52237</v>
@@ -17189,7 +17189,7 @@
         <v>46.0200004577637</v>
       </c>
       <c r="G580" t="n">
-        <v>41.0152931213379</v>
+        <v>41.0152969360352</v>
       </c>
       <c r="H580" t="n">
         <v>49188</v>
@@ -17218,7 +17218,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675514221191</v>
+        <v>39.7675476074219</v>
       </c>
       <c r="H581" t="n">
         <v>81341</v>
@@ -17247,7 +17247,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G582" t="n">
-        <v>39.8031959533691</v>
+        <v>39.8031997680664</v>
       </c>
       <c r="H582" t="n">
         <v>46802</v>
@@ -17276,7 +17276,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.108024597168</v>
+        <v>39.1080284118652</v>
       </c>
       <c r="H583" t="n">
         <v>48182</v>
@@ -17305,7 +17305,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479209899902</v>
       </c>
       <c r="H584" t="n">
         <v>83788</v>
@@ -17334,7 +17334,7 @@
         <v>44.6399993896484</v>
       </c>
       <c r="G585" t="n">
-        <v>39.7853736877441</v>
+        <v>39.7853775024414</v>
       </c>
       <c r="H585" t="n">
         <v>69470</v>
@@ -17363,7 +17363,7 @@
         <v>45.5</v>
       </c>
       <c r="G586" t="n">
-        <v>40.5518531799316</v>
+        <v>40.5518493652344</v>
       </c>
       <c r="H586" t="n">
         <v>51926</v>
@@ -17392,7 +17392,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7318954467773</v>
+        <v>39.7319030761719</v>
       </c>
       <c r="H587" t="n">
         <v>42227</v>
@@ -17421,7 +17421,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3040962219238</v>
+        <v>39.3041000366211</v>
       </c>
       <c r="H588" t="n">
         <v>50438</v>
@@ -17450,7 +17450,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675514221191</v>
+        <v>39.7675476074219</v>
       </c>
       <c r="H589" t="n">
         <v>23775</v>
@@ -17479,7 +17479,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488288879395</v>
+        <v>40.2488250732422</v>
       </c>
       <c r="H590" t="n">
         <v>41714</v>
@@ -17508,7 +17508,7 @@
         <v>44.7799987792969</v>
       </c>
       <c r="G591" t="n">
-        <v>39.9101448059082</v>
+        <v>39.9101486206055</v>
       </c>
       <c r="H591" t="n">
         <v>42778</v>
@@ -17537,7 +17537,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G592" t="n">
-        <v>39.4288749694824</v>
+        <v>39.4288787841797</v>
       </c>
       <c r="H592" t="n">
         <v>40222</v>
@@ -17566,7 +17566,7 @@
         <v>43.9199981689453</v>
       </c>
       <c r="G593" t="n">
-        <v>39.143669128418</v>
+        <v>39.1436729431152</v>
       </c>
       <c r="H593" t="n">
         <v>46759</v>
@@ -17595,7 +17595,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>39.0367202758789</v>
+        <v>39.0367240905762</v>
       </c>
       <c r="H594" t="n">
         <v>36577</v>
@@ -17624,7 +17624,7 @@
         <v>47.560001373291</v>
       </c>
       <c r="G595" t="n">
-        <v>42.387825012207</v>
+        <v>42.3878211975098</v>
       </c>
       <c r="H595" t="n">
         <v>180787</v>
@@ -17653,7 +17653,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479248046875</v>
+        <v>40.7479209899902</v>
       </c>
       <c r="H596" t="n">
         <v>103803</v>
@@ -17682,7 +17682,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.050952911377</v>
+        <v>41.0509452819824</v>
       </c>
       <c r="H597" t="n">
         <v>57439</v>
@@ -17740,7 +17740,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G599" t="n">
-        <v>41.0149230957031</v>
+        <v>41.0149269104004</v>
       </c>
       <c r="H599" t="n">
         <v>48985</v>
@@ -17769,7 +17769,7 @@
         <v>45.2000007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>40.7087059020996</v>
+        <v>40.7087097167969</v>
       </c>
       <c r="H600" t="n">
         <v>23543</v>
@@ -17798,7 +17798,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G601" t="n">
-        <v>40.6366539001465</v>
+        <v>40.6366577148438</v>
       </c>
       <c r="H601" t="n">
         <v>31298</v>
@@ -17856,7 +17856,7 @@
         <v>44.2400016784668</v>
       </c>
       <c r="G603" t="n">
-        <v>39.8440971374512</v>
+        <v>39.8441009521484</v>
       </c>
       <c r="H603" t="n">
         <v>60714</v>
@@ -17914,7 +17914,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.484432220459</v>
+        <v>37.4844360351562</v>
       </c>
       <c r="H605" t="n">
         <v>87797</v>
@@ -17943,7 +17943,7 @@
         <v>40.3400001525879</v>
       </c>
       <c r="G606" t="n">
-        <v>36.3316230773926</v>
+        <v>36.3316192626953</v>
       </c>
       <c r="H606" t="n">
         <v>66466</v>
@@ -18059,7 +18059,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.0073890686035</v>
+        <v>36.007396697998</v>
       </c>
       <c r="H610" t="n">
         <v>71270</v>
@@ -18146,7 +18146,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241401672363</v>
+        <v>34.2241363525391</v>
       </c>
       <c r="H613" t="n">
         <v>88495</v>
@@ -18175,7 +18175,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>33.4135627746582</v>
+        <v>33.4135589599609</v>
       </c>
       <c r="H614" t="n">
         <v>159133</v>
@@ -18291,7 +18291,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924629211426</v>
+        <v>34.6924705505371</v>
       </c>
       <c r="H618" t="n">
         <v>73867</v>
@@ -18349,7 +18349,7 @@
         <v>38.560001373291</v>
       </c>
       <c r="G620" t="n">
-        <v>34.7284927368164</v>
+        <v>34.7284889221191</v>
       </c>
       <c r="H620" t="n">
         <v>62523</v>
@@ -18436,7 +18436,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241401672363</v>
+        <v>34.2241363525391</v>
       </c>
       <c r="H623" t="n">
         <v>21903</v>
@@ -18552,7 +18552,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247711181641</v>
+        <v>35.1247749328613</v>
       </c>
       <c r="H627" t="n">
         <v>103614</v>
@@ -18581,7 +18581,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>33.5036239624023</v>
+        <v>33.5036315917969</v>
       </c>
       <c r="H628" t="n">
         <v>53029</v>
@@ -18610,7 +18610,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.4048500061035</v>
+        <v>32.404857635498</v>
       </c>
       <c r="H629" t="n">
         <v>77422</v>
@@ -18639,7 +18639,7 @@
         <v>35.9599990844727</v>
       </c>
       <c r="G630" t="n">
-        <v>32.3868370056152</v>
+        <v>32.3868408203125</v>
       </c>
       <c r="H630" t="n">
         <v>57634</v>
@@ -18668,7 +18668,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G631" t="n">
-        <v>31.468189239502</v>
+        <v>31.4681930541992</v>
       </c>
       <c r="H631" t="n">
         <v>192630</v>
@@ -18755,7 +18755,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.4867935180664</v>
+        <v>29.486795425415</v>
       </c>
       <c r="H634" t="n">
         <v>160938</v>
@@ -18784,7 +18784,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371166229248</v>
+        <v>29.9371147155762</v>
       </c>
       <c r="H635" t="n">
         <v>311338</v>
@@ -18813,7 +18813,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G636" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H636" t="n">
         <v>86489</v>
@@ -18842,7 +18842,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.153263092041</v>
+        <v>30.1532669067383</v>
       </c>
       <c r="H637" t="n">
         <v>47812</v>
@@ -18900,7 +18900,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147415161133</v>
+        <v>29.4147434234619</v>
       </c>
       <c r="H639" t="n">
         <v>66878</v>
@@ -18958,7 +18958,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G641" t="n">
-        <v>29.1265392303467</v>
+        <v>29.1265411376953</v>
       </c>
       <c r="H641" t="n">
         <v>126609</v>
@@ -19016,7 +19016,7 @@
         <v>33.9799995422363</v>
       </c>
       <c r="G643" t="n">
-        <v>30.6035804748535</v>
+        <v>30.6035842895508</v>
       </c>
       <c r="H643" t="n">
         <v>77878</v>
@@ -19045,7 +19045,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520408630371</v>
+        <v>31.2520427703857</v>
       </c>
       <c r="H644" t="n">
         <v>161628</v>
@@ -19074,7 +19074,7 @@
         <v>32.9199981689453</v>
       </c>
       <c r="G645" t="n">
-        <v>29.6489067077637</v>
+        <v>29.6489086151123</v>
       </c>
       <c r="H645" t="n">
         <v>97694</v>
@@ -19103,7 +19103,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551239013672</v>
+        <v>29.9551219940186</v>
       </c>
       <c r="H646" t="n">
         <v>48258</v>
@@ -19132,7 +19132,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172351837158</v>
+        <v>30.1172389984131</v>
       </c>
       <c r="H647" t="n">
         <v>44619</v>
@@ -19161,7 +19161,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054374694824</v>
+        <v>30.4054412841797</v>
       </c>
       <c r="H648" t="n">
         <v>33638</v>
@@ -19248,7 +19248,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>31.6483211517334</v>
+        <v>31.6483154296875</v>
       </c>
       <c r="H651" t="n">
         <v>95229</v>
@@ -19277,7 +19277,7 @@
         <v>35.6199989318848</v>
       </c>
       <c r="G652" t="n">
-        <v>32.080623626709</v>
+        <v>32.0806198120117</v>
       </c>
       <c r="H652" t="n">
         <v>85998</v>
@@ -19306,7 +19306,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>31.1079387664795</v>
+        <v>31.1079368591309</v>
       </c>
       <c r="H653" t="n">
         <v>70388</v>
@@ -19335,7 +19335,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601169586182</v>
+        <v>31.3601131439209</v>
       </c>
       <c r="H654" t="n">
         <v>42779</v>
@@ -19393,7 +19393,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G656" t="n">
-        <v>31.7383842468262</v>
+        <v>31.7383861541748</v>
       </c>
       <c r="H656" t="n">
         <v>58243</v>
@@ -19422,7 +19422,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520408630371</v>
+        <v>31.2520427703857</v>
       </c>
       <c r="H657" t="n">
         <v>35703</v>
@@ -19451,7 +19451,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122875213623</v>
+        <v>31.6122894287109</v>
       </c>
       <c r="H658" t="n">
         <v>29583</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.901086807251</v>
+        <v>29.9010887145996</v>
       </c>
       <c r="H662" t="n">
         <v>24019</v>
@@ -19596,7 +19596,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G663" t="n">
-        <v>29.2346172332764</v>
+        <v>29.2346153259277</v>
       </c>
       <c r="H663" t="n">
         <v>57598</v>
@@ -19625,7 +19625,7 @@
         <v>32.939998626709</v>
       </c>
       <c r="G664" t="n">
-        <v>29.6669216156006</v>
+        <v>29.666919708252</v>
       </c>
       <c r="H664" t="n">
         <v>25106</v>
@@ -19654,7 +19654,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>29.0905151367188</v>
+        <v>29.0905132293701</v>
       </c>
       <c r="H665" t="n">
         <v>24107</v>
@@ -19683,7 +19683,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>28.730260848999</v>
+        <v>28.7302627563477</v>
       </c>
       <c r="H666" t="n">
         <v>17220</v>
@@ -19770,7 +19770,7 @@
         <v>29.5799999237061</v>
       </c>
       <c r="G669" t="n">
-        <v>26.6407890319824</v>
+        <v>26.6407871246338</v>
       </c>
       <c r="H669" t="n">
         <v>54672</v>
@@ -19828,7 +19828,7 @@
         <v>28.9200000762939</v>
       </c>
       <c r="G671" t="n">
-        <v>26.0463695526123</v>
+        <v>26.0463676452637</v>
       </c>
       <c r="H671" t="n">
         <v>28977</v>
@@ -19857,7 +19857,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G672" t="n">
-        <v>26.5146980285645</v>
+        <v>26.5146999359131</v>
       </c>
       <c r="H672" t="n">
         <v>22536</v>
@@ -19915,7 +19915,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.0550804138184</v>
+        <v>27.055082321167</v>
       </c>
       <c r="H674" t="n">
         <v>59352</v>
@@ -20060,7 +20060,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693717956543</v>
+        <v>27.4693698883057</v>
       </c>
       <c r="H679" t="n">
         <v>30485</v>
@@ -20089,7 +20089,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196872711182</v>
       </c>
       <c r="H680" t="n">
         <v>46685</v>
@@ -20118,7 +20118,7 @@
         <v>30.6200008392334</v>
       </c>
       <c r="G681" t="n">
-        <v>27.5774478912354</v>
+        <v>27.577449798584</v>
       </c>
       <c r="H681" t="n">
         <v>43724</v>
@@ -20147,7 +20147,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G682" t="n">
-        <v>27.9377021789551</v>
+        <v>27.9377002716064</v>
       </c>
       <c r="H682" t="n">
         <v>34366</v>
@@ -20205,7 +20205,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476409912109</v>
+        <v>27.8476390838623</v>
       </c>
       <c r="H684" t="n">
         <v>50842</v>
@@ -20234,7 +20234,7 @@
         <v>30.8600006103516</v>
       </c>
       <c r="G685" t="n">
-        <v>27.7936000823975</v>
+        <v>27.7936019897461</v>
       </c>
       <c r="H685" t="n">
         <v>35760</v>
@@ -20263,7 +20263,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693717956543</v>
+        <v>27.4693698883057</v>
       </c>
       <c r="H686" t="n">
         <v>52867</v>
@@ -20321,7 +20321,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>28.0097522735596</v>
+        <v>28.0097541809082</v>
       </c>
       <c r="H688" t="n">
         <v>31923</v>
@@ -20379,7 +20379,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>28.0097522735596</v>
+        <v>28.0097541809082</v>
       </c>
       <c r="H690" t="n">
         <v>44005</v>
@@ -20437,7 +20437,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>28.730260848999</v>
+        <v>28.7302627563477</v>
       </c>
       <c r="H692" t="n">
         <v>50743</v>
@@ -20466,7 +20466,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G693" t="n">
-        <v>28.5501327514648</v>
+        <v>28.5501346588135</v>
       </c>
       <c r="H693" t="n">
         <v>27520</v>
@@ -20495,7 +20495,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>29.1805820465088</v>
+        <v>29.1805801391602</v>
       </c>
       <c r="H694" t="n">
         <v>37376</v>
@@ -20582,7 +20582,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401977539062</v>
+        <v>28.6401958465576</v>
       </c>
       <c r="H697" t="n">
         <v>27160</v>
@@ -20611,7 +20611,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762218475342</v>
+        <v>28.6762237548828</v>
       </c>
       <c r="H698" t="n">
         <v>35302</v>
@@ -20669,7 +20669,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.0550804138184</v>
+        <v>27.055082321167</v>
       </c>
       <c r="H700" t="n">
         <v>32431</v>
@@ -20727,7 +20727,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196872711182</v>
       </c>
       <c r="H702" t="n">
         <v>26734</v>
@@ -20756,7 +20756,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G703" t="n">
-        <v>27.4513607025146</v>
+        <v>27.451358795166</v>
       </c>
       <c r="H703" t="n">
         <v>119469</v>
@@ -20785,7 +20785,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196891784668</v>
+        <v>27.9196872711182</v>
       </c>
       <c r="H704" t="n">
         <v>37755</v>
@@ -20843,7 +20843,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>25.7581653594971</v>
+        <v>25.7581634521484</v>
       </c>
       <c r="H706" t="n">
         <v>55195</v>
@@ -20872,7 +20872,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320308685303</v>
+        <v>22.7320289611816</v>
       </c>
       <c r="H707" t="n">
         <v>196682</v>
@@ -20930,7 +20930,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233200073242</v>
+        <v>21.7233219146729</v>
       </c>
       <c r="H709" t="n">
         <v>130761</v>
@@ -21017,7 +21017,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G712" t="n">
-        <v>23.7047157287598</v>
+        <v>23.7047176361084</v>
       </c>
       <c r="H712" t="n">
         <v>61152</v>
@@ -21046,7 +21046,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G713" t="n">
-        <v>23.5606174468994</v>
+        <v>23.5606136322021</v>
       </c>
       <c r="H713" t="n">
         <v>38427</v>
@@ -21191,7 +21191,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G718" t="n">
-        <v>20.8226852416992</v>
+        <v>20.8226871490479</v>
       </c>
       <c r="H718" t="n">
         <v>40533</v>
@@ -21278,7 +21278,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.3450546264648</v>
+        <v>21.3450527191162</v>
       </c>
       <c r="H721" t="n">
         <v>38719</v>
@@ -21307,7 +21307,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>21.5972309112549</v>
+        <v>21.5972290039062</v>
       </c>
       <c r="H722" t="n">
         <v>28389</v>
@@ -21336,7 +21336,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G723" t="n">
-        <v>19.7239074707031</v>
+        <v>19.7239093780518</v>
       </c>
       <c r="H723" t="n">
         <v>114037</v>
@@ -21452,7 +21452,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.8773136138916</v>
+        <v>18.8773097991943</v>
       </c>
       <c r="H727" t="n">
         <v>78461</v>
@@ -21481,7 +21481,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G728" t="n">
-        <v>18.3909683227539</v>
+        <v>18.3909702301025</v>
       </c>
       <c r="H728" t="n">
         <v>70249</v>
@@ -21510,7 +21510,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G729" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H729" t="n">
         <v>46125</v>
@@ -21568,7 +21568,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.0036945343018</v>
+        <v>18.003698348999</v>
       </c>
       <c r="H731" t="n">
         <v>90396</v>
@@ -21597,7 +21597,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G732" t="n">
-        <v>17.139087677002</v>
+        <v>17.1390857696533</v>
       </c>
       <c r="H732" t="n">
         <v>49459</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120700836182</v>
+        <v>17.1120681762695</v>
       </c>
       <c r="H733" t="n">
         <v>71224</v>
@@ -21713,7 +21713,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.2024250030518</v>
+        <v>16.202428817749</v>
       </c>
       <c r="H736" t="n">
         <v>53336</v>
@@ -21742,7 +21742,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.9502458572388</v>
+        <v>15.950249671936</v>
       </c>
       <c r="H737" t="n">
         <v>57508</v>
@@ -21771,7 +21771,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.7160844802856</v>
+        <v>15.7160806655884</v>
       </c>
       <c r="H738" t="n">
         <v>81701</v>
@@ -21800,7 +21800,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800565719604</v>
       </c>
       <c r="H739" t="n">
         <v>56603</v>
@@ -21829,7 +21829,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G740" t="n">
-        <v>15.6170148849487</v>
+        <v>15.6170139312744</v>
       </c>
       <c r="H740" t="n">
         <v>28241</v>
@@ -21858,7 +21858,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G741" t="n">
-        <v>16.1573925018311</v>
+        <v>16.1573944091797</v>
       </c>
       <c r="H741" t="n">
         <v>30250</v>
@@ -21887,7 +21887,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077117919922</v>
+        <v>16.6077136993408</v>
       </c>
       <c r="H742" t="n">
         <v>126448</v>
@@ -21916,7 +21916,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G743" t="n">
-        <v>16.4005641937256</v>
+        <v>16.4005661010742</v>
       </c>
       <c r="H743" t="n">
         <v>110085</v>
@@ -21945,7 +21945,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>17.4723224639893</v>
+        <v>17.4723205566406</v>
       </c>
       <c r="H744" t="n">
         <v>93088</v>
@@ -22003,7 +22003,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G746" t="n">
-        <v>16.4906272888184</v>
+        <v>16.490629196167</v>
       </c>
       <c r="H746" t="n">
         <v>97703</v>
@@ -22032,7 +22032,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G747" t="n">
-        <v>17.9406490325928</v>
+        <v>17.9406509399414</v>
       </c>
       <c r="H747" t="n">
         <v>117827</v>
@@ -22090,7 +22090,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G749" t="n">
-        <v>17.6614551544189</v>
+        <v>17.6614570617676</v>
       </c>
       <c r="H749" t="n">
         <v>103574</v>
@@ -22148,7 +22148,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G751" t="n">
-        <v>16.4906272888184</v>
+        <v>16.490629196167</v>
       </c>
       <c r="H751" t="n">
         <v>70987</v>
@@ -22206,7 +22206,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G753" t="n">
-        <v>15.905216217041</v>
+        <v>15.9052171707153</v>
       </c>
       <c r="H753" t="n">
         <v>55986</v>
@@ -22235,7 +22235,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G754" t="n">
-        <v>16.2654705047607</v>
+        <v>16.2654685974121</v>
       </c>
       <c r="H754" t="n">
         <v>85504</v>
@@ -22264,7 +22264,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G755" t="n">
-        <v>16.1934185028076</v>
+        <v>16.1934204101562</v>
       </c>
       <c r="H755" t="n">
         <v>54198</v>
@@ -22293,7 +22293,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250881195068</v>
+        <v>15.7250890731812</v>
       </c>
       <c r="H756" t="n">
         <v>68222</v>
@@ -22322,7 +22322,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G757" t="n">
-        <v>15.4008617401123</v>
+        <v>15.4008626937866</v>
       </c>
       <c r="H757" t="n">
         <v>46935</v>
@@ -22351,7 +22351,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496129989624</v>
+        <v>15.0496139526367</v>
       </c>
       <c r="H758" t="n">
         <v>39650</v>
@@ -22380,7 +22380,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800584793091</v>
+        <v>15.6800565719604</v>
       </c>
       <c r="H759" t="n">
         <v>53012</v>
@@ -22438,7 +22438,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899934768677</v>
+        <v>15.5899925231934</v>
       </c>
       <c r="H761" t="n">
         <v>79930</v>
@@ -22467,7 +22467,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G762" t="n">
-        <v>15.1486825942993</v>
+        <v>15.1486835479736</v>
       </c>
       <c r="H762" t="n">
         <v>108666</v>
@@ -22496,7 +22496,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639053344727</v>
+        <v>15.4639024734497</v>
       </c>
       <c r="H763" t="n">
         <v>62260</v>
@@ -22583,7 +22583,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568050384521</v>
       </c>
       <c r="H766" t="n">
         <v>115896</v>
@@ -22641,7 +22641,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.3912658691406</v>
+        <v>17.3912620544434</v>
       </c>
       <c r="H768" t="n">
         <v>73850</v>
@@ -22728,7 +22728,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G771" t="n">
-        <v>18.228853225708</v>
+        <v>18.2288551330566</v>
       </c>
       <c r="H771" t="n">
         <v>74008</v>
@@ -22757,7 +22757,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G772" t="n">
-        <v>18.0307159423828</v>
+        <v>18.0307178497314</v>
       </c>
       <c r="H772" t="n">
         <v>42586</v>
@@ -22844,7 +22844,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.4543113708496</v>
+        <v>17.4543075561523</v>
       </c>
       <c r="H775" t="n">
         <v>38968</v>
@@ -22902,7 +22902,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G777" t="n">
-        <v>18.8052635192871</v>
+        <v>18.8052616119385</v>
       </c>
       <c r="H777" t="n">
         <v>56710</v>
@@ -22960,7 +22960,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G779" t="n">
-        <v>18.3369312286377</v>
+        <v>18.3369331359863</v>
       </c>
       <c r="H779" t="n">
         <v>51138</v>
@@ -23018,7 +23018,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H781" t="n">
         <v>52065</v>
@@ -23105,7 +23105,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G784" t="n">
-        <v>18.6971855163574</v>
+        <v>18.6971874237061</v>
       </c>
       <c r="H784" t="n">
         <v>38581</v>
@@ -23250,7 +23250,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>19.0034027099609</v>
+        <v>19.0034008026123</v>
       </c>
       <c r="H789" t="n">
         <v>81539</v>
@@ -23279,7 +23279,7 @@
         <v>19.9699993133545</v>
       </c>
       <c r="G790" t="n">
-        <v>17.9856834411621</v>
+        <v>17.9856815338135</v>
       </c>
       <c r="H790" t="n">
         <v>73749</v>
@@ -23308,7 +23308,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>17.3552417755127</v>
+        <v>17.3552398681641</v>
       </c>
       <c r="H791" t="n">
         <v>65355</v>
@@ -23395,7 +23395,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G794" t="n">
-        <v>18.6071224212646</v>
+        <v>18.607120513916</v>
       </c>
       <c r="H794" t="n">
         <v>106399</v>
@@ -23453,7 +23453,7 @@
         <v>21.8400001525879</v>
       </c>
       <c r="G796" t="n">
-        <v>19.6698703765869</v>
+        <v>19.6698722839355</v>
       </c>
       <c r="H796" t="n">
         <v>111608</v>
@@ -23482,7 +23482,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>20.2462787628174</v>
+        <v>20.2462749481201</v>
       </c>
       <c r="H797" t="n">
         <v>77155</v>
@@ -23540,7 +23540,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G799" t="n">
-        <v>19.9220485687256</v>
+        <v>19.9220504760742</v>
       </c>
       <c r="H799" t="n">
         <v>43219</v>
@@ -23598,7 +23598,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G801" t="n">
-        <v>19.4537220001221</v>
+        <v>19.4537200927734</v>
       </c>
       <c r="H801" t="n">
         <v>38620</v>
@@ -23685,7 +23685,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>17.7515201568604</v>
+        <v>17.7515163421631</v>
       </c>
       <c r="H804" t="n">
         <v>362073</v>
@@ -23772,7 +23772,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>17.7965488433838</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H807" t="n">
         <v>48825</v>
@@ -23801,7 +23801,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G808" t="n">
-        <v>17.5083484649658</v>
+        <v>17.5083446502686</v>
       </c>
       <c r="H808" t="n">
         <v>79412</v>
@@ -23859,7 +23859,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508815765381</v>
+        <v>16.8508834838867</v>
       </c>
       <c r="H810" t="n">
         <v>142958</v>
@@ -23888,7 +23888,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G811" t="n">
-        <v>16.9859771728516</v>
+        <v>16.9859790802002</v>
       </c>
       <c r="H811" t="n">
         <v>69819</v>
@@ -23946,7 +23946,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120700836182</v>
+        <v>17.1120681762695</v>
       </c>
       <c r="H813" t="n">
         <v>36891</v>
@@ -23975,7 +23975,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490207672119</v>
+        <v>17.0490226745605</v>
       </c>
       <c r="H814" t="n">
         <v>19771</v>
@@ -24033,7 +24033,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462314605713</v>
+        <v>17.3462352752686</v>
       </c>
       <c r="H816" t="n">
         <v>103910</v>
@@ -24178,7 +24178,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G821" t="n">
-        <v>17.976676940918</v>
+        <v>17.9766750335693</v>
       </c>
       <c r="H821" t="n">
         <v>368484</v>
@@ -24236,7 +24236,7 @@
         <v>19.5599994659424</v>
       </c>
       <c r="G823" t="n">
-        <v>17.6164245605469</v>
+        <v>17.6164226531982</v>
       </c>
       <c r="H823" t="n">
         <v>44316</v>
@@ -24265,7 +24265,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6614551544189</v>
+        <v>17.6614570617676</v>
       </c>
       <c r="H824" t="n">
         <v>72694</v>
@@ -24323,7 +24323,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.4543113708496</v>
+        <v>17.4543075561523</v>
       </c>
       <c r="H826" t="n">
         <v>48981</v>
@@ -24381,7 +24381,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G828" t="n">
-        <v>17.9136333465576</v>
+        <v>17.913631439209</v>
       </c>
       <c r="H828" t="n">
         <v>52651</v>
@@ -24468,7 +24468,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1928291320801</v>
+        <v>18.1928272247314</v>
       </c>
       <c r="H831" t="n">
         <v>225382</v>
@@ -24497,7 +24497,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G832" t="n">
-        <v>17.9496593475342</v>
+        <v>17.9496574401855</v>
       </c>
       <c r="H832" t="n">
         <v>46935</v>
@@ -24584,7 +24584,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G835" t="n">
-        <v>17.1300792694092</v>
+        <v>17.1300811767578</v>
       </c>
       <c r="H835" t="n">
         <v>63235</v>
@@ -24642,7 +24642,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676723480225</v>
+        <v>17.9676704406738</v>
       </c>
       <c r="H837" t="n">
         <v>49207</v>
@@ -24700,7 +24700,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G839" t="n">
-        <v>18.0667419433594</v>
+        <v>18.0667400360107</v>
       </c>
       <c r="H839" t="n">
         <v>64387</v>
@@ -24758,7 +24758,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G841" t="n">
-        <v>17.7965488433838</v>
+        <v>17.7965507507324</v>
       </c>
       <c r="H841" t="n">
         <v>59761</v>
@@ -24816,7 +24816,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6074180603027</v>
+        <v>17.6074161529541</v>
       </c>
       <c r="H843" t="n">
         <v>31630</v>
@@ -24845,7 +24845,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G844" t="n">
-        <v>17.5894050598145</v>
+        <v>17.5894069671631</v>
       </c>
       <c r="H844" t="n">
         <v>44622</v>
@@ -24874,7 +24874,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G845" t="n">
-        <v>17.76953125</v>
+        <v>17.7695331573486</v>
       </c>
       <c r="H845" t="n">
         <v>67664</v>
@@ -24932,7 +24932,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568031311035</v>
+        <v>18.1568050384521</v>
       </c>
       <c r="H847" t="n">
         <v>58676</v>
@@ -24961,7 +24961,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>18.6365585327148</v>
+        <v>18.6365566253662</v>
       </c>
       <c r="H848" t="n">
         <v>152183</v>
@@ -24990,7 +24990,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G849" t="n">
-        <v>17.24342918396</v>
+        <v>17.2434272766113</v>
       </c>
       <c r="H849" t="n">
         <v>303530</v>
@@ -25048,7 +25048,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G851" t="n">
-        <v>17.2249774932861</v>
+        <v>17.2249755859375</v>
       </c>
       <c r="H851" t="n">
         <v>61198</v>
@@ -25106,7 +25106,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>16.1916618347168</v>
+        <v>16.1916599273682</v>
       </c>
       <c r="H853" t="n">
         <v>63194</v>
@@ -25135,7 +25135,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.684232711792</v>
+        <v>15.6842317581177</v>
       </c>
       <c r="H854" t="n">
         <v>96763</v>
@@ -25193,7 +25193,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021240234375</v>
+        <v>13.8021230697632</v>
       </c>
       <c r="H856" t="n">
         <v>215640</v>
@@ -25222,7 +25222,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G857" t="n">
-        <v>13.9405145645142</v>
+        <v>13.9405136108398</v>
       </c>
       <c r="H857" t="n">
         <v>212931</v>
@@ -25280,7 +25280,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>13.3131456375122</v>
+        <v>13.3131446838379</v>
       </c>
       <c r="H859" t="n">
         <v>77696</v>
@@ -25338,7 +25338,7 @@
         <v>15</v>
       </c>
       <c r="G861" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H861" t="n">
         <v>78115</v>
@@ -25367,7 +25367,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G862" t="n">
-        <v>13.4792137145996</v>
+        <v>13.4792127609253</v>
       </c>
       <c r="H862" t="n">
         <v>74086</v>
@@ -25541,7 +25541,7 @@
         <v>14.5</v>
       </c>
       <c r="G868" t="n">
-        <v>13.3777265548706</v>
+        <v>13.3777275085449</v>
       </c>
       <c r="H868" t="n">
         <v>91736</v>
@@ -25570,7 +25570,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009464263916</v>
+        <v>13.1009454727173</v>
       </c>
       <c r="H869" t="n">
         <v>110683</v>
@@ -25657,7 +25657,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G872" t="n">
-        <v>13.7006378173828</v>
+        <v>13.7006387710571</v>
       </c>
       <c r="H872" t="n">
         <v>150643</v>
@@ -25686,7 +25686,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G873" t="n">
-        <v>14.475622177124</v>
+        <v>14.4756231307983</v>
       </c>
       <c r="H873" t="n">
         <v>197201</v>
@@ -25860,7 +25860,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G879" t="n">
-        <v>13.6914110183716</v>
+        <v>13.6914129257202</v>
       </c>
       <c r="H879" t="n">
         <v>39249</v>
@@ -25889,7 +25889,7 @@
         <v>15</v>
       </c>
       <c r="G880" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H880" t="n">
         <v>70407</v>
@@ -25947,7 +25947,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.5125274658203</v>
+        <v>14.512526512146</v>
       </c>
       <c r="H882" t="n">
         <v>171512</v>
@@ -26063,7 +26063,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486215591431</v>
       </c>
       <c r="H886" t="n">
         <v>520891</v>
@@ -26121,7 +26121,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G888" t="n">
-        <v>10.4069480895996</v>
+        <v>10.4069490432739</v>
       </c>
       <c r="H888" t="n">
         <v>237022</v>
@@ -26179,7 +26179,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G890" t="n">
-        <v>10.4069480895996</v>
+        <v>10.4069490432739</v>
       </c>
       <c r="H890" t="n">
         <v>125493</v>
@@ -26208,7 +26208,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G891" t="n">
-        <v>10.5914697647095</v>
+        <v>10.5914688110352</v>
       </c>
       <c r="H891" t="n">
         <v>113923</v>
@@ -26266,7 +26266,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.9236068725586</v>
+        <v>10.9236059188843</v>
       </c>
       <c r="H893" t="n">
         <v>126439</v>
@@ -26295,7 +26295,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G894" t="n">
-        <v>10.4807567596436</v>
+        <v>10.4807558059692</v>
       </c>
       <c r="H894" t="n">
         <v>222824</v>
@@ -26353,7 +26353,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G896" t="n">
-        <v>10.5361127853394</v>
+        <v>10.5361137390137</v>
       </c>
       <c r="H896" t="n">
         <v>218631</v>
@@ -26411,7 +26411,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.3700456619263</v>
+        <v>10.3700437545776</v>
       </c>
       <c r="H898" t="n">
         <v>110215</v>
@@ -26440,7 +26440,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G899" t="n">
-        <v>10.0471343994141</v>
+        <v>10.0471353530884</v>
       </c>
       <c r="H899" t="n">
         <v>182473</v>
@@ -26469,7 +26469,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762981414795</v>
+        <v>10.1762971878052</v>
       </c>
       <c r="H900" t="n">
         <v>261491</v>
@@ -26527,7 +26527,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964221954346</v>
+        <v>9.65964126586914</v>
       </c>
       <c r="H902" t="n">
         <v>198170</v>
@@ -26585,7 +26585,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G904" t="n">
-        <v>10.0932636260986</v>
+        <v>10.0932645797729</v>
       </c>
       <c r="H904" t="n">
         <v>154899</v>
@@ -26730,7 +26730,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G909" t="n">
-        <v>10.3054618835449</v>
+        <v>10.3054628372192</v>
       </c>
       <c r="H909" t="n">
         <v>167262</v>
@@ -26759,7 +26759,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438533782959</v>
+        <v>10.4438543319702</v>
       </c>
       <c r="H910" t="n">
         <v>188704</v>
@@ -26817,7 +26817,7 @@
         <v>11.5600004196167</v>
       </c>
       <c r="G912" t="n">
-        <v>10.6652774810791</v>
+        <v>10.6652784347534</v>
       </c>
       <c r="H912" t="n">
         <v>140872</v>
@@ -26846,7 +26846,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H913" t="n">
         <v>207382</v>
@@ -26875,7 +26875,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.96410083770752</v>
+        <v>9.9640998840332</v>
       </c>
       <c r="H914" t="n">
         <v>253876</v>
@@ -26904,7 +26904,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>10.0563611984253</v>
+        <v>10.056360244751</v>
       </c>
       <c r="H915" t="n">
         <v>185001</v>
@@ -26933,7 +26933,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486215591431</v>
       </c>
       <c r="H916" t="n">
         <v>218887</v>
@@ -26991,7 +26991,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G918" t="n">
-        <v>9.50279903411865</v>
+        <v>9.50279998779297</v>
       </c>
       <c r="H918" t="n">
         <v>261117</v>
@@ -27020,7 +27020,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G919" t="n">
-        <v>9.29059982299805</v>
+        <v>9.29060077667236</v>
       </c>
       <c r="H919" t="n">
         <v>131607</v>
@@ -27078,7 +27078,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G921" t="n">
-        <v>9.21217823028564</v>
+        <v>9.21217918395996</v>
       </c>
       <c r="H921" t="n">
         <v>72765</v>
@@ -27136,7 +27136,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964221954346</v>
+        <v>9.65964126586914</v>
       </c>
       <c r="H923" t="n">
         <v>86848</v>
@@ -27165,7 +27165,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G924" t="n">
-        <v>9.29059982299805</v>
+        <v>9.29060077667236</v>
       </c>
       <c r="H924" t="n">
         <v>94925</v>
@@ -27194,7 +27194,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G925" t="n">
-        <v>9.43821620941162</v>
+        <v>9.43821716308594</v>
       </c>
       <c r="H925" t="n">
         <v>137287</v>
@@ -27223,7 +27223,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G926" t="n">
-        <v>9.47512245178223</v>
+        <v>9.47512149810791</v>
       </c>
       <c r="H926" t="n">
         <v>155843</v>
@@ -27281,7 +27281,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G928" t="n">
-        <v>8.94001293182373</v>
+        <v>8.94001197814941</v>
       </c>
       <c r="H928" t="n">
         <v>231622</v>
@@ -27310,7 +27310,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G929" t="n">
-        <v>8.98614120483398</v>
+        <v>8.9861421585083</v>
       </c>
       <c r="H929" t="n">
         <v>131407</v>
@@ -27339,7 +27339,7 @@
         <v>9.625</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88004302978516</v>
+        <v>8.88004398345947</v>
       </c>
       <c r="H930" t="n">
         <v>287237</v>
@@ -27397,7 +27397,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447059631348</v>
+        <v>9.24447154998779</v>
       </c>
       <c r="H932" t="n">
         <v>161867</v>
@@ -27426,7 +27426,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G933" t="n">
-        <v>9.28137493133545</v>
+        <v>9.28137588500977</v>
       </c>
       <c r="H933" t="n">
         <v>133529</v>
@@ -27484,7 +27484,7 @@
         <v>9.98499965667725</v>
       </c>
       <c r="G935" t="n">
-        <v>9.21217823028564</v>
+        <v>9.21217918395996</v>
       </c>
       <c r="H935" t="n">
         <v>132335</v>
@@ -27513,7 +27513,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>9.88106536865234</v>
+        <v>9.88106632232666</v>
       </c>
       <c r="H936" t="n">
         <v>328350</v>
@@ -27571,7 +27571,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G938" t="n">
-        <v>9.99177742004395</v>
+        <v>9.99177837371826</v>
       </c>
       <c r="H938" t="n">
         <v>283851</v>
@@ -27600,7 +27600,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486196517944</v>
+        <v>10.1486215591431</v>
       </c>
       <c r="H939" t="n">
         <v>195612</v>
@@ -27745,7 +27745,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G944" t="n">
-        <v>10.0840377807617</v>
+        <v>10.084038734436</v>
       </c>
       <c r="H944" t="n">
         <v>156292</v>
@@ -27803,7 +27803,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286817550659</v>
+        <v>10.0286827087402</v>
       </c>
       <c r="H946" t="n">
         <v>131456</v>
@@ -27832,7 +27832,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G947" t="n">
-        <v>9.61351203918457</v>
+        <v>9.61351108551025</v>
       </c>
       <c r="H947" t="n">
         <v>385751</v>
@@ -27861,7 +27861,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886806488037</v>
+        <v>9.66886615753174</v>
       </c>
       <c r="H948" t="n">
         <v>129728</v>
@@ -27890,7 +27890,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G949" t="n">
-        <v>9.61351203918457</v>
+        <v>9.61351108551025</v>
       </c>
       <c r="H949" t="n">
         <v>82832</v>
@@ -27919,7 +27919,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G950" t="n">
-        <v>9.52125072479248</v>
+        <v>9.5212516784668</v>
       </c>
       <c r="H950" t="n">
         <v>59934</v>
@@ -27977,7 +27977,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886806488037</v>
+        <v>9.66886615753174</v>
       </c>
       <c r="H952" t="n">
         <v>80416</v>
@@ -28006,7 +28006,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G953" t="n">
-        <v>9.79803276062012</v>
+        <v>9.7980318069458</v>
       </c>
       <c r="H953" t="n">
         <v>64831</v>
@@ -28035,7 +28035,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G954" t="n">
-        <v>9.56738090515137</v>
+        <v>9.56738185882568</v>
       </c>
       <c r="H954" t="n">
         <v>113957</v>
@@ -28093,7 +28093,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G956" t="n">
-        <v>9.26292324066162</v>
+        <v>9.2629222869873</v>
       </c>
       <c r="H956" t="n">
         <v>124882</v>
@@ -28122,7 +28122,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>9.39208698272705</v>
+        <v>9.39208793640137</v>
       </c>
       <c r="H957" t="n">
         <v>68256</v>
@@ -28180,7 +28180,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G959" t="n">
-        <v>9.28137493133545</v>
+        <v>9.28137588500977</v>
       </c>
       <c r="H959" t="n">
         <v>162280</v>
@@ -28209,7 +28209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>9.31827926635742</v>
+        <v>9.31827831268311</v>
       </c>
       <c r="H960" t="n">
         <v>109157</v>
@@ -28325,7 +28325,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G964" t="n">
-        <v>9.88106536865234</v>
+        <v>9.88106632232666</v>
       </c>
       <c r="H964" t="n">
         <v>91898</v>
@@ -28383,7 +28383,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G966" t="n">
-        <v>9.7519006729126</v>
+        <v>9.75190162658691</v>
       </c>
       <c r="H966" t="n">
         <v>167211</v>
@@ -28412,7 +28412,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G967" t="n">
-        <v>9.49357318878174</v>
+        <v>9.49357223510742</v>
       </c>
       <c r="H967" t="n">
         <v>153985</v>
@@ -28470,7 +28470,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655860900879</v>
+        <v>10.0655851364136</v>
       </c>
       <c r="H969" t="n">
         <v>218375</v>
@@ -28499,7 +28499,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822448730469</v>
+        <v>10.5822439193726</v>
       </c>
       <c r="H970" t="n">
         <v>229401</v>
@@ -28528,7 +28528,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G971" t="n">
-        <v>10.7298603057861</v>
+        <v>10.7298612594604</v>
       </c>
       <c r="H971" t="n">
         <v>258960</v>
@@ -28586,7 +28586,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G973" t="n">
-        <v>10.5084362030029</v>
+        <v>10.5084352493286</v>
       </c>
       <c r="H973" t="n">
         <v>181987</v>
@@ -28731,7 +28731,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G978" t="n">
-        <v>11.6340084075928</v>
+        <v>11.6340093612671</v>
       </c>
       <c r="H978" t="n">
         <v>723041</v>
@@ -28760,7 +28760,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G979" t="n">
-        <v>12.2337017059326</v>
+        <v>12.2337007522583</v>
       </c>
       <c r="H979" t="n">
         <v>516034</v>
@@ -28847,7 +28847,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G982" t="n">
-        <v>12.086085319519</v>
+        <v>12.0860843658447</v>
       </c>
       <c r="H982" t="n">
         <v>247645</v>
@@ -28876,7 +28876,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G983" t="n">
-        <v>12.1414403915405</v>
+        <v>12.1414413452148</v>
       </c>
       <c r="H983" t="n">
         <v>156365</v>
@@ -28992,7 +28992,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G987" t="n">
-        <v>11.956919670105</v>
+        <v>11.9569206237793</v>
       </c>
       <c r="H987" t="n">
         <v>141835</v>
@@ -29021,7 +29021,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>11.7539482116699</v>
+        <v>11.7539472579956</v>
       </c>
       <c r="H988" t="n">
         <v>186372</v>
@@ -29253,7 +29253,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G996" t="n">
-        <v>13.0824956893921</v>
+        <v>13.0824947357178</v>
       </c>
       <c r="H996" t="n">
         <v>236235</v>
@@ -29282,7 +29282,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G997" t="n">
-        <v>13.5991506576538</v>
+        <v>13.5991516113281</v>
       </c>
       <c r="H997" t="n">
         <v>340199</v>
@@ -29311,7 +29311,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G998" t="n">
-        <v>13.40540599823</v>
+        <v>13.4054050445557</v>
       </c>
       <c r="H998" t="n">
         <v>614560</v>
@@ -29369,7 +29369,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7559928894043</v>
+        <v>13.7559938430786</v>
       </c>
       <c r="H1000" t="n">
         <v>343538</v>
@@ -29456,7 +29456,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1003" t="n">
-        <v>13.3408241271973</v>
+        <v>13.3408231735229</v>
       </c>
       <c r="H1003" t="n">
         <v>316644</v>
@@ -29514,7 +29514,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1005" t="n">
-        <v>13.719090461731</v>
+        <v>13.7190895080566</v>
       </c>
       <c r="H1005" t="n">
         <v>92655</v>
@@ -29543,7 +29543,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283163070679</v>
+        <v>13.7283153533936</v>
       </c>
       <c r="H1006" t="n">
         <v>219263</v>
@@ -29601,7 +29601,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.1342620849609</v>
+        <v>14.1342601776123</v>
       </c>
       <c r="H1008" t="n">
         <v>148543</v>
@@ -29688,7 +29688,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1011" t="n">
         <v>66991</v>
@@ -29717,7 +29717,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1012" t="n">
-        <v>13.6637353897095</v>
+        <v>13.6637344360352</v>
       </c>
       <c r="H1012" t="n">
         <v>165683</v>
@@ -29746,7 +29746,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1013" t="n">
-        <v>13.6637353897095</v>
+        <v>13.6637344360352</v>
       </c>
       <c r="H1013" t="n">
         <v>84386</v>
@@ -29804,7 +29804,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>13.7006378173828</v>
+        <v>13.7006387710571</v>
       </c>
       <c r="H1015" t="n">
         <v>89461</v>
@@ -29862,7 +29862,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1017" t="n">
         <v>211627</v>
@@ -29891,7 +29891,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1018" t="n">
-        <v>13.719090461731</v>
+        <v>13.7190895080566</v>
       </c>
       <c r="H1018" t="n">
         <v>328396</v>
@@ -29978,7 +29978,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1021" t="n">
-        <v>14.0512266159058</v>
+        <v>14.0512256622314</v>
       </c>
       <c r="H1021" t="n">
         <v>214446</v>
@@ -30007,7 +30007,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1022" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1022" t="n">
         <v>87476</v>
@@ -30036,7 +30036,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1023" t="n">
         <v>109674</v>
@@ -30065,7 +30065,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1024" t="n">
-        <v>14.0327749252319</v>
+        <v>14.0327739715576</v>
       </c>
       <c r="H1024" t="n">
         <v>138602</v>
@@ -30123,7 +30123,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6473264694214</v>
+        <v>15.64732837677</v>
       </c>
       <c r="H1026" t="n">
         <v>1111920</v>
@@ -30152,7 +30152,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303628921509</v>
+        <v>15.7303609848022</v>
       </c>
       <c r="H1027" t="n">
         <v>948892</v>
@@ -30181,7 +30181,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.0865879058838</v>
+        <v>17.0865859985352</v>
       </c>
       <c r="H1028" t="n">
         <v>635195</v>
@@ -30210,7 +30210,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.7913551330566</v>
+        <v>16.791353225708</v>
       </c>
       <c r="H1029" t="n">
         <v>366910</v>
@@ -30239,7 +30239,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.865161895752</v>
+        <v>16.8651638031006</v>
       </c>
       <c r="H1030" t="n">
         <v>257560</v>
@@ -30268,7 +30268,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.7452220916748</v>
+        <v>16.7452239990234</v>
       </c>
       <c r="H1031" t="n">
         <v>202159</v>
@@ -30297,7 +30297,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.8190307617188</v>
+        <v>16.8190326690674</v>
       </c>
       <c r="H1032" t="n">
         <v>152525</v>
@@ -30384,7 +30384,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333353042603</v>
+        <v>15.9333333969116</v>
       </c>
       <c r="H1035" t="n">
         <v>130687</v>
@@ -30413,7 +30413,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.4720335006714</v>
+        <v>15.4720344543457</v>
       </c>
       <c r="H1036" t="n">
         <v>234914</v>
@@ -30442,7 +30442,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.6785955429077</v>
+        <v>14.678596496582</v>
       </c>
       <c r="H1037" t="n">
         <v>251460</v>
@@ -30471,7 +30471,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.3187818527222</v>
+        <v>14.3187808990479</v>
       </c>
       <c r="H1038" t="n">
         <v>248886</v>
@@ -30558,7 +30558,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.204478263855</v>
+        <v>15.2044792175293</v>
       </c>
       <c r="H1041" t="n">
         <v>120054</v>
@@ -30587,7 +30587,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247247695923</v>
       </c>
       <c r="H1042" t="n">
         <v>250873</v>
@@ -30616,7 +30616,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247247695923</v>
       </c>
       <c r="H1043" t="n">
         <v>139842</v>
@@ -30674,7 +30674,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.1491241455078</v>
+        <v>15.1491222381592</v>
       </c>
       <c r="H1045" t="n">
         <v>133980</v>
@@ -30703,7 +30703,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506093978882</v>
+        <v>15.2506084442139</v>
       </c>
       <c r="H1046" t="n">
         <v>126441</v>
@@ -30761,7 +30761,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.1583490371704</v>
+        <v>15.1583480834961</v>
       </c>
       <c r="H1048" t="n">
         <v>75769</v>
@@ -30790,7 +30790,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G1049" t="n">
-        <v>15.204478263855</v>
+        <v>15.2044792175293</v>
       </c>
       <c r="H1049" t="n">
         <v>166255</v>
@@ -30819,7 +30819,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1050" t="n">
-        <v>15.0753154754639</v>
+        <v>15.0753145217896</v>
       </c>
       <c r="H1050" t="n">
         <v>149710</v>
@@ -30906,7 +30906,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>12.6027421951294</v>
+        <v>12.6027412414551</v>
       </c>
       <c r="H1053" t="n">
         <v>435284</v>
@@ -30935,7 +30935,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399551391602</v>
+        <v>12.0399541854858</v>
       </c>
       <c r="H1054" t="n">
         <v>314929</v>
@@ -31051,7 +31051,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.6006956100464</v>
+        <v>10.6006946563721</v>
       </c>
       <c r="H1058" t="n">
         <v>282297</v>
@@ -31109,7 +31109,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.1301689147949</v>
+        <v>10.1301679611206</v>
       </c>
       <c r="H1060" t="n">
         <v>421008</v>
@@ -31138,7 +31138,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1061" t="n">
-        <v>9.79803276062012</v>
+        <v>9.7980318069458</v>
       </c>
       <c r="H1061" t="n">
         <v>252887</v>
@@ -31225,7 +31225,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.9758939743042</v>
+        <v>7.97589349746704</v>
       </c>
       <c r="H1064" t="n">
         <v>361762</v>
@@ -31254,7 +31254,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.89285898208618</v>
+        <v>7.8928599357605</v>
       </c>
       <c r="H1065" t="n">
         <v>433976</v>
@@ -31283,7 +31283,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.5504732131958</v>
+        <v>6.55047273635864</v>
       </c>
       <c r="H1066" t="n">
         <v>390315</v>
@@ -31370,7 +31370,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409605026245</v>
+        <v>6.98409652709961</v>
       </c>
       <c r="H1069" t="n">
         <v>157083</v>
@@ -31428,7 +31428,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.01177406311035</v>
+        <v>7.01177358627319</v>
       </c>
       <c r="H1071" t="n">
         <v>100213</v>
@@ -31515,7 +31515,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697841644287</v>
+        <v>8.85697746276855</v>
       </c>
       <c r="H1074" t="n">
         <v>167191</v>
@@ -31602,7 +31602,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1077" t="n">
-        <v>8.39567756652832</v>
+        <v>8.395676612854</v>
       </c>
       <c r="H1077" t="n">
         <v>136313</v>
@@ -31631,7 +31631,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.40029048919678</v>
+        <v>8.40028953552246</v>
       </c>
       <c r="H1078" t="n">
         <v>48370</v>
@@ -31689,7 +31689,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.25728702545166</v>
+        <v>8.25728607177734</v>
       </c>
       <c r="H1080" t="n">
         <v>73798</v>
@@ -31718,7 +31718,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.11889553070068</v>
+        <v>8.11889743804932</v>
       </c>
       <c r="H1081" t="n">
         <v>72725</v>
@@ -31747,7 +31747,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1082" t="n">
-        <v>7.74985504150391</v>
+        <v>7.74985551834106</v>
       </c>
       <c r="H1082" t="n">
         <v>71777</v>
@@ -31776,7 +31776,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.92976331710815</v>
+        <v>7.929762840271</v>
       </c>
       <c r="H1083" t="n">
         <v>60718</v>
@@ -31805,7 +31805,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675889968872</v>
+        <v>7.78675937652588</v>
       </c>
       <c r="H1084" t="n">
         <v>156268</v>
@@ -31834,7 +31834,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.10966968536377</v>
+        <v>8.10967063903809</v>
       </c>
       <c r="H1085" t="n">
         <v>65803</v>
@@ -31863,7 +31863,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.89285898208618</v>
+        <v>7.8928599357605</v>
       </c>
       <c r="H1086" t="n">
         <v>212254</v>
@@ -31892,7 +31892,7 @@
         <v>8.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.842116355896</v>
+        <v>7.84211587905884</v>
       </c>
       <c r="H1087" t="n">
         <v>132894</v>
@@ -32037,7 +32037,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1092" t="n">
-        <v>7.26087713241577</v>
+        <v>7.26087665557861</v>
       </c>
       <c r="H1092" t="n">
         <v>83332</v>
@@ -32095,7 +32095,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1094" t="n">
-        <v>7.33468532562256</v>
+        <v>7.3346848487854</v>
       </c>
       <c r="H1094" t="n">
         <v>117087</v>
@@ -32211,7 +32211,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1098" t="n">
-        <v>7.93437623977661</v>
+        <v>7.93437719345093</v>
       </c>
       <c r="H1098" t="n">
         <v>138770</v>
@@ -32240,7 +32240,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1099" t="n">
-        <v>7.60223913192749</v>
+        <v>7.60223960876465</v>
       </c>
       <c r="H1099" t="n">
         <v>152629</v>
@@ -32269,7 +32269,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.33929777145386</v>
+        <v>7.33929824829102</v>
       </c>
       <c r="H1100" t="n">
         <v>190738</v>
@@ -32298,7 +32298,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920557022095</v>
+        <v>7.51920461654663</v>
       </c>
       <c r="H1101" t="n">
         <v>66663</v>
@@ -32327,7 +32327,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.3070068359375</v>
+        <v>7.30700635910034</v>
       </c>
       <c r="H1102" t="n">
         <v>85960</v>
@@ -32385,7 +32385,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403490066528</v>
+        <v>7.10403394699097</v>
       </c>
       <c r="H1104" t="n">
         <v>88763</v>
@@ -32414,7 +32414,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.15939092636108</v>
+        <v>7.15939044952393</v>
       </c>
       <c r="H1105" t="n">
         <v>90167</v>
@@ -32443,7 +32443,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.3070068359375</v>
+        <v>7.30700635910034</v>
       </c>
       <c r="H1106" t="n">
         <v>150317</v>
@@ -32472,7 +32472,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.06713104248047</v>
+        <v>7.06713008880615</v>
       </c>
       <c r="H1107" t="n">
         <v>140089</v>
@@ -32501,7 +32501,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874002456665</v>
+        <v>6.92874050140381</v>
       </c>
       <c r="H1108" t="n">
         <v>182143</v>
@@ -32530,7 +32530,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G1109" t="n">
-        <v>7.26087713241577</v>
+        <v>7.26087665557861</v>
       </c>
       <c r="H1109" t="n">
         <v>202426</v>
@@ -32559,7 +32559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533479690552</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1110" t="n">
         <v>160774</v>
@@ -32588,7 +32588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533479690552</v>
+        <v>7.56533527374268</v>
       </c>
       <c r="H1111" t="n">
         <v>124418</v>
@@ -32617,7 +32617,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1112" t="n">
-        <v>7.54227018356323</v>
+        <v>7.54227066040039</v>
       </c>
       <c r="H1112" t="n">
         <v>115707</v>
@@ -32646,7 +32646,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G1113" t="n">
-        <v>7.44539737701416</v>
+        <v>7.445396900177</v>
       </c>
       <c r="H1113" t="n">
         <v>89200</v>
@@ -32675,7 +32675,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010250091553</v>
+        <v>7.27010297775269</v>
       </c>
       <c r="H1114" t="n">
         <v>241372</v>
@@ -32704,7 +32704,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217750549316</v>
+        <v>7.72217798233032</v>
       </c>
       <c r="H1115" t="n">
         <v>329478</v>
@@ -32733,7 +32733,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948623657227</v>
+        <v>8.46948528289795</v>
       </c>
       <c r="H1116" t="n">
         <v>379600</v>
@@ -32820,7 +32820,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.54329395294189</v>
+        <v>8.54329299926758</v>
       </c>
       <c r="H1119" t="n">
         <v>162230</v>
@@ -32994,7 +32994,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.4956197738647</v>
+        <v>11.4956188201904</v>
       </c>
       <c r="H1125" t="n">
         <v>412132</v>
@@ -33023,7 +33023,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>11.2557420730591</v>
+        <v>11.2557430267334</v>
       </c>
       <c r="H1126" t="n">
         <v>312966</v>
@@ -33052,7 +33052,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420566558838</v>
+        <v>10.9420576095581</v>
       </c>
       <c r="H1127" t="n">
         <v>171397</v>
@@ -33197,7 +33197,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5084362030029</v>
+        <v>10.5084352493286</v>
       </c>
       <c r="H1132" t="n">
         <v>328890</v>
@@ -33226,7 +33226,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.1947507858276</v>
+        <v>10.1947498321533</v>
       </c>
       <c r="H1133" t="n">
         <v>166996</v>
@@ -33284,7 +33284,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1135" t="n">
-        <v>9.89029216766357</v>
+        <v>9.89029121398926</v>
       </c>
       <c r="H1135" t="n">
         <v>92083</v>
@@ -33313,7 +33313,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1136" t="n">
-        <v>10.5361127853394</v>
+        <v>10.5361137390137</v>
       </c>
       <c r="H1136" t="n">
         <v>357074</v>
@@ -33400,7 +33400,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.1301689147949</v>
+        <v>10.1301679611206</v>
       </c>
       <c r="H1139" t="n">
         <v>131328</v>
@@ -33429,7 +33429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.3700456619263</v>
+        <v>10.3700437545776</v>
       </c>
       <c r="H1140" t="n">
         <v>116026</v>
@@ -33487,7 +33487,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.2224283218384</v>
+        <v>10.2224292755127</v>
       </c>
       <c r="H1142" t="n">
         <v>90895</v>
@@ -33545,7 +33545,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1144" t="n">
-        <v>10.5361127853394</v>
+        <v>10.5361137390137</v>
       </c>
       <c r="H1144" t="n">
         <v>70628</v>
@@ -33603,7 +33603,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.7667646408081</v>
+        <v>10.7667636871338</v>
       </c>
       <c r="H1146" t="n">
         <v>215683</v>
@@ -33632,7 +33632,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1147" t="n">
-        <v>12.021502494812</v>
+        <v>12.0215015411377</v>
       </c>
       <c r="H1147" t="n">
         <v>726814</v>
@@ -33777,7 +33777,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.818531036377</v>
+        <v>11.8185300827026</v>
       </c>
       <c r="H1152" t="n">
         <v>187197</v>
@@ -33806,7 +33806,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1153" t="n">
-        <v>11.707818031311</v>
+        <v>11.7078170776367</v>
       </c>
       <c r="H1153" t="n">
         <v>120798</v>
@@ -33835,7 +33835,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.818531036377</v>
+        <v>11.8185300827026</v>
       </c>
       <c r="H1154" t="n">
         <v>76721</v>
@@ -33864,7 +33864,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.7539482116699</v>
+        <v>11.7539472579956</v>
       </c>
       <c r="H1155" t="n">
         <v>263178</v>
@@ -33922,7 +33922,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616878509521</v>
+        <v>11.6616888046265</v>
       </c>
       <c r="H1157" t="n">
         <v>54063</v>
@@ -33951,7 +33951,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.5694274902344</v>
+        <v>11.5694284439087</v>
       </c>
       <c r="H1158" t="n">
         <v>115659</v>
@@ -34038,7 +34038,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.2741956710815</v>
+        <v>11.2741947174072</v>
       </c>
       <c r="H1161" t="n">
         <v>62971</v>
@@ -34270,7 +34270,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1169" t="n">
-        <v>13.0548152923584</v>
+        <v>13.0548162460327</v>
       </c>
       <c r="H1169" t="n">
         <v>208552</v>
@@ -34299,7 +34299,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>13.0548152923584</v>
+        <v>13.0548162460327</v>
       </c>
       <c r="H1170" t="n">
         <v>98947</v>
@@ -34328,7 +34328,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961801528931</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1171" t="n">
         <v>197304</v>
@@ -34357,7 +34357,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.2854671478271</v>
+        <v>13.2854681015015</v>
       </c>
       <c r="H1172" t="n">
         <v>98903</v>
@@ -34386,7 +34386,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1173" t="n">
-        <v>13.4423084259033</v>
+        <v>13.4423093795776</v>
       </c>
       <c r="H1173" t="n">
         <v>141586</v>
@@ -34444,7 +34444,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.1286239624023</v>
+        <v>13.1286249160767</v>
       </c>
       <c r="H1175" t="n">
         <v>55804</v>
@@ -34502,7 +34502,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>13.230110168457</v>
+        <v>13.2301111221313</v>
       </c>
       <c r="H1177" t="n">
         <v>59759</v>
@@ -34560,7 +34560,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1179" t="n">
-        <v>13.1932077407837</v>
+        <v>13.1932067871094</v>
       </c>
       <c r="H1179" t="n">
         <v>142039</v>
@@ -34618,7 +34618,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500509262085</v>
+        <v>13.3500499725342</v>
       </c>
       <c r="H1181" t="n">
         <v>113455</v>
@@ -34647,7 +34647,7 @@
         <v>15</v>
       </c>
       <c r="G1182" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H1182" t="n">
         <v>172704</v>
@@ -34676,7 +34676,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714740753174</v>
+        <v>13.5714750289917</v>
       </c>
       <c r="H1183" t="n">
         <v>86309</v>
@@ -34792,7 +34792,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G1187" t="n">
-        <v>13.4976663589478</v>
+        <v>13.4976654052734</v>
       </c>
       <c r="H1187" t="n">
         <v>194560</v>
@@ -34821,7 +34821,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.1101722717285</v>
+        <v>13.1101732254028</v>
       </c>
       <c r="H1188" t="n">
         <v>183776</v>
@@ -34850,7 +34850,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1189" t="n">
-        <v>13.1932077407837</v>
+        <v>13.1932067871094</v>
       </c>
       <c r="H1189" t="n">
         <v>112671</v>
@@ -34879,7 +34879,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>13.1286239624023</v>
+        <v>13.1286249160767</v>
       </c>
       <c r="H1190" t="n">
         <v>59956</v>
@@ -34908,7 +34908,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1191" t="n">
-        <v>13.1655282974243</v>
+        <v>13.1655292510986</v>
       </c>
       <c r="H1191" t="n">
         <v>114078</v>
@@ -34966,7 +34966,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G1193" t="n">
-        <v>13.230110168457</v>
+        <v>13.2301111221313</v>
       </c>
       <c r="H1193" t="n">
         <v>90522</v>
@@ -34995,7 +34995,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G1194" t="n">
-        <v>13.2762403488159</v>
+        <v>13.2762413024902</v>
       </c>
       <c r="H1194" t="n">
         <v>121429</v>
@@ -35082,7 +35082,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.1747541427612</v>
+        <v>13.1747550964355</v>
       </c>
       <c r="H1197" t="n">
         <v>81797</v>
@@ -35111,7 +35111,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G1198" t="n">
-        <v>13.331597328186</v>
+        <v>13.3315963745117</v>
       </c>
       <c r="H1198" t="n">
         <v>81183</v>
@@ -35198,7 +35198,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.3813161849976</v>
+        <v>12.3813180923462</v>
       </c>
       <c r="H1201" t="n">
         <v>204999</v>
@@ -35227,7 +35227,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1202" t="n">
-        <v>12.6304197311401</v>
+        <v>12.6304187774658</v>
       </c>
       <c r="H1202" t="n">
         <v>101665</v>
@@ -35372,7 +35372,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1207" t="n">
-        <v>13.40540599823</v>
+        <v>13.4054050445557</v>
       </c>
       <c r="H1207" t="n">
         <v>164570</v>
@@ -35401,7 +35401,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1208" t="n">
-        <v>13.5068922042847</v>
+        <v>13.5068912506104</v>
       </c>
       <c r="H1208" t="n">
         <v>135804</v>
@@ -35430,7 +35430,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>13.4330825805664</v>
+        <v>13.4330835342407</v>
       </c>
       <c r="H1209" t="n">
         <v>134522</v>
@@ -35459,7 +35459,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.4515352249146</v>
+        <v>13.4515342712402</v>
       </c>
       <c r="H1210" t="n">
         <v>167243</v>
@@ -35488,7 +35488,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1211" t="n">
-        <v>14.1158094406128</v>
+        <v>14.1158084869385</v>
       </c>
       <c r="H1211" t="n">
         <v>282664</v>
@@ -35517,7 +35517,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>15.2690601348877</v>
+        <v>15.2690591812134</v>
       </c>
       <c r="H1212" t="n">
         <v>617005</v>
@@ -35546,7 +35546,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735177993774</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1213" t="n">
         <v>405514</v>
@@ -35575,7 +35575,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1214" t="n">
-        <v>15.8318462371826</v>
+        <v>15.8318471908569</v>
       </c>
       <c r="H1214" t="n">
         <v>215421</v>
@@ -35720,7 +35720,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.5125274658203</v>
+        <v>14.512526512146</v>
       </c>
       <c r="H1219" t="n">
         <v>194522</v>
@@ -35778,7 +35778,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G1221" t="n">
-        <v>14.5217542648315</v>
+        <v>14.5217533111572</v>
       </c>
       <c r="H1221" t="n">
         <v>113724</v>
@@ -35807,7 +35807,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1222" t="n">
-        <v>14.5955619812012</v>
+        <v>14.5955610275269</v>
       </c>
       <c r="H1222" t="n">
         <v>167540</v>
@@ -35865,7 +35865,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>14.3556861877441</v>
+        <v>14.3556852340698</v>
       </c>
       <c r="H1224" t="n">
         <v>118110</v>
@@ -36039,7 +36039,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033016204834</v>
+        <v>14.5033025741577</v>
       </c>
       <c r="H1230" t="n">
         <v>232002</v>
@@ -36126,7 +36126,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735177993774</v>
+        <v>15.5735187530518</v>
       </c>
       <c r="H1233" t="n">
         <v>375133</v>
@@ -36184,7 +36184,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1235" t="n">
-        <v>15.6750059127808</v>
+        <v>15.6750068664551</v>
       </c>
       <c r="H1235" t="n">
         <v>412079</v>
@@ -36213,7 +36213,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.4166765213013</v>
+        <v>15.4166774749756</v>
       </c>
       <c r="H1236" t="n">
         <v>175438</v>
@@ -36242,7 +36242,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G1237" t="n">
-        <v>15.1029930114746</v>
+        <v>15.1029939651489</v>
       </c>
       <c r="H1237" t="n">
         <v>167525</v>
@@ -36300,7 +36300,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1239" t="n">
-        <v>15.3889989852905</v>
+        <v>15.3889999389648</v>
       </c>
       <c r="H1239" t="n">
         <v>152784</v>
@@ -36358,7 +36358,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.5827465057373</v>
+        <v>15.582745552063</v>
       </c>
       <c r="H1241" t="n">
         <v>78857</v>
@@ -36387,7 +36387,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547584533691</v>
+        <v>16.1547603607178</v>
       </c>
       <c r="H1242" t="n">
         <v>259846</v>
@@ -36416,7 +36416,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.8133964538574</v>
+        <v>15.8133945465088</v>
       </c>
       <c r="H1243" t="n">
         <v>116062</v>
@@ -36445,7 +36445,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410758972168</v>
+        <v>15.8410720825195</v>
       </c>
       <c r="H1244" t="n">
         <v>51279</v>
@@ -36474,7 +36474,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1245" t="n">
-        <v>15.9241094589233</v>
+        <v>15.924108505249</v>
       </c>
       <c r="H1245" t="n">
         <v>72824</v>
@@ -36532,7 +36532,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1247" t="n">
-        <v>16.1178531646729</v>
+        <v>16.1178550720215</v>
       </c>
       <c r="H1247" t="n">
         <v>97235</v>
@@ -36561,7 +36561,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1248" t="n">
-        <v>15.8502998352051</v>
+        <v>15.8502988815308</v>
       </c>
       <c r="H1248" t="n">
         <v>38481</v>
@@ -36590,7 +36590,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G1249" t="n">
-        <v>15.8779783248901</v>
+        <v>15.8779773712158</v>
       </c>
       <c r="H1249" t="n">
         <v>70649</v>
@@ -36648,7 +36648,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1251" t="n">
-        <v>15.6381015777588</v>
+        <v>15.6381034851074</v>
       </c>
       <c r="H1251" t="n">
         <v>64739</v>
@@ -36677,7 +36677,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1252" t="n">
-        <v>15.4351282119751</v>
+        <v>15.4351291656494</v>
       </c>
       <c r="H1252" t="n">
         <v>60423</v>
@@ -36706,7 +36706,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919713973999</v>
+        <v>15.5919704437256</v>
       </c>
       <c r="H1253" t="n">
         <v>50800</v>
@@ -36735,7 +36735,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>15.8133964538574</v>
+        <v>15.8133945465088</v>
       </c>
       <c r="H1254" t="n">
         <v>89575</v>
@@ -36764,7 +36764,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1255" t="n">
-        <v>15.6381015777588</v>
+        <v>15.6381034851074</v>
       </c>
       <c r="H1255" t="n">
         <v>69044</v>
@@ -36793,7 +36793,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517879486084</v>
+        <v>15.9517869949341</v>
       </c>
       <c r="H1256" t="n">
         <v>77596</v>
@@ -36822,7 +36822,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.0994033813477</v>
+        <v>16.099401473999</v>
       </c>
       <c r="H1257" t="n">
         <v>135906</v>
@@ -36909,7 +36909,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>16.5145740509033</v>
+        <v>16.5145721435547</v>
       </c>
       <c r="H1260" t="n">
         <v>217179</v>
@@ -36967,7 +36967,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1262" t="n">
-        <v>17.3910446166992</v>
+        <v>17.3910465240479</v>
       </c>
       <c r="H1262" t="n">
         <v>199105</v>
@@ -37025,7 +37025,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G1264" t="n">
-        <v>17.0865879058838</v>
+        <v>17.0865859985352</v>
       </c>
       <c r="H1264" t="n">
         <v>80793</v>
@@ -37054,7 +37054,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1265" t="n">
-        <v>17.1142654418945</v>
+        <v>17.1142635345459</v>
       </c>
       <c r="H1265" t="n">
         <v>144721</v>
@@ -37141,7 +37141,7 @@
         <v>18.9099998474121</v>
       </c>
       <c r="G1268" t="n">
-        <v>17.446403503418</v>
+        <v>17.4464015960693</v>
       </c>
       <c r="H1268" t="n">
         <v>107802</v>
@@ -37170,7 +37170,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1269" t="n">
-        <v>17.5663414001465</v>
+        <v>17.5663394927979</v>
       </c>
       <c r="H1269" t="n">
         <v>89128</v>
@@ -37228,7 +37228,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1271" t="n">
-        <v>17.6216945648193</v>
+        <v>17.621696472168</v>
       </c>
       <c r="H1271" t="n">
         <v>125434</v>
@@ -37257,7 +37257,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1272" t="n">
-        <v>17.5478858947754</v>
+        <v>17.547887802124</v>
       </c>
       <c r="H1272" t="n">
         <v>81241</v>
@@ -37286,7 +37286,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.0368671417236</v>
+        <v>18.036865234375</v>
       </c>
       <c r="H1273" t="n">
         <v>111248</v>
@@ -37315,7 +37315,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.415132522583</v>
+        <v>18.4151306152344</v>
       </c>
       <c r="H1274" t="n">
         <v>123597</v>
@@ -37344,7 +37344,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.7657222747803</v>
+        <v>18.7657203674316</v>
       </c>
       <c r="H1275" t="n">
         <v>142765</v>
@@ -37373,7 +37373,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1276" t="n">
-        <v>19.6698703765869</v>
+        <v>19.6698722839355</v>
       </c>
       <c r="H1276" t="n">
         <v>259555</v>
@@ -37402,7 +37402,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>19.9835548400879</v>
+        <v>19.9835567474365</v>
       </c>
       <c r="H1277" t="n">
         <v>153145</v>
@@ -37518,7 +37518,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1281" t="n">
-        <v>19.2454738616943</v>
+        <v>19.245475769043</v>
       </c>
       <c r="H1281" t="n">
         <v>104819</v>
@@ -37576,7 +37576,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377361297607</v>
+        <v>19.3377323150635</v>
       </c>
       <c r="H1283" t="n">
         <v>45421</v>
@@ -37663,7 +37663,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>18.5443000793457</v>
+        <v>18.5442981719971</v>
       </c>
       <c r="H1286" t="n">
         <v>154581</v>
@@ -37692,7 +37692,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1287" t="n">
-        <v>18.5627498626709</v>
+        <v>18.5627517700195</v>
       </c>
       <c r="H1287" t="n">
         <v>64023</v>
@@ -37750,7 +37750,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1289" t="n">
-        <v>18.4704895019531</v>
+        <v>18.4704914093018</v>
       </c>
       <c r="H1289" t="n">
         <v>98728</v>
@@ -37779,7 +37779,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1290" t="n">
-        <v>17.972282409668</v>
+        <v>17.9722843170166</v>
       </c>
       <c r="H1290" t="n">
         <v>74769</v>
@@ -37895,7 +37895,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.6109237670898</v>
+        <v>20.6109256744385</v>
       </c>
       <c r="H1294" t="n">
         <v>103797</v>
@@ -37953,7 +37953,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1296" t="n">
-        <v>21.2567462921143</v>
+        <v>21.2567481994629</v>
       </c>
       <c r="H1296" t="n">
         <v>150867</v>
@@ -38011,7 +38011,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>21.312105178833</v>
+        <v>21.3121032714844</v>
       </c>
       <c r="H1298" t="n">
         <v>54089</v>
@@ -38040,7 +38040,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1299" t="n">
-        <v>21.1829395294189</v>
+        <v>21.1829376220703</v>
       </c>
       <c r="H1299" t="n">
         <v>58252</v>
@@ -38069,7 +38069,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G1300" t="n">
-        <v>21.2567462921143</v>
+        <v>21.2567481994629</v>
       </c>
       <c r="H1300" t="n">
         <v>61853</v>
@@ -38098,7 +38098,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1301" t="n">
-        <v>22.7513637542725</v>
+        <v>22.7513618469238</v>
       </c>
       <c r="H1301" t="n">
         <v>213721</v>
@@ -38127,7 +38127,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1302" t="n">
-        <v>22.7698173522949</v>
+        <v>22.7698135375977</v>
       </c>
       <c r="H1302" t="n">
         <v>125679</v>
@@ -38185,7 +38185,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1304" t="n">
         <v>107731</v>
@@ -38214,7 +38214,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745845794678</v>
+        <v>22.4745826721191</v>
       </c>
       <c r="H1305" t="n">
         <v>45171</v>
@@ -38359,7 +38359,7 @@
         <v>21.8799991607666</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.1865272521973</v>
+        <v>20.1865291595459</v>
       </c>
       <c r="H1310" t="n">
         <v>87245</v>
@@ -38446,7 +38446,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="n">
-        <v>21.2013912200928</v>
+        <v>21.2013893127441</v>
       </c>
       <c r="H1313" t="n">
         <v>97639</v>
@@ -38475,7 +38475,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4633083343506</v>
+        <v>20.4633102416992</v>
       </c>
       <c r="H1314" t="n">
         <v>180543</v>
@@ -38620,7 +38620,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.1091289520264</v>
+        <v>21.1091327667236</v>
       </c>
       <c r="H1319" t="n">
         <v>59299</v>
@@ -38649,7 +38649,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.1091289520264</v>
+        <v>21.1091327667236</v>
       </c>
       <c r="H1320" t="n">
         <v>52297</v>
@@ -38678,7 +38678,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="n">
-        <v>20.2234344482422</v>
+        <v>20.2234325408936</v>
       </c>
       <c r="H1321" t="n">
         <v>160358</v>
@@ -38707,7 +38707,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.9835548400879</v>
+        <v>19.9835567474365</v>
       </c>
       <c r="H1322" t="n">
         <v>182976</v>
@@ -38765,7 +38765,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1324" t="n">
         <v>133244</v>
@@ -38794,7 +38794,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>20.1127223968506</v>
+        <v>20.112720489502</v>
       </c>
       <c r="H1325" t="n">
         <v>134502</v>
@@ -38881,7 +38881,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1328" t="n">
         <v>213744</v>
@@ -38910,7 +38910,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1329" t="n">
         <v>111615</v>
@@ -38939,7 +38939,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1330" t="n">
         <v>74044</v>
@@ -39026,7 +39026,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="n">
-        <v>22.5483913421631</v>
+        <v>22.5483894348145</v>
       </c>
       <c r="H1333" t="n">
         <v>168907</v>
@@ -39113,7 +39113,7 @@
         <v>24</v>
       </c>
       <c r="G1336" t="n">
-        <v>22.1424465179443</v>
+        <v>22.1424446105957</v>
       </c>
       <c r="H1336" t="n">
         <v>58817</v>
@@ -39200,7 +39200,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317306518555</v>
+        <v>22.0317344665527</v>
       </c>
       <c r="H1339" t="n">
         <v>111019</v>
@@ -39258,7 +39258,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846775054932</v>
+        <v>23.7846755981445</v>
       </c>
       <c r="H1341" t="n">
         <v>181858</v>
@@ -39345,7 +39345,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>23.8953876495361</v>
+        <v>23.8953895568848</v>
       </c>
       <c r="H1344" t="n">
         <v>153185</v>
@@ -39374,7 +39374,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>23.0465927124023</v>
+        <v>23.046594619751</v>
       </c>
       <c r="H1345" t="n">
         <v>113640</v>
@@ -39490,7 +39490,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1349" t="n">
-        <v>23.3971862792969</v>
+        <v>23.3971843719482</v>
       </c>
       <c r="H1349" t="n">
         <v>78530</v>
@@ -39519,7 +39519,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817012786865</v>
+        <v>23.5817031860352</v>
       </c>
       <c r="H1350" t="n">
         <v>51355</v>
@@ -39548,7 +39548,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.1388549804688</v>
+        <v>23.1388568878174</v>
       </c>
       <c r="H1351" t="n">
         <v>110939</v>
@@ -39577,7 +39577,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1352" t="n">
-        <v>22.7513637542725</v>
+        <v>22.7513618469238</v>
       </c>
       <c r="H1352" t="n">
         <v>172624</v>
@@ -39606,7 +39606,7 @@
         <v>24.4799995422363</v>
       </c>
       <c r="G1353" t="n">
-        <v>22.5852947235107</v>
+        <v>22.5852928161621</v>
       </c>
       <c r="H1353" t="n">
         <v>208215</v>
@@ -39693,7 +39693,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1356" t="n">
-        <v>23.4894409179688</v>
+        <v>23.4894428253174</v>
       </c>
       <c r="H1356" t="n">
         <v>126113</v>
@@ -39722,7 +39722,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1357" t="n">
         <v>131691</v>
@@ -39751,7 +39751,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>23.8953876495361</v>
+        <v>23.8953895568848</v>
       </c>
       <c r="H1358" t="n">
         <v>57684</v>
@@ -39780,7 +39780,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662239074707</v>
+        <v>23.7662220001221</v>
       </c>
       <c r="H1359" t="n">
         <v>240302</v>
@@ -39867,7 +39867,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="n">
-        <v>23.6370620727539</v>
+        <v>23.6370601654053</v>
       </c>
       <c r="H1362" t="n">
         <v>264460</v>
@@ -39925,7 +39925,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1364" t="n">
         <v>236072</v>
@@ -39954,7 +39954,7 @@
         <v>29</v>
       </c>
       <c r="G1365" t="n">
-        <v>26.7554531097412</v>
+        <v>26.7554550170898</v>
       </c>
       <c r="H1365" t="n">
         <v>306129</v>
@@ -39983,7 +39983,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G1366" t="n">
-        <v>26.4786739349365</v>
+        <v>26.4786758422852</v>
       </c>
       <c r="H1366" t="n">
         <v>262217</v>
@@ -40012,7 +40012,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1367" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1367" t="n">
         <v>280231</v>
@@ -40041,7 +40041,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>27.1613998413086</v>
+        <v>27.1614017486572</v>
       </c>
       <c r="H1368" t="n">
         <v>189145</v>
@@ -40070,7 +40070,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="n">
-        <v>27.3828220367432</v>
+        <v>27.3828258514404</v>
       </c>
       <c r="H1369" t="n">
         <v>120408</v>
@@ -40099,7 +40099,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935340881348</v>
+        <v>27.4935359954834</v>
       </c>
       <c r="H1370" t="n">
         <v>201422</v>
@@ -40128,7 +40128,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="n">
-        <v>28.157808303833</v>
+        <v>28.1578102111816</v>
       </c>
       <c r="H1371" t="n">
         <v>113890</v>
@@ -40157,7 +40157,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>28.0470962524414</v>
+        <v>28.0470943450928</v>
       </c>
       <c r="H1372" t="n">
         <v>81326</v>
@@ -40186,7 +40186,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="n">
-        <v>28.0470962524414</v>
+        <v>28.0470943450928</v>
       </c>
       <c r="H1373" t="n">
         <v>74572</v>
@@ -40215,7 +40215,7 @@
         <v>29.5599994659424</v>
       </c>
       <c r="G1374" t="n">
-        <v>27.2721099853516</v>
+        <v>27.2721118927002</v>
       </c>
       <c r="H1374" t="n">
         <v>176103</v>
@@ -40273,7 +40273,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>27.3828220367432</v>
+        <v>27.3828258514404</v>
       </c>
       <c r="H1376" t="n">
         <v>44639</v>
@@ -40302,7 +40302,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>27.4012756347656</v>
+        <v>27.4012775421143</v>
       </c>
       <c r="H1377" t="n">
         <v>73760</v>
@@ -40331,7 +40331,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1378" t="n">
-        <v>27.1060447692871</v>
+        <v>27.1060428619385</v>
       </c>
       <c r="H1378" t="n">
         <v>74735</v>
@@ -40360,7 +40360,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="n">
-        <v>26.9030704498291</v>
+        <v>26.9030685424805</v>
       </c>
       <c r="H1379" t="n">
         <v>72804</v>
@@ -40418,7 +40418,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>25.9251098632812</v>
+        <v>25.9251136779785</v>
       </c>
       <c r="H1381" t="n">
         <v>64116</v>
@@ -40447,7 +40447,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="n">
-        <v>25.7221412658691</v>
+        <v>25.7221393585205</v>
       </c>
       <c r="H1382" t="n">
         <v>121764</v>
@@ -40505,7 +40505,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1384" t="n">
-        <v>26.6447410583496</v>
+        <v>26.644739151001</v>
       </c>
       <c r="H1384" t="n">
         <v>111064</v>
@@ -40534,7 +40534,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1385" t="n">
-        <v>26.4602203369141</v>
+        <v>26.4602222442627</v>
       </c>
       <c r="H1385" t="n">
         <v>51146</v>
@@ -40563,7 +40563,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1386" t="n">
-        <v>26.3864154815674</v>
+        <v>26.3864135742188</v>
       </c>
       <c r="H1386" t="n">
         <v>54044</v>
@@ -40592,7 +40592,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1387" t="n">
-        <v>25.9989204406738</v>
+        <v>25.9989223480225</v>
       </c>
       <c r="H1387" t="n">
         <v>84386</v>
@@ -40621,7 +40621,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>25.5007152557373</v>
+        <v>25.5007133483887</v>
       </c>
       <c r="H1388" t="n">
         <v>89097</v>
@@ -40708,7 +40708,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="n">
-        <v>25.7221412658691</v>
+        <v>25.7221393585205</v>
       </c>
       <c r="H1391" t="n">
         <v>36786</v>
@@ -40737,7 +40737,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1392" t="n">
-        <v>26.2572479248047</v>
+        <v>26.2572498321533</v>
       </c>
       <c r="H1392" t="n">
         <v>45196</v>
@@ -40766,7 +40766,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="n">
-        <v>26.1280841827393</v>
+        <v>26.1280860900879</v>
       </c>
       <c r="H1393" t="n">
         <v>32484</v>
@@ -40795,7 +40795,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>25.9620151519775</v>
+        <v>25.9620170593262</v>
       </c>
       <c r="H1394" t="n">
         <v>47886</v>
@@ -40824,7 +40824,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1395" t="n">
-        <v>26.6631946563721</v>
+        <v>26.6631927490234</v>
       </c>
       <c r="H1395" t="n">
         <v>88982</v>
@@ -40853,7 +40853,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G1396" t="n">
-        <v>25.9989204406738</v>
+        <v>25.9989223480225</v>
       </c>
       <c r="H1396" t="n">
         <v>59600</v>
@@ -40882,7 +40882,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G1397" t="n">
-        <v>26.3310565948486</v>
+        <v>26.3310585021973</v>
       </c>
       <c r="H1397" t="n">
         <v>52161</v>
@@ -40911,7 +40911,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G1398" t="n">
-        <v>26.4602203369141</v>
+        <v>26.4602222442627</v>
       </c>
       <c r="H1398" t="n">
         <v>26653</v>
@@ -40969,7 +40969,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G1400" t="n">
-        <v>25.9251098632812</v>
+        <v>25.9251136779785</v>
       </c>
       <c r="H1400" t="n">
         <v>40818</v>
@@ -40998,7 +40998,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="n">
-        <v>26.1280841827393</v>
+        <v>26.1280860900879</v>
       </c>
       <c r="H1401" t="n">
         <v>44132</v>
@@ -41085,7 +41085,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>26.7185478210449</v>
+        <v>26.7185497283936</v>
       </c>
       <c r="H1404" t="n">
         <v>28380</v>
@@ -41143,7 +41143,7 @@
         <v>29</v>
       </c>
       <c r="G1406" t="n">
-        <v>26.7554531097412</v>
+        <v>26.7554550170898</v>
       </c>
       <c r="H1406" t="n">
         <v>32743</v>
@@ -41346,7 +41346,7 @@
         <v>29.4799995422363</v>
       </c>
       <c r="G1413" t="n">
-        <v>27.1983013153076</v>
+        <v>27.1983032226562</v>
       </c>
       <c r="H1413" t="n">
         <v>79452</v>
@@ -41375,7 +41375,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750862121582</v>
+        <v>27.4750823974609</v>
       </c>
       <c r="H1414" t="n">
         <v>54200</v>
@@ -41433,7 +41433,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>30.4643135070801</v>
+        <v>30.4643115997314</v>
       </c>
       <c r="H1416" t="n">
         <v>215821</v>
@@ -41462,7 +41462,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1417" t="n">
-        <v>30.9625205993652</v>
+        <v>30.9625225067139</v>
       </c>
       <c r="H1417" t="n">
         <v>144420</v>
@@ -41491,7 +41491,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="n">
-        <v>29.5970687866211</v>
+        <v>29.5970706939697</v>
       </c>
       <c r="H1418" t="n">
         <v>191826</v>
@@ -41549,7 +41549,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1420" t="n">
-        <v>26.8846168518066</v>
+        <v>26.8846187591553</v>
       </c>
       <c r="H1420" t="n">
         <v>277218</v>
@@ -41636,7 +41636,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923603057861</v>
+        <v>26.7923583984375</v>
       </c>
       <c r="H1423" t="n">
         <v>119595</v>
@@ -41694,7 +41694,7 @@
         <v>29.4599990844727</v>
       </c>
       <c r="G1425" t="n">
-        <v>27.1798496246338</v>
+        <v>27.1798515319824</v>
       </c>
       <c r="H1425" t="n">
         <v>50534</v>
@@ -41723,7 +41723,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994789123535</v>
+        <v>27.8994808197021</v>
       </c>
       <c r="H1426" t="n">
         <v>102901</v>
@@ -41781,7 +41781,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G1428" t="n">
-        <v>27.2352085113525</v>
+        <v>27.2352066040039</v>
       </c>
       <c r="H1428" t="n">
         <v>56869</v>
@@ -41810,7 +41810,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1429" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1429" t="n">
         <v>76852</v>
@@ -41839,7 +41839,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167530059814</v>
       </c>
       <c r="H1430" t="n">
         <v>75930</v>
@@ -41897,7 +41897,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1432" t="n">
-        <v>26.9768772125244</v>
+        <v>26.976879119873</v>
       </c>
       <c r="H1432" t="n">
         <v>58614</v>
@@ -41926,7 +41926,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="n">
-        <v>26.6262912750244</v>
+        <v>26.6262893676758</v>
       </c>
       <c r="H1433" t="n">
         <v>47937</v>
@@ -41955,7 +41955,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167568206787</v>
+        <v>27.2167530059814</v>
       </c>
       <c r="H1434" t="n">
         <v>37007</v>
@@ -41984,7 +41984,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1435" t="n">
-        <v>27.2536602020264</v>
+        <v>27.2536582946777</v>
       </c>
       <c r="H1435" t="n">
         <v>71855</v>
@@ -42100,7 +42100,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.674467086792</v>
+        <v>28.6744651794434</v>
       </c>
       <c r="H1439" t="n">
         <v>107729</v>
@@ -42303,7 +42303,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1446" t="n">
-        <v>27.0506858825684</v>
+        <v>27.050687789917</v>
       </c>
       <c r="H1446" t="n">
         <v>113229</v>
@@ -42390,7 +42390,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732875823975</v>
+        <v>27.9732913970947</v>
       </c>
       <c r="H1449" t="n">
         <v>79612</v>
@@ -42477,7 +42477,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1452" t="n">
-        <v>28.0840034484863</v>
+        <v>28.0840015411377</v>
       </c>
       <c r="H1452" t="n">
         <v>49417</v>
@@ -42593,7 +42593,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1456" t="n">
-        <v>26.8846168518066</v>
+        <v>26.8846187591553</v>
       </c>
       <c r="H1456" t="n">
         <v>46219</v>
@@ -42622,7 +42622,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1457" t="n">
-        <v>26.9953327178955</v>
+        <v>26.9953308105469</v>
       </c>
       <c r="H1457" t="n">
         <v>157384</v>
@@ -42651,7 +42651,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>26.220344543457</v>
+        <v>26.2203464508057</v>
       </c>
       <c r="H1458" t="n">
         <v>92706</v>
@@ -42738,7 +42738,7 @@
         <v>26.1200008392334</v>
       </c>
       <c r="G1461" t="n">
-        <v>24.0983600616455</v>
+        <v>24.0983619689941</v>
       </c>
       <c r="H1461" t="n">
         <v>131079</v>
@@ -42883,7 +42883,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1466" t="n">
-        <v>23.3418254852295</v>
+        <v>23.3418273925781</v>
       </c>
       <c r="H1466" t="n">
         <v>110737</v>
@@ -42912,7 +42912,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1467" t="n">
-        <v>23.2680168151855</v>
+        <v>23.2680187225342</v>
       </c>
       <c r="H1467" t="n">
         <v>94425</v>
@@ -42941,7 +42941,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1468" t="n">
-        <v>23.3971862792969</v>
+        <v>23.3971843719482</v>
       </c>
       <c r="H1468" t="n">
         <v>76657</v>
@@ -43057,7 +43057,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1472" t="n">
-        <v>24.7441806793213</v>
+        <v>24.7441825866699</v>
       </c>
       <c r="H1472" t="n">
         <v>100651</v>
@@ -43115,7 +43115,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1474" t="n">
-        <v>25.2423896789551</v>
+        <v>25.2423858642578</v>
       </c>
       <c r="H1474" t="n">
         <v>98494</v>
@@ -43231,7 +43231,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763187408447</v>
+        <v>25.0763206481934</v>
       </c>
       <c r="H1478" t="n">
         <v>36215</v>
@@ -43521,7 +43521,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.9287033081055</v>
+        <v>24.9287014007568</v>
       </c>
       <c r="H1488" t="n">
         <v>107665</v>
@@ -43550,7 +43550,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1489" t="n">
-        <v>24.8364410400391</v>
+        <v>24.8364429473877</v>
       </c>
       <c r="H1489" t="n">
         <v>76383</v>
@@ -43637,7 +43637,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1492" t="n">
-        <v>23.8769359588623</v>
+        <v>23.8769340515137</v>
       </c>
       <c r="H1492" t="n">
         <v>42116</v>
@@ -43666,7 +43666,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1493" t="n">
         <v>64503</v>
@@ -43695,7 +43695,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477722167969</v>
+        <v>23.7477741241455</v>
       </c>
       <c r="H1494" t="n">
         <v>81730</v>
@@ -43724,7 +43724,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1495" t="n">
-        <v>23.8769359588623</v>
+        <v>23.8769340515137</v>
       </c>
       <c r="H1495" t="n">
         <v>57339</v>
@@ -43811,7 +43811,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1498" t="n">
-        <v>22.7698173522949</v>
+        <v>22.7698135375977</v>
       </c>
       <c r="H1498" t="n">
         <v>145644</v>
@@ -43869,7 +43869,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>21.8656635284424</v>
+        <v>21.865665435791</v>
       </c>
       <c r="H1500" t="n">
         <v>105201</v>
@@ -43898,7 +43898,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1501" t="n">
         <v>112882</v>
@@ -43927,7 +43927,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841133117676</v>
+        <v>21.8841152191162</v>
       </c>
       <c r="H1502" t="n">
         <v>111017</v>
@@ -44043,7 +44043,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.7364978790283</v>
+        <v>21.736499786377</v>
       </c>
       <c r="H1506" t="n">
         <v>138194</v>
@@ -44072,7 +44072,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="n">
-        <v>21.4597206115723</v>
+        <v>21.4597225189209</v>
       </c>
       <c r="H1507" t="n">
         <v>64711</v>
@@ -44130,7 +44130,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1509" t="n">
         <v>177120</v>
@@ -44188,7 +44188,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.8287620544434</v>
+        <v>21.8287601470947</v>
       </c>
       <c r="H1511" t="n">
         <v>119930</v>
@@ -44246,7 +44246,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.1091289520264</v>
+        <v>21.1091327667236</v>
       </c>
       <c r="H1513" t="n">
         <v>30601</v>
@@ -44304,7 +44304,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525943756104</v>
       </c>
       <c r="H1515" t="n">
         <v>74574</v>
@@ -44333,7 +44333,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311721801758</v>
+        <v>20.1311702728271</v>
       </c>
       <c r="H1516" t="n">
         <v>83075</v>
@@ -44391,7 +44391,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.3156929016113</v>
+        <v>20.31569480896</v>
       </c>
       <c r="H1518" t="n">
         <v>87616</v>
@@ -44420,7 +44420,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.352596282959</v>
+        <v>20.3525943756104</v>
       </c>
       <c r="H1519" t="n">
         <v>105798</v>
@@ -44478,7 +44478,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1521" t="n">
-        <v>21.9948272705078</v>
+        <v>21.9948291778564</v>
       </c>
       <c r="H1521" t="n">
         <v>112637</v>
@@ -44507,7 +44507,7 @@
         <v>24.6599998474121</v>
       </c>
       <c r="G1522" t="n">
-        <v>22.7513637542725</v>
+        <v>22.7513618469238</v>
       </c>
       <c r="H1522" t="n">
         <v>132645</v>
@@ -44536,7 +44536,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.529935836792</v>
+        <v>22.5299396514893</v>
       </c>
       <c r="H1523" t="n">
         <v>282491</v>
@@ -44565,7 +44565,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>22.5114841461182</v>
+        <v>22.5114860534668</v>
       </c>
       <c r="H1524" t="n">
         <v>72450</v>
@@ -44623,7 +44623,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.529935836792</v>
+        <v>22.5299396514893</v>
       </c>
       <c r="H1526" t="n">
         <v>35005</v>
@@ -44652,7 +44652,7 @@
         <v>25.0599994659424</v>
       </c>
       <c r="G1527" t="n">
-        <v>23.1204013824463</v>
+        <v>23.1204032897949</v>
       </c>
       <c r="H1527" t="n">
         <v>87054</v>
@@ -44739,7 +44739,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>22.3085136413574</v>
+        <v>22.3085155487061</v>
       </c>
       <c r="H1530" t="n">
         <v>64510</v>
@@ -44768,7 +44768,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>22.5114841461182</v>
+        <v>22.5114860534668</v>
       </c>
       <c r="H1531" t="n">
         <v>40554</v>
@@ -44855,7 +44855,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1534" t="n">
         <v>52052</v>
@@ -44884,7 +44884,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1535" t="n">
         <v>65819</v>
@@ -44913,7 +44913,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.8472137451172</v>
+        <v>21.8472118377686</v>
       </c>
       <c r="H1536" t="n">
         <v>64304</v>
@@ -45000,7 +45000,7 @@
         <v>23.3400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>21.5335292816162</v>
+        <v>21.5335273742676</v>
       </c>
       <c r="H1539" t="n">
         <v>67442</v>
@@ -45087,7 +45087,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.928201675415</v>
+        <v>19.9281997680664</v>
       </c>
       <c r="H1542" t="n">
         <v>354066</v>
@@ -45145,7 +45145,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.7954483032227</v>
+        <v>20.795446395874</v>
       </c>
       <c r="H1544" t="n">
         <v>73711</v>
@@ -45174,7 +45174,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877067565918</v>
+        <v>20.8877086639404</v>
       </c>
       <c r="H1545" t="n">
         <v>65560</v>
@@ -45261,7 +45261,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1548" t="n">
-        <v>21.312105178833</v>
+        <v>21.3121032714844</v>
       </c>
       <c r="H1548" t="n">
         <v>71843</v>
@@ -45348,7 +45348,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1551" t="n">
-        <v>20.4448566436768</v>
+        <v>20.4448585510254</v>
       </c>
       <c r="H1551" t="n">
         <v>52484</v>
@@ -45435,7 +45435,7 @@
         <v>22.5599994659424</v>
       </c>
       <c r="G1554" t="n">
-        <v>20.8138961791992</v>
+        <v>20.8138980865479</v>
       </c>
       <c r="H1554" t="n">
         <v>258855</v>
@@ -45522,7 +45522,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.9835548400879</v>
+        <v>19.9835567474365</v>
       </c>
       <c r="H1557" t="n">
         <v>232143</v>
@@ -45551,7 +45551,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1558" t="n">
-        <v>20.5002117156982</v>
+        <v>20.5002136230469</v>
       </c>
       <c r="H1558" t="n">
         <v>125638</v>
@@ -45609,7 +45609,7 @@
         <v>22.0799999237061</v>
       </c>
       <c r="G1560" t="n">
-        <v>20.3710498809814</v>
+        <v>20.3710479736328</v>
       </c>
       <c r="H1560" t="n">
         <v>107999</v>
@@ -45638,7 +45638,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1561" t="n">
-        <v>20.0204601287842</v>
+        <v>20.0204620361328</v>
       </c>
       <c r="H1561" t="n">
         <v>57646</v>
@@ -45667,7 +45667,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.9871463775635</v>
+        <v>18.9871444702148</v>
       </c>
       <c r="H1562" t="n">
         <v>163561</v>
@@ -45696,7 +45696,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.9871463775635</v>
+        <v>18.9871444702148</v>
       </c>
       <c r="H1563" t="n">
         <v>75921</v>
@@ -45725,7 +45725,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.5073947906494</v>
+        <v>18.5073909759521</v>
       </c>
       <c r="H1564" t="n">
         <v>48417</v>
@@ -45754,7 +45754,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770515441895</v>
+        <v>17.6770534515381</v>
       </c>
       <c r="H1565" t="n">
         <v>135742</v>
@@ -45783,7 +45783,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.1291236877441</v>
+        <v>18.1291255950928</v>
       </c>
       <c r="H1566" t="n">
         <v>145527</v>
@@ -45841,7 +45841,7 @@
         <v>18.5</v>
       </c>
       <c r="G1568" t="n">
-        <v>17.0681343078613</v>
+        <v>17.06813621521</v>
       </c>
       <c r="H1568" t="n">
         <v>50689</v>
@@ -45870,7 +45870,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633670806885</v>
+        <v>17.3633651733398</v>
       </c>
       <c r="H1569" t="n">
         <v>50964</v>
@@ -45928,7 +45928,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033016204834</v>
+        <v>14.5033025741577</v>
       </c>
       <c r="H1571" t="n">
         <v>197519</v>
@@ -45957,7 +45957,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>15.0845403671265</v>
+        <v>15.0845413208008</v>
       </c>
       <c r="H1572" t="n">
         <v>244822</v>
@@ -45986,7 +45986,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>15.23215675354</v>
+        <v>15.2321557998657</v>
       </c>
       <c r="H1573" t="n">
         <v>154625</v>
@@ -46044,7 +46044,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.1583490371704</v>
+        <v>15.1583480834961</v>
       </c>
       <c r="H1575" t="n">
         <v>113410</v>
@@ -46073,7 +46073,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1576" t="n">
-        <v>15.370548248291</v>
+        <v>15.3705463409424</v>
       </c>
       <c r="H1576" t="n">
         <v>128639</v>
@@ -46102,7 +46102,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.2377910614014</v>
+        <v>16.2377948760986</v>
       </c>
       <c r="H1577" t="n">
         <v>111126</v>
@@ -46160,7 +46160,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.2172937393188</v>
+        <v>14.2172946929932</v>
       </c>
       <c r="H1579" t="n">
         <v>614742</v>
@@ -46218,7 +46218,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.337233543396</v>
+        <v>14.3372325897217</v>
       </c>
       <c r="H1581" t="n">
         <v>304440</v>
@@ -46247,7 +46247,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878213882446</v>
+        <v>14.6878223419189</v>
       </c>
       <c r="H1582" t="n">
         <v>163036</v>
@@ -46334,7 +46334,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634258270264</v>
+        <v>14.2634248733521</v>
       </c>
       <c r="H1585" t="n">
         <v>112266</v>
@@ -46421,7 +46421,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.8226222991943</v>
+        <v>15.82262134552</v>
       </c>
       <c r="H1588" t="n">
         <v>261661</v>
@@ -46537,7 +46537,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.0753154754639</v>
+        <v>15.0753145217896</v>
       </c>
       <c r="H1592" t="n">
         <v>140875</v>
@@ -46595,7 +46595,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021240234375</v>
+        <v>13.8021230697632</v>
       </c>
       <c r="H1594" t="n">
         <v>167595</v>
@@ -46653,7 +46653,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.0327749252319</v>
+        <v>14.0327739715576</v>
       </c>
       <c r="H1596" t="n">
         <v>72466</v>
@@ -46682,7 +46682,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.0420017242432</v>
+        <v>14.0420007705688</v>
       </c>
       <c r="H1597" t="n">
         <v>49196</v>
@@ -46711,7 +46711,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.99587059021</v>
+        <v>13.9958715438843</v>
       </c>
       <c r="H1598" t="n">
         <v>55239</v>
@@ -46798,7 +46798,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497394561768</v>
+        <v>13.9497404098511</v>
       </c>
       <c r="H1601" t="n">
         <v>45680</v>
@@ -46856,7 +46856,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247266769409</v>
+        <v>14.7247247695923</v>
       </c>
       <c r="H1603" t="n">
         <v>73059</v>
@@ -46914,7 +46914,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.8667058944702</v>
+        <v>13.8667068481445</v>
       </c>
       <c r="H1605" t="n">
         <v>46964</v>
@@ -46943,7 +46943,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G1606" t="n">
-        <v>13.6176042556763</v>
+        <v>13.617603302002</v>
       </c>
       <c r="H1606" t="n">
         <v>94220</v>
@@ -47059,7 +47059,7 @@
         <v>15</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8390274047852</v>
+        <v>13.8390283584595</v>
       </c>
       <c r="H1610" t="n">
         <v>78749</v>
@@ -47146,7 +47146,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.2854671478271</v>
+        <v>13.2854681015015</v>
       </c>
       <c r="H1613" t="n">
         <v>58779</v>
@@ -47262,7 +47262,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1617" t="n">
-        <v>13.3592739105225</v>
+        <v>13.3592748641968</v>
       </c>
       <c r="H1617" t="n">
         <v>66051</v>
@@ -47291,7 +47291,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961801528931</v>
+        <v>13.3961791992188</v>
       </c>
       <c r="H1618" t="n">
         <v>99070</v>
@@ -47349,7 +47349,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476369857788</v>
+        <v>15.0476360321045</v>
       </c>
       <c r="H1620" t="n">
         <v>154501</v>
@@ -47378,7 +47378,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1621" t="n">
-        <v>15.8318462371826</v>
+        <v>15.8318471908569</v>
       </c>
       <c r="H1621" t="n">
         <v>131752</v>
@@ -47407,7 +47407,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.3059663772583</v>
+        <v>15.305965423584</v>
       </c>
       <c r="H1622" t="n">
         <v>88717</v>
@@ -47465,7 +47465,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384111404419</v>
+        <v>15.0384092330933</v>
       </c>
       <c r="H1624" t="n">
         <v>74404</v>
@@ -47523,7 +47523,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>14.7736368179321</v>
+        <v>14.7736358642578</v>
       </c>
       <c r="H1626" t="n">
         <v>61617</v>
@@ -47697,7 +47697,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.7137775421143</v>
+        <v>15.7137765884399</v>
       </c>
       <c r="H1632" t="n">
         <v>66096</v>
@@ -47755,7 +47755,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.780930519104</v>
+        <v>15.7809314727783</v>
       </c>
       <c r="H1634" t="n">
         <v>37135</v>
@@ -47784,7 +47784,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.0303535461426</v>
+        <v>16.0303554534912</v>
       </c>
       <c r="H1635" t="n">
         <v>43698</v>
@@ -47900,7 +47900,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1639" t="n">
-        <v>14.5529909133911</v>
+        <v>14.5529918670654</v>
       </c>
       <c r="H1639" t="n">
         <v>89694</v>
@@ -47958,7 +47958,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="n">
-        <v>13.5456981658936</v>
+        <v>13.5456972122192</v>
       </c>
       <c r="H1641" t="n">
         <v>86532</v>
@@ -47987,7 +47987,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>13.843090057373</v>
+        <v>13.8430891036987</v>
       </c>
       <c r="H1642" t="n">
         <v>116898</v>
@@ -48045,7 +48045,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1644" t="n">
-        <v>13.1427803039551</v>
+        <v>13.1427793502808</v>
       </c>
       <c r="H1644" t="n">
         <v>169292</v>
@@ -48161,7 +48161,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1648" t="n">
-        <v>12.4040994644165</v>
+        <v>12.4040985107422</v>
       </c>
       <c r="H1648" t="n">
         <v>78173</v>
@@ -48277,7 +48277,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="n">
-        <v>12.5959644317627</v>
+        <v>12.5959634780884</v>
       </c>
       <c r="H1652" t="n">
         <v>94645</v>
@@ -48364,7 +48364,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.7805366516113</v>
+        <v>11.780535697937</v>
       </c>
       <c r="H1655" t="n">
         <v>68390</v>
@@ -48393,7 +48393,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1656" t="n">
-        <v>11.5502986907959</v>
+        <v>11.5502977371216</v>
       </c>
       <c r="H1656" t="n">
         <v>106176</v>
@@ -48451,7 +48451,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="n">
-        <v>12.6247434616089</v>
+        <v>12.6247444152832</v>
       </c>
       <c r="H1658" t="n">
         <v>79138</v>
@@ -48480,7 +48480,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>13.0468473434448</v>
+        <v>13.0468482971191</v>
       </c>
       <c r="H1659" t="n">
         <v>65276</v>
@@ -48741,7 +48741,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="n">
-        <v>13.0468473434448</v>
+        <v>13.0468482971191</v>
       </c>
       <c r="H1668" t="n">
         <v>63442</v>
@@ -48770,7 +48770,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>13.1044082641602</v>
+        <v>13.1044073104858</v>
       </c>
       <c r="H1669" t="n">
         <v>22290</v>
@@ -49002,7 +49002,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.3154602050781</v>
+        <v>13.3154592514038</v>
       </c>
       <c r="H1677" t="n">
         <v>61589</v>
@@ -49031,7 +49031,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.1044082641602</v>
+        <v>13.1044073104858</v>
       </c>
       <c r="H1678" t="n">
         <v>78688</v>
@@ -49089,7 +49089,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1680" t="n">
-        <v>12.6055574417114</v>
+        <v>12.6055583953857</v>
       </c>
       <c r="H1680" t="n">
         <v>65707</v>
@@ -49205,7 +49205,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="n">
-        <v>12.6247434616089</v>
+        <v>12.6247444152832</v>
       </c>
       <c r="H1684" t="n">
         <v>34970</v>
@@ -49321,7 +49321,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1688" t="n">
-        <v>12.2506055831909</v>
+        <v>12.2506065368652</v>
       </c>
       <c r="H1688" t="n">
         <v>46659</v>
@@ -49350,7 +49350,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>11.7805366516113</v>
+        <v>11.780535697937</v>
       </c>
       <c r="H1689" t="n">
         <v>75821</v>
@@ -49466,7 +49466,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="n">
-        <v>12.2218265533447</v>
+        <v>12.2218255996704</v>
       </c>
       <c r="H1693" t="n">
         <v>114156</v>
@@ -49553,7 +49553,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1696" t="n">
-        <v>12.1834526062012</v>
+        <v>12.1834535598755</v>
       </c>
       <c r="H1696" t="n">
         <v>51664</v>
@@ -49727,7 +49727,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="n">
-        <v>11.3296527862549</v>
+        <v>11.3296518325806</v>
       </c>
       <c r="H1702" t="n">
         <v>48994</v>
@@ -49756,7 +49756,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="n">
-        <v>11.6654176712036</v>
+        <v>11.6654167175293</v>
       </c>
       <c r="H1703" t="n">
         <v>48478</v>
@@ -49785,7 +49785,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G1704" t="n">
-        <v>12.1354856491089</v>
+        <v>12.1354866027832</v>
       </c>
       <c r="H1704" t="n">
         <v>69346</v>
@@ -50017,7 +50017,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="n">
-        <v>11.2720928192139</v>
+        <v>11.2720937728882</v>
       </c>
       <c r="H1712" t="n">
         <v>57229</v>
@@ -50162,7 +50162,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.754056930542</v>
+        <v>10.7540559768677</v>
       </c>
       <c r="H1717" t="n">
         <v>47037</v>
@@ -50220,7 +50220,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="n">
-        <v>11.1090059280396</v>
+        <v>11.1090068817139</v>
       </c>
       <c r="H1719" t="n">
         <v>38067</v>
@@ -50249,7 +50249,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.6654176712036</v>
+        <v>11.6654167175293</v>
       </c>
       <c r="H1720" t="n">
         <v>60827</v>
@@ -50278,7 +50278,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1721" t="n">
-        <v>11.4159908294678</v>
+        <v>11.4159917831421</v>
       </c>
       <c r="H1721" t="n">
         <v>31311</v>
@@ -50336,7 +50336,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.5694856643677</v>
+        <v>11.5694847106934</v>
       </c>
       <c r="H1723" t="n">
         <v>30512</v>
@@ -50365,7 +50365,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1724" t="n">
-        <v>11.5790767669678</v>
+        <v>11.5790777206421</v>
       </c>
       <c r="H1724" t="n">
         <v>33530</v>
@@ -50423,7 +50423,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.2720928192139</v>
+        <v>11.2720937728882</v>
       </c>
       <c r="H1726" t="n">
         <v>45721</v>
@@ -50481,7 +50481,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.6654176712036</v>
+        <v>11.6654167175293</v>
       </c>
       <c r="H1728" t="n">
         <v>31281</v>
@@ -50510,7 +50510,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.8764686584473</v>
+        <v>11.8764696121216</v>
       </c>
       <c r="H1729" t="n">
         <v>26291</v>
@@ -50771,7 +50771,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="n">
-        <v>13.2003412246704</v>
+        <v>13.2003402709961</v>
       </c>
       <c r="H1738" t="n">
         <v>77128</v>
@@ -50800,7 +50800,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1739" t="n">
-        <v>11.6941957473755</v>
+        <v>11.6941967010498</v>
       </c>
       <c r="H1739" t="n">
         <v>447229</v>
@@ -50945,7 +50945,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1744" t="n">
-        <v>11.5790767669678</v>
+        <v>11.5790777206421</v>
       </c>
       <c r="H1744" t="n">
         <v>105065</v>
@@ -51061,7 +51061,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.7398624420166</v>
+        <v>12.7398633956909</v>
       </c>
       <c r="H1748" t="n">
         <v>160134</v>
@@ -51119,7 +51119,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.5959644317627</v>
+        <v>12.5959634780884</v>
       </c>
       <c r="H1750" t="n">
         <v>92825</v>
@@ -51148,7 +51148,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.2889804840088</v>
+        <v>12.2889795303345</v>
       </c>
       <c r="H1751" t="n">
         <v>103263</v>
@@ -51235,7 +51235,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930465698242</v>
+        <v>12.1930475234985</v>
       </c>
       <c r="H1754" t="n">
         <v>93258</v>
@@ -51264,7 +51264,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1755" t="n">
-        <v>12.2506055831909</v>
+        <v>12.2506065368652</v>
       </c>
       <c r="H1755" t="n">
         <v>28199</v>
@@ -51409,7 +51409,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1760" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H1760" t="n">
         <v>57784</v>
@@ -51496,7 +51496,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="n">
-        <v>12.7398624420166</v>
+        <v>12.7398633956909</v>
       </c>
       <c r="H1763" t="n">
         <v>76238</v>
@@ -51786,7 +51786,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1773" t="n">
-        <v>12.1834526062012</v>
+        <v>12.1834535598755</v>
       </c>
       <c r="H1773" t="n">
         <v>45619</v>
@@ -51815,7 +51815,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G1774" t="n">
-        <v>12.106707572937</v>
+        <v>12.1067066192627</v>
       </c>
       <c r="H1774" t="n">
         <v>28745</v>
@@ -51844,7 +51844,7 @@
         <v>12.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.9915885925293</v>
+        <v>11.991587638855</v>
       </c>
       <c r="H1775" t="n">
         <v>63441</v>
@@ -51931,7 +51931,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1778" t="n">
-        <v>12.0395536422729</v>
+        <v>12.0395545959473</v>
       </c>
       <c r="H1778" t="n">
         <v>24126</v>
@@ -52105,7 +52105,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.5000314712524</v>
+        <v>12.5000305175781</v>
       </c>
       <c r="H1784" t="n">
         <v>49900</v>
@@ -52308,7 +52308,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1791" t="n">
-        <v>13.7663431167603</v>
+        <v>13.7663440704346</v>
       </c>
       <c r="H1791" t="n">
         <v>71163</v>
@@ -52424,7 +52424,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.2364130020142</v>
+        <v>14.2364139556885</v>
       </c>
       <c r="H1795" t="n">
         <v>65651</v>
@@ -52453,7 +52453,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1796" t="n">
-        <v>13.7855281829834</v>
+        <v>13.7855291366577</v>
       </c>
       <c r="H1796" t="n">
         <v>52655</v>
@@ -52482,7 +52482,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.8143091201782</v>
+        <v>13.8143100738525</v>
       </c>
       <c r="H1797" t="n">
         <v>40053</v>
@@ -52511,7 +52511,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1798" t="n">
-        <v>13.8143091201782</v>
+        <v>13.8143100738525</v>
       </c>
       <c r="H1798" t="n">
         <v>44811</v>
@@ -52627,7 +52627,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1802" t="n">
-        <v>14.3707180023193</v>
+        <v>14.3707189559937</v>
       </c>
       <c r="H1802" t="n">
         <v>61789</v>
@@ -52685,7 +52685,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G1804" t="n">
-        <v>14.1692609786987</v>
+        <v>14.1692600250244</v>
       </c>
       <c r="H1804" t="n">
         <v>86857</v>
@@ -52743,7 +52743,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463157653809</v>
+        <v>14.9463148117065</v>
       </c>
       <c r="H1806" t="n">
         <v>121708</v>
@@ -52772,7 +52772,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1807" t="n">
-        <v>14.7736368179321</v>
+        <v>14.7736358642578</v>
       </c>
       <c r="H1807" t="n">
         <v>83586</v>
@@ -52830,7 +52830,7 @@
         <v>15</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.3899049758911</v>
+        <v>14.3899059295654</v>
       </c>
       <c r="H1809" t="n">
         <v>55734</v>
@@ -53004,7 +53004,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1815" t="n">
-        <v>14.5721778869629</v>
+        <v>14.5721769332886</v>
       </c>
       <c r="H1815" t="n">
         <v>43434</v>
@@ -53062,7 +53062,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.5721778869629</v>
+        <v>14.5721769332886</v>
       </c>
       <c r="H1817" t="n">
         <v>85926</v>
@@ -53120,7 +53120,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1819" t="n">
-        <v>14.5721778869629</v>
+        <v>14.5721769332886</v>
       </c>
       <c r="H1819" t="n">
         <v>79210</v>
@@ -53178,7 +53178,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1821" t="n">
-        <v>16.0879135131836</v>
+        <v>16.0879154205322</v>
       </c>
       <c r="H1821" t="n">
         <v>460810</v>
@@ -53207,7 +53207,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.8288974761963</v>
+        <v>15.8288955688477</v>
       </c>
       <c r="H1822" t="n">
         <v>177332</v>
@@ -53236,7 +53236,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1823" t="n">
-        <v>16.2510013580322</v>
+        <v>16.2509994506836</v>
       </c>
       <c r="H1823" t="n">
         <v>168955</v>
@@ -53294,7 +53294,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1825" t="n">
-        <v>16.7210712432861</v>
+        <v>16.7210693359375</v>
       </c>
       <c r="H1825" t="n">
         <v>176367</v>
@@ -53381,7 +53381,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1828" t="n">
-        <v>16.2030353546143</v>
+        <v>16.2030334472656</v>
       </c>
       <c r="H1828" t="n">
         <v>59759</v>
@@ -53468,7 +53468,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1831" t="n">
-        <v>16.2030353546143</v>
+        <v>16.2030334472656</v>
       </c>
       <c r="H1831" t="n">
         <v>39708</v>
@@ -53526,7 +53526,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.3588266372681</v>
+        <v>15.3588256835938</v>
       </c>
       <c r="H1833" t="n">
         <v>142239</v>
@@ -53555,7 +53555,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1834" t="n">
-        <v>16.0783195495605</v>
+        <v>16.0783214569092</v>
       </c>
       <c r="H1834" t="n">
         <v>161635</v>
@@ -53729,7 +53729,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1840" t="n">
-        <v>14.639331817627</v>
+        <v>14.6393308639526</v>
       </c>
       <c r="H1840" t="n">
         <v>102978</v>
@@ -53758,7 +53758,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1841" t="n">
-        <v>14.5529909133911</v>
+        <v>14.5529918670654</v>
       </c>
       <c r="H1841" t="n">
         <v>102046</v>
@@ -53787,7 +53787,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.1308879852295</v>
+        <v>14.1308870315552</v>
       </c>
       <c r="H1842" t="n">
         <v>109542</v>
@@ -53845,7 +53845,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1844" t="n">
-        <v>13.9486150741577</v>
+        <v>13.948616027832</v>
       </c>
       <c r="H1844" t="n">
         <v>54799</v>
@@ -54019,7 +54019,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="n">
-        <v>13.5456981658936</v>
+        <v>13.5456972122192</v>
       </c>
       <c r="H1850" t="n">
         <v>60451</v>
@@ -54135,7 +54135,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1854" t="n">
-        <v>13.4593572616577</v>
+        <v>13.459358215332</v>
       </c>
       <c r="H1854" t="n">
         <v>46148</v>
@@ -54222,7 +54222,7 @@
         <v>14</v>
       </c>
       <c r="G1857" t="n">
-        <v>13.4305791854858</v>
+        <v>13.4305782318115</v>
       </c>
       <c r="H1857" t="n">
         <v>134657</v>
@@ -54396,7 +54396,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G1863" t="n">
-        <v>12.9701013565063</v>
+        <v>12.9701023101807</v>
       </c>
       <c r="H1863" t="n">
         <v>106326</v>
@@ -54454,7 +54454,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2578992843628</v>
+        <v>13.2578983306885</v>
       </c>
       <c r="H1865" t="n">
         <v>39502</v>
@@ -54512,7 +54512,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1867" t="n">
-        <v>13.027660369873</v>
+        <v>13.0276613235474</v>
       </c>
       <c r="H1867" t="n">
         <v>39070</v>
@@ -80096,6 +80096,35 @@
         <v>116915</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>3.92499995231628</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>4.05999994277954</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>3.92000007629395</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>4.03999996185303</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>90949</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BSS.MI.xlsx
+++ b/data/BSS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>15.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2523984909058</v>
+        <v>13.2523975372314</v>
       </c>
       <c r="H2" t="n">
         <v>87173</v>
@@ -572,7 +572,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G7" t="n">
-        <v>12.243504524231</v>
+        <v>12.2435054779053</v>
       </c>
       <c r="H7" t="n">
         <v>86270</v>
@@ -630,7 +630,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G9" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409063339233</v>
       </c>
       <c r="H9" t="n">
         <v>34417</v>
@@ -659,7 +659,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G10" t="n">
-        <v>11.4825601577759</v>
+        <v>11.4825611114502</v>
       </c>
       <c r="H10" t="n">
         <v>137481</v>
@@ -688,7 +688,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G11" t="n">
-        <v>10.8584156036377</v>
+        <v>10.858416557312</v>
       </c>
       <c r="H11" t="n">
         <v>191378</v>
@@ -717,7 +717,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>9.79822444915771</v>
+        <v>9.79822540283203</v>
       </c>
       <c r="H12" t="n">
         <v>322059</v>
@@ -833,7 +833,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2941198348999</v>
+        <v>10.2941207885742</v>
       </c>
       <c r="H16" t="n">
         <v>136366</v>
@@ -920,7 +920,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G19" t="n">
-        <v>10.7301683425903</v>
+        <v>10.7301664352417</v>
       </c>
       <c r="H19" t="n">
         <v>71825</v>
@@ -949,7 +949,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G20" t="n">
-        <v>10.576268196106</v>
+        <v>10.5762691497803</v>
       </c>
       <c r="H20" t="n">
         <v>57072</v>
@@ -1036,7 +1036,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1915225982666</v>
+        <v>10.1915216445923</v>
       </c>
       <c r="H23" t="n">
         <v>90616</v>
@@ -1065,7 +1065,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4565687179565</v>
+        <v>10.4565677642822</v>
       </c>
       <c r="H24" t="n">
         <v>157219</v>
@@ -1094,7 +1094,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4907684326172</v>
+        <v>10.4907703399658</v>
       </c>
       <c r="H25" t="n">
         <v>150192</v>
@@ -1152,7 +1152,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G27" t="n">
-        <v>9.03728103637695</v>
+        <v>9.03728008270264</v>
       </c>
       <c r="H27" t="n">
         <v>127617</v>
@@ -1181,7 +1181,7 @@
         <v>10.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.97743129730225</v>
+        <v>8.97743034362793</v>
       </c>
       <c r="H28" t="n">
         <v>172224</v>
@@ -1210,7 +1210,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>9.40492820739746</v>
+        <v>9.40492725372314</v>
       </c>
       <c r="H29" t="n">
         <v>104278</v>
@@ -1239,7 +1239,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G30" t="n">
-        <v>9.14842987060547</v>
+        <v>9.14842891693115</v>
       </c>
       <c r="H30" t="n">
         <v>114215</v>
@@ -1326,7 +1326,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>9.66142559051514</v>
+        <v>9.66142654418945</v>
       </c>
       <c r="H33" t="n">
         <v>39366</v>
@@ -1384,7 +1384,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>10.345419883728</v>
+        <v>10.3454208374023</v>
       </c>
       <c r="H35" t="n">
         <v>81482</v>
@@ -1471,7 +1471,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G38" t="n">
-        <v>10.5506172180176</v>
+        <v>10.5506181716919</v>
       </c>
       <c r="H38" t="n">
         <v>97952</v>
@@ -1500,7 +1500,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>10.2257204055786</v>
+        <v>10.2257213592529</v>
       </c>
       <c r="H39" t="n">
         <v>73018</v>
@@ -1529,7 +1529,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G40" t="n">
-        <v>10.1829710006714</v>
+        <v>10.1829719543457</v>
       </c>
       <c r="H40" t="n">
         <v>68122</v>
@@ -1587,7 +1587,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G42" t="n">
-        <v>10.9097166061401</v>
+        <v>10.9097156524658</v>
       </c>
       <c r="H42" t="n">
         <v>105720</v>
@@ -1674,7 +1674,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G45" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H45" t="n">
         <v>110221</v>
@@ -1703,7 +1703,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G46" t="n">
-        <v>11.7732601165771</v>
+        <v>11.7732582092285</v>
       </c>
       <c r="H46" t="n">
         <v>75412</v>
@@ -1790,7 +1790,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G49" t="n">
-        <v>11.371413230896</v>
+        <v>11.3714122772217</v>
       </c>
       <c r="H49" t="n">
         <v>73494</v>
@@ -1819,7 +1819,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G50" t="n">
-        <v>11.3799629211426</v>
+        <v>11.3799619674683</v>
       </c>
       <c r="H50" t="n">
         <v>138699</v>
@@ -1848,7 +1848,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G51" t="n">
-        <v>11.6621112823486</v>
+        <v>11.6621103286743</v>
       </c>
       <c r="H51" t="n">
         <v>99643</v>
@@ -1877,7 +1877,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8416604995728</v>
+        <v>11.8416585922241</v>
       </c>
       <c r="H52" t="n">
         <v>101508</v>
@@ -1906,7 +1906,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G53" t="n">
-        <v>11.9186067581177</v>
+        <v>11.9186086654663</v>
       </c>
       <c r="H53" t="n">
         <v>56813</v>
@@ -1935,7 +1935,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G54" t="n">
-        <v>11.7989091873169</v>
+        <v>11.7989082336426</v>
       </c>
       <c r="H54" t="n">
         <v>67817</v>
@@ -1964,7 +1964,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G55" t="n">
-        <v>12.0468587875366</v>
+        <v>12.0468559265137</v>
       </c>
       <c r="H55" t="n">
         <v>93874</v>
@@ -2051,7 +2051,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G58" t="n">
-        <v>12.3375549316406</v>
+        <v>12.3375539779663</v>
       </c>
       <c r="H58" t="n">
         <v>61525</v>
@@ -2080,7 +2080,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409063339233</v>
       </c>
       <c r="H59" t="n">
         <v>40540</v>
@@ -2138,7 +2138,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G61" t="n">
-        <v>12.1665573120117</v>
+        <v>12.1665563583374</v>
       </c>
       <c r="H61" t="n">
         <v>40779</v>
@@ -2167,7 +2167,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>12.1067066192627</v>
+        <v>12.106707572937</v>
       </c>
       <c r="H62" t="n">
         <v>55469</v>
@@ -2196,7 +2196,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G63" t="n">
-        <v>12.2178554534912</v>
+        <v>12.2178564071655</v>
       </c>
       <c r="H63" t="n">
         <v>42659</v>
@@ -2225,7 +2225,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G64" t="n">
-        <v>11.9015092849731</v>
+        <v>11.9015083312988</v>
       </c>
       <c r="H64" t="n">
         <v>46495</v>
@@ -2254,7 +2254,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G65" t="n">
-        <v>12.140905380249</v>
+        <v>12.1409063339233</v>
       </c>
       <c r="H65" t="n">
         <v>58858</v>
@@ -2283,7 +2283,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>11.7989091873169</v>
+        <v>11.7989082336426</v>
       </c>
       <c r="H66" t="n">
         <v>51960</v>
@@ -2312,7 +2312,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5680599212646</v>
+        <v>11.5680618286133</v>
       </c>
       <c r="H67" t="n">
         <v>44037</v>
@@ -2370,7 +2370,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G69" t="n">
-        <v>11.7390594482422</v>
+        <v>11.7390584945679</v>
       </c>
       <c r="H69" t="n">
         <v>55839</v>
@@ -2428,7 +2428,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5680599212646</v>
+        <v>11.5680618286133</v>
       </c>
       <c r="H71" t="n">
         <v>41497</v>
@@ -2457,7 +2457,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G72" t="n">
-        <v>11.6621112823486</v>
+        <v>11.6621103286743</v>
       </c>
       <c r="H72" t="n">
         <v>25570</v>
@@ -2486,7 +2486,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>11.8160076141357</v>
+        <v>11.8160095214844</v>
       </c>
       <c r="H73" t="n">
         <v>56893</v>
@@ -2515,7 +2515,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G74" t="n">
-        <v>11.7048606872559</v>
+        <v>11.7048587799072</v>
       </c>
       <c r="H74" t="n">
         <v>28658</v>
@@ -2544,7 +2544,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G75" t="n">
-        <v>11.6022596359253</v>
+        <v>11.6022615432739</v>
       </c>
       <c r="H75" t="n">
         <v>40113</v>
@@ -2573,7 +2573,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G76" t="n">
-        <v>11.6621112823486</v>
+        <v>11.6621103286743</v>
       </c>
       <c r="H76" t="n">
         <v>47170</v>
@@ -2602,7 +2602,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>11.6364612579346</v>
+        <v>11.6364603042603</v>
       </c>
       <c r="H77" t="n">
         <v>21274</v>
@@ -2718,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="G81" t="n">
-        <v>11.1149139404297</v>
+        <v>11.1149129867554</v>
       </c>
       <c r="H81" t="n">
         <v>44600</v>
@@ -2747,7 +2747,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G82" t="n">
-        <v>11.3799629211426</v>
+        <v>11.3799619674683</v>
       </c>
       <c r="H82" t="n">
         <v>42005</v>
@@ -2834,7 +2834,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1576633453369</v>
+        <v>11.1576642990112</v>
       </c>
       <c r="H85" t="n">
         <v>20515</v>
@@ -2921,7 +2921,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1405639648438</v>
+        <v>11.1405649185181</v>
       </c>
       <c r="H88" t="n">
         <v>30374</v>
@@ -2979,7 +2979,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>10.9541397094727</v>
+        <v>10.954140663147</v>
       </c>
       <c r="H90" t="n">
         <v>55438</v>
@@ -3008,7 +3008,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>10.4346122741699</v>
+        <v>10.4346132278442</v>
       </c>
       <c r="H91" t="n">
         <v>102250</v>
@@ -3037,7 +3037,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G92" t="n">
-        <v>10.3553619384766</v>
+        <v>10.3553638458252</v>
       </c>
       <c r="H92" t="n">
         <v>41348</v>
@@ -3066,7 +3066,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G93" t="n">
-        <v>10.4346122741699</v>
+        <v>10.4346132278442</v>
       </c>
       <c r="H93" t="n">
         <v>49691</v>
@@ -3153,7 +3153,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G96" t="n">
-        <v>9.92388916015625</v>
+        <v>9.92388820648193</v>
       </c>
       <c r="H96" t="n">
         <v>101148</v>
@@ -3182,7 +3182,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G97" t="n">
-        <v>10.3201389312744</v>
+        <v>10.3201398849487</v>
       </c>
       <c r="H97" t="n">
         <v>37803</v>
@@ -3240,7 +3240,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G99" t="n">
-        <v>10.3025283813477</v>
+        <v>10.3025274276733</v>
       </c>
       <c r="H99" t="n">
         <v>48962</v>
@@ -3269,7 +3269,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H100" t="n">
         <v>39045</v>
@@ -3327,7 +3327,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G102" t="n">
-        <v>11.4120311737061</v>
+        <v>11.4120302200317</v>
       </c>
       <c r="H102" t="n">
         <v>156693</v>
@@ -3356,7 +3356,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302518844604</v>
       </c>
       <c r="H103" t="n">
         <v>70319</v>
@@ -3385,7 +3385,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G104" t="n">
-        <v>10.9189195632935</v>
+        <v>10.9189176559448</v>
       </c>
       <c r="H104" t="n">
         <v>30153</v>
@@ -3414,7 +3414,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>11.2359199523926</v>
+        <v>11.2359209060669</v>
       </c>
       <c r="H105" t="n">
         <v>13082</v>
@@ -3443,7 +3443,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G106" t="n">
-        <v>11.2799472808838</v>
+        <v>11.2799482345581</v>
       </c>
       <c r="H106" t="n">
         <v>56529</v>
@@ -3472,7 +3472,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G107" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302518844604</v>
       </c>
       <c r="H107" t="n">
         <v>63256</v>
@@ -3559,7 +3559,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>10.8396682739258</v>
+        <v>10.8396692276001</v>
       </c>
       <c r="H110" t="n">
         <v>35136</v>
@@ -3646,7 +3646,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G113" t="n">
-        <v>10.8132514953613</v>
+        <v>10.8132524490356</v>
       </c>
       <c r="H113" t="n">
         <v>12086</v>
@@ -3675,7 +3675,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G114" t="n">
-        <v>10.5138635635376</v>
+        <v>10.5138626098633</v>
       </c>
       <c r="H114" t="n">
         <v>43277</v>
@@ -3704,7 +3704,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G115" t="n">
-        <v>10.0647764205933</v>
+        <v>10.0647783279419</v>
       </c>
       <c r="H115" t="n">
         <v>60966</v>
@@ -3791,7 +3791,7 @@
         <v>11</v>
       </c>
       <c r="G118" t="n">
-        <v>9.68613815307617</v>
+        <v>9.68613910675049</v>
       </c>
       <c r="H118" t="n">
         <v>96012</v>
@@ -3820,7 +3820,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>10.0383605957031</v>
+        <v>10.0383596420288</v>
       </c>
       <c r="H119" t="n">
         <v>59338</v>
@@ -3849,7 +3849,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G120" t="n">
-        <v>10.4962520599365</v>
+        <v>10.4962511062622</v>
       </c>
       <c r="H120" t="n">
         <v>43223</v>
@@ -3878,7 +3878,7 @@
         <v>11.75</v>
       </c>
       <c r="G121" t="n">
-        <v>10.3465576171875</v>
+        <v>10.3465566635132</v>
       </c>
       <c r="H121" t="n">
         <v>50694</v>
@@ -3907,7 +3907,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G122" t="n">
-        <v>10.4522228240967</v>
+        <v>10.4522218704224</v>
       </c>
       <c r="H122" t="n">
         <v>40375</v>
@@ -3936,7 +3936,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G123" t="n">
-        <v>10.5843067169189</v>
+        <v>10.5843076705933</v>
       </c>
       <c r="H123" t="n">
         <v>36459</v>
@@ -3994,7 +3994,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G125" t="n">
-        <v>9.12257862091064</v>
+        <v>9.12258052825928</v>
       </c>
       <c r="H125" t="n">
         <v>55022</v>
@@ -4052,7 +4052,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G127" t="n">
-        <v>9.57166576385498</v>
+        <v>9.57166481018066</v>
       </c>
       <c r="H127" t="n">
         <v>24263</v>
@@ -4081,7 +4081,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G128" t="n">
-        <v>9.93269348144531</v>
+        <v>9.93269443511963</v>
       </c>
       <c r="H128" t="n">
         <v>27103</v>
@@ -4110,7 +4110,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1880559921265</v>
+        <v>10.1880550384521</v>
       </c>
       <c r="H129" t="n">
         <v>25733</v>
@@ -4139,7 +4139,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G130" t="n">
-        <v>9.98552703857422</v>
+        <v>9.98552799224854</v>
       </c>
       <c r="H130" t="n">
         <v>15581</v>
@@ -4168,7 +4168,7 @@
         <v>11</v>
       </c>
       <c r="G131" t="n">
-        <v>9.68613815307617</v>
+        <v>9.68613910675049</v>
       </c>
       <c r="H131" t="n">
         <v>15874</v>
@@ -4197,7 +4197,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G132" t="n">
-        <v>9.18421840667725</v>
+        <v>9.18422031402588</v>
       </c>
       <c r="H132" t="n">
         <v>96061</v>
@@ -4226,7 +4226,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G133" t="n">
-        <v>9.14019203186035</v>
+        <v>9.14019107818604</v>
       </c>
       <c r="H133" t="n">
         <v>64369</v>
@@ -4255,7 +4255,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G134" t="n">
-        <v>9.72135925292969</v>
+        <v>9.721360206604</v>
       </c>
       <c r="H134" t="n">
         <v>37896</v>
@@ -4284,7 +4284,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>10.0823888778687</v>
+        <v>10.0823879241943</v>
       </c>
       <c r="H135" t="n">
         <v>34424</v>
@@ -4313,7 +4313,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G136" t="n">
-        <v>10.381778717041</v>
+        <v>10.3817777633667</v>
       </c>
       <c r="H136" t="n">
         <v>45362</v>
@@ -4342,7 +4342,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G137" t="n">
-        <v>10.3201389312744</v>
+        <v>10.3201398849487</v>
       </c>
       <c r="H137" t="n">
         <v>22891</v>
@@ -4371,7 +4371,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G138" t="n">
-        <v>10.2849178314209</v>
+        <v>10.2849168777466</v>
       </c>
       <c r="H138" t="n">
         <v>15768</v>
@@ -4400,7 +4400,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G139" t="n">
-        <v>10.1352233886719</v>
+        <v>10.1352214813232</v>
       </c>
       <c r="H139" t="n">
         <v>7545</v>
@@ -4458,7 +4458,7 @@
         <v>11.5299997329712</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1528329849243</v>
+        <v>10.1528339385986</v>
       </c>
       <c r="H141" t="n">
         <v>23520</v>
@@ -4487,7 +4487,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G142" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H142" t="n">
         <v>53624</v>
@@ -4516,7 +4516,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G143" t="n">
-        <v>10.2496948242188</v>
+        <v>10.2496957778931</v>
       </c>
       <c r="H143" t="n">
         <v>15986</v>
@@ -4574,7 +4574,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>10.3025283813477</v>
+        <v>10.3025274276733</v>
       </c>
       <c r="H145" t="n">
         <v>26846</v>
@@ -4603,7 +4603,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>10.6987781524658</v>
+        <v>10.6987800598145</v>
       </c>
       <c r="H146" t="n">
         <v>35625</v>
@@ -4661,7 +4661,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G148" t="n">
-        <v>11.0157804489136</v>
+        <v>11.0157814025879</v>
       </c>
       <c r="H148" t="n">
         <v>49513</v>
@@ -4690,7 +4690,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>11.0333919525146</v>
+        <v>11.0333909988403</v>
       </c>
       <c r="H149" t="n">
         <v>32061</v>
@@ -4719,7 +4719,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G150" t="n">
-        <v>11.0333919525146</v>
+        <v>11.0333909988403</v>
       </c>
       <c r="H150" t="n">
         <v>31452</v>
@@ -4777,7 +4777,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G152" t="n">
-        <v>10.9893627166748</v>
+        <v>10.9893646240234</v>
       </c>
       <c r="H152" t="n">
         <v>42127</v>
@@ -4806,7 +4806,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>10.8748912811279</v>
+        <v>10.8748903274536</v>
       </c>
       <c r="H153" t="n">
         <v>39269</v>
@@ -4835,7 +4835,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>10.8748912811279</v>
+        <v>10.8748903274536</v>
       </c>
       <c r="H154" t="n">
         <v>23378</v>
@@ -4893,7 +4893,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>11.0950307846069</v>
+        <v>11.0950317382812</v>
       </c>
       <c r="H156" t="n">
         <v>40839</v>
@@ -4922,7 +4922,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G157" t="n">
-        <v>11.2535305023193</v>
+        <v>11.253529548645</v>
       </c>
       <c r="H157" t="n">
         <v>72265</v>
@@ -4951,7 +4951,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G158" t="n">
-        <v>11.3151712417603</v>
+        <v>11.3151702880859</v>
       </c>
       <c r="H158" t="n">
         <v>45498</v>
@@ -4980,7 +4980,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G159" t="n">
-        <v>11.2535305023193</v>
+        <v>11.253529548645</v>
       </c>
       <c r="H159" t="n">
         <v>20029</v>
@@ -5009,7 +5009,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G160" t="n">
-        <v>11.0157804489136</v>
+        <v>11.0157814025879</v>
       </c>
       <c r="H160" t="n">
         <v>57012</v>
@@ -5067,7 +5067,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G162" t="n">
-        <v>11.0510034561157</v>
+        <v>11.0510025024414</v>
       </c>
       <c r="H162" t="n">
         <v>19081</v>
@@ -5096,7 +5096,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G163" t="n">
-        <v>10.9013090133667</v>
+        <v>10.9013080596924</v>
       </c>
       <c r="H163" t="n">
         <v>12830</v>
@@ -5125,7 +5125,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>11.1654748916626</v>
+        <v>11.1654758453369</v>
       </c>
       <c r="H164" t="n">
         <v>19684</v>
@@ -5183,7 +5183,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G166" t="n">
-        <v>11.2183074951172</v>
+        <v>11.2183094024658</v>
       </c>
       <c r="H166" t="n">
         <v>21084</v>
@@ -5270,7 +5270,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G169" t="n">
-        <v>11.1302537918091</v>
+        <v>11.1302518844604</v>
       </c>
       <c r="H169" t="n">
         <v>50121</v>
@@ -5299,7 +5299,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>11.1830854415894</v>
+        <v>11.1830863952637</v>
       </c>
       <c r="H170" t="n">
         <v>34325</v>
@@ -5386,7 +5386,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G173" t="n">
-        <v>11.7466430664062</v>
+        <v>11.7466440200806</v>
       </c>
       <c r="H173" t="n">
         <v>47129</v>
@@ -5444,7 +5444,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G175" t="n">
-        <v>11.6850051879883</v>
+        <v>11.685004234314</v>
       </c>
       <c r="H175" t="n">
         <v>29281</v>
@@ -5473,7 +5473,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>11.7994756698608</v>
+        <v>11.7994766235352</v>
       </c>
       <c r="H176" t="n">
         <v>51577</v>
@@ -5589,7 +5589,7 @@
         <v>13</v>
       </c>
       <c r="G180" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H180" t="n">
         <v>64823</v>
@@ -5618,7 +5618,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G181" t="n">
-        <v>11.3239755630493</v>
+        <v>11.3239765167236</v>
       </c>
       <c r="H181" t="n">
         <v>72041</v>
@@ -5705,7 +5705,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G184" t="n">
-        <v>11.6938095092773</v>
+        <v>11.6938104629517</v>
       </c>
       <c r="H184" t="n">
         <v>56844</v>
@@ -5734,7 +5734,7 @@
         <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>11.4472532272339</v>
+        <v>11.4472541809082</v>
       </c>
       <c r="H185" t="n">
         <v>43283</v>
@@ -5763,7 +5763,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G186" t="n">
-        <v>11.6145582199097</v>
+        <v>11.614559173584</v>
       </c>
       <c r="H186" t="n">
         <v>25730</v>
@@ -5821,7 +5821,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G188" t="n">
-        <v>12.0372276306152</v>
+        <v>12.0372266769409</v>
       </c>
       <c r="H188" t="n">
         <v>83675</v>
@@ -5879,7 +5879,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G190" t="n">
-        <v>12.0636425018311</v>
+        <v>12.0636444091797</v>
       </c>
       <c r="H190" t="n">
         <v>38989</v>
@@ -5908,7 +5908,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G191" t="n">
-        <v>12.5039224624634</v>
+        <v>12.5039234161377</v>
       </c>
       <c r="H191" t="n">
         <v>102776</v>
@@ -5937,7 +5937,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G192" t="n">
-        <v>12.5303392410278</v>
+        <v>12.5303401947021</v>
       </c>
       <c r="H192" t="n">
         <v>109655</v>
@@ -5966,7 +5966,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>12.4070634841919</v>
+        <v>12.4070625305176</v>
       </c>
       <c r="H193" t="n">
         <v>92196</v>
@@ -5995,7 +5995,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G194" t="n">
-        <v>12.2837839126587</v>
+        <v>12.2837829589844</v>
       </c>
       <c r="H194" t="n">
         <v>42892</v>
@@ -6111,7 +6111,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>12.8561458587646</v>
+        <v>12.856146812439</v>
       </c>
       <c r="H198" t="n">
         <v>56736</v>
@@ -6198,7 +6198,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G201" t="n">
-        <v>13.5782032012939</v>
+        <v>13.5782041549683</v>
       </c>
       <c r="H201" t="n">
         <v>145739</v>
@@ -6227,7 +6227,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G202" t="n">
-        <v>13.6838693618774</v>
+        <v>13.6838712692261</v>
       </c>
       <c r="H202" t="n">
         <v>145564</v>
@@ -6256,7 +6256,7 @@
         <v>15.25</v>
       </c>
       <c r="G203" t="n">
-        <v>13.4285078048706</v>
+        <v>13.4285087585449</v>
       </c>
       <c r="H203" t="n">
         <v>304187</v>
@@ -6314,7 +6314,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>14.2210102081299</v>
+        <v>14.2210111618042</v>
       </c>
       <c r="H205" t="n">
         <v>191135</v>
@@ -6343,7 +6343,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G206" t="n">
-        <v>14.2562341690063</v>
+        <v>14.256233215332</v>
       </c>
       <c r="H206" t="n">
         <v>116903</v>
@@ -6372,7 +6372,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G207" t="n">
-        <v>14.1329555511475</v>
+        <v>14.1329545974731</v>
       </c>
       <c r="H207" t="n">
         <v>75250</v>
@@ -6401,7 +6401,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G208" t="n">
-        <v>14.1241502761841</v>
+        <v>14.1241493225098</v>
       </c>
       <c r="H208" t="n">
         <v>50427</v>
@@ -6430,7 +6430,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G209" t="n">
-        <v>14.0713157653809</v>
+        <v>14.0713148117065</v>
       </c>
       <c r="H209" t="n">
         <v>70266</v>
@@ -6459,7 +6459,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>13.9216222763062</v>
+        <v>13.9216203689575</v>
       </c>
       <c r="H210" t="n">
         <v>55040</v>
@@ -6488,7 +6488,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G211" t="n">
-        <v>13.7807302474976</v>
+        <v>13.7807321548462</v>
       </c>
       <c r="H211" t="n">
         <v>83561</v>
@@ -6546,7 +6546,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G213" t="n">
-        <v>13.7631206512451</v>
+        <v>13.7631225585938</v>
       </c>
       <c r="H213" t="n">
         <v>75863</v>
@@ -6604,7 +6604,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7278995513916</v>
+        <v>13.7278985977173</v>
       </c>
       <c r="H215" t="n">
         <v>17418</v>
@@ -6662,7 +6662,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G217" t="n">
-        <v>13.3756732940674</v>
+        <v>13.375675201416</v>
       </c>
       <c r="H217" t="n">
         <v>67398</v>
@@ -6720,7 +6720,7 @@
         <v>15.5</v>
       </c>
       <c r="G219" t="n">
-        <v>13.6486482620239</v>
+        <v>13.6486492156982</v>
       </c>
       <c r="H219" t="n">
         <v>47806</v>
@@ -6749,7 +6749,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>13.5605926513672</v>
+        <v>13.5605936050415</v>
       </c>
       <c r="H220" t="n">
         <v>47022</v>
@@ -6778,7 +6778,7 @@
         <v>15.25</v>
       </c>
       <c r="G221" t="n">
-        <v>13.4285078048706</v>
+        <v>13.4285087585449</v>
       </c>
       <c r="H221" t="n">
         <v>144794</v>
@@ -6807,7 +6807,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>13.7367038726807</v>
+        <v>13.736704826355</v>
       </c>
       <c r="H222" t="n">
         <v>115544</v>
@@ -6836,7 +6836,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>13.8775939941406</v>
+        <v>13.8775930404663</v>
       </c>
       <c r="H223" t="n">
         <v>134507</v>
@@ -6865,7 +6865,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>14.1769847869873</v>
+        <v>14.1769828796387</v>
       </c>
       <c r="H224" t="n">
         <v>125262</v>
@@ -6923,7 +6923,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G226" t="n">
-        <v>14.7845697402954</v>
+        <v>14.7845687866211</v>
       </c>
       <c r="H226" t="n">
         <v>325482</v>
@@ -6952,7 +6952,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G227" t="n">
-        <v>15.3040971755981</v>
+        <v>15.3040962219238</v>
       </c>
       <c r="H227" t="n">
         <v>258275</v>
@@ -6981,7 +6981,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G228" t="n">
-        <v>15.2776823043823</v>
+        <v>15.2776803970337</v>
       </c>
       <c r="H228" t="n">
         <v>398968</v>
@@ -7010,7 +7010,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G229" t="n">
-        <v>15.4890165328979</v>
+        <v>15.4890155792236</v>
       </c>
       <c r="H229" t="n">
         <v>247524</v>
@@ -7039,7 +7039,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>15.4978218078613</v>
+        <v>15.4978189468384</v>
       </c>
       <c r="H230" t="n">
         <v>289822</v>
@@ -7068,7 +7068,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G231" t="n">
-        <v>15.3657350540161</v>
+        <v>15.3657369613647</v>
       </c>
       <c r="H231" t="n">
         <v>110362</v>
@@ -7126,7 +7126,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G233" t="n">
-        <v>15.3393201828003</v>
+        <v>15.339319229126</v>
       </c>
       <c r="H233" t="n">
         <v>71686</v>
@@ -7155,7 +7155,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G234" t="n">
-        <v>15.5330419540405</v>
+        <v>15.5330410003662</v>
       </c>
       <c r="H234" t="n">
         <v>122396</v>
@@ -7184,7 +7184,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G235" t="n">
-        <v>15.6651248931885</v>
+        <v>15.6651268005371</v>
       </c>
       <c r="H235" t="n">
         <v>210948</v>
@@ -7242,7 +7242,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>15.2424564361572</v>
+        <v>15.2424573898315</v>
       </c>
       <c r="H237" t="n">
         <v>98091</v>
@@ -7271,7 +7271,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G238" t="n">
-        <v>15.2776823043823</v>
+        <v>15.2776803970337</v>
       </c>
       <c r="H238" t="n">
         <v>97203</v>
@@ -7300,7 +7300,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G239" t="n">
-        <v>15.8060169219971</v>
+        <v>15.8060159683228</v>
       </c>
       <c r="H239" t="n">
         <v>125335</v>
@@ -7329,7 +7329,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G240" t="n">
-        <v>16.1934604644775</v>
+        <v>16.1934585571289</v>
       </c>
       <c r="H240" t="n">
         <v>378003</v>
@@ -7358,7 +7358,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G241" t="n">
-        <v>16.3695735931396</v>
+        <v>16.369571685791</v>
       </c>
       <c r="H241" t="n">
         <v>106538</v>
@@ -7387,7 +7387,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.4664325714111</v>
+        <v>16.4664363861084</v>
       </c>
       <c r="H242" t="n">
         <v>118582</v>
@@ -7416,7 +7416,7 @@
         <v>18.75</v>
       </c>
       <c r="G243" t="n">
-        <v>16.5104637145996</v>
+        <v>16.510461807251</v>
       </c>
       <c r="H243" t="n">
         <v>85459</v>
@@ -7445,7 +7445,7 @@
         <v>18.75</v>
       </c>
       <c r="G244" t="n">
-        <v>16.5104637145996</v>
+        <v>16.510461807251</v>
       </c>
       <c r="H244" t="n">
         <v>184405</v>
@@ -7474,7 +7474,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H245" t="n">
         <v>177039</v>
@@ -7503,7 +7503,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G246" t="n">
-        <v>16.8891010284424</v>
+        <v>16.8891048431396</v>
       </c>
       <c r="H246" t="n">
         <v>240701</v>
@@ -7532,7 +7532,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G247" t="n">
-        <v>17.1532707214355</v>
+        <v>17.1532669067383</v>
       </c>
       <c r="H247" t="n">
         <v>100453</v>
@@ -7590,7 +7590,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>16.5544872283936</v>
+        <v>16.5544910430908</v>
       </c>
       <c r="H249" t="n">
         <v>545131</v>
@@ -7619,7 +7619,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G250" t="n">
-        <v>16.2374877929688</v>
+        <v>16.237491607666</v>
       </c>
       <c r="H250" t="n">
         <v>353155</v>
@@ -7648,7 +7648,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G251" t="n">
-        <v>16.5897121429443</v>
+        <v>16.589714050293</v>
       </c>
       <c r="H251" t="n">
         <v>110433</v>
@@ -7793,7 +7793,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G256" t="n">
-        <v>16.8802967071533</v>
+        <v>16.880298614502</v>
       </c>
       <c r="H256" t="n">
         <v>74391</v>
@@ -7822,7 +7822,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G257" t="n">
-        <v>16.8538799285889</v>
+        <v>16.8538780212402</v>
       </c>
       <c r="H257" t="n">
         <v>23740</v>
@@ -7851,7 +7851,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G258" t="n">
-        <v>17.0123767852783</v>
+        <v>17.012378692627</v>
       </c>
       <c r="H258" t="n">
         <v>25398</v>
@@ -7880,7 +7880,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>17.1532707214355</v>
+        <v>17.1532669067383</v>
       </c>
       <c r="H259" t="n">
         <v>100834</v>
@@ -7967,7 +7967,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>17.03879737854</v>
+        <v>17.0387954711914</v>
       </c>
       <c r="H262" t="n">
         <v>26170</v>
@@ -8025,7 +8025,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>17.0828247070312</v>
+        <v>17.0828227996826</v>
       </c>
       <c r="H264" t="n">
         <v>180948</v>
@@ -8083,7 +8083,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G266" t="n">
-        <v>17.2061042785645</v>
+        <v>17.2061061859131</v>
       </c>
       <c r="H266" t="n">
         <v>93971</v>
@@ -8112,7 +8112,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>17.3469924926758</v>
+        <v>17.3469944000244</v>
       </c>
       <c r="H267" t="n">
         <v>96917</v>
@@ -8141,7 +8141,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>17.6551876068115</v>
+        <v>17.6551856994629</v>
       </c>
       <c r="H268" t="n">
         <v>75995</v>
@@ -8228,7 +8228,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G271" t="n">
-        <v>17.7168273925781</v>
+        <v>17.7168292999268</v>
       </c>
       <c r="H271" t="n">
         <v>75032</v>
@@ -8257,7 +8257,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G272" t="n">
-        <v>17.4526596069336</v>
+        <v>17.452657699585</v>
       </c>
       <c r="H272" t="n">
         <v>52750</v>
@@ -8286,7 +8286,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G273" t="n">
-        <v>17.5583248138428</v>
+        <v>17.5583267211914</v>
       </c>
       <c r="H273" t="n">
         <v>24496</v>
@@ -8460,7 +8460,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G279" t="n">
-        <v>16.7658233642578</v>
+        <v>16.7658252716064</v>
       </c>
       <c r="H279" t="n">
         <v>82633</v>
@@ -8489,7 +8489,7 @@
         <v>19.25</v>
       </c>
       <c r="G280" t="n">
-        <v>16.9507427215576</v>
+        <v>16.950740814209</v>
       </c>
       <c r="H280" t="n">
         <v>60029</v>
@@ -8518,7 +8518,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G281" t="n">
-        <v>17.1620750427246</v>
+        <v>17.162073135376</v>
       </c>
       <c r="H281" t="n">
         <v>28651</v>
@@ -8547,7 +8547,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G282" t="n">
-        <v>17.2765483856201</v>
+        <v>17.2765464782715</v>
       </c>
       <c r="H282" t="n">
         <v>41713</v>
@@ -8605,7 +8605,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092376708984</v>
       </c>
       <c r="H284" t="n">
         <v>50524</v>
@@ -8663,7 +8663,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G286" t="n">
-        <v>16.8891010284424</v>
+        <v>16.8891048431396</v>
       </c>
       <c r="H286" t="n">
         <v>33722</v>
@@ -8721,7 +8721,7 @@
         <v>19.25</v>
       </c>
       <c r="G288" t="n">
-        <v>16.9507427215576</v>
+        <v>16.950740814209</v>
       </c>
       <c r="H288" t="n">
         <v>47872</v>
@@ -8750,7 +8750,7 @@
         <v>19.25</v>
       </c>
       <c r="G289" t="n">
-        <v>16.9507427215576</v>
+        <v>16.950740814209</v>
       </c>
       <c r="H289" t="n">
         <v>32145</v>
@@ -8808,7 +8808,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G291" t="n">
-        <v>17.0828247070312</v>
+        <v>17.0828227996826</v>
       </c>
       <c r="H291" t="n">
         <v>122243</v>
@@ -8895,7 +8895,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>17.1092414855957</v>
+        <v>17.1092376708984</v>
       </c>
       <c r="H294" t="n">
         <v>52387</v>
@@ -8953,7 +8953,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G296" t="n">
-        <v>17.2501277923584</v>
+        <v>17.2501316070557</v>
       </c>
       <c r="H296" t="n">
         <v>53304</v>
@@ -8982,7 +8982,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G297" t="n">
-        <v>17.4350452423096</v>
+        <v>17.4350471496582</v>
       </c>
       <c r="H297" t="n">
         <v>105130</v>
@@ -9011,7 +9011,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G298" t="n">
-        <v>17.3734092712402</v>
+        <v>17.3734073638916</v>
       </c>
       <c r="H298" t="n">
         <v>48083</v>
@@ -9069,7 +9069,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G300" t="n">
-        <v>17.9457683563232</v>
+        <v>17.9457702636719</v>
       </c>
       <c r="H300" t="n">
         <v>68868</v>
@@ -9098,7 +9098,7 @@
         <v>22</v>
       </c>
       <c r="G301" t="n">
-        <v>19.3722763061523</v>
+        <v>19.372278213501</v>
       </c>
       <c r="H301" t="n">
         <v>221346</v>
@@ -9127,7 +9127,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G302" t="n">
-        <v>19.9358348846436</v>
+        <v>19.9358291625977</v>
       </c>
       <c r="H302" t="n">
         <v>140384</v>
@@ -9185,7 +9185,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G304" t="n">
-        <v>20.5962505340576</v>
+        <v>20.5962524414062</v>
       </c>
       <c r="H304" t="n">
         <v>71698</v>
@@ -9301,7 +9301,7 @@
         <v>24.5100002288818</v>
       </c>
       <c r="G308" t="n">
-        <v>21.5824775695801</v>
+        <v>21.5824756622314</v>
       </c>
       <c r="H308" t="n">
         <v>115604</v>
@@ -9359,7 +9359,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G310" t="n">
-        <v>21.327112197876</v>
+        <v>21.3271141052246</v>
       </c>
       <c r="H310" t="n">
         <v>59333</v>
@@ -9417,7 +9417,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>21.7497825622559</v>
+        <v>21.7497806549072</v>
       </c>
       <c r="H312" t="n">
         <v>78215</v>
@@ -9533,7 +9533,7 @@
         <v>25.3099994659424</v>
       </c>
       <c r="G316" t="n">
-        <v>22.286922454834</v>
+        <v>22.2869205474854</v>
       </c>
       <c r="H316" t="n">
         <v>115542</v>
@@ -9562,7 +9562,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G317" t="n">
-        <v>22.2605075836182</v>
+        <v>22.2605037689209</v>
       </c>
       <c r="H317" t="n">
         <v>83792</v>
@@ -9620,7 +9620,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G319" t="n">
-        <v>22.3221454620361</v>
+        <v>22.3221473693848</v>
       </c>
       <c r="H319" t="n">
         <v>60853</v>
@@ -9649,7 +9649,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G320" t="n">
-        <v>22.1900615692139</v>
+        <v>22.1900634765625</v>
       </c>
       <c r="H320" t="n">
         <v>84678</v>
@@ -9678,7 +9678,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>22.6303424835205</v>
+        <v>22.6303405761719</v>
       </c>
       <c r="H321" t="n">
         <v>84960</v>
@@ -9707,7 +9707,7 @@
         <v>25.4799995422363</v>
       </c>
       <c r="G322" t="n">
-        <v>22.4366149902344</v>
+        <v>22.4366188049316</v>
       </c>
       <c r="H322" t="n">
         <v>60620</v>
@@ -9823,7 +9823,7 @@
         <v>25.6900005340576</v>
       </c>
       <c r="G326" t="n">
-        <v>22.6215362548828</v>
+        <v>22.6215343475342</v>
       </c>
       <c r="H326" t="n">
         <v>41825</v>
@@ -9852,7 +9852,7 @@
         <v>25.75</v>
       </c>
       <c r="G327" t="n">
-        <v>22.6743659973145</v>
+        <v>22.6743679046631</v>
       </c>
       <c r="H327" t="n">
         <v>33968</v>
@@ -9881,7 +9881,7 @@
         <v>26</v>
       </c>
       <c r="G328" t="n">
-        <v>22.8945064544678</v>
+        <v>22.8945083618164</v>
       </c>
       <c r="H328" t="n">
         <v>89327</v>
@@ -9910,7 +9910,7 @@
         <v>26.2299995422363</v>
       </c>
       <c r="G329" t="n">
-        <v>23.0970344543457</v>
+        <v>23.0970363616943</v>
       </c>
       <c r="H329" t="n">
         <v>85680</v>
@@ -9939,7 +9939,7 @@
         <v>25.9300003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>22.8328685760498</v>
+        <v>22.8328704833984</v>
       </c>
       <c r="H330" t="n">
         <v>68594</v>
@@ -9968,7 +9968,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>22.3749809265137</v>
+        <v>22.3749771118164</v>
       </c>
       <c r="H331" t="n">
         <v>41506</v>
@@ -10026,7 +10026,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G333" t="n">
-        <v>23.1938972473145</v>
+        <v>23.1938991546631</v>
       </c>
       <c r="H333" t="n">
         <v>56151</v>
@@ -10055,7 +10055,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G334" t="n">
-        <v>23.3876190185547</v>
+        <v>23.3876209259033</v>
       </c>
       <c r="H334" t="n">
         <v>64034</v>
@@ -10084,7 +10084,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G335" t="n">
-        <v>23.5108985900879</v>
+        <v>23.5109004974365</v>
       </c>
       <c r="H335" t="n">
         <v>94393</v>
@@ -10142,7 +10142,7 @@
         <v>27.5300006866455</v>
       </c>
       <c r="G337" t="n">
-        <v>24.2417640686035</v>
+        <v>24.2417602539062</v>
       </c>
       <c r="H337" t="n">
         <v>94347</v>
@@ -10229,7 +10229,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G340" t="n">
-        <v>24.9197902679443</v>
+        <v>24.9197883605957</v>
       </c>
       <c r="H340" t="n">
         <v>76611</v>
@@ -10258,7 +10258,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G341" t="n">
-        <v>25.0870971679688</v>
+        <v>25.0870990753174</v>
       </c>
       <c r="H341" t="n">
         <v>113660</v>
@@ -10316,7 +10316,7 @@
         <v>28.2700004577637</v>
       </c>
       <c r="G343" t="n">
-        <v>24.8933734893799</v>
+        <v>24.8933715820312</v>
       </c>
       <c r="H343" t="n">
         <v>72745</v>
@@ -10345,7 +10345,7 @@
         <v>30.0100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>26.4255466461182</v>
+        <v>26.4255447387695</v>
       </c>
       <c r="H344" t="n">
         <v>323645</v>
@@ -10374,7 +10374,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G345" t="n">
-        <v>26.4879341125488</v>
+        <v>26.4879302978516</v>
       </c>
       <c r="H345" t="n">
         <v>116456</v>
@@ -10461,7 +10461,7 @@
         <v>31.5900001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>28.1545696258545</v>
+        <v>28.1545677185059</v>
       </c>
       <c r="H348" t="n">
         <v>94775</v>
@@ -10519,7 +10519,7 @@
         <v>32.1800003051758</v>
       </c>
       <c r="G350" t="n">
-        <v>28.6804084777832</v>
+        <v>28.6804046630859</v>
       </c>
       <c r="H350" t="n">
         <v>101430</v>
@@ -10548,7 +10548,7 @@
         <v>32.9500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>29.3666706085205</v>
+        <v>29.3666687011719</v>
       </c>
       <c r="H351" t="n">
         <v>132004</v>
@@ -10577,7 +10577,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G352" t="n">
-        <v>27.8069820404053</v>
+        <v>27.8069839477539</v>
       </c>
       <c r="H352" t="n">
         <v>138482</v>
@@ -10606,7 +10606,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G353" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H353" t="n">
         <v>149589</v>
@@ -10635,7 +10635,7 @@
         <v>32.560001373291</v>
       </c>
       <c r="G354" t="n">
-        <v>29.019079208374</v>
+        <v>29.0190830230713</v>
       </c>
       <c r="H354" t="n">
         <v>134928</v>
@@ -10693,7 +10693,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G356" t="n">
-        <v>29.7677345275879</v>
+        <v>29.7677326202393</v>
       </c>
       <c r="H356" t="n">
         <v>96078</v>
@@ -10722,7 +10722,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>29.8746814727783</v>
+        <v>29.8746795654297</v>
       </c>
       <c r="H357" t="n">
         <v>77270</v>
@@ -10751,7 +10751,7 @@
         <v>34</v>
       </c>
       <c r="G358" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024787902832</v>
       </c>
       <c r="H358" t="n">
         <v>94582</v>
@@ -10780,7 +10780,7 @@
         <v>34.5299987792969</v>
       </c>
       <c r="G359" t="n">
-        <v>30.7748470306396</v>
+        <v>30.7748394012451</v>
       </c>
       <c r="H359" t="n">
         <v>96091</v>
@@ -10809,7 +10809,7 @@
         <v>33.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>30.2400913238525</v>
+        <v>30.2400970458984</v>
       </c>
       <c r="H360" t="n">
         <v>60227</v>
@@ -10867,7 +10867,7 @@
         <v>34.5900001525879</v>
       </c>
       <c r="G362" t="n">
-        <v>30.8283157348633</v>
+        <v>30.8283214569092</v>
       </c>
       <c r="H362" t="n">
         <v>119866</v>
@@ -10896,7 +10896,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G363" t="n">
-        <v>30.8996200561523</v>
+        <v>30.8996143341064</v>
       </c>
       <c r="H363" t="n">
         <v>56630</v>
@@ -10925,7 +10925,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>31.0154838562012</v>
+        <v>31.0154800415039</v>
       </c>
       <c r="H364" t="n">
         <v>62681</v>
@@ -10983,7 +10983,7 @@
         <v>34.7099990844727</v>
       </c>
       <c r="G366" t="n">
-        <v>30.9352684020996</v>
+        <v>30.935266494751</v>
       </c>
       <c r="H366" t="n">
         <v>57384</v>
@@ -11012,7 +11012,7 @@
         <v>34.3899993896484</v>
       </c>
       <c r="G367" t="n">
-        <v>30.6500701904297</v>
+        <v>30.6500644683838</v>
       </c>
       <c r="H367" t="n">
         <v>49692</v>
@@ -11041,7 +11041,7 @@
         <v>34.5</v>
       </c>
       <c r="G368" t="n">
-        <v>30.748104095459</v>
+        <v>30.7481060028076</v>
       </c>
       <c r="H368" t="n">
         <v>76769</v>
@@ -11070,7 +11070,7 @@
         <v>34.4300003051758</v>
       </c>
       <c r="G369" t="n">
-        <v>30.6857223510742</v>
+        <v>30.6857166290283</v>
       </c>
       <c r="H369" t="n">
         <v>81969</v>
@@ -11157,7 +11157,7 @@
         <v>32.8899993896484</v>
       </c>
       <c r="G372" t="n">
-        <v>29.3131942749023</v>
+        <v>29.3131923675537</v>
       </c>
       <c r="H372" t="n">
         <v>62583</v>
@@ -11186,7 +11186,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G373" t="n">
-        <v>29.2775402069092</v>
+        <v>29.2775421142578</v>
       </c>
       <c r="H373" t="n">
         <v>103705</v>
@@ -11215,7 +11215,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>30.168794631958</v>
+        <v>30.1687908172607</v>
       </c>
       <c r="H374" t="n">
         <v>129825</v>
@@ -11244,7 +11244,7 @@
         <v>33.810001373291</v>
       </c>
       <c r="G375" t="n">
-        <v>30.1331462860107</v>
+        <v>30.1331443786621</v>
       </c>
       <c r="H375" t="n">
         <v>53130</v>
@@ -11273,7 +11273,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G376" t="n">
-        <v>29.999454498291</v>
+        <v>29.9994564056396</v>
       </c>
       <c r="H376" t="n">
         <v>56145</v>
@@ -11302,7 +11302,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G377" t="n">
-        <v>29.9281578063965</v>
+        <v>29.9281597137451</v>
       </c>
       <c r="H377" t="n">
         <v>47170</v>
@@ -11418,7 +11418,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G381" t="n">
-        <v>28.912130355835</v>
+        <v>28.9121322631836</v>
       </c>
       <c r="H381" t="n">
         <v>56347</v>
@@ -11447,7 +11447,7 @@
         <v>32.6800003051758</v>
       </c>
       <c r="G382" t="n">
-        <v>29.1260299682617</v>
+        <v>29.1260318756104</v>
       </c>
       <c r="H382" t="n">
         <v>60542</v>
@@ -11476,7 +11476,7 @@
         <v>31.1599998474121</v>
       </c>
       <c r="G383" t="n">
-        <v>27.7713298797607</v>
+        <v>27.7713317871094</v>
       </c>
       <c r="H383" t="n">
         <v>57971</v>
@@ -11505,7 +11505,7 @@
         <v>31.3799991607666</v>
       </c>
       <c r="G384" t="n">
-        <v>27.9674053192139</v>
+        <v>27.9674072265625</v>
       </c>
       <c r="H384" t="n">
         <v>76067</v>
@@ -11534,7 +11534,7 @@
         <v>30.5799999237061</v>
       </c>
       <c r="G385" t="n">
-        <v>27.2544078826904</v>
+        <v>27.2544059753418</v>
       </c>
       <c r="H385" t="n">
         <v>71103</v>
@@ -11563,7 +11563,7 @@
         <v>31.0699996948242</v>
       </c>
       <c r="G386" t="n">
-        <v>27.6911201477051</v>
+        <v>27.6911182403564</v>
       </c>
       <c r="H386" t="n">
         <v>94629</v>
@@ -11592,7 +11592,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G387" t="n">
-        <v>27.4861316680908</v>
+        <v>27.4861335754395</v>
       </c>
       <c r="H387" t="n">
         <v>60669</v>
@@ -11679,7 +11679,7 @@
         <v>31.8099994659424</v>
       </c>
       <c r="G390" t="n">
-        <v>28.3506412506104</v>
+        <v>28.350643157959</v>
       </c>
       <c r="H390" t="n">
         <v>37980</v>
@@ -11708,7 +11708,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G391" t="n">
-        <v>27.7178573608398</v>
+        <v>27.7178592681885</v>
       </c>
       <c r="H391" t="n">
         <v>37483</v>
@@ -11737,7 +11737,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G392" t="n">
-        <v>28.5734577178955</v>
+        <v>28.5734596252441</v>
       </c>
       <c r="H392" t="n">
         <v>75319</v>
@@ -11766,7 +11766,7 @@
         <v>32.1100006103516</v>
       </c>
       <c r="G393" t="n">
-        <v>28.6180210113525</v>
+        <v>28.6180171966553</v>
       </c>
       <c r="H393" t="n">
         <v>25940</v>
@@ -11795,7 +11795,7 @@
         <v>32</v>
       </c>
       <c r="G394" t="n">
-        <v>28.5199813842773</v>
+        <v>28.519983291626</v>
       </c>
       <c r="H394" t="n">
         <v>36963</v>
@@ -11853,7 +11853,7 @@
         <v>31.9400005340576</v>
       </c>
       <c r="G396" t="n">
-        <v>28.4665069580078</v>
+        <v>28.4665050506592</v>
       </c>
       <c r="H396" t="n">
         <v>45353</v>
@@ -11882,7 +11882,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G397" t="n">
-        <v>29.7855567932129</v>
+        <v>29.7855491638184</v>
       </c>
       <c r="H397" t="n">
         <v>145142</v>
@@ -11911,7 +11911,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G398" t="n">
-        <v>29.5360069274902</v>
+        <v>29.536003112793</v>
       </c>
       <c r="H398" t="n">
         <v>60276</v>
@@ -11998,7 +11998,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>29.2329807281494</v>
+        <v>29.2329788208008</v>
       </c>
       <c r="H401" t="n">
         <v>46478</v>
@@ -12056,7 +12056,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G403" t="n">
-        <v>29.3221092224121</v>
+        <v>29.3221073150635</v>
       </c>
       <c r="H403" t="n">
         <v>93384</v>
@@ -12085,7 +12085,7 @@
         <v>32.5</v>
       </c>
       <c r="G404" t="n">
-        <v>28.9656047821045</v>
+        <v>28.9656028747559</v>
       </c>
       <c r="H404" t="n">
         <v>28407</v>
@@ -12143,7 +12143,7 @@
         <v>32.5</v>
       </c>
       <c r="G406" t="n">
-        <v>28.9656047821045</v>
+        <v>28.9656028747559</v>
       </c>
       <c r="H406" t="n">
         <v>55695</v>
@@ -12201,7 +12201,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G408" t="n">
-        <v>28.9477806091309</v>
+        <v>28.9477787017822</v>
       </c>
       <c r="H408" t="n">
         <v>25669</v>
@@ -12230,7 +12230,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G409" t="n">
-        <v>29.7677345275879</v>
+        <v>29.7677326202393</v>
       </c>
       <c r="H409" t="n">
         <v>74517</v>
@@ -12259,7 +12259,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G410" t="n">
-        <v>29.607307434082</v>
+        <v>29.6073093414307</v>
       </c>
       <c r="H410" t="n">
         <v>24264</v>
@@ -12288,7 +12288,7 @@
         <v>33.5</v>
       </c>
       <c r="G411" t="n">
-        <v>29.8568592071533</v>
+        <v>29.8568572998047</v>
       </c>
       <c r="H411" t="n">
         <v>92243</v>
@@ -12433,7 +12433,7 @@
         <v>33.310001373291</v>
       </c>
       <c r="G416" t="n">
-        <v>29.6875171661377</v>
+        <v>29.6875190734863</v>
       </c>
       <c r="H416" t="n">
         <v>61558</v>
@@ -12491,7 +12491,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G418" t="n">
-        <v>29.6786041259766</v>
+        <v>29.6786060333252</v>
       </c>
       <c r="H418" t="n">
         <v>29416</v>
@@ -12549,7 +12549,7 @@
         <v>33.8199996948242</v>
       </c>
       <c r="G420" t="n">
-        <v>30.142053604126</v>
+        <v>30.1420555114746</v>
       </c>
       <c r="H420" t="n">
         <v>33779</v>
@@ -12578,7 +12578,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G421" t="n">
-        <v>29.8390331268311</v>
+        <v>29.8390293121338</v>
       </c>
       <c r="H421" t="n">
         <v>26190</v>
@@ -12607,7 +12607,7 @@
         <v>33.8699989318848</v>
       </c>
       <c r="G422" t="n">
-        <v>30.1866149902344</v>
+        <v>30.1866207122803</v>
       </c>
       <c r="H422" t="n">
         <v>29191</v>
@@ -12665,7 +12665,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G424" t="n">
-        <v>29.5181770324707</v>
+        <v>29.518180847168</v>
       </c>
       <c r="H424" t="n">
         <v>23018</v>
@@ -12752,7 +12752,7 @@
         <v>34.0699996948242</v>
       </c>
       <c r="G427" t="n">
-        <v>30.3648643493652</v>
+        <v>30.3648681640625</v>
       </c>
       <c r="H427" t="n">
         <v>64685</v>
@@ -12781,7 +12781,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G428" t="n">
-        <v>30.4629096984863</v>
+        <v>30.4629058837891</v>
       </c>
       <c r="H428" t="n">
         <v>65836</v>
@@ -12810,7 +12810,7 @@
         <v>34</v>
       </c>
       <c r="G429" t="n">
-        <v>30.3024826049805</v>
+        <v>30.3024787902832</v>
       </c>
       <c r="H429" t="n">
         <v>35077</v>
@@ -12839,7 +12839,7 @@
         <v>34.189998626709</v>
       </c>
       <c r="G430" t="n">
-        <v>30.4718208312988</v>
+        <v>30.4718151092529</v>
       </c>
       <c r="H430" t="n">
         <v>35469</v>
@@ -12868,7 +12868,7 @@
         <v>33.9900016784668</v>
       </c>
       <c r="G431" t="n">
-        <v>30.2935676574707</v>
+        <v>30.2935657501221</v>
       </c>
       <c r="H431" t="n">
         <v>27202</v>
@@ -12897,7 +12897,7 @@
         <v>33.7700004577637</v>
       </c>
       <c r="G432" t="n">
-        <v>30.0974941253662</v>
+        <v>30.0974922180176</v>
       </c>
       <c r="H432" t="n">
         <v>12531</v>
@@ -12955,7 +12955,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G434" t="n">
-        <v>30.2311820983887</v>
+        <v>30.23118019104</v>
       </c>
       <c r="H434" t="n">
         <v>24161</v>
@@ -13042,7 +13042,7 @@
         <v>35.3400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>31.4967555999756</v>
+        <v>31.4967517852783</v>
       </c>
       <c r="H437" t="n">
         <v>105328</v>
@@ -13129,7 +13129,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G440" t="n">
-        <v>31.7730388641357</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H440" t="n">
         <v>27909</v>
@@ -13158,7 +13158,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G441" t="n">
-        <v>31.7730388641357</v>
+        <v>31.773042678833</v>
       </c>
       <c r="H441" t="n">
         <v>20121</v>
@@ -13187,7 +13187,7 @@
         <v>35.560001373291</v>
       </c>
       <c r="G442" t="n">
-        <v>31.6928272247314</v>
+        <v>31.6928291320801</v>
       </c>
       <c r="H442" t="n">
         <v>33799</v>
@@ -13274,7 +13274,7 @@
         <v>35.8499984741211</v>
       </c>
       <c r="G445" t="n">
-        <v>31.9512844085693</v>
+        <v>31.9512920379639</v>
       </c>
       <c r="H445" t="n">
         <v>54557</v>
@@ -13303,7 +13303,7 @@
         <v>36.25</v>
       </c>
       <c r="G446" t="n">
-        <v>32.3077964782715</v>
+        <v>32.307788848877</v>
       </c>
       <c r="H446" t="n">
         <v>79657</v>
@@ -13332,7 +13332,7 @@
         <v>37.25</v>
       </c>
       <c r="G447" t="n">
-        <v>33.1990394592285</v>
+        <v>33.1990432739258</v>
       </c>
       <c r="H447" t="n">
         <v>128921</v>
@@ -13448,7 +13448,7 @@
         <v>38.9700012207031</v>
       </c>
       <c r="G451" t="n">
-        <v>34.731990814209</v>
+        <v>34.7319869995117</v>
       </c>
       <c r="H451" t="n">
         <v>72300</v>
@@ -13506,7 +13506,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G453" t="n">
-        <v>34.2239761352539</v>
+        <v>34.2239799499512</v>
       </c>
       <c r="H453" t="n">
         <v>40089</v>
@@ -13535,7 +13535,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G454" t="n">
-        <v>34.437873840332</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H454" t="n">
         <v>22990</v>
@@ -13564,7 +13564,7 @@
         <v>38.6399993896484</v>
       </c>
       <c r="G455" t="n">
-        <v>34.437873840332</v>
+        <v>34.4378776550293</v>
       </c>
       <c r="H455" t="n">
         <v>25085</v>
@@ -13622,7 +13622,7 @@
         <v>38.7599983215332</v>
       </c>
       <c r="G457" t="n">
-        <v>34.5448265075684</v>
+        <v>34.5448303222656</v>
       </c>
       <c r="H457" t="n">
         <v>38480</v>
@@ -13651,7 +13651,7 @@
         <v>39.75</v>
       </c>
       <c r="G458" t="n">
-        <v>35.4271621704102</v>
+        <v>35.4271659851074</v>
       </c>
       <c r="H458" t="n">
         <v>72239</v>
@@ -13680,7 +13680,7 @@
         <v>39.5200004577637</v>
       </c>
       <c r="G459" t="n">
-        <v>35.2221755981445</v>
+        <v>35.2221794128418</v>
       </c>
       <c r="H459" t="n">
         <v>35360</v>
@@ -13709,7 +13709,7 @@
         <v>38.8899993896484</v>
       </c>
       <c r="G460" t="n">
-        <v>34.6606826782227</v>
+        <v>34.6606864929199</v>
       </c>
       <c r="H460" t="n">
         <v>44719</v>
@@ -13767,7 +13767,7 @@
         <v>38</v>
       </c>
       <c r="G462" t="n">
-        <v>33.8674774169922</v>
+        <v>33.8674736022949</v>
       </c>
       <c r="H462" t="n">
         <v>58890</v>
@@ -13825,7 +13825,7 @@
         <v>38.310001373291</v>
       </c>
       <c r="G464" t="n">
-        <v>34.1437644958496</v>
+        <v>34.1437683105469</v>
       </c>
       <c r="H464" t="n">
         <v>21788</v>
@@ -13854,7 +13854,7 @@
         <v>38</v>
       </c>
       <c r="G465" t="n">
-        <v>33.8674774169922</v>
+        <v>33.8674736022949</v>
       </c>
       <c r="H465" t="n">
         <v>19781</v>
@@ -13883,7 +13883,7 @@
         <v>37.8300018310547</v>
       </c>
       <c r="G466" t="n">
-        <v>33.7159652709961</v>
+        <v>33.7159690856934</v>
       </c>
       <c r="H466" t="n">
         <v>30408</v>
@@ -13941,7 +13941,7 @@
         <v>38.5</v>
       </c>
       <c r="G468" t="n">
-        <v>34.313102722168</v>
+        <v>34.3131065368652</v>
       </c>
       <c r="H468" t="n">
         <v>152768</v>
@@ -13970,7 +13970,7 @@
         <v>38.5</v>
       </c>
       <c r="G469" t="n">
-        <v>34.313102722168</v>
+        <v>34.3131065368652</v>
       </c>
       <c r="H469" t="n">
         <v>119331</v>
@@ -13999,7 +13999,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G470" t="n">
-        <v>34.1170272827148</v>
+        <v>34.1170310974121</v>
       </c>
       <c r="H470" t="n">
         <v>74592</v>
@@ -14028,7 +14028,7 @@
         <v>38.6199989318848</v>
       </c>
       <c r="G471" t="n">
-        <v>34.4200477600098</v>
+        <v>34.420051574707</v>
       </c>
       <c r="H471" t="n">
         <v>26257</v>
@@ -14057,7 +14057,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G472" t="n">
-        <v>34.1170272827148</v>
+        <v>34.1170310974121</v>
       </c>
       <c r="H472" t="n">
         <v>63699</v>
@@ -14086,7 +14086,7 @@
         <v>39.0200004577637</v>
       </c>
       <c r="G473" t="n">
-        <v>34.7765502929688</v>
+        <v>34.776554107666</v>
       </c>
       <c r="H473" t="n">
         <v>35970</v>
@@ -14115,7 +14115,7 @@
         <v>38.8400001525879</v>
       </c>
       <c r="G474" t="n">
-        <v>34.6161231994629</v>
+        <v>34.6161308288574</v>
       </c>
       <c r="H474" t="n">
         <v>28179</v>
@@ -14144,7 +14144,7 @@
         <v>38.4900016784668</v>
       </c>
       <c r="G475" t="n">
-        <v>34.3041877746582</v>
+        <v>34.3041915893555</v>
       </c>
       <c r="H475" t="n">
         <v>35545</v>
@@ -14173,7 +14173,7 @@
         <v>38.2700004577637</v>
       </c>
       <c r="G476" t="n">
-        <v>34.1081123352051</v>
+        <v>34.1081085205078</v>
       </c>
       <c r="H476" t="n">
         <v>84787</v>
@@ -14202,7 +14202,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G477" t="n">
-        <v>32.8425407409668</v>
+        <v>32.8425369262695</v>
       </c>
       <c r="H477" t="n">
         <v>88388</v>
@@ -14318,7 +14318,7 @@
         <v>40.7299995422363</v>
       </c>
       <c r="G481" t="n">
-        <v>36.3005905151367</v>
+        <v>36.3005867004395</v>
       </c>
       <c r="H481" t="n">
         <v>83025</v>
@@ -14376,7 +14376,7 @@
         <v>40.9500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>36.4966621398926</v>
+        <v>36.4966659545898</v>
       </c>
       <c r="H483" t="n">
         <v>94288</v>
@@ -14434,7 +14434,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G485" t="n">
-        <v>38.858470916748</v>
+        <v>38.8584747314453</v>
       </c>
       <c r="H485" t="n">
         <v>114697</v>
@@ -14463,7 +14463,7 @@
         <v>43.6699981689453</v>
       </c>
       <c r="G486" t="n">
-        <v>38.9208602905273</v>
+        <v>38.9208641052246</v>
       </c>
       <c r="H486" t="n">
         <v>113917</v>
@@ -14492,7 +14492,7 @@
         <v>43.3300018310547</v>
       </c>
       <c r="G487" t="n">
-        <v>38.6178398132324</v>
+        <v>38.6178359985352</v>
       </c>
       <c r="H487" t="n">
         <v>81528</v>
@@ -14521,7 +14521,7 @@
         <v>43.2900009155273</v>
       </c>
       <c r="G488" t="n">
-        <v>38.5821876525879</v>
+        <v>38.5821914672852</v>
       </c>
       <c r="H488" t="n">
         <v>84905</v>
@@ -14579,7 +14579,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G490" t="n">
-        <v>38.4306716918945</v>
+        <v>38.4306755065918</v>
       </c>
       <c r="H490" t="n">
         <v>37738</v>
@@ -14608,7 +14608,7 @@
         <v>44</v>
       </c>
       <c r="G491" t="n">
-        <v>39.2149772644043</v>
+        <v>39.214973449707</v>
       </c>
       <c r="H491" t="n">
         <v>80819</v>
@@ -14637,7 +14637,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G492" t="n">
-        <v>38.805004119873</v>
+        <v>38.8050003051758</v>
       </c>
       <c r="H492" t="n">
         <v>92161</v>
@@ -14666,7 +14666,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G493" t="n">
-        <v>37.8067970275879</v>
+        <v>37.8068008422852</v>
       </c>
       <c r="H493" t="n">
         <v>73604</v>
@@ -14753,7 +14753,7 @@
         <v>43.0499992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>38.3682899475098</v>
+        <v>38.3682823181152</v>
       </c>
       <c r="H496" t="n">
         <v>60370</v>
@@ -14782,7 +14782,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G497" t="n">
-        <v>38.3415489196777</v>
+        <v>38.341552734375</v>
       </c>
       <c r="H497" t="n">
         <v>44383</v>
@@ -14840,7 +14840,7 @@
         <v>43.2700004577637</v>
       </c>
       <c r="G499" t="n">
-        <v>38.5643653869629</v>
+        <v>38.5643615722656</v>
       </c>
       <c r="H499" t="n">
         <v>49640</v>
@@ -14869,7 +14869,7 @@
         <v>43.1199989318848</v>
       </c>
       <c r="G500" t="n">
-        <v>38.4306716918945</v>
+        <v>38.4306755065918</v>
       </c>
       <c r="H500" t="n">
         <v>89203</v>
@@ -14898,7 +14898,7 @@
         <v>43.3199996948242</v>
       </c>
       <c r="G501" t="n">
-        <v>38.6089248657227</v>
+        <v>38.6089210510254</v>
       </c>
       <c r="H501" t="n">
         <v>39100</v>
@@ -14927,7 +14927,7 @@
         <v>43.4099998474121</v>
       </c>
       <c r="G502" t="n">
-        <v>38.689136505127</v>
+        <v>38.6891403198242</v>
       </c>
       <c r="H502" t="n">
         <v>37927</v>
@@ -14985,7 +14985,7 @@
         <v>44.25</v>
       </c>
       <c r="G504" t="n">
-        <v>39.4377937316895</v>
+        <v>39.4377861022949</v>
       </c>
       <c r="H504" t="n">
         <v>47066</v>
@@ -15043,7 +15043,7 @@
         <v>43.8199996948242</v>
       </c>
       <c r="G506" t="n">
-        <v>39.0545539855957</v>
+        <v>39.0545501708984</v>
       </c>
       <c r="H506" t="n">
         <v>27453</v>
@@ -15188,7 +15188,7 @@
         <v>42.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>37.6998481750488</v>
+        <v>37.6998519897461</v>
       </c>
       <c r="H511" t="n">
         <v>40470</v>
@@ -15217,7 +15217,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G512" t="n">
-        <v>36.6125297546387</v>
+        <v>36.6125259399414</v>
       </c>
       <c r="H512" t="n">
         <v>50757</v>
@@ -15333,7 +15333,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G516" t="n">
-        <v>42.6551971435547</v>
+        <v>42.655200958252</v>
       </c>
       <c r="H516" t="n">
         <v>71031</v>
@@ -15362,7 +15362,7 @@
         <v>48.0400009155273</v>
       </c>
       <c r="G517" t="n">
-        <v>42.8156204223633</v>
+        <v>42.8156242370605</v>
       </c>
       <c r="H517" t="n">
         <v>52703</v>
@@ -15391,7 +15391,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G518" t="n">
-        <v>42.423469543457</v>
+        <v>42.4234733581543</v>
       </c>
       <c r="H518" t="n">
         <v>40840</v>
@@ -15449,7 +15449,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G520" t="n">
-        <v>42.0847930908203</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H520" t="n">
         <v>21408</v>
@@ -15507,7 +15507,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>41.6213455200195</v>
+        <v>41.6213493347168</v>
       </c>
       <c r="H522" t="n">
         <v>37738</v>
@@ -15594,7 +15594,7 @@
         <v>47.2200012207031</v>
       </c>
       <c r="G525" t="n">
-        <v>42.0847930908203</v>
+        <v>42.0848007202148</v>
       </c>
       <c r="H525" t="n">
         <v>27575</v>
@@ -15623,7 +15623,7 @@
         <v>47.2799987792969</v>
       </c>
       <c r="G526" t="n">
-        <v>42.1382713317871</v>
+        <v>42.1382751464844</v>
       </c>
       <c r="H526" t="n">
         <v>32130</v>
@@ -15681,7 +15681,7 @@
         <v>46.7799987792969</v>
       </c>
       <c r="G528" t="n">
-        <v>41.6926460266113</v>
+        <v>41.6926498413086</v>
       </c>
       <c r="H528" t="n">
         <v>21631</v>
@@ -15710,7 +15710,7 @@
         <v>46.5999984741211</v>
       </c>
       <c r="G529" t="n">
-        <v>41.5322151184082</v>
+        <v>41.5322227478027</v>
       </c>
       <c r="H529" t="n">
         <v>36997</v>
@@ -15739,7 +15739,7 @@
         <v>46.8800010681152</v>
       </c>
       <c r="G530" t="n">
-        <v>41.7817687988281</v>
+        <v>41.7817726135254</v>
       </c>
       <c r="H530" t="n">
         <v>30670</v>
@@ -15768,7 +15768,7 @@
         <v>46.4000015258789</v>
       </c>
       <c r="G531" t="n">
-        <v>41.3539695739746</v>
+        <v>41.3539733886719</v>
       </c>
       <c r="H531" t="n">
         <v>26139</v>
@@ -15797,7 +15797,7 @@
         <v>45.7999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>40.8192253112793</v>
+        <v>40.819221496582</v>
       </c>
       <c r="H532" t="n">
         <v>43823</v>
@@ -15826,7 +15826,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G533" t="n">
-        <v>40.3557777404785</v>
+        <v>40.355770111084</v>
       </c>
       <c r="H533" t="n">
         <v>51912</v>
@@ -15855,7 +15855,7 @@
         <v>45.5400009155273</v>
       </c>
       <c r="G534" t="n">
-        <v>40.5874977111816</v>
+        <v>40.5875015258789</v>
       </c>
       <c r="H534" t="n">
         <v>32810</v>
@@ -15884,7 +15884,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G535" t="n">
-        <v>39.8031997680664</v>
+        <v>39.8031959533691</v>
       </c>
       <c r="H535" t="n">
         <v>40370</v>
@@ -15942,7 +15942,7 @@
         <v>44.5200004577637</v>
       </c>
       <c r="G537" t="n">
-        <v>39.6784286499023</v>
+        <v>39.6784248352051</v>
       </c>
       <c r="H537" t="n">
         <v>153620</v>
@@ -16029,7 +16029,7 @@
         <v>43.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>38.6802291870117</v>
+        <v>38.6802253723145</v>
       </c>
       <c r="H540" t="n">
         <v>153076</v>
@@ -16145,7 +16145,7 @@
         <v>44.4199981689453</v>
       </c>
       <c r="G544" t="n">
-        <v>39.5892944335938</v>
+        <v>39.5893020629883</v>
       </c>
       <c r="H544" t="n">
         <v>70654</v>
@@ -16174,7 +16174,7 @@
         <v>45.0999984741211</v>
       </c>
       <c r="G545" t="n">
-        <v>40.1953468322754</v>
+        <v>40.1953506469727</v>
       </c>
       <c r="H545" t="n">
         <v>42666</v>
@@ -16203,7 +16203,7 @@
         <v>45</v>
       </c>
       <c r="G546" t="n">
-        <v>40.1062278747559</v>
+        <v>40.1062240600586</v>
       </c>
       <c r="H546" t="n">
         <v>31017</v>
@@ -16348,7 +16348,7 @@
         <v>46.1599998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>41.1400718688965</v>
+        <v>41.140079498291</v>
       </c>
       <c r="H551" t="n">
         <v>31765</v>
@@ -16377,7 +16377,7 @@
         <v>46</v>
       </c>
       <c r="G552" t="n">
-        <v>40.9974746704102</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H552" t="n">
         <v>62087</v>
@@ -16406,7 +16406,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G553" t="n">
-        <v>40.5161972045898</v>
+        <v>40.5162010192871</v>
       </c>
       <c r="H553" t="n">
         <v>34881</v>
@@ -16435,7 +16435,7 @@
         <v>45.9599990844727</v>
       </c>
       <c r="G554" t="n">
-        <v>40.9618186950684</v>
+        <v>40.9618263244629</v>
       </c>
       <c r="H554" t="n">
         <v>94078</v>
@@ -16464,7 +16464,7 @@
         <v>44.0400009155273</v>
       </c>
       <c r="G555" t="n">
-        <v>39.2506294250488</v>
+        <v>39.2506256103516</v>
       </c>
       <c r="H555" t="n">
         <v>114926</v>
@@ -16493,7 +16493,7 @@
         <v>43.9599990844727</v>
       </c>
       <c r="G556" t="n">
-        <v>39.1793251037598</v>
+        <v>39.1793212890625</v>
       </c>
       <c r="H556" t="n">
         <v>64193</v>
@@ -16522,7 +16522,7 @@
         <v>45.1199989318848</v>
       </c>
       <c r="G557" t="n">
-        <v>40.2131767272949</v>
+        <v>40.2131729125977</v>
       </c>
       <c r="H557" t="n">
         <v>48880</v>
@@ -16551,7 +16551,7 @@
         <v>45.3199996948242</v>
       </c>
       <c r="G558" t="n">
-        <v>40.3914260864258</v>
+        <v>40.3914222717285</v>
       </c>
       <c r="H558" t="n">
         <v>72029</v>
@@ -16580,7 +16580,7 @@
         <v>46</v>
       </c>
       <c r="G559" t="n">
-        <v>40.9974746704102</v>
+        <v>40.9974708557129</v>
       </c>
       <c r="H559" t="n">
         <v>66348</v>
@@ -16609,7 +16609,7 @@
         <v>46.439998626709</v>
       </c>
       <c r="G560" t="n">
-        <v>41.3896217346191</v>
+        <v>41.3896255493164</v>
       </c>
       <c r="H560" t="n">
         <v>94283</v>
@@ -16667,7 +16667,7 @@
         <v>49.9799995422363</v>
       </c>
       <c r="G562" t="n">
-        <v>44.5446434020996</v>
+        <v>44.5446472167969</v>
       </c>
       <c r="H562" t="n">
         <v>242564</v>
@@ -16783,7 +16783,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G566" t="n">
-        <v>44.9635314941406</v>
+        <v>44.9635276794434</v>
       </c>
       <c r="H566" t="n">
         <v>112572</v>
@@ -16841,7 +16841,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G568" t="n">
-        <v>47.3253440856934</v>
+        <v>47.3253402709961</v>
       </c>
       <c r="H568" t="n">
         <v>177354</v>
@@ -16870,7 +16870,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G569" t="n">
-        <v>45.9439125061035</v>
+        <v>45.9439086914062</v>
       </c>
       <c r="H569" t="n">
         <v>178635</v>
@@ -16899,7 +16899,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G570" t="n">
-        <v>45.5874099731445</v>
+        <v>45.5874061584473</v>
       </c>
       <c r="H570" t="n">
         <v>120878</v>
@@ -16957,7 +16957,7 @@
         <v>49.3800010681152</v>
       </c>
       <c r="G572" t="n">
-        <v>44.0098991394043</v>
+        <v>44.009895324707</v>
       </c>
       <c r="H572" t="n">
         <v>64462</v>
@@ -16986,7 +16986,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G573" t="n">
-        <v>43.8494720458984</v>
+        <v>43.8494758605957</v>
       </c>
       <c r="H573" t="n">
         <v>65658</v>
@@ -17044,7 +17044,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G575" t="n">
-        <v>42.6551971435547</v>
+        <v>42.655200958252</v>
       </c>
       <c r="H575" t="n">
         <v>111110</v>
@@ -17073,7 +17073,7 @@
         <v>46.5200004577637</v>
       </c>
       <c r="G576" t="n">
-        <v>41.4609260559082</v>
+        <v>41.4609222412109</v>
       </c>
       <c r="H576" t="n">
         <v>100832</v>
@@ -17131,7 +17131,7 @@
         <v>46.2000007629395</v>
       </c>
       <c r="G578" t="n">
-        <v>41.1757202148438</v>
+        <v>41.175724029541</v>
       </c>
       <c r="H578" t="n">
         <v>78204</v>
@@ -17160,7 +17160,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G579" t="n">
-        <v>41.1578941345215</v>
+        <v>41.1578979492188</v>
       </c>
       <c r="H579" t="n">
         <v>52237</v>
@@ -17189,7 +17189,7 @@
         <v>46.0200004577637</v>
       </c>
       <c r="G580" t="n">
-        <v>41.0152969360352</v>
+        <v>41.0153007507324</v>
       </c>
       <c r="H580" t="n">
         <v>49188</v>
@@ -17218,7 +17218,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G581" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675514221191</v>
       </c>
       <c r="H581" t="n">
         <v>81341</v>
@@ -17247,7 +17247,7 @@
         <v>44.6599998474121</v>
       </c>
       <c r="G582" t="n">
-        <v>39.8031997680664</v>
+        <v>39.8031959533691</v>
       </c>
       <c r="H582" t="n">
         <v>46802</v>
@@ -17276,7 +17276,7 @@
         <v>43.8800010681152</v>
       </c>
       <c r="G583" t="n">
-        <v>39.1080284118652</v>
+        <v>39.108024597168</v>
       </c>
       <c r="H583" t="n">
         <v>48182</v>
@@ -17305,7 +17305,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G584" t="n">
-        <v>40.7479209899902</v>
+        <v>40.7479248046875</v>
       </c>
       <c r="H584" t="n">
         <v>83788</v>
@@ -17334,7 +17334,7 @@
         <v>44.6399993896484</v>
       </c>
       <c r="G585" t="n">
-        <v>39.7853775024414</v>
+        <v>39.7853736877441</v>
       </c>
       <c r="H585" t="n">
         <v>69470</v>
@@ -17392,7 +17392,7 @@
         <v>44.5800018310547</v>
       </c>
       <c r="G587" t="n">
-        <v>39.7319030761719</v>
+        <v>39.7318992614746</v>
       </c>
       <c r="H587" t="n">
         <v>42227</v>
@@ -17421,7 +17421,7 @@
         <v>44.0999984741211</v>
       </c>
       <c r="G588" t="n">
-        <v>39.3041000366211</v>
+        <v>39.3040962219238</v>
       </c>
       <c r="H588" t="n">
         <v>50438</v>
@@ -17450,7 +17450,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G589" t="n">
-        <v>39.7675476074219</v>
+        <v>39.7675514221191</v>
       </c>
       <c r="H589" t="n">
         <v>23775</v>
@@ -17479,7 +17479,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G590" t="n">
-        <v>40.2488250732422</v>
+        <v>40.2488212585449</v>
       </c>
       <c r="H590" t="n">
         <v>41714</v>
@@ -17653,7 +17653,7 @@
         <v>45.7200012207031</v>
       </c>
       <c r="G596" t="n">
-        <v>40.7479209899902</v>
+        <v>40.7479248046875</v>
       </c>
       <c r="H596" t="n">
         <v>103803</v>
@@ -17682,7 +17682,7 @@
         <v>46.060001373291</v>
       </c>
       <c r="G597" t="n">
-        <v>41.0509452819824</v>
+        <v>41.050952911377</v>
       </c>
       <c r="H597" t="n">
         <v>57439</v>
@@ -17711,7 +17711,7 @@
         <v>46.560001373291</v>
       </c>
       <c r="G598" t="n">
-        <v>41.9335708618164</v>
+        <v>41.9335746765137</v>
       </c>
       <c r="H598" t="n">
         <v>41681</v>
@@ -17769,7 +17769,7 @@
         <v>45.2000007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>40.7087097167969</v>
+        <v>40.7087059020996</v>
       </c>
       <c r="H600" t="n">
         <v>23543</v>
@@ -17827,7 +17827,7 @@
         <v>45</v>
       </c>
       <c r="G602" t="n">
-        <v>40.5285835266113</v>
+        <v>40.5285797119141</v>
       </c>
       <c r="H602" t="n">
         <v>39659</v>
@@ -17914,7 +17914,7 @@
         <v>41.6199989318848</v>
       </c>
       <c r="G605" t="n">
-        <v>37.4844360351562</v>
+        <v>37.4844284057617</v>
       </c>
       <c r="H605" t="n">
         <v>87797</v>
@@ -18030,7 +18030,7 @@
         <v>40.6399993896484</v>
       </c>
       <c r="G609" t="n">
-        <v>36.6018104553223</v>
+        <v>36.6018142700195</v>
       </c>
       <c r="H609" t="n">
         <v>50992</v>
@@ -18059,7 +18059,7 @@
         <v>39.9799995422363</v>
       </c>
       <c r="G610" t="n">
-        <v>36.007396697998</v>
+        <v>36.0073928833008</v>
       </c>
       <c r="H610" t="n">
         <v>71270</v>
@@ -18146,7 +18146,7 @@
         <v>38</v>
       </c>
       <c r="G613" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H613" t="n">
         <v>88495</v>
@@ -18175,7 +18175,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G614" t="n">
-        <v>33.4135589599609</v>
+        <v>33.4135627746582</v>
       </c>
       <c r="H614" t="n">
         <v>159133</v>
@@ -18204,7 +18204,7 @@
         <v>37.3800010681152</v>
       </c>
       <c r="G615" t="n">
-        <v>33.6657409667969</v>
+        <v>33.6657371520996</v>
       </c>
       <c r="H615" t="n">
         <v>56794</v>
@@ -18262,7 +18262,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G617" t="n">
-        <v>34.4763107299805</v>
+        <v>34.4763145446777</v>
       </c>
       <c r="H617" t="n">
         <v>85349</v>
@@ -18291,7 +18291,7 @@
         <v>38.5200004577637</v>
       </c>
       <c r="G618" t="n">
-        <v>34.6924705505371</v>
+        <v>34.6924667358398</v>
       </c>
       <c r="H618" t="n">
         <v>73867</v>
@@ -18378,7 +18378,7 @@
         <v>38.3600006103516</v>
       </c>
       <c r="G621" t="n">
-        <v>34.5483627319336</v>
+        <v>34.5483665466309</v>
       </c>
       <c r="H621" t="n">
         <v>32667</v>
@@ -18436,7 +18436,7 @@
         <v>38</v>
       </c>
       <c r="G623" t="n">
-        <v>34.2241363525391</v>
+        <v>34.2241325378418</v>
       </c>
       <c r="H623" t="n">
         <v>21903</v>
@@ -18523,7 +18523,7 @@
         <v>38.2400016784668</v>
       </c>
       <c r="G626" t="n">
-        <v>34.4402885437012</v>
+        <v>34.4402923583984</v>
       </c>
       <c r="H626" t="n">
         <v>46240</v>
@@ -18552,7 +18552,7 @@
         <v>39</v>
       </c>
       <c r="G627" t="n">
-        <v>35.1247749328613</v>
+        <v>35.1247711181641</v>
       </c>
       <c r="H627" t="n">
         <v>103614</v>
@@ -18610,7 +18610,7 @@
         <v>35.9799995422363</v>
       </c>
       <c r="G629" t="n">
-        <v>32.404857635498</v>
+        <v>32.4048500061035</v>
       </c>
       <c r="H629" t="n">
         <v>77422</v>
@@ -18697,7 +18697,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G632" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744064331055</v>
       </c>
       <c r="H632" t="n">
         <v>126471</v>
@@ -18755,7 +18755,7 @@
         <v>32.7400016784668</v>
       </c>
       <c r="G634" t="n">
-        <v>29.486795425415</v>
+        <v>29.4867973327637</v>
       </c>
       <c r="H634" t="n">
         <v>160938</v>
@@ -18784,7 +18784,7 @@
         <v>33.2400016784668</v>
       </c>
       <c r="G635" t="n">
-        <v>29.9371147155762</v>
+        <v>29.9371128082275</v>
       </c>
       <c r="H635" t="n">
         <v>311338</v>
@@ -18842,7 +18842,7 @@
         <v>33.4799995422363</v>
       </c>
       <c r="G637" t="n">
-        <v>30.1532669067383</v>
+        <v>30.153263092041</v>
       </c>
       <c r="H637" t="n">
         <v>47812</v>
@@ -18900,7 +18900,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G639" t="n">
-        <v>29.4147434234619</v>
+        <v>29.4147453308105</v>
       </c>
       <c r="H639" t="n">
         <v>66878</v>
@@ -18958,7 +18958,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G641" t="n">
-        <v>29.1265411376953</v>
+        <v>29.1265430450439</v>
       </c>
       <c r="H641" t="n">
         <v>126609</v>
@@ -18987,7 +18987,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G642" t="n">
-        <v>29.5408325195312</v>
+        <v>29.5408306121826</v>
       </c>
       <c r="H642" t="n">
         <v>72223</v>
@@ -19045,7 +19045,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G644" t="n">
-        <v>31.2520427703857</v>
+        <v>31.2520370483398</v>
       </c>
       <c r="H644" t="n">
         <v>161628</v>
@@ -19103,7 +19103,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="G646" t="n">
-        <v>29.9551219940186</v>
+        <v>29.9551258087158</v>
       </c>
       <c r="H646" t="n">
         <v>48258</v>
@@ -19132,7 +19132,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G647" t="n">
-        <v>30.1172389984131</v>
+        <v>30.1172370910645</v>
       </c>
       <c r="H647" t="n">
         <v>44619</v>
@@ -19161,7 +19161,7 @@
         <v>33.7599983215332</v>
       </c>
       <c r="G648" t="n">
-        <v>30.4054412841797</v>
+        <v>30.4054431915283</v>
       </c>
       <c r="H648" t="n">
         <v>33638</v>
@@ -19248,7 +19248,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G651" t="n">
-        <v>31.6483154296875</v>
+        <v>31.6483192443848</v>
       </c>
       <c r="H651" t="n">
         <v>95229</v>
@@ -19306,7 +19306,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G653" t="n">
-        <v>31.1079368591309</v>
+        <v>31.1079406738281</v>
       </c>
       <c r="H653" t="n">
         <v>70388</v>
@@ -19335,7 +19335,7 @@
         <v>34.8199996948242</v>
       </c>
       <c r="G654" t="n">
-        <v>31.3601131439209</v>
+        <v>31.3601188659668</v>
       </c>
       <c r="H654" t="n">
         <v>42779</v>
@@ -19364,7 +19364,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>30.9818515777588</v>
+        <v>30.9818534851074</v>
       </c>
       <c r="H655" t="n">
         <v>44556</v>
@@ -19393,7 +19393,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G656" t="n">
-        <v>31.7383861541748</v>
+        <v>31.7383823394775</v>
       </c>
       <c r="H656" t="n">
         <v>58243</v>
@@ -19422,7 +19422,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>31.2520427703857</v>
+        <v>31.2520370483398</v>
       </c>
       <c r="H657" t="n">
         <v>35703</v>
@@ -19451,7 +19451,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G658" t="n">
-        <v>31.6122894287109</v>
+        <v>31.6122913360596</v>
       </c>
       <c r="H658" t="n">
         <v>29583</v>
@@ -19480,7 +19480,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G659" t="n">
-        <v>31.7744083404541</v>
+        <v>31.7744064331055</v>
       </c>
       <c r="H659" t="n">
         <v>43655</v>
@@ -19509,7 +19509,7 @@
         <v>34.2400016784668</v>
       </c>
       <c r="G660" t="n">
-        <v>30.8377475738525</v>
+        <v>30.8377494812012</v>
       </c>
       <c r="H660" t="n">
         <v>41227</v>
@@ -19538,7 +19538,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G661" t="n">
-        <v>29.9190998077393</v>
+        <v>29.9191036224365</v>
       </c>
       <c r="H661" t="n">
         <v>36448</v>
@@ -19567,7 +19567,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G662" t="n">
-        <v>29.9010887145996</v>
+        <v>29.901086807251</v>
       </c>
       <c r="H662" t="n">
         <v>24019</v>
@@ -19683,7 +19683,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G666" t="n">
-        <v>28.7302627563477</v>
+        <v>28.730260848999</v>
       </c>
       <c r="H666" t="n">
         <v>17220</v>
@@ -19741,7 +19741,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G668" t="n">
-        <v>27.5954608917236</v>
+        <v>27.595458984375</v>
       </c>
       <c r="H668" t="n">
         <v>30813</v>
@@ -19886,7 +19886,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G673" t="n">
-        <v>27.2352066040039</v>
+        <v>27.2352085113525</v>
       </c>
       <c r="H673" t="n">
         <v>40742</v>
@@ -19915,7 +19915,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G674" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H674" t="n">
         <v>59352</v>
@@ -19944,7 +19944,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G675" t="n">
-        <v>27.1091175079346</v>
+        <v>27.1091156005859</v>
       </c>
       <c r="H675" t="n">
         <v>14694</v>
@@ -19973,7 +19973,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>27.1091175079346</v>
+        <v>27.1091156005859</v>
       </c>
       <c r="H676" t="n">
         <v>21986</v>
@@ -20060,7 +20060,7 @@
         <v>30.5</v>
       </c>
       <c r="G679" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693717956543</v>
       </c>
       <c r="H679" t="n">
         <v>30485</v>
@@ -20089,7 +20089,7 @@
         <v>31</v>
       </c>
       <c r="G680" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H680" t="n">
         <v>46685</v>
@@ -20205,7 +20205,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G684" t="n">
-        <v>27.8476390838623</v>
+        <v>27.8476371765137</v>
       </c>
       <c r="H684" t="n">
         <v>50842</v>
@@ -20263,7 +20263,7 @@
         <v>30.5</v>
       </c>
       <c r="G686" t="n">
-        <v>27.4693698883057</v>
+        <v>27.4693717956543</v>
       </c>
       <c r="H686" t="n">
         <v>52867</v>
@@ -20437,7 +20437,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G692" t="n">
-        <v>28.7302627563477</v>
+        <v>28.730260848999</v>
       </c>
       <c r="H692" t="n">
         <v>50743</v>
@@ -20524,7 +20524,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G695" t="n">
-        <v>29.1625671386719</v>
+        <v>29.1625690460205</v>
       </c>
       <c r="H695" t="n">
         <v>62299</v>
@@ -20582,7 +20582,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G697" t="n">
-        <v>28.6401958465576</v>
+        <v>28.6401977539062</v>
       </c>
       <c r="H697" t="n">
         <v>27160</v>
@@ -20611,7 +20611,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>28.6762237548828</v>
+        <v>28.6762218475342</v>
       </c>
       <c r="H698" t="n">
         <v>35302</v>
@@ -20669,7 +20669,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G700" t="n">
-        <v>27.055082321167</v>
+        <v>27.0550785064697</v>
       </c>
       <c r="H700" t="n">
         <v>32431</v>
@@ -20698,7 +20698,7 @@
         <v>30.6399993896484</v>
       </c>
       <c r="G701" t="n">
-        <v>27.5954608917236</v>
+        <v>27.595458984375</v>
       </c>
       <c r="H701" t="n">
         <v>221272</v>
@@ -20727,7 +20727,7 @@
         <v>31</v>
       </c>
       <c r="G702" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H702" t="n">
         <v>26734</v>
@@ -20785,7 +20785,7 @@
         <v>31</v>
       </c>
       <c r="G704" t="n">
-        <v>27.9196872711182</v>
+        <v>27.9196891784668</v>
       </c>
       <c r="H704" t="n">
         <v>37755</v>
@@ -20814,7 +20814,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G705" t="n">
-        <v>27.5594367980957</v>
+        <v>27.5594348907471</v>
       </c>
       <c r="H705" t="n">
         <v>27627</v>
@@ -20843,7 +20843,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>25.7581634521484</v>
+        <v>25.7581653594971</v>
       </c>
       <c r="H706" t="n">
         <v>55195</v>
@@ -20872,7 +20872,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>22.7320289611816</v>
+        <v>22.7320308685303</v>
       </c>
       <c r="H707" t="n">
         <v>196682</v>
@@ -20930,7 +20930,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G709" t="n">
-        <v>21.7233219146729</v>
+        <v>21.7233200073242</v>
       </c>
       <c r="H709" t="n">
         <v>130761</v>
@@ -20959,7 +20959,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G710" t="n">
-        <v>22.7860679626465</v>
+        <v>22.7860698699951</v>
       </c>
       <c r="H710" t="n">
         <v>107966</v>
@@ -21017,7 +21017,7 @@
         <v>26.3199996948242</v>
       </c>
       <c r="G712" t="n">
-        <v>23.7047176361084</v>
+        <v>23.7047157287598</v>
       </c>
       <c r="H712" t="n">
         <v>61152</v>
@@ -21075,7 +21075,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>23.236385345459</v>
+        <v>23.2363872528076</v>
       </c>
       <c r="H714" t="n">
         <v>56594</v>
@@ -21104,7 +21104,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G715" t="n">
-        <v>23.4345283508301</v>
+        <v>23.4345245361328</v>
       </c>
       <c r="H715" t="n">
         <v>56928</v>
@@ -21191,7 +21191,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G718" t="n">
-        <v>20.8226871490479</v>
+        <v>20.8226852416992</v>
       </c>
       <c r="H718" t="n">
         <v>40533</v>
@@ -21220,7 +21220,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G719" t="n">
-        <v>21.3630638122559</v>
+        <v>21.3630657196045</v>
       </c>
       <c r="H719" t="n">
         <v>42932</v>
@@ -21249,7 +21249,7 @@
         <v>23.5799999237061</v>
       </c>
       <c r="G720" t="n">
-        <v>21.2369747161865</v>
+        <v>21.2369766235352</v>
       </c>
       <c r="H720" t="n">
         <v>38258</v>
@@ -21278,7 +21278,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>21.3450527191162</v>
+        <v>21.3450546264648</v>
       </c>
       <c r="H721" t="n">
         <v>38719</v>
@@ -21307,7 +21307,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>21.5972290039062</v>
+        <v>21.5972309112549</v>
       </c>
       <c r="H722" t="n">
         <v>28389</v>
@@ -21365,7 +21365,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G724" t="n">
-        <v>18.3189182281494</v>
+        <v>18.318920135498</v>
       </c>
       <c r="H724" t="n">
         <v>205787</v>
@@ -21452,7 +21452,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G727" t="n">
-        <v>18.8773097991943</v>
+        <v>18.877311706543</v>
       </c>
       <c r="H727" t="n">
         <v>78461</v>
@@ -21539,7 +21539,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G730" t="n">
-        <v>18.3189182281494</v>
+        <v>18.318920135498</v>
       </c>
       <c r="H730" t="n">
         <v>43093</v>
@@ -21568,7 +21568,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G731" t="n">
-        <v>18.003698348999</v>
+        <v>18.0036964416504</v>
       </c>
       <c r="H731" t="n">
         <v>90396</v>
@@ -21626,7 +21626,7 @@
         <v>19</v>
       </c>
       <c r="G733" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H733" t="n">
         <v>71224</v>
@@ -21655,7 +21655,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G734" t="n">
-        <v>17.2651748657227</v>
+        <v>17.2651767730713</v>
       </c>
       <c r="H734" t="n">
         <v>108269</v>
@@ -21713,7 +21713,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G736" t="n">
-        <v>16.202428817749</v>
+        <v>16.2024250030518</v>
       </c>
       <c r="H736" t="n">
         <v>53336</v>
@@ -21742,7 +21742,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G737" t="n">
-        <v>15.950249671936</v>
+        <v>15.9502487182617</v>
       </c>
       <c r="H737" t="n">
         <v>57508</v>
@@ -21771,7 +21771,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G738" t="n">
-        <v>15.7160806655884</v>
+        <v>15.7160835266113</v>
       </c>
       <c r="H738" t="n">
         <v>81701</v>
@@ -21800,7 +21800,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>15.6800565719604</v>
+        <v>15.6800594329834</v>
       </c>
       <c r="H739" t="n">
         <v>56603</v>
@@ -21887,7 +21887,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G742" t="n">
-        <v>16.6077136993408</v>
+        <v>16.6077117919922</v>
       </c>
       <c r="H742" t="n">
         <v>126448</v>
@@ -22061,7 +22061,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G748" t="n">
-        <v>18.8232727050781</v>
+        <v>18.8232746124268</v>
       </c>
       <c r="H748" t="n">
         <v>195178</v>
@@ -22090,7 +22090,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G749" t="n">
-        <v>17.6614570617676</v>
+        <v>17.6614551544189</v>
       </c>
       <c r="H749" t="n">
         <v>103574</v>
@@ -22119,7 +22119,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>16.7968444824219</v>
+        <v>16.7968482971191</v>
       </c>
       <c r="H750" t="n">
         <v>72692</v>
@@ -22235,7 +22235,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G754" t="n">
-        <v>16.2654685974121</v>
+        <v>16.2654705047607</v>
       </c>
       <c r="H754" t="n">
         <v>85504</v>
@@ -22293,7 +22293,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G756" t="n">
-        <v>15.7250890731812</v>
+        <v>15.7250881195068</v>
       </c>
       <c r="H756" t="n">
         <v>68222</v>
@@ -22351,7 +22351,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G758" t="n">
-        <v>15.0496139526367</v>
+        <v>15.0496101379395</v>
       </c>
       <c r="H758" t="n">
         <v>39650</v>
@@ -22380,7 +22380,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G759" t="n">
-        <v>15.6800565719604</v>
+        <v>15.6800594329834</v>
       </c>
       <c r="H759" t="n">
         <v>53012</v>
@@ -22438,7 +22438,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G761" t="n">
-        <v>15.5899925231934</v>
+        <v>15.5899934768677</v>
       </c>
       <c r="H761" t="n">
         <v>79930</v>
@@ -22496,7 +22496,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G763" t="n">
-        <v>15.4639024734497</v>
+        <v>15.463906288147</v>
       </c>
       <c r="H763" t="n">
         <v>62260</v>
@@ -22554,7 +22554,7 @@
         <v>19.75</v>
       </c>
       <c r="G765" t="n">
-        <v>17.7875442504883</v>
+        <v>17.7875423431396</v>
       </c>
       <c r="H765" t="n">
         <v>142876</v>
@@ -22583,7 +22583,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H766" t="n">
         <v>115896</v>
@@ -22641,7 +22641,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G768" t="n">
-        <v>17.3912620544434</v>
+        <v>17.391263961792</v>
       </c>
       <c r="H768" t="n">
         <v>73850</v>
@@ -22699,7 +22699,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G770" t="n">
-        <v>18.0487289428711</v>
+        <v>18.0487270355225</v>
       </c>
       <c r="H770" t="n">
         <v>44229</v>
@@ -22728,7 +22728,7 @@
         <v>20.2399997711182</v>
       </c>
       <c r="G771" t="n">
-        <v>18.2288551330566</v>
+        <v>18.228853225708</v>
       </c>
       <c r="H771" t="n">
         <v>74008</v>
@@ -22844,7 +22844,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G775" t="n">
-        <v>17.4543075561523</v>
+        <v>17.454309463501</v>
       </c>
       <c r="H775" t="n">
         <v>38968</v>
@@ -22873,7 +22873,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>18.6791725158691</v>
+        <v>18.6791744232178</v>
       </c>
       <c r="H776" t="n">
         <v>84665</v>
@@ -22902,7 +22902,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G777" t="n">
-        <v>18.8052616119385</v>
+        <v>18.8052597045898</v>
       </c>
       <c r="H777" t="n">
         <v>56710</v>
@@ -22931,7 +22931,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G778" t="n">
-        <v>18.6251335144043</v>
+        <v>18.6251354217529</v>
       </c>
       <c r="H778" t="n">
         <v>52083</v>
@@ -22960,7 +22960,7 @@
         <v>20.3600006103516</v>
       </c>
       <c r="G779" t="n">
-        <v>18.3369331359863</v>
+        <v>18.3369312286377</v>
       </c>
       <c r="H779" t="n">
         <v>51138</v>
@@ -22989,7 +22989,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G780" t="n">
-        <v>18.6251335144043</v>
+        <v>18.6251354217529</v>
       </c>
       <c r="H780" t="n">
         <v>25837</v>
@@ -23076,7 +23076,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G783" t="n">
-        <v>18.7872486114502</v>
+        <v>18.7872505187988</v>
       </c>
       <c r="H783" t="n">
         <v>33247</v>
@@ -23105,7 +23105,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G784" t="n">
-        <v>18.6971874237061</v>
+        <v>18.6971855163574</v>
       </c>
       <c r="H784" t="n">
         <v>38581</v>
@@ -23134,7 +23134,7 @@
         <v>20.3799991607666</v>
       </c>
       <c r="G785" t="n">
-        <v>18.354944229126</v>
+        <v>18.3549423217773</v>
       </c>
       <c r="H785" t="n">
         <v>61250</v>
@@ -23279,7 +23279,7 @@
         <v>19.9699993133545</v>
       </c>
       <c r="G790" t="n">
-        <v>17.9856815338135</v>
+        <v>17.9856834411621</v>
       </c>
       <c r="H790" t="n">
         <v>73749</v>
@@ -23308,7 +23308,7 @@
         <v>19.2700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>17.3552398681641</v>
+        <v>17.3552379608154</v>
       </c>
       <c r="H791" t="n">
         <v>65355</v>
@@ -23366,7 +23366,7 @@
         <v>20.3199996948242</v>
       </c>
       <c r="G793" t="n">
-        <v>18.3009052276611</v>
+        <v>18.3009071350098</v>
       </c>
       <c r="H793" t="n">
         <v>28327</v>
@@ -23395,7 +23395,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G794" t="n">
-        <v>18.607120513916</v>
+        <v>18.6071224212646</v>
       </c>
       <c r="H794" t="n">
         <v>106399</v>
@@ -23482,7 +23482,7 @@
         <v>22.4799995422363</v>
       </c>
       <c r="G797" t="n">
-        <v>20.2462749481201</v>
+        <v>20.2462768554688</v>
       </c>
       <c r="H797" t="n">
         <v>77155</v>
@@ -23627,7 +23627,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G802" t="n">
-        <v>20.2823028564453</v>
+        <v>20.2823047637939</v>
       </c>
       <c r="H802" t="n">
         <v>63858</v>
@@ -23656,7 +23656,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G803" t="n">
-        <v>18.8232727050781</v>
+        <v>18.8232746124268</v>
       </c>
       <c r="H803" t="n">
         <v>287829</v>
@@ -23685,7 +23685,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G804" t="n">
-        <v>17.7515163421631</v>
+        <v>17.7515182495117</v>
       </c>
       <c r="H804" t="n">
         <v>362073</v>
@@ -23714,7 +23714,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G805" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H805" t="n">
         <v>140580</v>
@@ -23743,7 +23743,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G806" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H806" t="n">
         <v>91990</v>
@@ -23801,7 +23801,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G808" t="n">
-        <v>17.5083446502686</v>
+        <v>17.5083484649658</v>
       </c>
       <c r="H808" t="n">
         <v>79412</v>
@@ -23859,7 +23859,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G810" t="n">
-        <v>16.8508834838867</v>
+        <v>16.8508815765381</v>
       </c>
       <c r="H810" t="n">
         <v>142958</v>
@@ -23917,7 +23917,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G812" t="n">
-        <v>16.868896484375</v>
+        <v>16.8688945770264</v>
       </c>
       <c r="H812" t="n">
         <v>61620</v>
@@ -23946,7 +23946,7 @@
         <v>19</v>
       </c>
       <c r="G813" t="n">
-        <v>17.1120681762695</v>
+        <v>17.1120662689209</v>
       </c>
       <c r="H813" t="n">
         <v>36891</v>
@@ -23975,7 +23975,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G814" t="n">
-        <v>17.0490226745605</v>
+        <v>17.0490245819092</v>
       </c>
       <c r="H814" t="n">
         <v>19771</v>
@@ -24033,7 +24033,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G816" t="n">
-        <v>17.3462352752686</v>
+        <v>17.3462333679199</v>
       </c>
       <c r="H816" t="n">
         <v>103910</v>
@@ -24062,7 +24062,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G817" t="n">
-        <v>17.2741813659668</v>
+        <v>17.2741832733154</v>
       </c>
       <c r="H817" t="n">
         <v>92869</v>
@@ -24091,7 +24091,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>17.3822574615479</v>
+        <v>17.3822555541992</v>
       </c>
       <c r="H818" t="n">
         <v>52262</v>
@@ -24120,7 +24120,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G819" t="n">
-        <v>17.2831878662109</v>
+        <v>17.2831897735596</v>
       </c>
       <c r="H819" t="n">
         <v>39049</v>
@@ -24207,7 +24207,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G822" t="n">
-        <v>17.7425117492676</v>
+        <v>17.7425136566162</v>
       </c>
       <c r="H822" t="n">
         <v>123143</v>
@@ -24265,7 +24265,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G824" t="n">
-        <v>17.6614570617676</v>
+        <v>17.6614551544189</v>
       </c>
       <c r="H824" t="n">
         <v>72694</v>
@@ -24323,7 +24323,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G826" t="n">
-        <v>17.4543075561523</v>
+        <v>17.454309463501</v>
       </c>
       <c r="H826" t="n">
         <v>48981</v>
@@ -24381,7 +24381,7 @@
         <v>19.8899993896484</v>
       </c>
       <c r="G828" t="n">
-        <v>17.913631439209</v>
+        <v>17.9136295318604</v>
       </c>
       <c r="H828" t="n">
         <v>52651</v>
@@ -24468,7 +24468,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G831" t="n">
-        <v>18.1928272247314</v>
+        <v>18.1928310394287</v>
       </c>
       <c r="H831" t="n">
         <v>225382</v>
@@ -24526,7 +24526,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>17.3822574615479</v>
+        <v>17.3822555541992</v>
       </c>
       <c r="H833" t="n">
         <v>127471</v>
@@ -24555,7 +24555,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G834" t="n">
-        <v>17.2381553649902</v>
+        <v>17.2381572723389</v>
       </c>
       <c r="H834" t="n">
         <v>111270</v>
@@ -24642,7 +24642,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>17.9676704406738</v>
+        <v>17.9676723480225</v>
       </c>
       <c r="H837" t="n">
         <v>49207</v>
@@ -24671,7 +24671,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G838" t="n">
-        <v>18.084753036499</v>
+        <v>18.0847549438477</v>
       </c>
       <c r="H838" t="n">
         <v>56369</v>
@@ -24729,7 +24729,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G840" t="n">
-        <v>17.8686008453369</v>
+        <v>17.8686027526855</v>
       </c>
       <c r="H840" t="n">
         <v>52488</v>
@@ -24816,7 +24816,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>17.6074161529541</v>
+        <v>17.6074180603027</v>
       </c>
       <c r="H843" t="n">
         <v>31630</v>
@@ -24903,7 +24903,7 @@
         <v>19.8400001525879</v>
       </c>
       <c r="G846" t="n">
-        <v>17.8686008453369</v>
+        <v>17.8686027526855</v>
       </c>
       <c r="H846" t="n">
         <v>91137</v>
@@ -24932,7 +24932,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G847" t="n">
-        <v>18.1568050384521</v>
+        <v>18.1568031311035</v>
       </c>
       <c r="H847" t="n">
         <v>58676</v>
@@ -24961,7 +24961,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G848" t="n">
-        <v>18.6365566253662</v>
+        <v>18.6365585327148</v>
       </c>
       <c r="H848" t="n">
         <v>152183</v>
@@ -25077,7 +25077,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G852" t="n">
-        <v>16.5330257415771</v>
+        <v>16.5330238342285</v>
       </c>
       <c r="H852" t="n">
         <v>79775</v>
@@ -25106,7 +25106,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G853" t="n">
-        <v>16.1916599273682</v>
+        <v>16.1916618347168</v>
       </c>
       <c r="H853" t="n">
         <v>63194</v>
@@ -25135,7 +25135,7 @@
         <v>17</v>
       </c>
       <c r="G854" t="n">
-        <v>15.6842317581177</v>
+        <v>15.6842308044434</v>
       </c>
       <c r="H854" t="n">
         <v>96763</v>
@@ -25164,7 +25164,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G855" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232404708862</v>
       </c>
       <c r="H855" t="n">
         <v>212131</v>
@@ -25193,7 +25193,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G856" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021249771118</v>
       </c>
       <c r="H856" t="n">
         <v>215640</v>
@@ -25222,7 +25222,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G857" t="n">
-        <v>13.9405136108398</v>
+        <v>13.9405145645142</v>
       </c>
       <c r="H857" t="n">
         <v>212931</v>
@@ -25251,7 +25251,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G858" t="n">
-        <v>13.7836713790894</v>
+        <v>13.7836723327637</v>
       </c>
       <c r="H858" t="n">
         <v>100376</v>
@@ -25280,7 +25280,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>13.3131446838379</v>
+        <v>13.3131456375122</v>
       </c>
       <c r="H859" t="n">
         <v>77696</v>
@@ -25425,7 +25425,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G864" t="n">
-        <v>13.0732688903809</v>
+        <v>13.0732679367065</v>
       </c>
       <c r="H864" t="n">
         <v>32835</v>
@@ -25454,7 +25454,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G865" t="n">
-        <v>13.0732688903809</v>
+        <v>13.0732679367065</v>
       </c>
       <c r="H865" t="n">
         <v>61566</v>
@@ -25483,7 +25483,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G866" t="n">
-        <v>13.0179119110107</v>
+        <v>13.0179128646851</v>
       </c>
       <c r="H866" t="n">
         <v>46939</v>
@@ -25570,7 +25570,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>13.1009454727173</v>
+        <v>13.1009473800659</v>
       </c>
       <c r="H869" t="n">
         <v>110683</v>
@@ -25628,7 +25628,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G871" t="n">
-        <v>13.9220628738403</v>
+        <v>13.922061920166</v>
       </c>
       <c r="H871" t="n">
         <v>162028</v>
@@ -25715,7 +25715,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>14.4202671051025</v>
+        <v>14.4202680587769</v>
       </c>
       <c r="H874" t="n">
         <v>118791</v>
@@ -25773,7 +25773,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G876" t="n">
-        <v>13.8298015594482</v>
+        <v>13.8298025131226</v>
       </c>
       <c r="H876" t="n">
         <v>258135</v>
@@ -25802,7 +25802,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G877" t="n">
-        <v>13.9220628738403</v>
+        <v>13.922061920166</v>
       </c>
       <c r="H877" t="n">
         <v>53138</v>
@@ -25860,7 +25860,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G879" t="n">
-        <v>13.6914129257202</v>
+        <v>13.6914119720459</v>
       </c>
       <c r="H879" t="n">
         <v>39249</v>
@@ -25918,7 +25918,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G881" t="n">
-        <v>13.7836713790894</v>
+        <v>13.7836723327637</v>
       </c>
       <c r="H881" t="n">
         <v>79376</v>
@@ -25947,7 +25947,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G882" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H882" t="n">
         <v>171512</v>
@@ -26063,7 +26063,7 @@
         <v>11</v>
       </c>
       <c r="G886" t="n">
-        <v>10.1486215591431</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H886" t="n">
         <v>520891</v>
@@ -26266,7 +26266,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.9236059188843</v>
+        <v>10.9236068725586</v>
       </c>
       <c r="H893" t="n">
         <v>126439</v>
@@ -26295,7 +26295,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G894" t="n">
-        <v>10.4807558059692</v>
+        <v>10.4807567596436</v>
       </c>
       <c r="H894" t="n">
         <v>222824</v>
@@ -26324,7 +26324,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G895" t="n">
-        <v>10.6837291717529</v>
+        <v>10.6837301254272</v>
       </c>
       <c r="H895" t="n">
         <v>124644</v>
@@ -26411,7 +26411,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G898" t="n">
-        <v>10.3700437545776</v>
+        <v>10.370044708252</v>
       </c>
       <c r="H898" t="n">
         <v>110215</v>
@@ -26469,7 +26469,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G900" t="n">
-        <v>10.1762971878052</v>
+        <v>10.1762981414795</v>
       </c>
       <c r="H900" t="n">
         <v>261491</v>
@@ -26527,7 +26527,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G902" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964317321777</v>
       </c>
       <c r="H902" t="n">
         <v>198170</v>
@@ -26672,7 +26672,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H907" t="n">
         <v>168958</v>
@@ -26759,7 +26759,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.4438543319702</v>
+        <v>10.4438524246216</v>
       </c>
       <c r="H910" t="n">
         <v>188704</v>
@@ -26788,7 +26788,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H911" t="n">
         <v>88660</v>
@@ -26846,7 +26846,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G913" t="n">
-        <v>10.0286827087402</v>
+        <v>10.0286817550659</v>
       </c>
       <c r="H913" t="n">
         <v>207382</v>
@@ -26875,7 +26875,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.9640998840332</v>
+        <v>9.96410083770752</v>
       </c>
       <c r="H914" t="n">
         <v>253876</v>
@@ -26933,7 +26933,7 @@
         <v>11</v>
       </c>
       <c r="G916" t="n">
-        <v>10.1486215591431</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H916" t="n">
         <v>218887</v>
@@ -26991,7 +26991,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G918" t="n">
-        <v>9.50279998779297</v>
+        <v>9.50279903411865</v>
       </c>
       <c r="H918" t="n">
         <v>261117</v>
@@ -27107,7 +27107,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G922" t="n">
-        <v>9.40131282806396</v>
+        <v>9.40131187438965</v>
       </c>
       <c r="H922" t="n">
         <v>105250</v>
@@ -27136,7 +27136,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G923" t="n">
-        <v>9.65964126586914</v>
+        <v>9.65964317321777</v>
       </c>
       <c r="H923" t="n">
         <v>86848</v>
@@ -27252,7 +27252,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G927" t="n">
-        <v>9.20295333862305</v>
+        <v>9.20295429229736</v>
       </c>
       <c r="H927" t="n">
         <v>196192</v>
@@ -27397,7 +27397,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G932" t="n">
-        <v>9.24447154998779</v>
+        <v>9.24447059631348</v>
       </c>
       <c r="H932" t="n">
         <v>161867</v>
@@ -27513,7 +27513,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G936" t="n">
-        <v>9.88106632232666</v>
+        <v>9.88106536865234</v>
       </c>
       <c r="H936" t="n">
         <v>328350</v>
@@ -27571,7 +27571,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G938" t="n">
-        <v>9.99177837371826</v>
+        <v>9.99177742004395</v>
       </c>
       <c r="H938" t="n">
         <v>283851</v>
@@ -27600,7 +27600,7 @@
         <v>11</v>
       </c>
       <c r="G939" t="n">
-        <v>10.1486215591431</v>
+        <v>10.1486206054688</v>
       </c>
       <c r="H939" t="n">
         <v>195612</v>
@@ -27629,7 +27629,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>10.2408809661865</v>
+        <v>10.2408819198608</v>
       </c>
       <c r="H940" t="n">
         <v>178359</v>
@@ -27687,7 +27687,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G942" t="n">
-        <v>10.4346284866333</v>
+        <v>10.434627532959</v>
       </c>
       <c r="H942" t="n">
         <v>114649</v>
@@ -27803,7 +27803,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G946" t="n">
-        <v>10.0286827087402</v>
+        <v>10.0286817550659</v>
       </c>
       <c r="H946" t="n">
         <v>131456</v>
@@ -27861,7 +27861,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G948" t="n">
-        <v>9.66886615753174</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H948" t="n">
         <v>129728</v>
@@ -27977,7 +27977,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>9.66886615753174</v>
+        <v>9.66886711120605</v>
       </c>
       <c r="H952" t="n">
         <v>80416</v>
@@ -28093,7 +28093,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G956" t="n">
-        <v>9.2629222869873</v>
+        <v>9.26292324066162</v>
       </c>
       <c r="H956" t="n">
         <v>124882</v>
@@ -28122,7 +28122,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G957" t="n">
-        <v>9.39208793640137</v>
+        <v>9.39208698272705</v>
       </c>
       <c r="H957" t="n">
         <v>68256</v>
@@ -28151,7 +28151,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G958" t="n">
-        <v>9.65041637420654</v>
+        <v>9.65041542053223</v>
       </c>
       <c r="H958" t="n">
         <v>160776</v>
@@ -28209,7 +28209,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>9.31827831268311</v>
+        <v>9.31827926635742</v>
       </c>
       <c r="H960" t="n">
         <v>109157</v>
@@ -28325,7 +28325,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G964" t="n">
-        <v>9.88106632232666</v>
+        <v>9.88106536865234</v>
       </c>
       <c r="H964" t="n">
         <v>91898</v>
@@ -28412,7 +28412,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G967" t="n">
-        <v>9.49357223510742</v>
+        <v>9.49357318878174</v>
       </c>
       <c r="H967" t="n">
         <v>153985</v>
@@ -28441,7 +28441,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G968" t="n">
-        <v>10.2777853012085</v>
+        <v>10.2777843475342</v>
       </c>
       <c r="H968" t="n">
         <v>321790</v>
@@ -28470,7 +28470,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G969" t="n">
-        <v>10.0655851364136</v>
+        <v>10.0655870437622</v>
       </c>
       <c r="H969" t="n">
         <v>218375</v>
@@ -28499,7 +28499,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G970" t="n">
-        <v>10.5822439193726</v>
+        <v>10.5822429656982</v>
       </c>
       <c r="H970" t="n">
         <v>229401</v>
@@ -28528,7 +28528,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G971" t="n">
-        <v>10.7298612594604</v>
+        <v>10.7298593521118</v>
       </c>
       <c r="H971" t="n">
         <v>258960</v>
@@ -28586,7 +28586,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G973" t="n">
-        <v>10.5084352493286</v>
+        <v>10.5084362030029</v>
       </c>
       <c r="H973" t="n">
         <v>181987</v>
@@ -28644,7 +28644,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G975" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H975" t="n">
         <v>397866</v>
@@ -28673,7 +28673,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>10.3515930175781</v>
+        <v>10.3515939712524</v>
       </c>
       <c r="H976" t="n">
         <v>149030</v>
@@ -28818,7 +28818,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G981" t="n">
-        <v>12.1322145462036</v>
+        <v>12.1322135925293</v>
       </c>
       <c r="H981" t="n">
         <v>240991</v>
@@ -28876,7 +28876,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G983" t="n">
-        <v>12.1414413452148</v>
+        <v>12.1414403915405</v>
       </c>
       <c r="H983" t="n">
         <v>156365</v>
@@ -28905,7 +28905,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>12.1875705718994</v>
+        <v>12.1875715255737</v>
       </c>
       <c r="H984" t="n">
         <v>154181</v>
@@ -28992,7 +28992,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G987" t="n">
-        <v>11.9569206237793</v>
+        <v>11.956919670105</v>
       </c>
       <c r="H987" t="n">
         <v>141835</v>
@@ -29021,7 +29021,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G988" t="n">
-        <v>11.7539472579956</v>
+        <v>11.7539482116699</v>
       </c>
       <c r="H988" t="n">
         <v>186372</v>
@@ -29108,7 +29108,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G991" t="n">
-        <v>11.7354955673218</v>
+        <v>11.7354965209961</v>
       </c>
       <c r="H991" t="n">
         <v>225836</v>
@@ -29137,7 +29137,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G992" t="n">
-        <v>12.0676326751709</v>
+        <v>12.0676317214966</v>
       </c>
       <c r="H992" t="n">
         <v>237186</v>
@@ -29166,7 +29166,7 @@
         <v>13.5</v>
       </c>
       <c r="G993" t="n">
-        <v>12.4551248550415</v>
+        <v>12.4551258087158</v>
       </c>
       <c r="H993" t="n">
         <v>251556</v>
@@ -29224,7 +29224,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G995" t="n">
-        <v>13.2485628128052</v>
+        <v>13.2485637664795</v>
       </c>
       <c r="H995" t="n">
         <v>409482</v>
@@ -29369,7 +29369,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1000" t="n">
-        <v>13.7559938430786</v>
+        <v>13.7559928894043</v>
       </c>
       <c r="H1000" t="n">
         <v>343538</v>
@@ -29398,7 +29398,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1001" t="n">
-        <v>13.7098636627197</v>
+        <v>13.7098627090454</v>
       </c>
       <c r="H1001" t="n">
         <v>329930</v>
@@ -29427,7 +29427,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G1002" t="n">
-        <v>13.7744464874268</v>
+        <v>13.7744455337524</v>
       </c>
       <c r="H1002" t="n">
         <v>214342</v>
@@ -29485,7 +29485,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G1004" t="n">
-        <v>13.7744464874268</v>
+        <v>13.7744455337524</v>
       </c>
       <c r="H1004" t="n">
         <v>370057</v>
@@ -29543,7 +29543,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1006" t="n">
-        <v>13.7283153533936</v>
+        <v>13.7283163070679</v>
       </c>
       <c r="H1006" t="n">
         <v>219263</v>
@@ -29572,7 +29572,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.0143213272095</v>
+        <v>14.0143222808838</v>
       </c>
       <c r="H1007" t="n">
         <v>371820</v>
@@ -29659,7 +29659,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G1010" t="n">
-        <v>13.7744464874268</v>
+        <v>13.7744455337524</v>
       </c>
       <c r="H1010" t="n">
         <v>195269</v>
@@ -29688,7 +29688,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1011" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497413635254</v>
       </c>
       <c r="H1011" t="n">
         <v>66991</v>
@@ -29833,7 +29833,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.4571714401245</v>
+        <v>14.4571704864502</v>
       </c>
       <c r="H1016" t="n">
         <v>517730</v>
@@ -30036,7 +30036,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1023" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497413635254</v>
       </c>
       <c r="H1023" t="n">
         <v>109674</v>
@@ -30094,7 +30094,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1025" t="n">
-        <v>13.9312887191772</v>
+        <v>13.9312896728516</v>
       </c>
       <c r="H1025" t="n">
         <v>191887</v>
@@ -30123,7 +30123,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.64732837677</v>
+        <v>15.6473274230957</v>
       </c>
       <c r="H1026" t="n">
         <v>1111920</v>
@@ -30152,7 +30152,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.7303609848022</v>
+        <v>15.7303619384766</v>
       </c>
       <c r="H1027" t="n">
         <v>948892</v>
@@ -30210,7 +30210,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1029" t="n">
-        <v>16.791353225708</v>
+        <v>16.7913551330566</v>
       </c>
       <c r="H1029" t="n">
         <v>366910</v>
@@ -30297,7 +30297,7 @@
         <v>18.2299995422363</v>
       </c>
       <c r="G1032" t="n">
-        <v>16.8190326690674</v>
+        <v>16.8190307617188</v>
       </c>
       <c r="H1032" t="n">
         <v>152525</v>
@@ -30384,7 +30384,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1035" t="n">
-        <v>15.9333333969116</v>
+        <v>15.9333362579346</v>
       </c>
       <c r="H1035" t="n">
         <v>130687</v>
@@ -30442,7 +30442,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.678596496582</v>
+        <v>14.6785955429077</v>
       </c>
       <c r="H1037" t="n">
         <v>251460</v>
@@ -30471,7 +30471,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.3187808990479</v>
+        <v>14.3187818527222</v>
       </c>
       <c r="H1038" t="n">
         <v>248886</v>
@@ -30500,7 +30500,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1039" t="n">
-        <v>14.8446645736694</v>
+        <v>14.8446636199951</v>
       </c>
       <c r="H1039" t="n">
         <v>220373</v>
@@ -30587,7 +30587,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1042" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1042" t="n">
         <v>250873</v>
@@ -30616,7 +30616,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1043" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1043" t="n">
         <v>139842</v>
@@ -30645,7 +30645,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>14.8538913726807</v>
+        <v>14.8538904190063</v>
       </c>
       <c r="H1044" t="n">
         <v>138232</v>
@@ -30703,7 +30703,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1046" t="n">
-        <v>15.2506084442139</v>
+        <v>15.2506103515625</v>
       </c>
       <c r="H1046" t="n">
         <v>126441</v>
@@ -30732,7 +30732,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1047" t="n">
-        <v>14.9830551147461</v>
+        <v>14.9830532073975</v>
       </c>
       <c r="H1047" t="n">
         <v>106006</v>
@@ -30761,7 +30761,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.1583480834961</v>
+        <v>15.1583490371704</v>
       </c>
       <c r="H1048" t="n">
         <v>75769</v>
@@ -30848,7 +30848,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1051" t="n">
-        <v>14.8538913726807</v>
+        <v>14.8538904190063</v>
       </c>
       <c r="H1051" t="n">
         <v>129321</v>
@@ -30906,7 +30906,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>12.6027412414551</v>
+        <v>12.6027421951294</v>
       </c>
       <c r="H1053" t="n">
         <v>435284</v>
@@ -30935,7 +30935,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>12.0399541854858</v>
+        <v>12.0399551391602</v>
       </c>
       <c r="H1054" t="n">
         <v>314929</v>
@@ -31022,7 +31022,7 @@
         <v>12.25</v>
       </c>
       <c r="G1057" t="n">
-        <v>11.3018732070923</v>
+        <v>11.301872253418</v>
       </c>
       <c r="H1057" t="n">
         <v>355369</v>
@@ -31051,7 +31051,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1058" t="n">
-        <v>10.6006946563721</v>
+        <v>10.6006956100464</v>
       </c>
       <c r="H1058" t="n">
         <v>282297</v>
@@ -31080,7 +31080,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1059" t="n">
-        <v>10.4254016876221</v>
+        <v>10.4254007339478</v>
       </c>
       <c r="H1059" t="n">
         <v>236701</v>
@@ -31225,7 +31225,7 @@
         <v>8.64500045776367</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.97589349746704</v>
+        <v>7.9758939743042</v>
       </c>
       <c r="H1064" t="n">
         <v>361762</v>
@@ -31254,7 +31254,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285898208618</v>
       </c>
       <c r="H1065" t="n">
         <v>433976</v>
@@ -31283,7 +31283,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.55047273635864</v>
+        <v>6.55047369003296</v>
       </c>
       <c r="H1066" t="n">
         <v>390315</v>
@@ -31370,7 +31370,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.98409652709961</v>
+        <v>6.98409605026245</v>
       </c>
       <c r="H1069" t="n">
         <v>157083</v>
@@ -31428,7 +31428,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.01177358627319</v>
+        <v>7.01177453994751</v>
       </c>
       <c r="H1071" t="n">
         <v>100213</v>
@@ -31515,7 +31515,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.85697746276855</v>
+        <v>8.85697841644287</v>
       </c>
       <c r="H1074" t="n">
         <v>167191</v>
@@ -31544,7 +31544,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1075" t="n">
-        <v>9.33673095703125</v>
+        <v>9.33673000335693</v>
       </c>
       <c r="H1075" t="n">
         <v>210439</v>
@@ -31602,7 +31602,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1077" t="n">
-        <v>8.395676612854</v>
+        <v>8.39567756652832</v>
       </c>
       <c r="H1077" t="n">
         <v>136313</v>
@@ -31631,7 +31631,7 @@
         <v>9.10499954223633</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.40028953552246</v>
+        <v>8.40029048919678</v>
       </c>
       <c r="H1078" t="n">
         <v>48370</v>
@@ -31689,7 +31689,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.25728607177734</v>
+        <v>8.25728702545166</v>
       </c>
       <c r="H1080" t="n">
         <v>73798</v>
@@ -31718,7 +31718,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.11889743804932</v>
+        <v>8.11889553070068</v>
       </c>
       <c r="H1081" t="n">
         <v>72725</v>
@@ -31776,7 +31776,7 @@
         <v>8.59500026702881</v>
       </c>
       <c r="G1083" t="n">
-        <v>7.929762840271</v>
+        <v>7.92976331710815</v>
       </c>
       <c r="H1083" t="n">
         <v>60718</v>
@@ -31805,7 +31805,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1084" t="n">
-        <v>7.78675937652588</v>
+        <v>7.78675985336304</v>
       </c>
       <c r="H1084" t="n">
         <v>156268</v>
@@ -31863,7 +31863,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1086" t="n">
-        <v>7.8928599357605</v>
+        <v>7.89285898208618</v>
       </c>
       <c r="H1086" t="n">
         <v>212254</v>
@@ -31892,7 +31892,7 @@
         <v>8.5</v>
       </c>
       <c r="G1087" t="n">
-        <v>7.84211587905884</v>
+        <v>7.84211540222168</v>
       </c>
       <c r="H1087" t="n">
         <v>132894</v>
@@ -31950,7 +31950,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1089" t="n">
-        <v>7.42694568634033</v>
+        <v>7.42694520950317</v>
       </c>
       <c r="H1089" t="n">
         <v>94583</v>
@@ -31979,7 +31979,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1090" t="n">
-        <v>7.42694568634033</v>
+        <v>7.42694520950317</v>
       </c>
       <c r="H1090" t="n">
         <v>124531</v>
@@ -32124,7 +32124,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G1095" t="n">
-        <v>7.11326026916504</v>
+        <v>7.1132607460022</v>
       </c>
       <c r="H1095" t="n">
         <v>69984</v>
@@ -32269,7 +32269,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>7.33929824829102</v>
+        <v>7.33929777145386</v>
       </c>
       <c r="H1100" t="n">
         <v>190738</v>
@@ -32298,7 +32298,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1101" t="n">
-        <v>7.51920461654663</v>
+        <v>7.51920509338379</v>
       </c>
       <c r="H1101" t="n">
         <v>66663</v>
@@ -32327,7 +32327,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>7.30700635910034</v>
+        <v>7.30700731277466</v>
       </c>
       <c r="H1102" t="n">
         <v>85960</v>
@@ -32385,7 +32385,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>7.10403394699097</v>
+        <v>7.10403442382812</v>
       </c>
       <c r="H1104" t="n">
         <v>88763</v>
@@ -32414,7 +32414,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1105" t="n">
-        <v>7.15939044952393</v>
+        <v>7.15939092636108</v>
       </c>
       <c r="H1105" t="n">
         <v>90167</v>
@@ -32443,7 +32443,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.30700635910034</v>
+        <v>7.30700731277466</v>
       </c>
       <c r="H1106" t="n">
         <v>150317</v>
@@ -32501,7 +32501,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.92874050140381</v>
+        <v>6.92874002456665</v>
       </c>
       <c r="H1108" t="n">
         <v>182143</v>
@@ -32559,7 +32559,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1110" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533479690552</v>
       </c>
       <c r="H1110" t="n">
         <v>160774</v>
@@ -32588,7 +32588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>7.56533527374268</v>
+        <v>7.56533479690552</v>
       </c>
       <c r="H1111" t="n">
         <v>124418</v>
@@ -32675,7 +32675,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1114" t="n">
-        <v>7.27010297775269</v>
+        <v>7.27010250091553</v>
       </c>
       <c r="H1114" t="n">
         <v>241372</v>
@@ -32704,7 +32704,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1115" t="n">
-        <v>7.72217798233032</v>
+        <v>7.72217750549316</v>
       </c>
       <c r="H1115" t="n">
         <v>329478</v>
@@ -32733,7 +32733,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.46948528289795</v>
+        <v>8.46948623657227</v>
       </c>
       <c r="H1116" t="n">
         <v>379600</v>
@@ -32762,7 +32762,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.66784477233887</v>
+        <v>8.66784572601318</v>
       </c>
       <c r="H1117" t="n">
         <v>353840</v>
@@ -32791,7 +32791,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1118" t="n">
-        <v>8.90310764312744</v>
+        <v>8.90310668945312</v>
       </c>
       <c r="H1118" t="n">
         <v>292199</v>
@@ -32849,7 +32849,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.69091033935547</v>
+        <v>8.69090938568115</v>
       </c>
       <c r="H1120" t="n">
         <v>95726</v>
@@ -32878,7 +32878,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.8754301071167</v>
+        <v>8.87543106079102</v>
       </c>
       <c r="H1121" t="n">
         <v>174840</v>
@@ -32907,7 +32907,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1122" t="n">
-        <v>9.32750511169434</v>
+        <v>9.32750415802002</v>
       </c>
       <c r="H1122" t="n">
         <v>250872</v>
@@ -32965,7 +32965,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>11.4863929748535</v>
+        <v>11.4863939285278</v>
       </c>
       <c r="H1124" t="n">
         <v>1306894</v>
@@ -32994,7 +32994,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1125" t="n">
-        <v>11.4956188201904</v>
+        <v>11.4956197738647</v>
       </c>
       <c r="H1125" t="n">
         <v>412132</v>
@@ -33023,7 +33023,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1126" t="n">
-        <v>11.2557430267334</v>
+        <v>11.2557420730591</v>
       </c>
       <c r="H1126" t="n">
         <v>312966</v>
@@ -33052,7 +33052,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.9420576095581</v>
+        <v>10.9420585632324</v>
       </c>
       <c r="H1127" t="n">
         <v>171397</v>
@@ -33139,7 +33139,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.74267768859863</v>
+        <v>9.74267482757568</v>
       </c>
       <c r="H1130" t="n">
         <v>168430</v>
@@ -33197,7 +33197,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.5084352493286</v>
+        <v>10.5084362030029</v>
       </c>
       <c r="H1132" t="n">
         <v>328890</v>
@@ -33226,7 +33226,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.1947498321533</v>
+        <v>10.194751739502</v>
       </c>
       <c r="H1133" t="n">
         <v>166996</v>
@@ -33255,7 +33255,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1134" t="n">
-        <v>10.019455909729</v>
+        <v>10.0194549560547</v>
       </c>
       <c r="H1134" t="n">
         <v>151652</v>
@@ -33342,7 +33342,7 @@
         <v>11.25</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.3792715072632</v>
+        <v>10.3792705535889</v>
       </c>
       <c r="H1137" t="n">
         <v>258796</v>
@@ -33429,7 +33429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.3700437545776</v>
+        <v>10.370044708252</v>
       </c>
       <c r="H1140" t="n">
         <v>116026</v>
@@ -33632,7 +33632,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1147" t="n">
-        <v>12.0215015411377</v>
+        <v>12.021502494812</v>
       </c>
       <c r="H1147" t="n">
         <v>726814</v>
@@ -33661,7 +33661,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1148" t="n">
-        <v>11.4402637481689</v>
+        <v>11.4402627944946</v>
       </c>
       <c r="H1148" t="n">
         <v>479226</v>
@@ -33748,7 +33748,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1151" t="n">
-        <v>11.8093042373657</v>
+        <v>11.8093032836914</v>
       </c>
       <c r="H1151" t="n">
         <v>223425</v>
@@ -33777,7 +33777,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.8185300827026</v>
+        <v>11.818531036377</v>
       </c>
       <c r="H1152" t="n">
         <v>187197</v>
@@ -33835,7 +33835,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.8185300827026</v>
+        <v>11.818531036377</v>
       </c>
       <c r="H1154" t="n">
         <v>76721</v>
@@ -33864,7 +33864,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1155" t="n">
-        <v>11.7539472579956</v>
+        <v>11.7539482116699</v>
       </c>
       <c r="H1155" t="n">
         <v>263178</v>
@@ -33922,7 +33922,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>11.6616888046265</v>
+        <v>11.6616868972778</v>
       </c>
       <c r="H1157" t="n">
         <v>54063</v>
@@ -33951,7 +33951,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G1158" t="n">
-        <v>11.5694284439087</v>
+        <v>11.5694274902344</v>
       </c>
       <c r="H1158" t="n">
         <v>115659</v>
@@ -33980,7 +33980,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.3480033874512</v>
+        <v>11.3480043411255</v>
       </c>
       <c r="H1159" t="n">
         <v>167840</v>
@@ -34038,7 +34038,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.2741947174072</v>
+        <v>11.2741956710815</v>
       </c>
       <c r="H1161" t="n">
         <v>62971</v>
@@ -34067,7 +34067,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.1450309753418</v>
+        <v>11.1450300216675</v>
       </c>
       <c r="H1162" t="n">
         <v>66873</v>
@@ -34154,7 +34154,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1165" t="n">
-        <v>12.0030508041382</v>
+        <v>12.0030498504639</v>
       </c>
       <c r="H1165" t="n">
         <v>386906</v>
@@ -34183,7 +34183,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1166" t="n">
-        <v>12.3167352676392</v>
+        <v>12.3167362213135</v>
       </c>
       <c r="H1166" t="n">
         <v>492358</v>
@@ -34328,7 +34328,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1171" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961801528931</v>
       </c>
       <c r="H1171" t="n">
         <v>197304</v>
@@ -34357,7 +34357,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>13.2854681015015</v>
+        <v>13.2854671478271</v>
       </c>
       <c r="H1172" t="n">
         <v>98903</v>
@@ -34444,7 +34444,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1175" t="n">
-        <v>13.1286249160767</v>
+        <v>13.1286239624023</v>
       </c>
       <c r="H1175" t="n">
         <v>55804</v>
@@ -34618,7 +34618,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1181" t="n">
-        <v>13.3500499725342</v>
+        <v>13.3500490188599</v>
       </c>
       <c r="H1181" t="n">
         <v>113455</v>
@@ -34676,7 +34676,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1183" t="n">
-        <v>13.5714750289917</v>
+        <v>13.5714731216431</v>
       </c>
       <c r="H1183" t="n">
         <v>86309</v>
@@ -34763,7 +34763,7 @@
         <v>14.25</v>
       </c>
       <c r="G1186" t="n">
-        <v>13.1470766067505</v>
+        <v>13.1470775604248</v>
       </c>
       <c r="H1186" t="n">
         <v>95712</v>
@@ -34821,7 +34821,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>13.1101732254028</v>
+        <v>13.1101722717285</v>
       </c>
       <c r="H1188" t="n">
         <v>183776</v>
@@ -34879,7 +34879,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>13.1286249160767</v>
+        <v>13.1286239624023</v>
       </c>
       <c r="H1190" t="n">
         <v>59956</v>
@@ -35082,7 +35082,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1197" t="n">
-        <v>13.1747550964355</v>
+        <v>13.1747541427612</v>
       </c>
       <c r="H1197" t="n">
         <v>81797</v>
@@ -35140,7 +35140,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1199" t="n">
-        <v>13.3869533538818</v>
+        <v>13.3869543075562</v>
       </c>
       <c r="H1199" t="n">
         <v>274486</v>
@@ -35169,7 +35169,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1200" t="n">
-        <v>12.5104808807373</v>
+        <v>12.5104818344116</v>
       </c>
       <c r="H1200" t="n">
         <v>248470</v>
@@ -35198,7 +35198,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1201" t="n">
-        <v>12.3813180923462</v>
+        <v>12.3813171386719</v>
       </c>
       <c r="H1201" t="n">
         <v>204999</v>
@@ -35256,7 +35256,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>12.3167352676392</v>
+        <v>12.3167362213135</v>
       </c>
       <c r="H1203" t="n">
         <v>128310</v>
@@ -35314,7 +35314,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1205" t="n">
-        <v>12.7872619628906</v>
+        <v>12.7872610092163</v>
       </c>
       <c r="H1205" t="n">
         <v>90314</v>
@@ -35343,7 +35343,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1206" t="n">
-        <v>13.3869533538818</v>
+        <v>13.3869543075562</v>
       </c>
       <c r="H1206" t="n">
         <v>357848</v>
@@ -35401,7 +35401,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1208" t="n">
-        <v>13.5068912506104</v>
+        <v>13.5068922042847</v>
       </c>
       <c r="H1208" t="n">
         <v>135804</v>
@@ -35459,7 +35459,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1210" t="n">
-        <v>13.4515342712402</v>
+        <v>13.4515352249146</v>
       </c>
       <c r="H1210" t="n">
         <v>167243</v>
@@ -35546,7 +35546,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1213" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735197067261</v>
       </c>
       <c r="H1213" t="n">
         <v>405514</v>
@@ -35604,7 +35604,7 @@
         <v>17.5</v>
       </c>
       <c r="G1215" t="n">
-        <v>16.1455326080322</v>
+        <v>16.1455307006836</v>
       </c>
       <c r="H1215" t="n">
         <v>178975</v>
@@ -35633,7 +35633,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>15.3613204956055</v>
+        <v>15.3613214492798</v>
       </c>
       <c r="H1216" t="n">
         <v>206453</v>
@@ -35662,7 +35662,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>15.4628076553345</v>
+        <v>15.4628067016602</v>
       </c>
       <c r="H1217" t="n">
         <v>170488</v>
@@ -35691,7 +35691,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G1218" t="n">
-        <v>14.6232395172119</v>
+        <v>14.6232404708862</v>
       </c>
       <c r="H1218" t="n">
         <v>281974</v>
@@ -35720,7 +35720,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>14.512526512146</v>
+        <v>14.5125274658203</v>
       </c>
       <c r="H1219" t="n">
         <v>194522</v>
@@ -35749,7 +35749,7 @@
         <v>16</v>
       </c>
       <c r="G1220" t="n">
-        <v>14.7616300582886</v>
+        <v>14.7616310119629</v>
       </c>
       <c r="H1220" t="n">
         <v>90320</v>
@@ -35865,7 +35865,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>14.3556852340698</v>
+        <v>14.3556861877441</v>
       </c>
       <c r="H1224" t="n">
         <v>118110</v>
@@ -35923,7 +35923,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G1226" t="n">
-        <v>13.9128351211548</v>
+        <v>13.9128360748291</v>
       </c>
       <c r="H1226" t="n">
         <v>228721</v>
@@ -35952,7 +35952,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1227" t="n">
-        <v>13.3869533538818</v>
+        <v>13.3869543075562</v>
       </c>
       <c r="H1227" t="n">
         <v>229089</v>
@@ -36010,7 +36010,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>13.6545076370239</v>
+        <v>13.6545085906982</v>
       </c>
       <c r="H1229" t="n">
         <v>211009</v>
@@ -36039,7 +36039,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1230" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1230" t="n">
         <v>232002</v>
@@ -36068,7 +36068,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1231" t="n">
-        <v>14.4110412597656</v>
+        <v>14.4110403060913</v>
       </c>
       <c r="H1231" t="n">
         <v>169157</v>
@@ -36126,7 +36126,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1233" t="n">
-        <v>15.5735187530518</v>
+        <v>15.5735197067261</v>
       </c>
       <c r="H1233" t="n">
         <v>375133</v>
@@ -36213,7 +36213,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1236" t="n">
-        <v>15.4166774749756</v>
+        <v>15.4166746139526</v>
       </c>
       <c r="H1236" t="n">
         <v>175438</v>
@@ -36271,7 +36271,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G1238" t="n">
-        <v>14.9184722900391</v>
+        <v>14.9184732437134</v>
       </c>
       <c r="H1238" t="n">
         <v>69332</v>
@@ -36300,7 +36300,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1239" t="n">
-        <v>15.3889999389648</v>
+        <v>15.3890008926392</v>
       </c>
       <c r="H1239" t="n">
         <v>152784</v>
@@ -36329,7 +36329,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1240" t="n">
-        <v>15.7764930725098</v>
+        <v>15.7764940261841</v>
       </c>
       <c r="H1240" t="n">
         <v>178894</v>
@@ -36358,7 +36358,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1241" t="n">
-        <v>15.582745552063</v>
+        <v>15.5827445983887</v>
       </c>
       <c r="H1241" t="n">
         <v>78857</v>
@@ -36387,7 +36387,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1242" t="n">
-        <v>16.1547603607178</v>
+        <v>16.1547584533691</v>
       </c>
       <c r="H1242" t="n">
         <v>259846</v>
@@ -36416,7 +36416,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1243" t="n">
-        <v>15.8133945465088</v>
+        <v>15.8133955001831</v>
       </c>
       <c r="H1243" t="n">
         <v>116062</v>
@@ -36445,7 +36445,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1244" t="n">
-        <v>15.8410720825195</v>
+        <v>15.8410749435425</v>
       </c>
       <c r="H1244" t="n">
         <v>51279</v>
@@ -36503,7 +36503,7 @@
         <v>17.5</v>
       </c>
       <c r="G1246" t="n">
-        <v>16.1455326080322</v>
+        <v>16.1455307006836</v>
       </c>
       <c r="H1246" t="n">
         <v>170904</v>
@@ -36590,7 +36590,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G1249" t="n">
-        <v>15.8779773712158</v>
+        <v>15.8779764175415</v>
       </c>
       <c r="H1249" t="n">
         <v>70649</v>
@@ -36706,7 +36706,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>15.5919704437256</v>
+        <v>15.5919713973999</v>
       </c>
       <c r="H1253" t="n">
         <v>50800</v>
@@ -36735,7 +36735,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1254" t="n">
-        <v>15.8133945465088</v>
+        <v>15.8133955001831</v>
       </c>
       <c r="H1254" t="n">
         <v>89575</v>
@@ -36793,7 +36793,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G1256" t="n">
-        <v>15.9517869949341</v>
+        <v>15.9517879486084</v>
       </c>
       <c r="H1256" t="n">
         <v>77596</v>
@@ -36822,7 +36822,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1257" t="n">
-        <v>16.099401473999</v>
+        <v>16.0994033813477</v>
       </c>
       <c r="H1257" t="n">
         <v>135906</v>
@@ -36851,7 +36851,7 @@
         <v>17.5</v>
       </c>
       <c r="G1258" t="n">
-        <v>16.1455326080322</v>
+        <v>16.1455307006836</v>
       </c>
       <c r="H1258" t="n">
         <v>99205</v>
@@ -36909,7 +36909,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>16.5145721435547</v>
+        <v>16.5145740509033</v>
       </c>
       <c r="H1260" t="n">
         <v>217179</v>
@@ -36996,7 +36996,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1263" t="n">
-        <v>17.4648532867432</v>
+        <v>17.4648551940918</v>
       </c>
       <c r="H1263" t="n">
         <v>97580</v>
@@ -37083,7 +37083,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G1266" t="n">
-        <v>17.2618808746338</v>
+        <v>17.2618789672852</v>
       </c>
       <c r="H1266" t="n">
         <v>72275</v>
@@ -37112,7 +37112,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1267" t="n">
-        <v>17.5386619567871</v>
+        <v>17.5386600494385</v>
       </c>
       <c r="H1267" t="n">
         <v>99892</v>
@@ -37199,7 +37199,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1270" t="n">
-        <v>17.3725929260254</v>
+        <v>17.3725910186768</v>
       </c>
       <c r="H1270" t="n">
         <v>76845</v>
@@ -37286,7 +37286,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1273" t="n">
-        <v>18.036865234375</v>
+        <v>18.0368671417236</v>
       </c>
       <c r="H1273" t="n">
         <v>111248</v>
@@ -37344,7 +37344,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.7657203674316</v>
+        <v>18.7657241821289</v>
       </c>
       <c r="H1275" t="n">
         <v>142765</v>
@@ -37402,7 +37402,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1277" t="n">
         <v>153145</v>
@@ -37489,7 +37489,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1280" t="n">
-        <v>18.728816986084</v>
+        <v>18.7288188934326</v>
       </c>
       <c r="H1280" t="n">
         <v>138251</v>
@@ -37576,7 +37576,7 @@
         <v>20.9599990844727</v>
       </c>
       <c r="G1283" t="n">
-        <v>19.3377323150635</v>
+        <v>19.3377342224121</v>
       </c>
       <c r="H1283" t="n">
         <v>45421</v>
@@ -37605,7 +37605,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1284" t="n">
-        <v>19.2639274597168</v>
+        <v>19.2639255523682</v>
       </c>
       <c r="H1284" t="n">
         <v>44320</v>
@@ -37634,7 +37634,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1285" t="n">
-        <v>19.2639274597168</v>
+        <v>19.2639255523682</v>
       </c>
       <c r="H1285" t="n">
         <v>59633</v>
@@ -37721,7 +37721,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1288" t="n">
-        <v>18.2029342651367</v>
+        <v>18.2029361724854</v>
       </c>
       <c r="H1288" t="n">
         <v>161850</v>
@@ -37924,7 +37924,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1295" t="n">
-        <v>20.9430618286133</v>
+        <v>20.9430637359619</v>
       </c>
       <c r="H1295" t="n">
         <v>142083</v>
@@ -38156,7 +38156,7 @@
         <v>24.1599998474121</v>
       </c>
       <c r="G1303" t="n">
-        <v>22.2900619506836</v>
+        <v>22.290060043335</v>
       </c>
       <c r="H1303" t="n">
         <v>110443</v>
@@ -38185,7 +38185,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1304" t="n">
         <v>107731</v>
@@ -38214,7 +38214,7 @@
         <v>24.3600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>22.4745826721191</v>
+        <v>22.4745807647705</v>
       </c>
       <c r="H1305" t="n">
         <v>45171</v>
@@ -38272,7 +38272,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.5371189117432</v>
+        <v>20.5371170043945</v>
       </c>
       <c r="H1307" t="n">
         <v>221676</v>
@@ -38417,7 +38417,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1312" t="n">
-        <v>20.6847343444824</v>
+        <v>20.6847362518311</v>
       </c>
       <c r="H1312" t="n">
         <v>43411</v>
@@ -38446,7 +38446,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1313" t="n">
-        <v>21.2013893127441</v>
+        <v>21.2013912200928</v>
       </c>
       <c r="H1313" t="n">
         <v>97639</v>
@@ -38475,7 +38475,7 @@
         <v>22.1800003051758</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4633102416992</v>
+        <v>20.4633083343506</v>
       </c>
       <c r="H1314" t="n">
         <v>180543</v>
@@ -38562,7 +38562,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>20.8508033752441</v>
+        <v>20.8508014678955</v>
       </c>
       <c r="H1317" t="n">
         <v>68057</v>
@@ -38620,7 +38620,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1319" t="n">
-        <v>21.1091327667236</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1319" t="n">
         <v>59299</v>
@@ -38649,7 +38649,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1320" t="n">
-        <v>21.1091327667236</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1320" t="n">
         <v>52297</v>
@@ -38678,7 +38678,7 @@
         <v>21.9200000762939</v>
       </c>
       <c r="G1321" t="n">
-        <v>20.2234325408936</v>
+        <v>20.2234344482422</v>
       </c>
       <c r="H1321" t="n">
         <v>160358</v>
@@ -38707,7 +38707,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1322" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1322" t="n">
         <v>182976</v>
@@ -38765,7 +38765,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311740875244</v>
       </c>
       <c r="H1324" t="n">
         <v>133244</v>
@@ -38823,7 +38823,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1326" t="n">
-        <v>19.6145172119141</v>
+        <v>19.6145153045654</v>
       </c>
       <c r="H1326" t="n">
         <v>83270</v>
@@ -38881,7 +38881,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1328" t="n">
         <v>213744</v>
@@ -38910,7 +38910,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1329" t="n">
         <v>111615</v>
@@ -38939,7 +38939,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311740875244</v>
       </c>
       <c r="H1330" t="n">
         <v>74044</v>
@@ -39026,7 +39026,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1333" t="n">
-        <v>22.5483894348145</v>
+        <v>22.5483913421631</v>
       </c>
       <c r="H1333" t="n">
         <v>168907</v>
@@ -39055,7 +39055,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1334" t="n">
-        <v>22.0686359405518</v>
+        <v>22.0686378479004</v>
       </c>
       <c r="H1334" t="n">
         <v>170852</v>
@@ -39084,7 +39084,7 @@
         <v>24.0799999237061</v>
       </c>
       <c r="G1335" t="n">
-        <v>22.2162532806396</v>
+        <v>22.216251373291</v>
       </c>
       <c r="H1335" t="n">
         <v>78096</v>
@@ -39200,7 +39200,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1339" t="n">
-        <v>22.0317344665527</v>
+        <v>22.0317306518555</v>
       </c>
       <c r="H1339" t="n">
         <v>111019</v>
@@ -39258,7 +39258,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1341" t="n">
-        <v>23.7846755981445</v>
+        <v>23.7846775054932</v>
       </c>
       <c r="H1341" t="n">
         <v>181858</v>
@@ -39316,7 +39316,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1343" t="n">
-        <v>24.3935928344727</v>
+        <v>24.393590927124</v>
       </c>
       <c r="H1343" t="n">
         <v>77573</v>
@@ -39345,7 +39345,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1344" t="n">
-        <v>23.8953895568848</v>
+        <v>23.8953876495361</v>
       </c>
       <c r="H1344" t="n">
         <v>153185</v>
@@ -39519,7 +39519,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1350" t="n">
-        <v>23.5817031860352</v>
+        <v>23.5817012786865</v>
       </c>
       <c r="H1350" t="n">
         <v>51355</v>
@@ -39548,7 +39548,7 @@
         <v>25.0799999237061</v>
       </c>
       <c r="G1351" t="n">
-        <v>23.1388568878174</v>
+        <v>23.1388549804688</v>
       </c>
       <c r="H1351" t="n">
         <v>110939</v>
@@ -39664,7 +39664,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1355" t="n">
-        <v>22.3454170227051</v>
+        <v>22.3454151153564</v>
       </c>
       <c r="H1355" t="n">
         <v>127437</v>
@@ -39722,7 +39722,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1357" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1357" t="n">
         <v>131691</v>
@@ -39751,7 +39751,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>23.8953895568848</v>
+        <v>23.8953876495361</v>
       </c>
       <c r="H1358" t="n">
         <v>57684</v>
@@ -39780,7 +39780,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1359" t="n">
-        <v>23.7662220001221</v>
+        <v>23.7662258148193</v>
       </c>
       <c r="H1359" t="n">
         <v>240302</v>
@@ -39867,7 +39867,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1362" t="n">
-        <v>23.6370601654053</v>
+        <v>23.6370620727539</v>
       </c>
       <c r="H1362" t="n">
         <v>264460</v>
@@ -39925,7 +39925,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1364" t="n">
-        <v>25.0763206481934</v>
+        <v>25.0763187408447</v>
       </c>
       <c r="H1364" t="n">
         <v>236072</v>
@@ -40041,7 +40041,7 @@
         <v>29.4400005340576</v>
       </c>
       <c r="G1368" t="n">
-        <v>27.1614017486572</v>
+        <v>27.1613998413086</v>
       </c>
       <c r="H1368" t="n">
         <v>189145</v>
@@ -40070,7 +40070,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1369" t="n">
-        <v>27.3828258514404</v>
+        <v>27.3828239440918</v>
       </c>
       <c r="H1369" t="n">
         <v>120408</v>
@@ -40099,7 +40099,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>27.4935359954834</v>
+        <v>27.4935340881348</v>
       </c>
       <c r="H1370" t="n">
         <v>201422</v>
@@ -40128,7 +40128,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1371" t="n">
-        <v>28.1578102111816</v>
+        <v>28.1578121185303</v>
       </c>
       <c r="H1371" t="n">
         <v>113890</v>
@@ -40157,7 +40157,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>28.0470943450928</v>
+        <v>28.04709815979</v>
       </c>
       <c r="H1372" t="n">
         <v>81326</v>
@@ -40186,7 +40186,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1373" t="n">
-        <v>28.0470943450928</v>
+        <v>28.04709815979</v>
       </c>
       <c r="H1373" t="n">
         <v>74572</v>
@@ -40244,7 +40244,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1375" t="n">
-        <v>27.5673427581787</v>
+        <v>27.5673446655273</v>
       </c>
       <c r="H1375" t="n">
         <v>108420</v>
@@ -40273,7 +40273,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>27.3828258514404</v>
+        <v>27.3828239440918</v>
       </c>
       <c r="H1376" t="n">
         <v>44639</v>
@@ -40360,7 +40360,7 @@
         <v>29.1599998474121</v>
       </c>
       <c r="G1379" t="n">
-        <v>26.9030685424805</v>
+        <v>26.9030704498291</v>
       </c>
       <c r="H1379" t="n">
         <v>72804</v>
@@ -40389,7 +40389,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1380" t="n">
-        <v>26.4971256256104</v>
+        <v>26.497127532959</v>
       </c>
       <c r="H1380" t="n">
         <v>98446</v>
@@ -40447,7 +40447,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1382" t="n">
-        <v>25.7221393585205</v>
+        <v>25.7221412658691</v>
       </c>
       <c r="H1382" t="n">
         <v>121764</v>
@@ -40476,7 +40476,7 @@
         <v>28.7199993133545</v>
       </c>
       <c r="G1383" t="n">
-        <v>26.4971256256104</v>
+        <v>26.497127532959</v>
       </c>
       <c r="H1383" t="n">
         <v>165675</v>
@@ -40621,7 +40621,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>25.5007133483887</v>
+        <v>25.5007152557373</v>
       </c>
       <c r="H1388" t="n">
         <v>89097</v>
@@ -40708,7 +40708,7 @@
         <v>27.8799991607666</v>
       </c>
       <c r="G1391" t="n">
-        <v>25.7221393585205</v>
+        <v>25.7221412658691</v>
       </c>
       <c r="H1391" t="n">
         <v>36786</v>
@@ -40737,7 +40737,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G1392" t="n">
-        <v>26.2572498321533</v>
+        <v>26.2572479248047</v>
       </c>
       <c r="H1392" t="n">
         <v>45196</v>
@@ -40766,7 +40766,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1393" t="n">
-        <v>26.1280860900879</v>
+        <v>26.1280841827393</v>
       </c>
       <c r="H1393" t="n">
         <v>32484</v>
@@ -40795,7 +40795,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1394" t="n">
-        <v>25.9620170593262</v>
+        <v>25.9620151519775</v>
       </c>
       <c r="H1394" t="n">
         <v>47886</v>
@@ -40998,7 +40998,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1401" t="n">
-        <v>26.1280860900879</v>
+        <v>26.1280841827393</v>
       </c>
       <c r="H1401" t="n">
         <v>44132</v>
@@ -41114,7 +41114,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1405" t="n">
-        <v>26.8292636871338</v>
+        <v>26.8292617797852</v>
       </c>
       <c r="H1405" t="n">
         <v>49024</v>
@@ -41375,7 +41375,7 @@
         <v>29.7800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>27.4750823974609</v>
+        <v>27.4750862121582</v>
       </c>
       <c r="H1414" t="n">
         <v>54200</v>
@@ -41404,7 +41404,7 @@
         <v>31.3400001525879</v>
       </c>
       <c r="G1415" t="n">
-        <v>28.914342880249</v>
+        <v>28.9143409729004</v>
       </c>
       <c r="H1415" t="n">
         <v>409404</v>
@@ -41433,7 +41433,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1416" t="n">
-        <v>30.4643115997314</v>
+        <v>30.4643173217773</v>
       </c>
       <c r="H1416" t="n">
         <v>215821</v>
@@ -41491,7 +41491,7 @@
         <v>32.0800018310547</v>
       </c>
       <c r="G1418" t="n">
-        <v>29.5970706939697</v>
+        <v>29.5970687866211</v>
       </c>
       <c r="H1418" t="n">
         <v>191826</v>
@@ -41636,7 +41636,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1423" t="n">
-        <v>26.7923583984375</v>
+        <v>26.7923603057861</v>
       </c>
       <c r="H1423" t="n">
         <v>119595</v>
@@ -41665,7 +41665,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1424" t="n">
-        <v>26.9399757385254</v>
+        <v>26.9399738311768</v>
       </c>
       <c r="H1424" t="n">
         <v>66230</v>
@@ -41723,7 +41723,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1426" t="n">
-        <v>27.8994808197021</v>
+        <v>27.8994827270508</v>
       </c>
       <c r="H1426" t="n">
         <v>102901</v>
@@ -41839,7 +41839,7 @@
         <v>29.5</v>
       </c>
       <c r="G1430" t="n">
-        <v>27.2167530059814</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1430" t="n">
         <v>75930</v>
@@ -41926,7 +41926,7 @@
         <v>28.8600006103516</v>
       </c>
       <c r="G1433" t="n">
-        <v>26.6262893676758</v>
+        <v>26.6262912750244</v>
       </c>
       <c r="H1433" t="n">
         <v>47937</v>
@@ -41955,7 +41955,7 @@
         <v>29.5</v>
       </c>
       <c r="G1434" t="n">
-        <v>27.2167530059814</v>
+        <v>27.2167549133301</v>
       </c>
       <c r="H1434" t="n">
         <v>37007</v>
@@ -42013,7 +42013,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G1436" t="n">
-        <v>27.7703170776367</v>
+        <v>27.7703151702881</v>
       </c>
       <c r="H1436" t="n">
         <v>77299</v>
@@ -42042,7 +42042,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>27.3090152740479</v>
+        <v>27.3090171813965</v>
       </c>
       <c r="H1437" t="n">
         <v>40719</v>
@@ -42100,7 +42100,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1439" t="n">
-        <v>28.6744651794434</v>
+        <v>28.674467086792</v>
       </c>
       <c r="H1439" t="n">
         <v>107729</v>
@@ -42129,7 +42129,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1440" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1440" t="n">
         <v>83693</v>
@@ -42245,7 +42245,7 @@
         <v>30.3799991607666</v>
       </c>
       <c r="G1444" t="n">
-        <v>28.0286426544189</v>
+        <v>28.0286445617676</v>
       </c>
       <c r="H1444" t="n">
         <v>25013</v>
@@ -42361,7 +42361,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G1448" t="n">
-        <v>27.8256702423096</v>
+        <v>27.8256721496582</v>
       </c>
       <c r="H1448" t="n">
         <v>61069</v>
@@ -42390,7 +42390,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G1449" t="n">
-        <v>27.9732913970947</v>
+        <v>27.9732875823975</v>
       </c>
       <c r="H1449" t="n">
         <v>79612</v>
@@ -42535,7 +42535,7 @@
         <v>28.5</v>
       </c>
       <c r="G1454" t="n">
-        <v>26.294153213501</v>
+        <v>26.2941551208496</v>
       </c>
       <c r="H1454" t="n">
         <v>156176</v>
@@ -42651,7 +42651,7 @@
         <v>28.4200000762939</v>
       </c>
       <c r="G1458" t="n">
-        <v>26.2203464508057</v>
+        <v>26.220344543457</v>
       </c>
       <c r="H1458" t="n">
         <v>92706</v>
@@ -42680,7 +42680,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G1459" t="n">
-        <v>25.5191688537598</v>
+        <v>25.5191669464111</v>
       </c>
       <c r="H1459" t="n">
         <v>176751</v>
@@ -42709,7 +42709,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1460" t="n">
-        <v>24.6150169372559</v>
+        <v>24.6150207519531</v>
       </c>
       <c r="H1460" t="n">
         <v>154714</v>
@@ -42767,7 +42767,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1462" t="n">
-        <v>24.9656066894531</v>
+        <v>24.9656047821045</v>
       </c>
       <c r="H1462" t="n">
         <v>161733</v>
@@ -42796,7 +42796,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1463" t="n">
-        <v>24.356689453125</v>
+        <v>24.3566913604736</v>
       </c>
       <c r="H1463" t="n">
         <v>92597</v>
@@ -42825,7 +42825,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1464" t="n">
-        <v>23.7108707427979</v>
+        <v>23.7108669281006</v>
       </c>
       <c r="H1464" t="n">
         <v>124786</v>
@@ -42999,7 +42999,7 @@
         <v>26.0799999237061</v>
       </c>
       <c r="G1470" t="n">
-        <v>24.0614566802979</v>
+        <v>24.0614585876465</v>
       </c>
       <c r="H1470" t="n">
         <v>127573</v>
@@ -43086,7 +43086,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1473" t="n">
-        <v>24.6334705352783</v>
+        <v>24.633472442627</v>
       </c>
       <c r="H1473" t="n">
         <v>95118</v>
@@ -43144,7 +43144,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1475" t="n">
-        <v>25.0947723388672</v>
+        <v>25.0947704315186</v>
       </c>
       <c r="H1475" t="n">
         <v>60911</v>
@@ -43173,7 +43173,7 @@
         <v>27</v>
       </c>
       <c r="G1476" t="n">
-        <v>24.910249710083</v>
+        <v>24.9102516174316</v>
       </c>
       <c r="H1476" t="n">
         <v>51659</v>
@@ -43202,7 +43202,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1477" t="n">
-        <v>24.984058380127</v>
+        <v>24.9840564727783</v>
       </c>
       <c r="H1477" t="n">
         <v>45457</v>
@@ -43231,7 +43231,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1478" t="n">
-        <v>25.0763206481934</v>
+        <v>25.0763187408447</v>
       </c>
       <c r="H1478" t="n">
         <v>36215</v>
@@ -43260,7 +43260,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1479" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179893493652</v>
       </c>
       <c r="H1479" t="n">
         <v>40510</v>
@@ -43289,7 +43289,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1480" t="n">
-        <v>25.1870288848877</v>
+        <v>25.1870307922363</v>
       </c>
       <c r="H1480" t="n">
         <v>49241</v>
@@ -43318,7 +43318,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G1481" t="n">
-        <v>25.1870288848877</v>
+        <v>25.1870307922363</v>
       </c>
       <c r="H1481" t="n">
         <v>63622</v>
@@ -43347,7 +43347,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>24.8179912567139</v>
+        <v>24.8179893493652</v>
       </c>
       <c r="H1482" t="n">
         <v>79431</v>
@@ -43405,7 +43405,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1484" t="n">
-        <v>25.5376205444336</v>
+        <v>25.537618637085</v>
       </c>
       <c r="H1484" t="n">
         <v>157497</v>
@@ -43434,7 +43434,7 @@
         <v>27</v>
       </c>
       <c r="G1485" t="n">
-        <v>24.910249710083</v>
+        <v>24.9102516174316</v>
       </c>
       <c r="H1485" t="n">
         <v>209407</v>
@@ -43492,7 +43492,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G1487" t="n">
-        <v>24.984058380127</v>
+        <v>24.9840564727783</v>
       </c>
       <c r="H1487" t="n">
         <v>69067</v>
@@ -43521,7 +43521,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1488" t="n">
-        <v>24.9287014007568</v>
+        <v>24.9287052154541</v>
       </c>
       <c r="H1488" t="n">
         <v>107665</v>
@@ -43579,7 +43579,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1490" t="n">
-        <v>24.2644290924072</v>
+        <v>24.2644271850586</v>
       </c>
       <c r="H1490" t="n">
         <v>92482</v>
@@ -43608,7 +43608,7 @@
         <v>26.3400001525879</v>
       </c>
       <c r="G1491" t="n">
-        <v>24.3013343811035</v>
+        <v>24.3013324737549</v>
       </c>
       <c r="H1491" t="n">
         <v>68256</v>
@@ -43666,7 +43666,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1493" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1493" t="n">
         <v>64503</v>
@@ -43695,7 +43695,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>23.7477741241455</v>
+        <v>23.7477722167969</v>
       </c>
       <c r="H1494" t="n">
         <v>81730</v>
@@ -43753,7 +43753,7 @@
         <v>25.5</v>
       </c>
       <c r="G1496" t="n">
-        <v>23.5263481140137</v>
+        <v>23.5263500213623</v>
       </c>
       <c r="H1496" t="n">
         <v>49797</v>
@@ -43927,7 +43927,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1502" t="n">
-        <v>21.8841152191162</v>
+        <v>21.8841171264648</v>
       </c>
       <c r="H1502" t="n">
         <v>111017</v>
@@ -43956,7 +43956,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.8508033752441</v>
+        <v>20.8508014678955</v>
       </c>
       <c r="H1503" t="n">
         <v>98505</v>
@@ -44014,7 +44014,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1505" t="n">
-        <v>20.7031860351562</v>
+        <v>20.7031879425049</v>
       </c>
       <c r="H1505" t="n">
         <v>133575</v>
@@ -44043,7 +44043,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.736499786377</v>
+        <v>21.7364978790283</v>
       </c>
       <c r="H1506" t="n">
         <v>138194</v>
@@ -44072,7 +44072,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1507" t="n">
-        <v>21.4597225189209</v>
+        <v>21.4597187042236</v>
       </c>
       <c r="H1507" t="n">
         <v>64711</v>
@@ -44159,7 +44159,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G1510" t="n">
-        <v>22.6591014862061</v>
+        <v>22.6591033935547</v>
       </c>
       <c r="H1510" t="n">
         <v>92110</v>
@@ -44217,7 +44217,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.4412670135498</v>
+        <v>21.4412651062012</v>
       </c>
       <c r="H1512" t="n">
         <v>37399</v>
@@ -44246,7 +44246,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.1091327667236</v>
+        <v>21.1091289520264</v>
       </c>
       <c r="H1513" t="n">
         <v>30601</v>
@@ -44275,7 +44275,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.7031860351562</v>
+        <v>20.7031879425049</v>
       </c>
       <c r="H1514" t="n">
         <v>46863</v>
@@ -44304,7 +44304,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1515" t="n">
-        <v>20.3525943756104</v>
+        <v>20.352596282959</v>
       </c>
       <c r="H1515" t="n">
         <v>74574</v>
@@ -44333,7 +44333,7 @@
         <v>21.8199996948242</v>
       </c>
       <c r="G1516" t="n">
-        <v>20.1311702728271</v>
+        <v>20.1311740875244</v>
       </c>
       <c r="H1516" t="n">
         <v>83075</v>
@@ -44391,7 +44391,7 @@
         <v>22.0200004577637</v>
       </c>
       <c r="G1518" t="n">
-        <v>20.31569480896</v>
+        <v>20.3156929016113</v>
       </c>
       <c r="H1518" t="n">
         <v>87616</v>
@@ -44420,7 +44420,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1519" t="n">
-        <v>20.3525943756104</v>
+        <v>20.352596282959</v>
       </c>
       <c r="H1519" t="n">
         <v>105798</v>
@@ -44536,7 +44536,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1523" t="n">
-        <v>22.5299396514893</v>
+        <v>22.5299377441406</v>
       </c>
       <c r="H1523" t="n">
         <v>282491</v>
@@ -44565,7 +44565,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1524" t="n">
-        <v>22.5114860534668</v>
+        <v>22.5114841461182</v>
       </c>
       <c r="H1524" t="n">
         <v>72450</v>
@@ -44594,7 +44594,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1525" t="n">
-        <v>22.6775531768799</v>
+        <v>22.6775550842285</v>
       </c>
       <c r="H1525" t="n">
         <v>102099</v>
@@ -44623,7 +44623,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G1526" t="n">
-        <v>22.5299396514893</v>
+        <v>22.5299377441406</v>
       </c>
       <c r="H1526" t="n">
         <v>35005</v>
@@ -44739,7 +44739,7 @@
         <v>24.1800003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>22.3085155487061</v>
+        <v>22.3085136413574</v>
       </c>
       <c r="H1530" t="n">
         <v>64510</v>
@@ -44768,7 +44768,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1531" t="n">
-        <v>22.5114860534668</v>
+        <v>22.5114841461182</v>
       </c>
       <c r="H1531" t="n">
         <v>40554</v>
@@ -44826,7 +44826,7 @@
         <v>23.1599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.3674583435059</v>
+        <v>21.3674602508545</v>
       </c>
       <c r="H1533" t="n">
         <v>40625</v>
@@ -44855,7 +44855,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1534" t="n">
         <v>52052</v>
@@ -44884,7 +44884,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1535" t="n">
         <v>65819</v>
@@ -44913,7 +44913,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>21.8472118377686</v>
+        <v>21.8472137451172</v>
       </c>
       <c r="H1536" t="n">
         <v>64304</v>
@@ -44942,7 +44942,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1537" t="n">
-        <v>22.0686359405518</v>
+        <v>22.0686378479004</v>
       </c>
       <c r="H1537" t="n">
         <v>72583</v>
@@ -44971,7 +44971,7 @@
         <v>23.2399997711182</v>
       </c>
       <c r="G1538" t="n">
-        <v>21.4412670135498</v>
+        <v>21.4412651062012</v>
       </c>
       <c r="H1538" t="n">
         <v>58113</v>
@@ -45087,7 +45087,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.9281997680664</v>
+        <v>19.928201675415</v>
       </c>
       <c r="H1542" t="n">
         <v>354066</v>
@@ -45116,7 +45116,7 @@
         <v>21.7600002288818</v>
       </c>
       <c r="G1543" t="n">
-        <v>20.0758171081543</v>
+        <v>20.0758152008057</v>
       </c>
       <c r="H1543" t="n">
         <v>220064</v>
@@ -45145,7 +45145,7 @@
         <v>22.5400009155273</v>
       </c>
       <c r="G1544" t="n">
-        <v>20.795446395874</v>
+        <v>20.7954483032227</v>
       </c>
       <c r="H1544" t="n">
         <v>73711</v>
@@ -45174,7 +45174,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>20.8877086639404</v>
+        <v>20.8877048492432</v>
       </c>
       <c r="H1545" t="n">
         <v>65560</v>
@@ -45377,7 +45377,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1552" t="n">
-        <v>20.2787895202637</v>
+        <v>20.278787612915</v>
       </c>
       <c r="H1552" t="n">
         <v>50610</v>
@@ -45464,7 +45464,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1555" t="n">
-        <v>20.5371189117432</v>
+        <v>20.5371170043945</v>
       </c>
       <c r="H1555" t="n">
         <v>162022</v>
@@ -45522,7 +45522,7 @@
         <v>21.6599998474121</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.9835567474365</v>
+        <v>19.9835548400879</v>
       </c>
       <c r="H1557" t="n">
         <v>232143</v>
@@ -45580,7 +45580,7 @@
         <v>22.5</v>
       </c>
       <c r="G1559" t="n">
-        <v>20.7585430145264</v>
+        <v>20.7585411071777</v>
       </c>
       <c r="H1559" t="n">
         <v>34621</v>
@@ -45667,7 +45667,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.9871444702148</v>
+        <v>18.9871463775635</v>
       </c>
       <c r="H1562" t="n">
         <v>163561</v>
@@ -45696,7 +45696,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.9871444702148</v>
+        <v>18.9871463775635</v>
       </c>
       <c r="H1563" t="n">
         <v>75921</v>
@@ -45725,7 +45725,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.5073909759521</v>
+        <v>18.5073928833008</v>
       </c>
       <c r="H1564" t="n">
         <v>48417</v>
@@ -45754,7 +45754,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1565" t="n">
-        <v>17.6770534515381</v>
+        <v>17.6770515441895</v>
       </c>
       <c r="H1565" t="n">
         <v>135742</v>
@@ -45812,7 +45812,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.1198997497559</v>
+        <v>18.1198978424072</v>
       </c>
       <c r="H1567" t="n">
         <v>87780</v>
@@ -45870,7 +45870,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1569" t="n">
-        <v>17.3633651733398</v>
+        <v>17.3633670806885</v>
       </c>
       <c r="H1569" t="n">
         <v>50964</v>
@@ -45899,7 +45899,7 @@
         <v>17.5</v>
       </c>
       <c r="G1570" t="n">
-        <v>16.1455326080322</v>
+        <v>16.1455307006836</v>
       </c>
       <c r="H1570" t="n">
         <v>92613</v>
@@ -45928,7 +45928,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1571" t="n">
-        <v>14.5033025741577</v>
+        <v>14.5033016204834</v>
       </c>
       <c r="H1571" t="n">
         <v>197519</v>
@@ -45986,7 +45986,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>15.2321557998657</v>
+        <v>15.2321586608887</v>
       </c>
       <c r="H1573" t="n">
         <v>154625</v>
@@ -46044,7 +46044,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G1575" t="n">
-        <v>15.1583480834961</v>
+        <v>15.1583490371704</v>
       </c>
       <c r="H1575" t="n">
         <v>113410</v>
@@ -46102,7 +46102,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.2377948760986</v>
+        <v>16.2377910614014</v>
       </c>
       <c r="H1577" t="n">
         <v>111126</v>
@@ -46131,7 +46131,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1578" t="n">
-        <v>13.4699878692627</v>
+        <v>13.4699869155884</v>
       </c>
       <c r="H1578" t="n">
         <v>921508</v>
@@ -46218,7 +46218,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.3372325897217</v>
+        <v>14.337233543396</v>
       </c>
       <c r="H1581" t="n">
         <v>304440</v>
@@ -46247,7 +46247,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.6878223419189</v>
+        <v>14.6878213882446</v>
       </c>
       <c r="H1582" t="n">
         <v>163036</v>
@@ -46334,7 +46334,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G1585" t="n">
-        <v>14.2634248733521</v>
+        <v>14.2634239196777</v>
       </c>
       <c r="H1585" t="n">
         <v>112266</v>
@@ -46566,7 +46566,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1593" t="n">
-        <v>14.4571714401245</v>
+        <v>14.4571704864502</v>
       </c>
       <c r="H1593" t="n">
         <v>111492</v>
@@ -46595,7 +46595,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1594" t="n">
-        <v>13.8021230697632</v>
+        <v>13.8021249771118</v>
       </c>
       <c r="H1594" t="n">
         <v>167595</v>
@@ -46624,7 +46624,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G1595" t="n">
-        <v>13.8298015594482</v>
+        <v>13.8298025131226</v>
       </c>
       <c r="H1595" t="n">
         <v>69755</v>
@@ -46711,7 +46711,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1598" t="n">
-        <v>13.9958715438843</v>
+        <v>13.99587059021</v>
       </c>
       <c r="H1598" t="n">
         <v>55239</v>
@@ -46769,7 +46769,7 @@
         <v>15.0900001525879</v>
       </c>
       <c r="G1600" t="n">
-        <v>13.9220628738403</v>
+        <v>13.922061920166</v>
       </c>
       <c r="H1600" t="n">
         <v>50011</v>
@@ -46798,7 +46798,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G1601" t="n">
-        <v>13.9497404098511</v>
+        <v>13.9497413635254</v>
       </c>
       <c r="H1601" t="n">
         <v>45680</v>
@@ -46856,7 +46856,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.7247247695923</v>
+        <v>14.7247266769409</v>
       </c>
       <c r="H1603" t="n">
         <v>73059</v>
@@ -46914,7 +46914,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.8667068481445</v>
+        <v>13.8667058944702</v>
       </c>
       <c r="H1605" t="n">
         <v>46964</v>
@@ -47001,7 +47001,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G1608" t="n">
-        <v>13.7836713790894</v>
+        <v>13.7836723327637</v>
       </c>
       <c r="H1608" t="n">
         <v>72354</v>
@@ -47030,7 +47030,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.8298015594482</v>
+        <v>13.8298025131226</v>
       </c>
       <c r="H1609" t="n">
         <v>48095</v>
@@ -47146,7 +47146,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.2854681015015</v>
+        <v>13.2854671478271</v>
       </c>
       <c r="H1613" t="n">
         <v>58779</v>
@@ -47204,7 +47204,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1615" t="n">
-        <v>12.8057136535645</v>
+        <v>12.8057146072388</v>
       </c>
       <c r="H1615" t="n">
         <v>81456</v>
@@ -47291,7 +47291,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.3961791992188</v>
+        <v>13.3961801528931</v>
       </c>
       <c r="H1618" t="n">
         <v>99070</v>
@@ -47349,7 +47349,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1620" t="n">
-        <v>15.0476360321045</v>
+        <v>15.0476369857788</v>
       </c>
       <c r="H1620" t="n">
         <v>154501</v>
@@ -47407,7 +47407,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.305965423584</v>
+        <v>15.3059644699097</v>
       </c>
       <c r="H1622" t="n">
         <v>88717</v>
@@ -47436,7 +47436,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1623" t="n">
-        <v>15.3428678512573</v>
+        <v>15.342869758606</v>
       </c>
       <c r="H1623" t="n">
         <v>75173</v>
@@ -47465,7 +47465,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.0384092330933</v>
+        <v>15.0384101867676</v>
       </c>
       <c r="H1624" t="n">
         <v>74404</v>
@@ -47639,7 +47639,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1630" t="n">
-        <v>15.9823875427246</v>
+        <v>15.9823884963989</v>
       </c>
       <c r="H1630" t="n">
         <v>64691</v>
@@ -47668,7 +47668,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>15.5410985946655</v>
+        <v>15.5410995483398</v>
       </c>
       <c r="H1631" t="n">
         <v>54984</v>
@@ -47697,7 +47697,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1632" t="n">
-        <v>15.7137765884399</v>
+        <v>15.7137775421143</v>
       </c>
       <c r="H1632" t="n">
         <v>66096</v>
@@ -47726,7 +47726,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1633" t="n">
-        <v>15.9823875427246</v>
+        <v>15.9823884963989</v>
       </c>
       <c r="H1633" t="n">
         <v>27898</v>
@@ -47755,7 +47755,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.7809314727783</v>
+        <v>15.780930519104</v>
       </c>
       <c r="H1634" t="n">
         <v>37135</v>
@@ -47784,7 +47784,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G1635" t="n">
-        <v>16.0303554534912</v>
+        <v>16.0303516387939</v>
       </c>
       <c r="H1635" t="n">
         <v>43698</v>
@@ -47813,7 +47813,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.8576755523682</v>
+        <v>15.8576784133911</v>
       </c>
       <c r="H1636" t="n">
         <v>45854</v>
@@ -47842,7 +47842,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G1637" t="n">
-        <v>15.6466236114502</v>
+        <v>15.6466245651245</v>
       </c>
       <c r="H1637" t="n">
         <v>47026</v>
@@ -47929,7 +47929,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.612850189209</v>
+        <v>13.6128511428833</v>
       </c>
       <c r="H1640" t="n">
         <v>99299</v>
@@ -47958,7 +47958,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1641" t="n">
-        <v>13.5456972122192</v>
+        <v>13.5456981658936</v>
       </c>
       <c r="H1641" t="n">
         <v>86532</v>
@@ -47987,7 +47987,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G1642" t="n">
-        <v>13.8430891036987</v>
+        <v>13.843090057373</v>
       </c>
       <c r="H1642" t="n">
         <v>116898</v>
@@ -48016,7 +48016,7 @@
         <v>13.5</v>
       </c>
       <c r="G1643" t="n">
-        <v>12.9509143829346</v>
+        <v>12.9509153366089</v>
       </c>
       <c r="H1643" t="n">
         <v>138654</v>
@@ -48132,7 +48132,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1647" t="n">
-        <v>12.7590503692627</v>
+        <v>12.7590494155884</v>
       </c>
       <c r="H1647" t="n">
         <v>79947</v>
@@ -48219,7 +48219,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1650" t="n">
-        <v>12.7494564056396</v>
+        <v>12.749457359314</v>
       </c>
       <c r="H1650" t="n">
         <v>47763</v>
@@ -48277,7 +48277,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1652" t="n">
-        <v>12.5959634780884</v>
+        <v>12.5959644317627</v>
       </c>
       <c r="H1652" t="n">
         <v>94645</v>
@@ -48306,7 +48306,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1653" t="n">
-        <v>12.1258945465088</v>
+        <v>12.1258935928345</v>
       </c>
       <c r="H1653" t="n">
         <v>121111</v>
@@ -48364,7 +48364,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1655" t="n">
-        <v>11.780535697937</v>
+        <v>11.7805366516113</v>
       </c>
       <c r="H1655" t="n">
         <v>68390</v>
@@ -48451,7 +48451,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1658" t="n">
-        <v>12.6247444152832</v>
+        <v>12.6247434616089</v>
       </c>
       <c r="H1658" t="n">
         <v>79138</v>
@@ -48480,7 +48480,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>13.0468482971191</v>
+        <v>13.0468473434448</v>
       </c>
       <c r="H1659" t="n">
         <v>65276</v>
@@ -48509,7 +48509,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G1660" t="n">
-        <v>12.7974224090576</v>
+        <v>12.7974233627319</v>
       </c>
       <c r="H1660" t="n">
         <v>30618</v>
@@ -48596,7 +48596,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1663" t="n">
-        <v>12.2026395797729</v>
+        <v>12.2026405334473</v>
       </c>
       <c r="H1663" t="n">
         <v>81970</v>
@@ -48625,7 +48625,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1664" t="n">
-        <v>12.7494564056396</v>
+        <v>12.749457359314</v>
       </c>
       <c r="H1664" t="n">
         <v>61824</v>
@@ -48654,7 +48654,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1665" t="n">
-        <v>12.8933544158936</v>
+        <v>12.8933553695679</v>
       </c>
       <c r="H1665" t="n">
         <v>35425</v>
@@ -48741,7 +48741,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1668" t="n">
-        <v>13.0468482971191</v>
+        <v>13.0468473434448</v>
       </c>
       <c r="H1668" t="n">
         <v>63442</v>
@@ -48770,7 +48770,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1669" t="n">
-        <v>13.1044073104858</v>
+        <v>13.1044082641602</v>
       </c>
       <c r="H1669" t="n">
         <v>22290</v>
@@ -48828,7 +48828,7 @@
         <v>13</v>
       </c>
       <c r="G1671" t="n">
-        <v>12.4712514877319</v>
+        <v>12.4712505340576</v>
       </c>
       <c r="H1671" t="n">
         <v>91907</v>
@@ -48915,7 +48915,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G1674" t="n">
-        <v>13.3058652877808</v>
+        <v>13.3058662414551</v>
       </c>
       <c r="H1674" t="n">
         <v>153447</v>
@@ -48944,7 +48944,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1675" t="n">
-        <v>13.0372552871704</v>
+        <v>13.0372543334961</v>
       </c>
       <c r="H1675" t="n">
         <v>84357</v>
@@ -48973,7 +48973,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1676" t="n">
-        <v>12.8933544158936</v>
+        <v>12.8933553695679</v>
       </c>
       <c r="H1676" t="n">
         <v>62853</v>
@@ -49002,7 +49002,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.3154592514038</v>
+        <v>13.3154602050781</v>
       </c>
       <c r="H1677" t="n">
         <v>61589</v>
@@ -49031,7 +49031,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.1044073104858</v>
+        <v>13.1044082641602</v>
       </c>
       <c r="H1678" t="n">
         <v>78688</v>
@@ -49060,7 +49060,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G1679" t="n">
-        <v>12.480845451355</v>
+        <v>12.4808444976807</v>
       </c>
       <c r="H1679" t="n">
         <v>126884</v>
@@ -49118,7 +49118,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1681" t="n">
-        <v>12.1738595962524</v>
+        <v>12.1738586425781</v>
       </c>
       <c r="H1681" t="n">
         <v>68306</v>
@@ -49205,7 +49205,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1684" t="n">
-        <v>12.6247444152832</v>
+        <v>12.6247434616089</v>
       </c>
       <c r="H1684" t="n">
         <v>34970</v>
@@ -49263,7 +49263,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1686" t="n">
-        <v>12.2793865203857</v>
+        <v>12.2793855667114</v>
       </c>
       <c r="H1686" t="n">
         <v>58651</v>
@@ -49350,7 +49350,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G1689" t="n">
-        <v>11.780535697937</v>
+        <v>11.7805366516113</v>
       </c>
       <c r="H1689" t="n">
         <v>75821</v>
@@ -49466,7 +49466,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G1693" t="n">
-        <v>12.2218255996704</v>
+        <v>12.2218265533447</v>
       </c>
       <c r="H1693" t="n">
         <v>114156</v>
@@ -49524,7 +49524,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.1162996292114</v>
+        <v>12.1163005828857</v>
       </c>
       <c r="H1695" t="n">
         <v>55534</v>
@@ -49640,7 +49640,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1699" t="n">
-        <v>11.4927368164062</v>
+        <v>11.4927377700806</v>
       </c>
       <c r="H1699" t="n">
         <v>80053</v>
@@ -49727,7 +49727,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1702" t="n">
-        <v>11.3296518325806</v>
+        <v>11.3296527862549</v>
       </c>
       <c r="H1702" t="n">
         <v>48994</v>
@@ -49756,7 +49756,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1703" t="n">
-        <v>11.6654167175293</v>
+        <v>11.665415763855</v>
       </c>
       <c r="H1703" t="n">
         <v>48478</v>
@@ -49959,7 +49959,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1710" t="n">
-        <v>11.1281938552856</v>
+        <v>11.12819480896</v>
       </c>
       <c r="H1710" t="n">
         <v>32547</v>
@@ -50017,7 +50017,7 @@
         <v>11.75</v>
       </c>
       <c r="G1712" t="n">
-        <v>11.2720937728882</v>
+        <v>11.2720928192139</v>
       </c>
       <c r="H1712" t="n">
         <v>57229</v>
@@ -50046,7 +50046,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1713" t="n">
-        <v>10.9363279342651</v>
+        <v>10.9363269805908</v>
       </c>
       <c r="H1713" t="n">
         <v>44317</v>
@@ -50104,7 +50104,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>10.8499898910522</v>
+        <v>10.8499889373779</v>
       </c>
       <c r="H1715" t="n">
         <v>25660</v>
@@ -50162,7 +50162,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G1717" t="n">
-        <v>10.7540559768677</v>
+        <v>10.754056930542</v>
       </c>
       <c r="H1717" t="n">
         <v>47037</v>
@@ -50220,7 +50220,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1719" t="n">
-        <v>11.1090068817139</v>
+        <v>11.1090078353882</v>
       </c>
       <c r="H1719" t="n">
         <v>38067</v>
@@ -50249,7 +50249,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1720" t="n">
-        <v>11.6654167175293</v>
+        <v>11.665415763855</v>
       </c>
       <c r="H1720" t="n">
         <v>60827</v>
@@ -50307,7 +50307,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G1722" t="n">
-        <v>11.6558227539062</v>
+        <v>11.6558237075806</v>
       </c>
       <c r="H1722" t="n">
         <v>48221</v>
@@ -50336,7 +50336,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1723" t="n">
-        <v>11.5694847106934</v>
+        <v>11.5694856643677</v>
       </c>
       <c r="H1723" t="n">
         <v>30512</v>
@@ -50423,7 +50423,7 @@
         <v>11.75</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.2720937728882</v>
+        <v>11.2720928192139</v>
       </c>
       <c r="H1726" t="n">
         <v>45721</v>
@@ -50481,7 +50481,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.6654167175293</v>
+        <v>11.665415763855</v>
       </c>
       <c r="H1728" t="n">
         <v>31281</v>
@@ -50539,7 +50539,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1730" t="n">
-        <v>12.0491485595703</v>
+        <v>12.049147605896</v>
       </c>
       <c r="H1730" t="n">
         <v>78509</v>
@@ -50597,7 +50597,7 @@
         <v>12.4700002670288</v>
       </c>
       <c r="G1732" t="n">
-        <v>11.9628086090088</v>
+        <v>11.9628076553345</v>
       </c>
       <c r="H1732" t="n">
         <v>17425</v>
@@ -50713,7 +50713,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1736" t="n">
-        <v>13.0372552871704</v>
+        <v>13.0372543334961</v>
       </c>
       <c r="H1736" t="n">
         <v>188772</v>
@@ -50742,7 +50742,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1737" t="n">
-        <v>12.9413223266602</v>
+        <v>12.9413213729858</v>
       </c>
       <c r="H1737" t="n">
         <v>38973</v>
@@ -50771,7 +50771,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1738" t="n">
-        <v>13.2003402709961</v>
+        <v>13.2003393173218</v>
       </c>
       <c r="H1738" t="n">
         <v>77128</v>
@@ -50829,7 +50829,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1740" t="n">
-        <v>11.3104658126831</v>
+        <v>11.3104648590088</v>
       </c>
       <c r="H1740" t="n">
         <v>230215</v>
@@ -50858,7 +50858,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1741" t="n">
-        <v>10.9267349243164</v>
+        <v>10.9267358779907</v>
       </c>
       <c r="H1741" t="n">
         <v>173791</v>
@@ -50916,7 +50916,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1743" t="n">
-        <v>11.1281938552856</v>
+        <v>11.12819480896</v>
       </c>
       <c r="H1743" t="n">
         <v>116746</v>
@@ -50974,7 +50974,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1745" t="n">
-        <v>11.895655632019</v>
+        <v>11.8956546783447</v>
       </c>
       <c r="H1745" t="n">
         <v>136967</v>
@@ -51003,7 +51003,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1746" t="n">
-        <v>11.7229766845703</v>
+        <v>11.7229776382446</v>
       </c>
       <c r="H1746" t="n">
         <v>71007</v>
@@ -51032,7 +51032,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1747" t="n">
-        <v>12.2026395797729</v>
+        <v>12.2026405334473</v>
       </c>
       <c r="H1747" t="n">
         <v>106861</v>
@@ -51061,7 +51061,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1748" t="n">
-        <v>12.7398633956909</v>
+        <v>12.7398624420166</v>
       </c>
       <c r="H1748" t="n">
         <v>160134</v>
@@ -51090,7 +51090,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1749" t="n">
-        <v>12.7494564056396</v>
+        <v>12.749457359314</v>
       </c>
       <c r="H1749" t="n">
         <v>105210</v>
@@ -51119,7 +51119,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1750" t="n">
-        <v>12.5959634780884</v>
+        <v>12.5959644317627</v>
       </c>
       <c r="H1750" t="n">
         <v>92825</v>
@@ -51148,7 +51148,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1751" t="n">
-        <v>12.2889795303345</v>
+        <v>12.2889804840088</v>
       </c>
       <c r="H1751" t="n">
         <v>103263</v>
@@ -51177,7 +51177,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1752" t="n">
-        <v>12.0875205993652</v>
+        <v>12.0875215530396</v>
       </c>
       <c r="H1752" t="n">
         <v>80042</v>
@@ -51206,7 +51206,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1753" t="n">
-        <v>12.260199546814</v>
+        <v>12.2601985931396</v>
       </c>
       <c r="H1753" t="n">
         <v>109812</v>
@@ -51235,7 +51235,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G1754" t="n">
-        <v>12.1930475234985</v>
+        <v>12.1930465698242</v>
       </c>
       <c r="H1754" t="n">
         <v>93258</v>
@@ -51322,7 +51322,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1757" t="n">
-        <v>12.4136905670166</v>
+        <v>12.4136915206909</v>
       </c>
       <c r="H1757" t="n">
         <v>36902</v>
@@ -51380,7 +51380,7 @@
         <v>12.75</v>
       </c>
       <c r="G1759" t="n">
-        <v>12.2314195632935</v>
+        <v>12.2314205169678</v>
       </c>
       <c r="H1759" t="n">
         <v>82723</v>
@@ -51438,7 +51438,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1761" t="n">
-        <v>12.0875205993652</v>
+        <v>12.0875215530396</v>
       </c>
       <c r="H1761" t="n">
         <v>90127</v>
@@ -51496,7 +51496,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G1763" t="n">
-        <v>12.7398633956909</v>
+        <v>12.7398624420166</v>
       </c>
       <c r="H1763" t="n">
         <v>76238</v>
@@ -51612,7 +51612,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>12.327353477478</v>
+        <v>12.3273525238037</v>
       </c>
       <c r="H1767" t="n">
         <v>48990</v>
@@ -51641,7 +51641,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1768" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1768" t="n">
         <v>41157</v>
@@ -51670,7 +51670,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1769" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1769" t="n">
         <v>40933</v>
@@ -51757,7 +51757,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1772" t="n">
-        <v>12.317759513855</v>
+        <v>12.3177585601807</v>
       </c>
       <c r="H1772" t="n">
         <v>56609</v>
@@ -51844,7 +51844,7 @@
         <v>12.5</v>
       </c>
       <c r="G1775" t="n">
-        <v>11.991587638855</v>
+        <v>11.9915885925293</v>
       </c>
       <c r="H1775" t="n">
         <v>63441</v>
@@ -51873,7 +51873,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1776" t="n">
-        <v>12.1162996292114</v>
+        <v>12.1163005828857</v>
       </c>
       <c r="H1776" t="n">
         <v>37188</v>
@@ -51989,7 +51989,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G1780" t="n">
-        <v>12.1738595962524</v>
+        <v>12.1738586425781</v>
       </c>
       <c r="H1780" t="n">
         <v>29284</v>
@@ -52076,7 +52076,7 @@
         <v>13</v>
       </c>
       <c r="G1783" t="n">
-        <v>12.4712514877319</v>
+        <v>12.4712505340576</v>
       </c>
       <c r="H1783" t="n">
         <v>44967</v>
@@ -52105,7 +52105,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1784" t="n">
-        <v>12.5000305175781</v>
+        <v>12.5000314712524</v>
       </c>
       <c r="H1784" t="n">
         <v>49900</v>
@@ -52163,7 +52163,7 @@
         <v>13.5</v>
       </c>
       <c r="G1786" t="n">
-        <v>12.9509143829346</v>
+        <v>12.9509153366089</v>
       </c>
       <c r="H1786" t="n">
         <v>75656</v>
@@ -52192,7 +52192,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G1787" t="n">
-        <v>13.0852222442627</v>
+        <v>13.0852212905884</v>
       </c>
       <c r="H1787" t="n">
         <v>34405</v>
@@ -52424,7 +52424,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.2364139556885</v>
+        <v>14.2364130020142</v>
       </c>
       <c r="H1795" t="n">
         <v>65651</v>
@@ -52482,7 +52482,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1797" t="n">
-        <v>13.8143100738525</v>
+        <v>13.8143091201782</v>
       </c>
       <c r="H1797" t="n">
         <v>40053</v>
@@ -52511,7 +52511,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1798" t="n">
-        <v>13.8143100738525</v>
+        <v>13.8143091201782</v>
       </c>
       <c r="H1798" t="n">
         <v>44811</v>
@@ -52540,7 +52540,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G1799" t="n">
-        <v>14.1404800415039</v>
+        <v>14.1404809951782</v>
       </c>
       <c r="H1799" t="n">
         <v>78517</v>
@@ -52569,7 +52569,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1800" t="n">
-        <v>14.1980400085449</v>
+        <v>14.1980409622192</v>
       </c>
       <c r="H1800" t="n">
         <v>78808</v>
@@ -52627,7 +52627,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1802" t="n">
-        <v>14.3707189559937</v>
+        <v>14.3707180023193</v>
       </c>
       <c r="H1802" t="n">
         <v>61789</v>
@@ -52656,7 +52656,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1803" t="n">
-        <v>14.2939729690552</v>
+        <v>14.2939720153809</v>
       </c>
       <c r="H1803" t="n">
         <v>84411</v>
@@ -52743,7 +52743,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.9463148117065</v>
+        <v>14.9463157653809</v>
       </c>
       <c r="H1806" t="n">
         <v>121708</v>
@@ -52888,7 +52888,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1811" t="n">
-        <v>14.4474649429321</v>
+        <v>14.4474658966064</v>
       </c>
       <c r="H1811" t="n">
         <v>60232</v>
@@ -52946,7 +52946,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.3323450088501</v>
+        <v>14.3323459625244</v>
       </c>
       <c r="H1813" t="n">
         <v>56523</v>
@@ -52975,7 +52975,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.3515319824219</v>
+        <v>14.3515329360962</v>
       </c>
       <c r="H1814" t="n">
         <v>36760</v>
@@ -53033,7 +53033,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1816" t="n">
-        <v>14.5242118835449</v>
+        <v>14.5242109298706</v>
       </c>
       <c r="H1816" t="n">
         <v>68875</v>
@@ -53149,7 +53149,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G1820" t="n">
-        <v>14.3611268997192</v>
+        <v>14.3611259460449</v>
       </c>
       <c r="H1820" t="n">
         <v>69943</v>
@@ -53207,7 +53207,7 @@
         <v>16.5</v>
       </c>
       <c r="G1822" t="n">
-        <v>15.8288955688477</v>
+        <v>15.828896522522</v>
       </c>
       <c r="H1822" t="n">
         <v>177332</v>
@@ -53236,7 +53236,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1823" t="n">
-        <v>16.2509994506836</v>
+        <v>16.2510013580322</v>
       </c>
       <c r="H1823" t="n">
         <v>168955</v>
@@ -53294,7 +53294,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1825" t="n">
-        <v>16.7210693359375</v>
+        <v>16.7210712432861</v>
       </c>
       <c r="H1825" t="n">
         <v>176367</v>
@@ -53323,7 +53323,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1826" t="n">
-        <v>15.9823875427246</v>
+        <v>15.9823884963989</v>
       </c>
       <c r="H1826" t="n">
         <v>183104</v>
@@ -53352,7 +53352,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1827" t="n">
-        <v>16.3277473449707</v>
+        <v>16.3277454376221</v>
       </c>
       <c r="H1827" t="n">
         <v>93891</v>
@@ -53439,7 +53439,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1830" t="n">
-        <v>16.1454734802246</v>
+        <v>16.1454753875732</v>
       </c>
       <c r="H1830" t="n">
         <v>33085</v>
@@ -53497,7 +53497,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1832" t="n">
-        <v>16.0207633972168</v>
+        <v>16.0207614898682</v>
       </c>
       <c r="H1832" t="n">
         <v>60293</v>
@@ -53526,7 +53526,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.3588256835938</v>
+        <v>15.3588266372681</v>
       </c>
       <c r="H1833" t="n">
         <v>142239</v>
@@ -53613,7 +53613,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1836" t="n">
-        <v>14.5242118835449</v>
+        <v>14.5242109298706</v>
       </c>
       <c r="H1836" t="n">
         <v>276851</v>
@@ -53671,7 +53671,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1838" t="n">
-        <v>14.1980400085449</v>
+        <v>14.1980409622192</v>
       </c>
       <c r="H1838" t="n">
         <v>283780</v>
@@ -53729,7 +53729,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1840" t="n">
-        <v>14.6393308639526</v>
+        <v>14.639331817627</v>
       </c>
       <c r="H1840" t="n">
         <v>102978</v>
@@ -53845,7 +53845,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1844" t="n">
-        <v>13.948616027832</v>
+        <v>13.9486150741577</v>
       </c>
       <c r="H1844" t="n">
         <v>54799</v>
@@ -53903,7 +53903,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G1846" t="n">
-        <v>13.939022064209</v>
+        <v>13.9390211105347</v>
       </c>
       <c r="H1846" t="n">
         <v>59999</v>
@@ -54019,7 +54019,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1850" t="n">
-        <v>13.5456972122192</v>
+        <v>13.5456981658936</v>
       </c>
       <c r="H1850" t="n">
         <v>60451</v>
@@ -54077,7 +54077,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1852" t="n">
-        <v>13.6416311264038</v>
+        <v>13.6416301727295</v>
       </c>
       <c r="H1852" t="n">
         <v>74990</v>
@@ -54106,7 +54106,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1853" t="n">
-        <v>13.555290222168</v>
+        <v>13.5552911758423</v>
       </c>
       <c r="H1853" t="n">
         <v>38120</v>
@@ -54164,7 +54164,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G1855" t="n">
-        <v>13.4497661590576</v>
+        <v>13.4497652053833</v>
       </c>
       <c r="H1855" t="n">
         <v>38433</v>
@@ -54251,7 +54251,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G1858" t="n">
-        <v>13.3538331985474</v>
+        <v>13.3538312911987</v>
       </c>
       <c r="H1858" t="n">
         <v>41011</v>
@@ -54280,7 +54280,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1859" t="n">
-        <v>13.2195272445679</v>
+        <v>13.2195262908936</v>
       </c>
       <c r="H1859" t="n">
         <v>38736</v>
@@ -54367,7 +54367,7 @@
         <v>13.75</v>
       </c>
       <c r="G1862" t="n">
-        <v>13.190746307373</v>
+        <v>13.1907472610474</v>
       </c>
       <c r="H1862" t="n">
         <v>54361</v>
@@ -54425,7 +54425,7 @@
         <v>13.75</v>
       </c>
       <c r="G1864" t="n">
-        <v>13.190746307373</v>
+        <v>13.1907472610474</v>
       </c>
       <c r="H1864" t="n">
         <v>43021</v>
@@ -54454,7 +54454,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1865" t="n">
-        <v>13.2578983306885</v>
+        <v>13.2579002380371</v>
       </c>
       <c r="H1865" t="n">
         <v>39502</v>
@@ -54541,7 +54541,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G1868" t="n">
-        <v>12.9413223266602</v>
+        <v>12.9413213729858</v>
       </c>
       <c r="H1868" t="n">
         <v>49934</v>
@@ -54686,7 +54686,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1873" t="n">
-        <v>12.8862733840942</v>
+        <v>12.8862724304199</v>
       </c>
       <c r="H1873" t="n">
         <v>74352</v>
@@ -54715,7 +54715,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1874" t="n">
-        <v>12.2768526077271</v>
+        <v>12.2768535614014</v>
       </c>
       <c r="H1874" t="n">
         <v>337436</v>
@@ -54831,7 +54831,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G1878" t="n">
-        <v>12.2080488204956</v>
+        <v>12.2080478668213</v>
       </c>
       <c r="H1878" t="n">
         <v>74114</v>
@@ -54889,7 +54889,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1880" t="n">
-        <v>12.7093458175659</v>
+        <v>12.7093448638916</v>
       </c>
       <c r="H1880" t="n">
         <v>114865</v>
@@ -55034,7 +55034,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G1885" t="n">
-        <v>11.7165803909302</v>
+        <v>11.7165813446045</v>
       </c>
       <c r="H1885" t="n">
         <v>61095</v>
@@ -55121,7 +55121,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1888" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1888" t="n">
         <v>49130</v>
@@ -55295,7 +55295,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1894" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
       </c>
       <c r="H1894" t="n">
         <v>62454</v>
@@ -55324,7 +55324,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1895" t="n">
-        <v>11.7755556106567</v>
+        <v>11.7755565643311</v>
       </c>
       <c r="H1895" t="n">
         <v>45711</v>
@@ -55411,7 +55411,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1898" t="n">
-        <v>11.9524850845337</v>
+        <v>11.9524841308594</v>
       </c>
       <c r="H1898" t="n">
         <v>50728</v>
@@ -55527,7 +55527,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1902" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1902" t="n">
         <v>60178</v>
@@ -55643,7 +55643,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G1906" t="n">
-        <v>11.5887994766235</v>
+        <v>11.5887985229492</v>
       </c>
       <c r="H1906" t="n">
         <v>66958</v>
@@ -55788,7 +55788,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G1911" t="n">
-        <v>11.5593109130859</v>
+        <v>11.5593118667603</v>
       </c>
       <c r="H1911" t="n">
         <v>39057</v>
@@ -55962,7 +55962,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1917" t="n">
-        <v>11.4217004776001</v>
+        <v>11.4216995239258</v>
       </c>
       <c r="H1917" t="n">
         <v>57508</v>
@@ -56020,7 +56020,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1919" t="n">
-        <v>11.4217004776001</v>
+        <v>11.4216995239258</v>
       </c>
       <c r="H1919" t="n">
         <v>35438</v>
@@ -56107,7 +56107,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1922" t="n">
-        <v>11.6969213485718</v>
+        <v>11.6969223022461</v>
   